--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-08-11.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-08-11.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="80" uniqueCount="80">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="116" uniqueCount="104">
   <si>
     <t>League</t>
   </si>
@@ -254,6 +254,78 @@
   </si>
   <si>
     <t>SnapshotTS</t>
+  </si>
+  <si>
+    <t>Brazilian Campeonato Women</t>
+  </si>
+  <si>
+    <t>Chilean Primera Division</t>
+  </si>
+  <si>
+    <t>Ecuadorian Serie A</t>
+  </si>
+  <si>
+    <t>Argentinian Primera Division</t>
+  </si>
+  <si>
+    <t>Colombian Primera A</t>
+  </si>
+  <si>
+    <t>Swedish Superettan</t>
+  </si>
+  <si>
+    <t>2026-08-11</t>
+  </si>
+  <si>
+    <t>00:00:00</t>
+  </si>
+  <si>
+    <t>00:15:00</t>
+  </si>
+  <si>
+    <t>01:05:00</t>
+  </si>
+  <si>
+    <t>17:00:00</t>
+  </si>
+  <si>
+    <t>America MG (W)</t>
+  </si>
+  <si>
+    <t>Audax Italiano</t>
+  </si>
+  <si>
+    <t>Deportivo Cuenca</t>
+  </si>
+  <si>
+    <t>Union Santa Fe</t>
+  </si>
+  <si>
+    <t>Junior FC Barranquilla</t>
+  </si>
+  <si>
+    <t>Helsingborgs</t>
+  </si>
+  <si>
+    <t>CR Flamengo (W)</t>
+  </si>
+  <si>
+    <t>Nublense</t>
+  </si>
+  <si>
+    <t>Manta FC</t>
+  </si>
+  <si>
+    <t>Central Cordoba (SdE)</t>
+  </si>
+  <si>
+    <t>Deportivo Pereira</t>
+  </si>
+  <si>
+    <t>Varnamo</t>
+  </si>
+  <si>
+    <t>2026-08-09 01:02:42</t>
   </si>
 </sst>
 </file>
@@ -585,7 +657,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:CB1"/>
+  <dimension ref="A1:CB7"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:80">
@@ -828,6 +900,1458 @@
       </c>
       <c r="CB1" t="s">
         <v>79</v>
+      </c>
+    </row>
+    <row r="2" spans="1:80">
+      <c r="A2" t="s">
+        <v>80</v>
+      </c>
+      <c r="B2" t="s">
+        <v>86</v>
+      </c>
+      <c r="C2" t="s">
+        <v>87</v>
+      </c>
+      <c r="D2" t="s">
+        <v>91</v>
+      </c>
+      <c r="E2" t="s">
+        <v>97</v>
+      </c>
+      <c r="F2">
+        <v>1.04</v>
+      </c>
+      <c r="G2">
+        <v>1000</v>
+      </c>
+      <c r="H2">
+        <v>1.04</v>
+      </c>
+      <c r="I2">
+        <v>1000</v>
+      </c>
+      <c r="J2">
+        <v>1.06</v>
+      </c>
+      <c r="K2">
+        <v>950</v>
+      </c>
+      <c r="L2">
+        <v>1.01</v>
+      </c>
+      <c r="M2">
+        <v>1.01</v>
+      </c>
+      <c r="N2">
+        <v>1.27</v>
+      </c>
+      <c r="O2">
+        <v>1.2</v>
+      </c>
+      <c r="P2">
+        <v>1.27</v>
+      </c>
+      <c r="Q2">
+        <v>1.19</v>
+      </c>
+      <c r="R2">
+        <v>1.18</v>
+      </c>
+      <c r="S2">
+        <v>1.2</v>
+      </c>
+      <c r="T2">
+        <v>1.01</v>
+      </c>
+      <c r="U2">
+        <v>1.01</v>
+      </c>
+      <c r="V2">
+        <v>1.02</v>
+      </c>
+      <c r="W2">
+        <v>1.02</v>
+      </c>
+      <c r="X2">
+        <v>1000</v>
+      </c>
+      <c r="Y2">
+        <v>1000</v>
+      </c>
+      <c r="Z2">
+        <v>1000</v>
+      </c>
+      <c r="AA2">
+        <v>1000</v>
+      </c>
+      <c r="AB2">
+        <v>1000</v>
+      </c>
+      <c r="AC2">
+        <v>1000</v>
+      </c>
+      <c r="AD2">
+        <v>1000</v>
+      </c>
+      <c r="AE2">
+        <v>1000</v>
+      </c>
+      <c r="AF2">
+        <v>1000</v>
+      </c>
+      <c r="AG2">
+        <v>1000</v>
+      </c>
+      <c r="AH2">
+        <v>1000</v>
+      </c>
+      <c r="AI2">
+        <v>1000</v>
+      </c>
+      <c r="AJ2">
+        <v>1000</v>
+      </c>
+      <c r="AK2">
+        <v>1000</v>
+      </c>
+      <c r="AL2">
+        <v>1000</v>
+      </c>
+      <c r="AM2">
+        <v>1000</v>
+      </c>
+      <c r="AN2">
+        <v>1000</v>
+      </c>
+      <c r="AO2">
+        <v>1000</v>
+      </c>
+      <c r="AP2">
+        <v>1.01</v>
+      </c>
+      <c r="AQ2">
+        <v>1.01</v>
+      </c>
+      <c r="AR2">
+        <v>1.01</v>
+      </c>
+      <c r="AS2">
+        <v>1.01</v>
+      </c>
+      <c r="AT2">
+        <v>1.01</v>
+      </c>
+      <c r="AU2">
+        <v>1.01</v>
+      </c>
+      <c r="AV2">
+        <v>1.01</v>
+      </c>
+      <c r="AW2">
+        <v>1.01</v>
+      </c>
+      <c r="AX2">
+        <v>1.01</v>
+      </c>
+      <c r="AY2">
+        <v>1.01</v>
+      </c>
+      <c r="AZ2">
+        <v>1.01</v>
+      </c>
+      <c r="BA2">
+        <v>1.01</v>
+      </c>
+      <c r="BB2">
+        <v>1.01</v>
+      </c>
+      <c r="BC2">
+        <v>1.01</v>
+      </c>
+      <c r="BD2">
+        <v>1.01</v>
+      </c>
+      <c r="BE2">
+        <v>1.01</v>
+      </c>
+      <c r="BF2">
+        <v>1.01</v>
+      </c>
+      <c r="BG2">
+        <v>1.01</v>
+      </c>
+      <c r="BH2">
+        <v>1000</v>
+      </c>
+      <c r="BI2">
+        <v>1.01</v>
+      </c>
+      <c r="BJ2">
+        <v>1000</v>
+      </c>
+      <c r="BK2">
+        <v>1.01</v>
+      </c>
+      <c r="BL2">
+        <v>1000</v>
+      </c>
+      <c r="BM2">
+        <v>1.01</v>
+      </c>
+      <c r="BN2">
+        <v>1000</v>
+      </c>
+      <c r="BO2">
+        <v>1.01</v>
+      </c>
+      <c r="BP2">
+        <v>1000</v>
+      </c>
+      <c r="BQ2">
+        <v>1.01</v>
+      </c>
+      <c r="BR2">
+        <v>1000</v>
+      </c>
+      <c r="BS2">
+        <v>1.01</v>
+      </c>
+      <c r="BT2">
+        <v>1000</v>
+      </c>
+      <c r="BU2">
+        <v>1.01</v>
+      </c>
+      <c r="BV2">
+        <v>1000</v>
+      </c>
+      <c r="BW2">
+        <v>1.01</v>
+      </c>
+      <c r="BX2">
+        <v>1000</v>
+      </c>
+      <c r="BY2">
+        <v>1.01</v>
+      </c>
+      <c r="BZ2">
+        <v>1000</v>
+      </c>
+      <c r="CA2">
+        <v>1.01</v>
+      </c>
+      <c r="CB2" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="3" spans="1:80">
+      <c r="A3" t="s">
+        <v>81</v>
+      </c>
+      <c r="B3" t="s">
+        <v>86</v>
+      </c>
+      <c r="C3" t="s">
+        <v>87</v>
+      </c>
+      <c r="D3" t="s">
+        <v>92</v>
+      </c>
+      <c r="E3" t="s">
+        <v>98</v>
+      </c>
+      <c r="F3">
+        <v>2.4</v>
+      </c>
+      <c r="G3">
+        <v>2.6</v>
+      </c>
+      <c r="H3">
+        <v>3.1</v>
+      </c>
+      <c r="I3">
+        <v>3.45</v>
+      </c>
+      <c r="J3">
+        <v>3.25</v>
+      </c>
+      <c r="K3">
+        <v>3.6</v>
+      </c>
+      <c r="L3">
+        <v>1.01</v>
+      </c>
+      <c r="M3">
+        <v>1.01</v>
+      </c>
+      <c r="N3">
+        <v>2.92</v>
+      </c>
+      <c r="O3">
+        <v>1.37</v>
+      </c>
+      <c r="P3">
+        <v>1.8</v>
+      </c>
+      <c r="Q3">
+        <v>2.06</v>
+      </c>
+      <c r="R3">
+        <v>1.26</v>
+      </c>
+      <c r="S3">
+        <v>3.35</v>
+      </c>
+      <c r="T3">
+        <v>1.01</v>
+      </c>
+      <c r="U3">
+        <v>1.85</v>
+      </c>
+      <c r="V3">
+        <v>1.4</v>
+      </c>
+      <c r="W3">
+        <v>1.62</v>
+      </c>
+      <c r="X3">
+        <v>17.5</v>
+      </c>
+      <c r="Y3">
+        <v>1000</v>
+      </c>
+      <c r="Z3">
+        <v>1000</v>
+      </c>
+      <c r="AA3">
+        <v>1000</v>
+      </c>
+      <c r="AB3">
+        <v>1000</v>
+      </c>
+      <c r="AC3">
+        <v>1000</v>
+      </c>
+      <c r="AD3">
+        <v>1000</v>
+      </c>
+      <c r="AE3">
+        <v>1000</v>
+      </c>
+      <c r="AF3">
+        <v>1000</v>
+      </c>
+      <c r="AG3">
+        <v>1000</v>
+      </c>
+      <c r="AH3">
+        <v>1000</v>
+      </c>
+      <c r="AI3">
+        <v>1000</v>
+      </c>
+      <c r="AJ3">
+        <v>1000</v>
+      </c>
+      <c r="AK3">
+        <v>1000</v>
+      </c>
+      <c r="AL3">
+        <v>1000</v>
+      </c>
+      <c r="AM3">
+        <v>1000</v>
+      </c>
+      <c r="AN3">
+        <v>1000</v>
+      </c>
+      <c r="AO3">
+        <v>1000</v>
+      </c>
+      <c r="AP3">
+        <v>1.01</v>
+      </c>
+      <c r="AQ3">
+        <v>1.06</v>
+      </c>
+      <c r="AR3">
+        <v>1.06</v>
+      </c>
+      <c r="AS3">
+        <v>1.06</v>
+      </c>
+      <c r="AT3">
+        <v>1.06</v>
+      </c>
+      <c r="AU3">
+        <v>1.06</v>
+      </c>
+      <c r="AV3">
+        <v>1.06</v>
+      </c>
+      <c r="AW3">
+        <v>1.06</v>
+      </c>
+      <c r="AX3">
+        <v>1.06</v>
+      </c>
+      <c r="AY3">
+        <v>1.06</v>
+      </c>
+      <c r="AZ3">
+        <v>1.06</v>
+      </c>
+      <c r="BA3">
+        <v>1.06</v>
+      </c>
+      <c r="BB3">
+        <v>1.06</v>
+      </c>
+      <c r="BC3">
+        <v>1.06</v>
+      </c>
+      <c r="BD3">
+        <v>1.06</v>
+      </c>
+      <c r="BE3">
+        <v>1.06</v>
+      </c>
+      <c r="BF3">
+        <v>1.06</v>
+      </c>
+      <c r="BG3">
+        <v>1.06</v>
+      </c>
+      <c r="BH3">
+        <v>3.9</v>
+      </c>
+      <c r="BI3">
+        <v>2.56</v>
+      </c>
+      <c r="BJ3">
+        <v>1000</v>
+      </c>
+      <c r="BK3">
+        <v>1.35</v>
+      </c>
+      <c r="BL3">
+        <v>1000</v>
+      </c>
+      <c r="BM3">
+        <v>1.35</v>
+      </c>
+      <c r="BN3">
+        <v>1000</v>
+      </c>
+      <c r="BO3">
+        <v>1.35</v>
+      </c>
+      <c r="BP3">
+        <v>1000</v>
+      </c>
+      <c r="BQ3">
+        <v>1.35</v>
+      </c>
+      <c r="BR3">
+        <v>1000</v>
+      </c>
+      <c r="BS3">
+        <v>1.35</v>
+      </c>
+      <c r="BT3">
+        <v>1000</v>
+      </c>
+      <c r="BU3">
+        <v>1.35</v>
+      </c>
+      <c r="BV3">
+        <v>1000</v>
+      </c>
+      <c r="BW3">
+        <v>1.35</v>
+      </c>
+      <c r="BX3">
+        <v>1000</v>
+      </c>
+      <c r="BY3">
+        <v>1.35</v>
+      </c>
+      <c r="BZ3">
+        <v>1000</v>
+      </c>
+      <c r="CA3">
+        <v>1.35</v>
+      </c>
+      <c r="CB3" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="4" spans="1:80">
+      <c r="A4" t="s">
+        <v>82</v>
+      </c>
+      <c r="B4" t="s">
+        <v>86</v>
+      </c>
+      <c r="C4" t="s">
+        <v>87</v>
+      </c>
+      <c r="D4" t="s">
+        <v>93</v>
+      </c>
+      <c r="E4" t="s">
+        <v>99</v>
+      </c>
+      <c r="F4">
+        <v>1.62</v>
+      </c>
+      <c r="G4">
+        <v>1.78</v>
+      </c>
+      <c r="H4">
+        <v>6.6</v>
+      </c>
+      <c r="I4">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="J4">
+        <v>3.5</v>
+      </c>
+      <c r="K4">
+        <v>4</v>
+      </c>
+      <c r="L4">
+        <v>1.01</v>
+      </c>
+      <c r="M4">
+        <v>1.09</v>
+      </c>
+      <c r="N4">
+        <v>2.28</v>
+      </c>
+      <c r="O4">
+        <v>1.49</v>
+      </c>
+      <c r="P4">
+        <v>1.48</v>
+      </c>
+      <c r="Q4">
+        <v>2.3</v>
+      </c>
+      <c r="R4">
+        <v>1.18</v>
+      </c>
+      <c r="S4">
+        <v>2.3</v>
+      </c>
+      <c r="T4">
+        <v>1.01</v>
+      </c>
+      <c r="U4">
+        <v>1.01</v>
+      </c>
+      <c r="V4">
+        <v>1.12</v>
+      </c>
+      <c r="W4">
+        <v>2.28</v>
+      </c>
+      <c r="X4">
+        <v>1000</v>
+      </c>
+      <c r="Y4">
+        <v>1000</v>
+      </c>
+      <c r="Z4">
+        <v>1000</v>
+      </c>
+      <c r="AA4">
+        <v>1000</v>
+      </c>
+      <c r="AB4">
+        <v>8</v>
+      </c>
+      <c r="AC4">
+        <v>12</v>
+      </c>
+      <c r="AD4">
+        <v>1000</v>
+      </c>
+      <c r="AE4">
+        <v>1000</v>
+      </c>
+      <c r="AF4">
+        <v>11.5</v>
+      </c>
+      <c r="AG4">
+        <v>15</v>
+      </c>
+      <c r="AH4">
+        <v>44</v>
+      </c>
+      <c r="AI4">
+        <v>1000</v>
+      </c>
+      <c r="AJ4">
+        <v>1000</v>
+      </c>
+      <c r="AK4">
+        <v>1000</v>
+      </c>
+      <c r="AL4">
+        <v>1000</v>
+      </c>
+      <c r="AM4">
+        <v>1000</v>
+      </c>
+      <c r="AN4">
+        <v>1000</v>
+      </c>
+      <c r="AO4">
+        <v>1000</v>
+      </c>
+      <c r="AP4">
+        <v>1.62</v>
+      </c>
+      <c r="AQ4">
+        <v>1.62</v>
+      </c>
+      <c r="AR4">
+        <v>1.62</v>
+      </c>
+      <c r="AS4">
+        <v>1.62</v>
+      </c>
+      <c r="AT4">
+        <v>4.1</v>
+      </c>
+      <c r="AU4">
+        <v>1.43</v>
+      </c>
+      <c r="AV4">
+        <v>1.62</v>
+      </c>
+      <c r="AW4">
+        <v>1.62</v>
+      </c>
+      <c r="AX4">
+        <v>5.6</v>
+      </c>
+      <c r="AY4">
+        <v>7</v>
+      </c>
+      <c r="AZ4">
+        <v>1.56</v>
+      </c>
+      <c r="BA4">
+        <v>1.62</v>
+      </c>
+      <c r="BB4">
+        <v>1.62</v>
+      </c>
+      <c r="BC4">
+        <v>1.62</v>
+      </c>
+      <c r="BD4">
+        <v>1.62</v>
+      </c>
+      <c r="BE4">
+        <v>1.62</v>
+      </c>
+      <c r="BF4">
+        <v>1.62</v>
+      </c>
+      <c r="BG4">
+        <v>1.62</v>
+      </c>
+      <c r="BH4">
+        <v>1000</v>
+      </c>
+      <c r="BI4">
+        <v>1.73</v>
+      </c>
+      <c r="BJ4">
+        <v>18</v>
+      </c>
+      <c r="BK4">
+        <v>1.58</v>
+      </c>
+      <c r="BL4">
+        <v>1000</v>
+      </c>
+      <c r="BM4">
+        <v>1.73</v>
+      </c>
+      <c r="BN4">
+        <v>5.1</v>
+      </c>
+      <c r="BO4">
+        <v>2.76</v>
+      </c>
+      <c r="BP4">
+        <v>17.5</v>
+      </c>
+      <c r="BQ4">
+        <v>1.57</v>
+      </c>
+      <c r="BR4">
+        <v>50</v>
+      </c>
+      <c r="BS4">
+        <v>1.67</v>
+      </c>
+      <c r="BT4">
+        <v>14.5</v>
+      </c>
+      <c r="BU4">
+        <v>1.54</v>
+      </c>
+      <c r="BV4">
+        <v>1000</v>
+      </c>
+      <c r="BW4">
+        <v>1.73</v>
+      </c>
+      <c r="BX4">
+        <v>1000</v>
+      </c>
+      <c r="BY4">
+        <v>1.73</v>
+      </c>
+      <c r="BZ4">
+        <v>46</v>
+      </c>
+      <c r="CA4">
+        <v>1.67</v>
+      </c>
+      <c r="CB4" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="5" spans="1:80">
+      <c r="A5" t="s">
+        <v>83</v>
+      </c>
+      <c r="B5" t="s">
+        <v>86</v>
+      </c>
+      <c r="C5" t="s">
+        <v>88</v>
+      </c>
+      <c r="D5" t="s">
+        <v>94</v>
+      </c>
+      <c r="E5" t="s">
+        <v>100</v>
+      </c>
+      <c r="F5">
+        <v>1.52</v>
+      </c>
+      <c r="G5">
+        <v>1.59</v>
+      </c>
+      <c r="H5">
+        <v>7.8</v>
+      </c>
+      <c r="I5">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="J5">
+        <v>4.1</v>
+      </c>
+      <c r="K5">
+        <v>4.4</v>
+      </c>
+      <c r="L5">
+        <v>1.01</v>
+      </c>
+      <c r="M5">
+        <v>1.08</v>
+      </c>
+      <c r="N5">
+        <v>3.35</v>
+      </c>
+      <c r="O5">
+        <v>1.37</v>
+      </c>
+      <c r="P5">
+        <v>1.8</v>
+      </c>
+      <c r="Q5">
+        <v>2.04</v>
+      </c>
+      <c r="R5">
+        <v>1.29</v>
+      </c>
+      <c r="S5">
+        <v>3.85</v>
+      </c>
+      <c r="T5">
+        <v>2.12</v>
+      </c>
+      <c r="U5">
+        <v>1.72</v>
+      </c>
+      <c r="V5">
+        <v>1.12</v>
+      </c>
+      <c r="W5">
+        <v>2.7</v>
+      </c>
+      <c r="X5">
+        <v>14</v>
+      </c>
+      <c r="Y5">
+        <v>23</v>
+      </c>
+      <c r="Z5">
+        <v>75</v>
+      </c>
+      <c r="AA5">
+        <v>350</v>
+      </c>
+      <c r="AB5">
+        <v>7.2</v>
+      </c>
+      <c r="AC5">
+        <v>10</v>
+      </c>
+      <c r="AD5">
+        <v>34</v>
+      </c>
+      <c r="AE5">
+        <v>180</v>
+      </c>
+      <c r="AF5">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AG5">
+        <v>11</v>
+      </c>
+      <c r="AH5">
+        <v>29</v>
+      </c>
+      <c r="AI5">
+        <v>160</v>
+      </c>
+      <c r="AJ5">
+        <v>15</v>
+      </c>
+      <c r="AK5">
+        <v>19.5</v>
+      </c>
+      <c r="AL5">
+        <v>48</v>
+      </c>
+      <c r="AM5">
+        <v>230</v>
+      </c>
+      <c r="AN5">
+        <v>11</v>
+      </c>
+      <c r="AO5">
+        <v>290</v>
+      </c>
+      <c r="AP5">
+        <v>11</v>
+      </c>
+      <c r="AQ5">
+        <v>18</v>
+      </c>
+      <c r="AR5">
+        <v>7.8</v>
+      </c>
+      <c r="AS5">
+        <v>8.6</v>
+      </c>
+      <c r="AT5">
+        <v>5.9</v>
+      </c>
+      <c r="AU5">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AV5">
+        <v>7</v>
+      </c>
+      <c r="AW5">
+        <v>8.4</v>
+      </c>
+      <c r="AX5">
+        <v>7</v>
+      </c>
+      <c r="AY5">
+        <v>9</v>
+      </c>
+      <c r="AZ5">
+        <v>6.8</v>
+      </c>
+      <c r="BA5">
+        <v>8.4</v>
+      </c>
+      <c r="BB5">
+        <v>12</v>
+      </c>
+      <c r="BC5">
+        <v>15.5</v>
+      </c>
+      <c r="BD5">
+        <v>7.4</v>
+      </c>
+      <c r="BE5">
+        <v>8.4</v>
+      </c>
+      <c r="BF5">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="BG5">
+        <v>8.6</v>
+      </c>
+      <c r="BH5">
+        <v>1000</v>
+      </c>
+      <c r="BI5">
+        <v>1.96</v>
+      </c>
+      <c r="BJ5">
+        <v>16</v>
+      </c>
+      <c r="BK5">
+        <v>1.75</v>
+      </c>
+      <c r="BL5">
+        <v>1000</v>
+      </c>
+      <c r="BM5">
+        <v>1.96</v>
+      </c>
+      <c r="BN5">
+        <v>4.8</v>
+      </c>
+      <c r="BO5">
+        <v>2.8</v>
+      </c>
+      <c r="BP5">
+        <v>13.5</v>
+      </c>
+      <c r="BQ5">
+        <v>1.71</v>
+      </c>
+      <c r="BR5">
+        <v>40</v>
+      </c>
+      <c r="BS5">
+        <v>1.87</v>
+      </c>
+      <c r="BT5">
+        <v>15</v>
+      </c>
+      <c r="BU5">
+        <v>1.73</v>
+      </c>
+      <c r="BV5">
+        <v>1000</v>
+      </c>
+      <c r="BW5">
+        <v>1.93</v>
+      </c>
+      <c r="BX5">
+        <v>1000</v>
+      </c>
+      <c r="BY5">
+        <v>1.93</v>
+      </c>
+      <c r="BZ5">
+        <v>30</v>
+      </c>
+      <c r="CA5">
+        <v>1.84</v>
+      </c>
+      <c r="CB5" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="6" spans="1:80">
+      <c r="A6" t="s">
+        <v>84</v>
+      </c>
+      <c r="B6" t="s">
+        <v>86</v>
+      </c>
+      <c r="C6" t="s">
+        <v>89</v>
+      </c>
+      <c r="D6" t="s">
+        <v>95</v>
+      </c>
+      <c r="E6" t="s">
+        <v>101</v>
+      </c>
+      <c r="F6">
+        <v>1.31</v>
+      </c>
+      <c r="G6">
+        <v>1.39</v>
+      </c>
+      <c r="H6">
+        <v>11.5</v>
+      </c>
+      <c r="I6">
+        <v>16</v>
+      </c>
+      <c r="J6">
+        <v>5.1</v>
+      </c>
+      <c r="K6">
+        <v>6.8</v>
+      </c>
+      <c r="L6">
+        <v>1.01</v>
+      </c>
+      <c r="M6">
+        <v>1.01</v>
+      </c>
+      <c r="N6">
+        <v>3.9</v>
+      </c>
+      <c r="O6">
+        <v>1.24</v>
+      </c>
+      <c r="P6">
+        <v>2.04</v>
+      </c>
+      <c r="Q6">
+        <v>1.73</v>
+      </c>
+      <c r="R6">
+        <v>1.38</v>
+      </c>
+      <c r="S6">
+        <v>2.8</v>
+      </c>
+      <c r="T6">
+        <v>1.01</v>
+      </c>
+      <c r="U6">
+        <v>1.01</v>
+      </c>
+      <c r="V6">
+        <v>1.06</v>
+      </c>
+      <c r="W6">
+        <v>3.55</v>
+      </c>
+      <c r="X6">
+        <v>1000</v>
+      </c>
+      <c r="Y6">
+        <v>1000</v>
+      </c>
+      <c r="Z6">
+        <v>1000</v>
+      </c>
+      <c r="AA6">
+        <v>1000</v>
+      </c>
+      <c r="AB6">
+        <v>1000</v>
+      </c>
+      <c r="AC6">
+        <v>1000</v>
+      </c>
+      <c r="AD6">
+        <v>1000</v>
+      </c>
+      <c r="AE6">
+        <v>1000</v>
+      </c>
+      <c r="AF6">
+        <v>1000</v>
+      </c>
+      <c r="AG6">
+        <v>1000</v>
+      </c>
+      <c r="AH6">
+        <v>1000</v>
+      </c>
+      <c r="AI6">
+        <v>1000</v>
+      </c>
+      <c r="AJ6">
+        <v>1000</v>
+      </c>
+      <c r="AK6">
+        <v>1000</v>
+      </c>
+      <c r="AL6">
+        <v>1000</v>
+      </c>
+      <c r="AM6">
+        <v>1000</v>
+      </c>
+      <c r="AN6">
+        <v>1000</v>
+      </c>
+      <c r="AO6">
+        <v>1000</v>
+      </c>
+      <c r="AP6">
+        <v>1.01</v>
+      </c>
+      <c r="AQ6">
+        <v>1.01</v>
+      </c>
+      <c r="AR6">
+        <v>1.01</v>
+      </c>
+      <c r="AS6">
+        <v>1.01</v>
+      </c>
+      <c r="AT6">
+        <v>1.01</v>
+      </c>
+      <c r="AU6">
+        <v>1.01</v>
+      </c>
+      <c r="AV6">
+        <v>1.01</v>
+      </c>
+      <c r="AW6">
+        <v>1.01</v>
+      </c>
+      <c r="AX6">
+        <v>1.01</v>
+      </c>
+      <c r="AY6">
+        <v>1.01</v>
+      </c>
+      <c r="AZ6">
+        <v>1.01</v>
+      </c>
+      <c r="BA6">
+        <v>1.01</v>
+      </c>
+      <c r="BB6">
+        <v>1.01</v>
+      </c>
+      <c r="BC6">
+        <v>1.01</v>
+      </c>
+      <c r="BD6">
+        <v>1.01</v>
+      </c>
+      <c r="BE6">
+        <v>1.01</v>
+      </c>
+      <c r="BF6">
+        <v>1.01</v>
+      </c>
+      <c r="BG6">
+        <v>1.01</v>
+      </c>
+      <c r="BH6">
+        <v>1000</v>
+      </c>
+      <c r="BI6">
+        <v>1.01</v>
+      </c>
+      <c r="BJ6">
+        <v>1000</v>
+      </c>
+      <c r="BK6">
+        <v>1.01</v>
+      </c>
+      <c r="BL6">
+        <v>1000</v>
+      </c>
+      <c r="BM6">
+        <v>1.01</v>
+      </c>
+      <c r="BN6">
+        <v>1000</v>
+      </c>
+      <c r="BO6">
+        <v>1.01</v>
+      </c>
+      <c r="BP6">
+        <v>1000</v>
+      </c>
+      <c r="BQ6">
+        <v>1.01</v>
+      </c>
+      <c r="BR6">
+        <v>1000</v>
+      </c>
+      <c r="BS6">
+        <v>1.01</v>
+      </c>
+      <c r="BT6">
+        <v>1000</v>
+      </c>
+      <c r="BU6">
+        <v>1.01</v>
+      </c>
+      <c r="BV6">
+        <v>1000</v>
+      </c>
+      <c r="BW6">
+        <v>1.01</v>
+      </c>
+      <c r="BX6">
+        <v>1000</v>
+      </c>
+      <c r="BY6">
+        <v>1.01</v>
+      </c>
+      <c r="BZ6">
+        <v>1000</v>
+      </c>
+      <c r="CA6">
+        <v>1.01</v>
+      </c>
+      <c r="CB6" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="7" spans="1:80">
+      <c r="A7" t="s">
+        <v>85</v>
+      </c>
+      <c r="B7" t="s">
+        <v>86</v>
+      </c>
+      <c r="C7" t="s">
+        <v>90</v>
+      </c>
+      <c r="D7" t="s">
+        <v>96</v>
+      </c>
+      <c r="E7" t="s">
+        <v>102</v>
+      </c>
+      <c r="F7">
+        <v>2.08</v>
+      </c>
+      <c r="G7">
+        <v>2.26</v>
+      </c>
+      <c r="H7">
+        <v>3.25</v>
+      </c>
+      <c r="I7">
+        <v>3.65</v>
+      </c>
+      <c r="J7">
+        <v>3.75</v>
+      </c>
+      <c r="K7">
+        <v>4.3</v>
+      </c>
+      <c r="L7">
+        <v>0</v>
+      </c>
+      <c r="M7">
+        <v>0</v>
+      </c>
+      <c r="N7">
+        <v>0</v>
+      </c>
+      <c r="O7">
+        <v>0</v>
+      </c>
+      <c r="P7">
+        <v>2.26</v>
+      </c>
+      <c r="Q7">
+        <v>1.61</v>
+      </c>
+      <c r="R7">
+        <v>0</v>
+      </c>
+      <c r="S7">
+        <v>0</v>
+      </c>
+      <c r="T7">
+        <v>0</v>
+      </c>
+      <c r="U7">
+        <v>0</v>
+      </c>
+      <c r="V7">
+        <v>0</v>
+      </c>
+      <c r="W7">
+        <v>0</v>
+      </c>
+      <c r="X7">
+        <v>0</v>
+      </c>
+      <c r="Y7">
+        <v>0</v>
+      </c>
+      <c r="Z7">
+        <v>0</v>
+      </c>
+      <c r="AA7">
+        <v>0</v>
+      </c>
+      <c r="AB7">
+        <v>0</v>
+      </c>
+      <c r="AC7">
+        <v>0</v>
+      </c>
+      <c r="AD7">
+        <v>0</v>
+      </c>
+      <c r="AE7">
+        <v>0</v>
+      </c>
+      <c r="AF7">
+        <v>0</v>
+      </c>
+      <c r="AG7">
+        <v>0</v>
+      </c>
+      <c r="AH7">
+        <v>0</v>
+      </c>
+      <c r="AI7">
+        <v>0</v>
+      </c>
+      <c r="AJ7">
+        <v>0</v>
+      </c>
+      <c r="AK7">
+        <v>0</v>
+      </c>
+      <c r="AL7">
+        <v>0</v>
+      </c>
+      <c r="AM7">
+        <v>0</v>
+      </c>
+      <c r="AN7">
+        <v>0</v>
+      </c>
+      <c r="AO7">
+        <v>0</v>
+      </c>
+      <c r="AP7">
+        <v>0</v>
+      </c>
+      <c r="AQ7">
+        <v>0</v>
+      </c>
+      <c r="AR7">
+        <v>0</v>
+      </c>
+      <c r="AS7">
+        <v>0</v>
+      </c>
+      <c r="AT7">
+        <v>0</v>
+      </c>
+      <c r="AU7">
+        <v>0</v>
+      </c>
+      <c r="AV7">
+        <v>0</v>
+      </c>
+      <c r="AW7">
+        <v>0</v>
+      </c>
+      <c r="AX7">
+        <v>0</v>
+      </c>
+      <c r="AY7">
+        <v>0</v>
+      </c>
+      <c r="AZ7">
+        <v>0</v>
+      </c>
+      <c r="BA7">
+        <v>0</v>
+      </c>
+      <c r="BB7">
+        <v>0</v>
+      </c>
+      <c r="BC7">
+        <v>0</v>
+      </c>
+      <c r="BD7">
+        <v>0</v>
+      </c>
+      <c r="BE7">
+        <v>0</v>
+      </c>
+      <c r="BF7">
+        <v>0</v>
+      </c>
+      <c r="BG7">
+        <v>0</v>
+      </c>
+      <c r="BH7">
+        <v>0</v>
+      </c>
+      <c r="BI7">
+        <v>0</v>
+      </c>
+      <c r="BJ7">
+        <v>0</v>
+      </c>
+      <c r="BK7">
+        <v>0</v>
+      </c>
+      <c r="BL7">
+        <v>0</v>
+      </c>
+      <c r="BM7">
+        <v>0</v>
+      </c>
+      <c r="BN7">
+        <v>0</v>
+      </c>
+      <c r="BO7">
+        <v>0</v>
+      </c>
+      <c r="BP7">
+        <v>0</v>
+      </c>
+      <c r="BQ7">
+        <v>0</v>
+      </c>
+      <c r="BR7">
+        <v>0</v>
+      </c>
+      <c r="BS7">
+        <v>0</v>
+      </c>
+      <c r="BT7">
+        <v>0</v>
+      </c>
+      <c r="BU7">
+        <v>0</v>
+      </c>
+      <c r="BV7">
+        <v>0</v>
+      </c>
+      <c r="BW7">
+        <v>0</v>
+      </c>
+      <c r="BX7">
+        <v>0</v>
+      </c>
+      <c r="BY7">
+        <v>0</v>
+      </c>
+      <c r="BZ7">
+        <v>0</v>
+      </c>
+      <c r="CA7">
+        <v>0</v>
+      </c>
+      <c r="CB7" t="s">
+        <v>103</v>
       </c>
     </row>
   </sheetData>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-08-11.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-08-11.xlsx
@@ -325,7 +325,7 @@
     <t>Varnamo</t>
   </si>
   <si>
-    <t>2026-08-09 01:02:42</t>
+    <t>2026-08-09 03:18:47</t>
   </si>
 </sst>
 </file>
@@ -919,19 +919,19 @@
         <v>97</v>
       </c>
       <c r="F2">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="G2">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="H2">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="I2">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="J2">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="K2">
         <v>950</v>
@@ -946,7 +946,7 @@
         <v>1.27</v>
       </c>
       <c r="O2">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="P2">
         <v>1.27</v>
@@ -958,7 +958,7 @@
         <v>1.18</v>
       </c>
       <c r="S2">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="T2">
         <v>1.01</v>
@@ -1027,52 +1027,52 @@
         <v>1000</v>
       </c>
       <c r="AP2">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AQ2">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AR2">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AS2">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AT2">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AU2">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AV2">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AW2">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AX2">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AY2">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AZ2">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BA2">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BB2">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BC2">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BD2">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BE2">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BF2">
         <v>1.01</v>
@@ -1161,22 +1161,22 @@
         <v>98</v>
       </c>
       <c r="F3">
-        <v>2.4</v>
+        <v>1.04</v>
       </c>
       <c r="G3">
-        <v>2.6</v>
+        <v>110</v>
       </c>
       <c r="H3">
-        <v>3.1</v>
+        <v>1.04</v>
       </c>
       <c r="I3">
-        <v>3.45</v>
+        <v>110</v>
       </c>
       <c r="J3">
-        <v>3.25</v>
+        <v>1.03</v>
       </c>
       <c r="K3">
-        <v>3.6</v>
+        <v>950</v>
       </c>
       <c r="L3">
         <v>1.01</v>
@@ -1185,37 +1185,37 @@
         <v>1.01</v>
       </c>
       <c r="N3">
-        <v>2.92</v>
+        <v>1.27</v>
       </c>
       <c r="O3">
         <v>1.37</v>
       </c>
       <c r="P3">
-        <v>1.8</v>
+        <v>1.27</v>
       </c>
       <c r="Q3">
-        <v>2.06</v>
+        <v>1.37</v>
       </c>
       <c r="R3">
-        <v>1.26</v>
+        <v>1.18</v>
       </c>
       <c r="S3">
-        <v>3.35</v>
+        <v>1.37</v>
       </c>
       <c r="T3">
         <v>1.01</v>
       </c>
       <c r="U3">
-        <v>1.85</v>
+        <v>1.01</v>
       </c>
       <c r="V3">
-        <v>1.4</v>
+        <v>1.01</v>
       </c>
       <c r="W3">
-        <v>1.62</v>
+        <v>1.01</v>
       </c>
       <c r="X3">
-        <v>17.5</v>
+        <v>1000</v>
       </c>
       <c r="Y3">
         <v>1000</v>
@@ -1272,115 +1272,115 @@
         <v>1.01</v>
       </c>
       <c r="AQ3">
-        <v>1.06</v>
+        <v>1.01</v>
       </c>
       <c r="AR3">
-        <v>1.06</v>
+        <v>1.01</v>
       </c>
       <c r="AS3">
-        <v>1.06</v>
+        <v>1.01</v>
       </c>
       <c r="AT3">
-        <v>1.06</v>
+        <v>1.01</v>
       </c>
       <c r="AU3">
-        <v>1.06</v>
+        <v>1.01</v>
       </c>
       <c r="AV3">
-        <v>1.06</v>
+        <v>1.01</v>
       </c>
       <c r="AW3">
-        <v>1.06</v>
+        <v>1.01</v>
       </c>
       <c r="AX3">
-        <v>1.06</v>
+        <v>1.01</v>
       </c>
       <c r="AY3">
-        <v>1.06</v>
+        <v>1.01</v>
       </c>
       <c r="AZ3">
-        <v>1.06</v>
+        <v>1.01</v>
       </c>
       <c r="BA3">
-        <v>1.06</v>
+        <v>1.01</v>
       </c>
       <c r="BB3">
-        <v>1.06</v>
+        <v>1.01</v>
       </c>
       <c r="BC3">
-        <v>1.06</v>
+        <v>1.01</v>
       </c>
       <c r="BD3">
-        <v>1.06</v>
+        <v>1.01</v>
       </c>
       <c r="BE3">
-        <v>1.06</v>
+        <v>1.01</v>
       </c>
       <c r="BF3">
-        <v>1.06</v>
+        <v>1.01</v>
       </c>
       <c r="BG3">
-        <v>1.06</v>
+        <v>1.01</v>
       </c>
       <c r="BH3">
-        <v>3.9</v>
+        <v>1000</v>
       </c>
       <c r="BI3">
-        <v>2.56</v>
+        <v>1.01</v>
       </c>
       <c r="BJ3">
         <v>1000</v>
       </c>
       <c r="BK3">
-        <v>1.35</v>
+        <v>1.01</v>
       </c>
       <c r="BL3">
         <v>1000</v>
       </c>
       <c r="BM3">
-        <v>1.35</v>
+        <v>1.01</v>
       </c>
       <c r="BN3">
         <v>1000</v>
       </c>
       <c r="BO3">
-        <v>1.35</v>
+        <v>1.01</v>
       </c>
       <c r="BP3">
         <v>1000</v>
       </c>
       <c r="BQ3">
-        <v>1.35</v>
+        <v>1.01</v>
       </c>
       <c r="BR3">
         <v>1000</v>
       </c>
       <c r="BS3">
-        <v>1.35</v>
+        <v>1.01</v>
       </c>
       <c r="BT3">
         <v>1000</v>
       </c>
       <c r="BU3">
-        <v>1.35</v>
+        <v>1.01</v>
       </c>
       <c r="BV3">
         <v>1000</v>
       </c>
       <c r="BW3">
-        <v>1.35</v>
+        <v>1.01</v>
       </c>
       <c r="BX3">
         <v>1000</v>
       </c>
       <c r="BY3">
-        <v>1.35</v>
+        <v>1.01</v>
       </c>
       <c r="BZ3">
         <v>1000</v>
       </c>
       <c r="CA3">
-        <v>1.35</v>
+        <v>1.01</v>
       </c>
       <c r="CB3" t="s">
         <v>103</v>
@@ -1403,22 +1403,22 @@
         <v>99</v>
       </c>
       <c r="F4">
-        <v>1.62</v>
+        <v>1.14</v>
       </c>
       <c r="G4">
-        <v>1.78</v>
+        <v>110</v>
       </c>
       <c r="H4">
-        <v>6.6</v>
+        <v>1.06</v>
       </c>
       <c r="I4">
-        <v>8.800000000000001</v>
+        <v>110</v>
       </c>
       <c r="J4">
-        <v>3.5</v>
+        <v>1.03</v>
       </c>
       <c r="K4">
-        <v>4</v>
+        <v>950</v>
       </c>
       <c r="L4">
         <v>1.01</v>
@@ -1427,22 +1427,22 @@
         <v>1.09</v>
       </c>
       <c r="N4">
-        <v>2.28</v>
+        <v>1.24</v>
       </c>
       <c r="O4">
         <v>1.49</v>
       </c>
       <c r="P4">
-        <v>1.48</v>
+        <v>1.25</v>
       </c>
       <c r="Q4">
-        <v>2.3</v>
+        <v>1.5</v>
       </c>
       <c r="R4">
         <v>1.18</v>
       </c>
       <c r="S4">
-        <v>2.3</v>
+        <v>1.02</v>
       </c>
       <c r="T4">
         <v>1.01</v>
@@ -1451,10 +1451,10 @@
         <v>1.01</v>
       </c>
       <c r="V4">
-        <v>1.12</v>
+        <v>1.01</v>
       </c>
       <c r="W4">
-        <v>2.28</v>
+        <v>1.01</v>
       </c>
       <c r="X4">
         <v>1000</v>
@@ -1469,10 +1469,10 @@
         <v>1000</v>
       </c>
       <c r="AB4">
-        <v>8</v>
+        <v>1000</v>
       </c>
       <c r="AC4">
-        <v>12</v>
+        <v>1000</v>
       </c>
       <c r="AD4">
         <v>1000</v>
@@ -1481,13 +1481,13 @@
         <v>1000</v>
       </c>
       <c r="AF4">
-        <v>11.5</v>
+        <v>1000</v>
       </c>
       <c r="AG4">
-        <v>15</v>
+        <v>1000</v>
       </c>
       <c r="AH4">
-        <v>44</v>
+        <v>1000</v>
       </c>
       <c r="AI4">
         <v>1000</v>
@@ -1511,118 +1511,118 @@
         <v>1000</v>
       </c>
       <c r="AP4">
-        <v>1.62</v>
+        <v>1.01</v>
       </c>
       <c r="AQ4">
-        <v>1.62</v>
+        <v>1.01</v>
       </c>
       <c r="AR4">
-        <v>1.62</v>
+        <v>1.01</v>
       </c>
       <c r="AS4">
-        <v>1.62</v>
+        <v>1.01</v>
       </c>
       <c r="AT4">
-        <v>4.1</v>
+        <v>1.01</v>
       </c>
       <c r="AU4">
-        <v>1.43</v>
+        <v>1.01</v>
       </c>
       <c r="AV4">
-        <v>1.62</v>
+        <v>1.01</v>
       </c>
       <c r="AW4">
-        <v>1.62</v>
+        <v>1.01</v>
       </c>
       <c r="AX4">
-        <v>5.6</v>
+        <v>1.01</v>
       </c>
       <c r="AY4">
-        <v>7</v>
+        <v>1.01</v>
       </c>
       <c r="AZ4">
-        <v>1.56</v>
+        <v>1.01</v>
       </c>
       <c r="BA4">
-        <v>1.62</v>
+        <v>1.01</v>
       </c>
       <c r="BB4">
-        <v>1.62</v>
+        <v>1.01</v>
       </c>
       <c r="BC4">
-        <v>1.62</v>
+        <v>1.01</v>
       </c>
       <c r="BD4">
-        <v>1.62</v>
+        <v>1.01</v>
       </c>
       <c r="BE4">
-        <v>1.62</v>
+        <v>1.01</v>
       </c>
       <c r="BF4">
-        <v>1.62</v>
+        <v>1.01</v>
       </c>
       <c r="BG4">
-        <v>1.62</v>
+        <v>1.01</v>
       </c>
       <c r="BH4">
         <v>1000</v>
       </c>
       <c r="BI4">
-        <v>1.73</v>
+        <v>1.01</v>
       </c>
       <c r="BJ4">
-        <v>18</v>
+        <v>1000</v>
       </c>
       <c r="BK4">
-        <v>1.58</v>
+        <v>1.01</v>
       </c>
       <c r="BL4">
         <v>1000</v>
       </c>
       <c r="BM4">
-        <v>1.73</v>
+        <v>1.01</v>
       </c>
       <c r="BN4">
-        <v>5.1</v>
+        <v>1000</v>
       </c>
       <c r="BO4">
-        <v>2.76</v>
+        <v>1.01</v>
       </c>
       <c r="BP4">
-        <v>17.5</v>
+        <v>1000</v>
       </c>
       <c r="BQ4">
-        <v>1.57</v>
+        <v>1.01</v>
       </c>
       <c r="BR4">
-        <v>50</v>
+        <v>1000</v>
       </c>
       <c r="BS4">
-        <v>1.67</v>
+        <v>1.01</v>
       </c>
       <c r="BT4">
-        <v>14.5</v>
+        <v>1000</v>
       </c>
       <c r="BU4">
-        <v>1.54</v>
+        <v>1.01</v>
       </c>
       <c r="BV4">
         <v>1000</v>
       </c>
       <c r="BW4">
-        <v>1.73</v>
+        <v>1.01</v>
       </c>
       <c r="BX4">
         <v>1000</v>
       </c>
       <c r="BY4">
-        <v>1.73</v>
+        <v>1.01</v>
       </c>
       <c r="BZ4">
-        <v>46</v>
+        <v>1000</v>
       </c>
       <c r="CA4">
-        <v>1.67</v>
+        <v>1.01</v>
       </c>
       <c r="CB4" t="s">
         <v>103</v>
@@ -1645,226 +1645,226 @@
         <v>100</v>
       </c>
       <c r="F5">
-        <v>1.52</v>
+        <v>1.04</v>
       </c>
       <c r="G5">
-        <v>1.59</v>
+        <v>110</v>
       </c>
       <c r="H5">
-        <v>7.8</v>
+        <v>1.04</v>
       </c>
       <c r="I5">
-        <v>9.199999999999999</v>
+        <v>110</v>
       </c>
       <c r="J5">
-        <v>4.1</v>
+        <v>1.03</v>
       </c>
       <c r="K5">
-        <v>4.4</v>
+        <v>950</v>
       </c>
       <c r="L5">
         <v>1.01</v>
       </c>
       <c r="M5">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="N5">
-        <v>3.35</v>
+        <v>1.01</v>
       </c>
       <c r="O5">
-        <v>1.37</v>
+        <v>1.35</v>
       </c>
       <c r="P5">
-        <v>1.8</v>
+        <v>1.25</v>
       </c>
       <c r="Q5">
-        <v>2.04</v>
+        <v>1.46</v>
       </c>
       <c r="R5">
-        <v>1.29</v>
+        <v>1.15</v>
       </c>
       <c r="S5">
-        <v>3.85</v>
+        <v>1.01</v>
       </c>
       <c r="T5">
-        <v>2.12</v>
+        <v>1.01</v>
       </c>
       <c r="U5">
-        <v>1.72</v>
+        <v>1.01</v>
       </c>
       <c r="V5">
-        <v>1.12</v>
+        <v>1.01</v>
       </c>
       <c r="W5">
-        <v>2.7</v>
+        <v>1.01</v>
       </c>
       <c r="X5">
-        <v>14</v>
+        <v>1000</v>
       </c>
       <c r="Y5">
-        <v>23</v>
+        <v>1000</v>
       </c>
       <c r="Z5">
-        <v>75</v>
+        <v>1000</v>
       </c>
       <c r="AA5">
-        <v>350</v>
+        <v>1000</v>
       </c>
       <c r="AB5">
-        <v>7.2</v>
+        <v>1000</v>
       </c>
       <c r="AC5">
-        <v>10</v>
+        <v>1000</v>
       </c>
       <c r="AD5">
-        <v>34</v>
+        <v>1000</v>
       </c>
       <c r="AE5">
-        <v>180</v>
+        <v>1000</v>
       </c>
       <c r="AF5">
-        <v>8.800000000000001</v>
+        <v>1000</v>
       </c>
       <c r="AG5">
-        <v>11</v>
+        <v>1000</v>
       </c>
       <c r="AH5">
-        <v>29</v>
+        <v>1000</v>
       </c>
       <c r="AI5">
-        <v>160</v>
+        <v>1000</v>
       </c>
       <c r="AJ5">
-        <v>15</v>
+        <v>1000</v>
       </c>
       <c r="AK5">
-        <v>19.5</v>
+        <v>1000</v>
       </c>
       <c r="AL5">
-        <v>48</v>
+        <v>1000</v>
       </c>
       <c r="AM5">
-        <v>230</v>
+        <v>1000</v>
       </c>
       <c r="AN5">
-        <v>11</v>
+        <v>1000</v>
       </c>
       <c r="AO5">
-        <v>290</v>
+        <v>1000</v>
       </c>
       <c r="AP5">
-        <v>11</v>
+        <v>1.01</v>
       </c>
       <c r="AQ5">
-        <v>18</v>
+        <v>1.01</v>
       </c>
       <c r="AR5">
-        <v>7.8</v>
+        <v>1.01</v>
       </c>
       <c r="AS5">
-        <v>8.6</v>
+        <v>1.01</v>
       </c>
       <c r="AT5">
-        <v>5.9</v>
+        <v>1.01</v>
       </c>
       <c r="AU5">
-        <v>8.199999999999999</v>
+        <v>1.01</v>
       </c>
       <c r="AV5">
-        <v>7</v>
+        <v>1.01</v>
       </c>
       <c r="AW5">
-        <v>8.4</v>
+        <v>1.01</v>
       </c>
       <c r="AX5">
-        <v>7</v>
+        <v>1.01</v>
       </c>
       <c r="AY5">
-        <v>9</v>
+        <v>1.01</v>
       </c>
       <c r="AZ5">
-        <v>6.8</v>
+        <v>1.01</v>
       </c>
       <c r="BA5">
-        <v>8.4</v>
+        <v>1.01</v>
       </c>
       <c r="BB5">
-        <v>12</v>
+        <v>1.01</v>
       </c>
       <c r="BC5">
-        <v>15.5</v>
+        <v>1.01</v>
       </c>
       <c r="BD5">
-        <v>7.4</v>
+        <v>1.01</v>
       </c>
       <c r="BE5">
-        <v>8.4</v>
+        <v>1.01</v>
       </c>
       <c r="BF5">
-        <v>8.800000000000001</v>
+        <v>1.01</v>
       </c>
       <c r="BG5">
-        <v>8.6</v>
+        <v>1.01</v>
       </c>
       <c r="BH5">
         <v>1000</v>
       </c>
       <c r="BI5">
-        <v>1.96</v>
+        <v>1.01</v>
       </c>
       <c r="BJ5">
-        <v>16</v>
+        <v>1000</v>
       </c>
       <c r="BK5">
-        <v>1.75</v>
+        <v>1.01</v>
       </c>
       <c r="BL5">
         <v>1000</v>
       </c>
       <c r="BM5">
-        <v>1.96</v>
+        <v>1.01</v>
       </c>
       <c r="BN5">
-        <v>4.8</v>
+        <v>1000</v>
       </c>
       <c r="BO5">
-        <v>2.8</v>
+        <v>1.01</v>
       </c>
       <c r="BP5">
-        <v>13.5</v>
+        <v>1000</v>
       </c>
       <c r="BQ5">
-        <v>1.71</v>
+        <v>1.01</v>
       </c>
       <c r="BR5">
-        <v>40</v>
+        <v>1000</v>
       </c>
       <c r="BS5">
-        <v>1.87</v>
+        <v>1.01</v>
       </c>
       <c r="BT5">
-        <v>15</v>
+        <v>1000</v>
       </c>
       <c r="BU5">
-        <v>1.73</v>
+        <v>1.01</v>
       </c>
       <c r="BV5">
         <v>1000</v>
       </c>
       <c r="BW5">
-        <v>1.93</v>
+        <v>1.01</v>
       </c>
       <c r="BX5">
         <v>1000</v>
       </c>
       <c r="BY5">
-        <v>1.93</v>
+        <v>1.01</v>
       </c>
       <c r="BZ5">
-        <v>30</v>
+        <v>1000</v>
       </c>
       <c r="CA5">
-        <v>1.84</v>
+        <v>1.01</v>
       </c>
       <c r="CB5" t="s">
         <v>103</v>
@@ -1887,22 +1887,22 @@
         <v>101</v>
       </c>
       <c r="F6">
-        <v>1.31</v>
+        <v>1.04</v>
       </c>
       <c r="G6">
-        <v>1.39</v>
+        <v>1.45</v>
       </c>
       <c r="H6">
-        <v>11.5</v>
+        <v>1.04</v>
       </c>
       <c r="I6">
-        <v>16</v>
+        <v>1000</v>
       </c>
       <c r="J6">
-        <v>5.1</v>
+        <v>1.03</v>
       </c>
       <c r="K6">
-        <v>6.8</v>
+        <v>950</v>
       </c>
       <c r="L6">
         <v>1.01</v>
@@ -1911,22 +1911,22 @@
         <v>1.01</v>
       </c>
       <c r="N6">
-        <v>3.9</v>
+        <v>1.25</v>
       </c>
       <c r="O6">
         <v>1.24</v>
       </c>
       <c r="P6">
-        <v>2.04</v>
+        <v>1.25</v>
       </c>
       <c r="Q6">
-        <v>1.73</v>
+        <v>1.24</v>
       </c>
       <c r="R6">
-        <v>1.38</v>
+        <v>1.15</v>
       </c>
       <c r="S6">
-        <v>2.8</v>
+        <v>1.24</v>
       </c>
       <c r="T6">
         <v>1.01</v>
@@ -1935,10 +1935,10 @@
         <v>1.01</v>
       </c>
       <c r="V6">
-        <v>1.06</v>
+        <v>1.01</v>
       </c>
       <c r="W6">
-        <v>3.55</v>
+        <v>1.01</v>
       </c>
       <c r="X6">
         <v>1000</v>
@@ -1995,49 +1995,49 @@
         <v>1000</v>
       </c>
       <c r="AP6">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AQ6">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AR6">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AS6">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AT6">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AU6">
         <v>1.01</v>
       </c>
       <c r="AV6">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AW6">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AX6">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AY6">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AZ6">
         <v>1.01</v>
       </c>
       <c r="BA6">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BB6">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BC6">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BD6">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BE6">
         <v>1.01</v>
@@ -2129,22 +2129,22 @@
         <v>102</v>
       </c>
       <c r="F7">
-        <v>2.08</v>
+        <v>1.04</v>
       </c>
       <c r="G7">
-        <v>2.26</v>
+        <v>1000</v>
       </c>
       <c r="H7">
-        <v>3.25</v>
+        <v>1.04</v>
       </c>
       <c r="I7">
-        <v>3.65</v>
+        <v>1000</v>
       </c>
       <c r="J7">
-        <v>3.75</v>
+        <v>1.02</v>
       </c>
       <c r="K7">
-        <v>4.3</v>
+        <v>950</v>
       </c>
       <c r="L7">
         <v>0</v>
@@ -2159,10 +2159,10 @@
         <v>0</v>
       </c>
       <c r="P7">
-        <v>2.26</v>
+        <v>1.24</v>
       </c>
       <c r="Q7">
-        <v>1.61</v>
+        <v>1.01</v>
       </c>
       <c r="R7">
         <v>0</v>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-08-11.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-08-11.xlsx
@@ -325,7 +325,7 @@
     <t>Varnamo</t>
   </si>
   <si>
-    <t>2026-08-09 03:18:47</t>
+    <t>2026-08-09 05:34:30</t>
   </si>
 </sst>
 </file>
@@ -919,19 +919,19 @@
         <v>97</v>
       </c>
       <c r="F2">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="G2">
         <v>110</v>
       </c>
       <c r="H2">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="I2">
         <v>110</v>
       </c>
       <c r="J2">
-        <v>1.08</v>
+        <v>1.06</v>
       </c>
       <c r="K2">
         <v>950</v>
@@ -943,22 +943,22 @@
         <v>1.01</v>
       </c>
       <c r="N2">
-        <v>1.27</v>
+        <v>1.29</v>
       </c>
       <c r="O2">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="P2">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="Q2">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="R2">
         <v>1.18</v>
       </c>
       <c r="S2">
-        <v>1.21</v>
+        <v>1.18</v>
       </c>
       <c r="T2">
         <v>1.01</v>
@@ -1161,166 +1161,166 @@
         <v>98</v>
       </c>
       <c r="F3">
-        <v>1.04</v>
+        <v>2.4</v>
       </c>
       <c r="G3">
-        <v>110</v>
+        <v>2.58</v>
       </c>
       <c r="H3">
-        <v>1.04</v>
+        <v>3.15</v>
       </c>
       <c r="I3">
-        <v>110</v>
+        <v>3.45</v>
       </c>
       <c r="J3">
-        <v>1.03</v>
+        <v>3.1</v>
       </c>
       <c r="K3">
-        <v>950</v>
+        <v>3.8</v>
       </c>
       <c r="L3">
-        <v>1.01</v>
+        <v>1.42</v>
       </c>
       <c r="M3">
-        <v>1.01</v>
+        <v>1.08</v>
       </c>
       <c r="N3">
-        <v>1.27</v>
+        <v>3.35</v>
       </c>
       <c r="O3">
         <v>1.37</v>
       </c>
       <c r="P3">
-        <v>1.27</v>
+        <v>1.8</v>
       </c>
       <c r="Q3">
-        <v>1.37</v>
+        <v>2.08</v>
       </c>
       <c r="R3">
-        <v>1.18</v>
+        <v>1.31</v>
       </c>
       <c r="S3">
-        <v>1.37</v>
+        <v>3.8</v>
       </c>
       <c r="T3">
-        <v>1.01</v>
+        <v>1.82</v>
       </c>
       <c r="U3">
-        <v>1.01</v>
+        <v>2.06</v>
       </c>
       <c r="V3">
-        <v>1.01</v>
+        <v>1.41</v>
       </c>
       <c r="W3">
-        <v>1.01</v>
+        <v>1.63</v>
       </c>
       <c r="X3">
-        <v>1000</v>
+        <v>15.5</v>
       </c>
       <c r="Y3">
-        <v>1000</v>
+        <v>14.5</v>
       </c>
       <c r="Z3">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="AA3">
-        <v>1000</v>
+        <v>75</v>
       </c>
       <c r="AB3">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="AC3">
-        <v>1000</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AD3">
-        <v>1000</v>
+        <v>17</v>
       </c>
       <c r="AE3">
-        <v>1000</v>
+        <v>50</v>
       </c>
       <c r="AF3">
-        <v>1000</v>
+        <v>16</v>
       </c>
       <c r="AG3">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="AH3">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="AI3">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AJ3">
-        <v>1000</v>
+        <v>44</v>
       </c>
       <c r="AK3">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="AL3">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AM3">
-        <v>1000</v>
+        <v>130</v>
       </c>
       <c r="AN3">
-        <v>1000</v>
+        <v>30</v>
       </c>
       <c r="AO3">
-        <v>1000</v>
+        <v>50</v>
       </c>
       <c r="AP3">
-        <v>1.01</v>
+        <v>11</v>
       </c>
       <c r="AQ3">
-        <v>1.01</v>
+        <v>10.5</v>
       </c>
       <c r="AR3">
-        <v>1.01</v>
+        <v>16</v>
       </c>
       <c r="AS3">
-        <v>1.01</v>
+        <v>4.7</v>
       </c>
       <c r="AT3">
-        <v>1.01</v>
+        <v>8.6</v>
       </c>
       <c r="AU3">
-        <v>1.01</v>
+        <v>6.8</v>
       </c>
       <c r="AV3">
-        <v>1.01</v>
+        <v>10</v>
       </c>
       <c r="AW3">
-        <v>1.01</v>
+        <v>4.6</v>
       </c>
       <c r="AX3">
-        <v>1.01</v>
+        <v>13.5</v>
       </c>
       <c r="AY3">
-        <v>1.01</v>
+        <v>10</v>
       </c>
       <c r="AZ3">
-        <v>1.01</v>
+        <v>4.1</v>
       </c>
       <c r="BA3">
-        <v>1.01</v>
+        <v>4.7</v>
       </c>
       <c r="BB3">
-        <v>1.01</v>
+        <v>4.5</v>
       </c>
       <c r="BC3">
-        <v>1.01</v>
+        <v>20</v>
       </c>
       <c r="BD3">
-        <v>1.01</v>
+        <v>4.6</v>
       </c>
       <c r="BE3">
-        <v>1.01</v>
+        <v>4.9</v>
       </c>
       <c r="BF3">
-        <v>1.01</v>
+        <v>17.5</v>
       </c>
       <c r="BG3">
-        <v>1.01</v>
+        <v>4.6</v>
       </c>
       <c r="BH3">
         <v>1000</v>
@@ -1403,226 +1403,226 @@
         <v>99</v>
       </c>
       <c r="F4">
-        <v>1.14</v>
+        <v>1.62</v>
       </c>
       <c r="G4">
-        <v>110</v>
+        <v>1.76</v>
       </c>
       <c r="H4">
-        <v>1.06</v>
+        <v>6.6</v>
       </c>
       <c r="I4">
-        <v>110</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="J4">
-        <v>1.03</v>
+        <v>3.55</v>
       </c>
       <c r="K4">
-        <v>950</v>
+        <v>4</v>
       </c>
       <c r="L4">
         <v>1.01</v>
       </c>
       <c r="M4">
-        <v>1.09</v>
+        <v>1.11</v>
       </c>
       <c r="N4">
-        <v>1.24</v>
+        <v>2.66</v>
       </c>
       <c r="O4">
         <v>1.49</v>
       </c>
       <c r="P4">
-        <v>1.25</v>
+        <v>1.56</v>
       </c>
       <c r="Q4">
-        <v>1.5</v>
+        <v>2.42</v>
       </c>
       <c r="R4">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="S4">
-        <v>1.02</v>
+        <v>4.9</v>
       </c>
       <c r="T4">
-        <v>1.01</v>
+        <v>2.28</v>
       </c>
       <c r="U4">
-        <v>1.01</v>
+        <v>1.62</v>
       </c>
       <c r="V4">
-        <v>1.01</v>
+        <v>1.13</v>
       </c>
       <c r="W4">
-        <v>1.01</v>
+        <v>2.3</v>
       </c>
       <c r="X4">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="Y4">
-        <v>1000</v>
+        <v>19</v>
       </c>
       <c r="Z4">
-        <v>1000</v>
+        <v>70</v>
       </c>
       <c r="AA4">
-        <v>1000</v>
+        <v>330</v>
       </c>
       <c r="AB4">
-        <v>1000</v>
+        <v>6.8</v>
       </c>
       <c r="AC4">
-        <v>1000</v>
+        <v>10</v>
       </c>
       <c r="AD4">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="AE4">
-        <v>1000</v>
+        <v>180</v>
       </c>
       <c r="AF4">
-        <v>1000</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AG4">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="AH4">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="AI4">
-        <v>1000</v>
+        <v>190</v>
       </c>
       <c r="AJ4">
-        <v>1000</v>
+        <v>20</v>
       </c>
       <c r="AK4">
-        <v>1000</v>
+        <v>27</v>
       </c>
       <c r="AL4">
-        <v>1000</v>
+        <v>70</v>
       </c>
       <c r="AM4">
-        <v>1000</v>
+        <v>310</v>
       </c>
       <c r="AN4">
-        <v>1000</v>
+        <v>19.5</v>
       </c>
       <c r="AO4">
-        <v>1000</v>
+        <v>360</v>
       </c>
       <c r="AP4">
-        <v>1.01</v>
+        <v>7.4</v>
       </c>
       <c r="AQ4">
-        <v>1.01</v>
+        <v>13</v>
       </c>
       <c r="AR4">
-        <v>1.01</v>
+        <v>5</v>
       </c>
       <c r="AS4">
-        <v>1.01</v>
+        <v>5.3</v>
       </c>
       <c r="AT4">
-        <v>1.01</v>
+        <v>4.8</v>
       </c>
       <c r="AU4">
-        <v>1.01</v>
+        <v>7.4</v>
       </c>
       <c r="AV4">
-        <v>1.01</v>
+        <v>22</v>
       </c>
       <c r="AW4">
-        <v>1.01</v>
+        <v>5.2</v>
       </c>
       <c r="AX4">
-        <v>1.01</v>
+        <v>6.8</v>
       </c>
       <c r="AY4">
-        <v>1.01</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AZ4">
-        <v>1.01</v>
+        <v>4.6</v>
       </c>
       <c r="BA4">
-        <v>1.01</v>
+        <v>5.2</v>
       </c>
       <c r="BB4">
-        <v>1.01</v>
+        <v>13</v>
       </c>
       <c r="BC4">
-        <v>1.01</v>
+        <v>17.5</v>
       </c>
       <c r="BD4">
-        <v>1.01</v>
+        <v>5</v>
       </c>
       <c r="BE4">
-        <v>1.01</v>
+        <v>5.3</v>
       </c>
       <c r="BF4">
-        <v>1.01</v>
+        <v>12.5</v>
       </c>
       <c r="BG4">
-        <v>1.01</v>
+        <v>5.3</v>
       </c>
       <c r="BH4">
         <v>1000</v>
       </c>
       <c r="BI4">
-        <v>1.01</v>
+        <v>1.73</v>
       </c>
       <c r="BJ4">
-        <v>1000</v>
+        <v>18</v>
       </c>
       <c r="BK4">
-        <v>1.01</v>
+        <v>1.58</v>
       </c>
       <c r="BL4">
         <v>1000</v>
       </c>
       <c r="BM4">
-        <v>1.01</v>
+        <v>1.73</v>
       </c>
       <c r="BN4">
-        <v>1000</v>
+        <v>5.1</v>
       </c>
       <c r="BO4">
-        <v>1.01</v>
+        <v>2.8</v>
       </c>
       <c r="BP4">
-        <v>1000</v>
+        <v>17.5</v>
       </c>
       <c r="BQ4">
-        <v>1.01</v>
+        <v>1.57</v>
       </c>
       <c r="BR4">
-        <v>1000</v>
+        <v>50</v>
       </c>
       <c r="BS4">
-        <v>1.01</v>
+        <v>1.67</v>
       </c>
       <c r="BT4">
-        <v>1000</v>
+        <v>14.5</v>
       </c>
       <c r="BU4">
-        <v>1.01</v>
+        <v>1.54</v>
       </c>
       <c r="BV4">
         <v>1000</v>
       </c>
       <c r="BW4">
-        <v>1.01</v>
+        <v>1.73</v>
       </c>
       <c r="BX4">
         <v>1000</v>
       </c>
       <c r="BY4">
-        <v>1.01</v>
+        <v>1.73</v>
       </c>
       <c r="BZ4">
-        <v>1000</v>
+        <v>46</v>
       </c>
       <c r="CA4">
-        <v>1.01</v>
+        <v>1.67</v>
       </c>
       <c r="CB4" t="s">
         <v>103</v>
@@ -1645,166 +1645,166 @@
         <v>100</v>
       </c>
       <c r="F5">
-        <v>1.04</v>
+        <v>1.52</v>
       </c>
       <c r="G5">
-        <v>110</v>
+        <v>1.59</v>
       </c>
       <c r="H5">
-        <v>1.04</v>
+        <v>7.8</v>
       </c>
       <c r="I5">
-        <v>110</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="J5">
-        <v>1.03</v>
+        <v>4</v>
       </c>
       <c r="K5">
-        <v>950</v>
+        <v>4.4</v>
       </c>
       <c r="L5">
         <v>1.01</v>
       </c>
       <c r="M5">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="N5">
-        <v>1.01</v>
+        <v>3.25</v>
       </c>
       <c r="O5">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="P5">
-        <v>1.25</v>
+        <v>1.76</v>
       </c>
       <c r="Q5">
-        <v>1.46</v>
+        <v>2.06</v>
       </c>
       <c r="R5">
-        <v>1.15</v>
+        <v>1.29</v>
       </c>
       <c r="S5">
-        <v>1.01</v>
+        <v>3.9</v>
       </c>
       <c r="T5">
-        <v>1.01</v>
+        <v>2.14</v>
       </c>
       <c r="U5">
-        <v>1.01</v>
+        <v>1.71</v>
       </c>
       <c r="V5">
-        <v>1.01</v>
+        <v>1.12</v>
       </c>
       <c r="W5">
-        <v>1.01</v>
+        <v>2.7</v>
       </c>
       <c r="X5">
-        <v>1000</v>
+        <v>15</v>
       </c>
       <c r="Y5">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="Z5">
-        <v>1000</v>
+        <v>80</v>
       </c>
       <c r="AA5">
-        <v>1000</v>
+        <v>360</v>
       </c>
       <c r="AB5">
-        <v>1000</v>
+        <v>7.8</v>
       </c>
       <c r="AC5">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="AD5">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="AE5">
-        <v>1000</v>
+        <v>180</v>
       </c>
       <c r="AF5">
-        <v>1000</v>
+        <v>9.6</v>
       </c>
       <c r="AG5">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="AH5">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="AI5">
-        <v>1000</v>
+        <v>160</v>
       </c>
       <c r="AJ5">
-        <v>1000</v>
+        <v>16.5</v>
       </c>
       <c r="AK5">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="AL5">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AM5">
-        <v>1000</v>
+        <v>230</v>
       </c>
       <c r="AN5">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="AO5">
-        <v>1000</v>
+        <v>290</v>
       </c>
       <c r="AP5">
-        <v>1.01</v>
+        <v>11</v>
       </c>
       <c r="AQ5">
-        <v>1.01</v>
+        <v>17</v>
       </c>
       <c r="AR5">
-        <v>1.01</v>
+        <v>5.3</v>
       </c>
       <c r="AS5">
-        <v>1.01</v>
+        <v>5.6</v>
       </c>
       <c r="AT5">
-        <v>1.01</v>
+        <v>5.9</v>
       </c>
       <c r="AU5">
-        <v>1.01</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AV5">
-        <v>1.01</v>
+        <v>4.9</v>
       </c>
       <c r="AW5">
-        <v>1.01</v>
+        <v>5.5</v>
       </c>
       <c r="AX5">
-        <v>1.01</v>
+        <v>6.4</v>
       </c>
       <c r="AY5">
-        <v>1.01</v>
+        <v>9</v>
       </c>
       <c r="AZ5">
-        <v>1.01</v>
+        <v>21</v>
       </c>
       <c r="BA5">
-        <v>1.01</v>
+        <v>5.5</v>
       </c>
       <c r="BB5">
-        <v>1.01</v>
+        <v>11</v>
       </c>
       <c r="BC5">
-        <v>1.01</v>
+        <v>15.5</v>
       </c>
       <c r="BD5">
-        <v>1.01</v>
+        <v>34</v>
       </c>
       <c r="BE5">
-        <v>1.01</v>
+        <v>5.5</v>
       </c>
       <c r="BF5">
-        <v>1.01</v>
+        <v>8</v>
       </c>
       <c r="BG5">
-        <v>1.01</v>
+        <v>5.5</v>
       </c>
       <c r="BH5">
         <v>1000</v>
@@ -1887,22 +1887,22 @@
         <v>101</v>
       </c>
       <c r="F6">
-        <v>1.04</v>
+        <v>1.29</v>
       </c>
       <c r="G6">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="H6">
-        <v>1.04</v>
+        <v>9.6</v>
       </c>
       <c r="I6">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="J6">
-        <v>1.03</v>
+        <v>1.09</v>
       </c>
       <c r="K6">
-        <v>950</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="L6">
         <v>1.01</v>
@@ -1911,40 +1911,40 @@
         <v>1.01</v>
       </c>
       <c r="N6">
-        <v>1.25</v>
+        <v>3.25</v>
       </c>
       <c r="O6">
         <v>1.24</v>
       </c>
       <c r="P6">
-        <v>1.25</v>
+        <v>2.06</v>
       </c>
       <c r="Q6">
-        <v>1.24</v>
+        <v>1.73</v>
       </c>
       <c r="R6">
-        <v>1.15</v>
+        <v>1.38</v>
       </c>
       <c r="S6">
-        <v>1.24</v>
+        <v>2.8</v>
       </c>
       <c r="T6">
-        <v>1.01</v>
+        <v>2.02</v>
       </c>
       <c r="U6">
-        <v>1.01</v>
+        <v>1.56</v>
       </c>
       <c r="V6">
-        <v>1.01</v>
+        <v>1.06</v>
       </c>
       <c r="W6">
-        <v>1.01</v>
+        <v>3.25</v>
       </c>
       <c r="X6">
         <v>1000</v>
       </c>
       <c r="Y6">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="Z6">
         <v>1000</v>
@@ -1953,7 +1953,7 @@
         <v>1000</v>
       </c>
       <c r="AB6">
-        <v>1000</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AC6">
         <v>1000</v>
@@ -1965,13 +1965,13 @@
         <v>1000</v>
       </c>
       <c r="AF6">
-        <v>1000</v>
+        <v>9</v>
       </c>
       <c r="AG6">
         <v>1000</v>
       </c>
       <c r="AH6">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="AI6">
         <v>1000</v>
@@ -1980,7 +1980,7 @@
         <v>1000</v>
       </c>
       <c r="AK6">
-        <v>1000</v>
+        <v>19.5</v>
       </c>
       <c r="AL6">
         <v>1000</v>
@@ -1989,64 +1989,64 @@
         <v>1000</v>
       </c>
       <c r="AN6">
-        <v>1000</v>
+        <v>7.4</v>
       </c>
       <c r="AO6">
         <v>1000</v>
       </c>
       <c r="AP6">
-        <v>1.03</v>
+        <v>1.83</v>
       </c>
       <c r="AQ6">
-        <v>1.03</v>
+        <v>1.75</v>
       </c>
       <c r="AR6">
-        <v>1.03</v>
+        <v>1.83</v>
       </c>
       <c r="AS6">
-        <v>1.03</v>
+        <v>1.83</v>
       </c>
       <c r="AT6">
-        <v>1.03</v>
+        <v>5.7</v>
       </c>
       <c r="AU6">
-        <v>1.01</v>
+        <v>1.83</v>
       </c>
       <c r="AV6">
-        <v>1.03</v>
+        <v>1.83</v>
       </c>
       <c r="AW6">
-        <v>1.03</v>
+        <v>1.83</v>
       </c>
       <c r="AX6">
-        <v>1.03</v>
+        <v>5.6</v>
       </c>
       <c r="AY6">
-        <v>1.03</v>
+        <v>1.83</v>
       </c>
       <c r="AZ6">
-        <v>1.01</v>
+        <v>1.75</v>
       </c>
       <c r="BA6">
-        <v>1.03</v>
+        <v>1.83</v>
       </c>
       <c r="BB6">
-        <v>1.03</v>
+        <v>1.83</v>
       </c>
       <c r="BC6">
-        <v>1.03</v>
+        <v>1.67</v>
       </c>
       <c r="BD6">
-        <v>1.03</v>
+        <v>1.83</v>
       </c>
       <c r="BE6">
-        <v>1.01</v>
+        <v>1.83</v>
       </c>
       <c r="BF6">
-        <v>1.01</v>
+        <v>4.6</v>
       </c>
       <c r="BG6">
-        <v>1.01</v>
+        <v>1.83</v>
       </c>
       <c r="BH6">
         <v>1000</v>
@@ -2055,7 +2055,7 @@
         <v>1.01</v>
       </c>
       <c r="BJ6">
-        <v>1000</v>
+        <v>18</v>
       </c>
       <c r="BK6">
         <v>1.01</v>
@@ -2067,25 +2067,25 @@
         <v>1.01</v>
       </c>
       <c r="BN6">
-        <v>1000</v>
+        <v>4.8</v>
       </c>
       <c r="BO6">
-        <v>1.01</v>
+        <v>2.62</v>
       </c>
       <c r="BP6">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="BQ6">
-        <v>1.01</v>
+        <v>5.1</v>
       </c>
       <c r="BR6">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="BS6">
         <v>1.01</v>
       </c>
       <c r="BT6">
-        <v>1000</v>
+        <v>20</v>
       </c>
       <c r="BU6">
         <v>1.01</v>
@@ -2103,7 +2103,7 @@
         <v>1.01</v>
       </c>
       <c r="BZ6">
-        <v>1000</v>
+        <v>19</v>
       </c>
       <c r="CA6">
         <v>1.01</v>
@@ -2129,22 +2129,22 @@
         <v>102</v>
       </c>
       <c r="F7">
-        <v>1.04</v>
+        <v>2.08</v>
       </c>
       <c r="G7">
-        <v>1000</v>
+        <v>2.32</v>
       </c>
       <c r="H7">
-        <v>1.04</v>
+        <v>3.2</v>
       </c>
       <c r="I7">
-        <v>1000</v>
+        <v>4</v>
       </c>
       <c r="J7">
-        <v>1.02</v>
+        <v>3.7</v>
       </c>
       <c r="K7">
-        <v>950</v>
+        <v>4.9</v>
       </c>
       <c r="L7">
         <v>0</v>
@@ -2159,10 +2159,10 @@
         <v>0</v>
       </c>
       <c r="P7">
-        <v>1.24</v>
+        <v>2.24</v>
       </c>
       <c r="Q7">
-        <v>1.01</v>
+        <v>1.6</v>
       </c>
       <c r="R7">
         <v>0</v>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-08-11.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-08-11.xlsx
@@ -325,7 +325,7 @@
     <t>Varnamo</t>
   </si>
   <si>
-    <t>2026-08-09 05:34:30</t>
+    <t>2026-08-09 07:52:07</t>
   </si>
 </sst>
 </file>
@@ -919,16 +919,16 @@
         <v>97</v>
       </c>
       <c r="F2">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="G2">
-        <v>110</v>
+        <v>970</v>
       </c>
       <c r="H2">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="I2">
-        <v>110</v>
+        <v>970</v>
       </c>
       <c r="J2">
         <v>1.06</v>
@@ -970,7 +970,7 @@
         <v>1.02</v>
       </c>
       <c r="W2">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="X2">
         <v>1000</v>
@@ -1209,7 +1209,7 @@
         <v>2.06</v>
       </c>
       <c r="V3">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="W3">
         <v>1.63</v>
@@ -1406,7 +1406,7 @@
         <v>1.62</v>
       </c>
       <c r="G4">
-        <v>1.76</v>
+        <v>1.77</v>
       </c>
       <c r="H4">
         <v>6.6</v>
@@ -1424,7 +1424,7 @@
         <v>1.01</v>
       </c>
       <c r="M4">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="N4">
         <v>2.66</v>
@@ -1442,7 +1442,7 @@
         <v>1.2</v>
       </c>
       <c r="S4">
-        <v>4.9</v>
+        <v>4.5</v>
       </c>
       <c r="T4">
         <v>2.28</v>
@@ -1451,7 +1451,7 @@
         <v>1.62</v>
       </c>
       <c r="V4">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="W4">
         <v>2.3</v>
@@ -1460,7 +1460,7 @@
         <v>11</v>
       </c>
       <c r="Y4">
-        <v>19</v>
+        <v>19.5</v>
       </c>
       <c r="Z4">
         <v>70</v>
@@ -1517,25 +1517,25 @@
         <v>13</v>
       </c>
       <c r="AR4">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="AS4">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="AT4">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="AU4">
         <v>7.4</v>
       </c>
       <c r="AV4">
-        <v>22</v>
+        <v>4.6</v>
       </c>
       <c r="AW4">
         <v>5.2</v>
       </c>
       <c r="AX4">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="AY4">
         <v>8.199999999999999</v>
@@ -1553,16 +1553,16 @@
         <v>17.5</v>
       </c>
       <c r="BD4">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="BE4">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="BF4">
         <v>12.5</v>
       </c>
       <c r="BG4">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="BH4">
         <v>1000</v>
@@ -1666,7 +1666,7 @@
         <v>1.01</v>
       </c>
       <c r="M5">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="N5">
         <v>3.25</v>
@@ -1678,7 +1678,7 @@
         <v>1.76</v>
       </c>
       <c r="Q5">
-        <v>2.06</v>
+        <v>2.08</v>
       </c>
       <c r="R5">
         <v>1.29</v>
@@ -1687,7 +1687,7 @@
         <v>3.9</v>
       </c>
       <c r="T5">
-        <v>2.14</v>
+        <v>2.16</v>
       </c>
       <c r="U5">
         <v>1.71</v>
@@ -1726,7 +1726,7 @@
         <v>9.6</v>
       </c>
       <c r="AG5">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AH5">
         <v>32</v>
@@ -1747,7 +1747,7 @@
         <v>230</v>
       </c>
       <c r="AN5">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AO5">
         <v>290</v>
@@ -1756,13 +1756,13 @@
         <v>11</v>
       </c>
       <c r="AQ5">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="AR5">
-        <v>5.3</v>
+        <v>5</v>
       </c>
       <c r="AS5">
-        <v>5.6</v>
+        <v>5.2</v>
       </c>
       <c r="AT5">
         <v>5.9</v>
@@ -1771,10 +1771,10 @@
         <v>8.199999999999999</v>
       </c>
       <c r="AV5">
-        <v>4.9</v>
+        <v>4.6</v>
       </c>
       <c r="AW5">
-        <v>5.5</v>
+        <v>5.2</v>
       </c>
       <c r="AX5">
         <v>6.4</v>
@@ -1786,7 +1786,7 @@
         <v>21</v>
       </c>
       <c r="BA5">
-        <v>5.5</v>
+        <v>5.1</v>
       </c>
       <c r="BB5">
         <v>11</v>
@@ -1795,16 +1795,16 @@
         <v>15.5</v>
       </c>
       <c r="BD5">
-        <v>34</v>
+        <v>4.8</v>
       </c>
       <c r="BE5">
-        <v>5.5</v>
+        <v>5.2</v>
       </c>
       <c r="BF5">
         <v>8</v>
       </c>
       <c r="BG5">
-        <v>5.5</v>
+        <v>5.2</v>
       </c>
       <c r="BH5">
         <v>1000</v>
@@ -1896,10 +1896,10 @@
         <v>9.6</v>
       </c>
       <c r="I6">
-        <v>110</v>
+        <v>16.5</v>
       </c>
       <c r="J6">
-        <v>1.09</v>
+        <v>4</v>
       </c>
       <c r="K6">
         <v>8.199999999999999</v>
@@ -1917,7 +1917,7 @@
         <v>1.24</v>
       </c>
       <c r="P6">
-        <v>2.06</v>
+        <v>1.99</v>
       </c>
       <c r="Q6">
         <v>1.73</v>
@@ -2052,19 +2052,19 @@
         <v>1000</v>
       </c>
       <c r="BI6">
-        <v>1.01</v>
+        <v>1.96</v>
       </c>
       <c r="BJ6">
         <v>18</v>
       </c>
       <c r="BK6">
-        <v>1.01</v>
+        <v>1.77</v>
       </c>
       <c r="BL6">
         <v>1000</v>
       </c>
       <c r="BM6">
-        <v>1.01</v>
+        <v>1.96</v>
       </c>
       <c r="BN6">
         <v>4.8</v>
@@ -2082,31 +2082,31 @@
         <v>38</v>
       </c>
       <c r="BS6">
-        <v>1.01</v>
+        <v>1.87</v>
       </c>
       <c r="BT6">
         <v>20</v>
       </c>
       <c r="BU6">
-        <v>1.01</v>
+        <v>1.79</v>
       </c>
       <c r="BV6">
         <v>1000</v>
       </c>
       <c r="BW6">
-        <v>1.01</v>
+        <v>1.96</v>
       </c>
       <c r="BX6">
         <v>1000</v>
       </c>
       <c r="BY6">
-        <v>1.01</v>
+        <v>1.96</v>
       </c>
       <c r="BZ6">
         <v>19</v>
       </c>
       <c r="CA6">
-        <v>1.01</v>
+        <v>1.78</v>
       </c>
       <c r="CB6" t="s">
         <v>103</v>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-08-11.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-08-11.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="116" uniqueCount="104">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="98" uniqueCount="93">
   <si>
     <t>League</t>
   </si>
@@ -262,18 +262,9 @@
     <t>Chilean Primera Division</t>
   </si>
   <si>
-    <t>Ecuadorian Serie A</t>
-  </si>
-  <si>
     <t>Argentinian Primera Division</t>
   </si>
   <si>
-    <t>Colombian Primera A</t>
-  </si>
-  <si>
-    <t>Swedish Superettan</t>
-  </si>
-  <si>
     <t>2026-08-11</t>
   </si>
   <si>
@@ -283,49 +274,25 @@
     <t>00:15:00</t>
   </si>
   <si>
-    <t>01:05:00</t>
-  </si>
-  <si>
-    <t>17:00:00</t>
-  </si>
-  <si>
     <t>America MG (W)</t>
   </si>
   <si>
     <t>Audax Italiano</t>
   </si>
   <si>
-    <t>Deportivo Cuenca</t>
-  </si>
-  <si>
     <t>Union Santa Fe</t>
   </si>
   <si>
-    <t>Junior FC Barranquilla</t>
-  </si>
-  <si>
-    <t>Helsingborgs</t>
-  </si>
-  <si>
     <t>CR Flamengo (W)</t>
   </si>
   <si>
     <t>Nublense</t>
   </si>
   <si>
-    <t>Manta FC</t>
-  </si>
-  <si>
     <t>Central Cordoba (SdE)</t>
   </si>
   <si>
-    <t>Deportivo Pereira</t>
-  </si>
-  <si>
-    <t>Varnamo</t>
-  </si>
-  <si>
-    <t>2026-08-09 07:52:07</t>
+    <t>2026-08-09 10:29:56</t>
   </si>
 </sst>
 </file>
@@ -657,7 +624,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:CB7"/>
+  <dimension ref="A1:CB4"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:80">
@@ -907,19 +874,19 @@
         <v>80</v>
       </c>
       <c r="B2" t="s">
+        <v>83</v>
+      </c>
+      <c r="C2" t="s">
+        <v>84</v>
+      </c>
+      <c r="D2" t="s">
         <v>86</v>
       </c>
-      <c r="C2" t="s">
-        <v>87</v>
-      </c>
-      <c r="D2" t="s">
-        <v>91</v>
-      </c>
       <c r="E2" t="s">
-        <v>97</v>
+        <v>89</v>
       </c>
       <c r="F2">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="G2">
         <v>970</v>
@@ -943,7 +910,7 @@
         <v>1.01</v>
       </c>
       <c r="N2">
-        <v>1.29</v>
+        <v>4.7</v>
       </c>
       <c r="O2">
         <v>1.18</v>
@@ -1141,7 +1108,7 @@
         <v>1.01</v>
       </c>
       <c r="CB2" t="s">
-        <v>103</v>
+        <v>92</v>
       </c>
     </row>
     <row r="3" spans="1:80">
@@ -1149,16 +1116,16 @@
         <v>81</v>
       </c>
       <c r="B3" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="C3" t="s">
+        <v>84</v>
+      </c>
+      <c r="D3" t="s">
         <v>87</v>
       </c>
-      <c r="D3" t="s">
-        <v>92</v>
-      </c>
       <c r="E3" t="s">
-        <v>98</v>
+        <v>90</v>
       </c>
       <c r="F3">
         <v>2.4</v>
@@ -1176,10 +1143,10 @@
         <v>3.1</v>
       </c>
       <c r="K3">
-        <v>3.8</v>
+        <v>3.6</v>
       </c>
       <c r="L3">
-        <v>1.42</v>
+        <v>1.44</v>
       </c>
       <c r="M3">
         <v>1.08</v>
@@ -1209,10 +1176,10 @@
         <v>2.06</v>
       </c>
       <c r="V3">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="W3">
-        <v>1.63</v>
+        <v>1.64</v>
       </c>
       <c r="X3">
         <v>15.5</v>
@@ -1323,67 +1290,67 @@
         <v>4.6</v>
       </c>
       <c r="BH3">
-        <v>1000</v>
+        <v>3.7</v>
       </c>
       <c r="BI3">
-        <v>1.01</v>
+        <v>2.58</v>
       </c>
       <c r="BJ3">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="BK3">
-        <v>1.01</v>
+        <v>3.4</v>
       </c>
       <c r="BL3">
         <v>1000</v>
       </c>
       <c r="BM3">
-        <v>1.01</v>
+        <v>4.6</v>
       </c>
       <c r="BN3">
-        <v>1000</v>
+        <v>6.4</v>
       </c>
       <c r="BO3">
-        <v>1.01</v>
+        <v>4</v>
       </c>
       <c r="BP3">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="BQ3">
-        <v>1.01</v>
+        <v>3.95</v>
       </c>
       <c r="BR3">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="BS3">
-        <v>1.01</v>
+        <v>4.3</v>
       </c>
       <c r="BT3">
-        <v>1000</v>
+        <v>7.6</v>
       </c>
       <c r="BU3">
-        <v>1.01</v>
+        <v>4.8</v>
       </c>
       <c r="BV3">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="BW3">
-        <v>1.01</v>
+        <v>4.2</v>
       </c>
       <c r="BX3">
-        <v>1000</v>
+        <v>48</v>
       </c>
       <c r="BY3">
-        <v>1.01</v>
+        <v>4.3</v>
       </c>
       <c r="BZ3">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="CA3">
-        <v>1.01</v>
+        <v>4.2</v>
       </c>
       <c r="CB3" t="s">
-        <v>103</v>
+        <v>92</v>
       </c>
     </row>
     <row r="4" spans="1:80">
@@ -1391,88 +1358,88 @@
         <v>82</v>
       </c>
       <c r="B4" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="C4" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="D4" t="s">
-        <v>93</v>
+        <v>88</v>
       </c>
       <c r="E4" t="s">
-        <v>99</v>
+        <v>91</v>
       </c>
       <c r="F4">
-        <v>1.62</v>
+        <v>1.52</v>
       </c>
       <c r="G4">
-        <v>1.77</v>
+        <v>1.59</v>
       </c>
       <c r="H4">
-        <v>6.6</v>
+        <v>7.8</v>
       </c>
       <c r="I4">
-        <v>8.199999999999999</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="J4">
-        <v>3.55</v>
+        <v>4</v>
       </c>
       <c r="K4">
-        <v>4</v>
+        <v>4.4</v>
       </c>
       <c r="L4">
         <v>1.01</v>
       </c>
       <c r="M4">
-        <v>1.1</v>
+        <v>1.08</v>
       </c>
       <c r="N4">
-        <v>2.66</v>
+        <v>3.25</v>
       </c>
       <c r="O4">
-        <v>1.49</v>
+        <v>1.36</v>
       </c>
       <c r="P4">
-        <v>1.56</v>
+        <v>1.76</v>
       </c>
       <c r="Q4">
-        <v>2.42</v>
+        <v>2.08</v>
       </c>
       <c r="R4">
-        <v>1.2</v>
+        <v>1.29</v>
       </c>
       <c r="S4">
-        <v>4.5</v>
+        <v>3.9</v>
       </c>
       <c r="T4">
-        <v>2.28</v>
+        <v>2.16</v>
       </c>
       <c r="U4">
-        <v>1.62</v>
+        <v>1.71</v>
       </c>
       <c r="V4">
-        <v>1.14</v>
+        <v>1.12</v>
       </c>
       <c r="W4">
-        <v>2.3</v>
+        <v>2.7</v>
       </c>
       <c r="X4">
+        <v>15</v>
+      </c>
+      <c r="Y4">
+        <v>25</v>
+      </c>
+      <c r="Z4">
+        <v>80</v>
+      </c>
+      <c r="AA4">
+        <v>360</v>
+      </c>
+      <c r="AB4">
+        <v>7.8</v>
+      </c>
+      <c r="AC4">
         <v>11</v>
-      </c>
-      <c r="Y4">
-        <v>19.5</v>
-      </c>
-      <c r="Z4">
-        <v>70</v>
-      </c>
-      <c r="AA4">
-        <v>330</v>
-      </c>
-      <c r="AB4">
-        <v>6.8</v>
-      </c>
-      <c r="AC4">
-        <v>10</v>
       </c>
       <c r="AD4">
         <v>36</v>
@@ -1481,52 +1448,52 @@
         <v>180</v>
       </c>
       <c r="AF4">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="AG4">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AH4">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="AI4">
-        <v>190</v>
+        <v>160</v>
       </c>
       <c r="AJ4">
-        <v>20</v>
+        <v>16.5</v>
       </c>
       <c r="AK4">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="AL4">
-        <v>70</v>
+        <v>55</v>
       </c>
       <c r="AM4">
-        <v>310</v>
+        <v>230</v>
       </c>
       <c r="AN4">
-        <v>19.5</v>
+        <v>12</v>
       </c>
       <c r="AO4">
-        <v>360</v>
+        <v>290</v>
       </c>
       <c r="AP4">
-        <v>7.4</v>
+        <v>11</v>
       </c>
       <c r="AQ4">
-        <v>13</v>
+        <v>16.5</v>
       </c>
       <c r="AR4">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="AS4">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="AT4">
-        <v>4.7</v>
+        <v>5.9</v>
       </c>
       <c r="AU4">
-        <v>7.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AV4">
         <v>4.6</v>
@@ -1535,22 +1502,22 @@
         <v>5.2</v>
       </c>
       <c r="AX4">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="AY4">
-        <v>8.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="AZ4">
-        <v>4.6</v>
+        <v>21</v>
       </c>
       <c r="BA4">
         <v>5.2</v>
       </c>
       <c r="BB4">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="BC4">
-        <v>17.5</v>
+        <v>15.5</v>
       </c>
       <c r="BD4">
         <v>4.9</v>
@@ -1559,7 +1526,7 @@
         <v>5.2</v>
       </c>
       <c r="BF4">
-        <v>12.5</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BG4">
         <v>5.2</v>
@@ -1568,790 +1535,64 @@
         <v>1000</v>
       </c>
       <c r="BI4">
-        <v>1.73</v>
+        <v>1.82</v>
       </c>
       <c r="BJ4">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="BK4">
-        <v>1.58</v>
+        <v>1.64</v>
       </c>
       <c r="BL4">
         <v>1000</v>
       </c>
       <c r="BM4">
-        <v>1.73</v>
+        <v>1.82</v>
       </c>
       <c r="BN4">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="BO4">
-        <v>2.8</v>
+        <v>2.84</v>
       </c>
       <c r="BP4">
-        <v>17.5</v>
+        <v>14.5</v>
       </c>
       <c r="BQ4">
-        <v>1.57</v>
+        <v>1.62</v>
       </c>
       <c r="BR4">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="BS4">
-        <v>1.67</v>
+        <v>1.75</v>
       </c>
       <c r="BT4">
-        <v>14.5</v>
+        <v>15.5</v>
       </c>
       <c r="BU4">
-        <v>1.54</v>
+        <v>1.63</v>
       </c>
       <c r="BV4">
         <v>1000</v>
       </c>
       <c r="BW4">
-        <v>1.73</v>
+        <v>1.82</v>
       </c>
       <c r="BX4">
         <v>1000</v>
       </c>
       <c r="BY4">
-        <v>1.73</v>
+        <v>1.82</v>
       </c>
       <c r="BZ4">
-        <v>46</v>
+        <v>30</v>
       </c>
       <c r="CA4">
-        <v>1.67</v>
+        <v>1.72</v>
       </c>
       <c r="CB4" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="5" spans="1:80">
-      <c r="A5" t="s">
-        <v>83</v>
-      </c>
-      <c r="B5" t="s">
-        <v>86</v>
-      </c>
-      <c r="C5" t="s">
-        <v>88</v>
-      </c>
-      <c r="D5" t="s">
-        <v>94</v>
-      </c>
-      <c r="E5" t="s">
-        <v>100</v>
-      </c>
-      <c r="F5">
-        <v>1.52</v>
-      </c>
-      <c r="G5">
-        <v>1.59</v>
-      </c>
-      <c r="H5">
-        <v>7.8</v>
-      </c>
-      <c r="I5">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="J5">
-        <v>4</v>
-      </c>
-      <c r="K5">
-        <v>4.4</v>
-      </c>
-      <c r="L5">
-        <v>1.01</v>
-      </c>
-      <c r="M5">
-        <v>1.07</v>
-      </c>
-      <c r="N5">
-        <v>3.25</v>
-      </c>
-      <c r="O5">
-        <v>1.36</v>
-      </c>
-      <c r="P5">
-        <v>1.76</v>
-      </c>
-      <c r="Q5">
-        <v>2.08</v>
-      </c>
-      <c r="R5">
-        <v>1.29</v>
-      </c>
-      <c r="S5">
-        <v>3.9</v>
-      </c>
-      <c r="T5">
-        <v>2.16</v>
-      </c>
-      <c r="U5">
-        <v>1.71</v>
-      </c>
-      <c r="V5">
-        <v>1.12</v>
-      </c>
-      <c r="W5">
-        <v>2.7</v>
-      </c>
-      <c r="X5">
-        <v>15</v>
-      </c>
-      <c r="Y5">
-        <v>25</v>
-      </c>
-      <c r="Z5">
-        <v>80</v>
-      </c>
-      <c r="AA5">
-        <v>360</v>
-      </c>
-      <c r="AB5">
-        <v>7.8</v>
-      </c>
-      <c r="AC5">
-        <v>11</v>
-      </c>
-      <c r="AD5">
-        <v>38</v>
-      </c>
-      <c r="AE5">
-        <v>180</v>
-      </c>
-      <c r="AF5">
-        <v>9.6</v>
-      </c>
-      <c r="AG5">
-        <v>12</v>
-      </c>
-      <c r="AH5">
-        <v>32</v>
-      </c>
-      <c r="AI5">
-        <v>160</v>
-      </c>
-      <c r="AJ5">
-        <v>16.5</v>
-      </c>
-      <c r="AK5">
-        <v>22</v>
-      </c>
-      <c r="AL5">
-        <v>55</v>
-      </c>
-      <c r="AM5">
-        <v>230</v>
-      </c>
-      <c r="AN5">
-        <v>12</v>
-      </c>
-      <c r="AO5">
-        <v>290</v>
-      </c>
-      <c r="AP5">
-        <v>11</v>
-      </c>
-      <c r="AQ5">
-        <v>16.5</v>
-      </c>
-      <c r="AR5">
-        <v>5</v>
-      </c>
-      <c r="AS5">
-        <v>5.2</v>
-      </c>
-      <c r="AT5">
-        <v>5.9</v>
-      </c>
-      <c r="AU5">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AV5">
-        <v>4.6</v>
-      </c>
-      <c r="AW5">
-        <v>5.2</v>
-      </c>
-      <c r="AX5">
-        <v>6.4</v>
-      </c>
-      <c r="AY5">
-        <v>9</v>
-      </c>
-      <c r="AZ5">
-        <v>21</v>
-      </c>
-      <c r="BA5">
-        <v>5.1</v>
-      </c>
-      <c r="BB5">
-        <v>11</v>
-      </c>
-      <c r="BC5">
-        <v>15.5</v>
-      </c>
-      <c r="BD5">
-        <v>4.8</v>
-      </c>
-      <c r="BE5">
-        <v>5.2</v>
-      </c>
-      <c r="BF5">
-        <v>8</v>
-      </c>
-      <c r="BG5">
-        <v>5.2</v>
-      </c>
-      <c r="BH5">
-        <v>1000</v>
-      </c>
-      <c r="BI5">
-        <v>1.01</v>
-      </c>
-      <c r="BJ5">
-        <v>1000</v>
-      </c>
-      <c r="BK5">
-        <v>1.01</v>
-      </c>
-      <c r="BL5">
-        <v>1000</v>
-      </c>
-      <c r="BM5">
-        <v>1.01</v>
-      </c>
-      <c r="BN5">
-        <v>1000</v>
-      </c>
-      <c r="BO5">
-        <v>1.01</v>
-      </c>
-      <c r="BP5">
-        <v>1000</v>
-      </c>
-      <c r="BQ5">
-        <v>1.01</v>
-      </c>
-      <c r="BR5">
-        <v>1000</v>
-      </c>
-      <c r="BS5">
-        <v>1.01</v>
-      </c>
-      <c r="BT5">
-        <v>1000</v>
-      </c>
-      <c r="BU5">
-        <v>1.01</v>
-      </c>
-      <c r="BV5">
-        <v>1000</v>
-      </c>
-      <c r="BW5">
-        <v>1.01</v>
-      </c>
-      <c r="BX5">
-        <v>1000</v>
-      </c>
-      <c r="BY5">
-        <v>1.01</v>
-      </c>
-      <c r="BZ5">
-        <v>1000</v>
-      </c>
-      <c r="CA5">
-        <v>1.01</v>
-      </c>
-      <c r="CB5" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="6" spans="1:80">
-      <c r="A6" t="s">
-        <v>84</v>
-      </c>
-      <c r="B6" t="s">
-        <v>86</v>
-      </c>
-      <c r="C6" t="s">
-        <v>89</v>
-      </c>
-      <c r="D6" t="s">
-        <v>95</v>
-      </c>
-      <c r="E6" t="s">
-        <v>101</v>
-      </c>
-      <c r="F6">
-        <v>1.29</v>
-      </c>
-      <c r="G6">
-        <v>1.44</v>
-      </c>
-      <c r="H6">
-        <v>9.6</v>
-      </c>
-      <c r="I6">
-        <v>16.5</v>
-      </c>
-      <c r="J6">
-        <v>4</v>
-      </c>
-      <c r="K6">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="L6">
-        <v>1.01</v>
-      </c>
-      <c r="M6">
-        <v>1.01</v>
-      </c>
-      <c r="N6">
-        <v>3.25</v>
-      </c>
-      <c r="O6">
-        <v>1.24</v>
-      </c>
-      <c r="P6">
-        <v>1.99</v>
-      </c>
-      <c r="Q6">
-        <v>1.73</v>
-      </c>
-      <c r="R6">
-        <v>1.38</v>
-      </c>
-      <c r="S6">
-        <v>2.8</v>
-      </c>
-      <c r="T6">
-        <v>2.02</v>
-      </c>
-      <c r="U6">
-        <v>1.56</v>
-      </c>
-      <c r="V6">
-        <v>1.06</v>
-      </c>
-      <c r="W6">
-        <v>3.25</v>
-      </c>
-      <c r="X6">
-        <v>1000</v>
-      </c>
-      <c r="Y6">
-        <v>42</v>
-      </c>
-      <c r="Z6">
-        <v>1000</v>
-      </c>
-      <c r="AA6">
-        <v>1000</v>
-      </c>
-      <c r="AB6">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AC6">
-        <v>1000</v>
-      </c>
-      <c r="AD6">
-        <v>1000</v>
-      </c>
-      <c r="AE6">
-        <v>1000</v>
-      </c>
-      <c r="AF6">
-        <v>9</v>
-      </c>
-      <c r="AG6">
-        <v>1000</v>
-      </c>
-      <c r="AH6">
-        <v>42</v>
-      </c>
-      <c r="AI6">
-        <v>1000</v>
-      </c>
-      <c r="AJ6">
-        <v>1000</v>
-      </c>
-      <c r="AK6">
-        <v>19.5</v>
-      </c>
-      <c r="AL6">
-        <v>1000</v>
-      </c>
-      <c r="AM6">
-        <v>1000</v>
-      </c>
-      <c r="AN6">
-        <v>7.4</v>
-      </c>
-      <c r="AO6">
-        <v>1000</v>
-      </c>
-      <c r="AP6">
-        <v>1.83</v>
-      </c>
-      <c r="AQ6">
-        <v>1.75</v>
-      </c>
-      <c r="AR6">
-        <v>1.83</v>
-      </c>
-      <c r="AS6">
-        <v>1.83</v>
-      </c>
-      <c r="AT6">
-        <v>5.7</v>
-      </c>
-      <c r="AU6">
-        <v>1.83</v>
-      </c>
-      <c r="AV6">
-        <v>1.83</v>
-      </c>
-      <c r="AW6">
-        <v>1.83</v>
-      </c>
-      <c r="AX6">
-        <v>5.6</v>
-      </c>
-      <c r="AY6">
-        <v>1.83</v>
-      </c>
-      <c r="AZ6">
-        <v>1.75</v>
-      </c>
-      <c r="BA6">
-        <v>1.83</v>
-      </c>
-      <c r="BB6">
-        <v>1.83</v>
-      </c>
-      <c r="BC6">
-        <v>1.67</v>
-      </c>
-      <c r="BD6">
-        <v>1.83</v>
-      </c>
-      <c r="BE6">
-        <v>1.83</v>
-      </c>
-      <c r="BF6">
-        <v>4.6</v>
-      </c>
-      <c r="BG6">
-        <v>1.83</v>
-      </c>
-      <c r="BH6">
-        <v>1000</v>
-      </c>
-      <c r="BI6">
-        <v>1.96</v>
-      </c>
-      <c r="BJ6">
-        <v>18</v>
-      </c>
-      <c r="BK6">
-        <v>1.77</v>
-      </c>
-      <c r="BL6">
-        <v>1000</v>
-      </c>
-      <c r="BM6">
-        <v>1.96</v>
-      </c>
-      <c r="BN6">
-        <v>4.8</v>
-      </c>
-      <c r="BO6">
-        <v>2.62</v>
-      </c>
-      <c r="BP6">
-        <v>10.5</v>
-      </c>
-      <c r="BQ6">
-        <v>5.1</v>
-      </c>
-      <c r="BR6">
-        <v>38</v>
-      </c>
-      <c r="BS6">
-        <v>1.87</v>
-      </c>
-      <c r="BT6">
-        <v>20</v>
-      </c>
-      <c r="BU6">
-        <v>1.79</v>
-      </c>
-      <c r="BV6">
-        <v>1000</v>
-      </c>
-      <c r="BW6">
-        <v>1.96</v>
-      </c>
-      <c r="BX6">
-        <v>1000</v>
-      </c>
-      <c r="BY6">
-        <v>1.96</v>
-      </c>
-      <c r="BZ6">
-        <v>19</v>
-      </c>
-      <c r="CA6">
-        <v>1.78</v>
-      </c>
-      <c r="CB6" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="7" spans="1:80">
-      <c r="A7" t="s">
-        <v>85</v>
-      </c>
-      <c r="B7" t="s">
-        <v>86</v>
-      </c>
-      <c r="C7" t="s">
-        <v>90</v>
-      </c>
-      <c r="D7" t="s">
-        <v>96</v>
-      </c>
-      <c r="E7" t="s">
-        <v>102</v>
-      </c>
-      <c r="F7">
-        <v>2.08</v>
-      </c>
-      <c r="G7">
-        <v>2.32</v>
-      </c>
-      <c r="H7">
-        <v>3.2</v>
-      </c>
-      <c r="I7">
-        <v>4</v>
-      </c>
-      <c r="J7">
-        <v>3.7</v>
-      </c>
-      <c r="K7">
-        <v>4.9</v>
-      </c>
-      <c r="L7">
-        <v>0</v>
-      </c>
-      <c r="M7">
-        <v>0</v>
-      </c>
-      <c r="N7">
-        <v>0</v>
-      </c>
-      <c r="O7">
-        <v>0</v>
-      </c>
-      <c r="P7">
-        <v>2.24</v>
-      </c>
-      <c r="Q7">
-        <v>1.6</v>
-      </c>
-      <c r="R7">
-        <v>0</v>
-      </c>
-      <c r="S7">
-        <v>0</v>
-      </c>
-      <c r="T7">
-        <v>0</v>
-      </c>
-      <c r="U7">
-        <v>0</v>
-      </c>
-      <c r="V7">
-        <v>0</v>
-      </c>
-      <c r="W7">
-        <v>0</v>
-      </c>
-      <c r="X7">
-        <v>0</v>
-      </c>
-      <c r="Y7">
-        <v>0</v>
-      </c>
-      <c r="Z7">
-        <v>0</v>
-      </c>
-      <c r="AA7">
-        <v>0</v>
-      </c>
-      <c r="AB7">
-        <v>0</v>
-      </c>
-      <c r="AC7">
-        <v>0</v>
-      </c>
-      <c r="AD7">
-        <v>0</v>
-      </c>
-      <c r="AE7">
-        <v>0</v>
-      </c>
-      <c r="AF7">
-        <v>0</v>
-      </c>
-      <c r="AG7">
-        <v>0</v>
-      </c>
-      <c r="AH7">
-        <v>0</v>
-      </c>
-      <c r="AI7">
-        <v>0</v>
-      </c>
-      <c r="AJ7">
-        <v>0</v>
-      </c>
-      <c r="AK7">
-        <v>0</v>
-      </c>
-      <c r="AL7">
-        <v>0</v>
-      </c>
-      <c r="AM7">
-        <v>0</v>
-      </c>
-      <c r="AN7">
-        <v>0</v>
-      </c>
-      <c r="AO7">
-        <v>0</v>
-      </c>
-      <c r="AP7">
-        <v>0</v>
-      </c>
-      <c r="AQ7">
-        <v>0</v>
-      </c>
-      <c r="AR7">
-        <v>0</v>
-      </c>
-      <c r="AS7">
-        <v>0</v>
-      </c>
-      <c r="AT7">
-        <v>0</v>
-      </c>
-      <c r="AU7">
-        <v>0</v>
-      </c>
-      <c r="AV7">
-        <v>0</v>
-      </c>
-      <c r="AW7">
-        <v>0</v>
-      </c>
-      <c r="AX7">
-        <v>0</v>
-      </c>
-      <c r="AY7">
-        <v>0</v>
-      </c>
-      <c r="AZ7">
-        <v>0</v>
-      </c>
-      <c r="BA7">
-        <v>0</v>
-      </c>
-      <c r="BB7">
-        <v>0</v>
-      </c>
-      <c r="BC7">
-        <v>0</v>
-      </c>
-      <c r="BD7">
-        <v>0</v>
-      </c>
-      <c r="BE7">
-        <v>0</v>
-      </c>
-      <c r="BF7">
-        <v>0</v>
-      </c>
-      <c r="BG7">
-        <v>0</v>
-      </c>
-      <c r="BH7">
-        <v>0</v>
-      </c>
-      <c r="BI7">
-        <v>0</v>
-      </c>
-      <c r="BJ7">
-        <v>0</v>
-      </c>
-      <c r="BK7">
-        <v>0</v>
-      </c>
-      <c r="BL7">
-        <v>0</v>
-      </c>
-      <c r="BM7">
-        <v>0</v>
-      </c>
-      <c r="BN7">
-        <v>0</v>
-      </c>
-      <c r="BO7">
-        <v>0</v>
-      </c>
-      <c r="BP7">
-        <v>0</v>
-      </c>
-      <c r="BQ7">
-        <v>0</v>
-      </c>
-      <c r="BR7">
-        <v>0</v>
-      </c>
-      <c r="BS7">
-        <v>0</v>
-      </c>
-      <c r="BT7">
-        <v>0</v>
-      </c>
-      <c r="BU7">
-        <v>0</v>
-      </c>
-      <c r="BV7">
-        <v>0</v>
-      </c>
-      <c r="BW7">
-        <v>0</v>
-      </c>
-      <c r="BX7">
-        <v>0</v>
-      </c>
-      <c r="BY7">
-        <v>0</v>
-      </c>
-      <c r="BZ7">
-        <v>0</v>
-      </c>
-      <c r="CA7">
-        <v>0</v>
-      </c>
-      <c r="CB7" t="s">
-        <v>103</v>
+        <v>92</v>
       </c>
     </row>
   </sheetData>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-08-11.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-08-11.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="98" uniqueCount="93">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="116" uniqueCount="104">
   <si>
     <t>League</t>
   </si>
@@ -262,9 +262,18 @@
     <t>Chilean Primera Division</t>
   </si>
   <si>
+    <t>Ecuadorian Serie A</t>
+  </si>
+  <si>
     <t>Argentinian Primera Division</t>
   </si>
   <si>
+    <t>Colombian Primera A</t>
+  </si>
+  <si>
+    <t>Swedish Superettan</t>
+  </si>
+  <si>
     <t>2026-08-11</t>
   </si>
   <si>
@@ -274,25 +283,49 @@
     <t>00:15:00</t>
   </si>
   <si>
+    <t>01:05:00</t>
+  </si>
+  <si>
+    <t>17:00:00</t>
+  </si>
+  <si>
     <t>America MG (W)</t>
   </si>
   <si>
     <t>Audax Italiano</t>
   </si>
   <si>
+    <t>Deportivo Cuenca</t>
+  </si>
+  <si>
     <t>Union Santa Fe</t>
   </si>
   <si>
+    <t>Junior FC Barranquilla</t>
+  </si>
+  <si>
+    <t>Helsingborgs</t>
+  </si>
+  <si>
     <t>CR Flamengo (W)</t>
   </si>
   <si>
     <t>Nublense</t>
   </si>
   <si>
+    <t>Manta FC</t>
+  </si>
+  <si>
     <t>Central Cordoba (SdE)</t>
   </si>
   <si>
-    <t>2026-08-09 10:29:56</t>
+    <t>Deportivo Pereira</t>
+  </si>
+  <si>
+    <t>Varnamo</t>
+  </si>
+  <si>
+    <t>2026-08-09 12:44:25</t>
   </si>
 </sst>
 </file>
@@ -624,7 +657,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:CB4"/>
+  <dimension ref="A1:CB7"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:80">
@@ -874,31 +907,31 @@
         <v>80</v>
       </c>
       <c r="B2" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="C2" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="D2" t="s">
-        <v>86</v>
+        <v>91</v>
       </c>
       <c r="E2" t="s">
-        <v>89</v>
+        <v>97</v>
       </c>
       <c r="F2">
-        <v>1.08</v>
+        <v>4</v>
       </c>
       <c r="G2">
         <v>970</v>
       </c>
       <c r="H2">
-        <v>1.08</v>
+        <v>1.15</v>
       </c>
       <c r="I2">
-        <v>970</v>
+        <v>2.4</v>
       </c>
       <c r="J2">
-        <v>1.06</v>
+        <v>3</v>
       </c>
       <c r="K2">
         <v>950</v>
@@ -910,7 +943,7 @@
         <v>1.01</v>
       </c>
       <c r="N2">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="O2">
         <v>1.18</v>
@@ -934,7 +967,7 @@
         <v>1.01</v>
       </c>
       <c r="V2">
-        <v>1.02</v>
+        <v>1.71</v>
       </c>
       <c r="W2">
         <v>1.01</v>
@@ -1108,7 +1141,7 @@
         <v>1.01</v>
       </c>
       <c r="CB2" t="s">
-        <v>92</v>
+        <v>103</v>
       </c>
     </row>
     <row r="3" spans="1:80">
@@ -1116,16 +1149,16 @@
         <v>81</v>
       </c>
       <c r="B3" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="C3" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="D3" t="s">
-        <v>87</v>
+        <v>92</v>
       </c>
       <c r="E3" t="s">
-        <v>90</v>
+        <v>98</v>
       </c>
       <c r="F3">
         <v>2.4</v>
@@ -1143,7 +1176,7 @@
         <v>3.1</v>
       </c>
       <c r="K3">
-        <v>3.6</v>
+        <v>3.55</v>
       </c>
       <c r="L3">
         <v>1.44</v>
@@ -1350,7 +1383,7 @@
         <v>4.2</v>
       </c>
       <c r="CB3" t="s">
-        <v>92</v>
+        <v>103</v>
       </c>
     </row>
     <row r="4" spans="1:80">
@@ -1358,130 +1391,130 @@
         <v>82</v>
       </c>
       <c r="B4" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="C4" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="D4" t="s">
-        <v>88</v>
+        <v>93</v>
       </c>
       <c r="E4" t="s">
-        <v>91</v>
+        <v>99</v>
       </c>
       <c r="F4">
-        <v>1.52</v>
+        <v>1.62</v>
       </c>
       <c r="G4">
-        <v>1.59</v>
+        <v>1.75</v>
       </c>
       <c r="H4">
-        <v>7.8</v>
+        <v>6.6</v>
       </c>
       <c r="I4">
-        <v>9.199999999999999</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="J4">
-        <v>4</v>
+        <v>3.55</v>
       </c>
       <c r="K4">
-        <v>4.4</v>
+        <v>3.95</v>
       </c>
       <c r="L4">
-        <v>1.01</v>
+        <v>1.46</v>
       </c>
       <c r="M4">
-        <v>1.08</v>
+        <v>1.11</v>
       </c>
       <c r="N4">
-        <v>3.25</v>
+        <v>2.68</v>
       </c>
       <c r="O4">
-        <v>1.36</v>
+        <v>1.49</v>
       </c>
       <c r="P4">
-        <v>1.76</v>
+        <v>1.56</v>
       </c>
       <c r="Q4">
-        <v>2.08</v>
+        <v>2.44</v>
       </c>
       <c r="R4">
-        <v>1.29</v>
+        <v>1.2</v>
       </c>
       <c r="S4">
-        <v>3.9</v>
+        <v>4.5</v>
       </c>
       <c r="T4">
-        <v>2.16</v>
+        <v>2.3</v>
       </c>
       <c r="U4">
-        <v>1.71</v>
+        <v>1.63</v>
       </c>
       <c r="V4">
-        <v>1.12</v>
+        <v>1.14</v>
       </c>
       <c r="W4">
-        <v>2.7</v>
+        <v>2.32</v>
       </c>
       <c r="X4">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="Y4">
-        <v>25</v>
+        <v>19.5</v>
       </c>
       <c r="Z4">
-        <v>80</v>
+        <v>70</v>
       </c>
       <c r="AA4">
-        <v>360</v>
+        <v>330</v>
       </c>
       <c r="AB4">
-        <v>7.8</v>
+        <v>6.8</v>
       </c>
       <c r="AC4">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AD4">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="AE4">
         <v>180</v>
       </c>
       <c r="AF4">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AG4">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="AH4">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="AI4">
-        <v>160</v>
+        <v>190</v>
       </c>
       <c r="AJ4">
-        <v>16.5</v>
+        <v>20</v>
       </c>
       <c r="AK4">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="AL4">
-        <v>55</v>
+        <v>70</v>
       </c>
       <c r="AM4">
-        <v>230</v>
+        <v>300</v>
       </c>
       <c r="AN4">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="AO4">
-        <v>290</v>
+        <v>350</v>
       </c>
       <c r="AP4">
-        <v>11</v>
+        <v>7.6</v>
       </c>
       <c r="AQ4">
-        <v>16.5</v>
+        <v>13</v>
       </c>
       <c r="AR4">
         <v>5</v>
@@ -1490,109 +1523,835 @@
         <v>5.3</v>
       </c>
       <c r="AT4">
-        <v>5.9</v>
+        <v>4.7</v>
       </c>
       <c r="AU4">
-        <v>8.199999999999999</v>
+        <v>7.4</v>
       </c>
       <c r="AV4">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="AW4">
         <v>5.2</v>
       </c>
       <c r="AX4">
+        <v>6.6</v>
+      </c>
+      <c r="AY4">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AZ4">
+        <v>4.7</v>
+      </c>
+      <c r="BA4">
+        <v>5.3</v>
+      </c>
+      <c r="BB4">
+        <v>13</v>
+      </c>
+      <c r="BC4">
+        <v>17.5</v>
+      </c>
+      <c r="BD4">
+        <v>5</v>
+      </c>
+      <c r="BE4">
+        <v>5.3</v>
+      </c>
+      <c r="BF4">
+        <v>12.5</v>
+      </c>
+      <c r="BG4">
+        <v>5.3</v>
+      </c>
+      <c r="BH4">
+        <v>2.94</v>
+      </c>
+      <c r="BI4">
+        <v>2.4</v>
+      </c>
+      <c r="BJ4">
+        <v>13.5</v>
+      </c>
+      <c r="BK4">
+        <v>5.9</v>
+      </c>
+      <c r="BL4">
+        <v>1000</v>
+      </c>
+      <c r="BM4">
+        <v>10</v>
+      </c>
+      <c r="BN4">
+        <v>4.1</v>
+      </c>
+      <c r="BO4">
+        <v>3.4</v>
+      </c>
+      <c r="BP4">
+        <v>13</v>
+      </c>
+      <c r="BQ4">
+        <v>5.8</v>
+      </c>
+      <c r="BR4">
+        <v>1000</v>
+      </c>
+      <c r="BS4">
+        <v>8.4</v>
+      </c>
+      <c r="BT4">
+        <v>11</v>
+      </c>
+      <c r="BU4">
+        <v>5.4</v>
+      </c>
+      <c r="BV4">
+        <v>1000</v>
+      </c>
+      <c r="BW4">
+        <v>9.4</v>
+      </c>
+      <c r="BX4">
+        <v>1000</v>
+      </c>
+      <c r="BY4">
+        <v>9.6</v>
+      </c>
+      <c r="BZ4">
+        <v>1000</v>
+      </c>
+      <c r="CA4">
+        <v>8</v>
+      </c>
+      <c r="CB4" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="5" spans="1:80">
+      <c r="A5" t="s">
+        <v>83</v>
+      </c>
+      <c r="B5" t="s">
+        <v>86</v>
+      </c>
+      <c r="C5" t="s">
+        <v>88</v>
+      </c>
+      <c r="D5" t="s">
+        <v>94</v>
+      </c>
+      <c r="E5" t="s">
+        <v>100</v>
+      </c>
+      <c r="F5">
+        <v>1.52</v>
+      </c>
+      <c r="G5">
+        <v>1.59</v>
+      </c>
+      <c r="H5">
+        <v>7.8</v>
+      </c>
+      <c r="I5">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="J5">
+        <v>4</v>
+      </c>
+      <c r="K5">
+        <v>4.4</v>
+      </c>
+      <c r="L5">
+        <v>1.01</v>
+      </c>
+      <c r="M5">
+        <v>1.08</v>
+      </c>
+      <c r="N5">
+        <v>3.25</v>
+      </c>
+      <c r="O5">
+        <v>1.36</v>
+      </c>
+      <c r="P5">
+        <v>1.76</v>
+      </c>
+      <c r="Q5">
+        <v>2.08</v>
+      </c>
+      <c r="R5">
+        <v>1.29</v>
+      </c>
+      <c r="S5">
+        <v>3.9</v>
+      </c>
+      <c r="T5">
+        <v>2.16</v>
+      </c>
+      <c r="U5">
+        <v>1.71</v>
+      </c>
+      <c r="V5">
+        <v>1.12</v>
+      </c>
+      <c r="W5">
+        <v>2.7</v>
+      </c>
+      <c r="X5">
+        <v>15</v>
+      </c>
+      <c r="Y5">
+        <v>25</v>
+      </c>
+      <c r="Z5">
+        <v>80</v>
+      </c>
+      <c r="AA5">
+        <v>360</v>
+      </c>
+      <c r="AB5">
+        <v>7.8</v>
+      </c>
+      <c r="AC5">
+        <v>11</v>
+      </c>
+      <c r="AD5">
+        <v>36</v>
+      </c>
+      <c r="AE5">
+        <v>180</v>
+      </c>
+      <c r="AF5">
+        <v>9.6</v>
+      </c>
+      <c r="AG5">
+        <v>12</v>
+      </c>
+      <c r="AH5">
+        <v>32</v>
+      </c>
+      <c r="AI5">
+        <v>160</v>
+      </c>
+      <c r="AJ5">
+        <v>16.5</v>
+      </c>
+      <c r="AK5">
+        <v>22</v>
+      </c>
+      <c r="AL5">
+        <v>55</v>
+      </c>
+      <c r="AM5">
+        <v>230</v>
+      </c>
+      <c r="AN5">
+        <v>12</v>
+      </c>
+      <c r="AO5">
+        <v>290</v>
+      </c>
+      <c r="AP5">
+        <v>11</v>
+      </c>
+      <c r="AQ5">
+        <v>16.5</v>
+      </c>
+      <c r="AR5">
+        <v>5</v>
+      </c>
+      <c r="AS5">
+        <v>5.3</v>
+      </c>
+      <c r="AT5">
+        <v>5.9</v>
+      </c>
+      <c r="AU5">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AV5">
+        <v>4.6</v>
+      </c>
+      <c r="AW5">
+        <v>5.2</v>
+      </c>
+      <c r="AX5">
         <v>6.4</v>
       </c>
-      <c r="AY4">
+      <c r="AY5">
         <v>9</v>
       </c>
-      <c r="AZ4">
+      <c r="AZ5">
         <v>21</v>
       </c>
-      <c r="BA4">
+      <c r="BA5">
         <v>5.2</v>
       </c>
-      <c r="BB4">
+      <c r="BB5">
         <v>11</v>
       </c>
-      <c r="BC4">
+      <c r="BC5">
         <v>15.5</v>
       </c>
-      <c r="BD4">
+      <c r="BD5">
         <v>4.9</v>
       </c>
-      <c r="BE4">
+      <c r="BE5">
         <v>5.2</v>
       </c>
-      <c r="BF4">
+      <c r="BF5">
         <v>8.199999999999999</v>
       </c>
-      <c r="BG4">
+      <c r="BG5">
         <v>5.2</v>
       </c>
-      <c r="BH4">
-        <v>1000</v>
-      </c>
-      <c r="BI4">
+      <c r="BH5">
+        <v>1000</v>
+      </c>
+      <c r="BI5">
         <v>1.82</v>
       </c>
-      <c r="BJ4">
+      <c r="BJ5">
         <v>17</v>
       </c>
-      <c r="BK4">
+      <c r="BK5">
         <v>1.64</v>
       </c>
-      <c r="BL4">
-        <v>1000</v>
-      </c>
-      <c r="BM4">
+      <c r="BL5">
+        <v>1000</v>
+      </c>
+      <c r="BM5">
         <v>1.82</v>
       </c>
-      <c r="BN4">
+      <c r="BN5">
         <v>5</v>
       </c>
-      <c r="BO4">
+      <c r="BO5">
         <v>2.84</v>
       </c>
-      <c r="BP4">
+      <c r="BP5">
         <v>14.5</v>
       </c>
-      <c r="BQ4">
+      <c r="BQ5">
         <v>1.62</v>
       </c>
-      <c r="BR4">
+      <c r="BR5">
         <v>44</v>
       </c>
-      <c r="BS4">
+      <c r="BS5">
         <v>1.75</v>
       </c>
-      <c r="BT4">
+      <c r="BT5">
         <v>15.5</v>
       </c>
-      <c r="BU4">
+      <c r="BU5">
         <v>1.63</v>
       </c>
-      <c r="BV4">
-        <v>1000</v>
-      </c>
-      <c r="BW4">
+      <c r="BV5">
+        <v>1000</v>
+      </c>
+      <c r="BW5">
         <v>1.82</v>
       </c>
-      <c r="BX4">
-        <v>1000</v>
-      </c>
-      <c r="BY4">
+      <c r="BX5">
+        <v>1000</v>
+      </c>
+      <c r="BY5">
         <v>1.82</v>
       </c>
-      <c r="BZ4">
+      <c r="BZ5">
         <v>30</v>
       </c>
-      <c r="CA4">
+      <c r="CA5">
         <v>1.72</v>
       </c>
-      <c r="CB4" t="s">
-        <v>92</v>
+      <c r="CB5" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="6" spans="1:80">
+      <c r="A6" t="s">
+        <v>84</v>
+      </c>
+      <c r="B6" t="s">
+        <v>86</v>
+      </c>
+      <c r="C6" t="s">
+        <v>89</v>
+      </c>
+      <c r="D6" t="s">
+        <v>95</v>
+      </c>
+      <c r="E6" t="s">
+        <v>101</v>
+      </c>
+      <c r="F6">
+        <v>1.32</v>
+      </c>
+      <c r="G6">
+        <v>1.39</v>
+      </c>
+      <c r="H6">
+        <v>11.5</v>
+      </c>
+      <c r="I6">
+        <v>16</v>
+      </c>
+      <c r="J6">
+        <v>5.1</v>
+      </c>
+      <c r="K6">
+        <v>6.2</v>
+      </c>
+      <c r="L6">
+        <v>1.35</v>
+      </c>
+      <c r="M6">
+        <v>1.05</v>
+      </c>
+      <c r="N6">
+        <v>4.2</v>
+      </c>
+      <c r="O6">
+        <v>1.26</v>
+      </c>
+      <c r="P6">
+        <v>2.1</v>
+      </c>
+      <c r="Q6">
+        <v>1.76</v>
+      </c>
+      <c r="R6">
+        <v>1.41</v>
+      </c>
+      <c r="S6">
+        <v>2.96</v>
+      </c>
+      <c r="T6">
+        <v>2.24</v>
+      </c>
+      <c r="U6">
+        <v>1.68</v>
+      </c>
+      <c r="V6">
+        <v>1.06</v>
+      </c>
+      <c r="W6">
+        <v>3.55</v>
+      </c>
+      <c r="X6">
+        <v>22</v>
+      </c>
+      <c r="Y6">
+        <v>40</v>
+      </c>
+      <c r="Z6">
+        <v>140</v>
+      </c>
+      <c r="AA6">
+        <v>1000</v>
+      </c>
+      <c r="AB6">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AC6">
+        <v>14.5</v>
+      </c>
+      <c r="AD6">
+        <v>55</v>
+      </c>
+      <c r="AE6">
+        <v>290</v>
+      </c>
+      <c r="AF6">
+        <v>8.6</v>
+      </c>
+      <c r="AG6">
+        <v>12.5</v>
+      </c>
+      <c r="AH6">
+        <v>40</v>
+      </c>
+      <c r="AI6">
+        <v>220</v>
+      </c>
+      <c r="AJ6">
+        <v>12</v>
+      </c>
+      <c r="AK6">
+        <v>18.5</v>
+      </c>
+      <c r="AL6">
+        <v>55</v>
+      </c>
+      <c r="AM6">
+        <v>260</v>
+      </c>
+      <c r="AN6">
+        <v>7</v>
+      </c>
+      <c r="AO6">
+        <v>470</v>
+      </c>
+      <c r="AP6">
+        <v>14</v>
+      </c>
+      <c r="AQ6">
+        <v>4.6</v>
+      </c>
+      <c r="AR6">
+        <v>5.1</v>
+      </c>
+      <c r="AS6">
+        <v>5.3</v>
+      </c>
+      <c r="AT6">
+        <v>6</v>
+      </c>
+      <c r="AU6">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AV6">
+        <v>4.8</v>
+      </c>
+      <c r="AW6">
+        <v>5.2</v>
+      </c>
+      <c r="AX6">
+        <v>5.9</v>
+      </c>
+      <c r="AY6">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AZ6">
+        <v>4.6</v>
+      </c>
+      <c r="BA6">
+        <v>5.1</v>
+      </c>
+      <c r="BB6">
+        <v>8</v>
+      </c>
+      <c r="BC6">
+        <v>12</v>
+      </c>
+      <c r="BD6">
+        <v>4.8</v>
+      </c>
+      <c r="BE6">
+        <v>5.2</v>
+      </c>
+      <c r="BF6">
+        <v>4.8</v>
+      </c>
+      <c r="BG6">
+        <v>5.2</v>
+      </c>
+      <c r="BH6">
+        <v>3.95</v>
+      </c>
+      <c r="BI6">
+        <v>3.1</v>
+      </c>
+      <c r="BJ6">
+        <v>14</v>
+      </c>
+      <c r="BK6">
+        <v>6</v>
+      </c>
+      <c r="BL6">
+        <v>1000</v>
+      </c>
+      <c r="BM6">
+        <v>10</v>
+      </c>
+      <c r="BN6">
+        <v>3.75</v>
+      </c>
+      <c r="BO6">
+        <v>2.98</v>
+      </c>
+      <c r="BP6">
+        <v>8</v>
+      </c>
+      <c r="BQ6">
+        <v>6</v>
+      </c>
+      <c r="BR6">
+        <v>28</v>
+      </c>
+      <c r="BS6">
+        <v>7.6</v>
+      </c>
+      <c r="BT6">
+        <v>15.5</v>
+      </c>
+      <c r="BU6">
+        <v>6.2</v>
+      </c>
+      <c r="BV6">
+        <v>1000</v>
+      </c>
+      <c r="BW6">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="BX6">
+        <v>1000</v>
+      </c>
+      <c r="BY6">
+        <v>9.6</v>
+      </c>
+      <c r="BZ6">
+        <v>14.5</v>
+      </c>
+      <c r="CA6">
+        <v>6</v>
+      </c>
+      <c r="CB6" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="7" spans="1:80">
+      <c r="A7" t="s">
+        <v>85</v>
+      </c>
+      <c r="B7" t="s">
+        <v>86</v>
+      </c>
+      <c r="C7" t="s">
+        <v>90</v>
+      </c>
+      <c r="D7" t="s">
+        <v>96</v>
+      </c>
+      <c r="E7" t="s">
+        <v>102</v>
+      </c>
+      <c r="F7">
+        <v>2.12</v>
+      </c>
+      <c r="G7">
+        <v>2.3</v>
+      </c>
+      <c r="H7">
+        <v>3.25</v>
+      </c>
+      <c r="I7">
+        <v>3.55</v>
+      </c>
+      <c r="J7">
+        <v>3.75</v>
+      </c>
+      <c r="K7">
+        <v>4.2</v>
+      </c>
+      <c r="L7">
+        <v>0</v>
+      </c>
+      <c r="M7">
+        <v>0</v>
+      </c>
+      <c r="N7">
+        <v>0</v>
+      </c>
+      <c r="O7">
+        <v>0</v>
+      </c>
+      <c r="P7">
+        <v>2.28</v>
+      </c>
+      <c r="Q7">
+        <v>1.68</v>
+      </c>
+      <c r="R7">
+        <v>0</v>
+      </c>
+      <c r="S7">
+        <v>0</v>
+      </c>
+      <c r="T7">
+        <v>0</v>
+      </c>
+      <c r="U7">
+        <v>0</v>
+      </c>
+      <c r="V7">
+        <v>0</v>
+      </c>
+      <c r="W7">
+        <v>0</v>
+      </c>
+      <c r="X7">
+        <v>0</v>
+      </c>
+      <c r="Y7">
+        <v>0</v>
+      </c>
+      <c r="Z7">
+        <v>0</v>
+      </c>
+      <c r="AA7">
+        <v>0</v>
+      </c>
+      <c r="AB7">
+        <v>0</v>
+      </c>
+      <c r="AC7">
+        <v>0</v>
+      </c>
+      <c r="AD7">
+        <v>0</v>
+      </c>
+      <c r="AE7">
+        <v>0</v>
+      </c>
+      <c r="AF7">
+        <v>0</v>
+      </c>
+      <c r="AG7">
+        <v>0</v>
+      </c>
+      <c r="AH7">
+        <v>0</v>
+      </c>
+      <c r="AI7">
+        <v>0</v>
+      </c>
+      <c r="AJ7">
+        <v>0</v>
+      </c>
+      <c r="AK7">
+        <v>0</v>
+      </c>
+      <c r="AL7">
+        <v>0</v>
+      </c>
+      <c r="AM7">
+        <v>0</v>
+      </c>
+      <c r="AN7">
+        <v>0</v>
+      </c>
+      <c r="AO7">
+        <v>0</v>
+      </c>
+      <c r="AP7">
+        <v>0</v>
+      </c>
+      <c r="AQ7">
+        <v>0</v>
+      </c>
+      <c r="AR7">
+        <v>0</v>
+      </c>
+      <c r="AS7">
+        <v>0</v>
+      </c>
+      <c r="AT7">
+        <v>0</v>
+      </c>
+      <c r="AU7">
+        <v>0</v>
+      </c>
+      <c r="AV7">
+        <v>0</v>
+      </c>
+      <c r="AW7">
+        <v>0</v>
+      </c>
+      <c r="AX7">
+        <v>0</v>
+      </c>
+      <c r="AY7">
+        <v>0</v>
+      </c>
+      <c r="AZ7">
+        <v>0</v>
+      </c>
+      <c r="BA7">
+        <v>0</v>
+      </c>
+      <c r="BB7">
+        <v>0</v>
+      </c>
+      <c r="BC7">
+        <v>0</v>
+      </c>
+      <c r="BD7">
+        <v>0</v>
+      </c>
+      <c r="BE7">
+        <v>0</v>
+      </c>
+      <c r="BF7">
+        <v>0</v>
+      </c>
+      <c r="BG7">
+        <v>0</v>
+      </c>
+      <c r="BH7">
+        <v>0</v>
+      </c>
+      <c r="BI7">
+        <v>0</v>
+      </c>
+      <c r="BJ7">
+        <v>0</v>
+      </c>
+      <c r="BK7">
+        <v>0</v>
+      </c>
+      <c r="BL7">
+        <v>0</v>
+      </c>
+      <c r="BM7">
+        <v>0</v>
+      </c>
+      <c r="BN7">
+        <v>0</v>
+      </c>
+      <c r="BO7">
+        <v>0</v>
+      </c>
+      <c r="BP7">
+        <v>0</v>
+      </c>
+      <c r="BQ7">
+        <v>0</v>
+      </c>
+      <c r="BR7">
+        <v>0</v>
+      </c>
+      <c r="BS7">
+        <v>0</v>
+      </c>
+      <c r="BT7">
+        <v>0</v>
+      </c>
+      <c r="BU7">
+        <v>0</v>
+      </c>
+      <c r="BV7">
+        <v>0</v>
+      </c>
+      <c r="BW7">
+        <v>0</v>
+      </c>
+      <c r="BX7">
+        <v>0</v>
+      </c>
+      <c r="BY7">
+        <v>0</v>
+      </c>
+      <c r="BZ7">
+        <v>0</v>
+      </c>
+      <c r="CA7">
+        <v>0</v>
+      </c>
+      <c r="CB7" t="s">
+        <v>103</v>
       </c>
     </row>
   </sheetData>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-08-11.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-08-11.xlsx
@@ -325,7 +325,7 @@
     <t>Varnamo</t>
   </si>
   <si>
-    <t>2026-08-09 12:44:25</t>
+    <t>2026-08-09 14:56:31</t>
   </si>
 </sst>
 </file>
@@ -967,7 +967,7 @@
         <v>1.01</v>
       </c>
       <c r="V2">
-        <v>1.71</v>
+        <v>1.73</v>
       </c>
       <c r="W2">
         <v>1.01</v>
@@ -1191,7 +1191,7 @@
         <v>1.37</v>
       </c>
       <c r="P3">
-        <v>1.8</v>
+        <v>1.83</v>
       </c>
       <c r="Q3">
         <v>2.08</v>
@@ -1586,7 +1586,7 @@
         <v>4.1</v>
       </c>
       <c r="BO4">
-        <v>3.4</v>
+        <v>3.15</v>
       </c>
       <c r="BP4">
         <v>13</v>
@@ -1663,7 +1663,7 @@
         <v>4.4</v>
       </c>
       <c r="L5">
-        <v>1.01</v>
+        <v>1.43</v>
       </c>
       <c r="M5">
         <v>1.08</v>
@@ -1702,10 +1702,10 @@
         <v>15</v>
       </c>
       <c r="Y5">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="Z5">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="AA5">
         <v>360</v>
@@ -1714,40 +1714,40 @@
         <v>7.8</v>
       </c>
       <c r="AC5">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AD5">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="AE5">
         <v>180</v>
       </c>
       <c r="AF5">
-        <v>9.6</v>
+        <v>8.6</v>
       </c>
       <c r="AG5">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AH5">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="AI5">
         <v>160</v>
       </c>
       <c r="AJ5">
-        <v>16.5</v>
+        <v>15</v>
       </c>
       <c r="AK5">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AL5">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="AM5">
         <v>230</v>
       </c>
       <c r="AN5">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AO5">
         <v>290</v>
@@ -1759,10 +1759,10 @@
         <v>16.5</v>
       </c>
       <c r="AR5">
-        <v>5</v>
+        <v>6.8</v>
       </c>
       <c r="AS5">
-        <v>5.3</v>
+        <v>7.4</v>
       </c>
       <c r="AT5">
         <v>5.9</v>
@@ -1771,10 +1771,10 @@
         <v>8.199999999999999</v>
       </c>
       <c r="AV5">
-        <v>4.6</v>
+        <v>6.2</v>
       </c>
       <c r="AW5">
-        <v>5.2</v>
+        <v>7.2</v>
       </c>
       <c r="AX5">
         <v>6.4</v>
@@ -1786,7 +1786,7 @@
         <v>21</v>
       </c>
       <c r="BA5">
-        <v>5.2</v>
+        <v>7.2</v>
       </c>
       <c r="BB5">
         <v>11</v>
@@ -1795,76 +1795,76 @@
         <v>15.5</v>
       </c>
       <c r="BD5">
-        <v>4.9</v>
+        <v>6.6</v>
       </c>
       <c r="BE5">
-        <v>5.2</v>
+        <v>7.4</v>
       </c>
       <c r="BF5">
         <v>8.199999999999999</v>
       </c>
       <c r="BG5">
-        <v>5.2</v>
+        <v>7.4</v>
       </c>
       <c r="BH5">
-        <v>1000</v>
+        <v>3.4</v>
       </c>
       <c r="BI5">
-        <v>1.82</v>
+        <v>2.72</v>
       </c>
       <c r="BJ5">
-        <v>17</v>
+        <v>12.5</v>
       </c>
       <c r="BK5">
-        <v>1.64</v>
+        <v>5.7</v>
       </c>
       <c r="BL5">
         <v>1000</v>
       </c>
       <c r="BM5">
-        <v>1.82</v>
+        <v>10</v>
       </c>
       <c r="BN5">
-        <v>5</v>
+        <v>3.95</v>
       </c>
       <c r="BO5">
-        <v>2.84</v>
+        <v>3.1</v>
       </c>
       <c r="BP5">
-        <v>14.5</v>
+        <v>11</v>
       </c>
       <c r="BQ5">
-        <v>1.62</v>
+        <v>5.4</v>
       </c>
       <c r="BR5">
-        <v>44</v>
+        <v>32</v>
       </c>
       <c r="BS5">
-        <v>1.75</v>
+        <v>8</v>
       </c>
       <c r="BT5">
-        <v>15.5</v>
+        <v>11.5</v>
       </c>
       <c r="BU5">
-        <v>1.63</v>
+        <v>5.5</v>
       </c>
       <c r="BV5">
-        <v>1000</v>
+        <v>85</v>
       </c>
       <c r="BW5">
-        <v>1.82</v>
+        <v>9.4</v>
       </c>
       <c r="BX5">
         <v>1000</v>
       </c>
       <c r="BY5">
-        <v>1.82</v>
+        <v>9.6</v>
       </c>
       <c r="BZ5">
-        <v>30</v>
+        <v>23</v>
       </c>
       <c r="CA5">
-        <v>1.72</v>
+        <v>7.2</v>
       </c>
       <c r="CB5" t="s">
         <v>103</v>
@@ -1899,7 +1899,7 @@
         <v>16</v>
       </c>
       <c r="J6">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="K6">
         <v>6.2</v>
@@ -1917,28 +1917,28 @@
         <v>1.26</v>
       </c>
       <c r="P6">
-        <v>2.1</v>
+        <v>2.06</v>
       </c>
       <c r="Q6">
         <v>1.76</v>
       </c>
       <c r="R6">
-        <v>1.41</v>
+        <v>1.43</v>
       </c>
       <c r="S6">
         <v>2.96</v>
       </c>
       <c r="T6">
-        <v>2.24</v>
+        <v>2.2</v>
       </c>
       <c r="U6">
-        <v>1.68</v>
+        <v>1.66</v>
       </c>
       <c r="V6">
         <v>1.06</v>
       </c>
       <c r="W6">
-        <v>3.55</v>
+        <v>3.35</v>
       </c>
       <c r="X6">
         <v>22</v>
@@ -2141,22 +2141,22 @@
         <v>3.55</v>
       </c>
       <c r="J7">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="K7">
         <v>4.2</v>
       </c>
       <c r="L7">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="M7">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="N7">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="O7">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="P7">
         <v>2.28</v>
@@ -2165,184 +2165,184 @@
         <v>1.68</v>
       </c>
       <c r="R7">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="S7">
-        <v>0</v>
+        <v>2.68</v>
       </c>
       <c r="T7">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="U7">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="V7">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="W7">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="X7">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="Y7">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="Z7">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="AA7">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="AB7">
-        <v>0</v>
+        <v>15.5</v>
       </c>
       <c r="AC7">
-        <v>0</v>
+        <v>11.5</v>
       </c>
       <c r="AD7">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="AE7">
-        <v>0</v>
+        <v>44</v>
       </c>
       <c r="AF7">
-        <v>0</v>
+        <v>19.5</v>
       </c>
       <c r="AG7">
-        <v>0</v>
+        <v>13.5</v>
       </c>
       <c r="AH7">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="AI7">
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="AJ7">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="AK7">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="AL7">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="AM7">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="AN7">
-        <v>0</v>
+        <v>15.5</v>
       </c>
       <c r="AO7">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="AP7">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="AQ7">
-        <v>0</v>
+        <v>14.5</v>
       </c>
       <c r="AR7">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="AS7">
-        <v>0</v>
+        <v>5.2</v>
       </c>
       <c r="AT7">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="AU7">
-        <v>0</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AV7">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="AW7">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="AX7">
-        <v>0</v>
+        <v>11.5</v>
       </c>
       <c r="AY7">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="AZ7">
-        <v>0</v>
+        <v>11.5</v>
       </c>
       <c r="BA7">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="BB7">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="BC7">
-        <v>0</v>
+        <v>15.5</v>
       </c>
       <c r="BD7">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="BE7">
-        <v>0</v>
+        <v>5.2</v>
       </c>
       <c r="BF7">
-        <v>0</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BG7">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="BH7">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="BI7">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="BJ7">
-        <v>0</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BK7">
-        <v>0</v>
+        <v>6.6</v>
       </c>
       <c r="BL7">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM7">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="BN7">
-        <v>0</v>
+        <v>5.4</v>
       </c>
       <c r="BO7">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="BP7">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="BQ7">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="BR7">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS7">
-        <v>0</v>
+        <v>14.5</v>
       </c>
       <c r="BT7">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="BU7">
-        <v>0</v>
+        <v>5.2</v>
       </c>
       <c r="BV7">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="BW7">
-        <v>0</v>
+        <v>14.5</v>
       </c>
       <c r="BX7">
-        <v>0</v>
+        <v>46</v>
       </c>
       <c r="BY7">
-        <v>0</v>
+        <v>18.5</v>
       </c>
       <c r="BZ7">
         <v>0</v>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-08-11.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-08-11.xlsx
@@ -325,7 +325,7 @@
     <t>Varnamo</t>
   </si>
   <si>
-    <t>2026-08-09 14:56:31</t>
+    <t>2026-08-09 17:07:04</t>
   </si>
 </sst>
 </file>
@@ -967,7 +967,7 @@
         <v>1.01</v>
       </c>
       <c r="V2">
-        <v>1.73</v>
+        <v>1.76</v>
       </c>
       <c r="W2">
         <v>1.01</v>
@@ -1173,7 +1173,7 @@
         <v>3.45</v>
       </c>
       <c r="J3">
-        <v>3.1</v>
+        <v>3.25</v>
       </c>
       <c r="K3">
         <v>3.55</v>
@@ -1403,7 +1403,7 @@
         <v>99</v>
       </c>
       <c r="F4">
-        <v>1.62</v>
+        <v>1.63</v>
       </c>
       <c r="G4">
         <v>1.75</v>
@@ -1645,7 +1645,7 @@
         <v>100</v>
       </c>
       <c r="F5">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="G5">
         <v>1.59</v>
@@ -1663,16 +1663,16 @@
         <v>4.4</v>
       </c>
       <c r="L5">
-        <v>1.43</v>
+        <v>1.38</v>
       </c>
       <c r="M5">
         <v>1.08</v>
       </c>
       <c r="N5">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="O5">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="P5">
         <v>1.76</v>
@@ -1687,7 +1687,7 @@
         <v>3.9</v>
       </c>
       <c r="T5">
-        <v>2.16</v>
+        <v>2.18</v>
       </c>
       <c r="U5">
         <v>1.71</v>
@@ -1711,7 +1711,7 @@
         <v>360</v>
       </c>
       <c r="AB5">
-        <v>7.8</v>
+        <v>7.2</v>
       </c>
       <c r="AC5">
         <v>10</v>
@@ -1759,10 +1759,10 @@
         <v>16.5</v>
       </c>
       <c r="AR5">
-        <v>6.8</v>
+        <v>7.4</v>
       </c>
       <c r="AS5">
-        <v>7.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AT5">
         <v>5.9</v>
@@ -1771,10 +1771,10 @@
         <v>8.199999999999999</v>
       </c>
       <c r="AV5">
-        <v>6.2</v>
+        <v>6.6</v>
       </c>
       <c r="AW5">
-        <v>7.2</v>
+        <v>8</v>
       </c>
       <c r="AX5">
         <v>6.4</v>
@@ -1786,7 +1786,7 @@
         <v>21</v>
       </c>
       <c r="BA5">
-        <v>7.2</v>
+        <v>7.8</v>
       </c>
       <c r="BB5">
         <v>11</v>
@@ -1795,16 +1795,16 @@
         <v>15.5</v>
       </c>
       <c r="BD5">
-        <v>6.6</v>
+        <v>7</v>
       </c>
       <c r="BE5">
-        <v>7.4</v>
+        <v>8</v>
       </c>
       <c r="BF5">
         <v>8.199999999999999</v>
       </c>
       <c r="BG5">
-        <v>7.4</v>
+        <v>8</v>
       </c>
       <c r="BH5">
         <v>3.4</v>
@@ -1887,7 +1887,7 @@
         <v>101</v>
       </c>
       <c r="F6">
-        <v>1.32</v>
+        <v>1.3</v>
       </c>
       <c r="G6">
         <v>1.39</v>
@@ -1899,13 +1899,13 @@
         <v>16</v>
       </c>
       <c r="J6">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="K6">
         <v>6.2</v>
       </c>
       <c r="L6">
-        <v>1.35</v>
+        <v>1.3</v>
       </c>
       <c r="M6">
         <v>1.05</v>
@@ -1917,13 +1917,13 @@
         <v>1.26</v>
       </c>
       <c r="P6">
-        <v>2.06</v>
+        <v>2.08</v>
       </c>
       <c r="Q6">
         <v>1.76</v>
       </c>
       <c r="R6">
-        <v>1.43</v>
+        <v>1.41</v>
       </c>
       <c r="S6">
         <v>2.96</v>
@@ -1932,13 +1932,13 @@
         <v>2.2</v>
       </c>
       <c r="U6">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="V6">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="W6">
-        <v>3.35</v>
+        <v>3.55</v>
       </c>
       <c r="X6">
         <v>22</v>
@@ -2144,13 +2144,13 @@
         <v>3.8</v>
       </c>
       <c r="K7">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="L7">
-        <v>1.33</v>
+        <v>1.27</v>
       </c>
       <c r="M7">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="N7">
         <v>4.8</v>
@@ -2168,13 +2168,13 @@
         <v>1.51</v>
       </c>
       <c r="S7">
-        <v>2.68</v>
+        <v>2.7</v>
       </c>
       <c r="T7">
-        <v>1.5</v>
+        <v>1.61</v>
       </c>
       <c r="U7">
-        <v>2.16</v>
+        <v>2.4</v>
       </c>
       <c r="V7">
         <v>1.39</v>
@@ -2237,10 +2237,10 @@
         <v>32</v>
       </c>
       <c r="AP7">
-        <v>4.5</v>
+        <v>15</v>
       </c>
       <c r="AQ7">
-        <v>14.5</v>
+        <v>12</v>
       </c>
       <c r="AR7">
         <v>19</v>
@@ -2279,7 +2279,7 @@
         <v>15.5</v>
       </c>
       <c r="BD7">
-        <v>4.7</v>
+        <v>21</v>
       </c>
       <c r="BE7">
         <v>5.2</v>
@@ -2300,13 +2300,13 @@
         <v>8.800000000000001</v>
       </c>
       <c r="BK7">
-        <v>6.6</v>
+        <v>1.01</v>
       </c>
       <c r="BL7">
         <v>1000</v>
       </c>
       <c r="BM7">
-        <v>21</v>
+        <v>1.01</v>
       </c>
       <c r="BN7">
         <v>5.4</v>
@@ -2318,13 +2318,13 @@
         <v>15</v>
       </c>
       <c r="BQ7">
-        <v>13</v>
+        <v>1.01</v>
       </c>
       <c r="BR7">
         <v>1000</v>
       </c>
       <c r="BS7">
-        <v>14.5</v>
+        <v>1.01</v>
       </c>
       <c r="BT7">
         <v>7</v>
@@ -2336,13 +2336,13 @@
         <v>34</v>
       </c>
       <c r="BW7">
-        <v>14.5</v>
+        <v>1.01</v>
       </c>
       <c r="BX7">
         <v>46</v>
       </c>
       <c r="BY7">
-        <v>18.5</v>
+        <v>1.01</v>
       </c>
       <c r="BZ7">
         <v>0</v>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-08-11.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-08-11.xlsx
@@ -325,7 +325,7 @@
     <t>Varnamo</t>
   </si>
   <si>
-    <t>2026-08-09 17:07:04</t>
+    <t>2026-08-09 19:17:25</t>
   </si>
 </sst>
 </file>
@@ -967,7 +967,7 @@
         <v>1.01</v>
       </c>
       <c r="V2">
-        <v>1.76</v>
+        <v>1.78</v>
       </c>
       <c r="W2">
         <v>1.01</v>
@@ -1164,16 +1164,16 @@
         <v>2.4</v>
       </c>
       <c r="G3">
-        <v>2.58</v>
+        <v>2.56</v>
       </c>
       <c r="H3">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="I3">
         <v>3.45</v>
       </c>
       <c r="J3">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="K3">
         <v>3.55</v>
@@ -1272,7 +1272,7 @@
         <v>11</v>
       </c>
       <c r="AQ3">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AR3">
         <v>16</v>
@@ -1403,7 +1403,7 @@
         <v>99</v>
       </c>
       <c r="F4">
-        <v>1.63</v>
+        <v>1.62</v>
       </c>
       <c r="G4">
         <v>1.75</v>
@@ -1460,7 +1460,7 @@
         <v>11</v>
       </c>
       <c r="Y4">
-        <v>19.5</v>
+        <v>18</v>
       </c>
       <c r="Z4">
         <v>70</v>
@@ -1481,10 +1481,10 @@
         <v>180</v>
       </c>
       <c r="AF4">
-        <v>9.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="AG4">
-        <v>12.5</v>
+        <v>11.5</v>
       </c>
       <c r="AH4">
         <v>36</v>
@@ -1517,22 +1517,22 @@
         <v>13</v>
       </c>
       <c r="AR4">
-        <v>5</v>
+        <v>5.6</v>
       </c>
       <c r="AS4">
-        <v>5.3</v>
+        <v>6</v>
       </c>
       <c r="AT4">
-        <v>4.7</v>
+        <v>5.2</v>
       </c>
       <c r="AU4">
         <v>7.4</v>
       </c>
       <c r="AV4">
-        <v>4.7</v>
+        <v>5.1</v>
       </c>
       <c r="AW4">
-        <v>5.2</v>
+        <v>5.9</v>
       </c>
       <c r="AX4">
         <v>6.6</v>
@@ -1541,10 +1541,10 @@
         <v>8.199999999999999</v>
       </c>
       <c r="AZ4">
-        <v>4.7</v>
+        <v>5.2</v>
       </c>
       <c r="BA4">
-        <v>5.3</v>
+        <v>5.9</v>
       </c>
       <c r="BB4">
         <v>13</v>
@@ -1553,16 +1553,16 @@
         <v>17.5</v>
       </c>
       <c r="BD4">
-        <v>5</v>
+        <v>5.6</v>
       </c>
       <c r="BE4">
-        <v>5.3</v>
+        <v>6</v>
       </c>
       <c r="BF4">
         <v>12.5</v>
       </c>
       <c r="BG4">
-        <v>5.3</v>
+        <v>6</v>
       </c>
       <c r="BH4">
         <v>2.94</v>
@@ -1574,7 +1574,7 @@
         <v>13.5</v>
       </c>
       <c r="BK4">
-        <v>5.9</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BL4">
         <v>1000</v>
@@ -1592,7 +1592,7 @@
         <v>13</v>
       </c>
       <c r="BQ4">
-        <v>5.8</v>
+        <v>9.4</v>
       </c>
       <c r="BR4">
         <v>1000</v>
@@ -1654,7 +1654,7 @@
         <v>7.8</v>
       </c>
       <c r="I5">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="J5">
         <v>4</v>
@@ -1663,7 +1663,7 @@
         <v>4.4</v>
       </c>
       <c r="L5">
-        <v>1.38</v>
+        <v>1.43</v>
       </c>
       <c r="M5">
         <v>1.08</v>
@@ -1687,16 +1687,16 @@
         <v>3.9</v>
       </c>
       <c r="T5">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="U5">
-        <v>1.71</v>
+        <v>1.72</v>
       </c>
       <c r="V5">
         <v>1.12</v>
       </c>
       <c r="W5">
-        <v>2.7</v>
+        <v>2.68</v>
       </c>
       <c r="X5">
         <v>15</v>
@@ -1705,10 +1705,10 @@
         <v>23</v>
       </c>
       <c r="Z5">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="AA5">
-        <v>360</v>
+        <v>350</v>
       </c>
       <c r="AB5">
         <v>7.2</v>
@@ -1717,7 +1717,7 @@
         <v>10</v>
       </c>
       <c r="AD5">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AE5">
         <v>180</v>
@@ -1738,13 +1738,13 @@
         <v>15</v>
       </c>
       <c r="AK5">
-        <v>21</v>
+        <v>19.5</v>
       </c>
       <c r="AL5">
         <v>50</v>
       </c>
       <c r="AM5">
-        <v>230</v>
+        <v>220</v>
       </c>
       <c r="AN5">
         <v>11</v>
@@ -1759,10 +1759,10 @@
         <v>16.5</v>
       </c>
       <c r="AR5">
-        <v>7.4</v>
+        <v>7.8</v>
       </c>
       <c r="AS5">
-        <v>8.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="AT5">
         <v>5.9</v>
@@ -1771,10 +1771,10 @@
         <v>8.199999999999999</v>
       </c>
       <c r="AV5">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="AW5">
-        <v>8</v>
+        <v>8.4</v>
       </c>
       <c r="AX5">
         <v>6.4</v>
@@ -1786,7 +1786,7 @@
         <v>21</v>
       </c>
       <c r="BA5">
-        <v>7.8</v>
+        <v>8.4</v>
       </c>
       <c r="BB5">
         <v>11</v>
@@ -1795,16 +1795,16 @@
         <v>15.5</v>
       </c>
       <c r="BD5">
-        <v>7</v>
+        <v>7.4</v>
       </c>
       <c r="BE5">
-        <v>8</v>
+        <v>8.4</v>
       </c>
       <c r="BF5">
         <v>8.199999999999999</v>
       </c>
       <c r="BG5">
-        <v>8</v>
+        <v>8.6</v>
       </c>
       <c r="BH5">
         <v>3.4</v>
@@ -1890,7 +1890,7 @@
         <v>1.3</v>
       </c>
       <c r="G6">
-        <v>1.39</v>
+        <v>1.37</v>
       </c>
       <c r="H6">
         <v>11.5</v>
@@ -1905,7 +1905,7 @@
         <v>6.2</v>
       </c>
       <c r="L6">
-        <v>1.3</v>
+        <v>1.34</v>
       </c>
       <c r="M6">
         <v>1.05</v>
@@ -1938,7 +1938,7 @@
         <v>1.07</v>
       </c>
       <c r="W6">
-        <v>3.55</v>
+        <v>3.7</v>
       </c>
       <c r="X6">
         <v>22</v>
@@ -1980,7 +1980,7 @@
         <v>12</v>
       </c>
       <c r="AK6">
-        <v>18.5</v>
+        <v>16.5</v>
       </c>
       <c r="AL6">
         <v>55</v>
@@ -1992,19 +1992,19 @@
         <v>7</v>
       </c>
       <c r="AO6">
-        <v>470</v>
+        <v>480</v>
       </c>
       <c r="AP6">
         <v>14</v>
       </c>
       <c r="AQ6">
-        <v>4.6</v>
+        <v>4.8</v>
       </c>
       <c r="AR6">
-        <v>5.1</v>
+        <v>5.3</v>
       </c>
       <c r="AS6">
-        <v>5.3</v>
+        <v>5.5</v>
       </c>
       <c r="AT6">
         <v>6</v>
@@ -2013,22 +2013,22 @@
         <v>9.800000000000001</v>
       </c>
       <c r="AV6">
-        <v>4.8</v>
+        <v>5</v>
       </c>
       <c r="AW6">
-        <v>5.2</v>
+        <v>5.4</v>
       </c>
       <c r="AX6">
         <v>5.9</v>
       </c>
       <c r="AY6">
-        <v>8.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="AZ6">
-        <v>4.6</v>
+        <v>4.8</v>
       </c>
       <c r="BA6">
-        <v>5.1</v>
+        <v>5.3</v>
       </c>
       <c r="BB6">
         <v>8</v>
@@ -2037,16 +2037,16 @@
         <v>12</v>
       </c>
       <c r="BD6">
-        <v>4.8</v>
+        <v>5</v>
       </c>
       <c r="BE6">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="BF6">
         <v>4.8</v>
       </c>
       <c r="BG6">
-        <v>5.2</v>
+        <v>5.4</v>
       </c>
       <c r="BH6">
         <v>3.95</v>
@@ -2240,7 +2240,7 @@
         <v>15</v>
       </c>
       <c r="AQ7">
-        <v>12</v>
+        <v>14.5</v>
       </c>
       <c r="AR7">
         <v>19</v>
@@ -2264,7 +2264,7 @@
         <v>11.5</v>
       </c>
       <c r="AY7">
-        <v>10</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AZ7">
         <v>11.5</v>
@@ -2279,7 +2279,7 @@
         <v>15.5</v>
       </c>
       <c r="BD7">
-        <v>21</v>
+        <v>4.7</v>
       </c>
       <c r="BE7">
         <v>5.2</v>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-08-11.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-08-11.xlsx
@@ -325,7 +325,7 @@
     <t>Varnamo</t>
   </si>
   <si>
-    <t>2026-08-09 19:17:25</t>
+    <t>2026-08-09 21:25:51</t>
   </si>
 </sst>
 </file>
@@ -943,22 +943,22 @@
         <v>1.01</v>
       </c>
       <c r="N2">
-        <v>4.8</v>
+        <v>1.29</v>
       </c>
       <c r="O2">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="P2">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="Q2">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="R2">
         <v>1.18</v>
       </c>
       <c r="S2">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="T2">
         <v>1.01</v>
@@ -967,7 +967,7 @@
         <v>1.01</v>
       </c>
       <c r="V2">
-        <v>1.78</v>
+        <v>1.8</v>
       </c>
       <c r="W2">
         <v>1.01</v>
@@ -1161,7 +1161,7 @@
         <v>98</v>
       </c>
       <c r="F3">
-        <v>2.4</v>
+        <v>2.42</v>
       </c>
       <c r="G3">
         <v>2.56</v>
@@ -1170,16 +1170,16 @@
         <v>3.1</v>
       </c>
       <c r="I3">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="J3">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="K3">
         <v>3.55</v>
       </c>
       <c r="L3">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="M3">
         <v>1.08</v>
@@ -1194,16 +1194,16 @@
         <v>1.83</v>
       </c>
       <c r="Q3">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="R3">
         <v>1.31</v>
       </c>
       <c r="S3">
-        <v>3.8</v>
+        <v>3.9</v>
       </c>
       <c r="T3">
-        <v>1.82</v>
+        <v>1.83</v>
       </c>
       <c r="U3">
         <v>2.06</v>
@@ -1215,7 +1215,7 @@
         <v>1.64</v>
       </c>
       <c r="X3">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="Y3">
         <v>14.5</v>
@@ -1224,7 +1224,7 @@
         <v>32</v>
       </c>
       <c r="AA3">
-        <v>75</v>
+        <v>85</v>
       </c>
       <c r="AB3">
         <v>12</v>
@@ -1278,7 +1278,7 @@
         <v>16</v>
       </c>
       <c r="AS3">
-        <v>4.7</v>
+        <v>5.1</v>
       </c>
       <c r="AT3">
         <v>8.6</v>
@@ -1287,10 +1287,10 @@
         <v>6.8</v>
       </c>
       <c r="AV3">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="AW3">
-        <v>4.6</v>
+        <v>4.9</v>
       </c>
       <c r="AX3">
         <v>13.5</v>
@@ -1299,34 +1299,34 @@
         <v>10</v>
       </c>
       <c r="AZ3">
-        <v>4.1</v>
+        <v>4.4</v>
       </c>
       <c r="BA3">
-        <v>4.7</v>
+        <v>5.1</v>
       </c>
       <c r="BB3">
-        <v>4.5</v>
+        <v>4.9</v>
       </c>
       <c r="BC3">
         <v>20</v>
       </c>
       <c r="BD3">
-        <v>4.6</v>
+        <v>5</v>
       </c>
       <c r="BE3">
-        <v>4.9</v>
+        <v>5.3</v>
       </c>
       <c r="BF3">
         <v>17.5</v>
       </c>
       <c r="BG3">
-        <v>4.6</v>
+        <v>4.9</v>
       </c>
       <c r="BH3">
         <v>3.7</v>
       </c>
       <c r="BI3">
-        <v>2.58</v>
+        <v>2.56</v>
       </c>
       <c r="BJ3">
         <v>12</v>
@@ -1344,13 +1344,13 @@
         <v>6.4</v>
       </c>
       <c r="BO3">
+        <v>4.1</v>
+      </c>
+      <c r="BP3">
+        <v>24</v>
+      </c>
+      <c r="BQ3">
         <v>4</v>
-      </c>
-      <c r="BP3">
-        <v>23</v>
-      </c>
-      <c r="BQ3">
-        <v>3.95</v>
       </c>
       <c r="BR3">
         <v>42</v>
@@ -1359,28 +1359,28 @@
         <v>4.3</v>
       </c>
       <c r="BT3">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="BU3">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="BV3">
         <v>32</v>
       </c>
       <c r="BW3">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="BX3">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="BY3">
+        <v>4.4</v>
+      </c>
+      <c r="BZ3">
+        <v>40</v>
+      </c>
+      <c r="CA3">
         <v>4.3</v>
-      </c>
-      <c r="BZ3">
-        <v>38</v>
-      </c>
-      <c r="CA3">
-        <v>4.2</v>
       </c>
       <c r="CB3" t="s">
         <v>103</v>
@@ -1403,19 +1403,19 @@
         <v>99</v>
       </c>
       <c r="F4">
-        <v>1.62</v>
+        <v>1.64</v>
       </c>
       <c r="G4">
-        <v>1.75</v>
+        <v>1.73</v>
       </c>
       <c r="H4">
         <v>6.6</v>
       </c>
       <c r="I4">
-        <v>8.199999999999999</v>
+        <v>7.8</v>
       </c>
       <c r="J4">
-        <v>3.55</v>
+        <v>3.45</v>
       </c>
       <c r="K4">
         <v>3.95</v>
@@ -1427,13 +1427,13 @@
         <v>1.11</v>
       </c>
       <c r="N4">
-        <v>2.68</v>
+        <v>2.7</v>
       </c>
       <c r="O4">
-        <v>1.49</v>
+        <v>1.5</v>
       </c>
       <c r="P4">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="Q4">
         <v>2.44</v>
@@ -1454,7 +1454,7 @@
         <v>1.14</v>
       </c>
       <c r="W4">
-        <v>2.32</v>
+        <v>2.36</v>
       </c>
       <c r="X4">
         <v>11</v>
@@ -1463,40 +1463,40 @@
         <v>18</v>
       </c>
       <c r="Z4">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="AA4">
-        <v>330</v>
+        <v>320</v>
       </c>
       <c r="AB4">
-        <v>6.8</v>
+        <v>6.4</v>
       </c>
       <c r="AC4">
         <v>10</v>
       </c>
       <c r="AD4">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AE4">
         <v>180</v>
       </c>
       <c r="AF4">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AG4">
         <v>11.5</v>
       </c>
       <c r="AH4">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="AI4">
         <v>190</v>
       </c>
       <c r="AJ4">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="AK4">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="AL4">
         <v>70</v>
@@ -1505,10 +1505,10 @@
         <v>300</v>
       </c>
       <c r="AN4">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="AO4">
-        <v>350</v>
+        <v>340</v>
       </c>
       <c r="AP4">
         <v>7.6</v>
@@ -1517,10 +1517,10 @@
         <v>13</v>
       </c>
       <c r="AR4">
-        <v>5.6</v>
+        <v>6.8</v>
       </c>
       <c r="AS4">
-        <v>6</v>
+        <v>7.6</v>
       </c>
       <c r="AT4">
         <v>5.2</v>
@@ -1529,22 +1529,22 @@
         <v>7.4</v>
       </c>
       <c r="AV4">
-        <v>5.1</v>
+        <v>6.2</v>
       </c>
       <c r="AW4">
-        <v>5.9</v>
+        <v>7.4</v>
       </c>
       <c r="AX4">
         <v>6.6</v>
       </c>
       <c r="AY4">
-        <v>8.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="AZ4">
-        <v>5.2</v>
+        <v>6.2</v>
       </c>
       <c r="BA4">
-        <v>5.9</v>
+        <v>7.4</v>
       </c>
       <c r="BB4">
         <v>13</v>
@@ -1553,16 +1553,16 @@
         <v>17.5</v>
       </c>
       <c r="BD4">
-        <v>5.6</v>
+        <v>7</v>
       </c>
       <c r="BE4">
-        <v>6</v>
+        <v>7.4</v>
       </c>
       <c r="BF4">
         <v>12.5</v>
       </c>
       <c r="BG4">
-        <v>6</v>
+        <v>7.6</v>
       </c>
       <c r="BH4">
         <v>2.94</v>
@@ -1574,7 +1574,7 @@
         <v>13.5</v>
       </c>
       <c r="BK4">
-        <v>9.800000000000001</v>
+        <v>5.9</v>
       </c>
       <c r="BL4">
         <v>1000</v>
@@ -1648,40 +1648,40 @@
         <v>1.53</v>
       </c>
       <c r="G5">
-        <v>1.59</v>
+        <v>1.54</v>
       </c>
       <c r="H5">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="I5">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="J5">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="K5">
         <v>4.4</v>
       </c>
       <c r="L5">
-        <v>1.43</v>
+        <v>1.38</v>
       </c>
       <c r="M5">
         <v>1.08</v>
       </c>
       <c r="N5">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="O5">
         <v>1.37</v>
       </c>
       <c r="P5">
-        <v>1.76</v>
+        <v>1.8</v>
       </c>
       <c r="Q5">
-        <v>2.08</v>
+        <v>2.12</v>
       </c>
       <c r="R5">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="S5">
         <v>3.9</v>
@@ -1693,16 +1693,16 @@
         <v>1.72</v>
       </c>
       <c r="V5">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="W5">
-        <v>2.68</v>
+        <v>2.84</v>
       </c>
       <c r="X5">
         <v>15</v>
       </c>
       <c r="Y5">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="Z5">
         <v>70</v>
@@ -1714,13 +1714,13 @@
         <v>7.2</v>
       </c>
       <c r="AC5">
-        <v>10</v>
+        <v>9.6</v>
       </c>
       <c r="AD5">
         <v>32</v>
       </c>
       <c r="AE5">
-        <v>180</v>
+        <v>170</v>
       </c>
       <c r="AF5">
         <v>8.6</v>
@@ -1729,7 +1729,7 @@
         <v>11</v>
       </c>
       <c r="AH5">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AI5">
         <v>160</v>
@@ -1759,10 +1759,10 @@
         <v>16.5</v>
       </c>
       <c r="AR5">
-        <v>7.8</v>
+        <v>8.4</v>
       </c>
       <c r="AS5">
-        <v>8.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AT5">
         <v>5.9</v>
@@ -1771,13 +1771,13 @@
         <v>8.199999999999999</v>
       </c>
       <c r="AV5">
-        <v>6.8</v>
+        <v>7.2</v>
       </c>
       <c r="AW5">
-        <v>8.4</v>
+        <v>9</v>
       </c>
       <c r="AX5">
-        <v>6.4</v>
+        <v>7.2</v>
       </c>
       <c r="AY5">
         <v>9</v>
@@ -1786,25 +1786,25 @@
         <v>21</v>
       </c>
       <c r="BA5">
-        <v>8.4</v>
+        <v>9</v>
       </c>
       <c r="BB5">
         <v>11</v>
       </c>
       <c r="BC5">
-        <v>15.5</v>
+        <v>16.5</v>
       </c>
       <c r="BD5">
-        <v>7.4</v>
+        <v>8</v>
       </c>
       <c r="BE5">
-        <v>8.4</v>
+        <v>9</v>
       </c>
       <c r="BF5">
         <v>8.199999999999999</v>
       </c>
       <c r="BG5">
-        <v>8.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BH5">
         <v>3.4</v>
@@ -1887,7 +1887,7 @@
         <v>101</v>
       </c>
       <c r="F6">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="G6">
         <v>1.37</v>
@@ -1980,7 +1980,7 @@
         <v>12</v>
       </c>
       <c r="AK6">
-        <v>16.5</v>
+        <v>17.5</v>
       </c>
       <c r="AL6">
         <v>55</v>
@@ -1998,13 +1998,13 @@
         <v>14</v>
       </c>
       <c r="AQ6">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="AR6">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="AS6">
-        <v>5.5</v>
+        <v>5.4</v>
       </c>
       <c r="AT6">
         <v>6</v>
@@ -2013,22 +2013,22 @@
         <v>9.800000000000001</v>
       </c>
       <c r="AV6">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="AW6">
-        <v>5.4</v>
+        <v>5.3</v>
       </c>
       <c r="AX6">
         <v>5.9</v>
       </c>
       <c r="AY6">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AZ6">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="BA6">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="BB6">
         <v>8</v>
@@ -2037,16 +2037,16 @@
         <v>12</v>
       </c>
       <c r="BD6">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="BE6">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="BF6">
         <v>4.8</v>
       </c>
       <c r="BG6">
-        <v>5.4</v>
+        <v>5.3</v>
       </c>
       <c r="BH6">
         <v>3.95</v>
@@ -2237,10 +2237,10 @@
         <v>32</v>
       </c>
       <c r="AP7">
-        <v>15</v>
+        <v>4.5</v>
       </c>
       <c r="AQ7">
-        <v>14.5</v>
+        <v>12</v>
       </c>
       <c r="AR7">
         <v>19</v>
@@ -2264,7 +2264,7 @@
         <v>11.5</v>
       </c>
       <c r="AY7">
-        <v>8.199999999999999</v>
+        <v>10</v>
       </c>
       <c r="AZ7">
         <v>11.5</v>
@@ -2279,7 +2279,7 @@
         <v>15.5</v>
       </c>
       <c r="BD7">
-        <v>4.7</v>
+        <v>21</v>
       </c>
       <c r="BE7">
         <v>5.2</v>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-08-11.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-08-11.xlsx
@@ -325,7 +325,7 @@
     <t>Varnamo</t>
   </si>
   <si>
-    <t>2026-08-09 21:25:51</t>
+    <t>2026-08-09 23:35:02</t>
   </si>
 </sst>
 </file>
@@ -919,226 +919,226 @@
         <v>97</v>
       </c>
       <c r="F2">
-        <v>4</v>
+        <v>9.4</v>
       </c>
       <c r="G2">
-        <v>970</v>
+        <v>15</v>
       </c>
       <c r="H2">
-        <v>1.15</v>
+        <v>1.31</v>
       </c>
       <c r="I2">
-        <v>2.4</v>
+        <v>1.37</v>
       </c>
       <c r="J2">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="K2">
-        <v>950</v>
+        <v>6.4</v>
       </c>
       <c r="L2">
-        <v>1.01</v>
+        <v>1.29</v>
       </c>
       <c r="M2">
         <v>1.01</v>
       </c>
       <c r="N2">
-        <v>1.29</v>
+        <v>4.8</v>
       </c>
       <c r="O2">
         <v>1.19</v>
       </c>
       <c r="P2">
-        <v>1.29</v>
+        <v>2.24</v>
       </c>
       <c r="Q2">
-        <v>1.19</v>
+        <v>1.61</v>
       </c>
       <c r="R2">
-        <v>1.18</v>
+        <v>1.5</v>
       </c>
       <c r="S2">
-        <v>1.19</v>
+        <v>2.54</v>
       </c>
       <c r="T2">
-        <v>1.01</v>
+        <v>2.04</v>
       </c>
       <c r="U2">
-        <v>1.01</v>
+        <v>1.75</v>
       </c>
       <c r="V2">
-        <v>1.8</v>
+        <v>3.55</v>
       </c>
       <c r="W2">
-        <v>1.01</v>
+        <v>1.07</v>
       </c>
       <c r="X2">
-        <v>1000</v>
+        <v>28</v>
       </c>
       <c r="Y2">
-        <v>1000</v>
+        <v>9.4</v>
       </c>
       <c r="Z2">
-        <v>1000</v>
+        <v>8.6</v>
       </c>
       <c r="AA2">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="AB2">
-        <v>1000</v>
+        <v>46</v>
       </c>
       <c r="AC2">
-        <v>1000</v>
+        <v>14</v>
       </c>
       <c r="AD2">
-        <v>1000</v>
+        <v>13</v>
       </c>
       <c r="AE2">
-        <v>1000</v>
+        <v>15.5</v>
       </c>
       <c r="AF2">
-        <v>1000</v>
+        <v>140</v>
       </c>
       <c r="AG2">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AH2">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="AI2">
-        <v>1000</v>
+        <v>46</v>
       </c>
       <c r="AJ2">
-        <v>1000</v>
+        <v>550</v>
       </c>
       <c r="AK2">
-        <v>1000</v>
+        <v>240</v>
       </c>
       <c r="AL2">
-        <v>1000</v>
+        <v>180</v>
       </c>
       <c r="AM2">
-        <v>1000</v>
+        <v>200</v>
       </c>
       <c r="AN2">
-        <v>1000</v>
+        <v>310</v>
       </c>
       <c r="AO2">
-        <v>1000</v>
+        <v>5.3</v>
       </c>
       <c r="AP2">
-        <v>1.03</v>
+        <v>5.5</v>
       </c>
       <c r="AQ2">
-        <v>1.03</v>
+        <v>3.95</v>
       </c>
       <c r="AR2">
-        <v>1.03</v>
+        <v>3.8</v>
       </c>
       <c r="AS2">
-        <v>1.03</v>
+        <v>4.4</v>
       </c>
       <c r="AT2">
-        <v>1.03</v>
+        <v>6</v>
       </c>
       <c r="AU2">
-        <v>1.03</v>
+        <v>4.6</v>
       </c>
       <c r="AV2">
-        <v>1.03</v>
+        <v>4.5</v>
       </c>
       <c r="AW2">
-        <v>1.03</v>
+        <v>4.8</v>
       </c>
       <c r="AX2">
-        <v>1.03</v>
+        <v>6.6</v>
       </c>
       <c r="AY2">
-        <v>1.03</v>
+        <v>6</v>
       </c>
       <c r="AZ2">
-        <v>1.03</v>
+        <v>5.8</v>
       </c>
       <c r="BA2">
-        <v>1.03</v>
+        <v>6</v>
       </c>
       <c r="BB2">
-        <v>1.03</v>
+        <v>6.8</v>
       </c>
       <c r="BC2">
-        <v>1.03</v>
+        <v>6.6</v>
       </c>
       <c r="BD2">
-        <v>1.03</v>
+        <v>6.6</v>
       </c>
       <c r="BE2">
-        <v>1.03</v>
+        <v>6.6</v>
       </c>
       <c r="BF2">
-        <v>1.01</v>
+        <v>6.8</v>
       </c>
       <c r="BG2">
-        <v>1.01</v>
+        <v>3</v>
       </c>
       <c r="BH2">
-        <v>1000</v>
+        <v>4.9</v>
       </c>
       <c r="BI2">
-        <v>1.01</v>
+        <v>2.42</v>
       </c>
       <c r="BJ2">
-        <v>1000</v>
+        <v>15</v>
       </c>
       <c r="BK2">
-        <v>1.01</v>
+        <v>3.65</v>
       </c>
       <c r="BL2">
         <v>1000</v>
       </c>
       <c r="BM2">
-        <v>1.01</v>
+        <v>4.7</v>
       </c>
       <c r="BN2">
-        <v>1000</v>
+        <v>17.5</v>
       </c>
       <c r="BO2">
-        <v>1.01</v>
+        <v>3.75</v>
       </c>
       <c r="BP2">
         <v>1000</v>
       </c>
       <c r="BQ2">
-        <v>1.01</v>
+        <v>4.6</v>
       </c>
       <c r="BR2">
         <v>1000</v>
       </c>
       <c r="BS2">
-        <v>1.01</v>
+        <v>4.6</v>
       </c>
       <c r="BT2">
-        <v>1000</v>
+        <v>4.4</v>
       </c>
       <c r="BU2">
-        <v>1.01</v>
+        <v>2.3</v>
       </c>
       <c r="BV2">
-        <v>1000</v>
+        <v>9</v>
       </c>
       <c r="BW2">
-        <v>1.01</v>
+        <v>3.15</v>
       </c>
       <c r="BX2">
-        <v>1000</v>
+        <v>29</v>
       </c>
       <c r="BY2">
-        <v>1.01</v>
+        <v>4.1</v>
       </c>
       <c r="BZ2">
-        <v>1000</v>
+        <v>14</v>
       </c>
       <c r="CA2">
-        <v>1.01</v>
+        <v>3.6</v>
       </c>
       <c r="CB2" t="s">
         <v>103</v>
@@ -1164,7 +1164,7 @@
         <v>2.42</v>
       </c>
       <c r="G3">
-        <v>2.56</v>
+        <v>2.62</v>
       </c>
       <c r="H3">
         <v>3.1</v>
@@ -1209,10 +1209,10 @@
         <v>2.06</v>
       </c>
       <c r="V3">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="W3">
-        <v>1.64</v>
+        <v>1.62</v>
       </c>
       <c r="X3">
         <v>15</v>
@@ -1230,7 +1230,7 @@
         <v>12</v>
       </c>
       <c r="AC3">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="AD3">
         <v>17</v>
@@ -1278,7 +1278,7 @@
         <v>16</v>
       </c>
       <c r="AS3">
-        <v>5.1</v>
+        <v>5.3</v>
       </c>
       <c r="AT3">
         <v>8.6</v>
@@ -1290,7 +1290,7 @@
         <v>12</v>
       </c>
       <c r="AW3">
-        <v>4.9</v>
+        <v>5.1</v>
       </c>
       <c r="AX3">
         <v>13.5</v>
@@ -1299,28 +1299,28 @@
         <v>10</v>
       </c>
       <c r="AZ3">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="BA3">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="BB3">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="BC3">
         <v>20</v>
       </c>
       <c r="BD3">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="BE3">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="BF3">
         <v>17.5</v>
       </c>
       <c r="BG3">
-        <v>4.9</v>
+        <v>5.1</v>
       </c>
       <c r="BH3">
         <v>3.7</v>
@@ -1406,7 +1406,7 @@
         <v>1.64</v>
       </c>
       <c r="G4">
-        <v>1.73</v>
+        <v>1.76</v>
       </c>
       <c r="H4">
         <v>6.6</v>
@@ -1433,7 +1433,7 @@
         <v>1.5</v>
       </c>
       <c r="P4">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="Q4">
         <v>2.44</v>
@@ -1454,13 +1454,13 @@
         <v>1.14</v>
       </c>
       <c r="W4">
-        <v>2.36</v>
+        <v>2.32</v>
       </c>
       <c r="X4">
         <v>11</v>
       </c>
       <c r="Y4">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="Z4">
         <v>65</v>
@@ -1487,7 +1487,7 @@
         <v>11.5</v>
       </c>
       <c r="AH4">
-        <v>32</v>
+        <v>950</v>
       </c>
       <c r="AI4">
         <v>190</v>
@@ -1499,7 +1499,7 @@
         <v>24</v>
       </c>
       <c r="AL4">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="AM4">
         <v>300</v>
@@ -1514,25 +1514,25 @@
         <v>7.6</v>
       </c>
       <c r="AQ4">
-        <v>13</v>
+        <v>14.5</v>
       </c>
       <c r="AR4">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="AS4">
         <v>7.6</v>
       </c>
       <c r="AT4">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="AU4">
         <v>7.4</v>
       </c>
       <c r="AV4">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="AW4">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="AX4">
         <v>6.6</v>
@@ -1541,10 +1541,10 @@
         <v>9</v>
       </c>
       <c r="AZ4">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="BA4">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="BB4">
         <v>13</v>
@@ -1556,13 +1556,13 @@
         <v>7</v>
       </c>
       <c r="BE4">
-        <v>7.4</v>
+        <v>7.8</v>
       </c>
       <c r="BF4">
         <v>12.5</v>
       </c>
       <c r="BG4">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="BH4">
         <v>2.94</v>
@@ -1592,7 +1592,7 @@
         <v>13</v>
       </c>
       <c r="BQ4">
-        <v>9.4</v>
+        <v>5.8</v>
       </c>
       <c r="BR4">
         <v>1000</v>
@@ -1645,25 +1645,25 @@
         <v>100</v>
       </c>
       <c r="F5">
-        <v>1.53</v>
+        <v>1.56</v>
       </c>
       <c r="G5">
-        <v>1.54</v>
+        <v>1.6</v>
       </c>
       <c r="H5">
-        <v>7.6</v>
+        <v>7.2</v>
       </c>
       <c r="I5">
-        <v>8.800000000000001</v>
+        <v>8</v>
       </c>
       <c r="J5">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="K5">
         <v>4.4</v>
       </c>
       <c r="L5">
-        <v>1.38</v>
+        <v>1.43</v>
       </c>
       <c r="M5">
         <v>1.08</v>
@@ -1678,13 +1678,13 @@
         <v>1.8</v>
       </c>
       <c r="Q5">
-        <v>2.12</v>
+        <v>2.16</v>
       </c>
       <c r="R5">
         <v>1.3</v>
       </c>
       <c r="S5">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="T5">
         <v>2.2</v>
@@ -1693,22 +1693,22 @@
         <v>1.72</v>
       </c>
       <c r="V5">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="W5">
-        <v>2.84</v>
+        <v>2.68</v>
       </c>
       <c r="X5">
         <v>15</v>
       </c>
       <c r="Y5">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="Z5">
         <v>70</v>
       </c>
       <c r="AA5">
-        <v>350</v>
+        <v>330</v>
       </c>
       <c r="AB5">
         <v>7.2</v>
@@ -1732,7 +1732,7 @@
         <v>28</v>
       </c>
       <c r="AI5">
-        <v>160</v>
+        <v>150</v>
       </c>
       <c r="AJ5">
         <v>15</v>
@@ -1750,7 +1750,7 @@
         <v>11</v>
       </c>
       <c r="AO5">
-        <v>290</v>
+        <v>270</v>
       </c>
       <c r="AP5">
         <v>11</v>
@@ -1759,22 +1759,22 @@
         <v>16.5</v>
       </c>
       <c r="AR5">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="AS5">
-        <v>9.199999999999999</v>
+        <v>9.6</v>
       </c>
       <c r="AT5">
-        <v>5.9</v>
+        <v>6.2</v>
       </c>
       <c r="AU5">
         <v>8.199999999999999</v>
       </c>
       <c r="AV5">
-        <v>7.2</v>
+        <v>23</v>
       </c>
       <c r="AW5">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AX5">
         <v>7.2</v>
@@ -1783,88 +1783,88 @@
         <v>9</v>
       </c>
       <c r="AZ5">
-        <v>21</v>
+        <v>7.2</v>
       </c>
       <c r="BA5">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BB5">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="BC5">
         <v>16.5</v>
       </c>
       <c r="BD5">
-        <v>8</v>
+        <v>34</v>
       </c>
       <c r="BE5">
+        <v>9.4</v>
+      </c>
+      <c r="BF5">
         <v>9</v>
       </c>
-      <c r="BF5">
-        <v>8.199999999999999</v>
-      </c>
       <c r="BG5">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="BH5">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="BI5">
-        <v>2.72</v>
+        <v>2.68</v>
       </c>
       <c r="BJ5">
-        <v>12.5</v>
+        <v>13.5</v>
       </c>
       <c r="BK5">
-        <v>5.7</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BL5">
         <v>1000</v>
       </c>
       <c r="BM5">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="BN5">
-        <v>3.95</v>
+        <v>3.9</v>
       </c>
       <c r="BO5">
         <v>3.1</v>
       </c>
       <c r="BP5">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="BQ5">
         <v>5.4</v>
       </c>
       <c r="BR5">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="BS5">
-        <v>8</v>
+        <v>8.4</v>
       </c>
       <c r="BT5">
         <v>11.5</v>
       </c>
       <c r="BU5">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="BV5">
         <v>85</v>
       </c>
       <c r="BW5">
-        <v>9.4</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BX5">
         <v>1000</v>
       </c>
       <c r="BY5">
-        <v>9.6</v>
+        <v>10</v>
       </c>
       <c r="BZ5">
         <v>23</v>
       </c>
       <c r="CA5">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="CB5" t="s">
         <v>103</v>
@@ -1887,7 +1887,7 @@
         <v>101</v>
       </c>
       <c r="F6">
-        <v>1.31</v>
+        <v>1.33</v>
       </c>
       <c r="G6">
         <v>1.37</v>
@@ -1902,10 +1902,10 @@
         <v>5.1</v>
       </c>
       <c r="K6">
-        <v>6.2</v>
+        <v>5.9</v>
       </c>
       <c r="L6">
-        <v>1.34</v>
+        <v>1.3</v>
       </c>
       <c r="M6">
         <v>1.05</v>
@@ -1917,25 +1917,25 @@
         <v>1.26</v>
       </c>
       <c r="P6">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="Q6">
-        <v>1.76</v>
+        <v>1.78</v>
       </c>
       <c r="R6">
-        <v>1.41</v>
+        <v>1.43</v>
       </c>
       <c r="S6">
         <v>2.96</v>
       </c>
       <c r="T6">
-        <v>2.2</v>
+        <v>2.24</v>
       </c>
       <c r="U6">
-        <v>1.67</v>
+        <v>1.7</v>
       </c>
       <c r="V6">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="W6">
         <v>3.7</v>
@@ -1953,7 +1953,7 @@
         <v>1000</v>
       </c>
       <c r="AB6">
-        <v>8.800000000000001</v>
+        <v>8</v>
       </c>
       <c r="AC6">
         <v>14.5</v>
@@ -1965,10 +1965,10 @@
         <v>290</v>
       </c>
       <c r="AF6">
-        <v>8.6</v>
+        <v>8</v>
       </c>
       <c r="AG6">
-        <v>12.5</v>
+        <v>11.5</v>
       </c>
       <c r="AH6">
         <v>40</v>
@@ -1980,7 +1980,7 @@
         <v>12</v>
       </c>
       <c r="AK6">
-        <v>17.5</v>
+        <v>16.5</v>
       </c>
       <c r="AL6">
         <v>55</v>
@@ -1989,64 +1989,64 @@
         <v>260</v>
       </c>
       <c r="AN6">
-        <v>7</v>
+        <v>6.4</v>
       </c>
       <c r="AO6">
-        <v>480</v>
+        <v>470</v>
       </c>
       <c r="AP6">
         <v>14</v>
       </c>
       <c r="AQ6">
-        <v>4.7</v>
+        <v>6.2</v>
       </c>
       <c r="AR6">
-        <v>5.2</v>
+        <v>7</v>
       </c>
       <c r="AS6">
-        <v>5.4</v>
+        <v>7.4</v>
       </c>
       <c r="AT6">
-        <v>6</v>
+        <v>6.6</v>
       </c>
       <c r="AU6">
         <v>9.800000000000001</v>
       </c>
       <c r="AV6">
-        <v>4.9</v>
+        <v>6.6</v>
       </c>
       <c r="AW6">
-        <v>5.3</v>
+        <v>7.2</v>
       </c>
       <c r="AX6">
-        <v>5.9</v>
+        <v>6.4</v>
       </c>
       <c r="AY6">
-        <v>8.800000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AZ6">
-        <v>4.7</v>
+        <v>6.2</v>
       </c>
       <c r="BA6">
-        <v>5.2</v>
+        <v>7.2</v>
       </c>
       <c r="BB6">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="BC6">
         <v>12</v>
       </c>
       <c r="BD6">
-        <v>4.9</v>
+        <v>6.6</v>
       </c>
       <c r="BE6">
-        <v>5.2</v>
+        <v>7.2</v>
       </c>
       <c r="BF6">
         <v>4.8</v>
       </c>
       <c r="BG6">
-        <v>5.3</v>
+        <v>7.4</v>
       </c>
       <c r="BH6">
         <v>3.95</v>
@@ -2055,7 +2055,7 @@
         <v>3.1</v>
       </c>
       <c r="BJ6">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="BK6">
         <v>6</v>
@@ -2067,25 +2067,25 @@
         <v>10</v>
       </c>
       <c r="BN6">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="BO6">
-        <v>2.98</v>
+        <v>3</v>
       </c>
       <c r="BP6">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BQ6">
         <v>6</v>
       </c>
       <c r="BR6">
-        <v>28</v>
+        <v>1000</v>
       </c>
       <c r="BS6">
         <v>7.6</v>
       </c>
       <c r="BT6">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="BU6">
         <v>6.2</v>
@@ -2100,7 +2100,7 @@
         <v>1000</v>
       </c>
       <c r="BY6">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BZ6">
         <v>14.5</v>
@@ -2147,7 +2147,7 @@
         <v>4.1</v>
       </c>
       <c r="L7">
-        <v>1.27</v>
+        <v>1.33</v>
       </c>
       <c r="M7">
         <v>1.04</v>
@@ -2174,7 +2174,7 @@
         <v>1.61</v>
       </c>
       <c r="U7">
-        <v>2.4</v>
+        <v>2.42</v>
       </c>
       <c r="V7">
         <v>1.39</v>
@@ -2264,7 +2264,7 @@
         <v>11.5</v>
       </c>
       <c r="AY7">
-        <v>10</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AZ7">
         <v>11.5</v>
@@ -2279,7 +2279,7 @@
         <v>15.5</v>
       </c>
       <c r="BD7">
-        <v>21</v>
+        <v>4.7</v>
       </c>
       <c r="BE7">
         <v>5.2</v>
@@ -2300,49 +2300,49 @@
         <v>8.800000000000001</v>
       </c>
       <c r="BK7">
-        <v>1.01</v>
+        <v>5.4</v>
       </c>
       <c r="BL7">
         <v>1000</v>
       </c>
       <c r="BM7">
-        <v>1.01</v>
+        <v>12</v>
       </c>
       <c r="BN7">
         <v>5.4</v>
       </c>
       <c r="BO7">
-        <v>4.1</v>
+        <v>4.8</v>
       </c>
       <c r="BP7">
         <v>15</v>
       </c>
       <c r="BQ7">
-        <v>1.01</v>
+        <v>7.2</v>
       </c>
       <c r="BR7">
         <v>1000</v>
       </c>
       <c r="BS7">
-        <v>1.01</v>
+        <v>9</v>
       </c>
       <c r="BT7">
         <v>7</v>
       </c>
       <c r="BU7">
-        <v>5.2</v>
+        <v>6</v>
       </c>
       <c r="BV7">
         <v>34</v>
       </c>
       <c r="BW7">
-        <v>1.01</v>
+        <v>9</v>
       </c>
       <c r="BX7">
         <v>46</v>
       </c>
       <c r="BY7">
-        <v>1.01</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BZ7">
         <v>0</v>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-08-11.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-08-11.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="116" uniqueCount="104">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="128" uniqueCount="112">
   <si>
     <t>League</t>
   </si>
@@ -274,6 +274,12 @@
     <t>Swedish Superettan</t>
   </si>
   <si>
+    <t>CONMEBOL Copa Libertadores</t>
+  </si>
+  <si>
+    <t>Brazilian Serie B</t>
+  </si>
+  <si>
     <t>2026-08-11</t>
   </si>
   <si>
@@ -289,6 +295,12 @@
     <t>17:00:00</t>
   </si>
   <si>
+    <t>22:00:00</t>
+  </si>
+  <si>
+    <t>22:30:00</t>
+  </si>
+  <si>
     <t>America MG (W)</t>
   </si>
   <si>
@@ -307,6 +319,12 @@
     <t>Helsingborgs</t>
   </si>
   <si>
+    <t>Fluminense</t>
+  </si>
+  <si>
+    <t>Avai</t>
+  </si>
+  <si>
     <t>CR Flamengo (W)</t>
   </si>
   <si>
@@ -325,7 +343,13 @@
     <t>Varnamo</t>
   </si>
   <si>
-    <t>2026-08-09 23:35:02</t>
+    <t>Independiente Rivadavia</t>
+  </si>
+  <si>
+    <t>CRB</t>
+  </si>
+  <si>
+    <t>2026-08-10 01:43:53</t>
   </si>
 </sst>
 </file>
@@ -657,7 +681,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:CB7"/>
+  <dimension ref="A1:CB9"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:80">
@@ -907,31 +931,31 @@
         <v>80</v>
       </c>
       <c r="B2" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="C2" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="D2" t="s">
-        <v>91</v>
+        <v>95</v>
       </c>
       <c r="E2" t="s">
-        <v>97</v>
+        <v>103</v>
       </c>
       <c r="F2">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="G2">
         <v>15</v>
       </c>
       <c r="H2">
-        <v>1.31</v>
+        <v>1.29</v>
       </c>
       <c r="I2">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="J2">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="K2">
         <v>6.4</v>
@@ -940,13 +964,13 @@
         <v>1.29</v>
       </c>
       <c r="M2">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="N2">
-        <v>4.8</v>
+        <v>4.4</v>
       </c>
       <c r="O2">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="P2">
         <v>2.24</v>
@@ -967,7 +991,7 @@
         <v>1.75</v>
       </c>
       <c r="V2">
-        <v>3.55</v>
+        <v>3.7</v>
       </c>
       <c r="W2">
         <v>1.07</v>
@@ -1141,7 +1165,7 @@
         <v>3.6</v>
       </c>
       <c r="CB2" t="s">
-        <v>103</v>
+        <v>111</v>
       </c>
     </row>
     <row r="3" spans="1:80">
@@ -1149,52 +1173,52 @@
         <v>81</v>
       </c>
       <c r="B3" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="C3" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="D3" t="s">
-        <v>92</v>
+        <v>96</v>
       </c>
       <c r="E3" t="s">
-        <v>98</v>
+        <v>104</v>
       </c>
       <c r="F3">
-        <v>2.42</v>
+        <v>2.38</v>
       </c>
       <c r="G3">
-        <v>2.62</v>
+        <v>2.46</v>
       </c>
       <c r="H3">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="I3">
         <v>3.4</v>
       </c>
       <c r="J3">
-        <v>3.25</v>
+        <v>3.45</v>
       </c>
       <c r="K3">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="L3">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="M3">
         <v>1.08</v>
       </c>
       <c r="N3">
-        <v>3.35</v>
+        <v>3.45</v>
       </c>
       <c r="O3">
         <v>1.37</v>
       </c>
       <c r="P3">
-        <v>1.83</v>
+        <v>1.82</v>
       </c>
       <c r="Q3">
-        <v>2.1</v>
+        <v>2.14</v>
       </c>
       <c r="R3">
         <v>1.31</v>
@@ -1203,7 +1227,7 @@
         <v>3.9</v>
       </c>
       <c r="T3">
-        <v>1.83</v>
+        <v>1.84</v>
       </c>
       <c r="U3">
         <v>2.06</v>
@@ -1212,7 +1236,7 @@
         <v>1.42</v>
       </c>
       <c r="W3">
-        <v>1.62</v>
+        <v>1.68</v>
       </c>
       <c r="X3">
         <v>15</v>
@@ -1227,10 +1251,10 @@
         <v>85</v>
       </c>
       <c r="AB3">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="AC3">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AD3">
         <v>17</v>
@@ -1239,10 +1263,10 @@
         <v>50</v>
       </c>
       <c r="AF3">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AG3">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AH3">
         <v>22</v>
@@ -1251,139 +1275,139 @@
         <v>65</v>
       </c>
       <c r="AJ3">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="AK3">
         <v>42</v>
       </c>
       <c r="AL3">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="AM3">
         <v>130</v>
       </c>
       <c r="AN3">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="AO3">
         <v>50</v>
       </c>
       <c r="AP3">
-        <v>11</v>
+        <v>9.6</v>
       </c>
       <c r="AQ3">
-        <v>10</v>
+        <v>9.4</v>
       </c>
       <c r="AR3">
         <v>16</v>
       </c>
       <c r="AS3">
-        <v>5.3</v>
+        <v>6.4</v>
       </c>
       <c r="AT3">
-        <v>8.6</v>
+        <v>6.8</v>
       </c>
       <c r="AU3">
-        <v>6.8</v>
+        <v>6</v>
       </c>
       <c r="AV3">
         <v>12</v>
       </c>
       <c r="AW3">
-        <v>5.1</v>
+        <v>6.2</v>
       </c>
       <c r="AX3">
-        <v>13.5</v>
+        <v>12.5</v>
       </c>
       <c r="AY3">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AZ3">
-        <v>4.5</v>
+        <v>14</v>
       </c>
       <c r="BA3">
-        <v>5.2</v>
+        <v>6.4</v>
       </c>
       <c r="BB3">
-        <v>5</v>
+        <v>23</v>
       </c>
       <c r="BC3">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="BD3">
-        <v>5.1</v>
+        <v>6.2</v>
       </c>
       <c r="BE3">
-        <v>5.4</v>
+        <v>6.6</v>
       </c>
       <c r="BF3">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="BG3">
-        <v>5.1</v>
+        <v>6.2</v>
       </c>
       <c r="BH3">
-        <v>3.7</v>
+        <v>3.65</v>
       </c>
       <c r="BI3">
-        <v>2.56</v>
+        <v>2.58</v>
       </c>
       <c r="BJ3">
         <v>12</v>
       </c>
       <c r="BK3">
-        <v>3.4</v>
+        <v>3.6</v>
       </c>
       <c r="BL3">
         <v>1000</v>
       </c>
       <c r="BM3">
-        <v>4.6</v>
+        <v>4.9</v>
       </c>
       <c r="BN3">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="BO3">
         <v>4.1</v>
       </c>
       <c r="BP3">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="BQ3">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="BR3">
         <v>42</v>
       </c>
       <c r="BS3">
-        <v>4.3</v>
+        <v>4.5</v>
       </c>
       <c r="BT3">
         <v>7.4</v>
       </c>
       <c r="BU3">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="BV3">
         <v>32</v>
       </c>
       <c r="BW3">
-        <v>4.1</v>
+        <v>4.4</v>
       </c>
       <c r="BX3">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="BY3">
-        <v>4.4</v>
+        <v>4.6</v>
       </c>
       <c r="BZ3">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="CA3">
-        <v>4.3</v>
+        <v>4.5</v>
       </c>
       <c r="CB3" t="s">
-        <v>103</v>
+        <v>111</v>
       </c>
     </row>
     <row r="4" spans="1:80">
@@ -1391,136 +1415,136 @@
         <v>82</v>
       </c>
       <c r="B4" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="C4" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="D4" t="s">
-        <v>93</v>
+        <v>97</v>
       </c>
       <c r="E4" t="s">
-        <v>99</v>
+        <v>105</v>
       </c>
       <c r="F4">
-        <v>1.64</v>
+        <v>1.67</v>
       </c>
       <c r="G4">
-        <v>1.76</v>
+        <v>1.72</v>
       </c>
       <c r="H4">
         <v>6.6</v>
       </c>
       <c r="I4">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="J4">
-        <v>3.45</v>
+        <v>3.6</v>
       </c>
       <c r="K4">
         <v>3.95</v>
       </c>
       <c r="L4">
-        <v>1.46</v>
+        <v>1.56</v>
       </c>
       <c r="M4">
         <v>1.11</v>
       </c>
       <c r="N4">
-        <v>2.7</v>
+        <v>2.88</v>
       </c>
       <c r="O4">
-        <v>1.5</v>
+        <v>1.48</v>
       </c>
       <c r="P4">
-        <v>1.58</v>
+        <v>1.61</v>
       </c>
       <c r="Q4">
-        <v>2.44</v>
+        <v>2.48</v>
       </c>
       <c r="R4">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="S4">
-        <v>4.5</v>
+        <v>5</v>
       </c>
       <c r="T4">
-        <v>2.3</v>
+        <v>2.28</v>
       </c>
       <c r="U4">
-        <v>1.63</v>
+        <v>1.65</v>
       </c>
       <c r="V4">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="W4">
-        <v>2.32</v>
+        <v>2.38</v>
       </c>
       <c r="X4">
         <v>11</v>
       </c>
       <c r="Y4">
-        <v>17.5</v>
+        <v>18.5</v>
       </c>
       <c r="Z4">
         <v>65</v>
       </c>
       <c r="AA4">
-        <v>320</v>
+        <v>300</v>
       </c>
       <c r="AB4">
         <v>6.4</v>
       </c>
       <c r="AC4">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AD4">
         <v>32</v>
       </c>
       <c r="AE4">
-        <v>180</v>
+        <v>170</v>
       </c>
       <c r="AF4">
         <v>8.800000000000001</v>
       </c>
       <c r="AG4">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AH4">
         <v>950</v>
       </c>
       <c r="AI4">
-        <v>190</v>
+        <v>170</v>
       </c>
       <c r="AJ4">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AK4">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AL4">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="AM4">
-        <v>300</v>
+        <v>270</v>
       </c>
       <c r="AN4">
-        <v>17</v>
+        <v>15.5</v>
       </c>
       <c r="AO4">
         <v>340</v>
       </c>
       <c r="AP4">
-        <v>7.6</v>
+        <v>8</v>
       </c>
       <c r="AQ4">
         <v>14.5</v>
       </c>
       <c r="AR4">
-        <v>7</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AS4">
-        <v>7.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AT4">
         <v>5.3</v>
@@ -1529,22 +1553,22 @@
         <v>7.4</v>
       </c>
       <c r="AV4">
-        <v>6.4</v>
+        <v>7.6</v>
       </c>
       <c r="AW4">
-        <v>7.6</v>
+        <v>9.6</v>
       </c>
       <c r="AX4">
-        <v>6.6</v>
+        <v>7.4</v>
       </c>
       <c r="AY4">
         <v>9</v>
       </c>
       <c r="AZ4">
-        <v>6.4</v>
+        <v>7.6</v>
       </c>
       <c r="BA4">
-        <v>7.6</v>
+        <v>9.6</v>
       </c>
       <c r="BB4">
         <v>13</v>
@@ -1553,79 +1577,79 @@
         <v>17.5</v>
       </c>
       <c r="BD4">
-        <v>7</v>
+        <v>8.6</v>
       </c>
       <c r="BE4">
-        <v>7.8</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BF4">
         <v>12.5</v>
       </c>
       <c r="BG4">
-        <v>7.8</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BH4">
-        <v>2.94</v>
+        <v>3</v>
       </c>
       <c r="BI4">
-        <v>2.4</v>
+        <v>2.44</v>
       </c>
       <c r="BJ4">
         <v>13.5</v>
       </c>
       <c r="BK4">
-        <v>5.9</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BL4">
         <v>1000</v>
       </c>
       <c r="BM4">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="BN4">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="BO4">
         <v>3.15</v>
       </c>
       <c r="BP4">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="BQ4">
-        <v>5.8</v>
+        <v>5.9</v>
       </c>
       <c r="BR4">
         <v>1000</v>
       </c>
       <c r="BS4">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="BT4">
         <v>11</v>
       </c>
       <c r="BU4">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="BV4">
         <v>1000</v>
       </c>
       <c r="BW4">
-        <v>9.4</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BX4">
         <v>1000</v>
       </c>
       <c r="BY4">
-        <v>9.6</v>
+        <v>10</v>
       </c>
       <c r="BZ4">
         <v>1000</v>
       </c>
       <c r="CA4">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="CB4" t="s">
-        <v>103</v>
+        <v>111</v>
       </c>
     </row>
     <row r="5" spans="1:80">
@@ -1633,25 +1657,25 @@
         <v>83</v>
       </c>
       <c r="B5" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="C5" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="D5" t="s">
-        <v>94</v>
+        <v>98</v>
       </c>
       <c r="E5" t="s">
-        <v>100</v>
+        <v>106</v>
       </c>
       <c r="F5">
         <v>1.56</v>
       </c>
       <c r="G5">
-        <v>1.6</v>
+        <v>1.62</v>
       </c>
       <c r="H5">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="I5">
         <v>8</v>
@@ -1660,34 +1684,34 @@
         <v>4.1</v>
       </c>
       <c r="K5">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="L5">
-        <v>1.43</v>
+        <v>1.45</v>
       </c>
       <c r="M5">
         <v>1.08</v>
       </c>
       <c r="N5">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="O5">
-        <v>1.37</v>
+        <v>1.39</v>
       </c>
       <c r="P5">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="Q5">
-        <v>2.16</v>
+        <v>2.18</v>
       </c>
       <c r="R5">
         <v>1.3</v>
       </c>
       <c r="S5">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="T5">
-        <v>2.2</v>
+        <v>2.22</v>
       </c>
       <c r="U5">
         <v>1.72</v>
@@ -1696,31 +1720,31 @@
         <v>1.14</v>
       </c>
       <c r="W5">
-        <v>2.68</v>
+        <v>2.62</v>
       </c>
       <c r="X5">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="Y5">
         <v>21</v>
       </c>
       <c r="Z5">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="AA5">
-        <v>330</v>
+        <v>310</v>
       </c>
       <c r="AB5">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="AC5">
         <v>9.6</v>
       </c>
       <c r="AD5">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="AE5">
-        <v>170</v>
+        <v>160</v>
       </c>
       <c r="AF5">
         <v>8.6</v>
@@ -1744,13 +1768,13 @@
         <v>50</v>
       </c>
       <c r="AM5">
-        <v>220</v>
+        <v>240</v>
       </c>
       <c r="AN5">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AO5">
-        <v>270</v>
+        <v>280</v>
       </c>
       <c r="AP5">
         <v>11</v>
@@ -1759,13 +1783,13 @@
         <v>16.5</v>
       </c>
       <c r="AR5">
-        <v>8.6</v>
+        <v>9</v>
       </c>
       <c r="AS5">
-        <v>9.6</v>
+        <v>10</v>
       </c>
       <c r="AT5">
-        <v>6.2</v>
+        <v>5.9</v>
       </c>
       <c r="AU5">
         <v>8.199999999999999</v>
@@ -1774,7 +1798,7 @@
         <v>23</v>
       </c>
       <c r="AW5">
-        <v>9.199999999999999</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AX5">
         <v>7.2</v>
@@ -1783,10 +1807,10 @@
         <v>9</v>
       </c>
       <c r="AZ5">
-        <v>7.2</v>
+        <v>24</v>
       </c>
       <c r="BA5">
-        <v>9.199999999999999</v>
+        <v>9.6</v>
       </c>
       <c r="BB5">
         <v>12</v>
@@ -1798,16 +1822,16 @@
         <v>34</v>
       </c>
       <c r="BE5">
-        <v>9.4</v>
+        <v>10</v>
       </c>
       <c r="BF5">
         <v>9</v>
       </c>
       <c r="BG5">
-        <v>9.4</v>
+        <v>10</v>
       </c>
       <c r="BH5">
-        <v>3.35</v>
+        <v>3.25</v>
       </c>
       <c r="BI5">
         <v>2.68</v>
@@ -1822,52 +1846,52 @@
         <v>1000</v>
       </c>
       <c r="BM5">
-        <v>10.5</v>
+        <v>12.5</v>
       </c>
       <c r="BN5">
         <v>3.9</v>
       </c>
       <c r="BO5">
-        <v>3.1</v>
+        <v>3.3</v>
       </c>
       <c r="BP5">
         <v>10.5</v>
       </c>
       <c r="BQ5">
-        <v>5.4</v>
+        <v>5.8</v>
       </c>
       <c r="BR5">
         <v>34</v>
       </c>
       <c r="BS5">
-        <v>8.4</v>
+        <v>9.4</v>
       </c>
       <c r="BT5">
+        <v>11</v>
+      </c>
+      <c r="BU5">
+        <v>6</v>
+      </c>
+      <c r="BV5">
+        <v>1000</v>
+      </c>
+      <c r="BW5">
+        <v>11</v>
+      </c>
+      <c r="BX5">
+        <v>1000</v>
+      </c>
+      <c r="BY5">
         <v>11.5</v>
-      </c>
-      <c r="BU5">
-        <v>5.6</v>
-      </c>
-      <c r="BV5">
-        <v>85</v>
-      </c>
-      <c r="BW5">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="BX5">
-        <v>1000</v>
-      </c>
-      <c r="BY5">
-        <v>10</v>
       </c>
       <c r="BZ5">
         <v>23</v>
       </c>
       <c r="CA5">
-        <v>7.4</v>
+        <v>8.4</v>
       </c>
       <c r="CB5" t="s">
-        <v>103</v>
+        <v>111</v>
       </c>
     </row>
     <row r="6" spans="1:80">
@@ -1875,148 +1899,148 @@
         <v>84</v>
       </c>
       <c r="B6" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="C6" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="D6" t="s">
-        <v>95</v>
+        <v>99</v>
       </c>
       <c r="E6" t="s">
-        <v>101</v>
+        <v>107</v>
       </c>
       <c r="F6">
-        <v>1.33</v>
+        <v>1.38</v>
       </c>
       <c r="G6">
-        <v>1.37</v>
+        <v>1.41</v>
       </c>
       <c r="H6">
-        <v>11.5</v>
+        <v>10.5</v>
       </c>
       <c r="I6">
-        <v>16</v>
+        <v>12.5</v>
       </c>
       <c r="J6">
         <v>5.1</v>
       </c>
       <c r="K6">
-        <v>5.9</v>
+        <v>5.5</v>
       </c>
       <c r="L6">
-        <v>1.3</v>
+        <v>1.36</v>
       </c>
       <c r="M6">
         <v>1.05</v>
       </c>
       <c r="N6">
-        <v>4.2</v>
+        <v>4.4</v>
       </c>
       <c r="O6">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="P6">
-        <v>2.1</v>
+        <v>2.14</v>
       </c>
       <c r="Q6">
-        <v>1.78</v>
+        <v>1.81</v>
       </c>
       <c r="R6">
         <v>1.43</v>
       </c>
       <c r="S6">
-        <v>2.96</v>
+        <v>3.1</v>
       </c>
       <c r="T6">
-        <v>2.24</v>
+        <v>2.12</v>
       </c>
       <c r="U6">
-        <v>1.7</v>
+        <v>1.75</v>
       </c>
       <c r="V6">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="W6">
-        <v>3.7</v>
+        <v>3.4</v>
       </c>
       <c r="X6">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="Y6">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="Z6">
-        <v>140</v>
+        <v>110</v>
       </c>
       <c r="AA6">
-        <v>1000</v>
+        <v>470</v>
       </c>
       <c r="AB6">
         <v>8</v>
       </c>
       <c r="AC6">
-        <v>14.5</v>
+        <v>12.5</v>
       </c>
       <c r="AD6">
-        <v>55</v>
+        <v>44</v>
       </c>
       <c r="AE6">
-        <v>290</v>
+        <v>210</v>
       </c>
       <c r="AF6">
         <v>8</v>
       </c>
       <c r="AG6">
+        <v>11</v>
+      </c>
+      <c r="AH6">
+        <v>34</v>
+      </c>
+      <c r="AI6">
+        <v>170</v>
+      </c>
+      <c r="AJ6">
         <v>11.5</v>
-      </c>
-      <c r="AH6">
-        <v>40</v>
-      </c>
-      <c r="AI6">
-        <v>220</v>
-      </c>
-      <c r="AJ6">
-        <v>12</v>
       </c>
       <c r="AK6">
         <v>16.5</v>
       </c>
       <c r="AL6">
-        <v>55</v>
+        <v>48</v>
       </c>
       <c r="AM6">
-        <v>260</v>
+        <v>210</v>
       </c>
       <c r="AN6">
         <v>6.4</v>
       </c>
       <c r="AO6">
-        <v>470</v>
+        <v>310</v>
       </c>
       <c r="AP6">
         <v>14</v>
       </c>
       <c r="AQ6">
-        <v>6.2</v>
+        <v>8</v>
       </c>
       <c r="AR6">
-        <v>7</v>
+        <v>9.4</v>
       </c>
       <c r="AS6">
-        <v>7.4</v>
+        <v>10</v>
       </c>
       <c r="AT6">
         <v>6.6</v>
       </c>
       <c r="AU6">
+        <v>10.5</v>
+      </c>
+      <c r="AV6">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AW6">
         <v>9.800000000000001</v>
-      </c>
-      <c r="AV6">
-        <v>6.6</v>
-      </c>
-      <c r="AW6">
-        <v>7.2</v>
       </c>
       <c r="AX6">
         <v>6.4</v>
@@ -2025,40 +2049,40 @@
         <v>9.199999999999999</v>
       </c>
       <c r="AZ6">
-        <v>6.2</v>
+        <v>7.8</v>
       </c>
       <c r="BA6">
-        <v>7.2</v>
+        <v>9.6</v>
       </c>
       <c r="BB6">
-        <v>9</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BC6">
         <v>12</v>
       </c>
       <c r="BD6">
-        <v>6.6</v>
+        <v>8.4</v>
       </c>
       <c r="BE6">
-        <v>7.2</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BF6">
-        <v>4.8</v>
+        <v>5.4</v>
       </c>
       <c r="BG6">
-        <v>7.4</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BH6">
-        <v>3.95</v>
+        <v>3.9</v>
       </c>
       <c r="BI6">
         <v>3.1</v>
       </c>
       <c r="BJ6">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="BK6">
-        <v>6</v>
+        <v>5.9</v>
       </c>
       <c r="BL6">
         <v>1000</v>
@@ -2067,34 +2091,34 @@
         <v>10</v>
       </c>
       <c r="BN6">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="BO6">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="BP6">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="BQ6">
+        <v>4.7</v>
+      </c>
+      <c r="BR6">
+        <v>27</v>
+      </c>
+      <c r="BS6">
+        <v>7.8</v>
+      </c>
+      <c r="BT6">
+        <v>14</v>
+      </c>
+      <c r="BU6">
         <v>6</v>
       </c>
-      <c r="BR6">
-        <v>1000</v>
-      </c>
-      <c r="BS6">
-        <v>7.6</v>
-      </c>
-      <c r="BT6">
-        <v>15</v>
-      </c>
-      <c r="BU6">
-        <v>6.2</v>
-      </c>
       <c r="BV6">
         <v>1000</v>
       </c>
       <c r="BW6">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="BX6">
         <v>1000</v>
@@ -2103,13 +2127,13 @@
         <v>9.800000000000001</v>
       </c>
       <c r="BZ6">
-        <v>14.5</v>
+        <v>15.5</v>
       </c>
       <c r="CA6">
-        <v>6</v>
+        <v>6.4</v>
       </c>
       <c r="CB6" t="s">
-        <v>103</v>
+        <v>111</v>
       </c>
     </row>
     <row r="7" spans="1:80">
@@ -2117,37 +2141,37 @@
         <v>85</v>
       </c>
       <c r="B7" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="C7" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="D7" t="s">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="E7" t="s">
-        <v>102</v>
+        <v>108</v>
       </c>
       <c r="F7">
-        <v>2.12</v>
+        <v>2.08</v>
       </c>
       <c r="G7">
-        <v>2.3</v>
+        <v>2.26</v>
       </c>
       <c r="H7">
         <v>3.25</v>
       </c>
       <c r="I7">
-        <v>3.55</v>
+        <v>3.65</v>
       </c>
       <c r="J7">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="K7">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="L7">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="M7">
         <v>1.04</v>
@@ -2156,43 +2180,43 @@
         <v>4.8</v>
       </c>
       <c r="O7">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="P7">
-        <v>2.28</v>
+        <v>2.3</v>
       </c>
       <c r="Q7">
-        <v>1.68</v>
+        <v>1.66</v>
       </c>
       <c r="R7">
-        <v>1.51</v>
+        <v>1.52</v>
       </c>
       <c r="S7">
-        <v>2.7</v>
+        <v>2.64</v>
       </c>
       <c r="T7">
-        <v>1.61</v>
+        <v>1.6</v>
       </c>
       <c r="U7">
         <v>2.42</v>
       </c>
       <c r="V7">
-        <v>1.39</v>
+        <v>1.37</v>
       </c>
       <c r="W7">
-        <v>1.77</v>
+        <v>1.79</v>
       </c>
       <c r="X7">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="Y7">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="Z7">
         <v>34</v>
       </c>
       <c r="AA7">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="AB7">
         <v>15.5</v>
@@ -2222,7 +2246,7 @@
         <v>36</v>
       </c>
       <c r="AK7">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AL7">
         <v>40</v>
@@ -2231,22 +2255,22 @@
         <v>80</v>
       </c>
       <c r="AN7">
-        <v>15.5</v>
+        <v>14.5</v>
       </c>
       <c r="AO7">
         <v>32</v>
       </c>
       <c r="AP7">
-        <v>4.5</v>
+        <v>15.5</v>
       </c>
       <c r="AQ7">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="AR7">
-        <v>19</v>
+        <v>19.5</v>
       </c>
       <c r="AS7">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="AT7">
         <v>11</v>
@@ -2255,10 +2279,10 @@
         <v>8.199999999999999</v>
       </c>
       <c r="AV7">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AW7">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="AX7">
         <v>11.5</v>
@@ -2270,22 +2294,22 @@
         <v>11.5</v>
       </c>
       <c r="BA7">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="BB7">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="BC7">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="BD7">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="BE7">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="BF7">
-        <v>9.199999999999999</v>
+        <v>10.5</v>
       </c>
       <c r="BG7">
         <v>19</v>
@@ -2300,31 +2324,31 @@
         <v>8.800000000000001</v>
       </c>
       <c r="BK7">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="BL7">
         <v>1000</v>
       </c>
       <c r="BM7">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="BN7">
         <v>5.4</v>
       </c>
       <c r="BO7">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="BP7">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="BQ7">
-        <v>7.2</v>
+        <v>11</v>
       </c>
       <c r="BR7">
         <v>1000</v>
       </c>
       <c r="BS7">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BT7">
         <v>7</v>
@@ -2336,13 +2360,13 @@
         <v>34</v>
       </c>
       <c r="BW7">
-        <v>9</v>
+        <v>9.4</v>
       </c>
       <c r="BX7">
         <v>46</v>
       </c>
       <c r="BY7">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="BZ7">
         <v>0</v>
@@ -2351,7 +2375,491 @@
         <v>0</v>
       </c>
       <c r="CB7" t="s">
-        <v>103</v>
+        <v>111</v>
+      </c>
+    </row>
+    <row r="8" spans="1:80">
+      <c r="A8" t="s">
+        <v>86</v>
+      </c>
+      <c r="B8" t="s">
+        <v>88</v>
+      </c>
+      <c r="C8" t="s">
+        <v>93</v>
+      </c>
+      <c r="D8" t="s">
+        <v>101</v>
+      </c>
+      <c r="E8" t="s">
+        <v>109</v>
+      </c>
+      <c r="F8">
+        <v>0</v>
+      </c>
+      <c r="G8">
+        <v>0</v>
+      </c>
+      <c r="H8">
+        <v>0</v>
+      </c>
+      <c r="I8">
+        <v>0</v>
+      </c>
+      <c r="J8">
+        <v>0</v>
+      </c>
+      <c r="K8">
+        <v>0</v>
+      </c>
+      <c r="L8">
+        <v>0</v>
+      </c>
+      <c r="M8">
+        <v>0</v>
+      </c>
+      <c r="N8">
+        <v>0</v>
+      </c>
+      <c r="O8">
+        <v>0</v>
+      </c>
+      <c r="P8">
+        <v>1.24</v>
+      </c>
+      <c r="Q8">
+        <v>1.01</v>
+      </c>
+      <c r="R8">
+        <v>0</v>
+      </c>
+      <c r="S8">
+        <v>0</v>
+      </c>
+      <c r="T8">
+        <v>0</v>
+      </c>
+      <c r="U8">
+        <v>0</v>
+      </c>
+      <c r="V8">
+        <v>0</v>
+      </c>
+      <c r="W8">
+        <v>0</v>
+      </c>
+      <c r="X8">
+        <v>0</v>
+      </c>
+      <c r="Y8">
+        <v>0</v>
+      </c>
+      <c r="Z8">
+        <v>0</v>
+      </c>
+      <c r="AA8">
+        <v>0</v>
+      </c>
+      <c r="AB8">
+        <v>0</v>
+      </c>
+      <c r="AC8">
+        <v>0</v>
+      </c>
+      <c r="AD8">
+        <v>0</v>
+      </c>
+      <c r="AE8">
+        <v>0</v>
+      </c>
+      <c r="AF8">
+        <v>0</v>
+      </c>
+      <c r="AG8">
+        <v>0</v>
+      </c>
+      <c r="AH8">
+        <v>0</v>
+      </c>
+      <c r="AI8">
+        <v>0</v>
+      </c>
+      <c r="AJ8">
+        <v>0</v>
+      </c>
+      <c r="AK8">
+        <v>0</v>
+      </c>
+      <c r="AL8">
+        <v>0</v>
+      </c>
+      <c r="AM8">
+        <v>0</v>
+      </c>
+      <c r="AN8">
+        <v>0</v>
+      </c>
+      <c r="AO8">
+        <v>0</v>
+      </c>
+      <c r="AP8">
+        <v>0</v>
+      </c>
+      <c r="AQ8">
+        <v>0</v>
+      </c>
+      <c r="AR8">
+        <v>0</v>
+      </c>
+      <c r="AS8">
+        <v>0</v>
+      </c>
+      <c r="AT8">
+        <v>0</v>
+      </c>
+      <c r="AU8">
+        <v>0</v>
+      </c>
+      <c r="AV8">
+        <v>0</v>
+      </c>
+      <c r="AW8">
+        <v>0</v>
+      </c>
+      <c r="AX8">
+        <v>0</v>
+      </c>
+      <c r="AY8">
+        <v>0</v>
+      </c>
+      <c r="AZ8">
+        <v>0</v>
+      </c>
+      <c r="BA8">
+        <v>0</v>
+      </c>
+      <c r="BB8">
+        <v>0</v>
+      </c>
+      <c r="BC8">
+        <v>0</v>
+      </c>
+      <c r="BD8">
+        <v>0</v>
+      </c>
+      <c r="BE8">
+        <v>0</v>
+      </c>
+      <c r="BF8">
+        <v>0</v>
+      </c>
+      <c r="BG8">
+        <v>0</v>
+      </c>
+      <c r="BH8">
+        <v>0</v>
+      </c>
+      <c r="BI8">
+        <v>0</v>
+      </c>
+      <c r="BJ8">
+        <v>0</v>
+      </c>
+      <c r="BK8">
+        <v>0</v>
+      </c>
+      <c r="BL8">
+        <v>0</v>
+      </c>
+      <c r="BM8">
+        <v>0</v>
+      </c>
+      <c r="BN8">
+        <v>0</v>
+      </c>
+      <c r="BO8">
+        <v>0</v>
+      </c>
+      <c r="BP8">
+        <v>0</v>
+      </c>
+      <c r="BQ8">
+        <v>0</v>
+      </c>
+      <c r="BR8">
+        <v>0</v>
+      </c>
+      <c r="BS8">
+        <v>0</v>
+      </c>
+      <c r="BT8">
+        <v>0</v>
+      </c>
+      <c r="BU8">
+        <v>0</v>
+      </c>
+      <c r="BV8">
+        <v>0</v>
+      </c>
+      <c r="BW8">
+        <v>0</v>
+      </c>
+      <c r="BX8">
+        <v>0</v>
+      </c>
+      <c r="BY8">
+        <v>0</v>
+      </c>
+      <c r="BZ8">
+        <v>0</v>
+      </c>
+      <c r="CA8">
+        <v>0</v>
+      </c>
+      <c r="CB8" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="9" spans="1:80">
+      <c r="A9" t="s">
+        <v>87</v>
+      </c>
+      <c r="B9" t="s">
+        <v>88</v>
+      </c>
+      <c r="C9" t="s">
+        <v>94</v>
+      </c>
+      <c r="D9" t="s">
+        <v>102</v>
+      </c>
+      <c r="E9" t="s">
+        <v>110</v>
+      </c>
+      <c r="F9">
+        <v>2.78</v>
+      </c>
+      <c r="G9">
+        <v>3.45</v>
+      </c>
+      <c r="H9">
+        <v>2.42</v>
+      </c>
+      <c r="I9">
+        <v>3.2</v>
+      </c>
+      <c r="J9">
+        <v>2.92</v>
+      </c>
+      <c r="K9">
+        <v>4.4</v>
+      </c>
+      <c r="L9">
+        <v>1.01</v>
+      </c>
+      <c r="M9">
+        <v>1.08</v>
+      </c>
+      <c r="N9">
+        <v>2.92</v>
+      </c>
+      <c r="O9">
+        <v>1.37</v>
+      </c>
+      <c r="P9">
+        <v>1.64</v>
+      </c>
+      <c r="Q9">
+        <v>2.12</v>
+      </c>
+      <c r="R9">
+        <v>1.23</v>
+      </c>
+      <c r="S9">
+        <v>3.3</v>
+      </c>
+      <c r="T9">
+        <v>1.65</v>
+      </c>
+      <c r="U9">
+        <v>1.87</v>
+      </c>
+      <c r="V9">
+        <v>1.46</v>
+      </c>
+      <c r="W9">
+        <v>1.4</v>
+      </c>
+      <c r="X9">
+        <v>1000</v>
+      </c>
+      <c r="Y9">
+        <v>1000</v>
+      </c>
+      <c r="Z9">
+        <v>1000</v>
+      </c>
+      <c r="AA9">
+        <v>1000</v>
+      </c>
+      <c r="AB9">
+        <v>1000</v>
+      </c>
+      <c r="AC9">
+        <v>1000</v>
+      </c>
+      <c r="AD9">
+        <v>1000</v>
+      </c>
+      <c r="AE9">
+        <v>1000</v>
+      </c>
+      <c r="AF9">
+        <v>1000</v>
+      </c>
+      <c r="AG9">
+        <v>1000</v>
+      </c>
+      <c r="AH9">
+        <v>1000</v>
+      </c>
+      <c r="AI9">
+        <v>1000</v>
+      </c>
+      <c r="AJ9">
+        <v>1000</v>
+      </c>
+      <c r="AK9">
+        <v>1000</v>
+      </c>
+      <c r="AL9">
+        <v>1000</v>
+      </c>
+      <c r="AM9">
+        <v>1000</v>
+      </c>
+      <c r="AN9">
+        <v>1000</v>
+      </c>
+      <c r="AO9">
+        <v>1000</v>
+      </c>
+      <c r="AP9">
+        <v>1.03</v>
+      </c>
+      <c r="AQ9">
+        <v>1.01</v>
+      </c>
+      <c r="AR9">
+        <v>1.01</v>
+      </c>
+      <c r="AS9">
+        <v>1.01</v>
+      </c>
+      <c r="AT9">
+        <v>1.01</v>
+      </c>
+      <c r="AU9">
+        <v>1.01</v>
+      </c>
+      <c r="AV9">
+        <v>1.03</v>
+      </c>
+      <c r="AW9">
+        <v>1.03</v>
+      </c>
+      <c r="AX9">
+        <v>1.03</v>
+      </c>
+      <c r="AY9">
+        <v>1.01</v>
+      </c>
+      <c r="AZ9">
+        <v>1.01</v>
+      </c>
+      <c r="BA9">
+        <v>1.03</v>
+      </c>
+      <c r="BB9">
+        <v>1.01</v>
+      </c>
+      <c r="BC9">
+        <v>1.03</v>
+      </c>
+      <c r="BD9">
+        <v>1.01</v>
+      </c>
+      <c r="BE9">
+        <v>1.01</v>
+      </c>
+      <c r="BF9">
+        <v>1.01</v>
+      </c>
+      <c r="BG9">
+        <v>1.01</v>
+      </c>
+      <c r="BH9">
+        <v>1000</v>
+      </c>
+      <c r="BI9">
+        <v>1.01</v>
+      </c>
+      <c r="BJ9">
+        <v>1000</v>
+      </c>
+      <c r="BK9">
+        <v>1.01</v>
+      </c>
+      <c r="BL9">
+        <v>1000</v>
+      </c>
+      <c r="BM9">
+        <v>1.01</v>
+      </c>
+      <c r="BN9">
+        <v>1000</v>
+      </c>
+      <c r="BO9">
+        <v>1.01</v>
+      </c>
+      <c r="BP9">
+        <v>1000</v>
+      </c>
+      <c r="BQ9">
+        <v>1.01</v>
+      </c>
+      <c r="BR9">
+        <v>1000</v>
+      </c>
+      <c r="BS9">
+        <v>1.01</v>
+      </c>
+      <c r="BT9">
+        <v>1000</v>
+      </c>
+      <c r="BU9">
+        <v>1.01</v>
+      </c>
+      <c r="BV9">
+        <v>1000</v>
+      </c>
+      <c r="BW9">
+        <v>1.01</v>
+      </c>
+      <c r="BX9">
+        <v>1000</v>
+      </c>
+      <c r="BY9">
+        <v>1.01</v>
+      </c>
+      <c r="BZ9">
+        <v>1000</v>
+      </c>
+      <c r="CA9">
+        <v>1.01</v>
+      </c>
+      <c r="CB9" t="s">
+        <v>111</v>
       </c>
     </row>
   </sheetData>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-08-11.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-08-11.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="128" uniqueCount="112">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="158" uniqueCount="126">
   <si>
     <t>League</t>
   </si>
@@ -274,12 +274,18 @@
     <t>Swedish Superettan</t>
   </si>
   <si>
+    <t>South African Premier Division</t>
+  </si>
+  <si>
     <t>CONMEBOL Copa Libertadores</t>
   </si>
   <si>
     <t>Brazilian Serie B</t>
   </si>
   <si>
+    <t>Chilean Primera B</t>
+  </si>
+  <si>
     <t>2026-08-11</t>
   </si>
   <si>
@@ -295,12 +301,18 @@
     <t>17:00:00</t>
   </si>
   <si>
+    <t>17:30:00</t>
+  </si>
+  <si>
     <t>22:00:00</t>
   </si>
   <si>
     <t>22:30:00</t>
   </si>
   <si>
+    <t>23:00:00</t>
+  </si>
+  <si>
     <t>America MG (W)</t>
   </si>
   <si>
@@ -319,12 +331,27 @@
     <t>Helsingborgs</t>
   </si>
   <si>
+    <t>Chippa Utd</t>
+  </si>
+  <si>
+    <t>TS Galaxy FC</t>
+  </si>
+  <si>
+    <t>Polokwane City</t>
+  </si>
+  <si>
+    <t>Marumo Gallants FC</t>
+  </si>
+  <si>
     <t>Fluminense</t>
   </si>
   <si>
     <t>Avai</t>
   </si>
   <si>
+    <t>Puerto Montt</t>
+  </si>
+  <si>
     <t>CR Flamengo (W)</t>
   </si>
   <si>
@@ -343,13 +370,28 @@
     <t>Varnamo</t>
   </si>
   <si>
+    <t>Richards Bay FC</t>
+  </si>
+  <si>
+    <t>Mamelodi Sundowns</t>
+  </si>
+  <si>
+    <t>Stellenbosch FC</t>
+  </si>
+  <si>
+    <t>Kruger United FC</t>
+  </si>
+  <si>
     <t>Independiente Rivadavia</t>
   </si>
   <si>
     <t>CRB</t>
   </si>
   <si>
-    <t>2026-08-10 01:43:53</t>
+    <t>Union Espanola</t>
+  </si>
+  <si>
+    <t>2026-08-10 03:53:36</t>
   </si>
 </sst>
 </file>
@@ -681,7 +723,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:CB9"/>
+  <dimension ref="A1:CB14"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:80">
@@ -931,34 +973,34 @@
         <v>80</v>
       </c>
       <c r="B2" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="C2" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="D2" t="s">
-        <v>95</v>
+        <v>99</v>
       </c>
       <c r="E2" t="s">
-        <v>103</v>
+        <v>112</v>
       </c>
       <c r="F2">
-        <v>9.199999999999999</v>
+        <v>10</v>
       </c>
       <c r="G2">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="H2">
         <v>1.29</v>
       </c>
       <c r="I2">
-        <v>1.36</v>
+        <v>1.34</v>
       </c>
       <c r="J2">
         <v>5.1</v>
       </c>
       <c r="K2">
-        <v>6.4</v>
+        <v>7.8</v>
       </c>
       <c r="L2">
         <v>1.29</v>
@@ -967,52 +1009,52 @@
         <v>1.03</v>
       </c>
       <c r="N2">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="O2">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="P2">
         <v>2.24</v>
       </c>
       <c r="Q2">
-        <v>1.61</v>
+        <v>1.6</v>
       </c>
       <c r="R2">
         <v>1.5</v>
       </c>
       <c r="S2">
-        <v>2.54</v>
+        <v>2.52</v>
       </c>
       <c r="T2">
-        <v>2.04</v>
+        <v>2.08</v>
       </c>
       <c r="U2">
-        <v>1.75</v>
+        <v>1.72</v>
       </c>
       <c r="V2">
-        <v>3.7</v>
+        <v>3.85</v>
       </c>
       <c r="W2">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="X2">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="Y2">
         <v>9.4</v>
       </c>
       <c r="Z2">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="AA2">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AB2">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="AC2">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AD2">
         <v>13</v>
@@ -1021,61 +1063,61 @@
         <v>15.5</v>
       </c>
       <c r="AF2">
-        <v>140</v>
+        <v>160</v>
       </c>
       <c r="AG2">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="AH2">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="AI2">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="AJ2">
-        <v>550</v>
+        <v>1000</v>
       </c>
       <c r="AK2">
-        <v>240</v>
+        <v>290</v>
       </c>
       <c r="AL2">
-        <v>180</v>
+        <v>220</v>
       </c>
       <c r="AM2">
-        <v>200</v>
+        <v>230</v>
       </c>
       <c r="AN2">
-        <v>310</v>
+        <v>420</v>
       </c>
       <c r="AO2">
-        <v>5.3</v>
+        <v>5.1</v>
       </c>
       <c r="AP2">
-        <v>5.5</v>
+        <v>5.4</v>
       </c>
       <c r="AQ2">
         <v>3.95</v>
       </c>
       <c r="AR2">
-        <v>3.8</v>
+        <v>3.75</v>
       </c>
       <c r="AS2">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="AT2">
-        <v>6</v>
+        <v>5.9</v>
       </c>
       <c r="AU2">
         <v>4.6</v>
       </c>
       <c r="AV2">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="AW2">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="AX2">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="AY2">
         <v>6</v>
@@ -1099,19 +1141,19 @@
         <v>6.6</v>
       </c>
       <c r="BF2">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="BG2">
-        <v>3</v>
+        <v>2.9</v>
       </c>
       <c r="BH2">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="BI2">
-        <v>2.42</v>
+        <v>2.44</v>
       </c>
       <c r="BJ2">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="BK2">
         <v>3.65</v>
@@ -1123,10 +1165,10 @@
         <v>4.7</v>
       </c>
       <c r="BN2">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="BO2">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="BP2">
         <v>1000</v>
@@ -1144,13 +1186,13 @@
         <v>4.4</v>
       </c>
       <c r="BU2">
-        <v>2.3</v>
+        <v>2.96</v>
       </c>
       <c r="BV2">
-        <v>9</v>
+        <v>8.6</v>
       </c>
       <c r="BW2">
-        <v>3.15</v>
+        <v>3.05</v>
       </c>
       <c r="BX2">
         <v>29</v>
@@ -1159,13 +1201,13 @@
         <v>4.1</v>
       </c>
       <c r="BZ2">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="CA2">
-        <v>3.6</v>
+        <v>3.55</v>
       </c>
       <c r="CB2" t="s">
-        <v>111</v>
+        <v>125</v>
       </c>
     </row>
     <row r="3" spans="1:80">
@@ -1173,28 +1215,28 @@
         <v>81</v>
       </c>
       <c r="B3" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="C3" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="D3" t="s">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="E3" t="s">
-        <v>104</v>
+        <v>113</v>
       </c>
       <c r="F3">
         <v>2.38</v>
       </c>
       <c r="G3">
-        <v>2.46</v>
+        <v>2.48</v>
       </c>
       <c r="H3">
-        <v>3.2</v>
+        <v>3.15</v>
       </c>
       <c r="I3">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="J3">
         <v>3.45</v>
@@ -1215,7 +1257,7 @@
         <v>1.37</v>
       </c>
       <c r="P3">
-        <v>1.82</v>
+        <v>1.83</v>
       </c>
       <c r="Q3">
         <v>2.14</v>
@@ -1224,10 +1266,10 @@
         <v>1.31</v>
       </c>
       <c r="S3">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="T3">
-        <v>1.84</v>
+        <v>1.83</v>
       </c>
       <c r="U3">
         <v>2.06</v>
@@ -1236,31 +1278,31 @@
         <v>1.42</v>
       </c>
       <c r="W3">
-        <v>1.68</v>
+        <v>1.67</v>
       </c>
       <c r="X3">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="Y3">
-        <v>14.5</v>
+        <v>13.5</v>
       </c>
       <c r="Z3">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="AA3">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="AB3">
-        <v>9</v>
+        <v>9.4</v>
       </c>
       <c r="AC3">
-        <v>9.199999999999999</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AD3">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AE3">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="AF3">
         <v>15</v>
@@ -1269,88 +1311,88 @@
         <v>11.5</v>
       </c>
       <c r="AH3">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AI3">
-        <v>65</v>
+        <v>390</v>
       </c>
       <c r="AJ3">
+        <v>38</v>
+      </c>
+      <c r="AK3">
         <v>40</v>
-      </c>
-      <c r="AK3">
-        <v>42</v>
       </c>
       <c r="AL3">
         <v>50</v>
       </c>
       <c r="AM3">
-        <v>130</v>
+        <v>1000</v>
       </c>
       <c r="AN3">
+        <v>27</v>
+      </c>
+      <c r="AO3">
+        <v>48</v>
+      </c>
+      <c r="AP3">
+        <v>11.5</v>
+      </c>
+      <c r="AQ3">
+        <v>10.5</v>
+      </c>
+      <c r="AR3">
+        <v>17.5</v>
+      </c>
+      <c r="AS3">
         <v>28</v>
       </c>
-      <c r="AO3">
-        <v>50</v>
-      </c>
-      <c r="AP3">
-        <v>9.6</v>
-      </c>
-      <c r="AQ3">
-        <v>9.4</v>
-      </c>
-      <c r="AR3">
-        <v>16</v>
-      </c>
-      <c r="AS3">
-        <v>6.4</v>
-      </c>
       <c r="AT3">
-        <v>6.8</v>
+        <v>8.6</v>
       </c>
       <c r="AU3">
-        <v>6</v>
+        <v>7.2</v>
       </c>
       <c r="AV3">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AW3">
-        <v>6.2</v>
+        <v>30</v>
       </c>
       <c r="AX3">
         <v>12.5</v>
       </c>
       <c r="AY3">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AZ3">
-        <v>14</v>
+        <v>16.5</v>
       </c>
       <c r="BA3">
-        <v>6.4</v>
+        <v>38</v>
       </c>
       <c r="BB3">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="BC3">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="BD3">
-        <v>6.2</v>
+        <v>32</v>
       </c>
       <c r="BE3">
-        <v>6.6</v>
+        <v>40</v>
       </c>
       <c r="BF3">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="BG3">
-        <v>6.2</v>
+        <v>30</v>
       </c>
       <c r="BH3">
         <v>3.65</v>
       </c>
       <c r="BI3">
-        <v>2.58</v>
+        <v>2.6</v>
       </c>
       <c r="BJ3">
         <v>12</v>
@@ -1362,7 +1404,7 @@
         <v>1000</v>
       </c>
       <c r="BM3">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="BN3">
         <v>6.2</v>
@@ -1377,7 +1419,7 @@
         <v>4.2</v>
       </c>
       <c r="BR3">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="BS3">
         <v>4.5</v>
@@ -1386,7 +1428,7 @@
         <v>7.4</v>
       </c>
       <c r="BU3">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="BV3">
         <v>32</v>
@@ -1407,7 +1449,7 @@
         <v>4.5</v>
       </c>
       <c r="CB3" t="s">
-        <v>111</v>
+        <v>125</v>
       </c>
     </row>
     <row r="4" spans="1:80">
@@ -1415,19 +1457,19 @@
         <v>82</v>
       </c>
       <c r="B4" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="C4" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="D4" t="s">
-        <v>97</v>
+        <v>101</v>
       </c>
       <c r="E4" t="s">
-        <v>105</v>
+        <v>114</v>
       </c>
       <c r="F4">
-        <v>1.67</v>
+        <v>1.65</v>
       </c>
       <c r="G4">
         <v>1.72</v>
@@ -1436,43 +1478,43 @@
         <v>6.6</v>
       </c>
       <c r="I4">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="J4">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="K4">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="L4">
-        <v>1.56</v>
+        <v>1.51</v>
       </c>
       <c r="M4">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="N4">
-        <v>2.88</v>
+        <v>3</v>
       </c>
       <c r="O4">
-        <v>1.48</v>
+        <v>1.47</v>
       </c>
       <c r="P4">
-        <v>1.61</v>
+        <v>1.66</v>
       </c>
       <c r="Q4">
-        <v>2.48</v>
+        <v>2.34</v>
       </c>
       <c r="R4">
-        <v>1.22</v>
+        <v>1.24</v>
       </c>
       <c r="S4">
-        <v>5</v>
+        <v>4.7</v>
       </c>
       <c r="T4">
-        <v>2.28</v>
+        <v>2.22</v>
       </c>
       <c r="U4">
-        <v>1.65</v>
+        <v>1.7</v>
       </c>
       <c r="V4">
         <v>1.15</v>
@@ -1481,25 +1523,25 @@
         <v>2.38</v>
       </c>
       <c r="X4">
-        <v>11</v>
+        <v>12.5</v>
       </c>
       <c r="Y4">
         <v>18.5</v>
       </c>
       <c r="Z4">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="AA4">
         <v>300</v>
       </c>
       <c r="AB4">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="AC4">
         <v>9</v>
       </c>
       <c r="AD4">
-        <v>32</v>
+        <v>950</v>
       </c>
       <c r="AE4">
         <v>170</v>
@@ -1514,28 +1556,28 @@
         <v>950</v>
       </c>
       <c r="AI4">
-        <v>170</v>
+        <v>160</v>
       </c>
       <c r="AJ4">
         <v>17</v>
       </c>
       <c r="AK4">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AL4">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AM4">
+        <v>240</v>
+      </c>
+      <c r="AN4">
+        <v>14.5</v>
+      </c>
+      <c r="AO4">
         <v>270</v>
       </c>
-      <c r="AN4">
-        <v>15.5</v>
-      </c>
-      <c r="AO4">
-        <v>340</v>
-      </c>
       <c r="AP4">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AQ4">
         <v>14.5</v>
@@ -1547,7 +1589,7 @@
         <v>9.800000000000001</v>
       </c>
       <c r="AT4">
-        <v>5.3</v>
+        <v>5.5</v>
       </c>
       <c r="AU4">
         <v>7.4</v>
@@ -1556,7 +1598,7 @@
         <v>7.6</v>
       </c>
       <c r="AW4">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="AX4">
         <v>7.4</v>
@@ -1568,10 +1610,10 @@
         <v>7.6</v>
       </c>
       <c r="BA4">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="BB4">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="BC4">
         <v>17.5</v>
@@ -1580,22 +1622,22 @@
         <v>8.6</v>
       </c>
       <c r="BE4">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="BF4">
+        <v>11</v>
+      </c>
+      <c r="BG4">
+        <v>9.6</v>
+      </c>
+      <c r="BH4">
+        <v>3.1</v>
+      </c>
+      <c r="BI4">
+        <v>2.56</v>
+      </c>
+      <c r="BJ4">
         <v>12.5</v>
-      </c>
-      <c r="BG4">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="BH4">
-        <v>3</v>
-      </c>
-      <c r="BI4">
-        <v>2.44</v>
-      </c>
-      <c r="BJ4">
-        <v>13.5</v>
       </c>
       <c r="BK4">
         <v>9.800000000000001</v>
@@ -1604,52 +1646,52 @@
         <v>1000</v>
       </c>
       <c r="BM4">
-        <v>10.5</v>
+        <v>12.5</v>
       </c>
       <c r="BN4">
         <v>4</v>
       </c>
       <c r="BO4">
-        <v>3.15</v>
+        <v>3.45</v>
       </c>
       <c r="BP4">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="BQ4">
+        <v>9.4</v>
+      </c>
+      <c r="BR4">
+        <v>1000</v>
+      </c>
+      <c r="BS4">
+        <v>9.6</v>
+      </c>
+      <c r="BT4">
+        <v>10.5</v>
+      </c>
+      <c r="BU4">
         <v>5.9</v>
       </c>
-      <c r="BR4">
-        <v>1000</v>
-      </c>
-      <c r="BS4">
-        <v>8.6</v>
-      </c>
-      <c r="BT4">
+      <c r="BV4">
+        <v>1000</v>
+      </c>
+      <c r="BW4">
         <v>11</v>
       </c>
-      <c r="BU4">
-        <v>5.5</v>
-      </c>
-      <c r="BV4">
-        <v>1000</v>
-      </c>
-      <c r="BW4">
-        <v>9.800000000000001</v>
-      </c>
       <c r="BX4">
         <v>1000</v>
       </c>
       <c r="BY4">
-        <v>10</v>
+        <v>11.5</v>
       </c>
       <c r="BZ4">
         <v>1000</v>
       </c>
       <c r="CA4">
-        <v>8.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="CB4" t="s">
-        <v>111</v>
+        <v>125</v>
       </c>
     </row>
     <row r="5" spans="1:80">
@@ -1657,28 +1699,28 @@
         <v>83</v>
       </c>
       <c r="B5" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="C5" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="D5" t="s">
-        <v>98</v>
+        <v>102</v>
       </c>
       <c r="E5" t="s">
-        <v>106</v>
+        <v>115</v>
       </c>
       <c r="F5">
         <v>1.56</v>
       </c>
       <c r="G5">
-        <v>1.62</v>
+        <v>1.6</v>
       </c>
       <c r="H5">
         <v>7.4</v>
       </c>
       <c r="I5">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="J5">
         <v>4.1</v>
@@ -1687,7 +1729,7 @@
         <v>4.3</v>
       </c>
       <c r="L5">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="M5">
         <v>1.08</v>
@@ -1699,16 +1741,16 @@
         <v>1.39</v>
       </c>
       <c r="P5">
-        <v>1.81</v>
+        <v>1.8</v>
       </c>
       <c r="Q5">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="R5">
         <v>1.3</v>
       </c>
       <c r="S5">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="T5">
         <v>2.22</v>
@@ -1717,13 +1759,13 @@
         <v>1.72</v>
       </c>
       <c r="V5">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="W5">
-        <v>2.62</v>
+        <v>2.66</v>
       </c>
       <c r="X5">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="Y5">
         <v>21</v>
@@ -1774,7 +1816,7 @@
         <v>11.5</v>
       </c>
       <c r="AO5">
-        <v>280</v>
+        <v>290</v>
       </c>
       <c r="AP5">
         <v>11</v>
@@ -1783,10 +1825,10 @@
         <v>16.5</v>
       </c>
       <c r="AR5">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AS5">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AT5">
         <v>5.9</v>
@@ -1798,7 +1840,7 @@
         <v>23</v>
       </c>
       <c r="AW5">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="AX5">
         <v>7.2</v>
@@ -1810,7 +1852,7 @@
         <v>24</v>
       </c>
       <c r="BA5">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="BB5">
         <v>12</v>
@@ -1822,13 +1864,13 @@
         <v>34</v>
       </c>
       <c r="BE5">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BF5">
         <v>9</v>
       </c>
       <c r="BG5">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BH5">
         <v>3.25</v>
@@ -1891,7 +1933,7 @@
         <v>8.4</v>
       </c>
       <c r="CB5" t="s">
-        <v>111</v>
+        <v>125</v>
       </c>
     </row>
     <row r="6" spans="1:80">
@@ -1899,34 +1941,34 @@
         <v>84</v>
       </c>
       <c r="B6" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="C6" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="D6" t="s">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="E6" t="s">
-        <v>107</v>
+        <v>116</v>
       </c>
       <c r="F6">
-        <v>1.38</v>
+        <v>1.35</v>
       </c>
       <c r="G6">
-        <v>1.41</v>
+        <v>1.37</v>
       </c>
       <c r="H6">
-        <v>10.5</v>
+        <v>11.5</v>
       </c>
       <c r="I6">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="J6">
-        <v>5.1</v>
+        <v>5.3</v>
       </c>
       <c r="K6">
-        <v>5.5</v>
+        <v>5.8</v>
       </c>
       <c r="L6">
         <v>1.36</v>
@@ -1941,28 +1983,28 @@
         <v>1.27</v>
       </c>
       <c r="P6">
-        <v>2.14</v>
+        <v>2.16</v>
       </c>
       <c r="Q6">
-        <v>1.81</v>
+        <v>1.8</v>
       </c>
       <c r="R6">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="S6">
-        <v>3.1</v>
+        <v>3.05</v>
       </c>
       <c r="T6">
-        <v>2.12</v>
+        <v>2.2</v>
       </c>
       <c r="U6">
-        <v>1.75</v>
+        <v>1.71</v>
       </c>
       <c r="V6">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="W6">
-        <v>3.4</v>
+        <v>3.7</v>
       </c>
       <c r="X6">
         <v>21</v>
@@ -1971,10 +2013,10 @@
         <v>36</v>
       </c>
       <c r="Z6">
-        <v>110</v>
+        <v>140</v>
       </c>
       <c r="AA6">
-        <v>470</v>
+        <v>1000</v>
       </c>
       <c r="AB6">
         <v>8</v>
@@ -1983,10 +2025,10 @@
         <v>12.5</v>
       </c>
       <c r="AD6">
-        <v>44</v>
+        <v>950</v>
       </c>
       <c r="AE6">
-        <v>210</v>
+        <v>280</v>
       </c>
       <c r="AF6">
         <v>8</v>
@@ -1998,10 +2040,10 @@
         <v>34</v>
       </c>
       <c r="AI6">
-        <v>170</v>
+        <v>220</v>
       </c>
       <c r="AJ6">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AK6">
         <v>16.5</v>
@@ -2016,19 +2058,19 @@
         <v>6.4</v>
       </c>
       <c r="AO6">
-        <v>310</v>
+        <v>460</v>
       </c>
       <c r="AP6">
         <v>14</v>
       </c>
       <c r="AQ6">
-        <v>8</v>
+        <v>7.6</v>
       </c>
       <c r="AR6">
-        <v>9.4</v>
+        <v>9</v>
       </c>
       <c r="AS6">
-        <v>10</v>
+        <v>9.6</v>
       </c>
       <c r="AT6">
         <v>6.6</v>
@@ -2037,10 +2079,10 @@
         <v>10.5</v>
       </c>
       <c r="AV6">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="AW6">
-        <v>9.800000000000001</v>
+        <v>9.4</v>
       </c>
       <c r="AX6">
         <v>6.4</v>
@@ -2049,70 +2091,70 @@
         <v>9.199999999999999</v>
       </c>
       <c r="AZ6">
-        <v>7.8</v>
+        <v>7.4</v>
       </c>
       <c r="BA6">
-        <v>9.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BB6">
-        <v>9.800000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BC6">
         <v>12</v>
       </c>
       <c r="BD6">
-        <v>8.4</v>
+        <v>8</v>
       </c>
       <c r="BE6">
-        <v>9.800000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BF6">
         <v>5.4</v>
       </c>
       <c r="BG6">
-        <v>9.800000000000001</v>
+        <v>9.4</v>
       </c>
       <c r="BH6">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="BI6">
         <v>3.1</v>
       </c>
       <c r="BJ6">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="BK6">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="BL6">
         <v>1000</v>
       </c>
       <c r="BM6">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="BN6">
-        <v>3.85</v>
+        <v>3.75</v>
       </c>
       <c r="BO6">
-        <v>3.05</v>
+        <v>3.2</v>
       </c>
       <c r="BP6">
-        <v>8.4</v>
+        <v>8</v>
       </c>
       <c r="BQ6">
-        <v>4.7</v>
+        <v>6</v>
       </c>
       <c r="BR6">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="BS6">
         <v>7.8</v>
       </c>
       <c r="BT6">
-        <v>14</v>
+        <v>15.5</v>
       </c>
       <c r="BU6">
-        <v>6</v>
+        <v>6.4</v>
       </c>
       <c r="BV6">
         <v>1000</v>
@@ -2124,16 +2166,16 @@
         <v>1000</v>
       </c>
       <c r="BY6">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="BZ6">
-        <v>15.5</v>
+        <v>14.5</v>
       </c>
       <c r="CA6">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="CB6" t="s">
-        <v>111</v>
+        <v>125</v>
       </c>
     </row>
     <row r="7" spans="1:80">
@@ -2141,37 +2183,37 @@
         <v>85</v>
       </c>
       <c r="B7" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="C7" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="D7" t="s">
-        <v>100</v>
+        <v>104</v>
       </c>
       <c r="E7" t="s">
-        <v>108</v>
+        <v>117</v>
       </c>
       <c r="F7">
-        <v>2.08</v>
+        <v>2.12</v>
       </c>
       <c r="G7">
-        <v>2.26</v>
+        <v>2.3</v>
       </c>
       <c r="H7">
         <v>3.25</v>
       </c>
       <c r="I7">
-        <v>3.65</v>
+        <v>3.55</v>
       </c>
       <c r="J7">
-        <v>3.85</v>
+        <v>3.8</v>
       </c>
       <c r="K7">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="L7">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="M7">
         <v>1.04</v>
@@ -2180,43 +2222,43 @@
         <v>4.8</v>
       </c>
       <c r="O7">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="P7">
         <v>2.3</v>
       </c>
       <c r="Q7">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="R7">
         <v>1.52</v>
       </c>
       <c r="S7">
-        <v>2.64</v>
+        <v>2.7</v>
       </c>
       <c r="T7">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="U7">
         <v>2.42</v>
       </c>
       <c r="V7">
-        <v>1.37</v>
+        <v>1.39</v>
       </c>
       <c r="W7">
-        <v>1.79</v>
+        <v>1.78</v>
       </c>
       <c r="X7">
         <v>26</v>
       </c>
       <c r="Y7">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="Z7">
         <v>34</v>
       </c>
       <c r="AA7">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="AB7">
         <v>15.5</v>
@@ -2246,7 +2288,7 @@
         <v>36</v>
       </c>
       <c r="AK7">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AL7">
         <v>40</v>
@@ -2255,22 +2297,22 @@
         <v>80</v>
       </c>
       <c r="AN7">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="AO7">
         <v>32</v>
       </c>
       <c r="AP7">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="AQ7">
-        <v>12.5</v>
+        <v>14.5</v>
       </c>
       <c r="AR7">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="AS7">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="AT7">
         <v>11</v>
@@ -2279,40 +2321,40 @@
         <v>8.199999999999999</v>
       </c>
       <c r="AV7">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AW7">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="AX7">
         <v>11.5</v>
       </c>
       <c r="AY7">
-        <v>8.199999999999999</v>
+        <v>10</v>
       </c>
       <c r="AZ7">
         <v>11.5</v>
       </c>
       <c r="BA7">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="BB7">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="BC7">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="BD7">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="BE7">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="BF7">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="BG7">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="BH7">
         <v>4.1</v>
@@ -2324,31 +2366,31 @@
         <v>8.800000000000001</v>
       </c>
       <c r="BK7">
-        <v>5.5</v>
+        <v>5.4</v>
       </c>
       <c r="BL7">
         <v>1000</v>
       </c>
       <c r="BM7">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="BN7">
         <v>5.4</v>
       </c>
       <c r="BO7">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="BP7">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="BQ7">
-        <v>11</v>
+        <v>7.2</v>
       </c>
       <c r="BR7">
         <v>1000</v>
       </c>
       <c r="BS7">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="BT7">
         <v>7</v>
@@ -2360,13 +2402,13 @@
         <v>34</v>
       </c>
       <c r="BW7">
-        <v>9.4</v>
+        <v>9</v>
       </c>
       <c r="BX7">
         <v>46</v>
       </c>
       <c r="BY7">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BZ7">
         <v>0</v>
@@ -2375,7 +2417,7 @@
         <v>0</v>
       </c>
       <c r="CB7" t="s">
-        <v>111</v>
+        <v>125</v>
       </c>
     </row>
     <row r="8" spans="1:80">
@@ -2383,46 +2425,46 @@
         <v>86</v>
       </c>
       <c r="B8" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="C8" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="D8" t="s">
-        <v>101</v>
+        <v>105</v>
       </c>
       <c r="E8" t="s">
-        <v>109</v>
+        <v>118</v>
       </c>
       <c r="F8">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="G8">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="H8">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="I8">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="J8">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="K8">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="L8">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M8">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N8">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="O8">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="P8">
         <v>1.24</v>
@@ -2431,264 +2473,264 @@
         <v>1.01</v>
       </c>
       <c r="R8">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="S8">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="T8">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="U8">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V8">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W8">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X8">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y8">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z8">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA8">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB8">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC8">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD8">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE8">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF8">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG8">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH8">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI8">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ8">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK8">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL8">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM8">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN8">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO8">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP8">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AQ8">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AR8">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AS8">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AT8">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AU8">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AV8">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AW8">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AX8">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AY8">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AZ8">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BA8">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BB8">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BC8">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BD8">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BE8">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BF8">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG8">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH8">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BI8">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BJ8">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BK8">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BL8">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM8">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BN8">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BO8">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BP8">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BQ8">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BR8">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS8">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BT8">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BU8">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BV8">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW8">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BX8">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY8">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BZ8">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA8">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="CB8" t="s">
-        <v>111</v>
+        <v>125</v>
       </c>
     </row>
     <row r="9" spans="1:80">
       <c r="A9" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="B9" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="C9" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="D9" t="s">
-        <v>102</v>
+        <v>106</v>
       </c>
       <c r="E9" t="s">
-        <v>110</v>
+        <v>119</v>
       </c>
       <c r="F9">
-        <v>2.78</v>
+        <v>1.04</v>
       </c>
       <c r="G9">
-        <v>3.45</v>
+        <v>1000</v>
       </c>
       <c r="H9">
-        <v>2.42</v>
+        <v>1.04</v>
       </c>
       <c r="I9">
-        <v>3.2</v>
+        <v>1000</v>
       </c>
       <c r="J9">
-        <v>2.92</v>
+        <v>1.01</v>
       </c>
       <c r="K9">
-        <v>4.4</v>
+        <v>1000</v>
       </c>
       <c r="L9">
         <v>1.01</v>
       </c>
       <c r="M9">
-        <v>1.08</v>
+        <v>1.01</v>
       </c>
       <c r="N9">
-        <v>2.92</v>
+        <v>1.24</v>
       </c>
       <c r="O9">
         <v>1.37</v>
       </c>
       <c r="P9">
-        <v>1.64</v>
+        <v>1.24</v>
       </c>
       <c r="Q9">
-        <v>2.12</v>
+        <v>1.37</v>
       </c>
       <c r="R9">
-        <v>1.23</v>
+        <v>1.13</v>
       </c>
       <c r="S9">
-        <v>3.3</v>
+        <v>1.37</v>
       </c>
       <c r="T9">
-        <v>1.65</v>
+        <v>1.01</v>
       </c>
       <c r="U9">
-        <v>1.87</v>
+        <v>1.01</v>
       </c>
       <c r="V9">
-        <v>1.46</v>
+        <v>1.01</v>
       </c>
       <c r="W9">
-        <v>1.4</v>
+        <v>1.01</v>
       </c>
       <c r="X9">
         <v>1000</v>
@@ -2745,7 +2787,7 @@
         <v>1000</v>
       </c>
       <c r="AP9">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AQ9">
         <v>1.01</v>
@@ -2763,13 +2805,13 @@
         <v>1.01</v>
       </c>
       <c r="AV9">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AW9">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AX9">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AY9">
         <v>1.01</v>
@@ -2778,13 +2820,13 @@
         <v>1.01</v>
       </c>
       <c r="BA9">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BB9">
         <v>1.01</v>
       </c>
       <c r="BC9">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BD9">
         <v>1.01</v>
@@ -2859,7 +2901,1217 @@
         <v>1.01</v>
       </c>
       <c r="CB9" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="10" spans="1:80">
+      <c r="A10" t="s">
+        <v>86</v>
+      </c>
+      <c r="B10" t="s">
+        <v>90</v>
+      </c>
+      <c r="C10" t="s">
+        <v>95</v>
+      </c>
+      <c r="D10" t="s">
+        <v>107</v>
+      </c>
+      <c r="E10" t="s">
+        <v>120</v>
+      </c>
+      <c r="F10">
+        <v>1.04</v>
+      </c>
+      <c r="G10">
+        <v>1000</v>
+      </c>
+      <c r="H10">
+        <v>1.04</v>
+      </c>
+      <c r="I10">
+        <v>1000</v>
+      </c>
+      <c r="J10">
+        <v>1.01</v>
+      </c>
+      <c r="K10">
+        <v>1000</v>
+      </c>
+      <c r="L10">
+        <v>1.01</v>
+      </c>
+      <c r="M10">
+        <v>1.01</v>
+      </c>
+      <c r="N10">
+        <v>1.24</v>
+      </c>
+      <c r="O10">
+        <v>1.01</v>
+      </c>
+      <c r="P10">
+        <v>1.24</v>
+      </c>
+      <c r="Q10">
+        <v>1.01</v>
+      </c>
+      <c r="R10">
+        <v>1.13</v>
+      </c>
+      <c r="S10">
+        <v>1.02</v>
+      </c>
+      <c r="T10">
+        <v>1.01</v>
+      </c>
+      <c r="U10">
+        <v>1.01</v>
+      </c>
+      <c r="V10">
+        <v>1.01</v>
+      </c>
+      <c r="W10">
+        <v>1.01</v>
+      </c>
+      <c r="X10">
+        <v>1000</v>
+      </c>
+      <c r="Y10">
+        <v>1000</v>
+      </c>
+      <c r="Z10">
+        <v>1000</v>
+      </c>
+      <c r="AA10">
+        <v>1000</v>
+      </c>
+      <c r="AB10">
+        <v>1000</v>
+      </c>
+      <c r="AC10">
+        <v>1000</v>
+      </c>
+      <c r="AD10">
+        <v>1000</v>
+      </c>
+      <c r="AE10">
+        <v>1000</v>
+      </c>
+      <c r="AF10">
+        <v>1000</v>
+      </c>
+      <c r="AG10">
+        <v>1000</v>
+      </c>
+      <c r="AH10">
+        <v>1000</v>
+      </c>
+      <c r="AI10">
+        <v>1000</v>
+      </c>
+      <c r="AJ10">
+        <v>1000</v>
+      </c>
+      <c r="AK10">
+        <v>1000</v>
+      </c>
+      <c r="AL10">
+        <v>1000</v>
+      </c>
+      <c r="AM10">
+        <v>1000</v>
+      </c>
+      <c r="AN10">
+        <v>1000</v>
+      </c>
+      <c r="AO10">
+        <v>1000</v>
+      </c>
+      <c r="AP10">
+        <v>1.01</v>
+      </c>
+      <c r="AQ10">
+        <v>1.01</v>
+      </c>
+      <c r="AR10">
+        <v>1.01</v>
+      </c>
+      <c r="AS10">
+        <v>1.01</v>
+      </c>
+      <c r="AT10">
+        <v>1.01</v>
+      </c>
+      <c r="AU10">
+        <v>1.01</v>
+      </c>
+      <c r="AV10">
+        <v>1.01</v>
+      </c>
+      <c r="AW10">
+        <v>1.01</v>
+      </c>
+      <c r="AX10">
+        <v>1.01</v>
+      </c>
+      <c r="AY10">
+        <v>1.01</v>
+      </c>
+      <c r="AZ10">
+        <v>1.01</v>
+      </c>
+      <c r="BA10">
+        <v>1.01</v>
+      </c>
+      <c r="BB10">
+        <v>1.01</v>
+      </c>
+      <c r="BC10">
+        <v>1.01</v>
+      </c>
+      <c r="BD10">
+        <v>1.01</v>
+      </c>
+      <c r="BE10">
+        <v>1.01</v>
+      </c>
+      <c r="BF10">
+        <v>1.01</v>
+      </c>
+      <c r="BG10">
+        <v>1.01</v>
+      </c>
+      <c r="BH10">
+        <v>1000</v>
+      </c>
+      <c r="BI10">
+        <v>1.01</v>
+      </c>
+      <c r="BJ10">
+        <v>1000</v>
+      </c>
+      <c r="BK10">
+        <v>1.01</v>
+      </c>
+      <c r="BL10">
+        <v>1000</v>
+      </c>
+      <c r="BM10">
+        <v>1.01</v>
+      </c>
+      <c r="BN10">
+        <v>1000</v>
+      </c>
+      <c r="BO10">
+        <v>1.01</v>
+      </c>
+      <c r="BP10">
+        <v>1000</v>
+      </c>
+      <c r="BQ10">
+        <v>1.01</v>
+      </c>
+      <c r="BR10">
+        <v>1000</v>
+      </c>
+      <c r="BS10">
+        <v>1.01</v>
+      </c>
+      <c r="BT10">
+        <v>1000</v>
+      </c>
+      <c r="BU10">
+        <v>1.01</v>
+      </c>
+      <c r="BV10">
+        <v>1000</v>
+      </c>
+      <c r="BW10">
+        <v>1.01</v>
+      </c>
+      <c r="BX10">
+        <v>1000</v>
+      </c>
+      <c r="BY10">
+        <v>1.01</v>
+      </c>
+      <c r="BZ10">
+        <v>1000</v>
+      </c>
+      <c r="CA10">
+        <v>1.01</v>
+      </c>
+      <c r="CB10" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="11" spans="1:80">
+      <c r="A11" t="s">
+        <v>86</v>
+      </c>
+      <c r="B11" t="s">
+        <v>90</v>
+      </c>
+      <c r="C11" t="s">
+        <v>95</v>
+      </c>
+      <c r="D11" t="s">
+        <v>108</v>
+      </c>
+      <c r="E11" t="s">
+        <v>121</v>
+      </c>
+      <c r="F11">
+        <v>1.04</v>
+      </c>
+      <c r="G11">
+        <v>1000</v>
+      </c>
+      <c r="H11">
+        <v>1.04</v>
+      </c>
+      <c r="I11">
+        <v>1000</v>
+      </c>
+      <c r="J11">
+        <v>1.01</v>
+      </c>
+      <c r="K11">
+        <v>1000</v>
+      </c>
+      <c r="L11">
+        <v>1.01</v>
+      </c>
+      <c r="M11">
+        <v>1.01</v>
+      </c>
+      <c r="N11">
+        <v>1.24</v>
+      </c>
+      <c r="O11">
+        <v>1.01</v>
+      </c>
+      <c r="P11">
+        <v>1.24</v>
+      </c>
+      <c r="Q11">
+        <v>1.01</v>
+      </c>
+      <c r="R11">
+        <v>1.13</v>
+      </c>
+      <c r="S11">
+        <v>1.02</v>
+      </c>
+      <c r="T11">
+        <v>1.01</v>
+      </c>
+      <c r="U11">
+        <v>1.01</v>
+      </c>
+      <c r="V11">
+        <v>1.01</v>
+      </c>
+      <c r="W11">
+        <v>1.01</v>
+      </c>
+      <c r="X11">
+        <v>1000</v>
+      </c>
+      <c r="Y11">
+        <v>1000</v>
+      </c>
+      <c r="Z11">
+        <v>1000</v>
+      </c>
+      <c r="AA11">
+        <v>1000</v>
+      </c>
+      <c r="AB11">
+        <v>1000</v>
+      </c>
+      <c r="AC11">
+        <v>1000</v>
+      </c>
+      <c r="AD11">
+        <v>1000</v>
+      </c>
+      <c r="AE11">
+        <v>1000</v>
+      </c>
+      <c r="AF11">
+        <v>1000</v>
+      </c>
+      <c r="AG11">
+        <v>1000</v>
+      </c>
+      <c r="AH11">
+        <v>1000</v>
+      </c>
+      <c r="AI11">
+        <v>1000</v>
+      </c>
+      <c r="AJ11">
+        <v>1000</v>
+      </c>
+      <c r="AK11">
+        <v>1000</v>
+      </c>
+      <c r="AL11">
+        <v>1000</v>
+      </c>
+      <c r="AM11">
+        <v>1000</v>
+      </c>
+      <c r="AN11">
+        <v>1000</v>
+      </c>
+      <c r="AO11">
+        <v>1000</v>
+      </c>
+      <c r="AP11">
+        <v>1.01</v>
+      </c>
+      <c r="AQ11">
+        <v>1.01</v>
+      </c>
+      <c r="AR11">
+        <v>1.01</v>
+      </c>
+      <c r="AS11">
+        <v>1.01</v>
+      </c>
+      <c r="AT11">
+        <v>1.01</v>
+      </c>
+      <c r="AU11">
+        <v>1.01</v>
+      </c>
+      <c r="AV11">
+        <v>1.01</v>
+      </c>
+      <c r="AW11">
+        <v>1.01</v>
+      </c>
+      <c r="AX11">
+        <v>1.01</v>
+      </c>
+      <c r="AY11">
+        <v>1.01</v>
+      </c>
+      <c r="AZ11">
+        <v>1.01</v>
+      </c>
+      <c r="BA11">
+        <v>1.01</v>
+      </c>
+      <c r="BB11">
+        <v>1.01</v>
+      </c>
+      <c r="BC11">
+        <v>1.01</v>
+      </c>
+      <c r="BD11">
+        <v>1.01</v>
+      </c>
+      <c r="BE11">
+        <v>1.01</v>
+      </c>
+      <c r="BF11">
+        <v>1.01</v>
+      </c>
+      <c r="BG11">
+        <v>1.01</v>
+      </c>
+      <c r="BH11">
+        <v>1000</v>
+      </c>
+      <c r="BI11">
+        <v>1.01</v>
+      </c>
+      <c r="BJ11">
+        <v>1000</v>
+      </c>
+      <c r="BK11">
+        <v>1.01</v>
+      </c>
+      <c r="BL11">
+        <v>1000</v>
+      </c>
+      <c r="BM11">
+        <v>1.01</v>
+      </c>
+      <c r="BN11">
+        <v>1000</v>
+      </c>
+      <c r="BO11">
+        <v>1.01</v>
+      </c>
+      <c r="BP11">
+        <v>1000</v>
+      </c>
+      <c r="BQ11">
+        <v>1.01</v>
+      </c>
+      <c r="BR11">
+        <v>1000</v>
+      </c>
+      <c r="BS11">
+        <v>1.01</v>
+      </c>
+      <c r="BT11">
+        <v>1000</v>
+      </c>
+      <c r="BU11">
+        <v>1.01</v>
+      </c>
+      <c r="BV11">
+        <v>1000</v>
+      </c>
+      <c r="BW11">
+        <v>1.01</v>
+      </c>
+      <c r="BX11">
+        <v>1000</v>
+      </c>
+      <c r="BY11">
+        <v>1.01</v>
+      </c>
+      <c r="BZ11">
+        <v>1000</v>
+      </c>
+      <c r="CA11">
+        <v>1.01</v>
+      </c>
+      <c r="CB11" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="12" spans="1:80">
+      <c r="A12" t="s">
+        <v>87</v>
+      </c>
+      <c r="B12" t="s">
+        <v>90</v>
+      </c>
+      <c r="C12" t="s">
+        <v>96</v>
+      </c>
+      <c r="D12" t="s">
+        <v>109</v>
+      </c>
+      <c r="E12" t="s">
+        <v>122</v>
+      </c>
+      <c r="F12">
+        <v>0</v>
+      </c>
+      <c r="G12">
+        <v>0</v>
+      </c>
+      <c r="H12">
+        <v>0</v>
+      </c>
+      <c r="I12">
+        <v>0</v>
+      </c>
+      <c r="J12">
+        <v>0</v>
+      </c>
+      <c r="K12">
+        <v>0</v>
+      </c>
+      <c r="L12">
+        <v>0</v>
+      </c>
+      <c r="M12">
+        <v>0</v>
+      </c>
+      <c r="N12">
+        <v>0</v>
+      </c>
+      <c r="O12">
+        <v>0</v>
+      </c>
+      <c r="P12">
+        <v>1.24</v>
+      </c>
+      <c r="Q12">
+        <v>1.01</v>
+      </c>
+      <c r="R12">
+        <v>0</v>
+      </c>
+      <c r="S12">
+        <v>0</v>
+      </c>
+      <c r="T12">
+        <v>0</v>
+      </c>
+      <c r="U12">
+        <v>0</v>
+      </c>
+      <c r="V12">
+        <v>0</v>
+      </c>
+      <c r="W12">
+        <v>0</v>
+      </c>
+      <c r="X12">
+        <v>0</v>
+      </c>
+      <c r="Y12">
+        <v>0</v>
+      </c>
+      <c r="Z12">
+        <v>0</v>
+      </c>
+      <c r="AA12">
+        <v>0</v>
+      </c>
+      <c r="AB12">
+        <v>0</v>
+      </c>
+      <c r="AC12">
+        <v>0</v>
+      </c>
+      <c r="AD12">
+        <v>0</v>
+      </c>
+      <c r="AE12">
+        <v>0</v>
+      </c>
+      <c r="AF12">
+        <v>0</v>
+      </c>
+      <c r="AG12">
+        <v>0</v>
+      </c>
+      <c r="AH12">
+        <v>0</v>
+      </c>
+      <c r="AI12">
+        <v>0</v>
+      </c>
+      <c r="AJ12">
+        <v>0</v>
+      </c>
+      <c r="AK12">
+        <v>0</v>
+      </c>
+      <c r="AL12">
+        <v>0</v>
+      </c>
+      <c r="AM12">
+        <v>0</v>
+      </c>
+      <c r="AN12">
+        <v>0</v>
+      </c>
+      <c r="AO12">
+        <v>0</v>
+      </c>
+      <c r="AP12">
+        <v>0</v>
+      </c>
+      <c r="AQ12">
+        <v>0</v>
+      </c>
+      <c r="AR12">
+        <v>0</v>
+      </c>
+      <c r="AS12">
+        <v>0</v>
+      </c>
+      <c r="AT12">
+        <v>0</v>
+      </c>
+      <c r="AU12">
+        <v>0</v>
+      </c>
+      <c r="AV12">
+        <v>0</v>
+      </c>
+      <c r="AW12">
+        <v>0</v>
+      </c>
+      <c r="AX12">
+        <v>0</v>
+      </c>
+      <c r="AY12">
+        <v>0</v>
+      </c>
+      <c r="AZ12">
+        <v>0</v>
+      </c>
+      <c r="BA12">
+        <v>0</v>
+      </c>
+      <c r="BB12">
+        <v>0</v>
+      </c>
+      <c r="BC12">
+        <v>0</v>
+      </c>
+      <c r="BD12">
+        <v>0</v>
+      </c>
+      <c r="BE12">
+        <v>0</v>
+      </c>
+      <c r="BF12">
+        <v>0</v>
+      </c>
+      <c r="BG12">
+        <v>0</v>
+      </c>
+      <c r="BH12">
+        <v>0</v>
+      </c>
+      <c r="BI12">
+        <v>0</v>
+      </c>
+      <c r="BJ12">
+        <v>0</v>
+      </c>
+      <c r="BK12">
+        <v>0</v>
+      </c>
+      <c r="BL12">
+        <v>0</v>
+      </c>
+      <c r="BM12">
+        <v>0</v>
+      </c>
+      <c r="BN12">
+        <v>0</v>
+      </c>
+      <c r="BO12">
+        <v>0</v>
+      </c>
+      <c r="BP12">
+        <v>0</v>
+      </c>
+      <c r="BQ12">
+        <v>0</v>
+      </c>
+      <c r="BR12">
+        <v>0</v>
+      </c>
+      <c r="BS12">
+        <v>0</v>
+      </c>
+      <c r="BT12">
+        <v>0</v>
+      </c>
+      <c r="BU12">
+        <v>0</v>
+      </c>
+      <c r="BV12">
+        <v>0</v>
+      </c>
+      <c r="BW12">
+        <v>0</v>
+      </c>
+      <c r="BX12">
+        <v>0</v>
+      </c>
+      <c r="BY12">
+        <v>0</v>
+      </c>
+      <c r="BZ12">
+        <v>0</v>
+      </c>
+      <c r="CA12">
+        <v>0</v>
+      </c>
+      <c r="CB12" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="13" spans="1:80">
+      <c r="A13" t="s">
+        <v>88</v>
+      </c>
+      <c r="B13" t="s">
+        <v>90</v>
+      </c>
+      <c r="C13" t="s">
+        <v>97</v>
+      </c>
+      <c r="D13" t="s">
+        <v>110</v>
+      </c>
+      <c r="E13" t="s">
+        <v>123</v>
+      </c>
+      <c r="F13">
+        <v>2.82</v>
+      </c>
+      <c r="G13">
+        <v>3.1</v>
+      </c>
+      <c r="H13">
+        <v>2.66</v>
+      </c>
+      <c r="I13">
+        <v>2.92</v>
+      </c>
+      <c r="J13">
+        <v>3.15</v>
+      </c>
+      <c r="K13">
+        <v>3.5</v>
+      </c>
+      <c r="L13">
+        <v>1.38</v>
+      </c>
+      <c r="M13">
+        <v>1.09</v>
+      </c>
+      <c r="N13">
+        <v>3.15</v>
+      </c>
+      <c r="O13">
+        <v>1.39</v>
+      </c>
+      <c r="P13">
+        <v>1.74</v>
+      </c>
+      <c r="Q13">
+        <v>2.16</v>
+      </c>
+      <c r="R13">
+        <v>1.28</v>
+      </c>
+      <c r="S13">
+        <v>4</v>
+      </c>
+      <c r="T13">
+        <v>1.85</v>
+      </c>
+      <c r="U13">
+        <v>2.02</v>
+      </c>
+      <c r="V13">
+        <v>1.53</v>
+      </c>
+      <c r="W13">
+        <v>1.49</v>
+      </c>
+      <c r="X13">
+        <v>14</v>
+      </c>
+      <c r="Y13">
+        <v>10.5</v>
+      </c>
+      <c r="Z13">
+        <v>18</v>
+      </c>
+      <c r="AA13">
+        <v>65</v>
+      </c>
+      <c r="AB13">
+        <v>10.5</v>
+      </c>
+      <c r="AC13">
+        <v>7.6</v>
+      </c>
+      <c r="AD13">
+        <v>13</v>
+      </c>
+      <c r="AE13">
+        <v>50</v>
+      </c>
+      <c r="AF13">
+        <v>19.5</v>
+      </c>
+      <c r="AG13">
+        <v>13.5</v>
+      </c>
+      <c r="AH13">
+        <v>18.5</v>
+      </c>
+      <c r="AI13">
+        <v>70</v>
+      </c>
+      <c r="AJ13">
+        <v>70</v>
+      </c>
+      <c r="AK13">
+        <v>38</v>
+      </c>
+      <c r="AL13">
+        <v>55</v>
+      </c>
+      <c r="AM13">
+        <v>140</v>
+      </c>
+      <c r="AN13">
+        <v>38</v>
+      </c>
+      <c r="AO13">
+        <v>34</v>
+      </c>
+      <c r="AP13">
+        <v>8.6</v>
+      </c>
+      <c r="AQ13">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AR13">
+        <v>15.5</v>
+      </c>
+      <c r="AS13">
+        <v>29</v>
+      </c>
+      <c r="AT13">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AU13">
+        <v>6.6</v>
+      </c>
+      <c r="AV13">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AW13">
+        <v>8</v>
+      </c>
+      <c r="AX13">
+        <v>14</v>
+      </c>
+      <c r="AY13">
+        <v>11.5</v>
+      </c>
+      <c r="AZ13">
+        <v>16</v>
+      </c>
+      <c r="BA13">
+        <v>8.6</v>
+      </c>
+      <c r="BB13">
+        <v>29</v>
+      </c>
+      <c r="BC13">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BD13">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="BE13">
+        <v>9.6</v>
+      </c>
+      <c r="BF13">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BG13">
+        <v>8</v>
+      </c>
+      <c r="BH13">
+        <v>3.15</v>
+      </c>
+      <c r="BI13">
+        <v>2.6</v>
+      </c>
+      <c r="BJ13">
+        <v>10</v>
+      </c>
+      <c r="BK13">
+        <v>6</v>
+      </c>
+      <c r="BL13">
+        <v>1000</v>
+      </c>
+      <c r="BM13">
+        <v>13.5</v>
+      </c>
+      <c r="BN13">
+        <v>5.9</v>
+      </c>
+      <c r="BO13">
+        <v>4.5</v>
+      </c>
+      <c r="BP13">
+        <v>24</v>
+      </c>
+      <c r="BQ13">
+        <v>9.4</v>
+      </c>
+      <c r="BR13">
+        <v>40</v>
+      </c>
+      <c r="BS13">
+        <v>11</v>
+      </c>
+      <c r="BT13">
+        <v>5.7</v>
+      </c>
+      <c r="BU13">
+        <v>4.3</v>
+      </c>
+      <c r="BV13">
+        <v>23</v>
+      </c>
+      <c r="BW13">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="BX13">
+        <v>1000</v>
+      </c>
+      <c r="BY13">
+        <v>10.5</v>
+      </c>
+      <c r="BZ13">
+        <v>1000</v>
+      </c>
+      <c r="CA13">
+        <v>10.5</v>
+      </c>
+      <c r="CB13" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="14" spans="1:80">
+      <c r="A14" t="s">
+        <v>89</v>
+      </c>
+      <c r="B14" t="s">
+        <v>90</v>
+      </c>
+      <c r="C14" t="s">
+        <v>98</v>
+      </c>
+      <c r="D14" t="s">
         <v>111</v>
+      </c>
+      <c r="E14" t="s">
+        <v>124</v>
+      </c>
+      <c r="F14">
+        <v>1.04</v>
+      </c>
+      <c r="G14">
+        <v>1000</v>
+      </c>
+      <c r="H14">
+        <v>1.04</v>
+      </c>
+      <c r="I14">
+        <v>1000</v>
+      </c>
+      <c r="J14">
+        <v>1.01</v>
+      </c>
+      <c r="K14">
+        <v>1000</v>
+      </c>
+      <c r="L14">
+        <v>1.01</v>
+      </c>
+      <c r="M14">
+        <v>1.01</v>
+      </c>
+      <c r="N14">
+        <v>1.24</v>
+      </c>
+      <c r="O14">
+        <v>1.01</v>
+      </c>
+      <c r="P14">
+        <v>1.24</v>
+      </c>
+      <c r="Q14">
+        <v>1.02</v>
+      </c>
+      <c r="R14">
+        <v>1.18</v>
+      </c>
+      <c r="S14">
+        <v>1.02</v>
+      </c>
+      <c r="T14">
+        <v>1.01</v>
+      </c>
+      <c r="U14">
+        <v>1.01</v>
+      </c>
+      <c r="V14">
+        <v>1.01</v>
+      </c>
+      <c r="W14">
+        <v>1.01</v>
+      </c>
+      <c r="X14">
+        <v>1000</v>
+      </c>
+      <c r="Y14">
+        <v>1000</v>
+      </c>
+      <c r="Z14">
+        <v>1000</v>
+      </c>
+      <c r="AA14">
+        <v>1000</v>
+      </c>
+      <c r="AB14">
+        <v>1000</v>
+      </c>
+      <c r="AC14">
+        <v>1000</v>
+      </c>
+      <c r="AD14">
+        <v>1000</v>
+      </c>
+      <c r="AE14">
+        <v>1000</v>
+      </c>
+      <c r="AF14">
+        <v>1000</v>
+      </c>
+      <c r="AG14">
+        <v>1000</v>
+      </c>
+      <c r="AH14">
+        <v>1000</v>
+      </c>
+      <c r="AI14">
+        <v>1000</v>
+      </c>
+      <c r="AJ14">
+        <v>1000</v>
+      </c>
+      <c r="AK14">
+        <v>1000</v>
+      </c>
+      <c r="AL14">
+        <v>1000</v>
+      </c>
+      <c r="AM14">
+        <v>1000</v>
+      </c>
+      <c r="AN14">
+        <v>1000</v>
+      </c>
+      <c r="AO14">
+        <v>1000</v>
+      </c>
+      <c r="AP14">
+        <v>1.01</v>
+      </c>
+      <c r="AQ14">
+        <v>1.01</v>
+      </c>
+      <c r="AR14">
+        <v>1.01</v>
+      </c>
+      <c r="AS14">
+        <v>1.01</v>
+      </c>
+      <c r="AT14">
+        <v>1.01</v>
+      </c>
+      <c r="AU14">
+        <v>1.01</v>
+      </c>
+      <c r="AV14">
+        <v>1.01</v>
+      </c>
+      <c r="AW14">
+        <v>1.01</v>
+      </c>
+      <c r="AX14">
+        <v>1.01</v>
+      </c>
+      <c r="AY14">
+        <v>1.01</v>
+      </c>
+      <c r="AZ14">
+        <v>1.01</v>
+      </c>
+      <c r="BA14">
+        <v>1.01</v>
+      </c>
+      <c r="BB14">
+        <v>1.01</v>
+      </c>
+      <c r="BC14">
+        <v>1.01</v>
+      </c>
+      <c r="BD14">
+        <v>1.01</v>
+      </c>
+      <c r="BE14">
+        <v>1.01</v>
+      </c>
+      <c r="BF14">
+        <v>1.01</v>
+      </c>
+      <c r="BG14">
+        <v>1.01</v>
+      </c>
+      <c r="BH14">
+        <v>1000</v>
+      </c>
+      <c r="BI14">
+        <v>1.01</v>
+      </c>
+      <c r="BJ14">
+        <v>1000</v>
+      </c>
+      <c r="BK14">
+        <v>1.01</v>
+      </c>
+      <c r="BL14">
+        <v>1000</v>
+      </c>
+      <c r="BM14">
+        <v>1.01</v>
+      </c>
+      <c r="BN14">
+        <v>1000</v>
+      </c>
+      <c r="BO14">
+        <v>1.01</v>
+      </c>
+      <c r="BP14">
+        <v>1000</v>
+      </c>
+      <c r="BQ14">
+        <v>1.01</v>
+      </c>
+      <c r="BR14">
+        <v>1000</v>
+      </c>
+      <c r="BS14">
+        <v>1.01</v>
+      </c>
+      <c r="BT14">
+        <v>1000</v>
+      </c>
+      <c r="BU14">
+        <v>1.01</v>
+      </c>
+      <c r="BV14">
+        <v>1000</v>
+      </c>
+      <c r="BW14">
+        <v>1.01</v>
+      </c>
+      <c r="BX14">
+        <v>1000</v>
+      </c>
+      <c r="BY14">
+        <v>1.01</v>
+      </c>
+      <c r="BZ14">
+        <v>1000</v>
+      </c>
+      <c r="CA14">
+        <v>1.01</v>
+      </c>
+      <c r="CB14" t="s">
+        <v>125</v>
       </c>
     </row>
   </sheetData>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-08-11.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-08-11.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="158" uniqueCount="126">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="176" uniqueCount="135">
   <si>
     <t>League</t>
   </si>
@@ -277,6 +277,9 @@
     <t>South African Premier Division</t>
   </si>
   <si>
+    <t>Colombian Primera B</t>
+  </si>
+  <si>
     <t>CONMEBOL Copa Libertadores</t>
   </si>
   <si>
@@ -304,12 +307,18 @@
     <t>17:30:00</t>
   </si>
   <si>
+    <t>20:30:00</t>
+  </si>
+  <si>
     <t>22:00:00</t>
   </si>
   <si>
     <t>22:30:00</t>
   </si>
   <si>
+    <t>22:45:00</t>
+  </si>
+  <si>
     <t>23:00:00</t>
   </si>
   <si>
@@ -343,15 +352,24 @@
     <t>Marumo Gallants FC</t>
   </si>
   <si>
+    <t>Real Santander</t>
+  </si>
+  <si>
     <t>Fluminense</t>
   </si>
   <si>
     <t>Avai</t>
   </si>
   <si>
+    <t>Real Cartagena</t>
+  </si>
+  <si>
     <t>Puerto Montt</t>
   </si>
   <si>
+    <t>Boyaca Patriotas</t>
+  </si>
+  <si>
     <t>CR Flamengo (W)</t>
   </si>
   <si>
@@ -382,16 +400,25 @@
     <t>Kruger United FC</t>
   </si>
   <si>
+    <t>Barranquilla</t>
+  </si>
+  <si>
     <t>Independiente Rivadavia</t>
   </si>
   <si>
     <t>CRB</t>
   </si>
   <si>
+    <t>Bogota</t>
+  </si>
+  <si>
     <t>Union Espanola</t>
   </si>
   <si>
-    <t>2026-08-10 03:53:36</t>
+    <t>Orsomarso</t>
+  </si>
+  <si>
+    <t>2026-08-10 06:03:16</t>
   </si>
 </sst>
 </file>
@@ -723,7 +750,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:CB14"/>
+  <dimension ref="A1:CB17"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:80">
@@ -973,25 +1000,25 @@
         <v>80</v>
       </c>
       <c r="B2" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="C2" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="D2" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="E2" t="s">
-        <v>112</v>
+        <v>118</v>
       </c>
       <c r="F2">
         <v>10</v>
       </c>
       <c r="G2">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="H2">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="I2">
         <v>1.34</v>
@@ -1000,52 +1027,52 @@
         <v>5.1</v>
       </c>
       <c r="K2">
-        <v>7.8</v>
+        <v>6.4</v>
       </c>
       <c r="L2">
         <v>1.29</v>
       </c>
       <c r="M2">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="N2">
         <v>4.5</v>
       </c>
       <c r="O2">
-        <v>1.19</v>
+        <v>1.25</v>
       </c>
       <c r="P2">
-        <v>2.24</v>
+        <v>2.22</v>
       </c>
       <c r="Q2">
-        <v>1.6</v>
+        <v>1.66</v>
       </c>
       <c r="R2">
-        <v>1.5</v>
+        <v>1.49</v>
       </c>
       <c r="S2">
-        <v>2.52</v>
+        <v>2.58</v>
       </c>
       <c r="T2">
-        <v>2.08</v>
+        <v>2.16</v>
       </c>
       <c r="U2">
-        <v>1.72</v>
+        <v>1.71</v>
       </c>
       <c r="V2">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="W2">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="X2">
         <v>27</v>
       </c>
       <c r="Y2">
-        <v>9.4</v>
+        <v>9</v>
       </c>
       <c r="Z2">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AA2">
         <v>12</v>
@@ -1054,7 +1081,7 @@
         <v>48</v>
       </c>
       <c r="AC2">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="AD2">
         <v>13</v>
@@ -1090,16 +1117,16 @@
         <v>420</v>
       </c>
       <c r="AO2">
-        <v>5.1</v>
+        <v>5.4</v>
       </c>
       <c r="AP2">
         <v>5.4</v>
       </c>
       <c r="AQ2">
-        <v>3.95</v>
+        <v>3.85</v>
       </c>
       <c r="AR2">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="AS2">
         <v>4.3</v>
@@ -1123,91 +1150,91 @@
         <v>6</v>
       </c>
       <c r="AZ2">
-        <v>5.8</v>
+        <v>5.7</v>
       </c>
       <c r="BA2">
-        <v>6</v>
+        <v>5.9</v>
       </c>
       <c r="BB2">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="BC2">
         <v>6.6</v>
       </c>
       <c r="BD2">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="BE2">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="BF2">
         <v>6.6</v>
       </c>
       <c r="BG2">
-        <v>2.9</v>
+        <v>3</v>
       </c>
       <c r="BH2">
-        <v>5</v>
+        <v>4.8</v>
       </c>
       <c r="BI2">
-        <v>2.44</v>
+        <v>2.42</v>
       </c>
       <c r="BJ2">
         <v>15.5</v>
       </c>
       <c r="BK2">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="BL2">
         <v>1000</v>
       </c>
       <c r="BM2">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="BN2">
         <v>18</v>
       </c>
       <c r="BO2">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="BP2">
         <v>1000</v>
       </c>
       <c r="BQ2">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="BR2">
         <v>1000</v>
       </c>
       <c r="BS2">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="BT2">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="BU2">
-        <v>2.96</v>
+        <v>2.94</v>
       </c>
       <c r="BV2">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BW2">
-        <v>3.05</v>
+        <v>3.15</v>
       </c>
       <c r="BX2">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="BY2">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="BZ2">
-        <v>13.5</v>
+        <v>14.5</v>
       </c>
       <c r="CA2">
-        <v>3.55</v>
+        <v>3.65</v>
       </c>
       <c r="CB2" t="s">
-        <v>125</v>
+        <v>134</v>
       </c>
     </row>
     <row r="3" spans="1:80">
@@ -1215,16 +1242,16 @@
         <v>81</v>
       </c>
       <c r="B3" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="C3" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="D3" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="E3" t="s">
-        <v>113</v>
+        <v>119</v>
       </c>
       <c r="F3">
         <v>2.38</v>
@@ -1236,13 +1263,13 @@
         <v>3.15</v>
       </c>
       <c r="I3">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="J3">
         <v>3.45</v>
       </c>
       <c r="K3">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="L3">
         <v>1.46</v>
@@ -1254,46 +1281,46 @@
         <v>3.45</v>
       </c>
       <c r="O3">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="P3">
         <v>1.83</v>
       </c>
       <c r="Q3">
-        <v>2.14</v>
+        <v>2.16</v>
       </c>
       <c r="R3">
         <v>1.31</v>
       </c>
       <c r="S3">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="T3">
-        <v>1.83</v>
+        <v>1.85</v>
       </c>
       <c r="U3">
         <v>2.06</v>
       </c>
       <c r="V3">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="W3">
-        <v>1.67</v>
+        <v>1.69</v>
       </c>
       <c r="X3">
         <v>14.5</v>
       </c>
       <c r="Y3">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="Z3">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="AA3">
         <v>80</v>
       </c>
       <c r="AB3">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="AC3">
         <v>8.199999999999999</v>
@@ -1314,7 +1341,7 @@
         <v>21</v>
       </c>
       <c r="AI3">
-        <v>390</v>
+        <v>350</v>
       </c>
       <c r="AJ3">
         <v>38</v>
@@ -1344,7 +1371,7 @@
         <v>17.5</v>
       </c>
       <c r="AS3">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AT3">
         <v>8.6</v>
@@ -1362,10 +1389,10 @@
         <v>12.5</v>
       </c>
       <c r="AY3">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AZ3">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="BA3">
         <v>38</v>
@@ -1374,7 +1401,7 @@
         <v>25</v>
       </c>
       <c r="BC3">
-        <v>18</v>
+        <v>18.5</v>
       </c>
       <c r="BD3">
         <v>32</v>
@@ -1386,7 +1413,7 @@
         <v>20</v>
       </c>
       <c r="BG3">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="BH3">
         <v>3.65</v>
@@ -1449,7 +1476,7 @@
         <v>4.5</v>
       </c>
       <c r="CB3" t="s">
-        <v>125</v>
+        <v>134</v>
       </c>
     </row>
     <row r="4" spans="1:80">
@@ -1457,67 +1484,67 @@
         <v>82</v>
       </c>
       <c r="B4" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="C4" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="D4" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="E4" t="s">
-        <v>114</v>
+        <v>120</v>
       </c>
       <c r="F4">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="G4">
         <v>1.72</v>
       </c>
       <c r="H4">
-        <v>6.6</v>
+        <v>6.2</v>
       </c>
       <c r="I4">
-        <v>7.8</v>
+        <v>7</v>
       </c>
       <c r="J4">
-        <v>3.7</v>
+        <v>3.65</v>
       </c>
       <c r="K4">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="L4">
-        <v>1.51</v>
+        <v>1.5</v>
       </c>
       <c r="M4">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="N4">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="O4">
-        <v>1.47</v>
+        <v>1.43</v>
       </c>
       <c r="P4">
-        <v>1.66</v>
+        <v>1.72</v>
       </c>
       <c r="Q4">
-        <v>2.34</v>
+        <v>2.3</v>
       </c>
       <c r="R4">
-        <v>1.24</v>
+        <v>1.26</v>
       </c>
       <c r="S4">
-        <v>4.7</v>
+        <v>4.4</v>
       </c>
       <c r="T4">
-        <v>2.22</v>
+        <v>2.18</v>
       </c>
       <c r="U4">
-        <v>1.7</v>
+        <v>1.73</v>
       </c>
       <c r="V4">
-        <v>1.15</v>
+        <v>1.16</v>
       </c>
       <c r="W4">
         <v>2.38</v>
@@ -1532,19 +1559,19 @@
         <v>60</v>
       </c>
       <c r="AA4">
-        <v>300</v>
+        <v>250</v>
       </c>
       <c r="AB4">
-        <v>6.6</v>
+        <v>7</v>
       </c>
       <c r="AC4">
         <v>9</v>
       </c>
       <c r="AD4">
-        <v>950</v>
+        <v>28</v>
       </c>
       <c r="AE4">
-        <v>170</v>
+        <v>140</v>
       </c>
       <c r="AF4">
         <v>8.800000000000001</v>
@@ -1553,13 +1580,13 @@
         <v>11</v>
       </c>
       <c r="AH4">
-        <v>950</v>
+        <v>28</v>
       </c>
       <c r="AI4">
-        <v>160</v>
+        <v>140</v>
       </c>
       <c r="AJ4">
-        <v>17</v>
+        <v>17.5</v>
       </c>
       <c r="AK4">
         <v>22</v>
@@ -1568,13 +1595,13 @@
         <v>55</v>
       </c>
       <c r="AM4">
-        <v>240</v>
+        <v>210</v>
       </c>
       <c r="AN4">
         <v>14.5</v>
       </c>
       <c r="AO4">
-        <v>270</v>
+        <v>220</v>
       </c>
       <c r="AP4">
         <v>9</v>
@@ -1583,34 +1610,34 @@
         <v>14.5</v>
       </c>
       <c r="AR4">
-        <v>8.800000000000001</v>
+        <v>8.4</v>
       </c>
       <c r="AS4">
-        <v>9.800000000000001</v>
+        <v>9.4</v>
       </c>
       <c r="AT4">
-        <v>5.5</v>
+        <v>5.8</v>
       </c>
       <c r="AU4">
         <v>7.4</v>
       </c>
       <c r="AV4">
-        <v>7.6</v>
+        <v>7.2</v>
       </c>
       <c r="AW4">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AX4">
-        <v>7.4</v>
+        <v>7</v>
       </c>
       <c r="AY4">
         <v>9</v>
       </c>
       <c r="AZ4">
-        <v>7.6</v>
+        <v>7.2</v>
       </c>
       <c r="BA4">
-        <v>9.4</v>
+        <v>9</v>
       </c>
       <c r="BB4">
         <v>14</v>
@@ -1619,25 +1646,25 @@
         <v>17.5</v>
       </c>
       <c r="BD4">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="BE4">
-        <v>9.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BF4">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="BG4">
-        <v>9.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BH4">
         <v>3.1</v>
       </c>
       <c r="BI4">
-        <v>2.56</v>
+        <v>2.6</v>
       </c>
       <c r="BJ4">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="BK4">
         <v>9.800000000000001</v>
@@ -1646,7 +1673,7 @@
         <v>1000</v>
       </c>
       <c r="BM4">
-        <v>12.5</v>
+        <v>13.5</v>
       </c>
       <c r="BN4">
         <v>4</v>
@@ -1658,40 +1685,40 @@
         <v>12</v>
       </c>
       <c r="BQ4">
-        <v>9.4</v>
+        <v>6.4</v>
       </c>
       <c r="BR4">
         <v>1000</v>
       </c>
       <c r="BS4">
-        <v>9.6</v>
+        <v>10</v>
       </c>
       <c r="BT4">
         <v>10.5</v>
       </c>
       <c r="BU4">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="BV4">
         <v>1000</v>
       </c>
       <c r="BW4">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="BX4">
         <v>1000</v>
       </c>
       <c r="BY4">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="BZ4">
         <v>1000</v>
       </c>
       <c r="CA4">
-        <v>9</v>
+        <v>9.4</v>
       </c>
       <c r="CB4" t="s">
-        <v>125</v>
+        <v>134</v>
       </c>
     </row>
     <row r="5" spans="1:80">
@@ -1699,19 +1726,19 @@
         <v>83</v>
       </c>
       <c r="B5" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="C5" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="D5" t="s">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="E5" t="s">
-        <v>115</v>
+        <v>121</v>
       </c>
       <c r="F5">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="G5">
         <v>1.6</v>
@@ -1720,13 +1747,13 @@
         <v>7.4</v>
       </c>
       <c r="I5">
-        <v>8.199999999999999</v>
+        <v>7.6</v>
       </c>
       <c r="J5">
         <v>4.1</v>
       </c>
       <c r="K5">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="L5">
         <v>1.46</v>
@@ -1735,7 +1762,7 @@
         <v>1.08</v>
       </c>
       <c r="N5">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="O5">
         <v>1.39</v>
@@ -1747,7 +1774,7 @@
         <v>2.2</v>
       </c>
       <c r="R5">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="S5">
         <v>4.2</v>
@@ -1759,7 +1786,7 @@
         <v>1.72</v>
       </c>
       <c r="V5">
-        <v>1.13</v>
+        <v>1.15</v>
       </c>
       <c r="W5">
         <v>2.66</v>
@@ -1792,7 +1819,7 @@
         <v>8.6</v>
       </c>
       <c r="AG5">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AH5">
         <v>28</v>
@@ -1825,13 +1852,13 @@
         <v>16.5</v>
       </c>
       <c r="AR5">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="AS5">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="AT5">
-        <v>5.9</v>
+        <v>6.2</v>
       </c>
       <c r="AU5">
         <v>8.199999999999999</v>
@@ -1840,7 +1867,7 @@
         <v>23</v>
       </c>
       <c r="AW5">
-        <v>9.6</v>
+        <v>10</v>
       </c>
       <c r="AX5">
         <v>7.2</v>
@@ -1852,7 +1879,7 @@
         <v>24</v>
       </c>
       <c r="BA5">
-        <v>9.4</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BB5">
         <v>12</v>
@@ -1864,13 +1891,13 @@
         <v>34</v>
       </c>
       <c r="BE5">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="BF5">
         <v>9</v>
       </c>
       <c r="BG5">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="BH5">
         <v>3.25</v>
@@ -1933,7 +1960,7 @@
         <v>8.4</v>
       </c>
       <c r="CB5" t="s">
-        <v>125</v>
+        <v>134</v>
       </c>
     </row>
     <row r="6" spans="1:80">
@@ -1941,16 +1968,16 @@
         <v>84</v>
       </c>
       <c r="B6" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="C6" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="D6" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="E6" t="s">
-        <v>116</v>
+        <v>122</v>
       </c>
       <c r="F6">
         <v>1.35</v>
@@ -1962,7 +1989,7 @@
         <v>11.5</v>
       </c>
       <c r="I6">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="J6">
         <v>5.3</v>
@@ -2136,7 +2163,7 @@
         <v>3.75</v>
       </c>
       <c r="BO6">
-        <v>3.2</v>
+        <v>3</v>
       </c>
       <c r="BP6">
         <v>8</v>
@@ -2175,7 +2202,7 @@
         <v>6.2</v>
       </c>
       <c r="CB6" t="s">
-        <v>125</v>
+        <v>134</v>
       </c>
     </row>
     <row r="7" spans="1:80">
@@ -2183,22 +2210,22 @@
         <v>85</v>
       </c>
       <c r="B7" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="C7" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="D7" t="s">
-        <v>104</v>
+        <v>107</v>
       </c>
       <c r="E7" t="s">
-        <v>117</v>
+        <v>123</v>
       </c>
       <c r="F7">
-        <v>2.12</v>
+        <v>2.14</v>
       </c>
       <c r="G7">
-        <v>2.3</v>
+        <v>2.28</v>
       </c>
       <c r="H7">
         <v>3.25</v>
@@ -2210,7 +2237,7 @@
         <v>3.8</v>
       </c>
       <c r="K7">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="L7">
         <v>1.33</v>
@@ -2219,37 +2246,37 @@
         <v>1.04</v>
       </c>
       <c r="N7">
-        <v>4.8</v>
+        <v>5.2</v>
       </c>
       <c r="O7">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="P7">
-        <v>2.3</v>
+        <v>2.36</v>
       </c>
       <c r="Q7">
-        <v>1.67</v>
+        <v>1.66</v>
       </c>
       <c r="R7">
-        <v>1.52</v>
+        <v>1.54</v>
       </c>
       <c r="S7">
-        <v>2.7</v>
+        <v>2.62</v>
       </c>
       <c r="T7">
         <v>1.61</v>
       </c>
       <c r="U7">
-        <v>2.42</v>
+        <v>2.48</v>
       </c>
       <c r="V7">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="W7">
         <v>1.78</v>
       </c>
       <c r="X7">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="Y7">
         <v>17</v>
@@ -2264,10 +2291,10 @@
         <v>15.5</v>
       </c>
       <c r="AC7">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AD7">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="AE7">
         <v>44</v>
@@ -2279,10 +2306,10 @@
         <v>13.5</v>
       </c>
       <c r="AH7">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="AI7">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="AJ7">
         <v>36</v>
@@ -2294,16 +2321,16 @@
         <v>40</v>
       </c>
       <c r="AM7">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="AN7">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="AO7">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="AP7">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="AQ7">
         <v>14.5</v>
@@ -2312,7 +2339,7 @@
         <v>19</v>
       </c>
       <c r="AS7">
-        <v>5.2</v>
+        <v>5.8</v>
       </c>
       <c r="AT7">
         <v>11</v>
@@ -2324,7 +2351,7 @@
         <v>10.5</v>
       </c>
       <c r="AW7">
-        <v>4.8</v>
+        <v>5.3</v>
       </c>
       <c r="AX7">
         <v>11.5</v>
@@ -2336,7 +2363,7 @@
         <v>11.5</v>
       </c>
       <c r="BA7">
-        <v>5</v>
+        <v>5.5</v>
       </c>
       <c r="BB7">
         <v>20</v>
@@ -2345,10 +2372,10 @@
         <v>15.5</v>
       </c>
       <c r="BD7">
-        <v>4.7</v>
+        <v>5.2</v>
       </c>
       <c r="BE7">
-        <v>5.2</v>
+        <v>5.8</v>
       </c>
       <c r="BF7">
         <v>11</v>
@@ -2417,7 +2444,7 @@
         <v>0</v>
       </c>
       <c r="CB7" t="s">
-        <v>125</v>
+        <v>134</v>
       </c>
     </row>
     <row r="8" spans="1:80">
@@ -2425,34 +2452,34 @@
         <v>86</v>
       </c>
       <c r="B8" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="C8" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="D8" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="E8" t="s">
-        <v>118</v>
+        <v>124</v>
       </c>
       <c r="F8">
         <v>1.04</v>
       </c>
       <c r="G8">
-        <v>1000</v>
+        <v>990</v>
       </c>
       <c r="H8">
         <v>1.04</v>
       </c>
       <c r="I8">
-        <v>1000</v>
+        <v>990</v>
       </c>
       <c r="J8">
-        <v>1.01</v>
+        <v>1.06</v>
       </c>
       <c r="K8">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="L8">
         <v>1.01</v>
@@ -2461,34 +2488,34 @@
         <v>1.01</v>
       </c>
       <c r="N8">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="O8">
-        <v>1.01</v>
+        <v>1.59</v>
       </c>
       <c r="P8">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="Q8">
-        <v>1.01</v>
+        <v>1.59</v>
       </c>
       <c r="R8">
         <v>1.13</v>
       </c>
       <c r="S8">
-        <v>1.01</v>
+        <v>1.59</v>
       </c>
       <c r="T8">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="U8">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="V8">
         <v>1.01</v>
       </c>
       <c r="W8">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="X8">
         <v>1000</v>
@@ -2545,52 +2572,52 @@
         <v>1000</v>
       </c>
       <c r="AP8">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AQ8">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AR8">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AS8">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AT8">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AU8">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AV8">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AW8">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AX8">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AY8">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AZ8">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BA8">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BB8">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BC8">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BD8">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BE8">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BF8">
         <v>1.01</v>
@@ -2602,64 +2629,64 @@
         <v>1000</v>
       </c>
       <c r="BI8">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BJ8">
         <v>1000</v>
       </c>
       <c r="BK8">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BL8">
         <v>1000</v>
       </c>
       <c r="BM8">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BN8">
         <v>1000</v>
       </c>
       <c r="BO8">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BP8">
         <v>1000</v>
       </c>
       <c r="BQ8">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BR8">
         <v>1000</v>
       </c>
       <c r="BS8">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BT8">
         <v>1000</v>
       </c>
       <c r="BU8">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BV8">
         <v>1000</v>
       </c>
       <c r="BW8">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BX8">
         <v>1000</v>
       </c>
       <c r="BY8">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BZ8">
         <v>1000</v>
       </c>
       <c r="CA8">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="CB8" t="s">
-        <v>125</v>
+        <v>134</v>
       </c>
     </row>
     <row r="9" spans="1:80">
@@ -2667,34 +2694,34 @@
         <v>86</v>
       </c>
       <c r="B9" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="C9" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="D9" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="E9" t="s">
-        <v>119</v>
+        <v>125</v>
       </c>
       <c r="F9">
-        <v>1.04</v>
+        <v>1.11</v>
       </c>
       <c r="G9">
-        <v>1000</v>
+        <v>990</v>
       </c>
       <c r="H9">
-        <v>1.04</v>
+        <v>1.11</v>
       </c>
       <c r="I9">
-        <v>1000</v>
+        <v>990</v>
       </c>
       <c r="J9">
-        <v>1.01</v>
+        <v>1.13</v>
       </c>
       <c r="K9">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="L9">
         <v>1.01</v>
@@ -2703,34 +2730,34 @@
         <v>1.01</v>
       </c>
       <c r="N9">
-        <v>1.24</v>
+        <v>1.28</v>
       </c>
       <c r="O9">
-        <v>1.37</v>
+        <v>1.35</v>
       </c>
       <c r="P9">
-        <v>1.24</v>
+        <v>1.28</v>
       </c>
       <c r="Q9">
-        <v>1.37</v>
+        <v>1.34</v>
       </c>
       <c r="R9">
-        <v>1.13</v>
+        <v>1.35</v>
       </c>
       <c r="S9">
-        <v>1.37</v>
+        <v>1.39</v>
       </c>
       <c r="T9">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="U9">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="V9">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="W9">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="X9">
         <v>1000</v>
@@ -2787,52 +2814,52 @@
         <v>1000</v>
       </c>
       <c r="AP9">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AQ9">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AR9">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AS9">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AT9">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AU9">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AV9">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AW9">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AX9">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AY9">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AZ9">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BA9">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BB9">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BC9">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BD9">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BE9">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BF9">
         <v>1.01</v>
@@ -2901,7 +2928,7 @@
         <v>1.01</v>
       </c>
       <c r="CB9" t="s">
-        <v>125</v>
+        <v>134</v>
       </c>
     </row>
     <row r="10" spans="1:80">
@@ -2909,34 +2936,34 @@
         <v>86</v>
       </c>
       <c r="B10" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="C10" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="D10" t="s">
-        <v>107</v>
+        <v>110</v>
       </c>
       <c r="E10" t="s">
-        <v>120</v>
+        <v>126</v>
       </c>
       <c r="F10">
-        <v>1.04</v>
+        <v>1.11</v>
       </c>
       <c r="G10">
-        <v>1000</v>
+        <v>990</v>
       </c>
       <c r="H10">
-        <v>1.04</v>
+        <v>1.13</v>
       </c>
       <c r="I10">
-        <v>1000</v>
+        <v>990</v>
       </c>
       <c r="J10">
-        <v>1.01</v>
+        <v>1.13</v>
       </c>
       <c r="K10">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="L10">
         <v>1.01</v>
@@ -2945,34 +2972,34 @@
         <v>1.01</v>
       </c>
       <c r="N10">
-        <v>1.24</v>
+        <v>1.26</v>
       </c>
       <c r="O10">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="P10">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="Q10">
-        <v>1.01</v>
+        <v>1.6</v>
       </c>
       <c r="R10">
         <v>1.13</v>
       </c>
       <c r="S10">
+        <v>1.6</v>
+      </c>
+      <c r="T10">
+        <v>1.11</v>
+      </c>
+      <c r="U10">
+        <v>1.11</v>
+      </c>
+      <c r="V10">
         <v>1.02</v>
       </c>
-      <c r="T10">
-        <v>1.01</v>
-      </c>
-      <c r="U10">
-        <v>1.01</v>
-      </c>
-      <c r="V10">
-        <v>1.01</v>
-      </c>
       <c r="W10">
-        <v>1.01</v>
+        <v>1.06</v>
       </c>
       <c r="X10">
         <v>1000</v>
@@ -3029,52 +3056,52 @@
         <v>1000</v>
       </c>
       <c r="AP10">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AQ10">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AR10">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AS10">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AT10">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AU10">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AV10">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AW10">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AX10">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AY10">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AZ10">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BA10">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BB10">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BC10">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BD10">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BE10">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BF10">
         <v>1.01</v>
@@ -3143,7 +3170,7 @@
         <v>1.01</v>
       </c>
       <c r="CB10" t="s">
-        <v>125</v>
+        <v>134</v>
       </c>
     </row>
     <row r="11" spans="1:80">
@@ -3151,34 +3178,34 @@
         <v>86</v>
       </c>
       <c r="B11" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="C11" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="D11" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="E11" t="s">
-        <v>121</v>
+        <v>127</v>
       </c>
       <c r="F11">
-        <v>1.04</v>
+        <v>1.15</v>
       </c>
       <c r="G11">
-        <v>1000</v>
+        <v>990</v>
       </c>
       <c r="H11">
-        <v>1.04</v>
+        <v>1.17</v>
       </c>
       <c r="I11">
-        <v>1000</v>
+        <v>990</v>
       </c>
       <c r="J11">
-        <v>1.01</v>
+        <v>1.18</v>
       </c>
       <c r="K11">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="L11">
         <v>1.01</v>
@@ -3187,34 +3214,34 @@
         <v>1.01</v>
       </c>
       <c r="N11">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="O11">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="P11">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="Q11">
-        <v>1.01</v>
+        <v>1.62</v>
       </c>
       <c r="R11">
         <v>1.13</v>
       </c>
       <c r="S11">
-        <v>1.02</v>
+        <v>1.62</v>
       </c>
       <c r="T11">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="U11">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="V11">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="W11">
-        <v>1.01</v>
+        <v>1.06</v>
       </c>
       <c r="X11">
         <v>1000</v>
@@ -3271,52 +3298,52 @@
         <v>1000</v>
       </c>
       <c r="AP11">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AQ11">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AR11">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AS11">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AT11">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AU11">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AV11">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AW11">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AX11">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AY11">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AZ11">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BA11">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BB11">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BC11">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BD11">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BE11">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BF11">
         <v>1.01</v>
@@ -3328,64 +3355,64 @@
         <v>1000</v>
       </c>
       <c r="BI11">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BJ11">
         <v>1000</v>
       </c>
       <c r="BK11">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BL11">
         <v>1000</v>
       </c>
       <c r="BM11">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BN11">
         <v>1000</v>
       </c>
       <c r="BO11">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BP11">
         <v>1000</v>
       </c>
       <c r="BQ11">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BR11">
         <v>1000</v>
       </c>
       <c r="BS11">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BT11">
         <v>1000</v>
       </c>
       <c r="BU11">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BV11">
         <v>1000</v>
       </c>
       <c r="BW11">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BX11">
         <v>1000</v>
       </c>
       <c r="BY11">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BZ11">
         <v>1000</v>
       </c>
       <c r="CA11">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="CB11" t="s">
-        <v>125</v>
+        <v>134</v>
       </c>
     </row>
     <row r="12" spans="1:80">
@@ -3393,241 +3420,241 @@
         <v>87</v>
       </c>
       <c r="B12" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="C12" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="D12" t="s">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="E12" t="s">
-        <v>122</v>
+        <v>128</v>
       </c>
       <c r="F12">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="G12">
-        <v>0</v>
+        <v>990</v>
       </c>
       <c r="H12">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="I12">
-        <v>0</v>
+        <v>990</v>
       </c>
       <c r="J12">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="K12">
-        <v>0</v>
+        <v>950</v>
       </c>
       <c r="L12">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M12">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N12">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="O12">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="P12">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="Q12">
-        <v>1.01</v>
+        <v>1.45</v>
       </c>
       <c r="R12">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="S12">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="T12">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="U12">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="V12">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W12">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X12">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y12">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z12">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA12">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB12">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC12">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD12">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE12">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF12">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG12">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH12">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI12">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ12">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK12">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL12">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM12">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN12">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO12">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP12">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AQ12">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AR12">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AS12">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AT12">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AU12">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AV12">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AW12">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AX12">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AY12">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AZ12">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BA12">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BB12">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BC12">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BD12">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BE12">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BF12">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG12">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH12">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BI12">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BJ12">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BK12">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BL12">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM12">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BN12">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BO12">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BP12">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BQ12">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BR12">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS12">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BT12">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BU12">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BV12">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW12">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BX12">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY12">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BZ12">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA12">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="CB12" t="s">
-        <v>125</v>
+        <v>134</v>
       </c>
     </row>
     <row r="13" spans="1:80">
@@ -3635,241 +3662,241 @@
         <v>88</v>
       </c>
       <c r="B13" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="C13" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="D13" t="s">
-        <v>110</v>
+        <v>113</v>
       </c>
       <c r="E13" t="s">
-        <v>123</v>
+        <v>129</v>
       </c>
       <c r="F13">
-        <v>2.82</v>
+        <v>0</v>
       </c>
       <c r="G13">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="H13">
-        <v>2.66</v>
+        <v>0</v>
       </c>
       <c r="I13">
-        <v>2.92</v>
+        <v>0</v>
       </c>
       <c r="J13">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="K13">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="L13">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="M13">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="N13">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="O13">
-        <v>1.39</v>
+        <v>0</v>
       </c>
       <c r="P13">
-        <v>1.74</v>
+        <v>1.24</v>
       </c>
       <c r="Q13">
-        <v>2.16</v>
+        <v>1.01</v>
       </c>
       <c r="R13">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="S13">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="T13">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="U13">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="V13">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="W13">
-        <v>1.49</v>
+        <v>0</v>
       </c>
       <c r="X13">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="Y13">
-        <v>10.5</v>
+        <v>0</v>
       </c>
       <c r="Z13">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="AA13">
-        <v>65</v>
+        <v>0</v>
       </c>
       <c r="AB13">
-        <v>10.5</v>
+        <v>0</v>
       </c>
       <c r="AC13">
-        <v>7.6</v>
+        <v>0</v>
       </c>
       <c r="AD13">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="AE13">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="AF13">
-        <v>19.5</v>
+        <v>0</v>
       </c>
       <c r="AG13">
-        <v>13.5</v>
+        <v>0</v>
       </c>
       <c r="AH13">
-        <v>18.5</v>
+        <v>0</v>
       </c>
       <c r="AI13">
-        <v>70</v>
+        <v>0</v>
       </c>
       <c r="AJ13">
-        <v>70</v>
+        <v>0</v>
       </c>
       <c r="AK13">
-        <v>38</v>
+        <v>0</v>
       </c>
       <c r="AL13">
-        <v>55</v>
+        <v>0</v>
       </c>
       <c r="AM13">
-        <v>140</v>
+        <v>0</v>
       </c>
       <c r="AN13">
-        <v>38</v>
+        <v>0</v>
       </c>
       <c r="AO13">
-        <v>34</v>
+        <v>0</v>
       </c>
       <c r="AP13">
-        <v>8.6</v>
+        <v>0</v>
       </c>
       <c r="AQ13">
-        <v>8.800000000000001</v>
+        <v>0</v>
       </c>
       <c r="AR13">
-        <v>15.5</v>
+        <v>0</v>
       </c>
       <c r="AS13">
-        <v>29</v>
+        <v>0</v>
       </c>
       <c r="AT13">
-        <v>9.199999999999999</v>
+        <v>0</v>
       </c>
       <c r="AU13">
-        <v>6.6</v>
+        <v>0</v>
       </c>
       <c r="AV13">
-        <v>9.199999999999999</v>
+        <v>0</v>
       </c>
       <c r="AW13">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="AX13">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="AY13">
-        <v>11.5</v>
+        <v>0</v>
       </c>
       <c r="AZ13">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="BA13">
-        <v>8.6</v>
+        <v>0</v>
       </c>
       <c r="BB13">
-        <v>29</v>
+        <v>0</v>
       </c>
       <c r="BC13">
-        <v>8.199999999999999</v>
+        <v>0</v>
       </c>
       <c r="BD13">
-        <v>8.800000000000001</v>
+        <v>0</v>
       </c>
       <c r="BE13">
-        <v>9.6</v>
+        <v>0</v>
       </c>
       <c r="BF13">
-        <v>8.199999999999999</v>
+        <v>0</v>
       </c>
       <c r="BG13">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="BH13">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="BI13">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="BJ13">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="BK13">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="BL13">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BM13">
-        <v>13.5</v>
+        <v>0</v>
       </c>
       <c r="BN13">
-        <v>5.9</v>
+        <v>0</v>
       </c>
       <c r="BO13">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="BP13">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="BQ13">
-        <v>9.4</v>
+        <v>0</v>
       </c>
       <c r="BR13">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="BS13">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="BT13">
-        <v>5.7</v>
+        <v>0</v>
       </c>
       <c r="BU13">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="BV13">
-        <v>23</v>
+        <v>0</v>
       </c>
       <c r="BW13">
-        <v>9.199999999999999</v>
+        <v>0</v>
       </c>
       <c r="BX13">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BY13">
-        <v>10.5</v>
+        <v>0</v>
       </c>
       <c r="BZ13">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="CA13">
-        <v>10.5</v>
+        <v>0</v>
       </c>
       <c r="CB13" t="s">
-        <v>125</v>
+        <v>134</v>
       </c>
     </row>
     <row r="14" spans="1:80">
@@ -3877,241 +3904,967 @@
         <v>89</v>
       </c>
       <c r="B14" t="s">
+        <v>91</v>
+      </c>
+      <c r="C14" t="s">
+        <v>99</v>
+      </c>
+      <c r="D14" t="s">
+        <v>114</v>
+      </c>
+      <c r="E14" t="s">
+        <v>130</v>
+      </c>
+      <c r="F14">
+        <v>2.82</v>
+      </c>
+      <c r="G14">
+        <v>3.1</v>
+      </c>
+      <c r="H14">
+        <v>2.66</v>
+      </c>
+      <c r="I14">
+        <v>2.9</v>
+      </c>
+      <c r="J14">
+        <v>3.15</v>
+      </c>
+      <c r="K14">
+        <v>3.5</v>
+      </c>
+      <c r="L14">
+        <v>1.38</v>
+      </c>
+      <c r="M14">
+        <v>1.09</v>
+      </c>
+      <c r="N14">
+        <v>3.15</v>
+      </c>
+      <c r="O14">
+        <v>1.39</v>
+      </c>
+      <c r="P14">
+        <v>1.74</v>
+      </c>
+      <c r="Q14">
+        <v>2.16</v>
+      </c>
+      <c r="R14">
+        <v>1.28</v>
+      </c>
+      <c r="S14">
+        <v>4</v>
+      </c>
+      <c r="T14">
+        <v>1.85</v>
+      </c>
+      <c r="U14">
+        <v>2.02</v>
+      </c>
+      <c r="V14">
+        <v>1.54</v>
+      </c>
+      <c r="W14">
+        <v>1.49</v>
+      </c>
+      <c r="X14">
+        <v>14</v>
+      </c>
+      <c r="Y14">
+        <v>10.5</v>
+      </c>
+      <c r="Z14">
+        <v>18</v>
+      </c>
+      <c r="AA14">
+        <v>65</v>
+      </c>
+      <c r="AB14">
+        <v>10.5</v>
+      </c>
+      <c r="AC14">
+        <v>7.6</v>
+      </c>
+      <c r="AD14">
+        <v>13</v>
+      </c>
+      <c r="AE14">
+        <v>50</v>
+      </c>
+      <c r="AF14">
+        <v>19.5</v>
+      </c>
+      <c r="AG14">
+        <v>13.5</v>
+      </c>
+      <c r="AH14">
+        <v>18.5</v>
+      </c>
+      <c r="AI14">
+        <v>70</v>
+      </c>
+      <c r="AJ14">
+        <v>70</v>
+      </c>
+      <c r="AK14">
+        <v>38</v>
+      </c>
+      <c r="AL14">
+        <v>55</v>
+      </c>
+      <c r="AM14">
+        <v>140</v>
+      </c>
+      <c r="AN14">
+        <v>38</v>
+      </c>
+      <c r="AO14">
+        <v>34</v>
+      </c>
+      <c r="AP14">
+        <v>8.6</v>
+      </c>
+      <c r="AQ14">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AR14">
+        <v>15.5</v>
+      </c>
+      <c r="AS14">
+        <v>29</v>
+      </c>
+      <c r="AT14">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AU14">
+        <v>6.6</v>
+      </c>
+      <c r="AV14">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AW14">
+        <v>8</v>
+      </c>
+      <c r="AX14">
+        <v>14</v>
+      </c>
+      <c r="AY14">
+        <v>11.5</v>
+      </c>
+      <c r="AZ14">
+        <v>16</v>
+      </c>
+      <c r="BA14">
+        <v>8.6</v>
+      </c>
+      <c r="BB14">
+        <v>29</v>
+      </c>
+      <c r="BC14">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BD14">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="BE14">
+        <v>9.6</v>
+      </c>
+      <c r="BF14">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BG14">
+        <v>8</v>
+      </c>
+      <c r="BH14">
+        <v>3.15</v>
+      </c>
+      <c r="BI14">
+        <v>2.6</v>
+      </c>
+      <c r="BJ14">
+        <v>10</v>
+      </c>
+      <c r="BK14">
+        <v>6</v>
+      </c>
+      <c r="BL14">
+        <v>1000</v>
+      </c>
+      <c r="BM14">
+        <v>13.5</v>
+      </c>
+      <c r="BN14">
+        <v>5.9</v>
+      </c>
+      <c r="BO14">
+        <v>4.5</v>
+      </c>
+      <c r="BP14">
+        <v>24</v>
+      </c>
+      <c r="BQ14">
+        <v>9.4</v>
+      </c>
+      <c r="BR14">
+        <v>40</v>
+      </c>
+      <c r="BS14">
+        <v>11</v>
+      </c>
+      <c r="BT14">
+        <v>5.7</v>
+      </c>
+      <c r="BU14">
+        <v>4.3</v>
+      </c>
+      <c r="BV14">
+        <v>23</v>
+      </c>
+      <c r="BW14">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="BX14">
+        <v>1000</v>
+      </c>
+      <c r="BY14">
+        <v>10.5</v>
+      </c>
+      <c r="BZ14">
+        <v>1000</v>
+      </c>
+      <c r="CA14">
+        <v>10.5</v>
+      </c>
+      <c r="CB14" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="15" spans="1:80">
+      <c r="A15" t="s">
+        <v>87</v>
+      </c>
+      <c r="B15" t="s">
+        <v>91</v>
+      </c>
+      <c r="C15" t="s">
+        <v>100</v>
+      </c>
+      <c r="D15" t="s">
+        <v>115</v>
+      </c>
+      <c r="E15" t="s">
+        <v>131</v>
+      </c>
+      <c r="F15">
+        <v>1.04</v>
+      </c>
+      <c r="G15">
+        <v>990</v>
+      </c>
+      <c r="H15">
+        <v>1.04</v>
+      </c>
+      <c r="I15">
+        <v>990</v>
+      </c>
+      <c r="J15">
+        <v>1.03</v>
+      </c>
+      <c r="K15">
+        <v>950</v>
+      </c>
+      <c r="L15">
+        <v>1.01</v>
+      </c>
+      <c r="M15">
+        <v>1.01</v>
+      </c>
+      <c r="N15">
+        <v>1.26</v>
+      </c>
+      <c r="O15">
+        <v>1.34</v>
+      </c>
+      <c r="P15">
+        <v>1.25</v>
+      </c>
+      <c r="Q15">
+        <v>1.34</v>
+      </c>
+      <c r="R15">
+        <v>1.13</v>
+      </c>
+      <c r="S15">
+        <v>1.34</v>
+      </c>
+      <c r="T15">
+        <v>1.11</v>
+      </c>
+      <c r="U15">
+        <v>1.11</v>
+      </c>
+      <c r="V15">
+        <v>1.01</v>
+      </c>
+      <c r="W15">
+        <v>1.01</v>
+      </c>
+      <c r="X15">
+        <v>1000</v>
+      </c>
+      <c r="Y15">
+        <v>1000</v>
+      </c>
+      <c r="Z15">
+        <v>1000</v>
+      </c>
+      <c r="AA15">
+        <v>1000</v>
+      </c>
+      <c r="AB15">
+        <v>1000</v>
+      </c>
+      <c r="AC15">
+        <v>1000</v>
+      </c>
+      <c r="AD15">
+        <v>1000</v>
+      </c>
+      <c r="AE15">
+        <v>1000</v>
+      </c>
+      <c r="AF15">
+        <v>1000</v>
+      </c>
+      <c r="AG15">
+        <v>1000</v>
+      </c>
+      <c r="AH15">
+        <v>1000</v>
+      </c>
+      <c r="AI15">
+        <v>1000</v>
+      </c>
+      <c r="AJ15">
+        <v>1000</v>
+      </c>
+      <c r="AK15">
+        <v>1000</v>
+      </c>
+      <c r="AL15">
+        <v>1000</v>
+      </c>
+      <c r="AM15">
+        <v>1000</v>
+      </c>
+      <c r="AN15">
+        <v>1000</v>
+      </c>
+      <c r="AO15">
+        <v>1000</v>
+      </c>
+      <c r="AP15">
+        <v>1.03</v>
+      </c>
+      <c r="AQ15">
+        <v>1.03</v>
+      </c>
+      <c r="AR15">
+        <v>1.03</v>
+      </c>
+      <c r="AS15">
+        <v>1.03</v>
+      </c>
+      <c r="AT15">
+        <v>1.03</v>
+      </c>
+      <c r="AU15">
+        <v>1.03</v>
+      </c>
+      <c r="AV15">
+        <v>1.03</v>
+      </c>
+      <c r="AW15">
+        <v>1.03</v>
+      </c>
+      <c r="AX15">
+        <v>1.03</v>
+      </c>
+      <c r="AY15">
+        <v>1.03</v>
+      </c>
+      <c r="AZ15">
+        <v>1.03</v>
+      </c>
+      <c r="BA15">
+        <v>1.03</v>
+      </c>
+      <c r="BB15">
+        <v>1.03</v>
+      </c>
+      <c r="BC15">
+        <v>1.03</v>
+      </c>
+      <c r="BD15">
+        <v>1.03</v>
+      </c>
+      <c r="BE15">
+        <v>1.03</v>
+      </c>
+      <c r="BF15">
+        <v>1.01</v>
+      </c>
+      <c r="BG15">
+        <v>1.01</v>
+      </c>
+      <c r="BH15">
+        <v>1000</v>
+      </c>
+      <c r="BI15">
+        <v>1.01</v>
+      </c>
+      <c r="BJ15">
+        <v>1000</v>
+      </c>
+      <c r="BK15">
+        <v>1.01</v>
+      </c>
+      <c r="BL15">
+        <v>1000</v>
+      </c>
+      <c r="BM15">
+        <v>1.01</v>
+      </c>
+      <c r="BN15">
+        <v>1000</v>
+      </c>
+      <c r="BO15">
+        <v>1.01</v>
+      </c>
+      <c r="BP15">
+        <v>1000</v>
+      </c>
+      <c r="BQ15">
+        <v>1.01</v>
+      </c>
+      <c r="BR15">
+        <v>1000</v>
+      </c>
+      <c r="BS15">
+        <v>1.01</v>
+      </c>
+      <c r="BT15">
+        <v>1000</v>
+      </c>
+      <c r="BU15">
+        <v>1.01</v>
+      </c>
+      <c r="BV15">
+        <v>1000</v>
+      </c>
+      <c r="BW15">
+        <v>1.01</v>
+      </c>
+      <c r="BX15">
+        <v>1000</v>
+      </c>
+      <c r="BY15">
+        <v>1.01</v>
+      </c>
+      <c r="BZ15">
+        <v>0</v>
+      </c>
+      <c r="CA15">
+        <v>0</v>
+      </c>
+      <c r="CB15" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="16" spans="1:80">
+      <c r="A16" t="s">
         <v>90</v>
       </c>
-      <c r="C14" t="s">
-        <v>98</v>
-      </c>
-      <c r="D14" t="s">
-        <v>111</v>
-      </c>
-      <c r="E14" t="s">
-        <v>124</v>
-      </c>
-      <c r="F14">
+      <c r="B16" t="s">
+        <v>91</v>
+      </c>
+      <c r="C16" t="s">
+        <v>101</v>
+      </c>
+      <c r="D16" t="s">
+        <v>116</v>
+      </c>
+      <c r="E16" t="s">
+        <v>132</v>
+      </c>
+      <c r="F16">
         <v>1.04</v>
       </c>
-      <c r="G14">
-        <v>1000</v>
-      </c>
-      <c r="H14">
+      <c r="G16">
+        <v>990</v>
+      </c>
+      <c r="H16">
         <v>1.04</v>
       </c>
-      <c r="I14">
-        <v>1000</v>
-      </c>
-      <c r="J14">
-        <v>1.01</v>
-      </c>
-      <c r="K14">
-        <v>1000</v>
-      </c>
-      <c r="L14">
-        <v>1.01</v>
-      </c>
-      <c r="M14">
-        <v>1.01</v>
-      </c>
-      <c r="N14">
-        <v>1.24</v>
-      </c>
-      <c r="O14">
-        <v>1.01</v>
-      </c>
-      <c r="P14">
-        <v>1.24</v>
-      </c>
-      <c r="Q14">
+      <c r="I16">
+        <v>990</v>
+      </c>
+      <c r="J16">
+        <v>1.06</v>
+      </c>
+      <c r="K16">
+        <v>950</v>
+      </c>
+      <c r="L16">
+        <v>1.01</v>
+      </c>
+      <c r="M16">
+        <v>1.01</v>
+      </c>
+      <c r="N16">
+        <v>1.26</v>
+      </c>
+      <c r="O16">
         <v>1.02</v>
       </c>
-      <c r="R14">
+      <c r="P16">
+        <v>1.25</v>
+      </c>
+      <c r="Q16">
+        <v>1.4</v>
+      </c>
+      <c r="R16">
         <v>1.18</v>
       </c>
-      <c r="S14">
+      <c r="S16">
+        <v>1.39</v>
+      </c>
+      <c r="T16">
+        <v>1.11</v>
+      </c>
+      <c r="U16">
+        <v>1.11</v>
+      </c>
+      <c r="V16">
         <v>1.02</v>
       </c>
-      <c r="T14">
-        <v>1.01</v>
-      </c>
-      <c r="U14">
-        <v>1.01</v>
-      </c>
-      <c r="V14">
-        <v>1.01</v>
-      </c>
-      <c r="W14">
-        <v>1.01</v>
-      </c>
-      <c r="X14">
-        <v>1000</v>
-      </c>
-      <c r="Y14">
-        <v>1000</v>
-      </c>
-      <c r="Z14">
-        <v>1000</v>
-      </c>
-      <c r="AA14">
-        <v>1000</v>
-      </c>
-      <c r="AB14">
-        <v>1000</v>
-      </c>
-      <c r="AC14">
-        <v>1000</v>
-      </c>
-      <c r="AD14">
-        <v>1000</v>
-      </c>
-      <c r="AE14">
-        <v>1000</v>
-      </c>
-      <c r="AF14">
-        <v>1000</v>
-      </c>
-      <c r="AG14">
-        <v>1000</v>
-      </c>
-      <c r="AH14">
-        <v>1000</v>
-      </c>
-      <c r="AI14">
-        <v>1000</v>
-      </c>
-      <c r="AJ14">
-        <v>1000</v>
-      </c>
-      <c r="AK14">
-        <v>1000</v>
-      </c>
-      <c r="AL14">
-        <v>1000</v>
-      </c>
-      <c r="AM14">
-        <v>1000</v>
-      </c>
-      <c r="AN14">
-        <v>1000</v>
-      </c>
-      <c r="AO14">
-        <v>1000</v>
-      </c>
-      <c r="AP14">
-        <v>1.01</v>
-      </c>
-      <c r="AQ14">
-        <v>1.01</v>
-      </c>
-      <c r="AR14">
-        <v>1.01</v>
-      </c>
-      <c r="AS14">
-        <v>1.01</v>
-      </c>
-      <c r="AT14">
-        <v>1.01</v>
-      </c>
-      <c r="AU14">
-        <v>1.01</v>
-      </c>
-      <c r="AV14">
-        <v>1.01</v>
-      </c>
-      <c r="AW14">
-        <v>1.01</v>
-      </c>
-      <c r="AX14">
-        <v>1.01</v>
-      </c>
-      <c r="AY14">
-        <v>1.01</v>
-      </c>
-      <c r="AZ14">
-        <v>1.01</v>
-      </c>
-      <c r="BA14">
-        <v>1.01</v>
-      </c>
-      <c r="BB14">
-        <v>1.01</v>
-      </c>
-      <c r="BC14">
-        <v>1.01</v>
-      </c>
-      <c r="BD14">
-        <v>1.01</v>
-      </c>
-      <c r="BE14">
-        <v>1.01</v>
-      </c>
-      <c r="BF14">
-        <v>1.01</v>
-      </c>
-      <c r="BG14">
-        <v>1.01</v>
-      </c>
-      <c r="BH14">
-        <v>1000</v>
-      </c>
-      <c r="BI14">
-        <v>1.01</v>
-      </c>
-      <c r="BJ14">
-        <v>1000</v>
-      </c>
-      <c r="BK14">
-        <v>1.01</v>
-      </c>
-      <c r="BL14">
-        <v>1000</v>
-      </c>
-      <c r="BM14">
-        <v>1.01</v>
-      </c>
-      <c r="BN14">
-        <v>1000</v>
-      </c>
-      <c r="BO14">
-        <v>1.01</v>
-      </c>
-      <c r="BP14">
-        <v>1000</v>
-      </c>
-      <c r="BQ14">
-        <v>1.01</v>
-      </c>
-      <c r="BR14">
-        <v>1000</v>
-      </c>
-      <c r="BS14">
-        <v>1.01</v>
-      </c>
-      <c r="BT14">
-        <v>1000</v>
-      </c>
-      <c r="BU14">
-        <v>1.01</v>
-      </c>
-      <c r="BV14">
-        <v>1000</v>
-      </c>
-      <c r="BW14">
-        <v>1.01</v>
-      </c>
-      <c r="BX14">
-        <v>1000</v>
-      </c>
-      <c r="BY14">
-        <v>1.01</v>
-      </c>
-      <c r="BZ14">
-        <v>1000</v>
-      </c>
-      <c r="CA14">
-        <v>1.01</v>
-      </c>
-      <c r="CB14" t="s">
-        <v>125</v>
+      <c r="W16">
+        <v>1.02</v>
+      </c>
+      <c r="X16">
+        <v>1000</v>
+      </c>
+      <c r="Y16">
+        <v>1000</v>
+      </c>
+      <c r="Z16">
+        <v>1000</v>
+      </c>
+      <c r="AA16">
+        <v>1000</v>
+      </c>
+      <c r="AB16">
+        <v>1000</v>
+      </c>
+      <c r="AC16">
+        <v>1000</v>
+      </c>
+      <c r="AD16">
+        <v>1000</v>
+      </c>
+      <c r="AE16">
+        <v>1000</v>
+      </c>
+      <c r="AF16">
+        <v>1000</v>
+      </c>
+      <c r="AG16">
+        <v>1000</v>
+      </c>
+      <c r="AH16">
+        <v>1000</v>
+      </c>
+      <c r="AI16">
+        <v>1000</v>
+      </c>
+      <c r="AJ16">
+        <v>1000</v>
+      </c>
+      <c r="AK16">
+        <v>1000</v>
+      </c>
+      <c r="AL16">
+        <v>1000</v>
+      </c>
+      <c r="AM16">
+        <v>1000</v>
+      </c>
+      <c r="AN16">
+        <v>1000</v>
+      </c>
+      <c r="AO16">
+        <v>1000</v>
+      </c>
+      <c r="AP16">
+        <v>1.03</v>
+      </c>
+      <c r="AQ16">
+        <v>1.03</v>
+      </c>
+      <c r="AR16">
+        <v>1.03</v>
+      </c>
+      <c r="AS16">
+        <v>1.03</v>
+      </c>
+      <c r="AT16">
+        <v>1.03</v>
+      </c>
+      <c r="AU16">
+        <v>1.03</v>
+      </c>
+      <c r="AV16">
+        <v>1.03</v>
+      </c>
+      <c r="AW16">
+        <v>1.03</v>
+      </c>
+      <c r="AX16">
+        <v>1.03</v>
+      </c>
+      <c r="AY16">
+        <v>1.03</v>
+      </c>
+      <c r="AZ16">
+        <v>1.03</v>
+      </c>
+      <c r="BA16">
+        <v>1.03</v>
+      </c>
+      <c r="BB16">
+        <v>1.03</v>
+      </c>
+      <c r="BC16">
+        <v>1.03</v>
+      </c>
+      <c r="BD16">
+        <v>1.03</v>
+      </c>
+      <c r="BE16">
+        <v>1.03</v>
+      </c>
+      <c r="BF16">
+        <v>1.01</v>
+      </c>
+      <c r="BG16">
+        <v>1.01</v>
+      </c>
+      <c r="BH16">
+        <v>1000</v>
+      </c>
+      <c r="BI16">
+        <v>1.01</v>
+      </c>
+      <c r="BJ16">
+        <v>1000</v>
+      </c>
+      <c r="BK16">
+        <v>1.01</v>
+      </c>
+      <c r="BL16">
+        <v>1000</v>
+      </c>
+      <c r="BM16">
+        <v>1.01</v>
+      </c>
+      <c r="BN16">
+        <v>1000</v>
+      </c>
+      <c r="BO16">
+        <v>1.01</v>
+      </c>
+      <c r="BP16">
+        <v>1000</v>
+      </c>
+      <c r="BQ16">
+        <v>1.01</v>
+      </c>
+      <c r="BR16">
+        <v>1000</v>
+      </c>
+      <c r="BS16">
+        <v>1.01</v>
+      </c>
+      <c r="BT16">
+        <v>1000</v>
+      </c>
+      <c r="BU16">
+        <v>1.01</v>
+      </c>
+      <c r="BV16">
+        <v>1000</v>
+      </c>
+      <c r="BW16">
+        <v>1.01</v>
+      </c>
+      <c r="BX16">
+        <v>1000</v>
+      </c>
+      <c r="BY16">
+        <v>1.01</v>
+      </c>
+      <c r="BZ16">
+        <v>1000</v>
+      </c>
+      <c r="CA16">
+        <v>1.01</v>
+      </c>
+      <c r="CB16" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="17" spans="1:80">
+      <c r="A17" t="s">
+        <v>87</v>
+      </c>
+      <c r="B17" t="s">
+        <v>91</v>
+      </c>
+      <c r="C17" t="s">
+        <v>101</v>
+      </c>
+      <c r="D17" t="s">
+        <v>117</v>
+      </c>
+      <c r="E17" t="s">
+        <v>133</v>
+      </c>
+      <c r="F17">
+        <v>1.04</v>
+      </c>
+      <c r="G17">
+        <v>600</v>
+      </c>
+      <c r="H17">
+        <v>1.04</v>
+      </c>
+      <c r="I17">
+        <v>870</v>
+      </c>
+      <c r="J17">
+        <v>1.03</v>
+      </c>
+      <c r="K17">
+        <v>950</v>
+      </c>
+      <c r="L17">
+        <v>1.01</v>
+      </c>
+      <c r="M17">
+        <v>1.01</v>
+      </c>
+      <c r="N17">
+        <v>1.26</v>
+      </c>
+      <c r="O17">
+        <v>1.01</v>
+      </c>
+      <c r="P17">
+        <v>1.25</v>
+      </c>
+      <c r="Q17">
+        <v>1.48</v>
+      </c>
+      <c r="R17">
+        <v>1.13</v>
+      </c>
+      <c r="S17">
+        <v>1.48</v>
+      </c>
+      <c r="T17">
+        <v>1.01</v>
+      </c>
+      <c r="U17">
+        <v>1.01</v>
+      </c>
+      <c r="V17">
+        <v>1.01</v>
+      </c>
+      <c r="W17">
+        <v>1.01</v>
+      </c>
+      <c r="X17">
+        <v>1000</v>
+      </c>
+      <c r="Y17">
+        <v>1000</v>
+      </c>
+      <c r="Z17">
+        <v>1000</v>
+      </c>
+      <c r="AA17">
+        <v>1000</v>
+      </c>
+      <c r="AB17">
+        <v>1000</v>
+      </c>
+      <c r="AC17">
+        <v>1000</v>
+      </c>
+      <c r="AD17">
+        <v>1000</v>
+      </c>
+      <c r="AE17">
+        <v>1000</v>
+      </c>
+      <c r="AF17">
+        <v>1000</v>
+      </c>
+      <c r="AG17">
+        <v>1000</v>
+      </c>
+      <c r="AH17">
+        <v>1000</v>
+      </c>
+      <c r="AI17">
+        <v>1000</v>
+      </c>
+      <c r="AJ17">
+        <v>1000</v>
+      </c>
+      <c r="AK17">
+        <v>1000</v>
+      </c>
+      <c r="AL17">
+        <v>1000</v>
+      </c>
+      <c r="AM17">
+        <v>1000</v>
+      </c>
+      <c r="AN17">
+        <v>1000</v>
+      </c>
+      <c r="AO17">
+        <v>1000</v>
+      </c>
+      <c r="AP17">
+        <v>1.03</v>
+      </c>
+      <c r="AQ17">
+        <v>1.03</v>
+      </c>
+      <c r="AR17">
+        <v>1.03</v>
+      </c>
+      <c r="AS17">
+        <v>1.03</v>
+      </c>
+      <c r="AT17">
+        <v>1.03</v>
+      </c>
+      <c r="AU17">
+        <v>1.03</v>
+      </c>
+      <c r="AV17">
+        <v>1.03</v>
+      </c>
+      <c r="AW17">
+        <v>1.03</v>
+      </c>
+      <c r="AX17">
+        <v>1.03</v>
+      </c>
+      <c r="AY17">
+        <v>1.03</v>
+      </c>
+      <c r="AZ17">
+        <v>1.03</v>
+      </c>
+      <c r="BA17">
+        <v>1.03</v>
+      </c>
+      <c r="BB17">
+        <v>1.03</v>
+      </c>
+      <c r="BC17">
+        <v>1.03</v>
+      </c>
+      <c r="BD17">
+        <v>1.03</v>
+      </c>
+      <c r="BE17">
+        <v>1.03</v>
+      </c>
+      <c r="BF17">
+        <v>1.01</v>
+      </c>
+      <c r="BG17">
+        <v>1.01</v>
+      </c>
+      <c r="BH17">
+        <v>1000</v>
+      </c>
+      <c r="BI17">
+        <v>1.01</v>
+      </c>
+      <c r="BJ17">
+        <v>1000</v>
+      </c>
+      <c r="BK17">
+        <v>1.01</v>
+      </c>
+      <c r="BL17">
+        <v>1000</v>
+      </c>
+      <c r="BM17">
+        <v>1.01</v>
+      </c>
+      <c r="BN17">
+        <v>1000</v>
+      </c>
+      <c r="BO17">
+        <v>1.01</v>
+      </c>
+      <c r="BP17">
+        <v>1000</v>
+      </c>
+      <c r="BQ17">
+        <v>1.01</v>
+      </c>
+      <c r="BR17">
+        <v>1000</v>
+      </c>
+      <c r="BS17">
+        <v>1.01</v>
+      </c>
+      <c r="BT17">
+        <v>1000</v>
+      </c>
+      <c r="BU17">
+        <v>1.01</v>
+      </c>
+      <c r="BV17">
+        <v>1000</v>
+      </c>
+      <c r="BW17">
+        <v>1.01</v>
+      </c>
+      <c r="BX17">
+        <v>1000</v>
+      </c>
+      <c r="BY17">
+        <v>1.01</v>
+      </c>
+      <c r="BZ17">
+        <v>0</v>
+      </c>
+      <c r="CA17">
+        <v>0</v>
+      </c>
+      <c r="CB17" t="s">
+        <v>134</v>
       </c>
     </row>
   </sheetData>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-08-11.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-08-11.xlsx
@@ -418,7 +418,7 @@
     <t>Orsomarso</t>
   </si>
   <si>
-    <t>2026-08-10 06:03:16</t>
+    <t>2026-08-10 08:12:44</t>
   </si>
 </sst>
 </file>
@@ -1012,226 +1012,226 @@
         <v>118</v>
       </c>
       <c r="F2">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="G2">
-        <v>15.5</v>
+        <v>1000</v>
       </c>
       <c r="H2">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="I2">
-        <v>1.34</v>
+        <v>1.38</v>
       </c>
       <c r="J2">
-        <v>5.1</v>
+        <v>4.4</v>
       </c>
       <c r="K2">
-        <v>6.4</v>
+        <v>7.4</v>
       </c>
       <c r="L2">
         <v>1.29</v>
       </c>
       <c r="M2">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="N2">
-        <v>4.5</v>
+        <v>2.28</v>
       </c>
       <c r="O2">
         <v>1.25</v>
       </c>
       <c r="P2">
-        <v>2.22</v>
+        <v>2.28</v>
       </c>
       <c r="Q2">
+        <v>1.67</v>
+      </c>
+      <c r="R2">
+        <v>1.52</v>
+      </c>
+      <c r="S2">
+        <v>2.56</v>
+      </c>
+      <c r="T2">
         <v>1.66</v>
       </c>
-      <c r="R2">
-        <v>1.49</v>
-      </c>
-      <c r="S2">
-        <v>2.58</v>
-      </c>
-      <c r="T2">
-        <v>2.16</v>
-      </c>
       <c r="U2">
-        <v>1.71</v>
+        <v>1.47</v>
       </c>
       <c r="V2">
-        <v>3.9</v>
+        <v>3.55</v>
       </c>
       <c r="W2">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="X2">
-        <v>27</v>
+        <v>1000</v>
       </c>
       <c r="Y2">
-        <v>9</v>
+        <v>1000</v>
       </c>
       <c r="Z2">
-        <v>8.199999999999999</v>
+        <v>1000</v>
       </c>
       <c r="AA2">
-        <v>12</v>
+        <v>1000</v>
       </c>
       <c r="AB2">
-        <v>48</v>
+        <v>1000</v>
       </c>
       <c r="AC2">
-        <v>14.5</v>
+        <v>1000</v>
       </c>
       <c r="AD2">
-        <v>13</v>
+        <v>1000</v>
       </c>
       <c r="AE2">
-        <v>15.5</v>
+        <v>1000</v>
       </c>
       <c r="AF2">
-        <v>160</v>
+        <v>1000</v>
       </c>
       <c r="AG2">
-        <v>60</v>
+        <v>1000</v>
       </c>
       <c r="AH2">
-        <v>40</v>
+        <v>1000</v>
       </c>
       <c r="AI2">
-        <v>50</v>
+        <v>1000</v>
       </c>
       <c r="AJ2">
         <v>1000</v>
       </c>
       <c r="AK2">
-        <v>290</v>
+        <v>1000</v>
       </c>
       <c r="AL2">
-        <v>220</v>
+        <v>1000</v>
       </c>
       <c r="AM2">
-        <v>230</v>
+        <v>1000</v>
       </c>
       <c r="AN2">
-        <v>420</v>
+        <v>1000</v>
       </c>
       <c r="AO2">
-        <v>5.4</v>
+        <v>1000</v>
       </c>
       <c r="AP2">
-        <v>5.4</v>
+        <v>1.01</v>
       </c>
       <c r="AQ2">
-        <v>3.85</v>
+        <v>1.01</v>
       </c>
       <c r="AR2">
-        <v>3.7</v>
+        <v>1.01</v>
       </c>
       <c r="AS2">
-        <v>4.3</v>
+        <v>1.01</v>
       </c>
       <c r="AT2">
-        <v>5.9</v>
+        <v>1.01</v>
       </c>
       <c r="AU2">
-        <v>4.6</v>
+        <v>1.01</v>
       </c>
       <c r="AV2">
-        <v>4.4</v>
+        <v>1.01</v>
       </c>
       <c r="AW2">
-        <v>4.7</v>
+        <v>1.01</v>
       </c>
       <c r="AX2">
-        <v>6.4</v>
+        <v>1.01</v>
       </c>
       <c r="AY2">
-        <v>6</v>
+        <v>1.01</v>
       </c>
       <c r="AZ2">
-        <v>5.7</v>
+        <v>1.01</v>
       </c>
       <c r="BA2">
-        <v>5.9</v>
+        <v>1.01</v>
       </c>
       <c r="BB2">
-        <v>6.6</v>
+        <v>1.01</v>
       </c>
       <c r="BC2">
-        <v>6.6</v>
+        <v>1.01</v>
       </c>
       <c r="BD2">
-        <v>6.4</v>
+        <v>1.01</v>
       </c>
       <c r="BE2">
-        <v>6.4</v>
+        <v>1.01</v>
       </c>
       <c r="BF2">
-        <v>6.6</v>
+        <v>1.01</v>
       </c>
       <c r="BG2">
-        <v>3</v>
+        <v>1.01</v>
       </c>
       <c r="BH2">
-        <v>4.8</v>
+        <v>1000</v>
       </c>
       <c r="BI2">
-        <v>2.42</v>
+        <v>1.04</v>
       </c>
       <c r="BJ2">
-        <v>15.5</v>
+        <v>1000</v>
       </c>
       <c r="BK2">
-        <v>3.7</v>
+        <v>1.04</v>
       </c>
       <c r="BL2">
         <v>1000</v>
       </c>
       <c r="BM2">
-        <v>4.8</v>
+        <v>1.04</v>
       </c>
       <c r="BN2">
-        <v>18</v>
+        <v>1000</v>
       </c>
       <c r="BO2">
-        <v>3.85</v>
+        <v>1.04</v>
       </c>
       <c r="BP2">
         <v>1000</v>
       </c>
       <c r="BQ2">
-        <v>4.7</v>
+        <v>1.04</v>
       </c>
       <c r="BR2">
         <v>1000</v>
       </c>
       <c r="BS2">
-        <v>4.7</v>
+        <v>1.04</v>
       </c>
       <c r="BT2">
-        <v>4.3</v>
+        <v>1000</v>
       </c>
       <c r="BU2">
-        <v>2.94</v>
+        <v>1.04</v>
       </c>
       <c r="BV2">
-        <v>8.800000000000001</v>
+        <v>1000</v>
       </c>
       <c r="BW2">
-        <v>3.15</v>
+        <v>1.04</v>
       </c>
       <c r="BX2">
-        <v>30</v>
+        <v>1000</v>
       </c>
       <c r="BY2">
-        <v>4.2</v>
+        <v>1.04</v>
       </c>
       <c r="BZ2">
-        <v>14.5</v>
+        <v>1000</v>
       </c>
       <c r="CA2">
-        <v>3.65</v>
+        <v>1.04</v>
       </c>
       <c r="CB2" t="s">
         <v>134</v>
@@ -1254,10 +1254,10 @@
         <v>119</v>
       </c>
       <c r="F3">
-        <v>2.38</v>
+        <v>2.4</v>
       </c>
       <c r="G3">
-        <v>2.48</v>
+        <v>2.46</v>
       </c>
       <c r="H3">
         <v>3.15</v>
@@ -1266,7 +1266,7 @@
         <v>3.3</v>
       </c>
       <c r="J3">
-        <v>3.45</v>
+        <v>3.55</v>
       </c>
       <c r="K3">
         <v>3.7</v>
@@ -1284,13 +1284,13 @@
         <v>1.38</v>
       </c>
       <c r="P3">
-        <v>1.83</v>
+        <v>1.82</v>
       </c>
       <c r="Q3">
         <v>2.16</v>
       </c>
       <c r="R3">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="S3">
         <v>4</v>
@@ -1299,181 +1299,181 @@
         <v>1.85</v>
       </c>
       <c r="U3">
-        <v>2.06</v>
+        <v>2</v>
       </c>
       <c r="V3">
         <v>1.43</v>
       </c>
       <c r="W3">
-        <v>1.69</v>
+        <v>1.68</v>
       </c>
       <c r="X3">
-        <v>14.5</v>
+        <v>15.5</v>
       </c>
       <c r="Y3">
         <v>13</v>
       </c>
       <c r="Z3">
-        <v>22</v>
+        <v>29</v>
       </c>
       <c r="AA3">
-        <v>80</v>
+        <v>410</v>
       </c>
       <c r="AB3">
-        <v>9.6</v>
+        <v>10.5</v>
       </c>
       <c r="AC3">
-        <v>8.199999999999999</v>
+        <v>7.8</v>
       </c>
       <c r="AD3">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AE3">
-        <v>48</v>
+        <v>95</v>
       </c>
       <c r="AF3">
         <v>15</v>
       </c>
       <c r="AG3">
+        <v>13.5</v>
+      </c>
+      <c r="AH3">
+        <v>26</v>
+      </c>
+      <c r="AI3">
+        <v>340</v>
+      </c>
+      <c r="AJ3">
+        <v>40</v>
+      </c>
+      <c r="AK3">
+        <v>44</v>
+      </c>
+      <c r="AL3">
+        <v>140</v>
+      </c>
+      <c r="AM3">
+        <v>1000</v>
+      </c>
+      <c r="AN3">
+        <v>34</v>
+      </c>
+      <c r="AO3">
+        <v>100</v>
+      </c>
+      <c r="AP3">
+        <v>10.5</v>
+      </c>
+      <c r="AQ3">
+        <v>9.4</v>
+      </c>
+      <c r="AR3">
+        <v>16.5</v>
+      </c>
+      <c r="AS3">
+        <v>40</v>
+      </c>
+      <c r="AT3">
+        <v>8</v>
+      </c>
+      <c r="AU3">
+        <v>6.6</v>
+      </c>
+      <c r="AV3">
+        <v>11</v>
+      </c>
+      <c r="AW3">
+        <v>29</v>
+      </c>
+      <c r="AX3">
         <v>11.5</v>
       </c>
-      <c r="AH3">
+      <c r="AY3">
+        <v>9.4</v>
+      </c>
+      <c r="AZ3">
+        <v>14.5</v>
+      </c>
+      <c r="BA3">
+        <v>36</v>
+      </c>
+      <c r="BB3">
         <v>21</v>
       </c>
-      <c r="AI3">
-        <v>350</v>
-      </c>
-      <c r="AJ3">
-        <v>38</v>
-      </c>
-      <c r="AK3">
-        <v>40</v>
-      </c>
-      <c r="AL3">
-        <v>50</v>
-      </c>
-      <c r="AM3">
-        <v>1000</v>
-      </c>
-      <c r="AN3">
-        <v>27</v>
-      </c>
-      <c r="AO3">
-        <v>48</v>
-      </c>
-      <c r="AP3">
-        <v>11.5</v>
-      </c>
-      <c r="AQ3">
-        <v>10.5</v>
-      </c>
-      <c r="AR3">
-        <v>17.5</v>
-      </c>
-      <c r="AS3">
-        <v>29</v>
-      </c>
-      <c r="AT3">
-        <v>8.6</v>
-      </c>
-      <c r="AU3">
-        <v>7.2</v>
-      </c>
-      <c r="AV3">
-        <v>11.5</v>
-      </c>
-      <c r="AW3">
-        <v>30</v>
-      </c>
-      <c r="AX3">
-        <v>12.5</v>
-      </c>
-      <c r="AY3">
-        <v>10.5</v>
-      </c>
-      <c r="AZ3">
-        <v>17</v>
-      </c>
-      <c r="BA3">
-        <v>38</v>
-      </c>
-      <c r="BB3">
-        <v>25</v>
-      </c>
       <c r="BC3">
-        <v>18.5</v>
+        <v>19.5</v>
       </c>
       <c r="BD3">
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="BE3">
         <v>40</v>
       </c>
       <c r="BF3">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="BG3">
-        <v>32</v>
+        <v>24</v>
       </c>
       <c r="BH3">
-        <v>3.65</v>
+        <v>1000</v>
       </c>
       <c r="BI3">
-        <v>2.6</v>
+        <v>1.04</v>
       </c>
       <c r="BJ3">
-        <v>12</v>
+        <v>1000</v>
       </c>
       <c r="BK3">
-        <v>3.6</v>
+        <v>1.04</v>
       </c>
       <c r="BL3">
         <v>1000</v>
       </c>
       <c r="BM3">
-        <v>5</v>
+        <v>1.04</v>
       </c>
       <c r="BN3">
-        <v>6.2</v>
+        <v>1000</v>
       </c>
       <c r="BO3">
-        <v>4.1</v>
+        <v>1.04</v>
       </c>
       <c r="BP3">
-        <v>23</v>
+        <v>1000</v>
       </c>
       <c r="BQ3">
-        <v>4.2</v>
+        <v>1.04</v>
       </c>
       <c r="BR3">
-        <v>40</v>
+        <v>1000</v>
       </c>
       <c r="BS3">
-        <v>4.5</v>
+        <v>1.04</v>
       </c>
       <c r="BT3">
-        <v>7.4</v>
+        <v>1000</v>
       </c>
       <c r="BU3">
-        <v>4.9</v>
+        <v>1.04</v>
       </c>
       <c r="BV3">
-        <v>32</v>
+        <v>1000</v>
       </c>
       <c r="BW3">
-        <v>4.4</v>
+        <v>1.04</v>
       </c>
       <c r="BX3">
-        <v>48</v>
+        <v>1000</v>
       </c>
       <c r="BY3">
-        <v>4.6</v>
+        <v>1.04</v>
       </c>
       <c r="BZ3">
-        <v>38</v>
+        <v>1000</v>
       </c>
       <c r="CA3">
-        <v>4.5</v>
+        <v>1.04</v>
       </c>
       <c r="CB3" t="s">
         <v>134</v>
@@ -1496,226 +1496,226 @@
         <v>120</v>
       </c>
       <c r="F4">
-        <v>1.66</v>
+        <v>1.73</v>
       </c>
       <c r="G4">
-        <v>1.72</v>
+        <v>1.79</v>
       </c>
       <c r="H4">
-        <v>6.2</v>
+        <v>5.4</v>
       </c>
       <c r="I4">
         <v>7</v>
       </c>
       <c r="J4">
-        <v>3.65</v>
+        <v>3.6</v>
       </c>
       <c r="K4">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="L4">
-        <v>1.5</v>
+        <v>1.49</v>
       </c>
       <c r="M4">
         <v>1.09</v>
       </c>
       <c r="N4">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="O4">
-        <v>1.43</v>
+        <v>1.42</v>
       </c>
       <c r="P4">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="Q4">
-        <v>2.3</v>
+        <v>2.24</v>
       </c>
       <c r="R4">
         <v>1.26</v>
       </c>
       <c r="S4">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="T4">
-        <v>2.18</v>
+        <v>1.11</v>
       </c>
       <c r="U4">
-        <v>1.73</v>
+        <v>1.11</v>
       </c>
       <c r="V4">
-        <v>1.16</v>
+        <v>1.18</v>
       </c>
       <c r="W4">
-        <v>2.38</v>
+        <v>2.24</v>
       </c>
       <c r="X4">
-        <v>12.5</v>
+        <v>1000</v>
       </c>
       <c r="Y4">
-        <v>18.5</v>
+        <v>1000</v>
       </c>
       <c r="Z4">
-        <v>60</v>
+        <v>1000</v>
       </c>
       <c r="AA4">
-        <v>250</v>
+        <v>1000</v>
       </c>
       <c r="AB4">
-        <v>7</v>
+        <v>1000</v>
       </c>
       <c r="AC4">
-        <v>9</v>
+        <v>1000</v>
       </c>
       <c r="AD4">
-        <v>28</v>
+        <v>1000</v>
       </c>
       <c r="AE4">
-        <v>140</v>
+        <v>1000</v>
       </c>
       <c r="AF4">
-        <v>8.800000000000001</v>
+        <v>1000</v>
       </c>
       <c r="AG4">
-        <v>11</v>
+        <v>1000</v>
       </c>
       <c r="AH4">
-        <v>28</v>
+        <v>1000</v>
       </c>
       <c r="AI4">
-        <v>140</v>
+        <v>1000</v>
       </c>
       <c r="AJ4">
-        <v>17.5</v>
+        <v>1000</v>
       </c>
       <c r="AK4">
-        <v>22</v>
+        <v>1000</v>
       </c>
       <c r="AL4">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="AM4">
-        <v>210</v>
+        <v>1000</v>
       </c>
       <c r="AN4">
-        <v>14.5</v>
+        <v>1000</v>
       </c>
       <c r="AO4">
-        <v>220</v>
+        <v>1000</v>
       </c>
       <c r="AP4">
-        <v>9</v>
+        <v>1.01</v>
       </c>
       <c r="AQ4">
-        <v>14.5</v>
+        <v>1.01</v>
       </c>
       <c r="AR4">
-        <v>8.4</v>
+        <v>1.01</v>
       </c>
       <c r="AS4">
-        <v>9.4</v>
+        <v>1.01</v>
       </c>
       <c r="AT4">
-        <v>5.8</v>
+        <v>1.01</v>
       </c>
       <c r="AU4">
-        <v>7.4</v>
+        <v>1.01</v>
       </c>
       <c r="AV4">
-        <v>7.2</v>
+        <v>1.01</v>
       </c>
       <c r="AW4">
-        <v>9.199999999999999</v>
+        <v>1.01</v>
       </c>
       <c r="AX4">
-        <v>7</v>
+        <v>1.01</v>
       </c>
       <c r="AY4">
-        <v>9</v>
+        <v>1.01</v>
       </c>
       <c r="AZ4">
-        <v>7.2</v>
+        <v>1.01</v>
       </c>
       <c r="BA4">
-        <v>9</v>
+        <v>1.01</v>
       </c>
       <c r="BB4">
-        <v>14</v>
+        <v>1.01</v>
       </c>
       <c r="BC4">
-        <v>17.5</v>
+        <v>1.01</v>
       </c>
       <c r="BD4">
-        <v>8.4</v>
+        <v>1.01</v>
       </c>
       <c r="BE4">
-        <v>9.199999999999999</v>
+        <v>1.01</v>
       </c>
       <c r="BF4">
-        <v>10.5</v>
+        <v>1.01</v>
       </c>
       <c r="BG4">
-        <v>9.199999999999999</v>
+        <v>1.01</v>
       </c>
       <c r="BH4">
-        <v>3.1</v>
+        <v>1000</v>
       </c>
       <c r="BI4">
-        <v>2.6</v>
+        <v>1.04</v>
       </c>
       <c r="BJ4">
-        <v>12</v>
+        <v>1000</v>
       </c>
       <c r="BK4">
-        <v>9.800000000000001</v>
+        <v>1.04</v>
       </c>
       <c r="BL4">
         <v>1000</v>
       </c>
       <c r="BM4">
-        <v>13.5</v>
+        <v>1.04</v>
       </c>
       <c r="BN4">
-        <v>4</v>
+        <v>1000</v>
       </c>
       <c r="BO4">
-        <v>3.45</v>
+        <v>1.04</v>
       </c>
       <c r="BP4">
-        <v>12</v>
+        <v>1000</v>
       </c>
       <c r="BQ4">
-        <v>6.4</v>
+        <v>1.04</v>
       </c>
       <c r="BR4">
         <v>1000</v>
       </c>
       <c r="BS4">
-        <v>10</v>
+        <v>1.04</v>
       </c>
       <c r="BT4">
-        <v>10.5</v>
+        <v>1000</v>
       </c>
       <c r="BU4">
-        <v>6</v>
+        <v>1.04</v>
       </c>
       <c r="BV4">
         <v>1000</v>
       </c>
       <c r="BW4">
-        <v>12</v>
+        <v>1.04</v>
       </c>
       <c r="BX4">
         <v>1000</v>
       </c>
       <c r="BY4">
-        <v>12</v>
+        <v>1.04</v>
       </c>
       <c r="BZ4">
         <v>1000</v>
       </c>
       <c r="CA4">
-        <v>9.4</v>
+        <v>1.04</v>
       </c>
       <c r="CB4" t="s">
         <v>134</v>
@@ -1738,22 +1738,22 @@
         <v>121</v>
       </c>
       <c r="F5">
-        <v>1.57</v>
+        <v>1.56</v>
       </c>
       <c r="G5">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="H5">
-        <v>7.4</v>
+        <v>6.6</v>
       </c>
       <c r="I5">
-        <v>7.6</v>
+        <v>8.6</v>
       </c>
       <c r="J5">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="K5">
-        <v>4.4</v>
+        <v>4.7</v>
       </c>
       <c r="L5">
         <v>1.46</v>
@@ -1762,7 +1762,7 @@
         <v>1.08</v>
       </c>
       <c r="N5">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="O5">
         <v>1.39</v>
@@ -1774,190 +1774,190 @@
         <v>2.2</v>
       </c>
       <c r="R5">
-        <v>1.31</v>
+        <v>1.29</v>
       </c>
       <c r="S5">
         <v>4.2</v>
       </c>
       <c r="T5">
-        <v>2.22</v>
+        <v>2.18</v>
       </c>
       <c r="U5">
         <v>1.72</v>
       </c>
       <c r="V5">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="W5">
-        <v>2.66</v>
+        <v>2.62</v>
       </c>
       <c r="X5">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="Y5">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="Z5">
-        <v>65</v>
+        <v>330</v>
       </c>
       <c r="AA5">
-        <v>310</v>
+        <v>1000</v>
       </c>
       <c r="AB5">
-        <v>7</v>
+        <v>7.4</v>
       </c>
       <c r="AC5">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AD5">
-        <v>30</v>
+        <v>50</v>
       </c>
       <c r="AE5">
-        <v>160</v>
+        <v>1000</v>
       </c>
       <c r="AF5">
         <v>8.6</v>
       </c>
       <c r="AG5">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AH5">
-        <v>28</v>
+        <v>50</v>
       </c>
       <c r="AI5">
-        <v>150</v>
+        <v>1000</v>
       </c>
       <c r="AJ5">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="AK5">
         <v>19.5</v>
       </c>
       <c r="AL5">
-        <v>50</v>
+        <v>240</v>
       </c>
       <c r="AM5">
-        <v>240</v>
+        <v>1000</v>
       </c>
       <c r="AN5">
-        <v>11.5</v>
+        <v>10.5</v>
       </c>
       <c r="AO5">
-        <v>290</v>
+        <v>1000</v>
       </c>
       <c r="AP5">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AQ5">
-        <v>16.5</v>
+        <v>14.5</v>
       </c>
       <c r="AR5">
-        <v>9</v>
+        <v>40</v>
       </c>
       <c r="AS5">
-        <v>10</v>
+        <v>48</v>
       </c>
       <c r="AT5">
         <v>6.2</v>
       </c>
       <c r="AU5">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="AV5">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="AW5">
-        <v>10</v>
+        <v>42</v>
       </c>
       <c r="AX5">
-        <v>7.2</v>
+        <v>6.8</v>
       </c>
       <c r="AY5">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AZ5">
-        <v>24</v>
+        <v>19.5</v>
       </c>
       <c r="BA5">
-        <v>9.800000000000001</v>
+        <v>42</v>
       </c>
       <c r="BB5">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="BC5">
-        <v>16.5</v>
+        <v>14</v>
       </c>
       <c r="BD5">
         <v>34</v>
       </c>
       <c r="BE5">
-        <v>10</v>
+        <v>48</v>
       </c>
       <c r="BF5">
-        <v>9</v>
+        <v>8.6</v>
       </c>
       <c r="BG5">
-        <v>10</v>
+        <v>48</v>
       </c>
       <c r="BH5">
-        <v>3.25</v>
+        <v>1000</v>
       </c>
       <c r="BI5">
-        <v>2.68</v>
+        <v>1.04</v>
       </c>
       <c r="BJ5">
-        <v>13.5</v>
+        <v>1000</v>
       </c>
       <c r="BK5">
-        <v>9.800000000000001</v>
+        <v>1.04</v>
       </c>
       <c r="BL5">
         <v>1000</v>
       </c>
       <c r="BM5">
-        <v>12.5</v>
+        <v>1.04</v>
       </c>
       <c r="BN5">
-        <v>3.9</v>
+        <v>1000</v>
       </c>
       <c r="BO5">
-        <v>3.3</v>
+        <v>1.04</v>
       </c>
       <c r="BP5">
-        <v>10.5</v>
+        <v>1000</v>
       </c>
       <c r="BQ5">
-        <v>5.8</v>
+        <v>1.04</v>
       </c>
       <c r="BR5">
-        <v>34</v>
+        <v>1000</v>
       </c>
       <c r="BS5">
-        <v>9.4</v>
+        <v>1.04</v>
       </c>
       <c r="BT5">
-        <v>11</v>
+        <v>1000</v>
       </c>
       <c r="BU5">
-        <v>6</v>
+        <v>1.04</v>
       </c>
       <c r="BV5">
         <v>1000</v>
       </c>
       <c r="BW5">
-        <v>11</v>
+        <v>1.04</v>
       </c>
       <c r="BX5">
         <v>1000</v>
       </c>
       <c r="BY5">
-        <v>11.5</v>
+        <v>1.04</v>
       </c>
       <c r="BZ5">
-        <v>23</v>
+        <v>1000</v>
       </c>
       <c r="CA5">
-        <v>8.4</v>
+        <v>1.04</v>
       </c>
       <c r="CB5" t="s">
         <v>134</v>
@@ -1983,19 +1983,19 @@
         <v>1.35</v>
       </c>
       <c r="G6">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="H6">
-        <v>11.5</v>
+        <v>9</v>
       </c>
       <c r="I6">
-        <v>13.5</v>
+        <v>15</v>
       </c>
       <c r="J6">
-        <v>5.3</v>
+        <v>5.1</v>
       </c>
       <c r="K6">
-        <v>5.8</v>
+        <v>6</v>
       </c>
       <c r="L6">
         <v>1.36</v>
@@ -2007,7 +2007,7 @@
         <v>4.4</v>
       </c>
       <c r="O6">
-        <v>1.27</v>
+        <v>1.26</v>
       </c>
       <c r="P6">
         <v>2.16</v>
@@ -2022,184 +2022,184 @@
         <v>3.05</v>
       </c>
       <c r="T6">
-        <v>2.2</v>
+        <v>2.16</v>
       </c>
       <c r="U6">
-        <v>1.71</v>
+        <v>1.39</v>
       </c>
       <c r="V6">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="W6">
-        <v>3.7</v>
+        <v>3.55</v>
       </c>
       <c r="X6">
-        <v>21</v>
+        <v>1000</v>
       </c>
       <c r="Y6">
-        <v>36</v>
+        <v>1000</v>
       </c>
       <c r="Z6">
-        <v>140</v>
+        <v>1000</v>
       </c>
       <c r="AA6">
         <v>1000</v>
       </c>
       <c r="AB6">
-        <v>8</v>
+        <v>1000</v>
       </c>
       <c r="AC6">
-        <v>12.5</v>
+        <v>1000</v>
       </c>
       <c r="AD6">
-        <v>950</v>
+        <v>1000</v>
       </c>
       <c r="AE6">
-        <v>280</v>
+        <v>1000</v>
       </c>
       <c r="AF6">
-        <v>8</v>
+        <v>1000</v>
       </c>
       <c r="AG6">
-        <v>11</v>
+        <v>1000</v>
       </c>
       <c r="AH6">
-        <v>34</v>
+        <v>1000</v>
       </c>
       <c r="AI6">
-        <v>220</v>
+        <v>1000</v>
       </c>
       <c r="AJ6">
-        <v>11</v>
+        <v>1000</v>
       </c>
       <c r="AK6">
-        <v>16.5</v>
+        <v>1000</v>
       </c>
       <c r="AL6">
-        <v>48</v>
+        <v>1000</v>
       </c>
       <c r="AM6">
-        <v>210</v>
+        <v>1000</v>
       </c>
       <c r="AN6">
-        <v>6.4</v>
+        <v>1000</v>
       </c>
       <c r="AO6">
-        <v>460</v>
+        <v>1000</v>
       </c>
       <c r="AP6">
-        <v>14</v>
+        <v>1.01</v>
       </c>
       <c r="AQ6">
-        <v>7.6</v>
+        <v>1.01</v>
       </c>
       <c r="AR6">
-        <v>9</v>
+        <v>1.01</v>
       </c>
       <c r="AS6">
-        <v>9.6</v>
+        <v>1.01</v>
       </c>
       <c r="AT6">
-        <v>6.6</v>
+        <v>1.01</v>
       </c>
       <c r="AU6">
-        <v>10.5</v>
+        <v>1.01</v>
       </c>
       <c r="AV6">
-        <v>8</v>
+        <v>1.01</v>
       </c>
       <c r="AW6">
-        <v>9.4</v>
+        <v>1.01</v>
       </c>
       <c r="AX6">
-        <v>6.4</v>
+        <v>1.01</v>
       </c>
       <c r="AY6">
-        <v>9.199999999999999</v>
+        <v>1.01</v>
       </c>
       <c r="AZ6">
-        <v>7.4</v>
+        <v>1.01</v>
       </c>
       <c r="BA6">
-        <v>9.199999999999999</v>
+        <v>1.01</v>
       </c>
       <c r="BB6">
-        <v>9.199999999999999</v>
+        <v>1.01</v>
       </c>
       <c r="BC6">
-        <v>12</v>
+        <v>1.01</v>
       </c>
       <c r="BD6">
-        <v>8</v>
+        <v>1.01</v>
       </c>
       <c r="BE6">
-        <v>9.199999999999999</v>
+        <v>1.01</v>
       </c>
       <c r="BF6">
-        <v>5.4</v>
+        <v>1.01</v>
       </c>
       <c r="BG6">
-        <v>9.4</v>
+        <v>1.01</v>
       </c>
       <c r="BH6">
-        <v>3.95</v>
+        <v>1000</v>
       </c>
       <c r="BI6">
-        <v>3.1</v>
+        <v>1.04</v>
       </c>
       <c r="BJ6">
-        <v>13.5</v>
+        <v>1000</v>
       </c>
       <c r="BK6">
-        <v>6</v>
+        <v>1.04</v>
       </c>
       <c r="BL6">
         <v>1000</v>
       </c>
       <c r="BM6">
-        <v>10.5</v>
+        <v>1.04</v>
       </c>
       <c r="BN6">
-        <v>3.75</v>
+        <v>1000</v>
       </c>
       <c r="BO6">
-        <v>3</v>
+        <v>1.04</v>
       </c>
       <c r="BP6">
-        <v>8</v>
+        <v>1000</v>
       </c>
       <c r="BQ6">
-        <v>6</v>
+        <v>1.04</v>
       </c>
       <c r="BR6">
-        <v>28</v>
+        <v>1000</v>
       </c>
       <c r="BS6">
-        <v>7.8</v>
+        <v>1.04</v>
       </c>
       <c r="BT6">
-        <v>15.5</v>
+        <v>1000</v>
       </c>
       <c r="BU6">
-        <v>6.4</v>
+        <v>1.04</v>
       </c>
       <c r="BV6">
         <v>1000</v>
       </c>
       <c r="BW6">
-        <v>10</v>
+        <v>1.04</v>
       </c>
       <c r="BX6">
         <v>1000</v>
       </c>
       <c r="BY6">
-        <v>10</v>
+        <v>1.04</v>
       </c>
       <c r="BZ6">
-        <v>14.5</v>
+        <v>1000</v>
       </c>
       <c r="CA6">
-        <v>6.2</v>
+        <v>1.04</v>
       </c>
       <c r="CB6" t="s">
         <v>134</v>
@@ -2222,22 +2222,22 @@
         <v>123</v>
       </c>
       <c r="F7">
-        <v>2.14</v>
+        <v>2.1</v>
       </c>
       <c r="G7">
-        <v>2.28</v>
+        <v>110</v>
       </c>
       <c r="H7">
-        <v>3.25</v>
+        <v>1.35</v>
       </c>
       <c r="I7">
-        <v>3.55</v>
+        <v>870</v>
       </c>
       <c r="J7">
-        <v>3.8</v>
+        <v>1.41</v>
       </c>
       <c r="K7">
-        <v>4.2</v>
+        <v>500</v>
       </c>
       <c r="L7">
         <v>1.33</v>
@@ -2249,193 +2249,193 @@
         <v>5.2</v>
       </c>
       <c r="O7">
-        <v>1.22</v>
+        <v>1.19</v>
       </c>
       <c r="P7">
-        <v>2.36</v>
+        <v>1.27</v>
       </c>
       <c r="Q7">
-        <v>1.66</v>
+        <v>1.01</v>
       </c>
       <c r="R7">
-        <v>1.54</v>
+        <v>1.27</v>
       </c>
       <c r="S7">
-        <v>2.62</v>
+        <v>1.98</v>
       </c>
       <c r="T7">
-        <v>1.61</v>
+        <v>1.25</v>
       </c>
       <c r="U7">
-        <v>2.48</v>
+        <v>2.02</v>
       </c>
       <c r="V7">
-        <v>1.4</v>
+        <v>1.38</v>
       </c>
       <c r="W7">
-        <v>1.78</v>
+        <v>1.73</v>
       </c>
       <c r="X7">
-        <v>25</v>
+        <v>1000</v>
       </c>
       <c r="Y7">
-        <v>17</v>
+        <v>1000</v>
       </c>
       <c r="Z7">
-        <v>34</v>
+        <v>1000</v>
       </c>
       <c r="AA7">
-        <v>70</v>
+        <v>1000</v>
       </c>
       <c r="AB7">
-        <v>15.5</v>
+        <v>1000</v>
       </c>
       <c r="AC7">
-        <v>11</v>
+        <v>1000</v>
       </c>
       <c r="AD7">
-        <v>19</v>
+        <v>1000</v>
       </c>
       <c r="AE7">
-        <v>44</v>
+        <v>1000</v>
       </c>
       <c r="AF7">
-        <v>19.5</v>
+        <v>1000</v>
       </c>
       <c r="AG7">
-        <v>13.5</v>
+        <v>1000</v>
       </c>
       <c r="AH7">
-        <v>20</v>
+        <v>1000</v>
       </c>
       <c r="AI7">
-        <v>46</v>
+        <v>1000</v>
       </c>
       <c r="AJ7">
-        <v>36</v>
+        <v>1000</v>
       </c>
       <c r="AK7">
-        <v>26</v>
+        <v>1000</v>
       </c>
       <c r="AL7">
-        <v>40</v>
+        <v>1000</v>
       </c>
       <c r="AM7">
-        <v>75</v>
+        <v>1000</v>
       </c>
       <c r="AN7">
-        <v>14.5</v>
+        <v>1000</v>
       </c>
       <c r="AO7">
-        <v>30</v>
+        <v>1000</v>
       </c>
       <c r="AP7">
-        <v>18</v>
+        <v>1.01</v>
       </c>
       <c r="AQ7">
-        <v>14.5</v>
+        <v>1.01</v>
       </c>
       <c r="AR7">
-        <v>19</v>
+        <v>1.01</v>
       </c>
       <c r="AS7">
-        <v>5.8</v>
+        <v>1.01</v>
       </c>
       <c r="AT7">
-        <v>11</v>
+        <v>1.01</v>
       </c>
       <c r="AU7">
-        <v>8.199999999999999</v>
+        <v>1.01</v>
       </c>
       <c r="AV7">
-        <v>10.5</v>
+        <v>1.01</v>
       </c>
       <c r="AW7">
-        <v>5.3</v>
+        <v>1.01</v>
       </c>
       <c r="AX7">
-        <v>11.5</v>
+        <v>1.01</v>
       </c>
       <c r="AY7">
-        <v>10</v>
+        <v>1.01</v>
       </c>
       <c r="AZ7">
-        <v>11.5</v>
+        <v>1.01</v>
       </c>
       <c r="BA7">
-        <v>5.5</v>
+        <v>1.01</v>
       </c>
       <c r="BB7">
-        <v>20</v>
+        <v>1.01</v>
       </c>
       <c r="BC7">
-        <v>15.5</v>
+        <v>1.01</v>
       </c>
       <c r="BD7">
-        <v>5.2</v>
+        <v>1.01</v>
       </c>
       <c r="BE7">
-        <v>5.8</v>
+        <v>1.01</v>
       </c>
       <c r="BF7">
-        <v>11</v>
+        <v>1.01</v>
       </c>
       <c r="BG7">
-        <v>18.5</v>
+        <v>1.01</v>
       </c>
       <c r="BH7">
-        <v>4.1</v>
+        <v>1000</v>
       </c>
       <c r="BI7">
-        <v>3.65</v>
+        <v>1.04</v>
       </c>
       <c r="BJ7">
-        <v>8.800000000000001</v>
+        <v>1000</v>
       </c>
       <c r="BK7">
-        <v>5.4</v>
+        <v>1.04</v>
       </c>
       <c r="BL7">
         <v>1000</v>
       </c>
       <c r="BM7">
-        <v>12</v>
+        <v>1.04</v>
       </c>
       <c r="BN7">
-        <v>5.4</v>
+        <v>1000</v>
       </c>
       <c r="BO7">
-        <v>4.8</v>
+        <v>1.04</v>
       </c>
       <c r="BP7">
-        <v>15</v>
+        <v>1000</v>
       </c>
       <c r="BQ7">
-        <v>7.2</v>
+        <v>1.04</v>
       </c>
       <c r="BR7">
         <v>1000</v>
       </c>
       <c r="BS7">
-        <v>9</v>
+        <v>1.04</v>
       </c>
       <c r="BT7">
-        <v>7</v>
+        <v>1000</v>
       </c>
       <c r="BU7">
-        <v>6</v>
+        <v>1.04</v>
       </c>
       <c r="BV7">
-        <v>34</v>
+        <v>1000</v>
       </c>
       <c r="BW7">
-        <v>9</v>
+        <v>1.04</v>
       </c>
       <c r="BX7">
-        <v>46</v>
+        <v>1000</v>
       </c>
       <c r="BY7">
-        <v>9.800000000000001</v>
+        <v>1.04</v>
       </c>
       <c r="BZ7">
         <v>0</v>
@@ -2464,19 +2464,19 @@
         <v>124</v>
       </c>
       <c r="F8">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="G8">
         <v>990</v>
       </c>
       <c r="H8">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="I8">
         <v>990</v>
       </c>
       <c r="J8">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="K8">
         <v>950</v>
@@ -2497,13 +2497,13 @@
         <v>1.25</v>
       </c>
       <c r="Q8">
-        <v>1.59</v>
+        <v>1.58</v>
       </c>
       <c r="R8">
         <v>1.13</v>
       </c>
       <c r="S8">
-        <v>1.59</v>
+        <v>1.6</v>
       </c>
       <c r="T8">
         <v>1.11</v>
@@ -2572,52 +2572,52 @@
         <v>1000</v>
       </c>
       <c r="AP8">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AQ8">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AR8">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AS8">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AT8">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AU8">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AV8">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AW8">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AX8">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AY8">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AZ8">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BA8">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BB8">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BC8">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BD8">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BE8">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BF8">
         <v>1.01</v>
@@ -2706,19 +2706,19 @@
         <v>125</v>
       </c>
       <c r="F9">
-        <v>1.11</v>
+        <v>1.09</v>
       </c>
       <c r="G9">
         <v>990</v>
       </c>
       <c r="H9">
+        <v>1.13</v>
+      </c>
+      <c r="I9">
+        <v>1.85</v>
+      </c>
+      <c r="J9">
         <v>1.11</v>
-      </c>
-      <c r="I9">
-        <v>990</v>
-      </c>
-      <c r="J9">
-        <v>1.13</v>
       </c>
       <c r="K9">
         <v>950</v>
@@ -2730,22 +2730,22 @@
         <v>1.01</v>
       </c>
       <c r="N9">
-        <v>1.28</v>
+        <v>1.25</v>
       </c>
       <c r="O9">
         <v>1.35</v>
       </c>
       <c r="P9">
-        <v>1.28</v>
+        <v>1.25</v>
       </c>
       <c r="Q9">
         <v>1.34</v>
       </c>
       <c r="R9">
-        <v>1.35</v>
+        <v>1.26</v>
       </c>
       <c r="S9">
-        <v>1.39</v>
+        <v>4.7</v>
       </c>
       <c r="T9">
         <v>1.11</v>
@@ -2754,10 +2754,10 @@
         <v>1.11</v>
       </c>
       <c r="V9">
-        <v>1.11</v>
+        <v>2.16</v>
       </c>
       <c r="W9">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="X9">
         <v>1000</v>
@@ -2814,52 +2814,52 @@
         <v>1000</v>
       </c>
       <c r="AP9">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AQ9">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AR9">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AS9">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AT9">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AU9">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AV9">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AW9">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AX9">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AY9">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AZ9">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BA9">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BB9">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BC9">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BD9">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BE9">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BF9">
         <v>1.01</v>
@@ -2871,61 +2871,61 @@
         <v>1000</v>
       </c>
       <c r="BI9">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BJ9">
         <v>1000</v>
       </c>
       <c r="BK9">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BL9">
         <v>1000</v>
       </c>
       <c r="BM9">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BN9">
         <v>1000</v>
       </c>
       <c r="BO9">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BP9">
         <v>1000</v>
       </c>
       <c r="BQ9">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BR9">
         <v>1000</v>
       </c>
       <c r="BS9">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BT9">
         <v>1000</v>
       </c>
       <c r="BU9">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BV9">
         <v>1000</v>
       </c>
       <c r="BW9">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BX9">
         <v>1000</v>
       </c>
       <c r="BY9">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BZ9">
         <v>1000</v>
       </c>
       <c r="CA9">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="CB9" t="s">
         <v>134</v>
@@ -2948,19 +2948,19 @@
         <v>126</v>
       </c>
       <c r="F10">
-        <v>1.11</v>
+        <v>1.13</v>
       </c>
       <c r="G10">
         <v>990</v>
       </c>
       <c r="H10">
-        <v>1.13</v>
+        <v>1.19</v>
       </c>
       <c r="I10">
-        <v>990</v>
+        <v>870</v>
       </c>
       <c r="J10">
-        <v>1.13</v>
+        <v>1.18</v>
       </c>
       <c r="K10">
         <v>950</v>
@@ -3056,52 +3056,52 @@
         <v>1000</v>
       </c>
       <c r="AP10">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AQ10">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AR10">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AS10">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AT10">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AU10">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AV10">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AW10">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AX10">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AY10">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AZ10">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BA10">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BB10">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BC10">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BD10">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BE10">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BF10">
         <v>1.01</v>
@@ -3113,61 +3113,61 @@
         <v>1000</v>
       </c>
       <c r="BI10">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BJ10">
         <v>1000</v>
       </c>
       <c r="BK10">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BL10">
         <v>1000</v>
       </c>
       <c r="BM10">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BN10">
         <v>1000</v>
       </c>
       <c r="BO10">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BP10">
         <v>1000</v>
       </c>
       <c r="BQ10">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BR10">
         <v>1000</v>
       </c>
       <c r="BS10">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BT10">
         <v>1000</v>
       </c>
       <c r="BU10">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BV10">
         <v>1000</v>
       </c>
       <c r="BW10">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BX10">
         <v>1000</v>
       </c>
       <c r="BY10">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BZ10">
         <v>1000</v>
       </c>
       <c r="CA10">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="CB10" t="s">
         <v>134</v>
@@ -3190,19 +3190,19 @@
         <v>127</v>
       </c>
       <c r="F11">
-        <v>1.15</v>
+        <v>1.18</v>
       </c>
       <c r="G11">
         <v>990</v>
       </c>
       <c r="H11">
-        <v>1.17</v>
+        <v>1.19</v>
       </c>
       <c r="I11">
         <v>990</v>
       </c>
       <c r="J11">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="K11">
         <v>950</v>
@@ -3298,52 +3298,52 @@
         <v>1000</v>
       </c>
       <c r="AP11">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AQ11">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AR11">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AS11">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AT11">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AU11">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AV11">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AW11">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AX11">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AY11">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AZ11">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BA11">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BB11">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BC11">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BD11">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BE11">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BF11">
         <v>1.01</v>
@@ -3444,7 +3444,7 @@
         <v>990</v>
       </c>
       <c r="J12">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="K12">
         <v>950</v>
@@ -3459,19 +3459,19 @@
         <v>1.26</v>
       </c>
       <c r="O12">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="P12">
         <v>1.25</v>
       </c>
       <c r="Q12">
-        <v>1.45</v>
+        <v>1.38</v>
       </c>
       <c r="R12">
         <v>1.13</v>
       </c>
       <c r="S12">
-        <v>1.45</v>
+        <v>1.38</v>
       </c>
       <c r="T12">
         <v>1.11</v>
@@ -3540,52 +3540,52 @@
         <v>1000</v>
       </c>
       <c r="AP12">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AQ12">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AR12">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AS12">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AT12">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AU12">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AV12">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AW12">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AX12">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AY12">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AZ12">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BA12">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BB12">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BC12">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BD12">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BE12">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BF12">
         <v>1.01</v>
@@ -3597,61 +3597,61 @@
         <v>1000</v>
       </c>
       <c r="BI12">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BJ12">
         <v>1000</v>
       </c>
       <c r="BK12">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BL12">
         <v>1000</v>
       </c>
       <c r="BM12">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BN12">
         <v>1000</v>
       </c>
       <c r="BO12">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BP12">
         <v>1000</v>
       </c>
       <c r="BQ12">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BR12">
         <v>1000</v>
       </c>
       <c r="BS12">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BT12">
         <v>1000</v>
       </c>
       <c r="BU12">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BV12">
         <v>1000</v>
       </c>
       <c r="BW12">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BX12">
         <v>1000</v>
       </c>
       <c r="BY12">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BZ12">
         <v>1000</v>
       </c>
       <c r="CA12">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="CB12" t="s">
         <v>134</v>
@@ -3916,226 +3916,226 @@
         <v>130</v>
       </c>
       <c r="F14">
-        <v>2.82</v>
+        <v>1.4</v>
       </c>
       <c r="G14">
-        <v>3.1</v>
+        <v>600</v>
       </c>
       <c r="H14">
-        <v>2.66</v>
+        <v>2.76</v>
       </c>
       <c r="I14">
-        <v>2.9</v>
+        <v>1000</v>
       </c>
       <c r="J14">
-        <v>3.15</v>
+        <v>1.53</v>
       </c>
       <c r="K14">
-        <v>3.5</v>
+        <v>1000</v>
       </c>
       <c r="L14">
-        <v>1.38</v>
+        <v>1.01</v>
       </c>
       <c r="M14">
-        <v>1.09</v>
+        <v>1.05</v>
       </c>
       <c r="N14">
-        <v>3.15</v>
+        <v>1.1</v>
       </c>
       <c r="O14">
-        <v>1.39</v>
+        <v>1.33</v>
       </c>
       <c r="P14">
-        <v>1.74</v>
+        <v>1.51</v>
       </c>
       <c r="Q14">
-        <v>2.16</v>
+        <v>1.75</v>
       </c>
       <c r="R14">
-        <v>1.28</v>
+        <v>1.18</v>
       </c>
       <c r="S14">
-        <v>4</v>
+        <v>2.12</v>
       </c>
       <c r="T14">
-        <v>1.85</v>
+        <v>1.11</v>
       </c>
       <c r="U14">
-        <v>2.02</v>
+        <v>1.11</v>
       </c>
       <c r="V14">
-        <v>1.54</v>
+        <v>1.01</v>
       </c>
       <c r="W14">
-        <v>1.49</v>
+        <v>1.51</v>
       </c>
       <c r="X14">
-        <v>14</v>
+        <v>1000</v>
       </c>
       <c r="Y14">
-        <v>10.5</v>
+        <v>1000</v>
       </c>
       <c r="Z14">
-        <v>18</v>
+        <v>1000</v>
       </c>
       <c r="AA14">
-        <v>65</v>
+        <v>1000</v>
       </c>
       <c r="AB14">
-        <v>10.5</v>
+        <v>1000</v>
       </c>
       <c r="AC14">
-        <v>7.6</v>
+        <v>1000</v>
       </c>
       <c r="AD14">
-        <v>13</v>
+        <v>1000</v>
       </c>
       <c r="AE14">
-        <v>50</v>
+        <v>1000</v>
       </c>
       <c r="AF14">
-        <v>19.5</v>
+        <v>1000</v>
       </c>
       <c r="AG14">
-        <v>13.5</v>
+        <v>1000</v>
       </c>
       <c r="AH14">
-        <v>18.5</v>
+        <v>1000</v>
       </c>
       <c r="AI14">
-        <v>70</v>
+        <v>1000</v>
       </c>
       <c r="AJ14">
-        <v>70</v>
+        <v>1000</v>
       </c>
       <c r="AK14">
-        <v>38</v>
+        <v>1000</v>
       </c>
       <c r="AL14">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="AM14">
-        <v>140</v>
+        <v>1000</v>
       </c>
       <c r="AN14">
-        <v>38</v>
+        <v>1000</v>
       </c>
       <c r="AO14">
-        <v>34</v>
+        <v>1000</v>
       </c>
       <c r="AP14">
-        <v>8.6</v>
+        <v>1.01</v>
       </c>
       <c r="AQ14">
-        <v>8.800000000000001</v>
+        <v>1.01</v>
       </c>
       <c r="AR14">
-        <v>15.5</v>
+        <v>1.01</v>
       </c>
       <c r="AS14">
-        <v>29</v>
+        <v>1.01</v>
       </c>
       <c r="AT14">
-        <v>9.199999999999999</v>
+        <v>1.01</v>
       </c>
       <c r="AU14">
-        <v>6.6</v>
+        <v>1.01</v>
       </c>
       <c r="AV14">
-        <v>9.199999999999999</v>
+        <v>1.01</v>
       </c>
       <c r="AW14">
-        <v>8</v>
+        <v>1.01</v>
       </c>
       <c r="AX14">
-        <v>14</v>
+        <v>1.01</v>
       </c>
       <c r="AY14">
-        <v>11.5</v>
+        <v>1.01</v>
       </c>
       <c r="AZ14">
-        <v>16</v>
+        <v>1.01</v>
       </c>
       <c r="BA14">
-        <v>8.6</v>
+        <v>1.01</v>
       </c>
       <c r="BB14">
-        <v>29</v>
+        <v>1.01</v>
       </c>
       <c r="BC14">
-        <v>8.199999999999999</v>
+        <v>1.01</v>
       </c>
       <c r="BD14">
-        <v>8.800000000000001</v>
+        <v>1.01</v>
       </c>
       <c r="BE14">
-        <v>9.6</v>
+        <v>1.01</v>
       </c>
       <c r="BF14">
-        <v>8.199999999999999</v>
+        <v>1.01</v>
       </c>
       <c r="BG14">
-        <v>8</v>
+        <v>1.01</v>
       </c>
       <c r="BH14">
-        <v>3.15</v>
+        <v>1000</v>
       </c>
       <c r="BI14">
-        <v>2.6</v>
+        <v>1.04</v>
       </c>
       <c r="BJ14">
-        <v>10</v>
+        <v>1000</v>
       </c>
       <c r="BK14">
-        <v>6</v>
+        <v>1.04</v>
       </c>
       <c r="BL14">
         <v>1000</v>
       </c>
       <c r="BM14">
-        <v>13.5</v>
+        <v>1.04</v>
       </c>
       <c r="BN14">
-        <v>5.9</v>
+        <v>1000</v>
       </c>
       <c r="BO14">
-        <v>4.5</v>
+        <v>1.04</v>
       </c>
       <c r="BP14">
-        <v>24</v>
+        <v>1000</v>
       </c>
       <c r="BQ14">
-        <v>9.4</v>
+        <v>1.04</v>
       </c>
       <c r="BR14">
-        <v>40</v>
+        <v>1000</v>
       </c>
       <c r="BS14">
-        <v>11</v>
+        <v>1.04</v>
       </c>
       <c r="BT14">
-        <v>5.7</v>
+        <v>1000</v>
       </c>
       <c r="BU14">
-        <v>4.3</v>
+        <v>1.04</v>
       </c>
       <c r="BV14">
-        <v>23</v>
+        <v>1000</v>
       </c>
       <c r="BW14">
-        <v>9.199999999999999</v>
+        <v>1.04</v>
       </c>
       <c r="BX14">
         <v>1000</v>
       </c>
       <c r="BY14">
-        <v>10.5</v>
+        <v>1.04</v>
       </c>
       <c r="BZ14">
         <v>1000</v>
       </c>
       <c r="CA14">
-        <v>10.5</v>
+        <v>1.04</v>
       </c>
       <c r="CB14" t="s">
         <v>134</v>
@@ -4170,7 +4170,7 @@
         <v>990</v>
       </c>
       <c r="J15">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="K15">
         <v>950</v>
@@ -4185,19 +4185,19 @@
         <v>1.26</v>
       </c>
       <c r="O15">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="P15">
         <v>1.25</v>
       </c>
       <c r="Q15">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="R15">
         <v>1.13</v>
       </c>
       <c r="S15">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="T15">
         <v>1.11</v>
@@ -4266,52 +4266,52 @@
         <v>1000</v>
       </c>
       <c r="AP15">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AQ15">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AR15">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AS15">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AT15">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AU15">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AV15">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AW15">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AX15">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AY15">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AZ15">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BA15">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BB15">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BC15">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BD15">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BE15">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BF15">
         <v>1.01</v>
@@ -4323,55 +4323,55 @@
         <v>1000</v>
       </c>
       <c r="BI15">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BJ15">
         <v>1000</v>
       </c>
       <c r="BK15">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BL15">
         <v>1000</v>
       </c>
       <c r="BM15">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BN15">
         <v>1000</v>
       </c>
       <c r="BO15">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BP15">
         <v>1000</v>
       </c>
       <c r="BQ15">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BR15">
         <v>1000</v>
       </c>
       <c r="BS15">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BT15">
         <v>1000</v>
       </c>
       <c r="BU15">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BV15">
         <v>1000</v>
       </c>
       <c r="BW15">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BX15">
         <v>1000</v>
       </c>
       <c r="BY15">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BZ15">
         <v>0</v>
@@ -4400,19 +4400,19 @@
         <v>132</v>
       </c>
       <c r="F16">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="G16">
         <v>990</v>
       </c>
       <c r="H16">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="I16">
         <v>990</v>
       </c>
       <c r="J16">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="K16">
         <v>950</v>
@@ -4508,52 +4508,52 @@
         <v>1000</v>
       </c>
       <c r="AP16">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AQ16">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AR16">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AS16">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AT16">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AU16">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AV16">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AW16">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AX16">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AY16">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AZ16">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BA16">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BB16">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BC16">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BD16">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BE16">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BF16">
         <v>1.01</v>
@@ -4565,61 +4565,61 @@
         <v>1000</v>
       </c>
       <c r="BI16">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BJ16">
         <v>1000</v>
       </c>
       <c r="BK16">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BL16">
         <v>1000</v>
       </c>
       <c r="BM16">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BN16">
         <v>1000</v>
       </c>
       <c r="BO16">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BP16">
         <v>1000</v>
       </c>
       <c r="BQ16">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BR16">
         <v>1000</v>
       </c>
       <c r="BS16">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BT16">
         <v>1000</v>
       </c>
       <c r="BU16">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BV16">
         <v>1000</v>
       </c>
       <c r="BW16">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BX16">
         <v>1000</v>
       </c>
       <c r="BY16">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BZ16">
         <v>1000</v>
       </c>
       <c r="CA16">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="CB16" t="s">
         <v>134</v>
@@ -4645,16 +4645,16 @@
         <v>1.04</v>
       </c>
       <c r="G17">
-        <v>600</v>
+        <v>990</v>
       </c>
       <c r="H17">
         <v>1.04</v>
       </c>
       <c r="I17">
-        <v>870</v>
+        <v>990</v>
       </c>
       <c r="J17">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="K17">
         <v>950</v>
@@ -4666,28 +4666,28 @@
         <v>1.01</v>
       </c>
       <c r="N17">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="O17">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="P17">
         <v>1.25</v>
       </c>
       <c r="Q17">
-        <v>1.48</v>
+        <v>1.47</v>
       </c>
       <c r="R17">
         <v>1.13</v>
       </c>
       <c r="S17">
-        <v>1.48</v>
+        <v>1.47</v>
       </c>
       <c r="T17">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="U17">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="V17">
         <v>1.01</v>
@@ -4750,52 +4750,52 @@
         <v>1000</v>
       </c>
       <c r="AP17">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AQ17">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AR17">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AS17">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AT17">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AU17">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AV17">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AW17">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AX17">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AY17">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AZ17">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BA17">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BB17">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BC17">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BD17">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BE17">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BF17">
         <v>1.01</v>
@@ -4807,55 +4807,55 @@
         <v>1000</v>
       </c>
       <c r="BI17">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BJ17">
         <v>1000</v>
       </c>
       <c r="BK17">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BL17">
         <v>1000</v>
       </c>
       <c r="BM17">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BN17">
         <v>1000</v>
       </c>
       <c r="BO17">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BP17">
         <v>1000</v>
       </c>
       <c r="BQ17">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BR17">
         <v>1000</v>
       </c>
       <c r="BS17">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BT17">
         <v>1000</v>
       </c>
       <c r="BU17">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BV17">
         <v>1000</v>
       </c>
       <c r="BW17">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BX17">
         <v>1000</v>
       </c>
       <c r="BY17">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BZ17">
         <v>0</v>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-08-11.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-08-11.xlsx
@@ -418,7 +418,7 @@
     <t>Orsomarso</t>
   </si>
   <si>
-    <t>2026-08-10 08:12:44</t>
+    <t>2026-08-10 10:22:49</t>
   </si>
 </sst>
 </file>
@@ -1024,13 +1024,13 @@
         <v>1.38</v>
       </c>
       <c r="J2">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="K2">
-        <v>7.4</v>
+        <v>7.8</v>
       </c>
       <c r="L2">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="M2">
         <v>1.03</v>
@@ -1045,7 +1045,7 @@
         <v>2.28</v>
       </c>
       <c r="Q2">
-        <v>1.67</v>
+        <v>1.69</v>
       </c>
       <c r="R2">
         <v>1.52</v>
@@ -1120,7 +1120,7 @@
         <v>1000</v>
       </c>
       <c r="AP2">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AQ2">
         <v>1.01</v>
@@ -1132,28 +1132,28 @@
         <v>1.01</v>
       </c>
       <c r="AT2">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AU2">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AV2">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AW2">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AX2">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AY2">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AZ2">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BA2">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BB2">
         <v>1.01</v>
@@ -1162,16 +1162,16 @@
         <v>1.01</v>
       </c>
       <c r="BD2">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BE2">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BF2">
         <v>1.01</v>
       </c>
       <c r="BG2">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="BH2">
         <v>1000</v>
@@ -1266,13 +1266,13 @@
         <v>3.3</v>
       </c>
       <c r="J3">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="K3">
         <v>3.7</v>
       </c>
       <c r="L3">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="M3">
         <v>1.08</v>
@@ -1299,7 +1299,7 @@
         <v>1.85</v>
       </c>
       <c r="U3">
-        <v>2</v>
+        <v>2.04</v>
       </c>
       <c r="V3">
         <v>1.43</v>
@@ -1308,58 +1308,58 @@
         <v>1.68</v>
       </c>
       <c r="X3">
-        <v>15.5</v>
+        <v>14.5</v>
       </c>
       <c r="Y3">
         <v>13</v>
       </c>
       <c r="Z3">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="AA3">
-        <v>410</v>
+        <v>80</v>
       </c>
       <c r="AB3">
-        <v>10.5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AC3">
-        <v>7.8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AD3">
         <v>17</v>
       </c>
       <c r="AE3">
-        <v>95</v>
+        <v>50</v>
       </c>
       <c r="AF3">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="AG3">
         <v>13.5</v>
       </c>
       <c r="AH3">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="AI3">
-        <v>340</v>
+        <v>80</v>
       </c>
       <c r="AJ3">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="AK3">
-        <v>44</v>
+        <v>36</v>
       </c>
       <c r="AL3">
-        <v>140</v>
+        <v>65</v>
       </c>
       <c r="AM3">
         <v>1000</v>
       </c>
       <c r="AN3">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="AO3">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="AP3">
         <v>10.5</v>
@@ -1368,7 +1368,7 @@
         <v>9.4</v>
       </c>
       <c r="AR3">
-        <v>16.5</v>
+        <v>17.5</v>
       </c>
       <c r="AS3">
         <v>40</v>
@@ -1392,28 +1392,28 @@
         <v>9.4</v>
       </c>
       <c r="AZ3">
-        <v>14.5</v>
+        <v>16.5</v>
       </c>
       <c r="BA3">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="BB3">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="BC3">
-        <v>19.5</v>
+        <v>22</v>
       </c>
       <c r="BD3">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="BE3">
         <v>40</v>
       </c>
       <c r="BF3">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="BG3">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="BH3">
         <v>1000</v>
@@ -1496,22 +1496,22 @@
         <v>120</v>
       </c>
       <c r="F4">
-        <v>1.73</v>
+        <v>1.71</v>
       </c>
       <c r="G4">
-        <v>1.79</v>
+        <v>1.77</v>
       </c>
       <c r="H4">
-        <v>5.4</v>
+        <v>5.6</v>
       </c>
       <c r="I4">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="J4">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="K4">
-        <v>4</v>
+        <v>3.9</v>
       </c>
       <c r="L4">
         <v>1.49</v>
@@ -1526,28 +1526,28 @@
         <v>1.42</v>
       </c>
       <c r="P4">
-        <v>1.73</v>
+        <v>1.72</v>
       </c>
       <c r="Q4">
-        <v>2.24</v>
+        <v>2.26</v>
       </c>
       <c r="R4">
         <v>1.26</v>
       </c>
       <c r="S4">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="T4">
         <v>1.11</v>
       </c>
       <c r="U4">
-        <v>1.11</v>
+        <v>1.75</v>
       </c>
       <c r="V4">
         <v>1.18</v>
       </c>
       <c r="W4">
-        <v>2.24</v>
+        <v>2.28</v>
       </c>
       <c r="X4">
         <v>1000</v>
@@ -1652,7 +1652,7 @@
         <v>1.01</v>
       </c>
       <c r="BF4">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="BG4">
         <v>1.01</v>
@@ -1673,7 +1673,7 @@
         <v>1000</v>
       </c>
       <c r="BM4">
-        <v>1.04</v>
+        <v>7.6</v>
       </c>
       <c r="BN4">
         <v>1000</v>
@@ -1741,19 +1741,19 @@
         <v>1.56</v>
       </c>
       <c r="G5">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="H5">
         <v>6.6</v>
       </c>
       <c r="I5">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="J5">
         <v>4</v>
       </c>
       <c r="K5">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="L5">
         <v>1.46</v>
@@ -1762,85 +1762,85 @@
         <v>1.08</v>
       </c>
       <c r="N5">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="O5">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="P5">
-        <v>1.8</v>
+        <v>1.79</v>
       </c>
       <c r="Q5">
-        <v>2.2</v>
+        <v>2.22</v>
       </c>
       <c r="R5">
         <v>1.29</v>
       </c>
       <c r="S5">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="T5">
-        <v>2.18</v>
+        <v>2.22</v>
       </c>
       <c r="U5">
-        <v>1.72</v>
+        <v>1.71</v>
       </c>
       <c r="V5">
         <v>1.14</v>
       </c>
       <c r="W5">
-        <v>2.62</v>
+        <v>2.6</v>
       </c>
       <c r="X5">
-        <v>15.5</v>
+        <v>13.5</v>
       </c>
       <c r="Y5">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="Z5">
-        <v>330</v>
+        <v>70</v>
       </c>
       <c r="AA5">
         <v>1000</v>
       </c>
       <c r="AB5">
-        <v>7.4</v>
+        <v>6.6</v>
       </c>
       <c r="AC5">
         <v>9.800000000000001</v>
       </c>
       <c r="AD5">
+        <v>32</v>
+      </c>
+      <c r="AE5">
+        <v>160</v>
+      </c>
+      <c r="AF5">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AG5">
+        <v>10.5</v>
+      </c>
+      <c r="AH5">
+        <v>30</v>
+      </c>
+      <c r="AI5">
+        <v>150</v>
+      </c>
+      <c r="AJ5">
+        <v>15.5</v>
+      </c>
+      <c r="AK5">
+        <v>20</v>
+      </c>
+      <c r="AL5">
         <v>50</v>
       </c>
-      <c r="AE5">
-        <v>1000</v>
-      </c>
-      <c r="AF5">
-        <v>8.6</v>
-      </c>
-      <c r="AG5">
-        <v>11</v>
-      </c>
-      <c r="AH5">
-        <v>50</v>
-      </c>
-      <c r="AI5">
-        <v>1000</v>
-      </c>
-      <c r="AJ5">
-        <v>14.5</v>
-      </c>
-      <c r="AK5">
-        <v>19.5</v>
-      </c>
-      <c r="AL5">
-        <v>240</v>
-      </c>
       <c r="AM5">
         <v>1000</v>
       </c>
       <c r="AN5">
-        <v>10.5</v>
+        <v>12</v>
       </c>
       <c r="AO5">
         <v>1000</v>
@@ -1849,7 +1849,7 @@
         <v>10.5</v>
       </c>
       <c r="AQ5">
-        <v>14.5</v>
+        <v>17</v>
       </c>
       <c r="AR5">
         <v>40</v>
@@ -1858,34 +1858,34 @@
         <v>48</v>
       </c>
       <c r="AT5">
-        <v>6.2</v>
+        <v>5.9</v>
       </c>
       <c r="AU5">
-        <v>8</v>
+        <v>8.4</v>
       </c>
       <c r="AV5">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="AW5">
         <v>42</v>
       </c>
       <c r="AX5">
-        <v>6.8</v>
+        <v>7.2</v>
       </c>
       <c r="AY5">
-        <v>8.800000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AZ5">
-        <v>19.5</v>
+        <v>22</v>
       </c>
       <c r="BA5">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="BB5">
-        <v>11</v>
+        <v>12.5</v>
       </c>
       <c r="BC5">
-        <v>14</v>
+        <v>16.5</v>
       </c>
       <c r="BD5">
         <v>34</v>
@@ -1894,7 +1894,7 @@
         <v>48</v>
       </c>
       <c r="BF5">
-        <v>8.6</v>
+        <v>10</v>
       </c>
       <c r="BG5">
         <v>48</v>
@@ -1980,22 +1980,22 @@
         <v>122</v>
       </c>
       <c r="F6">
+        <v>1.34</v>
+      </c>
+      <c r="G6">
         <v>1.35</v>
       </c>
-      <c r="G6">
-        <v>1.38</v>
-      </c>
       <c r="H6">
-        <v>9</v>
+        <v>10.5</v>
       </c>
       <c r="I6">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="J6">
-        <v>5.1</v>
+        <v>5.4</v>
       </c>
       <c r="K6">
-        <v>6</v>
+        <v>5.8</v>
       </c>
       <c r="L6">
         <v>1.36</v>
@@ -2013,25 +2013,25 @@
         <v>2.16</v>
       </c>
       <c r="Q6">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="R6">
         <v>1.44</v>
       </c>
       <c r="S6">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="T6">
-        <v>2.16</v>
+        <v>2.18</v>
       </c>
       <c r="U6">
-        <v>1.39</v>
+        <v>1.65</v>
       </c>
       <c r="V6">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="W6">
-        <v>3.55</v>
+        <v>3.85</v>
       </c>
       <c r="X6">
         <v>1000</v>
@@ -2049,7 +2049,7 @@
         <v>1000</v>
       </c>
       <c r="AC6">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AD6">
         <v>1000</v>
@@ -2073,7 +2073,7 @@
         <v>1000</v>
       </c>
       <c r="AK6">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AL6">
         <v>1000</v>
@@ -2088,58 +2088,58 @@
         <v>1000</v>
       </c>
       <c r="AP6">
-        <v>1.01</v>
+        <v>1.13</v>
       </c>
       <c r="AQ6">
-        <v>1.01</v>
+        <v>1.13</v>
       </c>
       <c r="AR6">
-        <v>1.01</v>
+        <v>1.14</v>
       </c>
       <c r="AS6">
-        <v>1.01</v>
+        <v>1.14</v>
       </c>
       <c r="AT6">
-        <v>1.01</v>
+        <v>1.13</v>
       </c>
       <c r="AU6">
-        <v>1.01</v>
+        <v>1.06</v>
       </c>
       <c r="AV6">
-        <v>1.01</v>
+        <v>1.13</v>
       </c>
       <c r="AW6">
-        <v>1.01</v>
+        <v>1.14</v>
       </c>
       <c r="AX6">
-        <v>1.01</v>
+        <v>1.13</v>
       </c>
       <c r="AY6">
-        <v>1.01</v>
+        <v>1.13</v>
       </c>
       <c r="AZ6">
-        <v>1.01</v>
+        <v>1.13</v>
       </c>
       <c r="BA6">
-        <v>1.01</v>
+        <v>1.14</v>
       </c>
       <c r="BB6">
-        <v>1.01</v>
+        <v>1.13</v>
       </c>
       <c r="BC6">
-        <v>1.01</v>
+        <v>1.3</v>
       </c>
       <c r="BD6">
-        <v>1.01</v>
+        <v>1.14</v>
       </c>
       <c r="BE6">
-        <v>1.01</v>
+        <v>1.14</v>
       </c>
       <c r="BF6">
-        <v>1.01</v>
+        <v>1.13</v>
       </c>
       <c r="BG6">
-        <v>1.01</v>
+        <v>1.14</v>
       </c>
       <c r="BH6">
         <v>1000</v>
@@ -2222,22 +2222,22 @@
         <v>123</v>
       </c>
       <c r="F7">
-        <v>2.1</v>
+        <v>2.14</v>
       </c>
       <c r="G7">
-        <v>110</v>
+        <v>2.28</v>
       </c>
       <c r="H7">
-        <v>1.35</v>
+        <v>3.25</v>
       </c>
       <c r="I7">
-        <v>870</v>
+        <v>3.55</v>
       </c>
       <c r="J7">
-        <v>1.41</v>
+        <v>3.15</v>
       </c>
       <c r="K7">
-        <v>500</v>
+        <v>4.9</v>
       </c>
       <c r="L7">
         <v>1.33</v>
@@ -2249,19 +2249,19 @@
         <v>5.2</v>
       </c>
       <c r="O7">
-        <v>1.19</v>
+        <v>1.22</v>
       </c>
       <c r="P7">
-        <v>1.27</v>
+        <v>2.36</v>
       </c>
       <c r="Q7">
-        <v>1.01</v>
+        <v>1.45</v>
       </c>
       <c r="R7">
-        <v>1.27</v>
+        <v>1.55</v>
       </c>
       <c r="S7">
-        <v>1.98</v>
+        <v>2.56</v>
       </c>
       <c r="T7">
         <v>1.25</v>
@@ -2270,10 +2270,10 @@
         <v>2.02</v>
       </c>
       <c r="V7">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="W7">
-        <v>1.73</v>
+        <v>1.8</v>
       </c>
       <c r="X7">
         <v>1000</v>
@@ -2282,160 +2282,160 @@
         <v>1000</v>
       </c>
       <c r="Z7">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="AA7">
         <v>1000</v>
       </c>
       <c r="AB7">
-        <v>1000</v>
+        <v>13.5</v>
       </c>
       <c r="AC7">
-        <v>1000</v>
+        <v>9.4</v>
       </c>
       <c r="AD7">
-        <v>1000</v>
+        <v>15</v>
       </c>
       <c r="AE7">
-        <v>1000</v>
+        <v>44</v>
       </c>
       <c r="AF7">
-        <v>1000</v>
+        <v>17</v>
       </c>
       <c r="AG7">
         <v>1000</v>
       </c>
       <c r="AH7">
-        <v>1000</v>
+        <v>15.5</v>
       </c>
       <c r="AI7">
         <v>1000</v>
       </c>
       <c r="AJ7">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="AK7">
         <v>1000</v>
       </c>
       <c r="AL7">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="AM7">
-        <v>1000</v>
+        <v>80</v>
       </c>
       <c r="AN7">
-        <v>1000</v>
+        <v>14.5</v>
       </c>
       <c r="AO7">
-        <v>1000</v>
+        <v>30</v>
       </c>
       <c r="AP7">
-        <v>1.01</v>
+        <v>2.68</v>
       </c>
       <c r="AQ7">
-        <v>1.01</v>
+        <v>15</v>
       </c>
       <c r="AR7">
-        <v>1.01</v>
+        <v>2.44</v>
       </c>
       <c r="AS7">
-        <v>1.01</v>
+        <v>2.7</v>
       </c>
       <c r="AT7">
-        <v>1.01</v>
+        <v>11.5</v>
       </c>
       <c r="AU7">
-        <v>1.01</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AV7">
-        <v>1.01</v>
+        <v>12.5</v>
       </c>
       <c r="AW7">
-        <v>1.01</v>
+        <v>2.5</v>
       </c>
       <c r="AX7">
-        <v>1.01</v>
+        <v>14.5</v>
       </c>
       <c r="AY7">
-        <v>1.01</v>
+        <v>10</v>
       </c>
       <c r="AZ7">
-        <v>1.01</v>
+        <v>13.5</v>
       </c>
       <c r="BA7">
-        <v>1.01</v>
+        <v>2.7</v>
       </c>
       <c r="BB7">
-        <v>1.01</v>
+        <v>2.46</v>
       </c>
       <c r="BC7">
-        <v>1.01</v>
+        <v>2.7</v>
       </c>
       <c r="BD7">
-        <v>1.01</v>
+        <v>2.46</v>
       </c>
       <c r="BE7">
-        <v>1.01</v>
+        <v>2.58</v>
       </c>
       <c r="BF7">
-        <v>1.01</v>
+        <v>10</v>
       </c>
       <c r="BG7">
-        <v>1.01</v>
+        <v>18</v>
       </c>
       <c r="BH7">
-        <v>1000</v>
+        <v>4.1</v>
       </c>
       <c r="BI7">
-        <v>1.04</v>
+        <v>3.65</v>
       </c>
       <c r="BJ7">
-        <v>1000</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BK7">
-        <v>1.04</v>
+        <v>5.4</v>
       </c>
       <c r="BL7">
         <v>1000</v>
       </c>
       <c r="BM7">
-        <v>1.04</v>
+        <v>12</v>
       </c>
       <c r="BN7">
-        <v>1000</v>
+        <v>5.4</v>
       </c>
       <c r="BO7">
-        <v>1.04</v>
+        <v>4.8</v>
       </c>
       <c r="BP7">
-        <v>1000</v>
+        <v>15</v>
       </c>
       <c r="BQ7">
-        <v>1.04</v>
+        <v>7.2</v>
       </c>
       <c r="BR7">
         <v>1000</v>
       </c>
       <c r="BS7">
-        <v>1.04</v>
+        <v>9</v>
       </c>
       <c r="BT7">
-        <v>1000</v>
+        <v>7</v>
       </c>
       <c r="BU7">
-        <v>1.04</v>
+        <v>6</v>
       </c>
       <c r="BV7">
         <v>1000</v>
       </c>
       <c r="BW7">
-        <v>1.04</v>
+        <v>9</v>
       </c>
       <c r="BX7">
         <v>1000</v>
       </c>
       <c r="BY7">
-        <v>1.04</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BZ7">
         <v>0</v>
@@ -2464,19 +2464,19 @@
         <v>124</v>
       </c>
       <c r="F8">
-        <v>1.05</v>
+        <v>1.08</v>
       </c>
       <c r="G8">
         <v>990</v>
       </c>
       <c r="H8">
-        <v>1.05</v>
+        <v>1.08</v>
       </c>
       <c r="I8">
         <v>990</v>
       </c>
       <c r="J8">
-        <v>1.08</v>
+        <v>1.12</v>
       </c>
       <c r="K8">
         <v>950</v>
@@ -2503,7 +2503,7 @@
         <v>1.13</v>
       </c>
       <c r="S8">
-        <v>1.6</v>
+        <v>1.59</v>
       </c>
       <c r="T8">
         <v>1.11</v>
@@ -2706,19 +2706,19 @@
         <v>125</v>
       </c>
       <c r="F9">
-        <v>1.09</v>
+        <v>2.26</v>
       </c>
       <c r="G9">
         <v>990</v>
       </c>
       <c r="H9">
-        <v>1.13</v>
+        <v>1.15</v>
       </c>
       <c r="I9">
         <v>1.85</v>
       </c>
       <c r="J9">
-        <v>1.11</v>
+        <v>1.13</v>
       </c>
       <c r="K9">
         <v>950</v>
@@ -2730,7 +2730,7 @@
         <v>1.01</v>
       </c>
       <c r="N9">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="O9">
         <v>1.35</v>
@@ -2739,13 +2739,13 @@
         <v>1.25</v>
       </c>
       <c r="Q9">
-        <v>1.34</v>
+        <v>1.01</v>
       </c>
       <c r="R9">
-        <v>1.26</v>
+        <v>1.13</v>
       </c>
       <c r="S9">
-        <v>4.7</v>
+        <v>1.39</v>
       </c>
       <c r="T9">
         <v>1.11</v>
@@ -2757,7 +2757,7 @@
         <v>2.16</v>
       </c>
       <c r="W9">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="X9">
         <v>1000</v>
@@ -2948,19 +2948,19 @@
         <v>126</v>
       </c>
       <c r="F10">
-        <v>1.13</v>
+        <v>1.15</v>
       </c>
       <c r="G10">
         <v>990</v>
       </c>
       <c r="H10">
-        <v>1.19</v>
+        <v>1.21</v>
       </c>
       <c r="I10">
         <v>870</v>
       </c>
       <c r="J10">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="K10">
         <v>950</v>
@@ -3190,19 +3190,19 @@
         <v>127</v>
       </c>
       <c r="F11">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="G11">
         <v>990</v>
       </c>
       <c r="H11">
-        <v>1.19</v>
+        <v>1.21</v>
       </c>
       <c r="I11">
         <v>990</v>
       </c>
       <c r="J11">
-        <v>1.22</v>
+        <v>1.27</v>
       </c>
       <c r="K11">
         <v>950</v>
@@ -3214,7 +3214,7 @@
         <v>1.01</v>
       </c>
       <c r="N11">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="O11">
         <v>1.02</v>
@@ -3432,7 +3432,7 @@
         <v>128</v>
       </c>
       <c r="F12">
-        <v>1.04</v>
+        <v>1.69</v>
       </c>
       <c r="G12">
         <v>990</v>
@@ -3444,7 +3444,7 @@
         <v>990</v>
       </c>
       <c r="J12">
-        <v>1.04</v>
+        <v>1.08</v>
       </c>
       <c r="K12">
         <v>950</v>
@@ -3456,22 +3456,22 @@
         <v>1.01</v>
       </c>
       <c r="N12">
-        <v>1.26</v>
+        <v>2.72</v>
       </c>
       <c r="O12">
-        <v>1.02</v>
+        <v>1.37</v>
       </c>
       <c r="P12">
-        <v>1.25</v>
+        <v>1.46</v>
       </c>
       <c r="Q12">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="R12">
         <v>1.13</v>
       </c>
       <c r="S12">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="T12">
         <v>1.11</v>
@@ -3480,7 +3480,7 @@
         <v>1.11</v>
       </c>
       <c r="V12">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="W12">
         <v>1.01</v>
@@ -3704,10 +3704,10 @@
         <v>0</v>
       </c>
       <c r="P13">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="Q13">
-        <v>1.01</v>
+        <v>1.9</v>
       </c>
       <c r="R13">
         <v>0</v>
@@ -3916,37 +3916,37 @@
         <v>130</v>
       </c>
       <c r="F14">
-        <v>1.4</v>
+        <v>1.43</v>
       </c>
       <c r="G14">
-        <v>600</v>
+        <v>1000</v>
       </c>
       <c r="H14">
-        <v>2.76</v>
+        <v>2.78</v>
       </c>
       <c r="I14">
         <v>1000</v>
       </c>
       <c r="J14">
-        <v>1.53</v>
+        <v>1.55</v>
       </c>
       <c r="K14">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="L14">
-        <v>1.01</v>
+        <v>1.46</v>
       </c>
       <c r="M14">
-        <v>1.05</v>
+        <v>1.08</v>
       </c>
       <c r="N14">
-        <v>1.1</v>
+        <v>3.2</v>
       </c>
       <c r="O14">
-        <v>1.33</v>
+        <v>1.39</v>
       </c>
       <c r="P14">
-        <v>1.51</v>
+        <v>1.52</v>
       </c>
       <c r="Q14">
         <v>1.75</v>
@@ -3958,16 +3958,16 @@
         <v>2.12</v>
       </c>
       <c r="T14">
-        <v>1.11</v>
+        <v>1.8</v>
       </c>
       <c r="U14">
-        <v>1.11</v>
+        <v>2.02</v>
       </c>
       <c r="V14">
-        <v>1.01</v>
+        <v>1.48</v>
       </c>
       <c r="W14">
-        <v>1.51</v>
+        <v>1.03</v>
       </c>
       <c r="X14">
         <v>1000</v>
@@ -4158,22 +4158,22 @@
         <v>131</v>
       </c>
       <c r="F15">
-        <v>1.04</v>
+        <v>1.52</v>
       </c>
       <c r="G15">
-        <v>990</v>
+        <v>1.68</v>
       </c>
       <c r="H15">
-        <v>1.04</v>
+        <v>6.8</v>
       </c>
       <c r="I15">
-        <v>990</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="J15">
-        <v>1.04</v>
+        <v>3.9</v>
       </c>
       <c r="K15">
-        <v>950</v>
+        <v>4.6</v>
       </c>
       <c r="L15">
         <v>1.01</v>
@@ -4182,22 +4182,22 @@
         <v>1.01</v>
       </c>
       <c r="N15">
-        <v>1.26</v>
+        <v>2.8</v>
       </c>
       <c r="O15">
         <v>1.33</v>
       </c>
       <c r="P15">
-        <v>1.25</v>
+        <v>1.77</v>
       </c>
       <c r="Q15">
-        <v>1.33</v>
+        <v>1.98</v>
       </c>
       <c r="R15">
-        <v>1.13</v>
+        <v>1.24</v>
       </c>
       <c r="S15">
-        <v>1.33</v>
+        <v>3.05</v>
       </c>
       <c r="T15">
         <v>1.11</v>
@@ -4206,10 +4206,10 @@
         <v>1.11</v>
       </c>
       <c r="V15">
-        <v>1.01</v>
+        <v>1.12</v>
       </c>
       <c r="W15">
-        <v>1.01</v>
+        <v>2.42</v>
       </c>
       <c r="X15">
         <v>1000</v>
@@ -4320,13 +4320,13 @@
         <v>1.01</v>
       </c>
       <c r="BH15">
-        <v>1000</v>
+        <v>3.45</v>
       </c>
       <c r="BI15">
-        <v>1.04</v>
+        <v>2.76</v>
       </c>
       <c r="BJ15">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="BK15">
         <v>1.04</v>
@@ -4338,13 +4338,13 @@
         <v>1.04</v>
       </c>
       <c r="BN15">
-        <v>1000</v>
+        <v>4.1</v>
       </c>
       <c r="BO15">
-        <v>1.04</v>
+        <v>3.2</v>
       </c>
       <c r="BP15">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="BQ15">
         <v>1.04</v>
@@ -4356,7 +4356,7 @@
         <v>1.04</v>
       </c>
       <c r="BT15">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="BU15">
         <v>1.04</v>
@@ -4400,19 +4400,19 @@
         <v>132</v>
       </c>
       <c r="F16">
-        <v>1.05</v>
+        <v>1.09</v>
       </c>
       <c r="G16">
-        <v>990</v>
+        <v>2.56</v>
       </c>
       <c r="H16">
-        <v>1.05</v>
+        <v>2.34</v>
       </c>
       <c r="I16">
         <v>990</v>
       </c>
       <c r="J16">
-        <v>1.08</v>
+        <v>3.2</v>
       </c>
       <c r="K16">
         <v>950</v>
@@ -4424,22 +4424,22 @@
         <v>1.01</v>
       </c>
       <c r="N16">
-        <v>1.26</v>
+        <v>3.05</v>
       </c>
       <c r="O16">
-        <v>1.02</v>
+        <v>1.37</v>
       </c>
       <c r="P16">
-        <v>1.25</v>
+        <v>1.73</v>
       </c>
       <c r="Q16">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="R16">
         <v>1.18</v>
       </c>
       <c r="S16">
-        <v>1.39</v>
+        <v>1.98</v>
       </c>
       <c r="T16">
         <v>1.11</v>
@@ -4448,10 +4448,10 @@
         <v>1.11</v>
       </c>
       <c r="V16">
-        <v>1.02</v>
+        <v>1.07</v>
       </c>
       <c r="W16">
-        <v>1.02</v>
+        <v>1.64</v>
       </c>
       <c r="X16">
         <v>1000</v>
@@ -4642,31 +4642,31 @@
         <v>133</v>
       </c>
       <c r="F17">
-        <v>1.04</v>
+        <v>1.65</v>
       </c>
       <c r="G17">
-        <v>990</v>
+        <v>1.83</v>
       </c>
       <c r="H17">
-        <v>1.04</v>
+        <v>5.9</v>
       </c>
       <c r="I17">
-        <v>990</v>
+        <v>8</v>
       </c>
       <c r="J17">
-        <v>1.04</v>
+        <v>3.2</v>
       </c>
       <c r="K17">
-        <v>950</v>
+        <v>4.1</v>
       </c>
       <c r="L17">
-        <v>1.01</v>
+        <v>1.42</v>
       </c>
       <c r="M17">
         <v>1.01</v>
       </c>
       <c r="N17">
-        <v>1.25</v>
+        <v>2.4</v>
       </c>
       <c r="O17">
         <v>1.02</v>
@@ -4675,13 +4675,13 @@
         <v>1.25</v>
       </c>
       <c r="Q17">
-        <v>1.47</v>
+        <v>2</v>
       </c>
       <c r="R17">
         <v>1.13</v>
       </c>
       <c r="S17">
-        <v>1.47</v>
+        <v>4.2</v>
       </c>
       <c r="T17">
         <v>1.11</v>
@@ -4690,16 +4690,16 @@
         <v>1.11</v>
       </c>
       <c r="V17">
-        <v>1.01</v>
+        <v>1.14</v>
       </c>
       <c r="W17">
-        <v>1.01</v>
+        <v>2.2</v>
       </c>
       <c r="X17">
         <v>1000</v>
       </c>
       <c r="Y17">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="Z17">
         <v>1000</v>
@@ -4738,7 +4738,7 @@
         <v>1000</v>
       </c>
       <c r="AL17">
-        <v>1000</v>
+        <v>70</v>
       </c>
       <c r="AM17">
         <v>1000</v>
@@ -4750,10 +4750,10 @@
         <v>1000</v>
       </c>
       <c r="AP17">
-        <v>1.01</v>
+        <v>8.6</v>
       </c>
       <c r="AQ17">
-        <v>1.01</v>
+        <v>13</v>
       </c>
       <c r="AR17">
         <v>1.01</v>
@@ -4762,34 +4762,34 @@
         <v>1.01</v>
       </c>
       <c r="AT17">
-        <v>1.01</v>
+        <v>5.3</v>
       </c>
       <c r="AU17">
-        <v>1.01</v>
+        <v>6.6</v>
       </c>
       <c r="AV17">
-        <v>1.01</v>
+        <v>19.5</v>
       </c>
       <c r="AW17">
         <v>1.01</v>
       </c>
       <c r="AX17">
-        <v>1.01</v>
+        <v>7.2</v>
       </c>
       <c r="AY17">
-        <v>1.01</v>
+        <v>8</v>
       </c>
       <c r="AZ17">
-        <v>1.01</v>
+        <v>19</v>
       </c>
       <c r="BA17">
         <v>1.01</v>
       </c>
       <c r="BB17">
-        <v>1.01</v>
+        <v>13.5</v>
       </c>
       <c r="BC17">
-        <v>1.01</v>
+        <v>16</v>
       </c>
       <c r="BD17">
         <v>1.01</v>
@@ -4798,19 +4798,19 @@
         <v>1.01</v>
       </c>
       <c r="BF17">
-        <v>1.01</v>
+        <v>11</v>
       </c>
       <c r="BG17">
         <v>1.01</v>
       </c>
       <c r="BH17">
-        <v>1000</v>
+        <v>3.15</v>
       </c>
       <c r="BI17">
-        <v>1.04</v>
+        <v>2.54</v>
       </c>
       <c r="BJ17">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="BK17">
         <v>1.04</v>
@@ -4822,13 +4822,13 @@
         <v>1.04</v>
       </c>
       <c r="BN17">
-        <v>1000</v>
+        <v>4.2</v>
       </c>
       <c r="BO17">
-        <v>1.04</v>
+        <v>3.3</v>
       </c>
       <c r="BP17">
-        <v>1000</v>
+        <v>13</v>
       </c>
       <c r="BQ17">
         <v>1.04</v>
@@ -4840,7 +4840,7 @@
         <v>1.04</v>
       </c>
       <c r="BT17">
-        <v>1000</v>
+        <v>10</v>
       </c>
       <c r="BU17">
         <v>1.04</v>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-08-11.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-08-11.xlsx
@@ -418,7 +418,7 @@
     <t>Orsomarso</t>
   </si>
   <si>
-    <t>2026-08-10 10:22:49</t>
+    <t>2026-08-10 12:32:55</t>
   </si>
 </sst>
 </file>
@@ -1015,10 +1015,10 @@
         <v>8</v>
       </c>
       <c r="G2">
-        <v>1000</v>
+        <v>990</v>
       </c>
       <c r="H2">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="I2">
         <v>1.38</v>
@@ -1027,40 +1027,40 @@
         <v>4.5</v>
       </c>
       <c r="K2">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="L2">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="M2">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="N2">
-        <v>2.28</v>
+        <v>4.4</v>
       </c>
       <c r="O2">
         <v>1.25</v>
       </c>
       <c r="P2">
-        <v>2.28</v>
+        <v>2.22</v>
       </c>
       <c r="Q2">
         <v>1.69</v>
       </c>
       <c r="R2">
-        <v>1.52</v>
+        <v>1.49</v>
       </c>
       <c r="S2">
-        <v>2.56</v>
+        <v>2.66</v>
       </c>
       <c r="T2">
         <v>1.66</v>
       </c>
       <c r="U2">
-        <v>1.47</v>
+        <v>1.49</v>
       </c>
       <c r="V2">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="W2">
         <v>1.05</v>
@@ -1290,16 +1290,16 @@
         <v>2.16</v>
       </c>
       <c r="R3">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="S3">
         <v>4</v>
       </c>
       <c r="T3">
-        <v>1.85</v>
+        <v>1.86</v>
       </c>
       <c r="U3">
-        <v>2.04</v>
+        <v>2.06</v>
       </c>
       <c r="V3">
         <v>1.43</v>
@@ -1308,103 +1308,103 @@
         <v>1.68</v>
       </c>
       <c r="X3">
-        <v>14.5</v>
+        <v>13</v>
       </c>
       <c r="Y3">
-        <v>13</v>
+        <v>11.5</v>
       </c>
       <c r="Z3">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="AA3">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="AB3">
-        <v>9.800000000000001</v>
+        <v>9.4</v>
       </c>
       <c r="AC3">
-        <v>8.199999999999999</v>
+        <v>7.8</v>
       </c>
       <c r="AD3">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="AE3">
         <v>50</v>
       </c>
       <c r="AF3">
+        <v>15</v>
+      </c>
+      <c r="AG3">
+        <v>11.5</v>
+      </c>
+      <c r="AH3">
+        <v>23</v>
+      </c>
+      <c r="AI3">
+        <v>70</v>
+      </c>
+      <c r="AJ3">
+        <v>38</v>
+      </c>
+      <c r="AK3">
+        <v>32</v>
+      </c>
+      <c r="AL3">
+        <v>50</v>
+      </c>
+      <c r="AM3">
+        <v>1000</v>
+      </c>
+      <c r="AN3">
+        <v>28</v>
+      </c>
+      <c r="AO3">
+        <v>48</v>
+      </c>
+      <c r="AP3">
+        <v>11.5</v>
+      </c>
+      <c r="AQ3">
+        <v>10</v>
+      </c>
+      <c r="AR3">
         <v>17</v>
       </c>
-      <c r="AG3">
+      <c r="AS3">
+        <v>44</v>
+      </c>
+      <c r="AT3">
+        <v>8.4</v>
+      </c>
+      <c r="AU3">
+        <v>7.2</v>
+      </c>
+      <c r="AV3">
+        <v>12</v>
+      </c>
+      <c r="AW3">
+        <v>28</v>
+      </c>
+      <c r="AX3">
         <v>13.5</v>
       </c>
-      <c r="AH3">
-        <v>24</v>
-      </c>
-      <c r="AI3">
-        <v>80</v>
-      </c>
-      <c r="AJ3">
-        <v>42</v>
-      </c>
-      <c r="AK3">
-        <v>36</v>
-      </c>
-      <c r="AL3">
-        <v>65</v>
-      </c>
-      <c r="AM3">
-        <v>1000</v>
-      </c>
-      <c r="AN3">
-        <v>30</v>
-      </c>
-      <c r="AO3">
-        <v>50</v>
-      </c>
-      <c r="AP3">
-        <v>10.5</v>
-      </c>
-      <c r="AQ3">
-        <v>9.4</v>
-      </c>
-      <c r="AR3">
-        <v>17.5</v>
-      </c>
-      <c r="AS3">
-        <v>40</v>
-      </c>
-      <c r="AT3">
-        <v>8</v>
-      </c>
-      <c r="AU3">
-        <v>6.6</v>
-      </c>
-      <c r="AV3">
-        <v>11</v>
-      </c>
-      <c r="AW3">
-        <v>29</v>
-      </c>
-      <c r="AX3">
-        <v>11.5</v>
-      </c>
       <c r="AY3">
-        <v>9.4</v>
+        <v>10</v>
       </c>
       <c r="AZ3">
         <v>16.5</v>
       </c>
       <c r="BA3">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="BB3">
         <v>25</v>
       </c>
       <c r="BC3">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="BD3">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="BE3">
         <v>40</v>
@@ -1416,64 +1416,64 @@
         <v>28</v>
       </c>
       <c r="BH3">
-        <v>1000</v>
+        <v>3.7</v>
       </c>
       <c r="BI3">
-        <v>1.04</v>
+        <v>2.56</v>
       </c>
       <c r="BJ3">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="BK3">
-        <v>1.04</v>
+        <v>3.4</v>
       </c>
       <c r="BL3">
         <v>1000</v>
       </c>
       <c r="BM3">
-        <v>1.04</v>
+        <v>4.6</v>
       </c>
       <c r="BN3">
-        <v>1000</v>
+        <v>6.4</v>
       </c>
       <c r="BO3">
-        <v>1.04</v>
+        <v>4</v>
       </c>
       <c r="BP3">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="BQ3">
-        <v>1.04</v>
+        <v>3.95</v>
       </c>
       <c r="BR3">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="BS3">
-        <v>1.04</v>
+        <v>4.2</v>
       </c>
       <c r="BT3">
-        <v>1000</v>
+        <v>7.6</v>
       </c>
       <c r="BU3">
-        <v>1.04</v>
+        <v>4.8</v>
       </c>
       <c r="BV3">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="BW3">
-        <v>1.04</v>
+        <v>4.1</v>
       </c>
       <c r="BX3">
-        <v>1000</v>
+        <v>50</v>
       </c>
       <c r="BY3">
-        <v>1.04</v>
+        <v>4.3</v>
       </c>
       <c r="BZ3">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="CA3">
-        <v>1.04</v>
+        <v>4.2</v>
       </c>
       <c r="CB3" t="s">
         <v>134</v>
@@ -1496,19 +1496,19 @@
         <v>120</v>
       </c>
       <c r="F4">
-        <v>1.71</v>
+        <v>1.74</v>
       </c>
       <c r="G4">
-        <v>1.77</v>
+        <v>1.81</v>
       </c>
       <c r="H4">
-        <v>5.6</v>
+        <v>5.5</v>
       </c>
       <c r="I4">
-        <v>7.2</v>
+        <v>6.4</v>
       </c>
       <c r="J4">
-        <v>3.65</v>
+        <v>3.6</v>
       </c>
       <c r="K4">
         <v>3.9</v>
@@ -1520,7 +1520,7 @@
         <v>1.09</v>
       </c>
       <c r="N4">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="O4">
         <v>1.42</v>
@@ -1529,7 +1529,7 @@
         <v>1.72</v>
       </c>
       <c r="Q4">
-        <v>2.26</v>
+        <v>2.28</v>
       </c>
       <c r="R4">
         <v>1.26</v>
@@ -1538,184 +1538,184 @@
         <v>4.4</v>
       </c>
       <c r="T4">
-        <v>1.11</v>
+        <v>2.08</v>
       </c>
       <c r="U4">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="V4">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="W4">
-        <v>2.28</v>
+        <v>2.2</v>
       </c>
       <c r="X4">
-        <v>1000</v>
+        <v>13.5</v>
       </c>
       <c r="Y4">
-        <v>1000</v>
+        <v>17</v>
       </c>
       <c r="Z4">
-        <v>1000</v>
+        <v>48</v>
       </c>
       <c r="AA4">
-        <v>1000</v>
+        <v>200</v>
       </c>
       <c r="AB4">
-        <v>1000</v>
+        <v>7.4</v>
       </c>
       <c r="AC4">
-        <v>1000</v>
+        <v>8.6</v>
       </c>
       <c r="AD4">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="AE4">
-        <v>1000</v>
+        <v>120</v>
       </c>
       <c r="AF4">
-        <v>1000</v>
+        <v>9.6</v>
       </c>
       <c r="AG4">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="AH4">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="AI4">
-        <v>1000</v>
+        <v>120</v>
       </c>
       <c r="AJ4">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="AK4">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="AL4">
-        <v>1000</v>
+        <v>50</v>
       </c>
       <c r="AM4">
-        <v>1000</v>
+        <v>190</v>
       </c>
       <c r="AN4">
-        <v>1000</v>
+        <v>17.5</v>
       </c>
       <c r="AO4">
-        <v>1000</v>
+        <v>170</v>
       </c>
       <c r="AP4">
-        <v>1.01</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AQ4">
-        <v>1.01</v>
+        <v>13.5</v>
       </c>
       <c r="AR4">
-        <v>1.01</v>
+        <v>6.8</v>
       </c>
       <c r="AS4">
-        <v>1.01</v>
+        <v>7.6</v>
       </c>
       <c r="AT4">
-        <v>1.01</v>
+        <v>6</v>
       </c>
       <c r="AU4">
-        <v>1.01</v>
+        <v>7.4</v>
       </c>
       <c r="AV4">
-        <v>1.01</v>
+        <v>20</v>
       </c>
       <c r="AW4">
-        <v>1.01</v>
+        <v>7.4</v>
       </c>
       <c r="AX4">
-        <v>1.01</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AY4">
-        <v>1.01</v>
+        <v>9</v>
       </c>
       <c r="AZ4">
-        <v>1.01</v>
+        <v>20</v>
       </c>
       <c r="BA4">
-        <v>1.01</v>
+        <v>7.4</v>
       </c>
       <c r="BB4">
-        <v>1.01</v>
+        <v>16</v>
       </c>
       <c r="BC4">
-        <v>1.01</v>
+        <v>18.5</v>
       </c>
       <c r="BD4">
-        <v>1.01</v>
+        <v>36</v>
       </c>
       <c r="BE4">
-        <v>1.01</v>
+        <v>7.6</v>
       </c>
       <c r="BF4">
-        <v>1.02</v>
+        <v>13</v>
       </c>
       <c r="BG4">
-        <v>1.01</v>
+        <v>7.4</v>
       </c>
       <c r="BH4">
-        <v>1000</v>
+        <v>3.2</v>
       </c>
       <c r="BI4">
-        <v>1.04</v>
+        <v>2.58</v>
       </c>
       <c r="BJ4">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="BK4">
-        <v>1.04</v>
+        <v>8.6</v>
       </c>
       <c r="BL4">
         <v>1000</v>
       </c>
       <c r="BM4">
-        <v>7.6</v>
+        <v>10.5</v>
       </c>
       <c r="BN4">
-        <v>1000</v>
+        <v>4.3</v>
       </c>
       <c r="BO4">
-        <v>1.04</v>
+        <v>3.65</v>
       </c>
       <c r="BP4">
-        <v>1000</v>
+        <v>13.5</v>
       </c>
       <c r="BQ4">
-        <v>1.04</v>
+        <v>6</v>
       </c>
       <c r="BR4">
         <v>1000</v>
       </c>
       <c r="BS4">
-        <v>1.04</v>
+        <v>8.4</v>
       </c>
       <c r="BT4">
-        <v>1000</v>
+        <v>9.4</v>
       </c>
       <c r="BU4">
-        <v>1.04</v>
+        <v>7</v>
       </c>
       <c r="BV4">
         <v>1000</v>
       </c>
       <c r="BW4">
-        <v>1.04</v>
+        <v>9.4</v>
       </c>
       <c r="BX4">
         <v>1000</v>
       </c>
       <c r="BY4">
-        <v>1.04</v>
+        <v>9.6</v>
       </c>
       <c r="BZ4">
-        <v>1000</v>
+        <v>30</v>
       </c>
       <c r="CA4">
-        <v>1.04</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="CB4" t="s">
         <v>134</v>
@@ -1741,19 +1741,19 @@
         <v>1.56</v>
       </c>
       <c r="G5">
-        <v>1.62</v>
+        <v>1.59</v>
       </c>
       <c r="H5">
-        <v>6.6</v>
+        <v>7.6</v>
       </c>
       <c r="I5">
-        <v>8.4</v>
+        <v>7.8</v>
       </c>
       <c r="J5">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="K5">
-        <v>4.6</v>
+        <v>4.4</v>
       </c>
       <c r="L5">
         <v>1.46</v>
@@ -1774,31 +1774,31 @@
         <v>2.22</v>
       </c>
       <c r="R5">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="S5">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="T5">
-        <v>2.22</v>
+        <v>2.26</v>
       </c>
       <c r="U5">
-        <v>1.71</v>
+        <v>1.73</v>
       </c>
       <c r="V5">
         <v>1.14</v>
       </c>
       <c r="W5">
-        <v>2.6</v>
+        <v>2.68</v>
       </c>
       <c r="X5">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="Y5">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="Z5">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="AA5">
         <v>1000</v>
@@ -1807,16 +1807,16 @@
         <v>6.6</v>
       </c>
       <c r="AC5">
-        <v>9.800000000000001</v>
+        <v>9.4</v>
       </c>
       <c r="AD5">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="AE5">
-        <v>160</v>
+        <v>1000</v>
       </c>
       <c r="AF5">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="AG5">
         <v>10.5</v>
@@ -1828,40 +1828,40 @@
         <v>150</v>
       </c>
       <c r="AJ5">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="AK5">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AL5">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="AM5">
         <v>1000</v>
       </c>
       <c r="AN5">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AO5">
         <v>1000</v>
       </c>
       <c r="AP5">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AQ5">
-        <v>17</v>
+        <v>17.5</v>
       </c>
       <c r="AR5">
-        <v>40</v>
+        <v>28</v>
       </c>
       <c r="AS5">
-        <v>48</v>
+        <v>95</v>
       </c>
       <c r="AT5">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="AU5">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="AV5">
         <v>22</v>
@@ -1876,19 +1876,19 @@
         <v>9.199999999999999</v>
       </c>
       <c r="AZ5">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="BA5">
         <v>44</v>
       </c>
       <c r="BB5">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="BC5">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="BD5">
-        <v>34</v>
+        <v>27</v>
       </c>
       <c r="BE5">
         <v>48</v>
@@ -1897,67 +1897,67 @@
         <v>10</v>
       </c>
       <c r="BG5">
-        <v>48</v>
+        <v>100</v>
       </c>
       <c r="BH5">
-        <v>1000</v>
+        <v>3.3</v>
       </c>
       <c r="BI5">
-        <v>1.04</v>
+        <v>2.66</v>
       </c>
       <c r="BJ5">
-        <v>1000</v>
+        <v>13</v>
       </c>
       <c r="BK5">
-        <v>1.04</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BL5">
-        <v>1000</v>
+        <v>220</v>
       </c>
       <c r="BM5">
-        <v>1.04</v>
+        <v>10</v>
       </c>
       <c r="BN5">
-        <v>1000</v>
+        <v>3.95</v>
       </c>
       <c r="BO5">
-        <v>1.04</v>
+        <v>3.1</v>
       </c>
       <c r="BP5">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="BQ5">
-        <v>1.04</v>
+        <v>5.4</v>
       </c>
       <c r="BR5">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="BS5">
-        <v>1.04</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BT5">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="BU5">
-        <v>1.04</v>
+        <v>5.6</v>
       </c>
       <c r="BV5">
-        <v>1000</v>
+        <v>85</v>
       </c>
       <c r="BW5">
-        <v>1.04</v>
+        <v>9.6</v>
       </c>
       <c r="BX5">
-        <v>1000</v>
+        <v>95</v>
       </c>
       <c r="BY5">
-        <v>1.04</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BZ5">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="CA5">
-        <v>1.04</v>
+        <v>7.4</v>
       </c>
       <c r="CB5" t="s">
         <v>134</v>
@@ -1983,16 +1983,16 @@
         <v>1.34</v>
       </c>
       <c r="G6">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="H6">
-        <v>10.5</v>
+        <v>11.5</v>
       </c>
       <c r="I6">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="J6">
-        <v>5.4</v>
+        <v>5.3</v>
       </c>
       <c r="K6">
         <v>5.8</v>
@@ -2022,184 +2022,184 @@
         <v>3.1</v>
       </c>
       <c r="T6">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="U6">
-        <v>1.65</v>
+        <v>1.76</v>
       </c>
       <c r="V6">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="W6">
-        <v>3.85</v>
+        <v>3.7</v>
       </c>
       <c r="X6">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="Y6">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="Z6">
-        <v>1000</v>
+        <v>140</v>
       </c>
       <c r="AA6">
         <v>1000</v>
       </c>
       <c r="AB6">
-        <v>1000</v>
+        <v>8.4</v>
       </c>
       <c r="AC6">
-        <v>970</v>
+        <v>12.5</v>
       </c>
       <c r="AD6">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AE6">
-        <v>1000</v>
+        <v>270</v>
       </c>
       <c r="AF6">
-        <v>1000</v>
+        <v>8</v>
       </c>
       <c r="AG6">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="AH6">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="AI6">
-        <v>1000</v>
+        <v>200</v>
       </c>
       <c r="AJ6">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="AK6">
-        <v>970</v>
+        <v>18</v>
       </c>
       <c r="AL6">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AM6">
-        <v>1000</v>
+        <v>240</v>
       </c>
       <c r="AN6">
-        <v>1000</v>
+        <v>6</v>
       </c>
       <c r="AO6">
-        <v>1000</v>
+        <v>420</v>
       </c>
       <c r="AP6">
-        <v>1.13</v>
+        <v>5.8</v>
       </c>
       <c r="AQ6">
-        <v>1.13</v>
+        <v>6.6</v>
       </c>
       <c r="AR6">
-        <v>1.14</v>
+        <v>7.2</v>
       </c>
       <c r="AS6">
-        <v>1.14</v>
+        <v>7.6</v>
       </c>
       <c r="AT6">
-        <v>1.13</v>
+        <v>7.2</v>
       </c>
       <c r="AU6">
-        <v>1.06</v>
+        <v>10.5</v>
       </c>
       <c r="AV6">
-        <v>1.13</v>
+        <v>7</v>
       </c>
       <c r="AW6">
-        <v>1.14</v>
+        <v>7.4</v>
       </c>
       <c r="AX6">
-        <v>1.13</v>
+        <v>6.6</v>
       </c>
       <c r="AY6">
-        <v>1.13</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AZ6">
-        <v>1.13</v>
+        <v>6.6</v>
       </c>
       <c r="BA6">
-        <v>1.14</v>
+        <v>7.4</v>
       </c>
       <c r="BB6">
-        <v>1.13</v>
+        <v>9.4</v>
       </c>
       <c r="BC6">
-        <v>1.3</v>
+        <v>5.6</v>
       </c>
       <c r="BD6">
-        <v>1.14</v>
+        <v>6.6</v>
       </c>
       <c r="BE6">
-        <v>1.14</v>
+        <v>7.4</v>
       </c>
       <c r="BF6">
-        <v>1.13</v>
+        <v>5.4</v>
       </c>
       <c r="BG6">
-        <v>1.14</v>
+        <v>7.4</v>
       </c>
       <c r="BH6">
-        <v>1000</v>
+        <v>3.95</v>
       </c>
       <c r="BI6">
-        <v>1.04</v>
+        <v>3.1</v>
       </c>
       <c r="BJ6">
-        <v>1000</v>
+        <v>13.5</v>
       </c>
       <c r="BK6">
-        <v>1.04</v>
+        <v>6</v>
       </c>
       <c r="BL6">
         <v>1000</v>
       </c>
       <c r="BM6">
-        <v>1.04</v>
+        <v>10</v>
       </c>
       <c r="BN6">
-        <v>1000</v>
+        <v>3.8</v>
       </c>
       <c r="BO6">
-        <v>1.04</v>
+        <v>3</v>
       </c>
       <c r="BP6">
-        <v>1000</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BQ6">
-        <v>1.04</v>
+        <v>6</v>
       </c>
       <c r="BR6">
         <v>1000</v>
       </c>
       <c r="BS6">
-        <v>1.04</v>
+        <v>7.6</v>
       </c>
       <c r="BT6">
-        <v>1000</v>
+        <v>15</v>
       </c>
       <c r="BU6">
-        <v>1.04</v>
+        <v>6.2</v>
       </c>
       <c r="BV6">
         <v>1000</v>
       </c>
       <c r="BW6">
-        <v>1.04</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BX6">
         <v>1000</v>
       </c>
       <c r="BY6">
-        <v>1.04</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BZ6">
-        <v>1000</v>
+        <v>14.5</v>
       </c>
       <c r="CA6">
-        <v>1.04</v>
+        <v>6</v>
       </c>
       <c r="CB6" t="s">
         <v>134</v>
@@ -2222,22 +2222,22 @@
         <v>123</v>
       </c>
       <c r="F7">
-        <v>2.14</v>
+        <v>2.12</v>
       </c>
       <c r="G7">
-        <v>2.28</v>
+        <v>2.26</v>
       </c>
       <c r="H7">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="I7">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="J7">
-        <v>3.15</v>
+        <v>3.9</v>
       </c>
       <c r="K7">
-        <v>4.9</v>
+        <v>4.2</v>
       </c>
       <c r="L7">
         <v>1.33</v>
@@ -2255,37 +2255,37 @@
         <v>2.36</v>
       </c>
       <c r="Q7">
-        <v>1.45</v>
+        <v>1.64</v>
       </c>
       <c r="R7">
-        <v>1.55</v>
+        <v>1.54</v>
       </c>
       <c r="S7">
-        <v>2.56</v>
+        <v>2.62</v>
       </c>
       <c r="T7">
-        <v>1.25</v>
+        <v>1.59</v>
       </c>
       <c r="U7">
-        <v>2.02</v>
+        <v>2.48</v>
       </c>
       <c r="V7">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="W7">
         <v>1.8</v>
       </c>
       <c r="X7">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="Y7">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="Z7">
         <v>36</v>
       </c>
       <c r="AA7">
-        <v>1000</v>
+        <v>80</v>
       </c>
       <c r="AB7">
         <v>13.5</v>
@@ -2300,46 +2300,46 @@
         <v>44</v>
       </c>
       <c r="AF7">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="AG7">
-        <v>1000</v>
+        <v>13.5</v>
       </c>
       <c r="AH7">
-        <v>15.5</v>
+        <v>20</v>
       </c>
       <c r="AI7">
-        <v>1000</v>
+        <v>46</v>
       </c>
       <c r="AJ7">
         <v>36</v>
       </c>
       <c r="AK7">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="AL7">
         <v>38</v>
       </c>
       <c r="AM7">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="AN7">
         <v>14.5</v>
       </c>
       <c r="AO7">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="AP7">
-        <v>2.68</v>
+        <v>5.9</v>
       </c>
       <c r="AQ7">
         <v>15</v>
       </c>
       <c r="AR7">
-        <v>2.44</v>
+        <v>6</v>
       </c>
       <c r="AS7">
-        <v>2.7</v>
+        <v>6.8</v>
       </c>
       <c r="AT7">
         <v>11.5</v>
@@ -2348,13 +2348,13 @@
         <v>8.199999999999999</v>
       </c>
       <c r="AV7">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="AW7">
-        <v>2.5</v>
+        <v>6.2</v>
       </c>
       <c r="AX7">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="AY7">
         <v>10</v>
@@ -2363,25 +2363,25 @@
         <v>13.5</v>
       </c>
       <c r="BA7">
-        <v>2.7</v>
+        <v>6.6</v>
       </c>
       <c r="BB7">
-        <v>2.46</v>
+        <v>6</v>
       </c>
       <c r="BC7">
-        <v>2.7</v>
+        <v>5.9</v>
       </c>
       <c r="BD7">
-        <v>2.46</v>
+        <v>6</v>
       </c>
       <c r="BE7">
-        <v>2.58</v>
+        <v>6.8</v>
       </c>
       <c r="BF7">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="BG7">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="BH7">
         <v>4.1</v>
@@ -2393,31 +2393,31 @@
         <v>8.800000000000001</v>
       </c>
       <c r="BK7">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="BL7">
         <v>1000</v>
       </c>
       <c r="BM7">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="BN7">
-        <v>5.4</v>
+        <v>5.3</v>
       </c>
       <c r="BO7">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="BP7">
         <v>15</v>
       </c>
       <c r="BQ7">
-        <v>7.2</v>
+        <v>10.5</v>
       </c>
       <c r="BR7">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="BS7">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BT7">
         <v>7</v>
@@ -2426,16 +2426,16 @@
         <v>6</v>
       </c>
       <c r="BV7">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="BW7">
-        <v>9</v>
+        <v>9.4</v>
       </c>
       <c r="BX7">
         <v>1000</v>
       </c>
       <c r="BY7">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="BZ7">
         <v>0</v>
@@ -2464,226 +2464,226 @@
         <v>124</v>
       </c>
       <c r="F8">
-        <v>1.08</v>
+        <v>2.88</v>
       </c>
       <c r="G8">
-        <v>990</v>
+        <v>3.3</v>
       </c>
       <c r="H8">
-        <v>1.08</v>
+        <v>2.82</v>
       </c>
       <c r="I8">
-        <v>990</v>
+        <v>3.2</v>
       </c>
       <c r="J8">
-        <v>1.12</v>
+        <v>2.76</v>
       </c>
       <c r="K8">
-        <v>950</v>
+        <v>3.2</v>
       </c>
       <c r="L8">
-        <v>1.01</v>
+        <v>1.61</v>
       </c>
       <c r="M8">
-        <v>1.01</v>
+        <v>1.14</v>
       </c>
       <c r="N8">
-        <v>1.25</v>
+        <v>2.34</v>
       </c>
       <c r="O8">
-        <v>1.59</v>
+        <v>1.61</v>
       </c>
       <c r="P8">
-        <v>1.25</v>
+        <v>1.45</v>
       </c>
       <c r="Q8">
-        <v>1.58</v>
+        <v>2.78</v>
       </c>
       <c r="R8">
-        <v>1.13</v>
+        <v>1.15</v>
       </c>
       <c r="S8">
-        <v>1.59</v>
+        <v>6</v>
       </c>
       <c r="T8">
-        <v>1.11</v>
+        <v>2.16</v>
       </c>
       <c r="U8">
-        <v>1.11</v>
+        <v>1.71</v>
       </c>
       <c r="V8">
-        <v>1.01</v>
+        <v>1.46</v>
       </c>
       <c r="W8">
-        <v>1.02</v>
+        <v>1.43</v>
       </c>
       <c r="X8">
-        <v>1000</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="Y8">
-        <v>1000</v>
+        <v>9.6</v>
       </c>
       <c r="Z8">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="AA8">
-        <v>1000</v>
+        <v>70</v>
       </c>
       <c r="AB8">
-        <v>1000</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AC8">
-        <v>1000</v>
+        <v>7.4</v>
       </c>
       <c r="AD8">
-        <v>1000</v>
+        <v>17</v>
       </c>
       <c r="AE8">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AF8">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="AG8">
-        <v>1000</v>
+        <v>17.5</v>
       </c>
       <c r="AH8">
-        <v>1000</v>
+        <v>30</v>
       </c>
       <c r="AI8">
-        <v>1000</v>
+        <v>100</v>
       </c>
       <c r="AJ8">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AK8">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AL8">
-        <v>1000</v>
+        <v>100</v>
       </c>
       <c r="AM8">
-        <v>1000</v>
+        <v>270</v>
       </c>
       <c r="AN8">
-        <v>1000</v>
+        <v>70</v>
       </c>
       <c r="AO8">
-        <v>1000</v>
+        <v>70</v>
       </c>
       <c r="AP8">
-        <v>1.01</v>
+        <v>5.8</v>
       </c>
       <c r="AQ8">
-        <v>1.01</v>
+        <v>6</v>
       </c>
       <c r="AR8">
-        <v>1.01</v>
+        <v>15</v>
       </c>
       <c r="AS8">
-        <v>1.01</v>
+        <v>4.9</v>
       </c>
       <c r="AT8">
-        <v>1.01</v>
+        <v>6.2</v>
       </c>
       <c r="AU8">
-        <v>1.01</v>
+        <v>5.3</v>
       </c>
       <c r="AV8">
-        <v>1.01</v>
+        <v>12</v>
       </c>
       <c r="AW8">
-        <v>1.01</v>
+        <v>4.8</v>
       </c>
       <c r="AX8">
-        <v>1.01</v>
+        <v>15.5</v>
       </c>
       <c r="AY8">
-        <v>1.01</v>
+        <v>12.5</v>
       </c>
       <c r="AZ8">
-        <v>1.01</v>
+        <v>20</v>
       </c>
       <c r="BA8">
-        <v>1.01</v>
+        <v>5</v>
       </c>
       <c r="BB8">
-        <v>1.01</v>
+        <v>4.9</v>
       </c>
       <c r="BC8">
-        <v>1.01</v>
+        <v>4.8</v>
       </c>
       <c r="BD8">
-        <v>1.01</v>
+        <v>5</v>
       </c>
       <c r="BE8">
-        <v>1.01</v>
+        <v>5.2</v>
       </c>
       <c r="BF8">
-        <v>1.01</v>
+        <v>4.9</v>
       </c>
       <c r="BG8">
-        <v>1.01</v>
+        <v>4.9</v>
       </c>
       <c r="BH8">
         <v>1000</v>
       </c>
       <c r="BI8">
-        <v>1.04</v>
+        <v>1.68</v>
       </c>
       <c r="BJ8">
-        <v>1000</v>
+        <v>16</v>
       </c>
       <c r="BK8">
-        <v>1.04</v>
+        <v>1.53</v>
       </c>
       <c r="BL8">
         <v>1000</v>
       </c>
       <c r="BM8">
-        <v>1.04</v>
+        <v>1.68</v>
       </c>
       <c r="BN8">
-        <v>1000</v>
+        <v>7.8</v>
       </c>
       <c r="BO8">
-        <v>1.04</v>
+        <v>3.9</v>
       </c>
       <c r="BP8">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="BQ8">
-        <v>1.04</v>
+        <v>1.62</v>
       </c>
       <c r="BR8">
         <v>1000</v>
       </c>
       <c r="BS8">
-        <v>1.04</v>
+        <v>1.65</v>
       </c>
       <c r="BT8">
-        <v>1000</v>
+        <v>7.8</v>
       </c>
       <c r="BU8">
-        <v>1.04</v>
+        <v>3.9</v>
       </c>
       <c r="BV8">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="BW8">
-        <v>1.04</v>
+        <v>1.62</v>
       </c>
       <c r="BX8">
         <v>1000</v>
       </c>
       <c r="BY8">
-        <v>1.04</v>
+        <v>1.65</v>
       </c>
       <c r="BZ8">
         <v>1000</v>
       </c>
       <c r="CA8">
-        <v>1.04</v>
+        <v>1.65</v>
       </c>
       <c r="CB8" t="s">
         <v>134</v>
@@ -2706,226 +2706,226 @@
         <v>125</v>
       </c>
       <c r="F9">
-        <v>2.26</v>
+        <v>6.6</v>
       </c>
       <c r="G9">
-        <v>990</v>
+        <v>9.4</v>
       </c>
       <c r="H9">
-        <v>1.15</v>
+        <v>1.55</v>
       </c>
       <c r="I9">
-        <v>1.85</v>
+        <v>1.64</v>
       </c>
       <c r="J9">
-        <v>1.13</v>
+        <v>3.95</v>
       </c>
       <c r="K9">
-        <v>950</v>
+        <v>4.4</v>
       </c>
       <c r="L9">
-        <v>1.01</v>
+        <v>1.41</v>
       </c>
       <c r="M9">
-        <v>1.01</v>
+        <v>1.07</v>
       </c>
       <c r="N9">
-        <v>1.26</v>
+        <v>3.45</v>
       </c>
       <c r="O9">
-        <v>1.35</v>
+        <v>1.32</v>
       </c>
       <c r="P9">
-        <v>1.25</v>
+        <v>1.84</v>
       </c>
       <c r="Q9">
-        <v>1.01</v>
+        <v>2</v>
       </c>
       <c r="R9">
-        <v>1.13</v>
+        <v>1.32</v>
       </c>
       <c r="S9">
-        <v>1.39</v>
+        <v>3.6</v>
       </c>
       <c r="T9">
-        <v>1.11</v>
+        <v>2.06</v>
       </c>
       <c r="U9">
-        <v>1.11</v>
+        <v>1.66</v>
       </c>
       <c r="V9">
-        <v>2.16</v>
+        <v>2.56</v>
       </c>
       <c r="W9">
-        <v>1.04</v>
+        <v>1.12</v>
       </c>
       <c r="X9">
-        <v>1000</v>
+        <v>16.5</v>
       </c>
       <c r="Y9">
-        <v>1000</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="Z9">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="AA9">
-        <v>1000</v>
+        <v>18</v>
       </c>
       <c r="AB9">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="AC9">
         <v>1000</v>
       </c>
       <c r="AD9">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="AE9">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="AF9">
-        <v>1000</v>
+        <v>75</v>
       </c>
       <c r="AG9">
         <v>1000</v>
       </c>
       <c r="AH9">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="AI9">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AJ9">
-        <v>1000</v>
+        <v>310</v>
       </c>
       <c r="AK9">
-        <v>1000</v>
+        <v>160</v>
       </c>
       <c r="AL9">
-        <v>1000</v>
+        <v>150</v>
       </c>
       <c r="AM9">
-        <v>1000</v>
+        <v>210</v>
       </c>
       <c r="AN9">
-        <v>1000</v>
+        <v>240</v>
       </c>
       <c r="AO9">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="AP9">
-        <v>1.01</v>
+        <v>10</v>
       </c>
       <c r="AQ9">
-        <v>1.01</v>
+        <v>5.5</v>
       </c>
       <c r="AR9">
-        <v>1.01</v>
+        <v>6.6</v>
       </c>
       <c r="AS9">
-        <v>1.01</v>
+        <v>10.5</v>
       </c>
       <c r="AT9">
-        <v>1.01</v>
+        <v>15</v>
       </c>
       <c r="AU9">
-        <v>1.01</v>
+        <v>2.9</v>
       </c>
       <c r="AV9">
-        <v>1.01</v>
+        <v>7.6</v>
       </c>
       <c r="AW9">
-        <v>1.01</v>
+        <v>13</v>
       </c>
       <c r="AX9">
-        <v>1.01</v>
+        <v>2.8</v>
       </c>
       <c r="AY9">
-        <v>1.01</v>
+        <v>20</v>
       </c>
       <c r="AZ9">
-        <v>1.01</v>
+        <v>18</v>
       </c>
       <c r="BA9">
-        <v>1.01</v>
+        <v>2.76</v>
       </c>
       <c r="BB9">
-        <v>1.01</v>
+        <v>2.88</v>
       </c>
       <c r="BC9">
-        <v>1.01</v>
+        <v>2.86</v>
       </c>
       <c r="BD9">
-        <v>1.01</v>
+        <v>2.84</v>
       </c>
       <c r="BE9">
-        <v>1.01</v>
+        <v>2.86</v>
       </c>
       <c r="BF9">
-        <v>1.01</v>
+        <v>2.86</v>
       </c>
       <c r="BG9">
-        <v>1.01</v>
+        <v>7.6</v>
       </c>
       <c r="BH9">
-        <v>1000</v>
+        <v>3.85</v>
       </c>
       <c r="BI9">
-        <v>1.04</v>
+        <v>2.68</v>
       </c>
       <c r="BJ9">
-        <v>1000</v>
+        <v>14</v>
       </c>
       <c r="BK9">
-        <v>1.04</v>
+        <v>3.65</v>
       </c>
       <c r="BL9">
         <v>1000</v>
       </c>
       <c r="BM9">
-        <v>1.04</v>
+        <v>4.8</v>
       </c>
       <c r="BN9">
-        <v>1000</v>
+        <v>13</v>
       </c>
       <c r="BO9">
-        <v>1.04</v>
+        <v>3.55</v>
       </c>
       <c r="BP9">
         <v>1000</v>
       </c>
       <c r="BQ9">
-        <v>1.04</v>
+        <v>4.6</v>
       </c>
       <c r="BR9">
         <v>1000</v>
       </c>
       <c r="BS9">
-        <v>1.04</v>
+        <v>4.7</v>
       </c>
       <c r="BT9">
-        <v>1000</v>
+        <v>4.6</v>
       </c>
       <c r="BU9">
-        <v>1.04</v>
+        <v>3.1</v>
       </c>
       <c r="BV9">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="BW9">
-        <v>1.04</v>
+        <v>3.5</v>
       </c>
       <c r="BX9">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="BY9">
-        <v>1.04</v>
+        <v>4.3</v>
       </c>
       <c r="BZ9">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="CA9">
-        <v>1.04</v>
+        <v>4.1</v>
       </c>
       <c r="CB9" t="s">
         <v>134</v>
@@ -2948,226 +2948,226 @@
         <v>126</v>
       </c>
       <c r="F10">
-        <v>1.15</v>
+        <v>2.74</v>
       </c>
       <c r="G10">
-        <v>990</v>
+        <v>3.05</v>
       </c>
       <c r="H10">
-        <v>1.21</v>
+        <v>3.1</v>
       </c>
       <c r="I10">
-        <v>870</v>
+        <v>3.55</v>
       </c>
       <c r="J10">
-        <v>1.22</v>
+        <v>2.66</v>
       </c>
       <c r="K10">
-        <v>950</v>
+        <v>3.05</v>
       </c>
       <c r="L10">
-        <v>1.01</v>
+        <v>1.67</v>
       </c>
       <c r="M10">
-        <v>1.01</v>
+        <v>1.16</v>
       </c>
       <c r="N10">
-        <v>1.26</v>
+        <v>2.16</v>
       </c>
       <c r="O10">
-        <v>1.02</v>
+        <v>1.68</v>
       </c>
       <c r="P10">
-        <v>1.25</v>
+        <v>1.38</v>
       </c>
       <c r="Q10">
-        <v>1.6</v>
+        <v>3.05</v>
       </c>
       <c r="R10">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="S10">
-        <v>1.6</v>
+        <v>6.4</v>
       </c>
       <c r="T10">
-        <v>1.11</v>
+        <v>2.3</v>
       </c>
       <c r="U10">
-        <v>1.11</v>
+        <v>1.53</v>
       </c>
       <c r="V10">
-        <v>1.02</v>
+        <v>1.39</v>
       </c>
       <c r="W10">
-        <v>1.06</v>
+        <v>1.48</v>
       </c>
       <c r="X10">
-        <v>1000</v>
+        <v>8</v>
       </c>
       <c r="Y10">
-        <v>1000</v>
+        <v>8.4</v>
       </c>
       <c r="Z10">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="AA10">
-        <v>1000</v>
+        <v>85</v>
       </c>
       <c r="AB10">
-        <v>1000</v>
+        <v>7.6</v>
       </c>
       <c r="AC10">
-        <v>1000</v>
+        <v>7.2</v>
       </c>
       <c r="AD10">
-        <v>1000</v>
+        <v>17</v>
       </c>
       <c r="AE10">
-        <v>1000</v>
+        <v>75</v>
       </c>
       <c r="AF10">
-        <v>1000</v>
+        <v>18</v>
       </c>
       <c r="AG10">
-        <v>1000</v>
+        <v>15.5</v>
       </c>
       <c r="AH10">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="AI10">
-        <v>1000</v>
+        <v>130</v>
       </c>
       <c r="AJ10">
-        <v>1000</v>
+        <v>70</v>
       </c>
       <c r="AK10">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AL10">
-        <v>1000</v>
+        <v>120</v>
       </c>
       <c r="AM10">
-        <v>1000</v>
+        <v>340</v>
       </c>
       <c r="AN10">
-        <v>1000</v>
+        <v>95</v>
       </c>
       <c r="AO10">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="AP10">
-        <v>1.01</v>
+        <v>5.1</v>
       </c>
       <c r="AQ10">
-        <v>1.01</v>
+        <v>6</v>
       </c>
       <c r="AR10">
-        <v>1.01</v>
+        <v>17</v>
       </c>
       <c r="AS10">
-        <v>1.01</v>
+        <v>7</v>
       </c>
       <c r="AT10">
-        <v>1.01</v>
+        <v>5.5</v>
       </c>
       <c r="AU10">
-        <v>1.01</v>
+        <v>6</v>
       </c>
       <c r="AV10">
-        <v>1.01</v>
+        <v>14</v>
       </c>
       <c r="AW10">
-        <v>1.01</v>
+        <v>6.8</v>
       </c>
       <c r="AX10">
-        <v>1.01</v>
+        <v>14.5</v>
       </c>
       <c r="AY10">
-        <v>1.01</v>
+        <v>12.5</v>
       </c>
       <c r="AZ10">
-        <v>1.01</v>
+        <v>17</v>
       </c>
       <c r="BA10">
-        <v>1.01</v>
+        <v>7.2</v>
       </c>
       <c r="BB10">
-        <v>1.01</v>
+        <v>6.8</v>
       </c>
       <c r="BC10">
-        <v>1.01</v>
+        <v>6.8</v>
       </c>
       <c r="BD10">
-        <v>1.01</v>
+        <v>7.2</v>
       </c>
       <c r="BE10">
-        <v>1.01</v>
+        <v>7.4</v>
       </c>
       <c r="BF10">
-        <v>1.01</v>
+        <v>7</v>
       </c>
       <c r="BG10">
-        <v>1.01</v>
+        <v>7</v>
       </c>
       <c r="BH10">
-        <v>1000</v>
+        <v>2.74</v>
       </c>
       <c r="BI10">
-        <v>1.04</v>
+        <v>2.02</v>
       </c>
       <c r="BJ10">
-        <v>1000</v>
+        <v>15</v>
       </c>
       <c r="BK10">
-        <v>1.04</v>
+        <v>4.3</v>
       </c>
       <c r="BL10">
         <v>1000</v>
       </c>
       <c r="BM10">
-        <v>1.04</v>
+        <v>5.9</v>
       </c>
       <c r="BN10">
-        <v>1000</v>
+        <v>5.8</v>
       </c>
       <c r="BO10">
-        <v>1.04</v>
+        <v>4.9</v>
       </c>
       <c r="BP10">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="BQ10">
-        <v>1.04</v>
+        <v>5.1</v>
       </c>
       <c r="BR10">
         <v>1000</v>
       </c>
       <c r="BS10">
-        <v>1.04</v>
+        <v>5.5</v>
       </c>
       <c r="BT10">
-        <v>1000</v>
+        <v>7.2</v>
       </c>
       <c r="BU10">
-        <v>1.04</v>
+        <v>4.6</v>
       </c>
       <c r="BV10">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="BW10">
-        <v>1.04</v>
+        <v>5.2</v>
       </c>
       <c r="BX10">
-        <v>1000</v>
+        <v>80</v>
       </c>
       <c r="BY10">
-        <v>1.04</v>
+        <v>5.6</v>
       </c>
       <c r="BZ10">
-        <v>1000</v>
+        <v>90</v>
       </c>
       <c r="CA10">
-        <v>1.04</v>
+        <v>5.6</v>
       </c>
       <c r="CB10" t="s">
         <v>134</v>
@@ -3190,46 +3190,46 @@
         <v>127</v>
       </c>
       <c r="F11">
-        <v>1.2</v>
+        <v>2.42</v>
       </c>
       <c r="G11">
-        <v>990</v>
+        <v>2.58</v>
       </c>
       <c r="H11">
-        <v>1.21</v>
+        <v>3.45</v>
       </c>
       <c r="I11">
-        <v>990</v>
+        <v>4.5</v>
       </c>
       <c r="J11">
-        <v>1.27</v>
+        <v>2.74</v>
       </c>
       <c r="K11">
-        <v>950</v>
+        <v>3.1</v>
       </c>
       <c r="L11">
         <v>1.01</v>
       </c>
       <c r="M11">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="N11">
-        <v>1.26</v>
+        <v>2.3</v>
       </c>
       <c r="O11">
-        <v>1.02</v>
+        <v>1.61</v>
       </c>
       <c r="P11">
-        <v>1.25</v>
+        <v>1.37</v>
       </c>
       <c r="Q11">
-        <v>1.62</v>
+        <v>2.68</v>
       </c>
       <c r="R11">
         <v>1.13</v>
       </c>
       <c r="S11">
-        <v>1.62</v>
+        <v>4.8</v>
       </c>
       <c r="T11">
         <v>1.11</v>
@@ -3238,43 +3238,43 @@
         <v>1.11</v>
       </c>
       <c r="V11">
-        <v>1.05</v>
+        <v>1.28</v>
       </c>
       <c r="W11">
-        <v>1.06</v>
+        <v>1.63</v>
       </c>
       <c r="X11">
         <v>1000</v>
       </c>
       <c r="Y11">
-        <v>1000</v>
+        <v>13</v>
       </c>
       <c r="Z11">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="AA11">
         <v>1000</v>
       </c>
       <c r="AB11">
-        <v>1000</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AC11">
-        <v>1000</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AD11">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="AE11">
         <v>1000</v>
       </c>
       <c r="AF11">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="AG11">
-        <v>1000</v>
+        <v>19.5</v>
       </c>
       <c r="AH11">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="AI11">
         <v>1000</v>
@@ -3298,58 +3298,58 @@
         <v>1000</v>
       </c>
       <c r="AP11">
-        <v>1.01</v>
+        <v>1.9</v>
       </c>
       <c r="AQ11">
-        <v>1.01</v>
+        <v>5.9</v>
       </c>
       <c r="AR11">
-        <v>1.01</v>
+        <v>14.5</v>
       </c>
       <c r="AS11">
-        <v>1.01</v>
+        <v>1.91</v>
       </c>
       <c r="AT11">
-        <v>1.01</v>
+        <v>4.6</v>
       </c>
       <c r="AU11">
-        <v>1.01</v>
+        <v>4.6</v>
       </c>
       <c r="AV11">
-        <v>1.01</v>
+        <v>11</v>
       </c>
       <c r="AW11">
-        <v>1.01</v>
+        <v>1.91</v>
       </c>
       <c r="AX11">
-        <v>1.01</v>
+        <v>9</v>
       </c>
       <c r="AY11">
-        <v>1.01</v>
+        <v>8.4</v>
       </c>
       <c r="AZ11">
-        <v>1.01</v>
+        <v>16</v>
       </c>
       <c r="BA11">
-        <v>1.01</v>
+        <v>1.91</v>
       </c>
       <c r="BB11">
-        <v>1.01</v>
+        <v>1.91</v>
       </c>
       <c r="BC11">
-        <v>1.01</v>
+        <v>1.91</v>
       </c>
       <c r="BD11">
-        <v>1.01</v>
+        <v>1.91</v>
       </c>
       <c r="BE11">
-        <v>1.01</v>
+        <v>1.91</v>
       </c>
       <c r="BF11">
-        <v>1.01</v>
+        <v>1.91</v>
       </c>
       <c r="BG11">
-        <v>1.01</v>
+        <v>1.91</v>
       </c>
       <c r="BH11">
         <v>1000</v>
@@ -3432,226 +3432,226 @@
         <v>128</v>
       </c>
       <c r="F12">
-        <v>1.69</v>
+        <v>2.5</v>
       </c>
       <c r="G12">
-        <v>990</v>
+        <v>2.84</v>
       </c>
       <c r="H12">
-        <v>1.04</v>
+        <v>2.84</v>
       </c>
       <c r="I12">
-        <v>990</v>
+        <v>3.25</v>
       </c>
       <c r="J12">
+        <v>2.94</v>
+      </c>
+      <c r="K12">
+        <v>3.65</v>
+      </c>
+      <c r="L12">
+        <v>1.39</v>
+      </c>
+      <c r="M12">
         <v>1.08</v>
       </c>
-      <c r="K12">
-        <v>950</v>
-      </c>
-      <c r="L12">
-        <v>1.01</v>
-      </c>
-      <c r="M12">
-        <v>1.01</v>
-      </c>
       <c r="N12">
-        <v>2.72</v>
+        <v>3.25</v>
       </c>
       <c r="O12">
         <v>1.37</v>
       </c>
       <c r="P12">
-        <v>1.46</v>
+        <v>1.77</v>
       </c>
       <c r="Q12">
-        <v>1.37</v>
+        <v>2.04</v>
       </c>
       <c r="R12">
-        <v>1.13</v>
+        <v>1.29</v>
       </c>
       <c r="S12">
-        <v>1.37</v>
+        <v>3.7</v>
       </c>
       <c r="T12">
-        <v>1.11</v>
+        <v>1.79</v>
       </c>
       <c r="U12">
-        <v>1.11</v>
+        <v>2.02</v>
       </c>
       <c r="V12">
-        <v>1.03</v>
+        <v>1.44</v>
       </c>
       <c r="W12">
-        <v>1.01</v>
+        <v>1.54</v>
       </c>
       <c r="X12">
-        <v>1000</v>
+        <v>14.5</v>
       </c>
       <c r="Y12">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="Z12">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="AA12">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AB12">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="AC12">
-        <v>1000</v>
+        <v>8</v>
       </c>
       <c r="AD12">
-        <v>1000</v>
+        <v>14</v>
       </c>
       <c r="AE12">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="AF12">
-        <v>1000</v>
+        <v>18</v>
       </c>
       <c r="AG12">
-        <v>1000</v>
+        <v>13</v>
       </c>
       <c r="AH12">
-        <v>1000</v>
+        <v>18.5</v>
       </c>
       <c r="AI12">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AJ12">
-        <v>1000</v>
+        <v>48</v>
       </c>
       <c r="AK12">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="AL12">
-        <v>1000</v>
+        <v>48</v>
       </c>
       <c r="AM12">
-        <v>1000</v>
+        <v>120</v>
       </c>
       <c r="AN12">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="AO12">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="AP12">
-        <v>1.01</v>
+        <v>9.6</v>
       </c>
       <c r="AQ12">
-        <v>1.01</v>
+        <v>9.6</v>
       </c>
       <c r="AR12">
-        <v>1.01</v>
+        <v>16</v>
       </c>
       <c r="AS12">
-        <v>1.01</v>
+        <v>7</v>
       </c>
       <c r="AT12">
-        <v>1.01</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AU12">
-        <v>1.01</v>
+        <v>6.2</v>
       </c>
       <c r="AV12">
-        <v>1.01</v>
+        <v>11.5</v>
       </c>
       <c r="AW12">
-        <v>1.01</v>
+        <v>6.6</v>
       </c>
       <c r="AX12">
-        <v>1.01</v>
+        <v>14.5</v>
       </c>
       <c r="AY12">
-        <v>1.01</v>
+        <v>10.5</v>
       </c>
       <c r="AZ12">
-        <v>1.01</v>
+        <v>15</v>
       </c>
       <c r="BA12">
-        <v>1.01</v>
+        <v>7</v>
       </c>
       <c r="BB12">
-        <v>1.01</v>
+        <v>6.8</v>
       </c>
       <c r="BC12">
-        <v>1.01</v>
+        <v>19.5</v>
       </c>
       <c r="BD12">
-        <v>1.01</v>
+        <v>6.8</v>
       </c>
       <c r="BE12">
-        <v>1.01</v>
+        <v>7.4</v>
       </c>
       <c r="BF12">
-        <v>1.01</v>
+        <v>21</v>
       </c>
       <c r="BG12">
-        <v>1.01</v>
+        <v>6.6</v>
       </c>
       <c r="BH12">
-        <v>1000</v>
+        <v>3.3</v>
       </c>
       <c r="BI12">
-        <v>1.04</v>
+        <v>2.66</v>
       </c>
       <c r="BJ12">
-        <v>1000</v>
+        <v>10</v>
       </c>
       <c r="BK12">
-        <v>1.04</v>
+        <v>5.3</v>
       </c>
       <c r="BL12">
         <v>1000</v>
       </c>
       <c r="BM12">
-        <v>1.04</v>
+        <v>10.5</v>
       </c>
       <c r="BN12">
-        <v>1000</v>
+        <v>5.7</v>
       </c>
       <c r="BO12">
-        <v>1.04</v>
+        <v>4.4</v>
       </c>
       <c r="BP12">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="BQ12">
-        <v>1.04</v>
+        <v>7.6</v>
       </c>
       <c r="BR12">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="BS12">
-        <v>1.04</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BT12">
-        <v>1000</v>
+        <v>6.2</v>
       </c>
       <c r="BU12">
-        <v>1.04</v>
+        <v>4.7</v>
       </c>
       <c r="BV12">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="BW12">
-        <v>1.04</v>
+        <v>7.8</v>
       </c>
       <c r="BX12">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="BY12">
-        <v>1.04</v>
+        <v>9</v>
       </c>
       <c r="BZ12">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="CA12">
-        <v>1.04</v>
+        <v>8.6</v>
       </c>
       <c r="CB12" t="s">
         <v>134</v>
@@ -3916,226 +3916,226 @@
         <v>130</v>
       </c>
       <c r="F14">
-        <v>1.43</v>
+        <v>2.82</v>
       </c>
       <c r="G14">
-        <v>1000</v>
+        <v>2.98</v>
       </c>
       <c r="H14">
-        <v>2.78</v>
+        <v>2.82</v>
       </c>
       <c r="I14">
-        <v>1000</v>
+        <v>2.9</v>
       </c>
       <c r="J14">
-        <v>1.55</v>
+        <v>3.15</v>
       </c>
       <c r="K14">
-        <v>950</v>
+        <v>3.5</v>
       </c>
       <c r="L14">
         <v>1.46</v>
       </c>
       <c r="M14">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="N14">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="O14">
         <v>1.39</v>
       </c>
       <c r="P14">
-        <v>1.52</v>
+        <v>1.75</v>
       </c>
       <c r="Q14">
-        <v>1.75</v>
+        <v>2.14</v>
       </c>
       <c r="R14">
-        <v>1.18</v>
+        <v>1.28</v>
       </c>
       <c r="S14">
-        <v>2.12</v>
+        <v>4</v>
       </c>
       <c r="T14">
-        <v>1.8</v>
+        <v>1.84</v>
       </c>
       <c r="U14">
         <v>2.02</v>
       </c>
       <c r="V14">
-        <v>1.48</v>
+        <v>1.52</v>
       </c>
       <c r="W14">
-        <v>1.03</v>
+        <v>1.52</v>
       </c>
       <c r="X14">
-        <v>1000</v>
+        <v>14.5</v>
       </c>
       <c r="Y14">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="Z14">
-        <v>1000</v>
+        <v>18</v>
       </c>
       <c r="AA14">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AB14">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="AC14">
-        <v>1000</v>
+        <v>7.6</v>
       </c>
       <c r="AD14">
-        <v>1000</v>
+        <v>13</v>
       </c>
       <c r="AE14">
-        <v>1000</v>
+        <v>50</v>
       </c>
       <c r="AF14">
-        <v>1000</v>
+        <v>19.5</v>
       </c>
       <c r="AG14">
-        <v>1000</v>
+        <v>13.5</v>
       </c>
       <c r="AH14">
-        <v>1000</v>
+        <v>18.5</v>
       </c>
       <c r="AI14">
-        <v>1000</v>
+        <v>70</v>
       </c>
       <c r="AJ14">
-        <v>1000</v>
+        <v>70</v>
       </c>
       <c r="AK14">
-        <v>1000</v>
+        <v>50</v>
       </c>
       <c r="AL14">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AM14">
-        <v>1000</v>
+        <v>140</v>
       </c>
       <c r="AN14">
-        <v>1000</v>
+        <v>50</v>
       </c>
       <c r="AO14">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="AP14">
-        <v>1.01</v>
+        <v>8.6</v>
       </c>
       <c r="AQ14">
-        <v>1.01</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AR14">
-        <v>1.01</v>
+        <v>15.5</v>
       </c>
       <c r="AS14">
-        <v>1.01</v>
+        <v>8.4</v>
       </c>
       <c r="AT14">
-        <v>1.01</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AU14">
-        <v>1.01</v>
+        <v>6.6</v>
       </c>
       <c r="AV14">
-        <v>1.01</v>
+        <v>11</v>
       </c>
       <c r="AW14">
-        <v>1.01</v>
+        <v>8</v>
       </c>
       <c r="AX14">
-        <v>1.01</v>
+        <v>16.5</v>
       </c>
       <c r="AY14">
-        <v>1.01</v>
+        <v>11.5</v>
       </c>
       <c r="AZ14">
-        <v>1.01</v>
+        <v>16</v>
       </c>
       <c r="BA14">
-        <v>1.01</v>
+        <v>8.6</v>
       </c>
       <c r="BB14">
-        <v>1.01</v>
+        <v>29</v>
       </c>
       <c r="BC14">
-        <v>1.01</v>
+        <v>8</v>
       </c>
       <c r="BD14">
-        <v>1.01</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BE14">
-        <v>1.01</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BF14">
-        <v>1.01</v>
+        <v>8</v>
       </c>
       <c r="BG14">
-        <v>1.01</v>
+        <v>8</v>
       </c>
       <c r="BH14">
-        <v>1000</v>
+        <v>3.15</v>
       </c>
       <c r="BI14">
-        <v>1.04</v>
+        <v>2.6</v>
       </c>
       <c r="BJ14">
-        <v>1000</v>
+        <v>10</v>
       </c>
       <c r="BK14">
-        <v>1.04</v>
+        <v>6</v>
       </c>
       <c r="BL14">
         <v>1000</v>
       </c>
       <c r="BM14">
-        <v>1.04</v>
+        <v>13.5</v>
       </c>
       <c r="BN14">
-        <v>1000</v>
+        <v>5.9</v>
       </c>
       <c r="BO14">
-        <v>1.04</v>
+        <v>4.4</v>
       </c>
       <c r="BP14">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="BQ14">
-        <v>1.04</v>
+        <v>9.4</v>
       </c>
       <c r="BR14">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="BS14">
-        <v>1.04</v>
+        <v>11</v>
       </c>
       <c r="BT14">
-        <v>1000</v>
+        <v>5.7</v>
       </c>
       <c r="BU14">
-        <v>1.04</v>
+        <v>4.3</v>
       </c>
       <c r="BV14">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="BW14">
-        <v>1.04</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BX14">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="BY14">
-        <v>1.04</v>
+        <v>10.5</v>
       </c>
       <c r="BZ14">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="CA14">
-        <v>1.04</v>
+        <v>10.5</v>
       </c>
       <c r="CB14" t="s">
         <v>134</v>
@@ -4158,220 +4158,220 @@
         <v>131</v>
       </c>
       <c r="F15">
-        <v>1.52</v>
+        <v>1.51</v>
       </c>
       <c r="G15">
-        <v>1.68</v>
+        <v>1.66</v>
       </c>
       <c r="H15">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="I15">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="J15">
-        <v>3.9</v>
+        <v>3.6</v>
       </c>
       <c r="K15">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="L15">
-        <v>1.01</v>
+        <v>1.36</v>
       </c>
       <c r="M15">
-        <v>1.01</v>
+        <v>1.07</v>
       </c>
       <c r="N15">
-        <v>2.8</v>
+        <v>3.35</v>
       </c>
       <c r="O15">
         <v>1.33</v>
       </c>
       <c r="P15">
-        <v>1.77</v>
+        <v>1.82</v>
       </c>
       <c r="Q15">
         <v>1.98</v>
       </c>
       <c r="R15">
-        <v>1.24</v>
+        <v>1.31</v>
       </c>
       <c r="S15">
-        <v>3.05</v>
+        <v>3.3</v>
       </c>
       <c r="T15">
+        <v>2.04</v>
+      </c>
+      <c r="U15">
+        <v>1.77</v>
+      </c>
+      <c r="V15">
         <v>1.11</v>
       </c>
-      <c r="U15">
-        <v>1.11</v>
-      </c>
-      <c r="V15">
-        <v>1.12</v>
-      </c>
       <c r="W15">
-        <v>2.42</v>
+        <v>2.52</v>
       </c>
       <c r="X15">
-        <v>1000</v>
+        <v>16</v>
       </c>
       <c r="Y15">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="Z15">
-        <v>1000</v>
+        <v>75</v>
       </c>
       <c r="AA15">
-        <v>1000</v>
+        <v>310</v>
       </c>
       <c r="AB15">
-        <v>1000</v>
+        <v>8.4</v>
       </c>
       <c r="AC15">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="AD15">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="AE15">
-        <v>1000</v>
+        <v>160</v>
       </c>
       <c r="AF15">
-        <v>1000</v>
+        <v>10</v>
       </c>
       <c r="AG15">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="AH15">
-        <v>1000</v>
+        <v>30</v>
       </c>
       <c r="AI15">
-        <v>1000</v>
+        <v>140</v>
       </c>
       <c r="AJ15">
-        <v>1000</v>
+        <v>17</v>
       </c>
       <c r="AK15">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="AL15">
-        <v>1000</v>
+        <v>50</v>
       </c>
       <c r="AM15">
-        <v>1000</v>
+        <v>200</v>
       </c>
       <c r="AN15">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="AO15">
-        <v>1000</v>
+        <v>240</v>
       </c>
       <c r="AP15">
-        <v>1.01</v>
+        <v>10.5</v>
       </c>
       <c r="AQ15">
-        <v>1.01</v>
+        <v>16.5</v>
       </c>
       <c r="AR15">
-        <v>1.01</v>
+        <v>4.9</v>
       </c>
       <c r="AS15">
-        <v>1.01</v>
+        <v>5.2</v>
       </c>
       <c r="AT15">
-        <v>1.01</v>
+        <v>5.9</v>
       </c>
       <c r="AU15">
-        <v>1.01</v>
+        <v>7.4</v>
       </c>
       <c r="AV15">
-        <v>1.01</v>
+        <v>4.5</v>
       </c>
       <c r="AW15">
-        <v>1.01</v>
+        <v>5.1</v>
       </c>
       <c r="AX15">
-        <v>1.01</v>
+        <v>6.8</v>
       </c>
       <c r="AY15">
-        <v>1.01</v>
+        <v>7.8</v>
       </c>
       <c r="AZ15">
-        <v>1.01</v>
+        <v>19.5</v>
       </c>
       <c r="BA15">
-        <v>1.01</v>
+        <v>5</v>
       </c>
       <c r="BB15">
-        <v>1.01</v>
+        <v>11</v>
       </c>
       <c r="BC15">
-        <v>1.01</v>
+        <v>13.5</v>
       </c>
       <c r="BD15">
-        <v>1.01</v>
+        <v>4.7</v>
       </c>
       <c r="BE15">
-        <v>1.01</v>
+        <v>5.1</v>
       </c>
       <c r="BF15">
-        <v>1.01</v>
+        <v>7.8</v>
       </c>
       <c r="BG15">
-        <v>1.01</v>
+        <v>5.1</v>
       </c>
       <c r="BH15">
         <v>3.45</v>
       </c>
       <c r="BI15">
-        <v>2.76</v>
+        <v>2.78</v>
       </c>
       <c r="BJ15">
         <v>12</v>
       </c>
       <c r="BK15">
-        <v>1.04</v>
+        <v>5.6</v>
       </c>
       <c r="BL15">
         <v>1000</v>
       </c>
       <c r="BM15">
-        <v>1.04</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BN15">
         <v>4.1</v>
       </c>
       <c r="BO15">
-        <v>3.2</v>
+        <v>3.15</v>
       </c>
       <c r="BP15">
         <v>11</v>
       </c>
       <c r="BQ15">
-        <v>1.04</v>
+        <v>5.3</v>
       </c>
       <c r="BR15">
         <v>1000</v>
       </c>
       <c r="BS15">
-        <v>1.04</v>
+        <v>7.6</v>
       </c>
       <c r="BT15">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="BU15">
-        <v>1.04</v>
+        <v>5.4</v>
       </c>
       <c r="BV15">
         <v>1000</v>
       </c>
       <c r="BW15">
-        <v>1.04</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BX15">
         <v>1000</v>
       </c>
       <c r="BY15">
-        <v>1.04</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BZ15">
         <v>0</v>
@@ -4400,226 +4400,226 @@
         <v>132</v>
       </c>
       <c r="F16">
-        <v>1.09</v>
+        <v>2.22</v>
       </c>
       <c r="G16">
-        <v>2.56</v>
+        <v>2.42</v>
       </c>
       <c r="H16">
-        <v>2.34</v>
+        <v>3.35</v>
       </c>
       <c r="I16">
-        <v>990</v>
+        <v>3.95</v>
       </c>
       <c r="J16">
         <v>3.2</v>
       </c>
       <c r="K16">
-        <v>950</v>
+        <v>3.6</v>
       </c>
       <c r="L16">
-        <v>1.01</v>
+        <v>1.39</v>
       </c>
       <c r="M16">
-        <v>1.01</v>
+        <v>1.08</v>
       </c>
       <c r="N16">
-        <v>3.05</v>
+        <v>3.25</v>
       </c>
       <c r="O16">
         <v>1.37</v>
       </c>
       <c r="P16">
-        <v>1.73</v>
+        <v>1.75</v>
       </c>
       <c r="Q16">
-        <v>1.41</v>
+        <v>2.02</v>
       </c>
       <c r="R16">
-        <v>1.18</v>
+        <v>1.28</v>
       </c>
       <c r="S16">
+        <v>3.75</v>
+      </c>
+      <c r="T16">
+        <v>1.81</v>
+      </c>
+      <c r="U16">
         <v>1.98</v>
       </c>
-      <c r="T16">
-        <v>1.11</v>
-      </c>
-      <c r="U16">
-        <v>1.11</v>
-      </c>
       <c r="V16">
-        <v>1.07</v>
+        <v>1.33</v>
       </c>
       <c r="W16">
-        <v>1.64</v>
+        <v>1.7</v>
       </c>
       <c r="X16">
-        <v>1000</v>
+        <v>14.5</v>
       </c>
       <c r="Y16">
-        <v>1000</v>
+        <v>14.5</v>
       </c>
       <c r="Z16">
-        <v>1000</v>
+        <v>30</v>
       </c>
       <c r="AA16">
-        <v>1000</v>
+        <v>85</v>
       </c>
       <c r="AB16">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="AC16">
-        <v>1000</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AD16">
-        <v>1000</v>
+        <v>18</v>
       </c>
       <c r="AE16">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AF16">
-        <v>1000</v>
+        <v>16.5</v>
       </c>
       <c r="AG16">
-        <v>1000</v>
+        <v>13</v>
       </c>
       <c r="AH16">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="AI16">
-        <v>1000</v>
+        <v>70</v>
       </c>
       <c r="AJ16">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="AK16">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="AL16">
-        <v>1000</v>
+        <v>50</v>
       </c>
       <c r="AM16">
-        <v>1000</v>
+        <v>130</v>
       </c>
       <c r="AN16">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="AO16">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AP16">
-        <v>1.01</v>
+        <v>9.4</v>
       </c>
       <c r="AQ16">
-        <v>1.01</v>
+        <v>9.6</v>
       </c>
       <c r="AR16">
-        <v>1.01</v>
+        <v>19</v>
       </c>
       <c r="AS16">
-        <v>1.01</v>
+        <v>4.8</v>
       </c>
       <c r="AT16">
-        <v>1.01</v>
+        <v>7.6</v>
       </c>
       <c r="AU16">
-        <v>1.01</v>
+        <v>6</v>
       </c>
       <c r="AV16">
-        <v>1.01</v>
+        <v>11.5</v>
       </c>
       <c r="AW16">
-        <v>1.01</v>
+        <v>4.6</v>
       </c>
       <c r="AX16">
-        <v>1.01</v>
+        <v>11</v>
       </c>
       <c r="AY16">
-        <v>1.01</v>
+        <v>8.6</v>
       </c>
       <c r="AZ16">
-        <v>1.01</v>
+        <v>14</v>
       </c>
       <c r="BA16">
-        <v>1.01</v>
+        <v>4.7</v>
       </c>
       <c r="BB16">
-        <v>1.01</v>
+        <v>4.4</v>
       </c>
       <c r="BC16">
-        <v>1.01</v>
+        <v>20</v>
       </c>
       <c r="BD16">
-        <v>1.01</v>
+        <v>4.6</v>
       </c>
       <c r="BE16">
-        <v>1.01</v>
+        <v>4.9</v>
       </c>
       <c r="BF16">
-        <v>1.01</v>
+        <v>16.5</v>
       </c>
       <c r="BG16">
-        <v>1.01</v>
+        <v>4.7</v>
       </c>
       <c r="BH16">
-        <v>1000</v>
+        <v>3.3</v>
       </c>
       <c r="BI16">
-        <v>1.04</v>
+        <v>2.66</v>
       </c>
       <c r="BJ16">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="BK16">
-        <v>1.04</v>
+        <v>5.2</v>
       </c>
       <c r="BL16">
         <v>1000</v>
       </c>
       <c r="BM16">
-        <v>1.04</v>
+        <v>9.6</v>
       </c>
       <c r="BN16">
-        <v>1000</v>
+        <v>5.2</v>
       </c>
       <c r="BO16">
-        <v>1.04</v>
+        <v>4</v>
       </c>
       <c r="BP16">
-        <v>1000</v>
+        <v>18.5</v>
       </c>
       <c r="BQ16">
-        <v>1.04</v>
+        <v>6.6</v>
       </c>
       <c r="BR16">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="BS16">
-        <v>1.04</v>
+        <v>8</v>
       </c>
       <c r="BT16">
-        <v>1000</v>
+        <v>7</v>
       </c>
       <c r="BU16">
-        <v>1.04</v>
+        <v>5.8</v>
       </c>
       <c r="BV16">
         <v>1000</v>
       </c>
       <c r="BW16">
-        <v>1.04</v>
+        <v>7.8</v>
       </c>
       <c r="BX16">
         <v>1000</v>
       </c>
       <c r="BY16">
-        <v>1.04</v>
+        <v>8.4</v>
       </c>
       <c r="BZ16">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="CA16">
-        <v>1.04</v>
+        <v>7.8</v>
       </c>
       <c r="CB16" t="s">
         <v>134</v>
@@ -4645,109 +4645,109 @@
         <v>1.65</v>
       </c>
       <c r="G17">
-        <v>1.83</v>
+        <v>1.81</v>
       </c>
       <c r="H17">
         <v>5.9</v>
       </c>
       <c r="I17">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="J17">
-        <v>3.2</v>
+        <v>3.5</v>
       </c>
       <c r="K17">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="L17">
-        <v>1.42</v>
+        <v>1.34</v>
       </c>
       <c r="M17">
-        <v>1.01</v>
+        <v>1.09</v>
       </c>
       <c r="N17">
-        <v>2.4</v>
+        <v>2.96</v>
       </c>
       <c r="O17">
-        <v>1.02</v>
+        <v>1.41</v>
       </c>
       <c r="P17">
+        <v>1.67</v>
+      </c>
+      <c r="Q17">
+        <v>2.2</v>
+      </c>
+      <c r="R17">
         <v>1.25</v>
-      </c>
-      <c r="Q17">
-        <v>2</v>
-      </c>
-      <c r="R17">
-        <v>1.13</v>
       </c>
       <c r="S17">
         <v>4.2</v>
       </c>
       <c r="T17">
-        <v>1.11</v>
+        <v>2.1</v>
       </c>
       <c r="U17">
-        <v>1.11</v>
+        <v>1.75</v>
       </c>
       <c r="V17">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="W17">
-        <v>2.2</v>
+        <v>2.22</v>
       </c>
       <c r="X17">
-        <v>1000</v>
+        <v>13</v>
       </c>
       <c r="Y17">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="Z17">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AA17">
-        <v>1000</v>
+        <v>250</v>
       </c>
       <c r="AB17">
-        <v>1000</v>
+        <v>7.8</v>
       </c>
       <c r="AC17">
-        <v>1000</v>
+        <v>9.6</v>
       </c>
       <c r="AD17">
-        <v>1000</v>
+        <v>30</v>
       </c>
       <c r="AE17">
-        <v>1000</v>
+        <v>140</v>
       </c>
       <c r="AF17">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="AG17">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="AH17">
-        <v>1000</v>
+        <v>30</v>
       </c>
       <c r="AI17">
-        <v>1000</v>
+        <v>140</v>
       </c>
       <c r="AJ17">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="AK17">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="AL17">
-        <v>70</v>
+        <v>60</v>
       </c>
       <c r="AM17">
-        <v>1000</v>
+        <v>220</v>
       </c>
       <c r="AN17">
-        <v>1000</v>
+        <v>17</v>
       </c>
       <c r="AO17">
-        <v>1000</v>
+        <v>220</v>
       </c>
       <c r="AP17">
         <v>8.6</v>
@@ -4756,25 +4756,25 @@
         <v>13</v>
       </c>
       <c r="AR17">
-        <v>1.01</v>
+        <v>38</v>
       </c>
       <c r="AS17">
-        <v>1.01</v>
+        <v>5.1</v>
       </c>
       <c r="AT17">
         <v>5.3</v>
       </c>
       <c r="AU17">
-        <v>6.6</v>
+        <v>7.2</v>
       </c>
       <c r="AV17">
         <v>19.5</v>
       </c>
       <c r="AW17">
-        <v>1.01</v>
+        <v>5</v>
       </c>
       <c r="AX17">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="AY17">
         <v>8</v>
@@ -4783,7 +4783,7 @@
         <v>19</v>
       </c>
       <c r="BA17">
-        <v>1.01</v>
+        <v>5</v>
       </c>
       <c r="BB17">
         <v>13.5</v>
@@ -4792,70 +4792,70 @@
         <v>16</v>
       </c>
       <c r="BD17">
-        <v>1.01</v>
+        <v>4.8</v>
       </c>
       <c r="BE17">
-        <v>1.01</v>
+        <v>5.1</v>
       </c>
       <c r="BF17">
         <v>11</v>
       </c>
       <c r="BG17">
-        <v>1.01</v>
+        <v>5.1</v>
       </c>
       <c r="BH17">
-        <v>3.15</v>
+        <v>1000</v>
       </c>
       <c r="BI17">
-        <v>2.54</v>
+        <v>1.82</v>
       </c>
       <c r="BJ17">
-        <v>12.5</v>
+        <v>16</v>
       </c>
       <c r="BK17">
-        <v>1.04</v>
+        <v>1.64</v>
       </c>
       <c r="BL17">
         <v>1000</v>
       </c>
       <c r="BM17">
-        <v>1.04</v>
+        <v>1.82</v>
       </c>
       <c r="BN17">
-        <v>4.2</v>
+        <v>5.4</v>
       </c>
       <c r="BO17">
-        <v>3.3</v>
+        <v>2.88</v>
       </c>
       <c r="BP17">
+        <v>17</v>
+      </c>
+      <c r="BQ17">
+        <v>1.65</v>
+      </c>
+      <c r="BR17">
+        <v>46</v>
+      </c>
+      <c r="BS17">
+        <v>1.75</v>
+      </c>
+      <c r="BT17">
         <v>13</v>
       </c>
-      <c r="BQ17">
-        <v>1.04</v>
-      </c>
-      <c r="BR17">
-        <v>1000</v>
-      </c>
-      <c r="BS17">
-        <v>1.04</v>
-      </c>
-      <c r="BT17">
-        <v>10</v>
-      </c>
       <c r="BU17">
-        <v>1.04</v>
+        <v>1.6</v>
       </c>
       <c r="BV17">
         <v>1000</v>
       </c>
       <c r="BW17">
-        <v>1.04</v>
+        <v>1.79</v>
       </c>
       <c r="BX17">
         <v>1000</v>
       </c>
       <c r="BY17">
-        <v>1.04</v>
+        <v>1.79</v>
       </c>
       <c r="BZ17">
         <v>0</v>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-08-11.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-08-11.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="176" uniqueCount="135">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="182" uniqueCount="137">
   <si>
     <t>League</t>
   </si>
@@ -268,18 +268,18 @@
     <t>Argentinian Primera Division</t>
   </si>
   <si>
+    <t>Swedish Superettan</t>
+  </si>
+  <si>
+    <t>South African Premier Division</t>
+  </si>
+  <si>
+    <t>Colombian Primera B</t>
+  </si>
+  <si>
     <t>Colombian Primera A</t>
   </si>
   <si>
-    <t>Swedish Superettan</t>
-  </si>
-  <si>
-    <t>South African Premier Division</t>
-  </si>
-  <si>
-    <t>Colombian Primera B</t>
-  </si>
-  <si>
     <t>CONMEBOL Copa Libertadores</t>
   </si>
   <si>
@@ -298,9 +298,6 @@
     <t>00:15:00</t>
   </si>
   <si>
-    <t>01:05:00</t>
-  </si>
-  <si>
     <t>17:00:00</t>
   </si>
   <si>
@@ -310,6 +307,9 @@
     <t>20:30:00</t>
   </si>
   <si>
+    <t>21:00:00</t>
+  </si>
+  <si>
     <t>22:00:00</t>
   </si>
   <si>
@@ -334,27 +334,27 @@
     <t>Union Santa Fe</t>
   </si>
   <si>
-    <t>Junior FC Barranquilla</t>
-  </si>
-  <si>
     <t>Helsingborgs</t>
   </si>
   <si>
+    <t>Polokwane City</t>
+  </si>
+  <si>
+    <t>Marumo Gallants FC</t>
+  </si>
+  <si>
     <t>Chippa Utd</t>
   </si>
   <si>
     <t>TS Galaxy FC</t>
   </si>
   <si>
-    <t>Polokwane City</t>
-  </si>
-  <si>
-    <t>Marumo Gallants FC</t>
-  </si>
-  <si>
     <t>Real Santander</t>
   </si>
   <si>
+    <t>Aguilas Doradas</t>
+  </si>
+  <si>
     <t>Fluminense</t>
   </si>
   <si>
@@ -364,6 +364,9 @@
     <t>Real Cartagena</t>
   </si>
   <si>
+    <t>Ind Medellin</t>
+  </si>
+  <si>
     <t>Puerto Montt</t>
   </si>
   <si>
@@ -382,27 +385,27 @@
     <t>Central Cordoba (SdE)</t>
   </si>
   <si>
-    <t>Deportivo Pereira</t>
-  </si>
-  <si>
     <t>Varnamo</t>
   </si>
   <si>
+    <t>Stellenbosch FC</t>
+  </si>
+  <si>
+    <t>Kruger United FC</t>
+  </si>
+  <si>
     <t>Richards Bay FC</t>
   </si>
   <si>
     <t>Mamelodi Sundowns</t>
   </si>
   <si>
-    <t>Stellenbosch FC</t>
-  </si>
-  <si>
-    <t>Kruger United FC</t>
-  </si>
-  <si>
     <t>Barranquilla</t>
   </si>
   <si>
+    <t>Llaneros FC</t>
+  </si>
+  <si>
     <t>Independiente Rivadavia</t>
   </si>
   <si>
@@ -412,13 +415,16 @@
     <t>Bogota</t>
   </si>
   <si>
+    <t>Millonarios</t>
+  </si>
+  <si>
     <t>Union Espanola</t>
   </si>
   <si>
     <t>Orsomarso</t>
   </si>
   <si>
-    <t>2026-08-10 12:32:55</t>
+    <t>2026-08-10 14:41:40</t>
   </si>
 </sst>
 </file>
@@ -750,7 +756,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:CB17"/>
+  <dimension ref="A1:CB18"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:80">
@@ -1009,37 +1015,37 @@
         <v>102</v>
       </c>
       <c r="E2" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="F2">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="G2">
-        <v>990</v>
+        <v>55</v>
       </c>
       <c r="H2">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="I2">
         <v>1.38</v>
       </c>
       <c r="J2">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="K2">
-        <v>8</v>
+        <v>6.6</v>
       </c>
       <c r="L2">
-        <v>1.31</v>
+        <v>1.33</v>
       </c>
       <c r="M2">
         <v>1.04</v>
       </c>
       <c r="N2">
-        <v>4.4</v>
+        <v>3</v>
       </c>
       <c r="O2">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="P2">
         <v>2.22</v>
@@ -1054,10 +1060,10 @@
         <v>2.66</v>
       </c>
       <c r="T2">
-        <v>1.66</v>
+        <v>1.68</v>
       </c>
       <c r="U2">
-        <v>1.49</v>
+        <v>1.73</v>
       </c>
       <c r="V2">
         <v>3.6</v>
@@ -1126,7 +1132,7 @@
         <v>1.01</v>
       </c>
       <c r="AR2">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AS2">
         <v>1.01</v>
@@ -1234,7 +1240,7 @@
         <v>1.04</v>
       </c>
       <c r="CB2" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
     </row>
     <row r="3" spans="1:80">
@@ -1251,25 +1257,25 @@
         <v>103</v>
       </c>
       <c r="E3" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="F3">
-        <v>2.4</v>
+        <v>2.42</v>
       </c>
       <c r="G3">
-        <v>2.46</v>
+        <v>2.5</v>
       </c>
       <c r="H3">
         <v>3.15</v>
       </c>
       <c r="I3">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="J3">
         <v>3.5</v>
       </c>
       <c r="K3">
-        <v>3.7</v>
+        <v>3.6</v>
       </c>
       <c r="L3">
         <v>1.47</v>
@@ -1284,13 +1290,13 @@
         <v>1.38</v>
       </c>
       <c r="P3">
-        <v>1.82</v>
+        <v>1.83</v>
       </c>
       <c r="Q3">
         <v>2.16</v>
       </c>
       <c r="R3">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="S3">
         <v>4</v>
@@ -1299,13 +1305,13 @@
         <v>1.86</v>
       </c>
       <c r="U3">
-        <v>2.06</v>
+        <v>2.08</v>
       </c>
       <c r="V3">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="W3">
-        <v>1.68</v>
+        <v>1.66</v>
       </c>
       <c r="X3">
         <v>13</v>
@@ -1317,10 +1323,10 @@
         <v>23</v>
       </c>
       <c r="AA3">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="AB3">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="AC3">
         <v>7.8</v>
@@ -1329,10 +1335,10 @@
         <v>14</v>
       </c>
       <c r="AE3">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="AF3">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="AG3">
         <v>11.5</v>
@@ -1341,13 +1347,13 @@
         <v>23</v>
       </c>
       <c r="AI3">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="AJ3">
         <v>38</v>
       </c>
       <c r="AK3">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="AL3">
         <v>50</v>
@@ -1374,16 +1380,16 @@
         <v>44</v>
       </c>
       <c r="AT3">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="AU3">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="AV3">
         <v>12</v>
       </c>
       <c r="AW3">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="AX3">
         <v>13.5</v>
@@ -1413,7 +1419,7 @@
         <v>18</v>
       </c>
       <c r="BG3">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="BH3">
         <v>3.7</v>
@@ -1422,61 +1428,61 @@
         <v>2.56</v>
       </c>
       <c r="BJ3">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="BK3">
-        <v>3.4</v>
+        <v>4.4</v>
       </c>
       <c r="BL3">
         <v>1000</v>
       </c>
       <c r="BM3">
-        <v>4.6</v>
+        <v>7</v>
       </c>
       <c r="BN3">
-        <v>6.4</v>
+        <v>5.3</v>
       </c>
       <c r="BO3">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="BP3">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="BQ3">
-        <v>3.95</v>
+        <v>5.6</v>
       </c>
       <c r="BR3">
         <v>42</v>
       </c>
       <c r="BS3">
-        <v>4.2</v>
+        <v>6.2</v>
       </c>
       <c r="BT3">
-        <v>7.6</v>
+        <v>6.4</v>
       </c>
       <c r="BU3">
         <v>4.8</v>
       </c>
       <c r="BV3">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="BW3">
-        <v>4.1</v>
+        <v>6</v>
       </c>
       <c r="BX3">
         <v>50</v>
       </c>
       <c r="BY3">
-        <v>4.3</v>
+        <v>6.4</v>
       </c>
       <c r="BZ3">
         <v>38</v>
       </c>
       <c r="CA3">
-        <v>4.2</v>
+        <v>6.2</v>
       </c>
       <c r="CB3" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
     </row>
     <row r="4" spans="1:80">
@@ -1493,25 +1499,25 @@
         <v>104</v>
       </c>
       <c r="E4" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="F4">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="G4">
-        <v>1.81</v>
+        <v>1.8</v>
       </c>
       <c r="H4">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="I4">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="J4">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="K4">
-        <v>3.9</v>
+        <v>3.85</v>
       </c>
       <c r="L4">
         <v>1.49</v>
@@ -1520,19 +1526,19 @@
         <v>1.09</v>
       </c>
       <c r="N4">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="O4">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="P4">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="Q4">
         <v>2.28</v>
       </c>
       <c r="R4">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="S4">
         <v>4.4</v>
@@ -1541,82 +1547,82 @@
         <v>2.08</v>
       </c>
       <c r="U4">
-        <v>1.76</v>
+        <v>1.8</v>
       </c>
       <c r="V4">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="W4">
-        <v>2.2</v>
+        <v>2.24</v>
       </c>
       <c r="X4">
-        <v>13.5</v>
+        <v>12.5</v>
       </c>
       <c r="Y4">
         <v>17</v>
       </c>
       <c r="Z4">
-        <v>48</v>
+        <v>75</v>
       </c>
       <c r="AA4">
         <v>200</v>
       </c>
       <c r="AB4">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="AC4">
         <v>8.6</v>
       </c>
       <c r="AD4">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="AE4">
-        <v>120</v>
+        <v>160</v>
       </c>
       <c r="AF4">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AG4">
         <v>11</v>
       </c>
       <c r="AH4">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AI4">
-        <v>120</v>
+        <v>150</v>
       </c>
       <c r="AJ4">
+        <v>19.5</v>
+      </c>
+      <c r="AK4">
         <v>22</v>
       </c>
-      <c r="AK4">
-        <v>25</v>
-      </c>
       <c r="AL4">
-        <v>50</v>
+        <v>75</v>
       </c>
       <c r="AM4">
+        <v>180</v>
+      </c>
+      <c r="AN4">
+        <v>15</v>
+      </c>
+      <c r="AO4">
         <v>190</v>
-      </c>
-      <c r="AN4">
-        <v>17.5</v>
-      </c>
-      <c r="AO4">
-        <v>170</v>
       </c>
       <c r="AP4">
         <v>9.800000000000001</v>
       </c>
       <c r="AQ4">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="AR4">
-        <v>6.8</v>
+        <v>32</v>
       </c>
       <c r="AS4">
-        <v>7.6</v>
+        <v>10.5</v>
       </c>
       <c r="AT4">
-        <v>6</v>
+        <v>6.4</v>
       </c>
       <c r="AU4">
         <v>7.4</v>
@@ -1625,37 +1631,37 @@
         <v>20</v>
       </c>
       <c r="AW4">
-        <v>7.4</v>
+        <v>55</v>
       </c>
       <c r="AX4">
-        <v>8.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="AY4">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AZ4">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="BA4">
-        <v>7.4</v>
+        <v>55</v>
       </c>
       <c r="BB4">
         <v>16</v>
       </c>
       <c r="BC4">
-        <v>18.5</v>
+        <v>16.5</v>
       </c>
       <c r="BD4">
         <v>36</v>
       </c>
       <c r="BE4">
-        <v>7.6</v>
+        <v>10.5</v>
       </c>
       <c r="BF4">
         <v>13</v>
       </c>
       <c r="BG4">
-        <v>7.4</v>
+        <v>10</v>
       </c>
       <c r="BH4">
         <v>3.2</v>
@@ -1667,58 +1673,58 @@
         <v>11.5</v>
       </c>
       <c r="BK4">
-        <v>8.6</v>
+        <v>5.5</v>
       </c>
       <c r="BL4">
         <v>1000</v>
       </c>
       <c r="BM4">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="BN4">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="BO4">
-        <v>3.65</v>
+        <v>3.4</v>
       </c>
       <c r="BP4">
         <v>13.5</v>
       </c>
       <c r="BQ4">
-        <v>6</v>
+        <v>5.9</v>
       </c>
       <c r="BR4">
         <v>1000</v>
       </c>
       <c r="BS4">
-        <v>8.4</v>
+        <v>8</v>
       </c>
       <c r="BT4">
         <v>9.4</v>
       </c>
       <c r="BU4">
-        <v>7</v>
+        <v>4.9</v>
       </c>
       <c r="BV4">
         <v>1000</v>
       </c>
       <c r="BW4">
-        <v>9.4</v>
+        <v>9</v>
       </c>
       <c r="BX4">
         <v>1000</v>
       </c>
       <c r="BY4">
-        <v>9.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BZ4">
         <v>30</v>
       </c>
       <c r="CA4">
-        <v>8.199999999999999</v>
+        <v>7.8</v>
       </c>
       <c r="CB4" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
     </row>
     <row r="5" spans="1:80">
@@ -1735,25 +1741,25 @@
         <v>105</v>
       </c>
       <c r="E5" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="F5">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="G5">
-        <v>1.59</v>
+        <v>1.6</v>
       </c>
       <c r="H5">
         <v>7.6</v>
       </c>
       <c r="I5">
-        <v>7.8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="J5">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="K5">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="L5">
         <v>1.46</v>
@@ -1774,7 +1780,7 @@
         <v>2.22</v>
       </c>
       <c r="R5">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="S5">
         <v>4.2</v>
@@ -1783,7 +1789,7 @@
         <v>2.26</v>
       </c>
       <c r="U5">
-        <v>1.73</v>
+        <v>1.75</v>
       </c>
       <c r="V5">
         <v>1.14</v>
@@ -1807,10 +1813,10 @@
         <v>6.6</v>
       </c>
       <c r="AC5">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AD5">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AE5">
         <v>1000</v>
@@ -1828,19 +1834,19 @@
         <v>150</v>
       </c>
       <c r="AJ5">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="AK5">
         <v>19</v>
       </c>
       <c r="AL5">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="AM5">
         <v>1000</v>
       </c>
       <c r="AN5">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AO5">
         <v>1000</v>
@@ -1852,7 +1858,7 @@
         <v>17.5</v>
       </c>
       <c r="AR5">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AS5">
         <v>95</v>
@@ -1864,22 +1870,22 @@
         <v>8.6</v>
       </c>
       <c r="AV5">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="AW5">
-        <v>42</v>
+        <v>50</v>
       </c>
       <c r="AX5">
         <v>7.2</v>
       </c>
       <c r="AY5">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="AZ5">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="BA5">
-        <v>44</v>
+        <v>55</v>
       </c>
       <c r="BB5">
         <v>13</v>
@@ -1888,7 +1894,7 @@
         <v>17</v>
       </c>
       <c r="BD5">
-        <v>27</v>
+        <v>38</v>
       </c>
       <c r="BE5">
         <v>48</v>
@@ -1909,7 +1915,7 @@
         <v>13</v>
       </c>
       <c r="BK5">
-        <v>9.800000000000001</v>
+        <v>5.9</v>
       </c>
       <c r="BL5">
         <v>220</v>
@@ -1939,7 +1945,7 @@
         <v>11.5</v>
       </c>
       <c r="BU5">
-        <v>5.6</v>
+        <v>5.5</v>
       </c>
       <c r="BV5">
         <v>85</v>
@@ -1948,19 +1954,19 @@
         <v>9.6</v>
       </c>
       <c r="BX5">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="BY5">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="BZ5">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="CA5">
         <v>7.4</v>
       </c>
       <c r="CB5" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
     </row>
     <row r="6" spans="1:80">
@@ -1977,211 +1983,211 @@
         <v>106</v>
       </c>
       <c r="E6" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="F6">
-        <v>1.34</v>
+        <v>2.14</v>
       </c>
       <c r="G6">
-        <v>1.36</v>
+        <v>2.26</v>
       </c>
       <c r="H6">
+        <v>3.3</v>
+      </c>
+      <c r="I6">
+        <v>3.55</v>
+      </c>
+      <c r="J6">
+        <v>3.9</v>
+      </c>
+      <c r="K6">
+        <v>4.2</v>
+      </c>
+      <c r="L6">
+        <v>1.33</v>
+      </c>
+      <c r="M6">
+        <v>1.04</v>
+      </c>
+      <c r="N6">
+        <v>5.2</v>
+      </c>
+      <c r="O6">
+        <v>1.22</v>
+      </c>
+      <c r="P6">
+        <v>2.38</v>
+      </c>
+      <c r="Q6">
+        <v>1.64</v>
+      </c>
+      <c r="R6">
+        <v>1.55</v>
+      </c>
+      <c r="S6">
+        <v>2.6</v>
+      </c>
+      <c r="T6">
+        <v>1.59</v>
+      </c>
+      <c r="U6">
+        <v>2.5</v>
+      </c>
+      <c r="V6">
+        <v>1.4</v>
+      </c>
+      <c r="W6">
+        <v>1.8</v>
+      </c>
+      <c r="X6">
+        <v>26</v>
+      </c>
+      <c r="Y6">
+        <v>22</v>
+      </c>
+      <c r="Z6">
+        <v>36</v>
+      </c>
+      <c r="AA6">
+        <v>80</v>
+      </c>
+      <c r="AB6">
+        <v>13.5</v>
+      </c>
+      <c r="AC6">
+        <v>9.4</v>
+      </c>
+      <c r="AD6">
+        <v>15</v>
+      </c>
+      <c r="AE6">
+        <v>44</v>
+      </c>
+      <c r="AF6">
+        <v>21</v>
+      </c>
+      <c r="AG6">
+        <v>13.5</v>
+      </c>
+      <c r="AH6">
+        <v>20</v>
+      </c>
+      <c r="AI6">
+        <v>46</v>
+      </c>
+      <c r="AJ6">
+        <v>36</v>
+      </c>
+      <c r="AK6">
+        <v>25</v>
+      </c>
+      <c r="AL6">
+        <v>38</v>
+      </c>
+      <c r="AM6">
+        <v>85</v>
+      </c>
+      <c r="AN6">
+        <v>14</v>
+      </c>
+      <c r="AO6">
+        <v>32</v>
+      </c>
+      <c r="AP6">
+        <v>7.2</v>
+      </c>
+      <c r="AQ6">
+        <v>15</v>
+      </c>
+      <c r="AR6">
+        <v>7</v>
+      </c>
+      <c r="AS6">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AT6">
         <v>11.5</v>
       </c>
-      <c r="I6">
-        <v>12.5</v>
-      </c>
-      <c r="J6">
-        <v>5.3</v>
-      </c>
-      <c r="K6">
-        <v>5.8</v>
-      </c>
-      <c r="L6">
-        <v>1.36</v>
-      </c>
-      <c r="M6">
-        <v>1.05</v>
-      </c>
-      <c r="N6">
-        <v>4.4</v>
-      </c>
-      <c r="O6">
-        <v>1.26</v>
-      </c>
-      <c r="P6">
-        <v>2.16</v>
-      </c>
-      <c r="Q6">
-        <v>1.81</v>
-      </c>
-      <c r="R6">
-        <v>1.44</v>
-      </c>
-      <c r="S6">
-        <v>3.1</v>
-      </c>
-      <c r="T6">
-        <v>2.2</v>
-      </c>
-      <c r="U6">
-        <v>1.76</v>
-      </c>
-      <c r="V6">
-        <v>1.09</v>
-      </c>
-      <c r="W6">
-        <v>3.7</v>
-      </c>
-      <c r="X6">
-        <v>22</v>
-      </c>
-      <c r="Y6">
-        <v>38</v>
-      </c>
-      <c r="Z6">
-        <v>140</v>
-      </c>
-      <c r="AA6">
-        <v>1000</v>
-      </c>
-      <c r="AB6">
-        <v>8.4</v>
-      </c>
-      <c r="AC6">
-        <v>12.5</v>
-      </c>
-      <c r="AD6">
-        <v>55</v>
-      </c>
-      <c r="AE6">
-        <v>270</v>
-      </c>
-      <c r="AF6">
-        <v>8</v>
-      </c>
-      <c r="AG6">
-        <v>11.5</v>
-      </c>
-      <c r="AH6">
-        <v>38</v>
-      </c>
-      <c r="AI6">
-        <v>200</v>
-      </c>
-      <c r="AJ6">
-        <v>12.5</v>
-      </c>
-      <c r="AK6">
-        <v>18</v>
-      </c>
-      <c r="AL6">
-        <v>55</v>
-      </c>
-      <c r="AM6">
-        <v>240</v>
-      </c>
-      <c r="AN6">
-        <v>6</v>
-      </c>
-      <c r="AO6">
-        <v>420</v>
-      </c>
-      <c r="AP6">
-        <v>5.8</v>
-      </c>
-      <c r="AQ6">
-        <v>6.6</v>
-      </c>
-      <c r="AR6">
-        <v>7.2</v>
-      </c>
-      <c r="AS6">
-        <v>7.6</v>
-      </c>
-      <c r="AT6">
-        <v>7.2</v>
-      </c>
       <c r="AU6">
-        <v>10.5</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AV6">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="AW6">
         <v>7.4</v>
       </c>
       <c r="AX6">
-        <v>6.6</v>
+        <v>14</v>
       </c>
       <c r="AY6">
-        <v>9.199999999999999</v>
+        <v>10</v>
       </c>
       <c r="AZ6">
-        <v>6.6</v>
+        <v>13.5</v>
       </c>
       <c r="BA6">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="BB6">
-        <v>9.4</v>
+        <v>7</v>
       </c>
       <c r="BC6">
-        <v>5.6</v>
+        <v>6.8</v>
       </c>
       <c r="BD6">
-        <v>6.6</v>
+        <v>7</v>
       </c>
       <c r="BE6">
-        <v>7.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BF6">
-        <v>5.4</v>
+        <v>10.5</v>
       </c>
       <c r="BG6">
-        <v>7.4</v>
+        <v>21</v>
       </c>
       <c r="BH6">
-        <v>3.95</v>
+        <v>4.1</v>
       </c>
       <c r="BI6">
-        <v>3.1</v>
+        <v>3.65</v>
       </c>
       <c r="BJ6">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="BK6">
+        <v>5.7</v>
+      </c>
+      <c r="BL6">
+        <v>1000</v>
+      </c>
+      <c r="BM6">
         <v>13.5</v>
       </c>
-      <c r="BK6">
-        <v>6</v>
-      </c>
-      <c r="BL6">
-        <v>1000</v>
-      </c>
-      <c r="BM6">
-        <v>10</v>
-      </c>
       <c r="BN6">
-        <v>3.8</v>
+        <v>5.3</v>
       </c>
       <c r="BO6">
-        <v>3</v>
+        <v>4.7</v>
       </c>
       <c r="BP6">
-        <v>8.199999999999999</v>
+        <v>1000</v>
       </c>
       <c r="BQ6">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="BR6">
         <v>1000</v>
       </c>
       <c r="BS6">
-        <v>7.6</v>
+        <v>9.6</v>
       </c>
       <c r="BT6">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="BU6">
-        <v>6.2</v>
+        <v>5</v>
       </c>
       <c r="BV6">
         <v>1000</v>
@@ -2193,16 +2199,16 @@
         <v>1000</v>
       </c>
       <c r="BY6">
-        <v>9.800000000000001</v>
+        <v>10.5</v>
       </c>
       <c r="BZ6">
-        <v>14.5</v>
+        <v>0</v>
       </c>
       <c r="CA6">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="CB6" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
     </row>
     <row r="7" spans="1:80">
@@ -2219,958 +2225,958 @@
         <v>107</v>
       </c>
       <c r="E7" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="F7">
-        <v>2.12</v>
+        <v>2.48</v>
       </c>
       <c r="G7">
-        <v>2.26</v>
+        <v>2.7</v>
       </c>
       <c r="H7">
-        <v>3.3</v>
+        <v>3.7</v>
       </c>
       <c r="I7">
-        <v>3.6</v>
+        <v>3.9</v>
       </c>
       <c r="J7">
-        <v>3.9</v>
+        <v>2.7</v>
       </c>
       <c r="K7">
-        <v>4.2</v>
+        <v>3.05</v>
       </c>
       <c r="L7">
-        <v>1.33</v>
+        <v>1.64</v>
       </c>
       <c r="M7">
-        <v>1.04</v>
+        <v>1.16</v>
       </c>
       <c r="N7">
+        <v>2.22</v>
+      </c>
+      <c r="O7">
+        <v>1.66</v>
+      </c>
+      <c r="P7">
+        <v>1.4</v>
+      </c>
+      <c r="Q7">
+        <v>2.98</v>
+      </c>
+      <c r="R7">
+        <v>1.13</v>
+      </c>
+      <c r="S7">
+        <v>6</v>
+      </c>
+      <c r="T7">
+        <v>2.32</v>
+      </c>
+      <c r="U7">
+        <v>1.64</v>
+      </c>
+      <c r="V7">
+        <v>1.34</v>
+      </c>
+      <c r="W7">
+        <v>1.59</v>
+      </c>
+      <c r="X7">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="Y7">
+        <v>9.4</v>
+      </c>
+      <c r="Z7">
+        <v>27</v>
+      </c>
+      <c r="AA7">
+        <v>110</v>
+      </c>
+      <c r="AB7">
+        <v>7.2</v>
+      </c>
+      <c r="AC7">
+        <v>7.2</v>
+      </c>
+      <c r="AD7">
+        <v>18.5</v>
+      </c>
+      <c r="AE7">
+        <v>85</v>
+      </c>
+      <c r="AF7">
+        <v>15.5</v>
+      </c>
+      <c r="AG7">
+        <v>14.5</v>
+      </c>
+      <c r="AH7">
+        <v>29</v>
+      </c>
+      <c r="AI7">
+        <v>130</v>
+      </c>
+      <c r="AJ7">
+        <v>55</v>
+      </c>
+      <c r="AK7">
+        <v>55</v>
+      </c>
+      <c r="AL7">
+        <v>100</v>
+      </c>
+      <c r="AM7">
+        <v>300</v>
+      </c>
+      <c r="AN7">
+        <v>65</v>
+      </c>
+      <c r="AO7">
+        <v>130</v>
+      </c>
+      <c r="AP7">
+        <v>5.4</v>
+      </c>
+      <c r="AQ7">
+        <v>7.4</v>
+      </c>
+      <c r="AR7">
+        <v>19</v>
+      </c>
+      <c r="AS7">
+        <v>7.2</v>
+      </c>
+      <c r="AT7">
+        <v>5.9</v>
+      </c>
+      <c r="AU7">
+        <v>6</v>
+      </c>
+      <c r="AV7">
+        <v>14.5</v>
+      </c>
+      <c r="AW7">
+        <v>7</v>
+      </c>
+      <c r="AX7">
+        <v>12</v>
+      </c>
+      <c r="AY7">
+        <v>11.5</v>
+      </c>
+      <c r="AZ7">
+        <v>20</v>
+      </c>
+      <c r="BA7">
+        <v>7.2</v>
+      </c>
+      <c r="BB7">
+        <v>29</v>
+      </c>
+      <c r="BC7">
+        <v>27</v>
+      </c>
+      <c r="BD7">
+        <v>7.2</v>
+      </c>
+      <c r="BE7">
+        <v>7.4</v>
+      </c>
+      <c r="BF7">
+        <v>32</v>
+      </c>
+      <c r="BG7">
+        <v>7.2</v>
+      </c>
+      <c r="BH7">
+        <v>2.78</v>
+      </c>
+      <c r="BI7">
+        <v>2.04</v>
+      </c>
+      <c r="BJ7">
+        <v>14</v>
+      </c>
+      <c r="BK7">
+        <v>4.4</v>
+      </c>
+      <c r="BL7">
+        <v>1000</v>
+      </c>
+      <c r="BM7">
+        <v>6.2</v>
+      </c>
+      <c r="BN7">
+        <v>6.2</v>
+      </c>
+      <c r="BO7">
+        <v>4.5</v>
+      </c>
+      <c r="BP7">
+        <v>28</v>
+      </c>
+      <c r="BQ7">
         <v>5.2</v>
       </c>
-      <c r="O7">
-        <v>1.22</v>
-      </c>
-      <c r="P7">
-        <v>2.36</v>
-      </c>
-      <c r="Q7">
-        <v>1.64</v>
-      </c>
-      <c r="R7">
-        <v>1.54</v>
-      </c>
-      <c r="S7">
-        <v>2.62</v>
-      </c>
-      <c r="T7">
-        <v>1.59</v>
-      </c>
-      <c r="U7">
-        <v>2.48</v>
-      </c>
-      <c r="V7">
-        <v>1.39</v>
-      </c>
-      <c r="W7">
-        <v>1.8</v>
-      </c>
-      <c r="X7">
-        <v>26</v>
-      </c>
-      <c r="Y7">
-        <v>22</v>
-      </c>
-      <c r="Z7">
-        <v>36</v>
-      </c>
-      <c r="AA7">
+      <c r="BR7">
+        <v>70</v>
+      </c>
+      <c r="BS7">
+        <v>5.8</v>
+      </c>
+      <c r="BT7">
+        <v>6.8</v>
+      </c>
+      <c r="BU7">
+        <v>5.6</v>
+      </c>
+      <c r="BV7">
+        <v>48</v>
+      </c>
+      <c r="BW7">
+        <v>5.6</v>
+      </c>
+      <c r="BX7">
+        <v>85</v>
+      </c>
+      <c r="BY7">
+        <v>5.9</v>
+      </c>
+      <c r="BZ7">
         <v>80</v>
       </c>
-      <c r="AB7">
-        <v>13.5</v>
-      </c>
-      <c r="AC7">
-        <v>9.4</v>
-      </c>
-      <c r="AD7">
-        <v>15</v>
-      </c>
-      <c r="AE7">
-        <v>44</v>
-      </c>
-      <c r="AF7">
-        <v>21</v>
-      </c>
-      <c r="AG7">
-        <v>13.5</v>
-      </c>
-      <c r="AH7">
-        <v>20</v>
-      </c>
-      <c r="AI7">
-        <v>46</v>
-      </c>
-      <c r="AJ7">
-        <v>36</v>
-      </c>
-      <c r="AK7">
-        <v>25</v>
-      </c>
-      <c r="AL7">
-        <v>38</v>
-      </c>
-      <c r="AM7">
-        <v>85</v>
-      </c>
-      <c r="AN7">
-        <v>14.5</v>
-      </c>
-      <c r="AO7">
-        <v>32</v>
-      </c>
-      <c r="AP7">
+      <c r="CA7">
         <v>5.9</v>
       </c>
-      <c r="AQ7">
-        <v>15</v>
-      </c>
-      <c r="AR7">
-        <v>6</v>
-      </c>
-      <c r="AS7">
-        <v>6.8</v>
-      </c>
-      <c r="AT7">
-        <v>11.5</v>
-      </c>
-      <c r="AU7">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AV7">
-        <v>13</v>
-      </c>
-      <c r="AW7">
-        <v>6.2</v>
-      </c>
-      <c r="AX7">
-        <v>14</v>
-      </c>
-      <c r="AY7">
-        <v>10</v>
-      </c>
-      <c r="AZ7">
-        <v>13.5</v>
-      </c>
-      <c r="BA7">
-        <v>6.6</v>
-      </c>
-      <c r="BB7">
-        <v>6</v>
-      </c>
-      <c r="BC7">
-        <v>5.9</v>
-      </c>
-      <c r="BD7">
-        <v>6</v>
-      </c>
-      <c r="BE7">
-        <v>6.8</v>
-      </c>
-      <c r="BF7">
-        <v>10.5</v>
-      </c>
-      <c r="BG7">
-        <v>21</v>
-      </c>
-      <c r="BH7">
-        <v>4.1</v>
-      </c>
-      <c r="BI7">
-        <v>3.65</v>
-      </c>
-      <c r="BJ7">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="BK7">
-        <v>5.5</v>
-      </c>
-      <c r="BL7">
-        <v>1000</v>
-      </c>
-      <c r="BM7">
-        <v>12.5</v>
-      </c>
-      <c r="BN7">
-        <v>5.3</v>
-      </c>
-      <c r="BO7">
-        <v>4.7</v>
-      </c>
-      <c r="BP7">
-        <v>15</v>
-      </c>
-      <c r="BQ7">
-        <v>10.5</v>
-      </c>
-      <c r="BR7">
-        <v>36</v>
-      </c>
-      <c r="BS7">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="BT7">
-        <v>7</v>
-      </c>
-      <c r="BU7">
-        <v>6</v>
-      </c>
-      <c r="BV7">
-        <v>36</v>
-      </c>
-      <c r="BW7">
-        <v>9.4</v>
-      </c>
-      <c r="BX7">
-        <v>1000</v>
-      </c>
-      <c r="BY7">
-        <v>10</v>
-      </c>
-      <c r="BZ7">
-        <v>0</v>
-      </c>
-      <c r="CA7">
-        <v>0</v>
-      </c>
       <c r="CB7" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
     </row>
     <row r="8" spans="1:80">
       <c r="A8" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="B8" t="s">
         <v>91</v>
       </c>
       <c r="C8" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="D8" t="s">
         <v>108</v>
       </c>
       <c r="E8" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="F8">
-        <v>2.88</v>
+        <v>2.42</v>
       </c>
       <c r="G8">
-        <v>3.3</v>
+        <v>2.58</v>
       </c>
       <c r="H8">
-        <v>2.82</v>
+        <v>3.45</v>
       </c>
       <c r="I8">
-        <v>3.2</v>
+        <v>4.5</v>
       </c>
       <c r="J8">
         <v>2.76</v>
       </c>
       <c r="K8">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="L8">
-        <v>1.61</v>
+        <v>1.01</v>
       </c>
       <c r="M8">
-        <v>1.14</v>
+        <v>1.11</v>
       </c>
       <c r="N8">
-        <v>2.34</v>
+        <v>2.3</v>
       </c>
       <c r="O8">
-        <v>1.61</v>
+        <v>1.63</v>
       </c>
       <c r="P8">
-        <v>1.45</v>
+        <v>1.4</v>
       </c>
       <c r="Q8">
-        <v>2.78</v>
+        <v>2.68</v>
       </c>
       <c r="R8">
-        <v>1.15</v>
+        <v>1.13</v>
       </c>
       <c r="S8">
-        <v>6</v>
+        <v>4.8</v>
       </c>
       <c r="T8">
-        <v>2.16</v>
+        <v>2.14</v>
       </c>
       <c r="U8">
-        <v>1.71</v>
+        <v>1.58</v>
       </c>
       <c r="V8">
-        <v>1.46</v>
+        <v>1.33</v>
       </c>
       <c r="W8">
-        <v>1.43</v>
+        <v>1.63</v>
       </c>
       <c r="X8">
-        <v>9.199999999999999</v>
+        <v>1000</v>
       </c>
       <c r="Y8">
-        <v>9.6</v>
+        <v>13</v>
       </c>
       <c r="Z8">
-        <v>21</v>
+        <v>34</v>
       </c>
       <c r="AA8">
-        <v>70</v>
+        <v>1000</v>
       </c>
       <c r="AB8">
         <v>9.800000000000001</v>
       </c>
       <c r="AC8">
-        <v>7.4</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AD8">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="AE8">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="AF8">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AG8">
-        <v>17.5</v>
+        <v>19.5</v>
       </c>
       <c r="AH8">
-        <v>30</v>
+        <v>950</v>
       </c>
       <c r="AI8">
-        <v>100</v>
+        <v>1000</v>
       </c>
       <c r="AJ8">
-        <v>65</v>
+        <v>1000</v>
       </c>
       <c r="AK8">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="AL8">
-        <v>100</v>
+        <v>1000</v>
       </c>
       <c r="AM8">
-        <v>270</v>
+        <v>1000</v>
       </c>
       <c r="AN8">
-        <v>70</v>
+        <v>1000</v>
       </c>
       <c r="AO8">
-        <v>70</v>
+        <v>1000</v>
       </c>
       <c r="AP8">
-        <v>5.8</v>
+        <v>1.9</v>
       </c>
       <c r="AQ8">
-        <v>6</v>
+        <v>5.9</v>
       </c>
       <c r="AR8">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="AS8">
-        <v>4.9</v>
+        <v>1.91</v>
       </c>
       <c r="AT8">
-        <v>6.2</v>
+        <v>4.6</v>
       </c>
       <c r="AU8">
-        <v>5.3</v>
+        <v>4.6</v>
       </c>
       <c r="AV8">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AW8">
-        <v>4.8</v>
+        <v>1.91</v>
       </c>
       <c r="AX8">
-        <v>15.5</v>
+        <v>9</v>
       </c>
       <c r="AY8">
-        <v>12.5</v>
+        <v>8.4</v>
       </c>
       <c r="AZ8">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="BA8">
-        <v>5</v>
+        <v>1.91</v>
       </c>
       <c r="BB8">
-        <v>4.9</v>
+        <v>1.91</v>
       </c>
       <c r="BC8">
-        <v>4.8</v>
+        <v>1.91</v>
       </c>
       <c r="BD8">
-        <v>5</v>
+        <v>1.91</v>
       </c>
       <c r="BE8">
-        <v>5.2</v>
+        <v>1.91</v>
       </c>
       <c r="BF8">
-        <v>4.9</v>
+        <v>1.91</v>
       </c>
       <c r="BG8">
-        <v>4.9</v>
+        <v>1.91</v>
       </c>
       <c r="BH8">
         <v>1000</v>
       </c>
       <c r="BI8">
-        <v>1.68</v>
+        <v>1.04</v>
       </c>
       <c r="BJ8">
-        <v>16</v>
+        <v>1000</v>
       </c>
       <c r="BK8">
-        <v>1.53</v>
+        <v>1.04</v>
       </c>
       <c r="BL8">
         <v>1000</v>
       </c>
       <c r="BM8">
-        <v>1.68</v>
+        <v>1.04</v>
       </c>
       <c r="BN8">
-        <v>7.8</v>
+        <v>1000</v>
       </c>
       <c r="BO8">
-        <v>3.9</v>
+        <v>1.04</v>
       </c>
       <c r="BP8">
-        <v>42</v>
+        <v>1000</v>
       </c>
       <c r="BQ8">
-        <v>1.62</v>
+        <v>1.04</v>
       </c>
       <c r="BR8">
         <v>1000</v>
       </c>
       <c r="BS8">
-        <v>1.65</v>
+        <v>1.04</v>
       </c>
       <c r="BT8">
-        <v>7.8</v>
+        <v>1000</v>
       </c>
       <c r="BU8">
-        <v>3.9</v>
+        <v>1.04</v>
       </c>
       <c r="BV8">
-        <v>40</v>
+        <v>1000</v>
       </c>
       <c r="BW8">
-        <v>1.62</v>
+        <v>1.04</v>
       </c>
       <c r="BX8">
         <v>1000</v>
       </c>
       <c r="BY8">
-        <v>1.65</v>
+        <v>1.04</v>
       </c>
       <c r="BZ8">
         <v>1000</v>
       </c>
       <c r="CA8">
-        <v>1.65</v>
+        <v>1.04</v>
       </c>
       <c r="CB8" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
     </row>
     <row r="9" spans="1:80">
       <c r="A9" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="B9" t="s">
         <v>91</v>
       </c>
       <c r="C9" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="D9" t="s">
         <v>109</v>
       </c>
       <c r="E9" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="F9">
-        <v>6.6</v>
+        <v>2.9</v>
       </c>
       <c r="G9">
+        <v>3.25</v>
+      </c>
+      <c r="H9">
+        <v>2.84</v>
+      </c>
+      <c r="I9">
+        <v>3.15</v>
+      </c>
+      <c r="J9">
+        <v>2.76</v>
+      </c>
+      <c r="K9">
+        <v>3.1</v>
+      </c>
+      <c r="L9">
+        <v>1.52</v>
+      </c>
+      <c r="M9">
+        <v>1.14</v>
+      </c>
+      <c r="N9">
+        <v>2.36</v>
+      </c>
+      <c r="O9">
+        <v>1.61</v>
+      </c>
+      <c r="P9">
+        <v>1.45</v>
+      </c>
+      <c r="Q9">
+        <v>2.82</v>
+      </c>
+      <c r="R9">
+        <v>1.16</v>
+      </c>
+      <c r="S9">
+        <v>6</v>
+      </c>
+      <c r="T9">
+        <v>2.18</v>
+      </c>
+      <c r="U9">
+        <v>1.71</v>
+      </c>
+      <c r="V9">
+        <v>1.47</v>
+      </c>
+      <c r="W9">
+        <v>1.44</v>
+      </c>
+      <c r="X9">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="Y9">
+        <v>9.6</v>
+      </c>
+      <c r="Z9">
+        <v>21</v>
+      </c>
+      <c r="AA9">
+        <v>70</v>
+      </c>
+      <c r="AB9">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AC9">
+        <v>7.4</v>
+      </c>
+      <c r="AD9">
+        <v>17</v>
+      </c>
+      <c r="AE9">
+        <v>55</v>
+      </c>
+      <c r="AF9">
+        <v>22</v>
+      </c>
+      <c r="AG9">
+        <v>17.5</v>
+      </c>
+      <c r="AH9">
+        <v>30</v>
+      </c>
+      <c r="AI9">
+        <v>100</v>
+      </c>
+      <c r="AJ9">
+        <v>65</v>
+      </c>
+      <c r="AK9">
+        <v>55</v>
+      </c>
+      <c r="AL9">
+        <v>100</v>
+      </c>
+      <c r="AM9">
+        <v>270</v>
+      </c>
+      <c r="AN9">
+        <v>70</v>
+      </c>
+      <c r="AO9">
+        <v>70</v>
+      </c>
+      <c r="AP9">
+        <v>5.8</v>
+      </c>
+      <c r="AQ9">
+        <v>6</v>
+      </c>
+      <c r="AR9">
+        <v>15</v>
+      </c>
+      <c r="AS9">
+        <v>4.9</v>
+      </c>
+      <c r="AT9">
+        <v>6.2</v>
+      </c>
+      <c r="AU9">
+        <v>6</v>
+      </c>
+      <c r="AV9">
+        <v>12</v>
+      </c>
+      <c r="AW9">
+        <v>4.8</v>
+      </c>
+      <c r="AX9">
+        <v>15.5</v>
+      </c>
+      <c r="AY9">
+        <v>12.5</v>
+      </c>
+      <c r="AZ9">
+        <v>20</v>
+      </c>
+      <c r="BA9">
+        <v>5</v>
+      </c>
+      <c r="BB9">
+        <v>4.9</v>
+      </c>
+      <c r="BC9">
+        <v>4.8</v>
+      </c>
+      <c r="BD9">
+        <v>5</v>
+      </c>
+      <c r="BE9">
+        <v>5.2</v>
+      </c>
+      <c r="BF9">
+        <v>4.9</v>
+      </c>
+      <c r="BG9">
+        <v>4.9</v>
+      </c>
+      <c r="BH9">
+        <v>2.64</v>
+      </c>
+      <c r="BI9">
+        <v>2.12</v>
+      </c>
+      <c r="BJ9">
+        <v>12.5</v>
+      </c>
+      <c r="BK9">
+        <v>5.8</v>
+      </c>
+      <c r="BL9">
+        <v>1000</v>
+      </c>
+      <c r="BM9">
+        <v>10.5</v>
+      </c>
+      <c r="BN9">
+        <v>6</v>
+      </c>
+      <c r="BO9">
+        <v>4.4</v>
+      </c>
+      <c r="BP9">
+        <v>32</v>
+      </c>
+      <c r="BQ9">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BR9">
+        <v>60</v>
+      </c>
+      <c r="BS9">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="BT9">
+        <v>6</v>
+      </c>
+      <c r="BU9">
+        <v>4.4</v>
+      </c>
+      <c r="BV9">
+        <v>30</v>
+      </c>
+      <c r="BW9">
+        <v>8</v>
+      </c>
+      <c r="BX9">
+        <v>60</v>
+      </c>
+      <c r="BY9">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="BZ9">
+        <v>65</v>
+      </c>
+      <c r="CA9">
         <v>9.4</v>
       </c>
-      <c r="H9">
-        <v>1.55</v>
-      </c>
-      <c r="I9">
-        <v>1.64</v>
-      </c>
-      <c r="J9">
-        <v>3.95</v>
-      </c>
-      <c r="K9">
-        <v>4.4</v>
-      </c>
-      <c r="L9">
-        <v>1.41</v>
-      </c>
-      <c r="M9">
-        <v>1.07</v>
-      </c>
-      <c r="N9">
-        <v>3.45</v>
-      </c>
-      <c r="O9">
-        <v>1.32</v>
-      </c>
-      <c r="P9">
-        <v>1.84</v>
-      </c>
-      <c r="Q9">
-        <v>2</v>
-      </c>
-      <c r="R9">
-        <v>1.32</v>
-      </c>
-      <c r="S9">
-        <v>3.6</v>
-      </c>
-      <c r="T9">
-        <v>2.06</v>
-      </c>
-      <c r="U9">
-        <v>1.66</v>
-      </c>
-      <c r="V9">
-        <v>2.56</v>
-      </c>
-      <c r="W9">
-        <v>1.12</v>
-      </c>
-      <c r="X9">
-        <v>16.5</v>
-      </c>
-      <c r="Y9">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="Z9">
-        <v>10.5</v>
-      </c>
-      <c r="AA9">
-        <v>18</v>
-      </c>
-      <c r="AB9">
-        <v>26</v>
-      </c>
-      <c r="AC9">
-        <v>1000</v>
-      </c>
-      <c r="AD9">
-        <v>12.5</v>
-      </c>
-      <c r="AE9">
-        <v>23</v>
-      </c>
-      <c r="AF9">
-        <v>75</v>
-      </c>
-      <c r="AG9">
-        <v>1000</v>
-      </c>
-      <c r="AH9">
-        <v>32</v>
-      </c>
-      <c r="AI9">
-        <v>55</v>
-      </c>
-      <c r="AJ9">
-        <v>310</v>
-      </c>
-      <c r="AK9">
-        <v>160</v>
-      </c>
-      <c r="AL9">
-        <v>150</v>
-      </c>
-      <c r="AM9">
-        <v>210</v>
-      </c>
-      <c r="AN9">
-        <v>240</v>
-      </c>
-      <c r="AO9">
-        <v>12.5</v>
-      </c>
-      <c r="AP9">
-        <v>10</v>
-      </c>
-      <c r="AQ9">
-        <v>5.5</v>
-      </c>
-      <c r="AR9">
-        <v>6.6</v>
-      </c>
-      <c r="AS9">
-        <v>10.5</v>
-      </c>
-      <c r="AT9">
-        <v>15</v>
-      </c>
-      <c r="AU9">
-        <v>2.9</v>
-      </c>
-      <c r="AV9">
-        <v>7.6</v>
-      </c>
-      <c r="AW9">
-        <v>13</v>
-      </c>
-      <c r="AX9">
-        <v>2.8</v>
-      </c>
-      <c r="AY9">
-        <v>20</v>
-      </c>
-      <c r="AZ9">
-        <v>18</v>
-      </c>
-      <c r="BA9">
-        <v>2.76</v>
-      </c>
-      <c r="BB9">
-        <v>2.88</v>
-      </c>
-      <c r="BC9">
-        <v>2.86</v>
-      </c>
-      <c r="BD9">
-        <v>2.84</v>
-      </c>
-      <c r="BE9">
-        <v>2.86</v>
-      </c>
-      <c r="BF9">
-        <v>2.86</v>
-      </c>
-      <c r="BG9">
-        <v>7.6</v>
-      </c>
-      <c r="BH9">
-        <v>3.85</v>
-      </c>
-      <c r="BI9">
-        <v>2.68</v>
-      </c>
-      <c r="BJ9">
-        <v>14</v>
-      </c>
-      <c r="BK9">
-        <v>3.65</v>
-      </c>
-      <c r="BL9">
-        <v>1000</v>
-      </c>
-      <c r="BM9">
-        <v>4.8</v>
-      </c>
-      <c r="BN9">
-        <v>13</v>
-      </c>
-      <c r="BO9">
-        <v>3.55</v>
-      </c>
-      <c r="BP9">
-        <v>1000</v>
-      </c>
-      <c r="BQ9">
-        <v>4.6</v>
-      </c>
-      <c r="BR9">
-        <v>1000</v>
-      </c>
-      <c r="BS9">
-        <v>4.7</v>
-      </c>
-      <c r="BT9">
-        <v>4.6</v>
-      </c>
-      <c r="BU9">
-        <v>3.1</v>
-      </c>
-      <c r="BV9">
-        <v>12.5</v>
-      </c>
-      <c r="BW9">
-        <v>3.5</v>
-      </c>
-      <c r="BX9">
-        <v>36</v>
-      </c>
-      <c r="BY9">
-        <v>4.3</v>
-      </c>
-      <c r="BZ9">
-        <v>26</v>
-      </c>
-      <c r="CA9">
-        <v>4.1</v>
-      </c>
       <c r="CB9" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
     </row>
     <row r="10" spans="1:80">
       <c r="A10" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="B10" t="s">
         <v>91</v>
       </c>
       <c r="C10" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="D10" t="s">
         <v>110</v>
       </c>
       <c r="E10" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="F10">
-        <v>2.74</v>
+        <v>7</v>
       </c>
       <c r="G10">
-        <v>3.05</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="H10">
+        <v>1.55</v>
+      </c>
+      <c r="I10">
+        <v>1.64</v>
+      </c>
+      <c r="J10">
+        <v>3.95</v>
+      </c>
+      <c r="K10">
+        <v>4.4</v>
+      </c>
+      <c r="L10">
+        <v>1.35</v>
+      </c>
+      <c r="M10">
+        <v>1.07</v>
+      </c>
+      <c r="N10">
+        <v>3.45</v>
+      </c>
+      <c r="O10">
+        <v>1.34</v>
+      </c>
+      <c r="P10">
+        <v>1.84</v>
+      </c>
+      <c r="Q10">
+        <v>2.04</v>
+      </c>
+      <c r="R10">
+        <v>1.32</v>
+      </c>
+      <c r="S10">
+        <v>3.65</v>
+      </c>
+      <c r="T10">
+        <v>2.06</v>
+      </c>
+      <c r="U10">
+        <v>1.8</v>
+      </c>
+      <c r="V10">
+        <v>2.56</v>
+      </c>
+      <c r="W10">
+        <v>1.14</v>
+      </c>
+      <c r="X10">
+        <v>16.5</v>
+      </c>
+      <c r="Y10">
+        <v>8.6</v>
+      </c>
+      <c r="Z10">
+        <v>10.5</v>
+      </c>
+      <c r="AA10">
+        <v>18</v>
+      </c>
+      <c r="AB10">
+        <v>26</v>
+      </c>
+      <c r="AC10">
+        <v>11.5</v>
+      </c>
+      <c r="AD10">
+        <v>12.5</v>
+      </c>
+      <c r="AE10">
+        <v>23</v>
+      </c>
+      <c r="AF10">
+        <v>75</v>
+      </c>
+      <c r="AG10">
+        <v>34</v>
+      </c>
+      <c r="AH10">
+        <v>32</v>
+      </c>
+      <c r="AI10">
+        <v>55</v>
+      </c>
+      <c r="AJ10">
+        <v>310</v>
+      </c>
+      <c r="AK10">
+        <v>160</v>
+      </c>
+      <c r="AL10">
+        <v>150</v>
+      </c>
+      <c r="AM10">
+        <v>210</v>
+      </c>
+      <c r="AN10">
+        <v>240</v>
+      </c>
+      <c r="AO10">
+        <v>12.5</v>
+      </c>
+      <c r="AP10">
+        <v>10</v>
+      </c>
+      <c r="AQ10">
+        <v>5.5</v>
+      </c>
+      <c r="AR10">
+        <v>6.6</v>
+      </c>
+      <c r="AS10">
+        <v>10.5</v>
+      </c>
+      <c r="AT10">
+        <v>15</v>
+      </c>
+      <c r="AU10">
+        <v>7</v>
+      </c>
+      <c r="AV10">
+        <v>7.6</v>
+      </c>
+      <c r="AW10">
+        <v>16</v>
+      </c>
+      <c r="AX10">
+        <v>4.1</v>
+      </c>
+      <c r="AY10">
+        <v>20</v>
+      </c>
+      <c r="AZ10">
+        <v>18</v>
+      </c>
+      <c r="BA10">
+        <v>4</v>
+      </c>
+      <c r="BB10">
+        <v>4.3</v>
+      </c>
+      <c r="BC10">
+        <v>4.3</v>
+      </c>
+      <c r="BD10">
+        <v>4.2</v>
+      </c>
+      <c r="BE10">
+        <v>4.3</v>
+      </c>
+      <c r="BF10">
+        <v>4.3</v>
+      </c>
+      <c r="BG10">
+        <v>7.8</v>
+      </c>
+      <c r="BH10">
+        <v>3.85</v>
+      </c>
+      <c r="BI10">
+        <v>3</v>
+      </c>
+      <c r="BJ10">
+        <v>14</v>
+      </c>
+      <c r="BK10">
+        <v>3.65</v>
+      </c>
+      <c r="BL10">
+        <v>1000</v>
+      </c>
+      <c r="BM10">
+        <v>4.8</v>
+      </c>
+      <c r="BN10">
+        <v>13</v>
+      </c>
+      <c r="BO10">
+        <v>3.55</v>
+      </c>
+      <c r="BP10">
+        <v>1000</v>
+      </c>
+      <c r="BQ10">
+        <v>4.6</v>
+      </c>
+      <c r="BR10">
+        <v>1000</v>
+      </c>
+      <c r="BS10">
+        <v>4.7</v>
+      </c>
+      <c r="BT10">
+        <v>4.6</v>
+      </c>
+      <c r="BU10">
         <v>3.1</v>
       </c>
-      <c r="I10">
-        <v>3.55</v>
-      </c>
-      <c r="J10">
-        <v>2.66</v>
-      </c>
-      <c r="K10">
-        <v>3.05</v>
-      </c>
-      <c r="L10">
-        <v>1.67</v>
-      </c>
-      <c r="M10">
-        <v>1.16</v>
-      </c>
-      <c r="N10">
-        <v>2.16</v>
-      </c>
-      <c r="O10">
-        <v>1.68</v>
-      </c>
-      <c r="P10">
-        <v>1.38</v>
-      </c>
-      <c r="Q10">
-        <v>3.05</v>
-      </c>
-      <c r="R10">
-        <v>1.14</v>
-      </c>
-      <c r="S10">
-        <v>6.4</v>
-      </c>
-      <c r="T10">
-        <v>2.3</v>
-      </c>
-      <c r="U10">
-        <v>1.53</v>
-      </c>
-      <c r="V10">
-        <v>1.39</v>
-      </c>
-      <c r="W10">
-        <v>1.48</v>
-      </c>
-      <c r="X10">
-        <v>8</v>
-      </c>
-      <c r="Y10">
-        <v>8.4</v>
-      </c>
-      <c r="Z10">
-        <v>21</v>
-      </c>
-      <c r="AA10">
-        <v>85</v>
-      </c>
-      <c r="AB10">
-        <v>7.6</v>
-      </c>
-      <c r="AC10">
-        <v>7.2</v>
-      </c>
-      <c r="AD10">
-        <v>17</v>
-      </c>
-      <c r="AE10">
-        <v>75</v>
-      </c>
-      <c r="AF10">
-        <v>18</v>
-      </c>
-      <c r="AG10">
-        <v>15.5</v>
-      </c>
-      <c r="AH10">
-        <v>40</v>
-      </c>
-      <c r="AI10">
-        <v>130</v>
-      </c>
-      <c r="AJ10">
-        <v>70</v>
-      </c>
-      <c r="AK10">
-        <v>65</v>
-      </c>
-      <c r="AL10">
-        <v>120</v>
-      </c>
-      <c r="AM10">
-        <v>340</v>
-      </c>
-      <c r="AN10">
-        <v>95</v>
-      </c>
-      <c r="AO10">
-        <v>110</v>
-      </c>
-      <c r="AP10">
-        <v>5.1</v>
-      </c>
-      <c r="AQ10">
-        <v>6</v>
-      </c>
-      <c r="AR10">
-        <v>17</v>
-      </c>
-      <c r="AS10">
-        <v>7</v>
-      </c>
-      <c r="AT10">
-        <v>5.5</v>
-      </c>
-      <c r="AU10">
-        <v>6</v>
-      </c>
-      <c r="AV10">
-        <v>14</v>
-      </c>
-      <c r="AW10">
-        <v>6.8</v>
-      </c>
-      <c r="AX10">
-        <v>14.5</v>
-      </c>
-      <c r="AY10">
+      <c r="BV10">
         <v>12.5</v>
       </c>
-      <c r="AZ10">
-        <v>17</v>
-      </c>
-      <c r="BA10">
-        <v>7.2</v>
-      </c>
-      <c r="BB10">
-        <v>6.8</v>
-      </c>
-      <c r="BC10">
-        <v>6.8</v>
-      </c>
-      <c r="BD10">
-        <v>7.2</v>
-      </c>
-      <c r="BE10">
-        <v>7.4</v>
-      </c>
-      <c r="BF10">
-        <v>7</v>
-      </c>
-      <c r="BG10">
-        <v>7</v>
-      </c>
-      <c r="BH10">
-        <v>2.74</v>
-      </c>
-      <c r="BI10">
-        <v>2.02</v>
-      </c>
-      <c r="BJ10">
-        <v>15</v>
-      </c>
-      <c r="BK10">
+      <c r="BW10">
+        <v>3.5</v>
+      </c>
+      <c r="BX10">
+        <v>36</v>
+      </c>
+      <c r="BY10">
         <v>4.3</v>
       </c>
-      <c r="BL10">
-        <v>1000</v>
-      </c>
-      <c r="BM10">
-        <v>5.9</v>
-      </c>
-      <c r="BN10">
-        <v>5.8</v>
-      </c>
-      <c r="BO10">
-        <v>4.9</v>
-      </c>
-      <c r="BP10">
-        <v>36</v>
-      </c>
-      <c r="BQ10">
-        <v>5.1</v>
-      </c>
-      <c r="BR10">
-        <v>1000</v>
-      </c>
-      <c r="BS10">
-        <v>5.5</v>
-      </c>
-      <c r="BT10">
-        <v>7.2</v>
-      </c>
-      <c r="BU10">
-        <v>4.6</v>
-      </c>
-      <c r="BV10">
-        <v>42</v>
-      </c>
-      <c r="BW10">
-        <v>5.2</v>
-      </c>
-      <c r="BX10">
-        <v>80</v>
-      </c>
-      <c r="BY10">
-        <v>5.6</v>
-      </c>
       <c r="BZ10">
-        <v>90</v>
+        <v>26</v>
       </c>
       <c r="CA10">
-        <v>5.6</v>
+        <v>4.1</v>
       </c>
       <c r="CB10" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
     </row>
     <row r="11" spans="1:80">
@@ -3187,232 +3193,232 @@
         <v>111</v>
       </c>
       <c r="E11" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="F11">
-        <v>2.42</v>
+        <v>2.5</v>
       </c>
       <c r="G11">
-        <v>2.58</v>
+        <v>2.82</v>
       </c>
       <c r="H11">
-        <v>3.45</v>
+        <v>2.86</v>
       </c>
       <c r="I11">
-        <v>4.5</v>
+        <v>3.3</v>
       </c>
       <c r="J11">
-        <v>2.74</v>
+        <v>3.2</v>
       </c>
       <c r="K11">
-        <v>3.1</v>
+        <v>3.65</v>
       </c>
       <c r="L11">
-        <v>1.01</v>
+        <v>1.39</v>
       </c>
       <c r="M11">
-        <v>1.11</v>
+        <v>1.08</v>
       </c>
       <c r="N11">
-        <v>2.3</v>
+        <v>3.25</v>
       </c>
       <c r="O11">
-        <v>1.61</v>
+        <v>1.37</v>
       </c>
       <c r="P11">
-        <v>1.37</v>
+        <v>1.76</v>
       </c>
       <c r="Q11">
-        <v>2.68</v>
+        <v>2.08</v>
       </c>
       <c r="R11">
-        <v>1.13</v>
+        <v>1.29</v>
       </c>
       <c r="S11">
+        <v>3.75</v>
+      </c>
+      <c r="T11">
+        <v>1.8</v>
+      </c>
+      <c r="U11">
+        <v>2.02</v>
+      </c>
+      <c r="V11">
+        <v>1.43</v>
+      </c>
+      <c r="W11">
+        <v>1.54</v>
+      </c>
+      <c r="X11">
+        <v>14</v>
+      </c>
+      <c r="Y11">
+        <v>11.5</v>
+      </c>
+      <c r="Z11">
+        <v>21</v>
+      </c>
+      <c r="AA11">
+        <v>55</v>
+      </c>
+      <c r="AB11">
+        <v>10.5</v>
+      </c>
+      <c r="AC11">
+        <v>7.8</v>
+      </c>
+      <c r="AD11">
+        <v>14</v>
+      </c>
+      <c r="AE11">
+        <v>40</v>
+      </c>
+      <c r="AF11">
+        <v>17.5</v>
+      </c>
+      <c r="AG11">
+        <v>13</v>
+      </c>
+      <c r="AH11">
+        <v>19</v>
+      </c>
+      <c r="AI11">
+        <v>55</v>
+      </c>
+      <c r="AJ11">
+        <v>42</v>
+      </c>
+      <c r="AK11">
+        <v>32</v>
+      </c>
+      <c r="AL11">
+        <v>48</v>
+      </c>
+      <c r="AM11">
+        <v>130</v>
+      </c>
+      <c r="AN11">
+        <v>34</v>
+      </c>
+      <c r="AO11">
+        <v>38</v>
+      </c>
+      <c r="AP11">
+        <v>9.4</v>
+      </c>
+      <c r="AQ11">
+        <v>9.4</v>
+      </c>
+      <c r="AR11">
+        <v>17</v>
+      </c>
+      <c r="AS11">
+        <v>7.6</v>
+      </c>
+      <c r="AT11">
+        <v>8.6</v>
+      </c>
+      <c r="AU11">
+        <v>6.4</v>
+      </c>
+      <c r="AV11">
+        <v>11.5</v>
+      </c>
+      <c r="AW11">
+        <v>29</v>
+      </c>
+      <c r="AX11">
+        <v>14</v>
+      </c>
+      <c r="AY11">
+        <v>10.5</v>
+      </c>
+      <c r="AZ11">
+        <v>15.5</v>
+      </c>
+      <c r="BA11">
+        <v>36</v>
+      </c>
+      <c r="BB11">
+        <v>7.2</v>
+      </c>
+      <c r="BC11">
+        <v>19.5</v>
+      </c>
+      <c r="BD11">
+        <v>7.4</v>
+      </c>
+      <c r="BE11">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BF11">
+        <v>21</v>
+      </c>
+      <c r="BG11">
+        <v>7.2</v>
+      </c>
+      <c r="BH11">
+        <v>3.3</v>
+      </c>
+      <c r="BI11">
+        <v>2.86</v>
+      </c>
+      <c r="BJ11">
+        <v>10</v>
+      </c>
+      <c r="BK11">
+        <v>5.3</v>
+      </c>
+      <c r="BL11">
+        <v>1000</v>
+      </c>
+      <c r="BM11">
+        <v>10.5</v>
+      </c>
+      <c r="BN11">
+        <v>5.7</v>
+      </c>
+      <c r="BO11">
+        <v>4.4</v>
+      </c>
+      <c r="BP11">
+        <v>22</v>
+      </c>
+      <c r="BQ11">
+        <v>7.4</v>
+      </c>
+      <c r="BR11">
+        <v>36</v>
+      </c>
+      <c r="BS11">
+        <v>8.6</v>
+      </c>
+      <c r="BT11">
+        <v>6.2</v>
+      </c>
+      <c r="BU11">
         <v>4.8</v>
       </c>
-      <c r="T11">
-        <v>1.11</v>
-      </c>
-      <c r="U11">
-        <v>1.11</v>
-      </c>
-      <c r="V11">
-        <v>1.28</v>
-      </c>
-      <c r="W11">
-        <v>1.63</v>
-      </c>
-      <c r="X11">
-        <v>1000</v>
-      </c>
-      <c r="Y11">
-        <v>13</v>
-      </c>
-      <c r="Z11">
+      <c r="BV11">
+        <v>26</v>
+      </c>
+      <c r="BW11">
+        <v>7.8</v>
+      </c>
+      <c r="BX11">
+        <v>40</v>
+      </c>
+      <c r="BY11">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="BZ11">
         <v>34</v>
       </c>
-      <c r="AA11">
-        <v>1000</v>
-      </c>
-      <c r="AB11">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AC11">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AD11">
-        <v>25</v>
-      </c>
-      <c r="AE11">
-        <v>1000</v>
-      </c>
-      <c r="AF11">
-        <v>21</v>
-      </c>
-      <c r="AG11">
-        <v>19.5</v>
-      </c>
-      <c r="AH11">
-        <v>950</v>
-      </c>
-      <c r="AI11">
-        <v>1000</v>
-      </c>
-      <c r="AJ11">
-        <v>1000</v>
-      </c>
-      <c r="AK11">
-        <v>1000</v>
-      </c>
-      <c r="AL11">
-        <v>1000</v>
-      </c>
-      <c r="AM11">
-        <v>1000</v>
-      </c>
-      <c r="AN11">
-        <v>1000</v>
-      </c>
-      <c r="AO11">
-        <v>1000</v>
-      </c>
-      <c r="AP11">
-        <v>1.9</v>
-      </c>
-      <c r="AQ11">
-        <v>5.9</v>
-      </c>
-      <c r="AR11">
-        <v>14.5</v>
-      </c>
-      <c r="AS11">
-        <v>1.91</v>
-      </c>
-      <c r="AT11">
-        <v>4.6</v>
-      </c>
-      <c r="AU11">
-        <v>4.6</v>
-      </c>
-      <c r="AV11">
-        <v>11</v>
-      </c>
-      <c r="AW11">
-        <v>1.91</v>
-      </c>
-      <c r="AX11">
-        <v>9</v>
-      </c>
-      <c r="AY11">
+      <c r="CA11">
         <v>8.4</v>
       </c>
-      <c r="AZ11">
-        <v>16</v>
-      </c>
-      <c r="BA11">
-        <v>1.91</v>
-      </c>
-      <c r="BB11">
-        <v>1.91</v>
-      </c>
-      <c r="BC11">
-        <v>1.91</v>
-      </c>
-      <c r="BD11">
-        <v>1.91</v>
-      </c>
-      <c r="BE11">
-        <v>1.91</v>
-      </c>
-      <c r="BF11">
-        <v>1.91</v>
-      </c>
-      <c r="BG11">
-        <v>1.91</v>
-      </c>
-      <c r="BH11">
-        <v>1000</v>
-      </c>
-      <c r="BI11">
-        <v>1.04</v>
-      </c>
-      <c r="BJ11">
-        <v>1000</v>
-      </c>
-      <c r="BK11">
-        <v>1.04</v>
-      </c>
-      <c r="BL11">
-        <v>1000</v>
-      </c>
-      <c r="BM11">
-        <v>1.04</v>
-      </c>
-      <c r="BN11">
-        <v>1000</v>
-      </c>
-      <c r="BO11">
-        <v>1.04</v>
-      </c>
-      <c r="BP11">
-        <v>1000</v>
-      </c>
-      <c r="BQ11">
-        <v>1.04</v>
-      </c>
-      <c r="BR11">
-        <v>1000</v>
-      </c>
-      <c r="BS11">
-        <v>1.04</v>
-      </c>
-      <c r="BT11">
-        <v>1000</v>
-      </c>
-      <c r="BU11">
-        <v>1.04</v>
-      </c>
-      <c r="BV11">
-        <v>1000</v>
-      </c>
-      <c r="BW11">
-        <v>1.04</v>
-      </c>
-      <c r="BX11">
-        <v>1000</v>
-      </c>
-      <c r="BY11">
-        <v>1.04</v>
-      </c>
-      <c r="BZ11">
-        <v>1000</v>
-      </c>
-      <c r="CA11">
-        <v>1.04</v>
-      </c>
       <c r="CB11" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
     </row>
     <row r="12" spans="1:80">
@@ -3429,232 +3435,232 @@
         <v>112</v>
       </c>
       <c r="E12" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="F12">
-        <v>2.5</v>
+        <v>1.9</v>
       </c>
       <c r="G12">
-        <v>2.84</v>
+        <v>2.08</v>
       </c>
       <c r="H12">
-        <v>2.84</v>
+        <v>4.1</v>
       </c>
       <c r="I12">
-        <v>3.25</v>
+        <v>5.4</v>
       </c>
       <c r="J12">
-        <v>2.94</v>
+        <v>3.5</v>
       </c>
       <c r="K12">
-        <v>3.65</v>
+        <v>3.85</v>
       </c>
       <c r="L12">
-        <v>1.39</v>
+        <v>1.01</v>
       </c>
       <c r="M12">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="N12">
-        <v>3.25</v>
+        <v>1.64</v>
       </c>
       <c r="O12">
-        <v>1.37</v>
+        <v>1.43</v>
       </c>
       <c r="P12">
-        <v>1.77</v>
+        <v>1.64</v>
       </c>
       <c r="Q12">
-        <v>2.04</v>
+        <v>2.24</v>
       </c>
       <c r="R12">
-        <v>1.29</v>
+        <v>1.13</v>
       </c>
       <c r="S12">
-        <v>3.7</v>
+        <v>2.24</v>
       </c>
       <c r="T12">
-        <v>1.79</v>
+        <v>1.7</v>
       </c>
       <c r="U12">
-        <v>2.02</v>
+        <v>1.45</v>
       </c>
       <c r="V12">
-        <v>1.44</v>
+        <v>1.23</v>
       </c>
       <c r="W12">
-        <v>1.54</v>
+        <v>1.92</v>
       </c>
       <c r="X12">
-        <v>14.5</v>
+        <v>19</v>
       </c>
       <c r="Y12">
-        <v>11.5</v>
+        <v>16.5</v>
       </c>
       <c r="Z12">
-        <v>21</v>
+        <v>95</v>
       </c>
       <c r="AA12">
-        <v>60</v>
+        <v>500</v>
       </c>
       <c r="AB12">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AC12">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="AD12">
-        <v>14</v>
+        <v>970</v>
       </c>
       <c r="AE12">
-        <v>42</v>
+        <v>500</v>
       </c>
       <c r="AF12">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AG12">
-        <v>13</v>
+        <v>18.5</v>
       </c>
       <c r="AH12">
-        <v>18.5</v>
+        <v>55</v>
       </c>
       <c r="AI12">
-        <v>60</v>
+        <v>500</v>
       </c>
       <c r="AJ12">
         <v>48</v>
       </c>
       <c r="AK12">
-        <v>32</v>
+        <v>65</v>
       </c>
       <c r="AL12">
-        <v>48</v>
+        <v>500</v>
       </c>
       <c r="AM12">
-        <v>120</v>
+        <v>580</v>
       </c>
       <c r="AN12">
+        <v>500</v>
+      </c>
+      <c r="AO12">
+        <v>130</v>
+      </c>
+      <c r="AP12">
+        <v>8.6</v>
+      </c>
+      <c r="AQ12">
+        <v>11.5</v>
+      </c>
+      <c r="AR12">
+        <v>15.5</v>
+      </c>
+      <c r="AS12">
+        <v>2.72</v>
+      </c>
+      <c r="AT12">
+        <v>5.7</v>
+      </c>
+      <c r="AU12">
+        <v>6</v>
+      </c>
+      <c r="AV12">
+        <v>15</v>
+      </c>
+      <c r="AW12">
+        <v>23</v>
+      </c>
+      <c r="AX12">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AY12">
+        <v>8.4</v>
+      </c>
+      <c r="AZ12">
+        <v>19</v>
+      </c>
+      <c r="BA12">
+        <v>17.5</v>
+      </c>
+      <c r="BB12">
+        <v>12</v>
+      </c>
+      <c r="BC12">
+        <v>18</v>
+      </c>
+      <c r="BD12">
         <v>34</v>
       </c>
-      <c r="AO12">
-        <v>38</v>
-      </c>
-      <c r="AP12">
-        <v>9.6</v>
-      </c>
-      <c r="AQ12">
-        <v>9.6</v>
-      </c>
-      <c r="AR12">
-        <v>16</v>
-      </c>
-      <c r="AS12">
-        <v>7</v>
-      </c>
-      <c r="AT12">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AU12">
-        <v>6.2</v>
-      </c>
-      <c r="AV12">
-        <v>11.5</v>
-      </c>
-      <c r="AW12">
-        <v>6.6</v>
-      </c>
-      <c r="AX12">
-        <v>14.5</v>
-      </c>
-      <c r="AY12">
-        <v>10.5</v>
-      </c>
-      <c r="AZ12">
+      <c r="BE12">
+        <v>2.74</v>
+      </c>
+      <c r="BF12">
         <v>15</v>
       </c>
-      <c r="BA12">
-        <v>7</v>
-      </c>
-      <c r="BB12">
-        <v>6.8</v>
-      </c>
-      <c r="BC12">
-        <v>19.5</v>
-      </c>
-      <c r="BD12">
-        <v>6.8</v>
-      </c>
-      <c r="BE12">
-        <v>7.4</v>
-      </c>
-      <c r="BF12">
-        <v>21</v>
-      </c>
       <c r="BG12">
-        <v>6.6</v>
+        <v>2.64</v>
       </c>
       <c r="BH12">
-        <v>3.3</v>
+        <v>1000</v>
       </c>
       <c r="BI12">
-        <v>2.66</v>
+        <v>1.04</v>
       </c>
       <c r="BJ12">
-        <v>10</v>
+        <v>1000</v>
       </c>
       <c r="BK12">
-        <v>5.3</v>
+        <v>1.04</v>
       </c>
       <c r="BL12">
         <v>1000</v>
       </c>
       <c r="BM12">
-        <v>10.5</v>
+        <v>1.04</v>
       </c>
       <c r="BN12">
-        <v>5.7</v>
+        <v>1000</v>
       </c>
       <c r="BO12">
-        <v>4.4</v>
+        <v>1.04</v>
       </c>
       <c r="BP12">
-        <v>22</v>
+        <v>1000</v>
       </c>
       <c r="BQ12">
-        <v>7.6</v>
+        <v>1.04</v>
       </c>
       <c r="BR12">
-        <v>36</v>
+        <v>1000</v>
       </c>
       <c r="BS12">
-        <v>8.800000000000001</v>
+        <v>1.04</v>
       </c>
       <c r="BT12">
-        <v>6.2</v>
+        <v>1000</v>
       </c>
       <c r="BU12">
-        <v>4.7</v>
+        <v>1.04</v>
       </c>
       <c r="BV12">
-        <v>25</v>
+        <v>1000</v>
       </c>
       <c r="BW12">
-        <v>7.8</v>
+        <v>1.04</v>
       </c>
       <c r="BX12">
-        <v>40</v>
+        <v>1000</v>
       </c>
       <c r="BY12">
-        <v>9</v>
+        <v>1.04</v>
       </c>
       <c r="BZ12">
-        <v>34</v>
+        <v>1000</v>
       </c>
       <c r="CA12">
-        <v>8.6</v>
+        <v>1.04</v>
       </c>
       <c r="CB12" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
     </row>
     <row r="13" spans="1:80">
@@ -3671,7 +3677,7 @@
         <v>113</v>
       </c>
       <c r="E13" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="F13">
         <v>0</v>
@@ -3896,7 +3902,7 @@
         <v>0</v>
       </c>
       <c r="CB13" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
     </row>
     <row r="14" spans="1:80">
@@ -3913,13 +3919,13 @@
         <v>114</v>
       </c>
       <c r="E14" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="F14">
-        <v>2.82</v>
+        <v>2.8</v>
       </c>
       <c r="G14">
-        <v>2.98</v>
+        <v>2.96</v>
       </c>
       <c r="H14">
         <v>2.82</v>
@@ -3928,7 +3934,7 @@
         <v>2.9</v>
       </c>
       <c r="J14">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="K14">
         <v>3.5</v>
@@ -3940,19 +3946,19 @@
         <v>1.09</v>
       </c>
       <c r="N14">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="O14">
         <v>1.39</v>
       </c>
       <c r="P14">
-        <v>1.75</v>
+        <v>1.77</v>
       </c>
       <c r="Q14">
         <v>2.14</v>
       </c>
       <c r="R14">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="S14">
         <v>4</v>
@@ -4012,19 +4018,19 @@
         <v>50</v>
       </c>
       <c r="AL14">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="AM14">
-        <v>140</v>
+        <v>130</v>
       </c>
       <c r="AN14">
         <v>50</v>
       </c>
       <c r="AO14">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AP14">
-        <v>8.6</v>
+        <v>9</v>
       </c>
       <c r="AQ14">
         <v>8.800000000000001</v>
@@ -4033,7 +4039,7 @@
         <v>15.5</v>
       </c>
       <c r="AS14">
-        <v>8.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AT14">
         <v>9.199999999999999</v>
@@ -4045,7 +4051,7 @@
         <v>11</v>
       </c>
       <c r="AW14">
-        <v>8</v>
+        <v>8.4</v>
       </c>
       <c r="AX14">
         <v>16.5</v>
@@ -4057,25 +4063,25 @@
         <v>16</v>
       </c>
       <c r="BA14">
-        <v>8.6</v>
+        <v>9</v>
       </c>
       <c r="BB14">
-        <v>29</v>
+        <v>9</v>
       </c>
       <c r="BC14">
-        <v>8</v>
+        <v>8.4</v>
       </c>
       <c r="BD14">
-        <v>8.800000000000001</v>
+        <v>30</v>
       </c>
       <c r="BE14">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="BF14">
-        <v>8</v>
+        <v>8.4</v>
       </c>
       <c r="BG14">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BH14">
         <v>3.15</v>
@@ -4138,12 +4144,12 @@
         <v>10.5</v>
       </c>
       <c r="CB14" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
     </row>
     <row r="15" spans="1:80">
       <c r="A15" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="B15" t="s">
         <v>91</v>
@@ -4155,13 +4161,13 @@
         <v>115</v>
       </c>
       <c r="E15" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="F15">
         <v>1.51</v>
       </c>
       <c r="G15">
-        <v>1.66</v>
+        <v>1.64</v>
       </c>
       <c r="H15">
         <v>7</v>
@@ -4170,7 +4176,7 @@
         <v>9.4</v>
       </c>
       <c r="J15">
-        <v>3.6</v>
+        <v>3.8</v>
       </c>
       <c r="K15">
         <v>4.7</v>
@@ -4197,7 +4203,7 @@
         <v>1.31</v>
       </c>
       <c r="S15">
-        <v>3.3</v>
+        <v>3.5</v>
       </c>
       <c r="T15">
         <v>2.04</v>
@@ -4209,7 +4215,7 @@
         <v>1.11</v>
       </c>
       <c r="W15">
-        <v>2.52</v>
+        <v>2.56</v>
       </c>
       <c r="X15">
         <v>16</v>
@@ -4278,10 +4284,10 @@
         <v>5.2</v>
       </c>
       <c r="AT15">
-        <v>5.9</v>
+        <v>5.7</v>
       </c>
       <c r="AU15">
-        <v>7.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AV15">
         <v>4.5</v>
@@ -4380,12 +4386,12 @@
         <v>0</v>
       </c>
       <c r="CB15" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
     </row>
     <row r="16" spans="1:80">
       <c r="A16" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="B16" t="s">
         <v>91</v>
@@ -4397,237 +4403,237 @@
         <v>116</v>
       </c>
       <c r="E16" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="F16">
+        <v>2.9</v>
+      </c>
+      <c r="G16">
+        <v>2.98</v>
+      </c>
+      <c r="H16">
+        <v>2.74</v>
+      </c>
+      <c r="I16">
+        <v>2.8</v>
+      </c>
+      <c r="J16">
+        <v>3.3</v>
+      </c>
+      <c r="K16">
+        <v>3.45</v>
+      </c>
+      <c r="L16">
+        <v>1.46</v>
+      </c>
+      <c r="M16">
+        <v>1.09</v>
+      </c>
+      <c r="N16">
+        <v>3.4</v>
+      </c>
+      <c r="O16">
+        <v>1.39</v>
+      </c>
+      <c r="P16">
+        <v>1.78</v>
+      </c>
+      <c r="Q16">
         <v>2.22</v>
       </c>
-      <c r="G16">
-        <v>2.42</v>
-      </c>
-      <c r="H16">
-        <v>3.35</v>
-      </c>
-      <c r="I16">
-        <v>3.95</v>
-      </c>
-      <c r="J16">
-        <v>3.2</v>
-      </c>
-      <c r="K16">
-        <v>3.6</v>
-      </c>
-      <c r="L16">
-        <v>1.39</v>
-      </c>
-      <c r="M16">
-        <v>1.08</v>
-      </c>
-      <c r="N16">
-        <v>3.25</v>
-      </c>
-      <c r="O16">
-        <v>1.37</v>
-      </c>
-      <c r="P16">
-        <v>1.75</v>
-      </c>
-      <c r="Q16">
-        <v>2.02</v>
-      </c>
       <c r="R16">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="S16">
-        <v>3.75</v>
+        <v>4.2</v>
       </c>
       <c r="T16">
-        <v>1.81</v>
+        <v>1.85</v>
       </c>
       <c r="U16">
-        <v>1.98</v>
+        <v>2.04</v>
       </c>
       <c r="V16">
-        <v>1.33</v>
+        <v>1.55</v>
       </c>
       <c r="W16">
-        <v>1.7</v>
+        <v>1.51</v>
       </c>
       <c r="X16">
-        <v>14.5</v>
+        <v>970</v>
       </c>
       <c r="Y16">
-        <v>14.5</v>
+        <v>16.5</v>
       </c>
       <c r="Z16">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="AA16">
-        <v>85</v>
+        <v>55</v>
       </c>
       <c r="AB16">
-        <v>10.5</v>
+        <v>16.5</v>
       </c>
       <c r="AC16">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="AD16">
-        <v>18</v>
+        <v>970</v>
       </c>
       <c r="AE16">
         <v>55</v>
       </c>
       <c r="AF16">
-        <v>16.5</v>
+        <v>22</v>
       </c>
       <c r="AG16">
-        <v>13</v>
+        <v>15.5</v>
       </c>
       <c r="AH16">
+        <v>32</v>
+      </c>
+      <c r="AI16">
+        <v>95</v>
+      </c>
+      <c r="AJ16">
+        <v>55</v>
+      </c>
+      <c r="AK16">
+        <v>46</v>
+      </c>
+      <c r="AL16">
+        <v>95</v>
+      </c>
+      <c r="AM16">
+        <v>170</v>
+      </c>
+      <c r="AN16">
+        <v>65</v>
+      </c>
+      <c r="AO16">
+        <v>50</v>
+      </c>
+      <c r="AP16">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AQ16">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AR16">
+        <v>14</v>
+      </c>
+      <c r="AS16">
+        <v>32</v>
+      </c>
+      <c r="AT16">
+        <v>8</v>
+      </c>
+      <c r="AU16">
+        <v>5.7</v>
+      </c>
+      <c r="AV16">
+        <v>10</v>
+      </c>
+      <c r="AW16">
+        <v>24</v>
+      </c>
+      <c r="AX16">
+        <v>15</v>
+      </c>
+      <c r="AY16">
+        <v>10.5</v>
+      </c>
+      <c r="AZ16">
+        <v>15</v>
+      </c>
+      <c r="BA16">
+        <v>36</v>
+      </c>
+      <c r="BB16">
+        <v>34</v>
+      </c>
+      <c r="BC16">
+        <v>27</v>
+      </c>
+      <c r="BD16">
+        <v>38</v>
+      </c>
+      <c r="BE16">
+        <v>3.15</v>
+      </c>
+      <c r="BF16">
+        <v>25</v>
+      </c>
+      <c r="BG16">
         <v>22</v>
       </c>
-      <c r="AI16">
-        <v>70</v>
-      </c>
-      <c r="AJ16">
-        <v>36</v>
-      </c>
-      <c r="AK16">
-        <v>32</v>
-      </c>
-      <c r="AL16">
-        <v>50</v>
-      </c>
-      <c r="AM16">
-        <v>130</v>
-      </c>
-      <c r="AN16">
-        <v>26</v>
-      </c>
-      <c r="AO16">
-        <v>60</v>
-      </c>
-      <c r="AP16">
-        <v>9.4</v>
-      </c>
-      <c r="AQ16">
-        <v>9.6</v>
-      </c>
-      <c r="AR16">
-        <v>19</v>
-      </c>
-      <c r="AS16">
-        <v>4.8</v>
-      </c>
-      <c r="AT16">
-        <v>7.6</v>
-      </c>
-      <c r="AU16">
-        <v>6</v>
-      </c>
-      <c r="AV16">
-        <v>11.5</v>
-      </c>
-      <c r="AW16">
-        <v>4.6</v>
-      </c>
-      <c r="AX16">
-        <v>11</v>
-      </c>
-      <c r="AY16">
-        <v>8.6</v>
-      </c>
-      <c r="AZ16">
-        <v>14</v>
-      </c>
-      <c r="BA16">
-        <v>4.7</v>
-      </c>
-      <c r="BB16">
-        <v>4.4</v>
-      </c>
-      <c r="BC16">
-        <v>20</v>
-      </c>
-      <c r="BD16">
-        <v>4.6</v>
-      </c>
-      <c r="BE16">
-        <v>4.9</v>
-      </c>
-      <c r="BF16">
-        <v>16.5</v>
-      </c>
-      <c r="BG16">
-        <v>4.7</v>
-      </c>
       <c r="BH16">
-        <v>3.3</v>
+        <v>1000</v>
       </c>
       <c r="BI16">
-        <v>2.66</v>
+        <v>1.04</v>
       </c>
       <c r="BJ16">
-        <v>10.5</v>
+        <v>1000</v>
       </c>
       <c r="BK16">
-        <v>5.2</v>
+        <v>1.04</v>
       </c>
       <c r="BL16">
         <v>1000</v>
       </c>
       <c r="BM16">
-        <v>9.6</v>
+        <v>1.04</v>
       </c>
       <c r="BN16">
-        <v>5.2</v>
+        <v>1000</v>
       </c>
       <c r="BO16">
-        <v>4</v>
+        <v>1.04</v>
       </c>
       <c r="BP16">
-        <v>18.5</v>
+        <v>1000</v>
       </c>
       <c r="BQ16">
-        <v>6.6</v>
+        <v>1.04</v>
       </c>
       <c r="BR16">
-        <v>36</v>
+        <v>1000</v>
       </c>
       <c r="BS16">
-        <v>8</v>
+        <v>1.04</v>
       </c>
       <c r="BT16">
-        <v>7</v>
+        <v>1000</v>
       </c>
       <c r="BU16">
-        <v>5.8</v>
+        <v>1.04</v>
       </c>
       <c r="BV16">
         <v>1000</v>
       </c>
       <c r="BW16">
-        <v>7.8</v>
+        <v>1.04</v>
       </c>
       <c r="BX16">
         <v>1000</v>
       </c>
       <c r="BY16">
-        <v>8.4</v>
+        <v>1.04</v>
       </c>
       <c r="BZ16">
-        <v>34</v>
+        <v>1000</v>
       </c>
       <c r="CA16">
-        <v>7.8</v>
+        <v>1.04</v>
       </c>
       <c r="CB16" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
     </row>
     <row r="17" spans="1:80">
       <c r="A17" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="B17" t="s">
         <v>91</v>
@@ -4639,232 +4645,474 @@
         <v>117</v>
       </c>
       <c r="E17" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="F17">
+        <v>2.22</v>
+      </c>
+      <c r="G17">
+        <v>2.42</v>
+      </c>
+      <c r="H17">
+        <v>3.35</v>
+      </c>
+      <c r="I17">
+        <v>3.95</v>
+      </c>
+      <c r="J17">
+        <v>3.2</v>
+      </c>
+      <c r="K17">
+        <v>3.6</v>
+      </c>
+      <c r="L17">
+        <v>1.39</v>
+      </c>
+      <c r="M17">
+        <v>1.08</v>
+      </c>
+      <c r="N17">
+        <v>3.1</v>
+      </c>
+      <c r="O17">
+        <v>1.37</v>
+      </c>
+      <c r="P17">
+        <v>1.75</v>
+      </c>
+      <c r="Q17">
+        <v>2.06</v>
+      </c>
+      <c r="R17">
+        <v>1.28</v>
+      </c>
+      <c r="S17">
+        <v>3.75</v>
+      </c>
+      <c r="T17">
+        <v>1.82</v>
+      </c>
+      <c r="U17">
+        <v>1.98</v>
+      </c>
+      <c r="V17">
+        <v>1.33</v>
+      </c>
+      <c r="W17">
+        <v>1.7</v>
+      </c>
+      <c r="X17">
+        <v>14.5</v>
+      </c>
+      <c r="Y17">
+        <v>14.5</v>
+      </c>
+      <c r="Z17">
+        <v>30</v>
+      </c>
+      <c r="AA17">
+        <v>80</v>
+      </c>
+      <c r="AB17">
+        <v>10.5</v>
+      </c>
+      <c r="AC17">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AD17">
+        <v>18</v>
+      </c>
+      <c r="AE17">
+        <v>55</v>
+      </c>
+      <c r="AF17">
+        <v>16.5</v>
+      </c>
+      <c r="AG17">
+        <v>13</v>
+      </c>
+      <c r="AH17">
+        <v>22</v>
+      </c>
+      <c r="AI17">
+        <v>70</v>
+      </c>
+      <c r="AJ17">
+        <v>36</v>
+      </c>
+      <c r="AK17">
+        <v>32</v>
+      </c>
+      <c r="AL17">
+        <v>50</v>
+      </c>
+      <c r="AM17">
+        <v>130</v>
+      </c>
+      <c r="AN17">
+        <v>26</v>
+      </c>
+      <c r="AO17">
+        <v>60</v>
+      </c>
+      <c r="AP17">
+        <v>9.4</v>
+      </c>
+      <c r="AQ17">
+        <v>9.6</v>
+      </c>
+      <c r="AR17">
+        <v>19</v>
+      </c>
+      <c r="AS17">
+        <v>4.8</v>
+      </c>
+      <c r="AT17">
+        <v>7.6</v>
+      </c>
+      <c r="AU17">
+        <v>6</v>
+      </c>
+      <c r="AV17">
+        <v>11.5</v>
+      </c>
+      <c r="AW17">
+        <v>4.7</v>
+      </c>
+      <c r="AX17">
+        <v>11</v>
+      </c>
+      <c r="AY17">
+        <v>8.6</v>
+      </c>
+      <c r="AZ17">
+        <v>14</v>
+      </c>
+      <c r="BA17">
+        <v>4.8</v>
+      </c>
+      <c r="BB17">
+        <v>4.5</v>
+      </c>
+      <c r="BC17">
+        <v>20</v>
+      </c>
+      <c r="BD17">
+        <v>4.6</v>
+      </c>
+      <c r="BE17">
+        <v>4.9</v>
+      </c>
+      <c r="BF17">
+        <v>16.5</v>
+      </c>
+      <c r="BG17">
+        <v>4.7</v>
+      </c>
+      <c r="BH17">
+        <v>3.3</v>
+      </c>
+      <c r="BI17">
+        <v>2.64</v>
+      </c>
+      <c r="BJ17">
+        <v>10.5</v>
+      </c>
+      <c r="BK17">
+        <v>5.2</v>
+      </c>
+      <c r="BL17">
+        <v>1000</v>
+      </c>
+      <c r="BM17">
+        <v>9.6</v>
+      </c>
+      <c r="BN17">
+        <v>5.2</v>
+      </c>
+      <c r="BO17">
+        <v>4</v>
+      </c>
+      <c r="BP17">
+        <v>18.5</v>
+      </c>
+      <c r="BQ17">
+        <v>6.6</v>
+      </c>
+      <c r="BR17">
+        <v>36</v>
+      </c>
+      <c r="BS17">
+        <v>8</v>
+      </c>
+      <c r="BT17">
+        <v>7</v>
+      </c>
+      <c r="BU17">
+        <v>5.3</v>
+      </c>
+      <c r="BV17">
+        <v>1000</v>
+      </c>
+      <c r="BW17">
+        <v>7.8</v>
+      </c>
+      <c r="BX17">
+        <v>1000</v>
+      </c>
+      <c r="BY17">
+        <v>8.4</v>
+      </c>
+      <c r="BZ17">
+        <v>34</v>
+      </c>
+      <c r="CA17">
+        <v>7.8</v>
+      </c>
+      <c r="CB17" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="18" spans="1:80">
+      <c r="A18" t="s">
+        <v>86</v>
+      </c>
+      <c r="B18" t="s">
+        <v>91</v>
+      </c>
+      <c r="C18" t="s">
+        <v>101</v>
+      </c>
+      <c r="D18" t="s">
+        <v>118</v>
+      </c>
+      <c r="E18" t="s">
+        <v>135</v>
+      </c>
+      <c r="F18">
         <v>1.65</v>
       </c>
-      <c r="G17">
+      <c r="G18">
         <v>1.81</v>
       </c>
-      <c r="H17">
+      <c r="H18">
         <v>5.9</v>
       </c>
-      <c r="I17">
+      <c r="I18">
         <v>7.8</v>
       </c>
-      <c r="J17">
-        <v>3.5</v>
-      </c>
-      <c r="K17">
+      <c r="J18">
+        <v>3.45</v>
+      </c>
+      <c r="K18">
+        <v>4.1</v>
+      </c>
+      <c r="L18">
+        <v>1.33</v>
+      </c>
+      <c r="M18">
+        <v>1.09</v>
+      </c>
+      <c r="N18">
+        <v>3</v>
+      </c>
+      <c r="O18">
+        <v>1.41</v>
+      </c>
+      <c r="P18">
+        <v>1.67</v>
+      </c>
+      <c r="Q18">
+        <v>2.2</v>
+      </c>
+      <c r="R18">
+        <v>1.25</v>
+      </c>
+      <c r="S18">
         <v>4</v>
       </c>
-      <c r="L17">
-        <v>1.34</v>
-      </c>
-      <c r="M17">
-        <v>1.09</v>
-      </c>
-      <c r="N17">
-        <v>2.96</v>
-      </c>
-      <c r="O17">
-        <v>1.41</v>
-      </c>
-      <c r="P17">
-        <v>1.67</v>
-      </c>
-      <c r="Q17">
-        <v>2.2</v>
-      </c>
-      <c r="R17">
-        <v>1.25</v>
-      </c>
-      <c r="S17">
-        <v>4.2</v>
-      </c>
-      <c r="T17">
-        <v>2.1</v>
-      </c>
-      <c r="U17">
-        <v>1.75</v>
-      </c>
-      <c r="V17">
-        <v>1.15</v>
-      </c>
-      <c r="W17">
+      <c r="T18">
+        <v>2.08</v>
+      </c>
+      <c r="U18">
+        <v>1.73</v>
+      </c>
+      <c r="V18">
+        <v>1.14</v>
+      </c>
+      <c r="W18">
         <v>2.22</v>
       </c>
-      <c r="X17">
+      <c r="X18">
         <v>13</v>
       </c>
-      <c r="Y17">
+      <c r="Y18">
+        <v>18</v>
+      </c>
+      <c r="Z18">
+        <v>60</v>
+      </c>
+      <c r="AA18">
+        <v>250</v>
+      </c>
+      <c r="AB18">
+        <v>7.8</v>
+      </c>
+      <c r="AC18">
+        <v>9</v>
+      </c>
+      <c r="AD18">
+        <v>30</v>
+      </c>
+      <c r="AE18">
+        <v>140</v>
+      </c>
+      <c r="AF18">
+        <v>11</v>
+      </c>
+      <c r="AG18">
+        <v>11</v>
+      </c>
+      <c r="AH18">
+        <v>30</v>
+      </c>
+      <c r="AI18">
+        <v>140</v>
+      </c>
+      <c r="AJ18">
         <v>20</v>
       </c>
-      <c r="Z17">
+      <c r="AK18">
+        <v>25</v>
+      </c>
+      <c r="AL18">
         <v>60</v>
       </c>
-      <c r="AA17">
-        <v>250</v>
-      </c>
-      <c r="AB17">
+      <c r="AM18">
+        <v>220</v>
+      </c>
+      <c r="AN18">
+        <v>15.5</v>
+      </c>
+      <c r="AO18">
+        <v>220</v>
+      </c>
+      <c r="AP18">
+        <v>8.6</v>
+      </c>
+      <c r="AQ18">
+        <v>13</v>
+      </c>
+      <c r="AR18">
+        <v>5.5</v>
+      </c>
+      <c r="AS18">
+        <v>5.9</v>
+      </c>
+      <c r="AT18">
+        <v>5.3</v>
+      </c>
+      <c r="AU18">
+        <v>7.2</v>
+      </c>
+      <c r="AV18">
+        <v>21</v>
+      </c>
+      <c r="AW18">
+        <v>5.8</v>
+      </c>
+      <c r="AX18">
         <v>7.8</v>
       </c>
-      <c r="AC17">
-        <v>9.6</v>
-      </c>
-      <c r="AD17">
-        <v>30</v>
-      </c>
-      <c r="AE17">
-        <v>140</v>
-      </c>
-      <c r="AF17">
+      <c r="AY18">
+        <v>8</v>
+      </c>
+      <c r="AZ18">
+        <v>21</v>
+      </c>
+      <c r="BA18">
+        <v>5.8</v>
+      </c>
+      <c r="BB18">
+        <v>13.5</v>
+      </c>
+      <c r="BC18">
+        <v>16</v>
+      </c>
+      <c r="BD18">
+        <v>5.5</v>
+      </c>
+      <c r="BE18">
+        <v>5.9</v>
+      </c>
+      <c r="BF18">
         <v>11</v>
       </c>
-      <c r="AG17">
-        <v>12</v>
-      </c>
-      <c r="AH17">
-        <v>30</v>
-      </c>
-      <c r="AI17">
-        <v>140</v>
-      </c>
-      <c r="AJ17">
-        <v>21</v>
-      </c>
-      <c r="AK17">
-        <v>25</v>
-      </c>
-      <c r="AL17">
-        <v>60</v>
-      </c>
-      <c r="AM17">
-        <v>220</v>
-      </c>
-      <c r="AN17">
+      <c r="BG18">
+        <v>5.9</v>
+      </c>
+      <c r="BH18">
+        <v>1000</v>
+      </c>
+      <c r="BI18">
+        <v>1.83</v>
+      </c>
+      <c r="BJ18">
+        <v>16</v>
+      </c>
+      <c r="BK18">
+        <v>1.64</v>
+      </c>
+      <c r="BL18">
+        <v>1000</v>
+      </c>
+      <c r="BM18">
+        <v>1.83</v>
+      </c>
+      <c r="BN18">
+        <v>5.3</v>
+      </c>
+      <c r="BO18">
+        <v>2.84</v>
+      </c>
+      <c r="BP18">
         <v>17</v>
       </c>
-      <c r="AO17">
-        <v>220</v>
-      </c>
-      <c r="AP17">
-        <v>8.6</v>
-      </c>
-      <c r="AQ17">
+      <c r="BQ18">
+        <v>1.65</v>
+      </c>
+      <c r="BR18">
+        <v>46</v>
+      </c>
+      <c r="BS18">
+        <v>1.76</v>
+      </c>
+      <c r="BT18">
         <v>13</v>
       </c>
-      <c r="AR17">
-        <v>38</v>
-      </c>
-      <c r="AS17">
-        <v>5.1</v>
-      </c>
-      <c r="AT17">
-        <v>5.3</v>
-      </c>
-      <c r="AU17">
-        <v>7.2</v>
-      </c>
-      <c r="AV17">
-        <v>19.5</v>
-      </c>
-      <c r="AW17">
-        <v>5</v>
-      </c>
-      <c r="AX17">
-        <v>7.4</v>
-      </c>
-      <c r="AY17">
-        <v>8</v>
-      </c>
-      <c r="AZ17">
-        <v>19</v>
-      </c>
-      <c r="BA17">
-        <v>5</v>
-      </c>
-      <c r="BB17">
-        <v>13.5</v>
-      </c>
-      <c r="BC17">
-        <v>16</v>
-      </c>
-      <c r="BD17">
-        <v>4.8</v>
-      </c>
-      <c r="BE17">
-        <v>5.1</v>
-      </c>
-      <c r="BF17">
-        <v>11</v>
-      </c>
-      <c r="BG17">
-        <v>5.1</v>
-      </c>
-      <c r="BH17">
-        <v>1000</v>
-      </c>
-      <c r="BI17">
-        <v>1.82</v>
-      </c>
-      <c r="BJ17">
-        <v>16</v>
-      </c>
-      <c r="BK17">
-        <v>1.64</v>
-      </c>
-      <c r="BL17">
-        <v>1000</v>
-      </c>
-      <c r="BM17">
-        <v>1.82</v>
-      </c>
-      <c r="BN17">
-        <v>5.4</v>
-      </c>
-      <c r="BO17">
-        <v>2.88</v>
-      </c>
-      <c r="BP17">
-        <v>17</v>
-      </c>
-      <c r="BQ17">
-        <v>1.65</v>
-      </c>
-      <c r="BR17">
-        <v>46</v>
-      </c>
-      <c r="BS17">
-        <v>1.75</v>
-      </c>
-      <c r="BT17">
-        <v>13</v>
-      </c>
-      <c r="BU17">
-        <v>1.6</v>
-      </c>
-      <c r="BV17">
-        <v>1000</v>
-      </c>
-      <c r="BW17">
-        <v>1.79</v>
-      </c>
-      <c r="BX17">
-        <v>1000</v>
-      </c>
-      <c r="BY17">
-        <v>1.79</v>
-      </c>
-      <c r="BZ17">
-        <v>0</v>
-      </c>
-      <c r="CA17">
-        <v>0</v>
-      </c>
-      <c r="CB17" t="s">
-        <v>134</v>
+      <c r="BU18">
+        <v>1.61</v>
+      </c>
+      <c r="BV18">
+        <v>1000</v>
+      </c>
+      <c r="BW18">
+        <v>1.8</v>
+      </c>
+      <c r="BX18">
+        <v>1000</v>
+      </c>
+      <c r="BY18">
+        <v>1.8</v>
+      </c>
+      <c r="BZ18">
+        <v>0</v>
+      </c>
+      <c r="CA18">
+        <v>0</v>
+      </c>
+      <c r="CB18" t="s">
+        <v>136</v>
       </c>
     </row>
   </sheetData>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-08-11.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-08-11.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="182" uniqueCount="137">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="194" uniqueCount="142">
   <si>
     <t>League</t>
   </si>
@@ -304,6 +304,9 @@
     <t>17:30:00</t>
   </si>
   <si>
+    <t>19:00:00</t>
+  </si>
+  <si>
     <t>20:30:00</t>
   </si>
   <si>
@@ -337,16 +340,19 @@
     <t>Helsingborgs</t>
   </si>
   <si>
+    <t>Chippa Utd</t>
+  </si>
+  <si>
+    <t>TS Galaxy FC</t>
+  </si>
+  <si>
     <t>Polokwane City</t>
   </si>
   <si>
     <t>Marumo Gallants FC</t>
   </si>
   <si>
-    <t>Chippa Utd</t>
-  </si>
-  <si>
-    <t>TS Galaxy FC</t>
+    <t>Tigres FC Zipaquira</t>
   </si>
   <si>
     <t>Real Santander</t>
@@ -364,15 +370,18 @@
     <t>Real Cartagena</t>
   </si>
   <si>
+    <t>Puerto Montt</t>
+  </si>
+  <si>
     <t>Ind Medellin</t>
   </si>
   <si>
-    <t>Puerto Montt</t>
-  </si>
-  <si>
     <t>Boyaca Patriotas</t>
   </si>
   <si>
+    <t>Leones FC</t>
+  </si>
+  <si>
     <t>CR Flamengo (W)</t>
   </si>
   <si>
@@ -388,16 +397,19 @@
     <t>Varnamo</t>
   </si>
   <si>
+    <t>Richards Bay FC</t>
+  </si>
+  <si>
+    <t>Mamelodi Sundowns</t>
+  </si>
+  <si>
     <t>Stellenbosch FC</t>
   </si>
   <si>
     <t>Kruger United FC</t>
   </si>
   <si>
-    <t>Richards Bay FC</t>
-  </si>
-  <si>
-    <t>Mamelodi Sundowns</t>
+    <t>Envigado</t>
   </si>
   <si>
     <t>Barranquilla</t>
@@ -415,16 +427,19 @@
     <t>Bogota</t>
   </si>
   <si>
+    <t>Union Espanola</t>
+  </si>
+  <si>
     <t>Millonarios</t>
   </si>
   <si>
-    <t>Union Espanola</t>
-  </si>
-  <si>
     <t>Orsomarso</t>
   </si>
   <si>
-    <t>2026-08-10 14:41:40</t>
+    <t>Real Soacha Cundinamarca FC</t>
+  </si>
+  <si>
+    <t>2026-08-10 16:49:46</t>
   </si>
 </sst>
 </file>
@@ -756,7 +771,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:CB18"/>
+  <dimension ref="A1:CB20"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:80">
@@ -1012,235 +1027,235 @@
         <v>92</v>
       </c>
       <c r="D2" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="E2" t="s">
-        <v>119</v>
+        <v>122</v>
       </c>
       <c r="F2">
-        <v>8.199999999999999</v>
+        <v>10.5</v>
       </c>
       <c r="G2">
-        <v>55</v>
+        <v>16</v>
       </c>
       <c r="H2">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="I2">
-        <v>1.38</v>
+        <v>1.35</v>
       </c>
       <c r="J2">
-        <v>4.6</v>
+        <v>5</v>
       </c>
       <c r="K2">
-        <v>6.6</v>
+        <v>7.2</v>
       </c>
       <c r="L2">
         <v>1.33</v>
       </c>
       <c r="M2">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="N2">
-        <v>3</v>
+        <v>4.2</v>
       </c>
       <c r="O2">
         <v>1.26</v>
       </c>
       <c r="P2">
-        <v>2.22</v>
+        <v>2.16</v>
       </c>
       <c r="Q2">
-        <v>1.69</v>
+        <v>1.73</v>
       </c>
       <c r="R2">
-        <v>1.49</v>
+        <v>1.46</v>
       </c>
       <c r="S2">
-        <v>2.66</v>
+        <v>2.82</v>
       </c>
       <c r="T2">
-        <v>1.68</v>
+        <v>2.2</v>
       </c>
       <c r="U2">
-        <v>1.73</v>
+        <v>1.71</v>
       </c>
       <c r="V2">
-        <v>3.6</v>
+        <v>3.75</v>
       </c>
       <c r="W2">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="X2">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="Y2">
-        <v>1000</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="Z2">
-        <v>1000</v>
+        <v>8</v>
       </c>
       <c r="AA2">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="AB2">
-        <v>1000</v>
+        <v>46</v>
       </c>
       <c r="AC2">
-        <v>1000</v>
+        <v>13.5</v>
       </c>
       <c r="AD2">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="AE2">
-        <v>1000</v>
+        <v>16</v>
       </c>
       <c r="AF2">
-        <v>1000</v>
+        <v>160</v>
       </c>
       <c r="AG2">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AH2">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="AI2">
-        <v>1000</v>
+        <v>48</v>
       </c>
       <c r="AJ2">
         <v>1000</v>
       </c>
       <c r="AK2">
-        <v>1000</v>
+        <v>320</v>
       </c>
       <c r="AL2">
-        <v>1000</v>
+        <v>240</v>
       </c>
       <c r="AM2">
-        <v>1000</v>
+        <v>250</v>
       </c>
       <c r="AN2">
-        <v>1000</v>
+        <v>480</v>
       </c>
       <c r="AO2">
-        <v>1000</v>
+        <v>6</v>
       </c>
       <c r="AP2">
-        <v>1.03</v>
+        <v>6</v>
       </c>
       <c r="AQ2">
-        <v>1.01</v>
+        <v>4.2</v>
       </c>
       <c r="AR2">
-        <v>1.03</v>
+        <v>4.1</v>
       </c>
       <c r="AS2">
-        <v>1.01</v>
+        <v>4.7</v>
       </c>
       <c r="AT2">
-        <v>1.03</v>
+        <v>7</v>
       </c>
       <c r="AU2">
-        <v>1.03</v>
+        <v>5.1</v>
       </c>
       <c r="AV2">
-        <v>1.03</v>
+        <v>4.9</v>
       </c>
       <c r="AW2">
-        <v>1.03</v>
+        <v>5.5</v>
       </c>
       <c r="AX2">
-        <v>1.03</v>
+        <v>7.8</v>
       </c>
       <c r="AY2">
-        <v>1.03</v>
+        <v>7.2</v>
       </c>
       <c r="AZ2">
-        <v>1.03</v>
+        <v>6.8</v>
       </c>
       <c r="BA2">
-        <v>1.03</v>
+        <v>7</v>
       </c>
       <c r="BB2">
-        <v>1.01</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BC2">
-        <v>1.01</v>
+        <v>8</v>
       </c>
       <c r="BD2">
-        <v>1.03</v>
+        <v>8</v>
       </c>
       <c r="BE2">
-        <v>1.03</v>
+        <v>8</v>
       </c>
       <c r="BF2">
-        <v>1.01</v>
+        <v>8</v>
       </c>
       <c r="BG2">
-        <v>1.02</v>
+        <v>4.8</v>
       </c>
       <c r="BH2">
-        <v>1000</v>
+        <v>4.6</v>
       </c>
       <c r="BI2">
-        <v>1.04</v>
+        <v>2.52</v>
       </c>
       <c r="BJ2">
-        <v>1000</v>
+        <v>15.5</v>
       </c>
       <c r="BK2">
-        <v>1.04</v>
+        <v>4.1</v>
       </c>
       <c r="BL2">
         <v>1000</v>
       </c>
       <c r="BM2">
-        <v>1.04</v>
+        <v>5.4</v>
       </c>
       <c r="BN2">
-        <v>1000</v>
+        <v>17.5</v>
       </c>
       <c r="BO2">
-        <v>1.04</v>
+        <v>4.2</v>
       </c>
       <c r="BP2">
         <v>1000</v>
       </c>
       <c r="BQ2">
-        <v>1.04</v>
+        <v>5.3</v>
       </c>
       <c r="BR2">
         <v>1000</v>
       </c>
       <c r="BS2">
-        <v>1.04</v>
+        <v>5.3</v>
       </c>
       <c r="BT2">
-        <v>1000</v>
+        <v>4.1</v>
       </c>
       <c r="BU2">
-        <v>1.04</v>
+        <v>2.92</v>
       </c>
       <c r="BV2">
-        <v>1000</v>
+        <v>8.6</v>
       </c>
       <c r="BW2">
-        <v>1.04</v>
+        <v>3.35</v>
       </c>
       <c r="BX2">
-        <v>1000</v>
+        <v>30</v>
       </c>
       <c r="BY2">
-        <v>1.04</v>
+        <v>4.7</v>
       </c>
       <c r="BZ2">
-        <v>1000</v>
+        <v>14.5</v>
       </c>
       <c r="CA2">
-        <v>1.04</v>
+        <v>4</v>
       </c>
       <c r="CB2" t="s">
-        <v>136</v>
+        <v>141</v>
       </c>
     </row>
     <row r="3" spans="1:80">
@@ -1254,19 +1269,19 @@
         <v>92</v>
       </c>
       <c r="D3" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="E3" t="s">
-        <v>120</v>
+        <v>123</v>
       </c>
       <c r="F3">
-        <v>2.42</v>
+        <v>2.44</v>
       </c>
       <c r="G3">
         <v>2.5</v>
       </c>
       <c r="H3">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="I3">
         <v>3.25</v>
@@ -1275,7 +1290,7 @@
         <v>3.5</v>
       </c>
       <c r="K3">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="L3">
         <v>1.47</v>
@@ -1290,7 +1305,7 @@
         <v>1.38</v>
       </c>
       <c r="P3">
-        <v>1.83</v>
+        <v>1.84</v>
       </c>
       <c r="Q3">
         <v>2.16</v>
@@ -1302,7 +1317,7 @@
         <v>4</v>
       </c>
       <c r="T3">
-        <v>1.86</v>
+        <v>1.85</v>
       </c>
       <c r="U3">
         <v>2.08</v>
@@ -1317,7 +1332,7 @@
         <v>13</v>
       </c>
       <c r="Y3">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="Z3">
         <v>23</v>
@@ -1365,7 +1380,7 @@
         <v>28</v>
       </c>
       <c r="AO3">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="AP3">
         <v>11.5</v>
@@ -1425,19 +1440,19 @@
         <v>3.7</v>
       </c>
       <c r="BI3">
-        <v>2.56</v>
+        <v>2.62</v>
       </c>
       <c r="BJ3">
-        <v>11</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BK3">
-        <v>4.4</v>
+        <v>4.7</v>
       </c>
       <c r="BL3">
         <v>1000</v>
       </c>
       <c r="BM3">
-        <v>7</v>
+        <v>8.6</v>
       </c>
       <c r="BN3">
         <v>5.3</v>
@@ -1446,16 +1461,16 @@
         <v>4.1</v>
       </c>
       <c r="BP3">
-        <v>24</v>
+        <v>19.5</v>
       </c>
       <c r="BQ3">
-        <v>5.6</v>
+        <v>6.2</v>
       </c>
       <c r="BR3">
         <v>42</v>
       </c>
       <c r="BS3">
-        <v>6.2</v>
+        <v>7.2</v>
       </c>
       <c r="BT3">
         <v>6.4</v>
@@ -1464,25 +1479,25 @@
         <v>4.8</v>
       </c>
       <c r="BV3">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="BW3">
-        <v>6</v>
+        <v>6.8</v>
       </c>
       <c r="BX3">
         <v>50</v>
       </c>
       <c r="BY3">
-        <v>6.4</v>
+        <v>7.6</v>
       </c>
       <c r="BZ3">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="CA3">
-        <v>6.2</v>
+        <v>7</v>
       </c>
       <c r="CB3" t="s">
-        <v>136</v>
+        <v>141</v>
       </c>
     </row>
     <row r="4" spans="1:80">
@@ -1496,22 +1511,22 @@
         <v>92</v>
       </c>
       <c r="D4" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="E4" t="s">
-        <v>121</v>
+        <v>124</v>
       </c>
       <c r="F4">
-        <v>1.75</v>
+        <v>1.74</v>
       </c>
       <c r="G4">
-        <v>1.8</v>
+        <v>1.79</v>
       </c>
       <c r="H4">
-        <v>5.6</v>
+        <v>5.9</v>
       </c>
       <c r="I4">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="J4">
         <v>3.65</v>
@@ -1529,40 +1544,40 @@
         <v>3.2</v>
       </c>
       <c r="O4">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="P4">
         <v>1.73</v>
       </c>
       <c r="Q4">
-        <v>2.28</v>
+        <v>2.3</v>
       </c>
       <c r="R4">
-        <v>1.27</v>
+        <v>1.26</v>
       </c>
       <c r="S4">
         <v>4.4</v>
       </c>
       <c r="T4">
-        <v>2.08</v>
+        <v>2.16</v>
       </c>
       <c r="U4">
-        <v>1.8</v>
+        <v>1.79</v>
       </c>
       <c r="V4">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="W4">
-        <v>2.24</v>
+        <v>2.26</v>
       </c>
       <c r="X4">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="Y4">
         <v>17</v>
       </c>
       <c r="Z4">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="AA4">
         <v>200</v>
@@ -1571,28 +1586,28 @@
         <v>7.2</v>
       </c>
       <c r="AC4">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AD4">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="AE4">
         <v>160</v>
       </c>
       <c r="AF4">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="AG4">
         <v>11</v>
       </c>
       <c r="AH4">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AI4">
-        <v>150</v>
+        <v>130</v>
       </c>
       <c r="AJ4">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="AK4">
         <v>22</v>
@@ -1601,16 +1616,16 @@
         <v>75</v>
       </c>
       <c r="AM4">
-        <v>180</v>
+        <v>200</v>
       </c>
       <c r="AN4">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="AO4">
         <v>190</v>
       </c>
       <c r="AP4">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="AQ4">
         <v>14</v>
@@ -1619,10 +1634,10 @@
         <v>32</v>
       </c>
       <c r="AS4">
-        <v>10.5</v>
+        <v>9.6</v>
       </c>
       <c r="AT4">
-        <v>6.4</v>
+        <v>5.9</v>
       </c>
       <c r="AU4">
         <v>7.4</v>
@@ -1634,7 +1649,7 @@
         <v>55</v>
       </c>
       <c r="AX4">
-        <v>8.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AY4">
         <v>9.199999999999999</v>
@@ -1646,85 +1661,85 @@
         <v>55</v>
       </c>
       <c r="BB4">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="BC4">
-        <v>16.5</v>
+        <v>18</v>
       </c>
       <c r="BD4">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="BE4">
-        <v>10.5</v>
+        <v>9.6</v>
       </c>
       <c r="BF4">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="BG4">
-        <v>10</v>
+        <v>90</v>
       </c>
       <c r="BH4">
         <v>3.2</v>
       </c>
       <c r="BI4">
-        <v>2.58</v>
+        <v>2.6</v>
       </c>
       <c r="BJ4">
         <v>11.5</v>
       </c>
       <c r="BK4">
-        <v>5.5</v>
+        <v>5.8</v>
       </c>
       <c r="BL4">
         <v>1000</v>
       </c>
       <c r="BM4">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="BN4">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="BO4">
         <v>3.4</v>
       </c>
       <c r="BP4">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="BQ4">
-        <v>5.9</v>
+        <v>6.2</v>
       </c>
       <c r="BR4">
         <v>1000</v>
       </c>
       <c r="BS4">
-        <v>8</v>
+        <v>8.6</v>
       </c>
       <c r="BT4">
         <v>9.4</v>
       </c>
       <c r="BU4">
-        <v>4.9</v>
+        <v>7</v>
       </c>
       <c r="BV4">
         <v>1000</v>
       </c>
       <c r="BW4">
-        <v>9</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BX4">
         <v>1000</v>
       </c>
       <c r="BY4">
-        <v>9.199999999999999</v>
+        <v>10</v>
       </c>
       <c r="BZ4">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="CA4">
-        <v>7.8</v>
+        <v>8.4</v>
       </c>
       <c r="CB4" t="s">
-        <v>136</v>
+        <v>141</v>
       </c>
     </row>
     <row r="5" spans="1:80">
@@ -1738,28 +1753,28 @@
         <v>93</v>
       </c>
       <c r="D5" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="E5" t="s">
-        <v>122</v>
+        <v>125</v>
       </c>
       <c r="F5">
         <v>1.57</v>
       </c>
       <c r="G5">
-        <v>1.6</v>
+        <v>1.59</v>
       </c>
       <c r="H5">
         <v>7.6</v>
       </c>
       <c r="I5">
-        <v>8.199999999999999</v>
+        <v>7.8</v>
       </c>
       <c r="J5">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="K5">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="L5">
         <v>1.46</v>
@@ -1768,25 +1783,25 @@
         <v>1.08</v>
       </c>
       <c r="N5">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="O5">
         <v>1.4</v>
       </c>
       <c r="P5">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="Q5">
-        <v>2.22</v>
+        <v>2.2</v>
       </c>
       <c r="R5">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="S5">
         <v>4.2</v>
       </c>
       <c r="T5">
-        <v>2.26</v>
+        <v>2.24</v>
       </c>
       <c r="U5">
         <v>1.75</v>
@@ -1798,22 +1813,22 @@
         <v>2.68</v>
       </c>
       <c r="X5">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="Y5">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="Z5">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="AA5">
-        <v>1000</v>
+        <v>320</v>
       </c>
       <c r="AB5">
         <v>6.6</v>
       </c>
       <c r="AC5">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="AD5">
         <v>32</v>
@@ -1828,13 +1843,13 @@
         <v>10.5</v>
       </c>
       <c r="AH5">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AI5">
         <v>150</v>
       </c>
       <c r="AJ5">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="AK5">
         <v>19</v>
@@ -1849,7 +1864,7 @@
         <v>11</v>
       </c>
       <c r="AO5">
-        <v>1000</v>
+        <v>280</v>
       </c>
       <c r="AP5">
         <v>11</v>
@@ -1858,43 +1873,43 @@
         <v>17.5</v>
       </c>
       <c r="AR5">
-        <v>29</v>
+        <v>42</v>
       </c>
       <c r="AS5">
-        <v>95</v>
+        <v>70</v>
       </c>
       <c r="AT5">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="AU5">
         <v>8.6</v>
       </c>
       <c r="AV5">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AW5">
         <v>50</v>
       </c>
       <c r="AX5">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="AY5">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AZ5">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="BA5">
         <v>55</v>
       </c>
       <c r="BB5">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="BC5">
         <v>17</v>
       </c>
       <c r="BD5">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="BE5">
         <v>48</v>
@@ -1918,10 +1933,10 @@
         <v>5.9</v>
       </c>
       <c r="BL5">
-        <v>220</v>
+        <v>1000</v>
       </c>
       <c r="BM5">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="BN5">
         <v>3.95</v>
@@ -1933,7 +1948,7 @@
         <v>11</v>
       </c>
       <c r="BQ5">
-        <v>5.4</v>
+        <v>8</v>
       </c>
       <c r="BR5">
         <v>34</v>
@@ -1945,7 +1960,7 @@
         <v>11.5</v>
       </c>
       <c r="BU5">
-        <v>5.5</v>
+        <v>8.4</v>
       </c>
       <c r="BV5">
         <v>85</v>
@@ -1957,16 +1972,16 @@
         <v>90</v>
       </c>
       <c r="BY5">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BZ5">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="CA5">
         <v>7.4</v>
       </c>
       <c r="CB5" t="s">
-        <v>136</v>
+        <v>141</v>
       </c>
     </row>
     <row r="6" spans="1:80">
@@ -1980,16 +1995,16 @@
         <v>94</v>
       </c>
       <c r="D6" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="E6" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="F6">
         <v>2.14</v>
       </c>
       <c r="G6">
-        <v>2.26</v>
+        <v>2.24</v>
       </c>
       <c r="H6">
         <v>3.3</v>
@@ -2001,7 +2016,7 @@
         <v>3.9</v>
       </c>
       <c r="K6">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="L6">
         <v>1.33</v>
@@ -2022,10 +2037,10 @@
         <v>1.64</v>
       </c>
       <c r="R6">
-        <v>1.55</v>
+        <v>1.56</v>
       </c>
       <c r="S6">
-        <v>2.6</v>
+        <v>2.58</v>
       </c>
       <c r="T6">
         <v>1.59</v>
@@ -2034,7 +2049,7 @@
         <v>2.5</v>
       </c>
       <c r="V6">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="W6">
         <v>1.8</v>
@@ -2133,10 +2148,10 @@
         <v>7</v>
       </c>
       <c r="BC6">
-        <v>6.8</v>
+        <v>15</v>
       </c>
       <c r="BD6">
-        <v>7</v>
+        <v>7.4</v>
       </c>
       <c r="BE6">
         <v>8.199999999999999</v>
@@ -2208,7 +2223,7 @@
         <v>0</v>
       </c>
       <c r="CB6" t="s">
-        <v>136</v>
+        <v>141</v>
       </c>
     </row>
     <row r="7" spans="1:80">
@@ -2222,103 +2237,103 @@
         <v>95</v>
       </c>
       <c r="D7" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="E7" t="s">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="F7">
-        <v>2.48</v>
+        <v>2.9</v>
       </c>
       <c r="G7">
-        <v>2.7</v>
+        <v>3.25</v>
       </c>
       <c r="H7">
-        <v>3.7</v>
+        <v>2.84</v>
       </c>
       <c r="I7">
-        <v>3.9</v>
+        <v>3.15</v>
       </c>
       <c r="J7">
-        <v>2.7</v>
+        <v>2.76</v>
       </c>
       <c r="K7">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="L7">
-        <v>1.64</v>
+        <v>1.61</v>
       </c>
       <c r="M7">
+        <v>1.15</v>
+      </c>
+      <c r="N7">
+        <v>2.4</v>
+      </c>
+      <c r="O7">
+        <v>1.61</v>
+      </c>
+      <c r="P7">
+        <v>1.45</v>
+      </c>
+      <c r="Q7">
+        <v>2.84</v>
+      </c>
+      <c r="R7">
         <v>1.16</v>
-      </c>
-      <c r="N7">
-        <v>2.22</v>
-      </c>
-      <c r="O7">
-        <v>1.66</v>
-      </c>
-      <c r="P7">
-        <v>1.4</v>
-      </c>
-      <c r="Q7">
-        <v>2.98</v>
-      </c>
-      <c r="R7">
-        <v>1.13</v>
       </c>
       <c r="S7">
         <v>6</v>
       </c>
       <c r="T7">
-        <v>2.32</v>
+        <v>2.2</v>
       </c>
       <c r="U7">
-        <v>1.64</v>
+        <v>1.71</v>
       </c>
       <c r="V7">
-        <v>1.34</v>
+        <v>1.47</v>
       </c>
       <c r="W7">
-        <v>1.59</v>
+        <v>1.44</v>
       </c>
       <c r="X7">
-        <v>8.199999999999999</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="Y7">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="Z7">
-        <v>27</v>
+        <v>21</v>
       </c>
       <c r="AA7">
-        <v>110</v>
+        <v>70</v>
       </c>
       <c r="AB7">
-        <v>7.2</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AC7">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="AD7">
-        <v>18.5</v>
+        <v>17</v>
       </c>
       <c r="AE7">
-        <v>85</v>
+        <v>55</v>
       </c>
       <c r="AF7">
-        <v>15.5</v>
+        <v>22</v>
       </c>
       <c r="AG7">
-        <v>14.5</v>
+        <v>17.5</v>
       </c>
       <c r="AH7">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="AI7">
-        <v>130</v>
+        <v>100</v>
       </c>
       <c r="AJ7">
-        <v>55</v>
+        <v>65</v>
       </c>
       <c r="AK7">
         <v>55</v>
@@ -2327,130 +2342,130 @@
         <v>100</v>
       </c>
       <c r="AM7">
-        <v>300</v>
+        <v>270</v>
       </c>
       <c r="AN7">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="AO7">
-        <v>130</v>
+        <v>70</v>
       </c>
       <c r="AP7">
-        <v>5.4</v>
+        <v>5.8</v>
       </c>
       <c r="AQ7">
-        <v>7.4</v>
+        <v>6</v>
       </c>
       <c r="AR7">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="AS7">
-        <v>7.2</v>
+        <v>4.9</v>
       </c>
       <c r="AT7">
-        <v>5.9</v>
+        <v>6.2</v>
       </c>
       <c r="AU7">
         <v>6</v>
       </c>
       <c r="AV7">
-        <v>14.5</v>
+        <v>12</v>
       </c>
       <c r="AW7">
-        <v>7</v>
+        <v>4.8</v>
       </c>
       <c r="AX7">
-        <v>12</v>
+        <v>15.5</v>
       </c>
       <c r="AY7">
-        <v>11.5</v>
+        <v>12.5</v>
       </c>
       <c r="AZ7">
         <v>20</v>
       </c>
       <c r="BA7">
-        <v>7.2</v>
+        <v>5</v>
       </c>
       <c r="BB7">
-        <v>29</v>
+        <v>4.9</v>
       </c>
       <c r="BC7">
-        <v>27</v>
+        <v>4.8</v>
       </c>
       <c r="BD7">
-        <v>7.2</v>
+        <v>5</v>
       </c>
       <c r="BE7">
-        <v>7.4</v>
+        <v>5.2</v>
       </c>
       <c r="BF7">
+        <v>4.9</v>
+      </c>
+      <c r="BG7">
+        <v>4.9</v>
+      </c>
+      <c r="BH7">
+        <v>2.64</v>
+      </c>
+      <c r="BI7">
+        <v>2.12</v>
+      </c>
+      <c r="BJ7">
+        <v>12.5</v>
+      </c>
+      <c r="BK7">
+        <v>5.8</v>
+      </c>
+      <c r="BL7">
+        <v>1000</v>
+      </c>
+      <c r="BM7">
+        <v>10.5</v>
+      </c>
+      <c r="BN7">
+        <v>6</v>
+      </c>
+      <c r="BO7">
+        <v>4.4</v>
+      </c>
+      <c r="BP7">
         <v>32</v>
       </c>
-      <c r="BG7">
-        <v>7.2</v>
-      </c>
-      <c r="BH7">
-        <v>2.78</v>
-      </c>
-      <c r="BI7">
-        <v>2.04</v>
-      </c>
-      <c r="BJ7">
-        <v>14</v>
-      </c>
-      <c r="BK7">
+      <c r="BQ7">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BR7">
+        <v>60</v>
+      </c>
+      <c r="BS7">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="BT7">
+        <v>6</v>
+      </c>
+      <c r="BU7">
         <v>4.4</v>
       </c>
-      <c r="BL7">
-        <v>1000</v>
-      </c>
-      <c r="BM7">
-        <v>6.2</v>
-      </c>
-      <c r="BN7">
-        <v>6.2</v>
-      </c>
-      <c r="BO7">
-        <v>4.5</v>
-      </c>
-      <c r="BP7">
-        <v>28</v>
-      </c>
-      <c r="BQ7">
-        <v>5.2</v>
-      </c>
-      <c r="BR7">
-        <v>70</v>
-      </c>
-      <c r="BS7">
-        <v>5.8</v>
-      </c>
-      <c r="BT7">
-        <v>6.8</v>
-      </c>
-      <c r="BU7">
-        <v>5.6</v>
-      </c>
       <c r="BV7">
-        <v>48</v>
+        <v>30</v>
       </c>
       <c r="BW7">
-        <v>5.6</v>
+        <v>8</v>
       </c>
       <c r="BX7">
-        <v>85</v>
+        <v>60</v>
       </c>
       <c r="BY7">
-        <v>5.9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BZ7">
-        <v>80</v>
+        <v>65</v>
       </c>
       <c r="CA7">
-        <v>5.9</v>
+        <v>9.4</v>
       </c>
       <c r="CB7" t="s">
-        <v>136</v>
+        <v>141</v>
       </c>
     </row>
     <row r="8" spans="1:80">
@@ -2464,235 +2479,235 @@
         <v>95</v>
       </c>
       <c r="D8" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="E8" t="s">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="F8">
-        <v>2.42</v>
+        <v>7</v>
       </c>
       <c r="G8">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="H8">
+        <v>1.55</v>
+      </c>
+      <c r="I8">
+        <v>1.63</v>
+      </c>
+      <c r="J8">
+        <v>3.95</v>
+      </c>
+      <c r="K8">
+        <v>4.4</v>
+      </c>
+      <c r="L8">
+        <v>1.41</v>
+      </c>
+      <c r="M8">
+        <v>1.07</v>
+      </c>
+      <c r="N8">
+        <v>3.45</v>
+      </c>
+      <c r="O8">
+        <v>1.34</v>
+      </c>
+      <c r="P8">
+        <v>1.84</v>
+      </c>
+      <c r="Q8">
+        <v>2.04</v>
+      </c>
+      <c r="R8">
+        <v>1.32</v>
+      </c>
+      <c r="S8">
+        <v>3.65</v>
+      </c>
+      <c r="T8">
+        <v>2.06</v>
+      </c>
+      <c r="U8">
+        <v>1.8</v>
+      </c>
+      <c r="V8">
         <v>2.58</v>
       </c>
-      <c r="H8">
-        <v>3.45</v>
-      </c>
-      <c r="I8">
-        <v>4.5</v>
-      </c>
-      <c r="J8">
-        <v>2.76</v>
-      </c>
-      <c r="K8">
+      <c r="W8">
+        <v>1.14</v>
+      </c>
+      <c r="X8">
+        <v>16.5</v>
+      </c>
+      <c r="Y8">
+        <v>8.6</v>
+      </c>
+      <c r="Z8">
+        <v>10.5</v>
+      </c>
+      <c r="AA8">
+        <v>18</v>
+      </c>
+      <c r="AB8">
+        <v>26</v>
+      </c>
+      <c r="AC8">
+        <v>11.5</v>
+      </c>
+      <c r="AD8">
+        <v>12.5</v>
+      </c>
+      <c r="AE8">
+        <v>23</v>
+      </c>
+      <c r="AF8">
+        <v>75</v>
+      </c>
+      <c r="AG8">
+        <v>34</v>
+      </c>
+      <c r="AH8">
+        <v>32</v>
+      </c>
+      <c r="AI8">
+        <v>55</v>
+      </c>
+      <c r="AJ8">
+        <v>310</v>
+      </c>
+      <c r="AK8">
+        <v>160</v>
+      </c>
+      <c r="AL8">
+        <v>150</v>
+      </c>
+      <c r="AM8">
+        <v>210</v>
+      </c>
+      <c r="AN8">
+        <v>240</v>
+      </c>
+      <c r="AO8">
+        <v>12.5</v>
+      </c>
+      <c r="AP8">
+        <v>10</v>
+      </c>
+      <c r="AQ8">
+        <v>5.5</v>
+      </c>
+      <c r="AR8">
+        <v>6.6</v>
+      </c>
+      <c r="AS8">
+        <v>10.5</v>
+      </c>
+      <c r="AT8">
+        <v>3.75</v>
+      </c>
+      <c r="AU8">
+        <v>7</v>
+      </c>
+      <c r="AV8">
+        <v>7.6</v>
+      </c>
+      <c r="AW8">
+        <v>16</v>
+      </c>
+      <c r="AX8">
+        <v>4.1</v>
+      </c>
+      <c r="AY8">
+        <v>20</v>
+      </c>
+      <c r="AZ8">
+        <v>18</v>
+      </c>
+      <c r="BA8">
+        <v>4</v>
+      </c>
+      <c r="BB8">
+        <v>4.3</v>
+      </c>
+      <c r="BC8">
+        <v>4.3</v>
+      </c>
+      <c r="BD8">
+        <v>4.2</v>
+      </c>
+      <c r="BE8">
+        <v>4.3</v>
+      </c>
+      <c r="BF8">
+        <v>4.3</v>
+      </c>
+      <c r="BG8">
+        <v>7.8</v>
+      </c>
+      <c r="BH8">
+        <v>3.85</v>
+      </c>
+      <c r="BI8">
+        <v>2.68</v>
+      </c>
+      <c r="BJ8">
+        <v>14</v>
+      </c>
+      <c r="BK8">
+        <v>3.65</v>
+      </c>
+      <c r="BL8">
+        <v>1000</v>
+      </c>
+      <c r="BM8">
+        <v>4.8</v>
+      </c>
+      <c r="BN8">
+        <v>13</v>
+      </c>
+      <c r="BO8">
+        <v>3.55</v>
+      </c>
+      <c r="BP8">
+        <v>1000</v>
+      </c>
+      <c r="BQ8">
+        <v>4.6</v>
+      </c>
+      <c r="BR8">
+        <v>1000</v>
+      </c>
+      <c r="BS8">
+        <v>4.7</v>
+      </c>
+      <c r="BT8">
+        <v>4.6</v>
+      </c>
+      <c r="BU8">
         <v>3.1</v>
       </c>
-      <c r="L8">
-        <v>1.01</v>
-      </c>
-      <c r="M8">
-        <v>1.11</v>
-      </c>
-      <c r="N8">
-        <v>2.3</v>
-      </c>
-      <c r="O8">
-        <v>1.63</v>
-      </c>
-      <c r="P8">
-        <v>1.4</v>
-      </c>
-      <c r="Q8">
-        <v>2.68</v>
-      </c>
-      <c r="R8">
-        <v>1.13</v>
-      </c>
-      <c r="S8">
-        <v>4.8</v>
-      </c>
-      <c r="T8">
-        <v>2.14</v>
-      </c>
-      <c r="U8">
-        <v>1.58</v>
-      </c>
-      <c r="V8">
-        <v>1.33</v>
-      </c>
-      <c r="W8">
-        <v>1.63</v>
-      </c>
-      <c r="X8">
-        <v>1000</v>
-      </c>
-      <c r="Y8">
-        <v>13</v>
-      </c>
-      <c r="Z8">
-        <v>34</v>
-      </c>
-      <c r="AA8">
-        <v>1000</v>
-      </c>
-      <c r="AB8">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AC8">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AD8">
-        <v>25</v>
-      </c>
-      <c r="AE8">
-        <v>1000</v>
-      </c>
-      <c r="AF8">
-        <v>21</v>
-      </c>
-      <c r="AG8">
-        <v>19.5</v>
-      </c>
-      <c r="AH8">
-        <v>950</v>
-      </c>
-      <c r="AI8">
-        <v>1000</v>
-      </c>
-      <c r="AJ8">
-        <v>1000</v>
-      </c>
-      <c r="AK8">
-        <v>1000</v>
-      </c>
-      <c r="AL8">
-        <v>1000</v>
-      </c>
-      <c r="AM8">
-        <v>1000</v>
-      </c>
-      <c r="AN8">
-        <v>1000</v>
-      </c>
-      <c r="AO8">
-        <v>1000</v>
-      </c>
-      <c r="AP8">
-        <v>1.9</v>
-      </c>
-      <c r="AQ8">
-        <v>5.9</v>
-      </c>
-      <c r="AR8">
-        <v>14.5</v>
-      </c>
-      <c r="AS8">
-        <v>1.91</v>
-      </c>
-      <c r="AT8">
-        <v>4.6</v>
-      </c>
-      <c r="AU8">
-        <v>4.6</v>
-      </c>
-      <c r="AV8">
-        <v>11</v>
-      </c>
-      <c r="AW8">
-        <v>1.91</v>
-      </c>
-      <c r="AX8">
-        <v>9</v>
-      </c>
-      <c r="AY8">
-        <v>8.4</v>
-      </c>
-      <c r="AZ8">
-        <v>16</v>
-      </c>
-      <c r="BA8">
-        <v>1.91</v>
-      </c>
-      <c r="BB8">
-        <v>1.91</v>
-      </c>
-      <c r="BC8">
-        <v>1.91</v>
-      </c>
-      <c r="BD8">
-        <v>1.91</v>
-      </c>
-      <c r="BE8">
-        <v>1.91</v>
-      </c>
-      <c r="BF8">
-        <v>1.91</v>
-      </c>
-      <c r="BG8">
-        <v>1.91</v>
-      </c>
-      <c r="BH8">
-        <v>1000</v>
-      </c>
-      <c r="BI8">
-        <v>1.04</v>
-      </c>
-      <c r="BJ8">
-        <v>1000</v>
-      </c>
-      <c r="BK8">
-        <v>1.04</v>
-      </c>
-      <c r="BL8">
-        <v>1000</v>
-      </c>
-      <c r="BM8">
-        <v>1.04</v>
-      </c>
-      <c r="BN8">
-        <v>1000</v>
-      </c>
-      <c r="BO8">
-        <v>1.04</v>
-      </c>
-      <c r="BP8">
-        <v>1000</v>
-      </c>
-      <c r="BQ8">
-        <v>1.04</v>
-      </c>
-      <c r="BR8">
-        <v>1000</v>
-      </c>
-      <c r="BS8">
-        <v>1.04</v>
-      </c>
-      <c r="BT8">
-        <v>1000</v>
-      </c>
-      <c r="BU8">
-        <v>1.04</v>
-      </c>
       <c r="BV8">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="BW8">
-        <v>1.04</v>
+        <v>3.5</v>
       </c>
       <c r="BX8">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="BY8">
-        <v>1.04</v>
+        <v>4.3</v>
       </c>
       <c r="BZ8">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="CA8">
-        <v>1.04</v>
+        <v>4.1</v>
       </c>
       <c r="CB8" t="s">
-        <v>136</v>
+        <v>141</v>
       </c>
     </row>
     <row r="9" spans="1:80">
@@ -2706,103 +2721,103 @@
         <v>95</v>
       </c>
       <c r="D9" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="E9" t="s">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c r="F9">
-        <v>2.9</v>
+        <v>2.48</v>
       </c>
       <c r="G9">
-        <v>3.25</v>
+        <v>2.7</v>
       </c>
       <c r="H9">
-        <v>2.84</v>
+        <v>3.4</v>
       </c>
       <c r="I9">
-        <v>3.15</v>
+        <v>3.95</v>
       </c>
       <c r="J9">
-        <v>2.76</v>
+        <v>2.7</v>
       </c>
       <c r="K9">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="L9">
-        <v>1.52</v>
+        <v>1.65</v>
       </c>
       <c r="M9">
-        <v>1.14</v>
+        <v>1.16</v>
       </c>
       <c r="N9">
-        <v>2.36</v>
+        <v>2.22</v>
       </c>
       <c r="O9">
-        <v>1.61</v>
+        <v>1.66</v>
       </c>
       <c r="P9">
-        <v>1.45</v>
+        <v>1.4</v>
       </c>
       <c r="Q9">
-        <v>2.82</v>
+        <v>3</v>
       </c>
       <c r="R9">
-        <v>1.16</v>
+        <v>1.13</v>
       </c>
       <c r="S9">
         <v>6</v>
       </c>
       <c r="T9">
-        <v>2.18</v>
+        <v>2.32</v>
       </c>
       <c r="U9">
-        <v>1.71</v>
+        <v>1.64</v>
       </c>
       <c r="V9">
-        <v>1.47</v>
+        <v>1.34</v>
       </c>
       <c r="W9">
-        <v>1.44</v>
+        <v>1.59</v>
       </c>
       <c r="X9">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="Y9">
         <v>9.199999999999999</v>
       </c>
-      <c r="Y9">
-        <v>9.6</v>
-      </c>
       <c r="Z9">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="AA9">
-        <v>70</v>
+        <v>110</v>
       </c>
       <c r="AB9">
-        <v>9.800000000000001</v>
+        <v>7.2</v>
       </c>
       <c r="AC9">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="AD9">
-        <v>17</v>
+        <v>18.5</v>
       </c>
       <c r="AE9">
+        <v>85</v>
+      </c>
+      <c r="AF9">
+        <v>15.5</v>
+      </c>
+      <c r="AG9">
+        <v>14.5</v>
+      </c>
+      <c r="AH9">
+        <v>29</v>
+      </c>
+      <c r="AI9">
+        <v>130</v>
+      </c>
+      <c r="AJ9">
         <v>55</v>
-      </c>
-      <c r="AF9">
-        <v>22</v>
-      </c>
-      <c r="AG9">
-        <v>17.5</v>
-      </c>
-      <c r="AH9">
-        <v>30</v>
-      </c>
-      <c r="AI9">
-        <v>100</v>
-      </c>
-      <c r="AJ9">
-        <v>65</v>
       </c>
       <c r="AK9">
         <v>55</v>
@@ -2811,130 +2826,130 @@
         <v>100</v>
       </c>
       <c r="AM9">
-        <v>270</v>
+        <v>300</v>
       </c>
       <c r="AN9">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="AO9">
-        <v>70</v>
+        <v>130</v>
       </c>
       <c r="AP9">
-        <v>5.8</v>
+        <v>5.4</v>
       </c>
       <c r="AQ9">
-        <v>6</v>
+        <v>7.4</v>
       </c>
       <c r="AR9">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="AS9">
-        <v>4.9</v>
+        <v>7.2</v>
       </c>
       <c r="AT9">
-        <v>6.2</v>
+        <v>5.9</v>
       </c>
       <c r="AU9">
         <v>6</v>
       </c>
       <c r="AV9">
+        <v>14.5</v>
+      </c>
+      <c r="AW9">
+        <v>7.2</v>
+      </c>
+      <c r="AX9">
         <v>12</v>
       </c>
-      <c r="AW9">
-        <v>4.8</v>
-      </c>
-      <c r="AX9">
-        <v>15.5</v>
-      </c>
       <c r="AY9">
-        <v>12.5</v>
+        <v>11.5</v>
       </c>
       <c r="AZ9">
         <v>20</v>
       </c>
       <c r="BA9">
-        <v>5</v>
+        <v>7.4</v>
       </c>
       <c r="BB9">
-        <v>4.9</v>
+        <v>29</v>
       </c>
       <c r="BC9">
-        <v>4.8</v>
+        <v>27</v>
       </c>
       <c r="BD9">
-        <v>5</v>
+        <v>7.2</v>
       </c>
       <c r="BE9">
-        <v>5.2</v>
+        <v>7.6</v>
       </c>
       <c r="BF9">
-        <v>4.9</v>
+        <v>32</v>
       </c>
       <c r="BG9">
-        <v>4.9</v>
+        <v>7.4</v>
       </c>
       <c r="BH9">
-        <v>2.64</v>
+        <v>2.76</v>
       </c>
       <c r="BI9">
-        <v>2.12</v>
+        <v>2.04</v>
       </c>
       <c r="BJ9">
-        <v>12.5</v>
+        <v>15</v>
       </c>
       <c r="BK9">
-        <v>5.8</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BL9">
         <v>1000</v>
       </c>
       <c r="BM9">
-        <v>10.5</v>
+        <v>6.8</v>
       </c>
       <c r="BN9">
-        <v>6</v>
+        <v>5.4</v>
       </c>
       <c r="BO9">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="BP9">
         <v>32</v>
       </c>
       <c r="BQ9">
-        <v>8.199999999999999</v>
+        <v>5.7</v>
       </c>
       <c r="BR9">
-        <v>60</v>
+        <v>70</v>
       </c>
       <c r="BS9">
-        <v>9.199999999999999</v>
+        <v>6.2</v>
       </c>
       <c r="BT9">
-        <v>6</v>
+        <v>6.8</v>
       </c>
       <c r="BU9">
-        <v>4.4</v>
+        <v>5.6</v>
       </c>
       <c r="BV9">
-        <v>30</v>
+        <v>48</v>
       </c>
       <c r="BW9">
-        <v>8</v>
+        <v>5.9</v>
       </c>
       <c r="BX9">
-        <v>60</v>
+        <v>1000</v>
       </c>
       <c r="BY9">
-        <v>9.199999999999999</v>
+        <v>6.4</v>
       </c>
       <c r="BZ9">
-        <v>65</v>
+        <v>85</v>
       </c>
       <c r="CA9">
-        <v>9.4</v>
+        <v>6.4</v>
       </c>
       <c r="CB9" t="s">
-        <v>136</v>
+        <v>141</v>
       </c>
     </row>
     <row r="10" spans="1:80">
@@ -2948,235 +2963,235 @@
         <v>95</v>
       </c>
       <c r="D10" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="E10" t="s">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="F10">
-        <v>7</v>
+        <v>2.42</v>
       </c>
       <c r="G10">
-        <v>8.199999999999999</v>
+        <v>2.58</v>
       </c>
       <c r="H10">
-        <v>1.55</v>
+        <v>3.55</v>
       </c>
       <c r="I10">
-        <v>1.64</v>
+        <v>4.5</v>
       </c>
       <c r="J10">
-        <v>3.95</v>
+        <v>2.76</v>
       </c>
       <c r="K10">
-        <v>4.4</v>
+        <v>3.1</v>
       </c>
       <c r="L10">
-        <v>1.35</v>
+        <v>1.01</v>
       </c>
       <c r="M10">
-        <v>1.07</v>
+        <v>1.11</v>
       </c>
       <c r="N10">
-        <v>3.45</v>
+        <v>2.28</v>
       </c>
       <c r="O10">
-        <v>1.34</v>
+        <v>1.62</v>
       </c>
       <c r="P10">
-        <v>1.84</v>
+        <v>1.43</v>
       </c>
       <c r="Q10">
-        <v>2.04</v>
+        <v>2.68</v>
       </c>
       <c r="R10">
+        <v>1.13</v>
+      </c>
+      <c r="S10">
+        <v>4.8</v>
+      </c>
+      <c r="T10">
+        <v>2.14</v>
+      </c>
+      <c r="U10">
+        <v>1.58</v>
+      </c>
+      <c r="V10">
         <v>1.32</v>
       </c>
-      <c r="S10">
-        <v>3.65</v>
-      </c>
-      <c r="T10">
-        <v>2.06</v>
-      </c>
-      <c r="U10">
-        <v>1.8</v>
-      </c>
-      <c r="V10">
-        <v>2.56</v>
-      </c>
       <c r="W10">
-        <v>1.14</v>
+        <v>1.63</v>
       </c>
       <c r="X10">
-        <v>16.5</v>
+        <v>1000</v>
       </c>
       <c r="Y10">
-        <v>8.6</v>
+        <v>13</v>
       </c>
       <c r="Z10">
-        <v>10.5</v>
+        <v>34</v>
       </c>
       <c r="AA10">
-        <v>18</v>
+        <v>1000</v>
       </c>
       <c r="AB10">
-        <v>26</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AC10">
-        <v>11.5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AD10">
-        <v>12.5</v>
+        <v>25</v>
       </c>
       <c r="AE10">
-        <v>23</v>
+        <v>1000</v>
       </c>
       <c r="AF10">
-        <v>75</v>
+        <v>21</v>
       </c>
       <c r="AG10">
-        <v>34</v>
+        <v>19.5</v>
       </c>
       <c r="AH10">
-        <v>32</v>
+        <v>950</v>
       </c>
       <c r="AI10">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="AJ10">
-        <v>310</v>
+        <v>1000</v>
       </c>
       <c r="AK10">
-        <v>160</v>
+        <v>1000</v>
       </c>
       <c r="AL10">
-        <v>150</v>
+        <v>1000</v>
       </c>
       <c r="AM10">
-        <v>210</v>
+        <v>1000</v>
       </c>
       <c r="AN10">
-        <v>240</v>
+        <v>1000</v>
       </c>
       <c r="AO10">
-        <v>12.5</v>
+        <v>1000</v>
       </c>
       <c r="AP10">
-        <v>10</v>
+        <v>1.9</v>
       </c>
       <c r="AQ10">
-        <v>5.5</v>
+        <v>5.9</v>
       </c>
       <c r="AR10">
-        <v>6.6</v>
+        <v>14.5</v>
       </c>
       <c r="AS10">
-        <v>10.5</v>
+        <v>1.91</v>
       </c>
       <c r="AT10">
-        <v>15</v>
+        <v>4.6</v>
       </c>
       <c r="AU10">
-        <v>7</v>
+        <v>4.6</v>
       </c>
       <c r="AV10">
-        <v>7.6</v>
+        <v>11</v>
       </c>
       <c r="AW10">
+        <v>1.91</v>
+      </c>
+      <c r="AX10">
+        <v>9</v>
+      </c>
+      <c r="AY10">
+        <v>8.4</v>
+      </c>
+      <c r="AZ10">
         <v>16</v>
       </c>
-      <c r="AX10">
-        <v>4.1</v>
-      </c>
-      <c r="AY10">
-        <v>20</v>
-      </c>
-      <c r="AZ10">
-        <v>18</v>
-      </c>
       <c r="BA10">
-        <v>4</v>
+        <v>1.91</v>
       </c>
       <c r="BB10">
-        <v>4.3</v>
+        <v>1.91</v>
       </c>
       <c r="BC10">
-        <v>4.3</v>
+        <v>1.91</v>
       </c>
       <c r="BD10">
-        <v>4.2</v>
+        <v>1.91</v>
       </c>
       <c r="BE10">
-        <v>4.3</v>
+        <v>1.91</v>
       </c>
       <c r="BF10">
-        <v>4.3</v>
+        <v>1.91</v>
       </c>
       <c r="BG10">
-        <v>7.8</v>
+        <v>1.91</v>
       </c>
       <c r="BH10">
-        <v>3.85</v>
+        <v>1000</v>
       </c>
       <c r="BI10">
-        <v>3</v>
+        <v>1.04</v>
       </c>
       <c r="BJ10">
-        <v>14</v>
+        <v>1000</v>
       </c>
       <c r="BK10">
-        <v>3.65</v>
+        <v>1.04</v>
       </c>
       <c r="BL10">
         <v>1000</v>
       </c>
       <c r="BM10">
-        <v>4.8</v>
+        <v>1.04</v>
       </c>
       <c r="BN10">
-        <v>13</v>
+        <v>1000</v>
       </c>
       <c r="BO10">
-        <v>3.55</v>
+        <v>1.04</v>
       </c>
       <c r="BP10">
         <v>1000</v>
       </c>
       <c r="BQ10">
-        <v>4.6</v>
+        <v>1.04</v>
       </c>
       <c r="BR10">
         <v>1000</v>
       </c>
       <c r="BS10">
-        <v>4.7</v>
+        <v>1.04</v>
       </c>
       <c r="BT10">
-        <v>4.6</v>
+        <v>1000</v>
       </c>
       <c r="BU10">
-        <v>3.1</v>
+        <v>1.04</v>
       </c>
       <c r="BV10">
-        <v>12.5</v>
+        <v>1000</v>
       </c>
       <c r="BW10">
-        <v>3.5</v>
+        <v>1.04</v>
       </c>
       <c r="BX10">
-        <v>36</v>
+        <v>1000</v>
       </c>
       <c r="BY10">
-        <v>4.3</v>
+        <v>1.04</v>
       </c>
       <c r="BZ10">
-        <v>26</v>
+        <v>1000</v>
       </c>
       <c r="CA10">
-        <v>4.1</v>
+        <v>1.04</v>
       </c>
       <c r="CB10" t="s">
-        <v>136</v>
+        <v>141</v>
       </c>
     </row>
     <row r="11" spans="1:80">
@@ -3190,240 +3205,240 @@
         <v>96</v>
       </c>
       <c r="D11" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="E11" t="s">
-        <v>128</v>
+        <v>131</v>
       </c>
       <c r="F11">
-        <v>2.5</v>
+        <v>3.15</v>
       </c>
       <c r="G11">
-        <v>2.82</v>
+        <v>3.9</v>
       </c>
       <c r="H11">
-        <v>2.86</v>
+        <v>2.48</v>
       </c>
       <c r="I11">
-        <v>3.3</v>
+        <v>2.96</v>
       </c>
       <c r="J11">
-        <v>3.2</v>
+        <v>2.7</v>
       </c>
       <c r="K11">
-        <v>3.65</v>
+        <v>2.94</v>
       </c>
       <c r="L11">
-        <v>1.39</v>
+        <v>1.28</v>
       </c>
       <c r="M11">
-        <v>1.08</v>
+        <v>1.01</v>
       </c>
       <c r="N11">
-        <v>3.25</v>
+        <v>1.02</v>
       </c>
       <c r="O11">
-        <v>1.37</v>
+        <v>1.01</v>
       </c>
       <c r="P11">
-        <v>1.76</v>
+        <v>1.18</v>
       </c>
       <c r="Q11">
-        <v>2.08</v>
+        <v>1.19</v>
       </c>
       <c r="R11">
-        <v>1.29</v>
+        <v>1.02</v>
       </c>
       <c r="S11">
-        <v>3.75</v>
+        <v>1.05</v>
       </c>
       <c r="T11">
         <v>1.8</v>
       </c>
       <c r="U11">
-        <v>2.02</v>
+        <v>1.71</v>
       </c>
       <c r="V11">
-        <v>1.43</v>
+        <v>1.01</v>
       </c>
       <c r="W11">
-        <v>1.54</v>
+        <v>1.01</v>
       </c>
       <c r="X11">
-        <v>14</v>
+        <v>970</v>
       </c>
       <c r="Y11">
-        <v>11.5</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="Z11">
-        <v>21</v>
+        <v>17.5</v>
       </c>
       <c r="AA11">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="AB11">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AC11">
         <v>7.8</v>
       </c>
       <c r="AD11">
-        <v>14</v>
+        <v>970</v>
       </c>
       <c r="AE11">
-        <v>40</v>
+        <v>55</v>
       </c>
       <c r="AF11">
-        <v>17.5</v>
+        <v>25</v>
       </c>
       <c r="AG11">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="AH11">
-        <v>19</v>
+        <v>32</v>
       </c>
       <c r="AI11">
-        <v>55</v>
+        <v>95</v>
       </c>
       <c r="AJ11">
-        <v>42</v>
+        <v>90</v>
       </c>
       <c r="AK11">
-        <v>32</v>
+        <v>80</v>
       </c>
       <c r="AL11">
-        <v>48</v>
+        <v>110</v>
       </c>
       <c r="AM11">
-        <v>130</v>
+        <v>230</v>
       </c>
       <c r="AN11">
-        <v>34</v>
+        <v>160</v>
       </c>
       <c r="AO11">
-        <v>38</v>
+        <v>65</v>
       </c>
       <c r="AP11">
-        <v>9.4</v>
+        <v>6.2</v>
       </c>
       <c r="AQ11">
-        <v>9.4</v>
+        <v>6.2</v>
       </c>
       <c r="AR11">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="AS11">
-        <v>7.6</v>
+        <v>30</v>
       </c>
       <c r="AT11">
-        <v>8.6</v>
+        <v>7</v>
       </c>
       <c r="AU11">
-        <v>6.4</v>
+        <v>5.5</v>
       </c>
       <c r="AV11">
-        <v>11.5</v>
+        <v>10</v>
       </c>
       <c r="AW11">
         <v>29</v>
       </c>
       <c r="AX11">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="AY11">
-        <v>10.5</v>
+        <v>11.5</v>
       </c>
       <c r="AZ11">
-        <v>15.5</v>
+        <v>20</v>
       </c>
       <c r="BA11">
+        <v>50</v>
+      </c>
+      <c r="BB11">
+        <v>46</v>
+      </c>
+      <c r="BC11">
+        <v>40</v>
+      </c>
+      <c r="BD11">
+        <v>55</v>
+      </c>
+      <c r="BE11">
+        <v>5</v>
+      </c>
+      <c r="BF11">
+        <v>5.5</v>
+      </c>
+      <c r="BG11">
         <v>36</v>
       </c>
-      <c r="BB11">
-        <v>7.2</v>
-      </c>
-      <c r="BC11">
-        <v>19.5</v>
-      </c>
-      <c r="BD11">
-        <v>7.4</v>
-      </c>
-      <c r="BE11">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="BF11">
-        <v>21</v>
-      </c>
-      <c r="BG11">
-        <v>7.2</v>
-      </c>
       <c r="BH11">
-        <v>3.3</v>
+        <v>1000</v>
       </c>
       <c r="BI11">
-        <v>2.86</v>
+        <v>1.04</v>
       </c>
       <c r="BJ11">
-        <v>10</v>
+        <v>1000</v>
       </c>
       <c r="BK11">
-        <v>5.3</v>
+        <v>1.04</v>
       </c>
       <c r="BL11">
         <v>1000</v>
       </c>
       <c r="BM11">
-        <v>10.5</v>
+        <v>1.04</v>
       </c>
       <c r="BN11">
-        <v>5.7</v>
+        <v>1000</v>
       </c>
       <c r="BO11">
-        <v>4.4</v>
+        <v>1.04</v>
       </c>
       <c r="BP11">
-        <v>22</v>
+        <v>1000</v>
       </c>
       <c r="BQ11">
-        <v>7.4</v>
+        <v>1.04</v>
       </c>
       <c r="BR11">
-        <v>36</v>
+        <v>1000</v>
       </c>
       <c r="BS11">
-        <v>8.6</v>
+        <v>1.04</v>
       </c>
       <c r="BT11">
-        <v>6.2</v>
+        <v>1000</v>
       </c>
       <c r="BU11">
-        <v>4.8</v>
+        <v>1.04</v>
       </c>
       <c r="BV11">
-        <v>26</v>
+        <v>1000</v>
       </c>
       <c r="BW11">
-        <v>7.8</v>
+        <v>1.04</v>
       </c>
       <c r="BX11">
-        <v>40</v>
+        <v>1000</v>
       </c>
       <c r="BY11">
-        <v>8.800000000000001</v>
+        <v>1.04</v>
       </c>
       <c r="BZ11">
-        <v>34</v>
+        <v>1000</v>
       </c>
       <c r="CA11">
-        <v>8.4</v>
+        <v>1.04</v>
       </c>
       <c r="CB11" t="s">
-        <v>136</v>
+        <v>141</v>
       </c>
     </row>
     <row r="12" spans="1:80">
       <c r="A12" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="B12" t="s">
         <v>91</v>
@@ -3432,240 +3447,240 @@
         <v>97</v>
       </c>
       <c r="D12" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="E12" t="s">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="F12">
-        <v>1.9</v>
+        <v>2.34</v>
       </c>
       <c r="G12">
-        <v>2.08</v>
+        <v>2.94</v>
       </c>
       <c r="H12">
-        <v>4.1</v>
+        <v>2.8</v>
       </c>
       <c r="I12">
+        <v>3.95</v>
+      </c>
+      <c r="J12">
+        <v>2.72</v>
+      </c>
+      <c r="K12">
+        <v>3.65</v>
+      </c>
+      <c r="L12">
+        <v>1.43</v>
+      </c>
+      <c r="M12">
+        <v>1.08</v>
+      </c>
+      <c r="N12">
+        <v>3.25</v>
+      </c>
+      <c r="O12">
+        <v>1.37</v>
+      </c>
+      <c r="P12">
+        <v>1.66</v>
+      </c>
+      <c r="Q12">
+        <v>2.02</v>
+      </c>
+      <c r="R12">
+        <v>1.29</v>
+      </c>
+      <c r="S12">
+        <v>3.45</v>
+      </c>
+      <c r="T12">
+        <v>1.11</v>
+      </c>
+      <c r="U12">
+        <v>1.11</v>
+      </c>
+      <c r="V12">
+        <v>1.34</v>
+      </c>
+      <c r="W12">
+        <v>1.51</v>
+      </c>
+      <c r="X12">
+        <v>14</v>
+      </c>
+      <c r="Y12">
+        <v>11.5</v>
+      </c>
+      <c r="Z12">
+        <v>21</v>
+      </c>
+      <c r="AA12">
+        <v>55</v>
+      </c>
+      <c r="AB12">
+        <v>10.5</v>
+      </c>
+      <c r="AC12">
+        <v>7.8</v>
+      </c>
+      <c r="AD12">
+        <v>14</v>
+      </c>
+      <c r="AE12">
+        <v>38</v>
+      </c>
+      <c r="AF12">
+        <v>17.5</v>
+      </c>
+      <c r="AG12">
+        <v>13</v>
+      </c>
+      <c r="AH12">
+        <v>18.5</v>
+      </c>
+      <c r="AI12">
+        <v>55</v>
+      </c>
+      <c r="AJ12">
+        <v>42</v>
+      </c>
+      <c r="AK12">
+        <v>32</v>
+      </c>
+      <c r="AL12">
+        <v>48</v>
+      </c>
+      <c r="AM12">
+        <v>120</v>
+      </c>
+      <c r="AN12">
+        <v>34</v>
+      </c>
+      <c r="AO12">
+        <v>38</v>
+      </c>
+      <c r="AP12">
+        <v>9.4</v>
+      </c>
+      <c r="AQ12">
+        <v>9.4</v>
+      </c>
+      <c r="AR12">
+        <v>17</v>
+      </c>
+      <c r="AS12">
+        <v>38</v>
+      </c>
+      <c r="AT12">
+        <v>8.6</v>
+      </c>
+      <c r="AU12">
+        <v>6.4</v>
+      </c>
+      <c r="AV12">
+        <v>11.5</v>
+      </c>
+      <c r="AW12">
+        <v>29</v>
+      </c>
+      <c r="AX12">
+        <v>14</v>
+      </c>
+      <c r="AY12">
+        <v>10.5</v>
+      </c>
+      <c r="AZ12">
+        <v>15.5</v>
+      </c>
+      <c r="BA12">
+        <v>36</v>
+      </c>
+      <c r="BB12">
+        <v>7.4</v>
+      </c>
+      <c r="BC12">
+        <v>19.5</v>
+      </c>
+      <c r="BD12">
+        <v>7.6</v>
+      </c>
+      <c r="BE12">
+        <v>8.4</v>
+      </c>
+      <c r="BF12">
+        <v>21</v>
+      </c>
+      <c r="BG12">
+        <v>7.4</v>
+      </c>
+      <c r="BH12">
+        <v>3.25</v>
+      </c>
+      <c r="BI12">
+        <v>2.86</v>
+      </c>
+      <c r="BJ12">
+        <v>10</v>
+      </c>
+      <c r="BK12">
         <v>5.4</v>
       </c>
-      <c r="J12">
-        <v>3.5</v>
-      </c>
-      <c r="K12">
-        <v>3.85</v>
-      </c>
-      <c r="L12">
-        <v>1.01</v>
-      </c>
-      <c r="M12">
-        <v>1.09</v>
-      </c>
-      <c r="N12">
-        <v>1.64</v>
-      </c>
-      <c r="O12">
-        <v>1.43</v>
-      </c>
-      <c r="P12">
-        <v>1.64</v>
-      </c>
-      <c r="Q12">
-        <v>2.24</v>
-      </c>
-      <c r="R12">
-        <v>1.13</v>
-      </c>
-      <c r="S12">
-        <v>2.24</v>
-      </c>
-      <c r="T12">
-        <v>1.7</v>
-      </c>
-      <c r="U12">
-        <v>1.45</v>
-      </c>
-      <c r="V12">
-        <v>1.23</v>
-      </c>
-      <c r="W12">
-        <v>1.92</v>
-      </c>
-      <c r="X12">
-        <v>19</v>
-      </c>
-      <c r="Y12">
-        <v>16.5</v>
-      </c>
-      <c r="Z12">
-        <v>95</v>
-      </c>
-      <c r="AA12">
-        <v>500</v>
-      </c>
-      <c r="AB12">
+      <c r="BL12">
+        <v>1000</v>
+      </c>
+      <c r="BM12">
         <v>11</v>
       </c>
-      <c r="AC12">
-        <v>13</v>
-      </c>
-      <c r="AD12">
-        <v>970</v>
-      </c>
-      <c r="AE12">
-        <v>500</v>
-      </c>
-      <c r="AF12">
-        <v>17</v>
-      </c>
-      <c r="AG12">
-        <v>18.5</v>
-      </c>
-      <c r="AH12">
-        <v>55</v>
-      </c>
-      <c r="AI12">
-        <v>500</v>
-      </c>
-      <c r="AJ12">
-        <v>48</v>
-      </c>
-      <c r="AK12">
-        <v>65</v>
-      </c>
-      <c r="AL12">
-        <v>500</v>
-      </c>
-      <c r="AM12">
-        <v>580</v>
-      </c>
-      <c r="AN12">
-        <v>500</v>
-      </c>
-      <c r="AO12">
-        <v>130</v>
-      </c>
-      <c r="AP12">
-        <v>8.6</v>
-      </c>
-      <c r="AQ12">
-        <v>11.5</v>
-      </c>
-      <c r="AR12">
-        <v>15.5</v>
-      </c>
-      <c r="AS12">
-        <v>2.72</v>
-      </c>
-      <c r="AT12">
-        <v>5.7</v>
-      </c>
-      <c r="AU12">
-        <v>6</v>
-      </c>
-      <c r="AV12">
-        <v>15</v>
-      </c>
-      <c r="AW12">
-        <v>23</v>
-      </c>
-      <c r="AX12">
+      <c r="BN12">
+        <v>5.6</v>
+      </c>
+      <c r="BO12">
+        <v>4.3</v>
+      </c>
+      <c r="BP12">
+        <v>21</v>
+      </c>
+      <c r="BQ12">
+        <v>7.6</v>
+      </c>
+      <c r="BR12">
+        <v>36</v>
+      </c>
+      <c r="BS12">
+        <v>9</v>
+      </c>
+      <c r="BT12">
+        <v>6.4</v>
+      </c>
+      <c r="BU12">
+        <v>4.8</v>
+      </c>
+      <c r="BV12">
+        <v>26</v>
+      </c>
+      <c r="BW12">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BX12">
+        <v>40</v>
+      </c>
+      <c r="BY12">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="BZ12">
+        <v>34</v>
+      </c>
+      <c r="CA12">
         <v>8.800000000000001</v>
       </c>
-      <c r="AY12">
-        <v>8.4</v>
-      </c>
-      <c r="AZ12">
-        <v>19</v>
-      </c>
-      <c r="BA12">
-        <v>17.5</v>
-      </c>
-      <c r="BB12">
-        <v>12</v>
-      </c>
-      <c r="BC12">
-        <v>18</v>
-      </c>
-      <c r="BD12">
-        <v>34</v>
-      </c>
-      <c r="BE12">
-        <v>2.74</v>
-      </c>
-      <c r="BF12">
-        <v>15</v>
-      </c>
-      <c r="BG12">
-        <v>2.64</v>
-      </c>
-      <c r="BH12">
-        <v>1000</v>
-      </c>
-      <c r="BI12">
-        <v>1.04</v>
-      </c>
-      <c r="BJ12">
-        <v>1000</v>
-      </c>
-      <c r="BK12">
-        <v>1.04</v>
-      </c>
-      <c r="BL12">
-        <v>1000</v>
-      </c>
-      <c r="BM12">
-        <v>1.04</v>
-      </c>
-      <c r="BN12">
-        <v>1000</v>
-      </c>
-      <c r="BO12">
-        <v>1.04</v>
-      </c>
-      <c r="BP12">
-        <v>1000</v>
-      </c>
-      <c r="BQ12">
-        <v>1.04</v>
-      </c>
-      <c r="BR12">
-        <v>1000</v>
-      </c>
-      <c r="BS12">
-        <v>1.04</v>
-      </c>
-      <c r="BT12">
-        <v>1000</v>
-      </c>
-      <c r="BU12">
-        <v>1.04</v>
-      </c>
-      <c r="BV12">
-        <v>1000</v>
-      </c>
-      <c r="BW12">
-        <v>1.04</v>
-      </c>
-      <c r="BX12">
-        <v>1000</v>
-      </c>
-      <c r="BY12">
-        <v>1.04</v>
-      </c>
-      <c r="BZ12">
-        <v>1000</v>
-      </c>
-      <c r="CA12">
-        <v>1.04</v>
-      </c>
       <c r="CB12" t="s">
-        <v>136</v>
+        <v>141</v>
       </c>
     </row>
     <row r="13" spans="1:80">
       <c r="A13" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="B13" t="s">
         <v>91</v>
@@ -3674,240 +3689,240 @@
         <v>98</v>
       </c>
       <c r="D13" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="E13" t="s">
-        <v>130</v>
+        <v>133</v>
       </c>
       <c r="F13">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="G13">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="H13">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="I13">
-        <v>0</v>
+        <v>5.1</v>
       </c>
       <c r="J13">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="K13">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="L13">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="M13">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="N13">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="O13">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="P13">
-        <v>1.25</v>
+        <v>1.71</v>
       </c>
       <c r="Q13">
-        <v>1.9</v>
+        <v>2.32</v>
       </c>
       <c r="R13">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="S13">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="T13">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="U13">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="V13">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="W13">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="X13">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="Y13">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="Z13">
-        <v>0</v>
+        <v>85</v>
       </c>
       <c r="AA13">
-        <v>0</v>
+        <v>500</v>
       </c>
       <c r="AB13">
-        <v>0</v>
+        <v>7.4</v>
       </c>
       <c r="AC13">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="AD13">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="AE13">
-        <v>0</v>
+        <v>190</v>
       </c>
       <c r="AF13">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="AG13">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="AH13">
-        <v>0</v>
+        <v>42</v>
       </c>
       <c r="AI13">
-        <v>0</v>
+        <v>230</v>
       </c>
       <c r="AJ13">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="AK13">
-        <v>0</v>
+        <v>46</v>
       </c>
       <c r="AL13">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="AM13">
-        <v>0</v>
+        <v>580</v>
       </c>
       <c r="AN13">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="AO13">
-        <v>0</v>
+        <v>140</v>
       </c>
       <c r="AP13">
-        <v>0</v>
+        <v>8.6</v>
       </c>
       <c r="AQ13">
-        <v>0</v>
+        <v>11.5</v>
       </c>
       <c r="AR13">
-        <v>0</v>
+        <v>15.5</v>
       </c>
       <c r="AS13">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="AT13">
-        <v>0</v>
+        <v>5.7</v>
       </c>
       <c r="AU13">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="AV13">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="AW13">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="AX13">
-        <v>0</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AY13">
-        <v>0</v>
+        <v>8.4</v>
       </c>
       <c r="AZ13">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="BA13">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="BB13">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="BC13">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="BD13">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="BE13">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="BF13">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="BG13">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="BH13">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="BI13">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="BJ13">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="BK13">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="BL13">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM13">
-        <v>0</v>
+        <v>5.8</v>
       </c>
       <c r="BN13">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="BO13">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="BP13">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="BQ13">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="BR13">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="BS13">
-        <v>0</v>
+        <v>5.2</v>
       </c>
       <c r="BT13">
-        <v>0</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BU13">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="BV13">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW13">
-        <v>0</v>
+        <v>5.4</v>
       </c>
       <c r="BX13">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY13">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="BZ13">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="CA13">
-        <v>0</v>
+        <v>5.2</v>
       </c>
       <c r="CB13" t="s">
-        <v>136</v>
+        <v>141</v>
       </c>
     </row>
     <row r="14" spans="1:80">
       <c r="A14" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="B14" t="s">
         <v>91</v>
@@ -3916,240 +3931,240 @@
         <v>99</v>
       </c>
       <c r="D14" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="E14" t="s">
-        <v>131</v>
+        <v>134</v>
       </c>
       <c r="F14">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="G14">
-        <v>2.96</v>
+        <v>0</v>
       </c>
       <c r="H14">
-        <v>2.82</v>
+        <v>0</v>
       </c>
       <c r="I14">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="J14">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="K14">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="L14">
-        <v>1.46</v>
+        <v>0</v>
       </c>
       <c r="M14">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="N14">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="O14">
-        <v>1.39</v>
+        <v>0</v>
       </c>
       <c r="P14">
-        <v>1.77</v>
+        <v>1.25</v>
       </c>
       <c r="Q14">
-        <v>2.14</v>
+        <v>1.9</v>
       </c>
       <c r="R14">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="S14">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="T14">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="U14">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="V14">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="W14">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="X14">
-        <v>14.5</v>
+        <v>0</v>
       </c>
       <c r="Y14">
-        <v>10.5</v>
+        <v>0</v>
       </c>
       <c r="Z14">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="AA14">
-        <v>65</v>
+        <v>0</v>
       </c>
       <c r="AB14">
-        <v>10.5</v>
+        <v>0</v>
       </c>
       <c r="AC14">
-        <v>7.6</v>
+        <v>0</v>
       </c>
       <c r="AD14">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="AE14">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="AF14">
-        <v>19.5</v>
+        <v>0</v>
       </c>
       <c r="AG14">
-        <v>13.5</v>
+        <v>0</v>
       </c>
       <c r="AH14">
-        <v>18.5</v>
+        <v>0</v>
       </c>
       <c r="AI14">
-        <v>70</v>
+        <v>0</v>
       </c>
       <c r="AJ14">
-        <v>70</v>
+        <v>0</v>
       </c>
       <c r="AK14">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="AL14">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="AM14">
-        <v>130</v>
+        <v>0</v>
       </c>
       <c r="AN14">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="AO14">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="AP14">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="AQ14">
-        <v>8.800000000000001</v>
+        <v>0</v>
       </c>
       <c r="AR14">
-        <v>15.5</v>
+        <v>0</v>
       </c>
       <c r="AS14">
-        <v>8.800000000000001</v>
+        <v>0</v>
       </c>
       <c r="AT14">
-        <v>9.199999999999999</v>
+        <v>0</v>
       </c>
       <c r="AU14">
-        <v>6.6</v>
+        <v>0</v>
       </c>
       <c r="AV14">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="AW14">
-        <v>8.4</v>
+        <v>0</v>
       </c>
       <c r="AX14">
-        <v>16.5</v>
+        <v>0</v>
       </c>
       <c r="AY14">
-        <v>11.5</v>
+        <v>0</v>
       </c>
       <c r="AZ14">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="BA14">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="BB14">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="BC14">
-        <v>8.4</v>
+        <v>0</v>
       </c>
       <c r="BD14">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="BE14">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="BF14">
-        <v>8.4</v>
+        <v>0</v>
       </c>
       <c r="BG14">
-        <v>8.199999999999999</v>
+        <v>0</v>
       </c>
       <c r="BH14">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="BI14">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="BJ14">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="BK14">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="BL14">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BM14">
-        <v>13.5</v>
+        <v>0</v>
       </c>
       <c r="BN14">
-        <v>5.9</v>
+        <v>0</v>
       </c>
       <c r="BO14">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="BP14">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="BQ14">
-        <v>9.4</v>
+        <v>0</v>
       </c>
       <c r="BR14">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="BS14">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="BT14">
-        <v>5.7</v>
+        <v>0</v>
       </c>
       <c r="BU14">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="BV14">
-        <v>23</v>
+        <v>0</v>
       </c>
       <c r="BW14">
-        <v>9.199999999999999</v>
+        <v>0</v>
       </c>
       <c r="BX14">
-        <v>38</v>
+        <v>0</v>
       </c>
       <c r="BY14">
-        <v>10.5</v>
+        <v>0</v>
       </c>
       <c r="BZ14">
-        <v>34</v>
+        <v>0</v>
       </c>
       <c r="CA14">
-        <v>10.5</v>
+        <v>0</v>
       </c>
       <c r="CB14" t="s">
-        <v>136</v>
+        <v>141</v>
       </c>
     </row>
     <row r="15" spans="1:80">
       <c r="A15" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="B15" t="s">
         <v>91</v>
@@ -4158,240 +4173,240 @@
         <v>100</v>
       </c>
       <c r="D15" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="E15" t="s">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="F15">
+        <v>2.8</v>
+      </c>
+      <c r="G15">
+        <v>2.98</v>
+      </c>
+      <c r="H15">
+        <v>2.74</v>
+      </c>
+      <c r="I15">
+        <v>2.9</v>
+      </c>
+      <c r="J15">
+        <v>3.2</v>
+      </c>
+      <c r="K15">
+        <v>3.5</v>
+      </c>
+      <c r="L15">
+        <v>1.38</v>
+      </c>
+      <c r="M15">
+        <v>1.09</v>
+      </c>
+      <c r="N15">
+        <v>3.2</v>
+      </c>
+      <c r="O15">
+        <v>1.39</v>
+      </c>
+      <c r="P15">
+        <v>1.77</v>
+      </c>
+      <c r="Q15">
+        <v>2.14</v>
+      </c>
+      <c r="R15">
+        <v>1.29</v>
+      </c>
+      <c r="S15">
+        <v>4</v>
+      </c>
+      <c r="T15">
+        <v>1.85</v>
+      </c>
+      <c r="U15">
+        <v>2.02</v>
+      </c>
+      <c r="V15">
+        <v>1.53</v>
+      </c>
+      <c r="W15">
         <v>1.51</v>
       </c>
-      <c r="G15">
-        <v>1.64</v>
-      </c>
-      <c r="H15">
-        <v>7</v>
-      </c>
-      <c r="I15">
-        <v>9.4</v>
-      </c>
-      <c r="J15">
-        <v>3.8</v>
-      </c>
-      <c r="K15">
-        <v>4.7</v>
-      </c>
-      <c r="L15">
-        <v>1.36</v>
-      </c>
-      <c r="M15">
-        <v>1.07</v>
-      </c>
-      <c r="N15">
-        <v>3.35</v>
-      </c>
-      <c r="O15">
-        <v>1.33</v>
-      </c>
-      <c r="P15">
-        <v>1.82</v>
-      </c>
-      <c r="Q15">
-        <v>1.98</v>
-      </c>
-      <c r="R15">
-        <v>1.31</v>
-      </c>
-      <c r="S15">
-        <v>3.5</v>
-      </c>
-      <c r="T15">
-        <v>2.04</v>
-      </c>
-      <c r="U15">
-        <v>1.77</v>
-      </c>
-      <c r="V15">
-        <v>1.11</v>
-      </c>
-      <c r="W15">
-        <v>2.56</v>
-      </c>
       <c r="X15">
-        <v>16</v>
+        <v>14.5</v>
       </c>
       <c r="Y15">
-        <v>25</v>
+        <v>10.5</v>
       </c>
       <c r="Z15">
-        <v>75</v>
+        <v>18</v>
       </c>
       <c r="AA15">
-        <v>310</v>
+        <v>65</v>
       </c>
       <c r="AB15">
-        <v>8.4</v>
+        <v>10.5</v>
       </c>
       <c r="AC15">
-        <v>11</v>
+        <v>7.6</v>
       </c>
       <c r="AD15">
-        <v>34</v>
+        <v>13</v>
       </c>
       <c r="AE15">
-        <v>160</v>
+        <v>50</v>
       </c>
       <c r="AF15">
-        <v>10</v>
+        <v>19.5</v>
       </c>
       <c r="AG15">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AH15">
-        <v>30</v>
+        <v>18.5</v>
       </c>
       <c r="AI15">
-        <v>140</v>
+        <v>70</v>
       </c>
       <c r="AJ15">
-        <v>17</v>
+        <v>70</v>
       </c>
       <c r="AK15">
-        <v>21</v>
+        <v>50</v>
       </c>
       <c r="AL15">
         <v>50</v>
       </c>
       <c r="AM15">
-        <v>200</v>
+        <v>130</v>
       </c>
       <c r="AN15">
+        <v>50</v>
+      </c>
+      <c r="AO15">
+        <v>32</v>
+      </c>
+      <c r="AP15">
+        <v>9</v>
+      </c>
+      <c r="AQ15">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AR15">
+        <v>15.5</v>
+      </c>
+      <c r="AS15">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AT15">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AU15">
+        <v>6.6</v>
+      </c>
+      <c r="AV15">
+        <v>11</v>
+      </c>
+      <c r="AW15">
+        <v>8.6</v>
+      </c>
+      <c r="AX15">
+        <v>16.5</v>
+      </c>
+      <c r="AY15">
         <v>11.5</v>
       </c>
-      <c r="AO15">
-        <v>240</v>
-      </c>
-      <c r="AP15">
+      <c r="AZ15">
+        <v>16</v>
+      </c>
+      <c r="BA15">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="BB15">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="BC15">
+        <v>8.6</v>
+      </c>
+      <c r="BD15">
+        <v>30</v>
+      </c>
+      <c r="BE15">
         <v>10.5</v>
       </c>
-      <c r="AQ15">
-        <v>16.5</v>
-      </c>
-      <c r="AR15">
-        <v>4.9</v>
-      </c>
-      <c r="AS15">
-        <v>5.2</v>
-      </c>
-      <c r="AT15">
+      <c r="BF15">
+        <v>8.6</v>
+      </c>
+      <c r="BG15">
+        <v>8.4</v>
+      </c>
+      <c r="BH15">
+        <v>3.15</v>
+      </c>
+      <c r="BI15">
+        <v>2.6</v>
+      </c>
+      <c r="BJ15">
+        <v>10</v>
+      </c>
+      <c r="BK15">
+        <v>6</v>
+      </c>
+      <c r="BL15">
+        <v>1000</v>
+      </c>
+      <c r="BM15">
+        <v>13.5</v>
+      </c>
+      <c r="BN15">
+        <v>5.9</v>
+      </c>
+      <c r="BO15">
+        <v>4.4</v>
+      </c>
+      <c r="BP15">
+        <v>24</v>
+      </c>
+      <c r="BQ15">
+        <v>9.4</v>
+      </c>
+      <c r="BR15">
+        <v>40</v>
+      </c>
+      <c r="BS15">
+        <v>11</v>
+      </c>
+      <c r="BT15">
         <v>5.7</v>
       </c>
-      <c r="AU15">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AV15">
-        <v>4.5</v>
-      </c>
-      <c r="AW15">
-        <v>5.1</v>
-      </c>
-      <c r="AX15">
-        <v>6.8</v>
-      </c>
-      <c r="AY15">
-        <v>7.8</v>
-      </c>
-      <c r="AZ15">
-        <v>19.5</v>
-      </c>
-      <c r="BA15">
-        <v>5</v>
-      </c>
-      <c r="BB15">
-        <v>11</v>
-      </c>
-      <c r="BC15">
-        <v>13.5</v>
-      </c>
-      <c r="BD15">
-        <v>4.7</v>
-      </c>
-      <c r="BE15">
-        <v>5.1</v>
-      </c>
-      <c r="BF15">
-        <v>7.8</v>
-      </c>
-      <c r="BG15">
-        <v>5.1</v>
-      </c>
-      <c r="BH15">
-        <v>3.45</v>
-      </c>
-      <c r="BI15">
-        <v>2.78</v>
-      </c>
-      <c r="BJ15">
-        <v>12</v>
-      </c>
-      <c r="BK15">
-        <v>5.6</v>
-      </c>
-      <c r="BL15">
-        <v>1000</v>
-      </c>
-      <c r="BM15">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="BN15">
-        <v>4.1</v>
-      </c>
-      <c r="BO15">
-        <v>3.15</v>
-      </c>
-      <c r="BP15">
-        <v>11</v>
-      </c>
-      <c r="BQ15">
-        <v>5.3</v>
-      </c>
-      <c r="BR15">
-        <v>1000</v>
-      </c>
-      <c r="BS15">
-        <v>7.6</v>
-      </c>
-      <c r="BT15">
-        <v>11.5</v>
-      </c>
       <c r="BU15">
-        <v>5.4</v>
+        <v>4.3</v>
       </c>
       <c r="BV15">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="BW15">
         <v>9.199999999999999</v>
       </c>
       <c r="BX15">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="BY15">
-        <v>9.199999999999999</v>
+        <v>10.5</v>
       </c>
       <c r="BZ15">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="CA15">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="CB15" t="s">
-        <v>136</v>
+        <v>141</v>
       </c>
     </row>
     <row r="16" spans="1:80">
       <c r="A16" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="B16" t="s">
         <v>91</v>
@@ -4400,235 +4415,235 @@
         <v>101</v>
       </c>
       <c r="D16" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="E16" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="F16">
-        <v>2.9</v>
+        <v>1.48</v>
       </c>
       <c r="G16">
-        <v>2.98</v>
+        <v>1.66</v>
       </c>
       <c r="H16">
-        <v>2.74</v>
+        <v>6.2</v>
       </c>
       <c r="I16">
-        <v>2.8</v>
+        <v>9.4</v>
       </c>
       <c r="J16">
-        <v>3.3</v>
+        <v>3.45</v>
       </c>
       <c r="K16">
-        <v>3.45</v>
+        <v>4.7</v>
       </c>
       <c r="L16">
-        <v>1.46</v>
+        <v>1.38</v>
       </c>
       <c r="M16">
-        <v>1.09</v>
+        <v>1.07</v>
       </c>
       <c r="N16">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="O16">
-        <v>1.39</v>
+        <v>1.33</v>
       </c>
       <c r="P16">
-        <v>1.78</v>
+        <v>1.82</v>
       </c>
       <c r="Q16">
-        <v>2.22</v>
+        <v>1.92</v>
       </c>
       <c r="R16">
-        <v>1.29</v>
+        <v>1.31</v>
       </c>
       <c r="S16">
+        <v>3.5</v>
+      </c>
+      <c r="T16">
+        <v>2.04</v>
+      </c>
+      <c r="U16">
+        <v>1.77</v>
+      </c>
+      <c r="V16">
+        <v>1.11</v>
+      </c>
+      <c r="W16">
+        <v>2.46</v>
+      </c>
+      <c r="X16">
+        <v>16</v>
+      </c>
+      <c r="Y16">
+        <v>25</v>
+      </c>
+      <c r="Z16">
+        <v>75</v>
+      </c>
+      <c r="AA16">
+        <v>310</v>
+      </c>
+      <c r="AB16">
+        <v>7.6</v>
+      </c>
+      <c r="AC16">
+        <v>11</v>
+      </c>
+      <c r="AD16">
+        <v>34</v>
+      </c>
+      <c r="AE16">
+        <v>160</v>
+      </c>
+      <c r="AF16">
+        <v>10</v>
+      </c>
+      <c r="AG16">
+        <v>12</v>
+      </c>
+      <c r="AH16">
+        <v>30</v>
+      </c>
+      <c r="AI16">
+        <v>140</v>
+      </c>
+      <c r="AJ16">
+        <v>16.5</v>
+      </c>
+      <c r="AK16">
+        <v>21</v>
+      </c>
+      <c r="AL16">
+        <v>50</v>
+      </c>
+      <c r="AM16">
+        <v>200</v>
+      </c>
+      <c r="AN16">
+        <v>11.5</v>
+      </c>
+      <c r="AO16">
+        <v>240</v>
+      </c>
+      <c r="AP16">
         <v>4.2</v>
       </c>
-      <c r="T16">
-        <v>1.85</v>
-      </c>
-      <c r="U16">
-        <v>2.04</v>
-      </c>
-      <c r="V16">
-        <v>1.55</v>
-      </c>
-      <c r="W16">
-        <v>1.51</v>
-      </c>
-      <c r="X16">
-        <v>970</v>
-      </c>
-      <c r="Y16">
-        <v>16.5</v>
-      </c>
-      <c r="Z16">
-        <v>20</v>
-      </c>
-      <c r="AA16">
-        <v>55</v>
-      </c>
-      <c r="AB16">
-        <v>16.5</v>
-      </c>
-      <c r="AC16">
+      <c r="AQ16">
+        <v>4.6</v>
+      </c>
+      <c r="AR16">
+        <v>5.3</v>
+      </c>
+      <c r="AS16">
+        <v>5.6</v>
+      </c>
+      <c r="AT16">
+        <v>3.25</v>
+      </c>
+      <c r="AU16">
+        <v>3.75</v>
+      </c>
+      <c r="AV16">
+        <v>4.9</v>
+      </c>
+      <c r="AW16">
+        <v>5.5</v>
+      </c>
+      <c r="AX16">
+        <v>3.6</v>
+      </c>
+      <c r="AY16">
+        <v>3.85</v>
+      </c>
+      <c r="AZ16">
+        <v>4.8</v>
+      </c>
+      <c r="BA16">
+        <v>5.5</v>
+      </c>
+      <c r="BB16">
+        <v>4.2</v>
+      </c>
+      <c r="BC16">
+        <v>4.4</v>
+      </c>
+      <c r="BD16">
+        <v>5.1</v>
+      </c>
+      <c r="BE16">
+        <v>5.5</v>
+      </c>
+      <c r="BF16">
+        <v>3.8</v>
+      </c>
+      <c r="BG16">
+        <v>5.5</v>
+      </c>
+      <c r="BH16">
+        <v>3.5</v>
+      </c>
+      <c r="BI16">
+        <v>2.78</v>
+      </c>
+      <c r="BJ16">
+        <v>12.5</v>
+      </c>
+      <c r="BK16">
+        <v>5.4</v>
+      </c>
+      <c r="BL16">
+        <v>1000</v>
+      </c>
+      <c r="BM16">
+        <v>9</v>
+      </c>
+      <c r="BN16">
+        <v>4.1</v>
+      </c>
+      <c r="BO16">
+        <v>3.15</v>
+      </c>
+      <c r="BP16">
+        <v>11</v>
+      </c>
+      <c r="BQ16">
+        <v>5.1</v>
+      </c>
+      <c r="BR16">
+        <v>1000</v>
+      </c>
+      <c r="BS16">
+        <v>7.2</v>
+      </c>
+      <c r="BT16">
+        <v>11.5</v>
+      </c>
+      <c r="BU16">
+        <v>5.2</v>
+      </c>
+      <c r="BV16">
+        <v>1000</v>
+      </c>
+      <c r="BW16">
+        <v>8.4</v>
+      </c>
+      <c r="BX16">
+        <v>1000</v>
+      </c>
+      <c r="BY16">
         <v>8.6</v>
       </c>
-      <c r="AD16">
-        <v>970</v>
-      </c>
-      <c r="AE16">
-        <v>55</v>
-      </c>
-      <c r="AF16">
-        <v>22</v>
-      </c>
-      <c r="AG16">
-        <v>15.5</v>
-      </c>
-      <c r="AH16">
-        <v>32</v>
-      </c>
-      <c r="AI16">
-        <v>95</v>
-      </c>
-      <c r="AJ16">
-        <v>55</v>
-      </c>
-      <c r="AK16">
-        <v>46</v>
-      </c>
-      <c r="AL16">
-        <v>95</v>
-      </c>
-      <c r="AM16">
-        <v>170</v>
-      </c>
-      <c r="AN16">
-        <v>65</v>
-      </c>
-      <c r="AO16">
-        <v>50</v>
-      </c>
-      <c r="AP16">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AQ16">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AR16">
-        <v>14</v>
-      </c>
-      <c r="AS16">
-        <v>32</v>
-      </c>
-      <c r="AT16">
-        <v>8</v>
-      </c>
-      <c r="AU16">
-        <v>5.7</v>
-      </c>
-      <c r="AV16">
-        <v>10</v>
-      </c>
-      <c r="AW16">
-        <v>24</v>
-      </c>
-      <c r="AX16">
-        <v>15</v>
-      </c>
-      <c r="AY16">
-        <v>10.5</v>
-      </c>
-      <c r="AZ16">
-        <v>15</v>
-      </c>
-      <c r="BA16">
-        <v>36</v>
-      </c>
-      <c r="BB16">
-        <v>34</v>
-      </c>
-      <c r="BC16">
-        <v>27</v>
-      </c>
-      <c r="BD16">
-        <v>38</v>
-      </c>
-      <c r="BE16">
-        <v>3.15</v>
-      </c>
-      <c r="BF16">
-        <v>25</v>
-      </c>
-      <c r="BG16">
-        <v>22</v>
-      </c>
-      <c r="BH16">
-        <v>1000</v>
-      </c>
-      <c r="BI16">
-        <v>1.04</v>
-      </c>
-      <c r="BJ16">
-        <v>1000</v>
-      </c>
-      <c r="BK16">
-        <v>1.04</v>
-      </c>
-      <c r="BL16">
-        <v>1000</v>
-      </c>
-      <c r="BM16">
-        <v>1.04</v>
-      </c>
-      <c r="BN16">
-        <v>1000</v>
-      </c>
-      <c r="BO16">
-        <v>1.04</v>
-      </c>
-      <c r="BP16">
-        <v>1000</v>
-      </c>
-      <c r="BQ16">
-        <v>1.04</v>
-      </c>
-      <c r="BR16">
-        <v>1000</v>
-      </c>
-      <c r="BS16">
-        <v>1.04</v>
-      </c>
-      <c r="BT16">
-        <v>1000</v>
-      </c>
-      <c r="BU16">
-        <v>1.04</v>
-      </c>
-      <c r="BV16">
-        <v>1000</v>
-      </c>
-      <c r="BW16">
-        <v>1.04</v>
-      </c>
-      <c r="BX16">
-        <v>1000</v>
-      </c>
-      <c r="BY16">
-        <v>1.04</v>
-      </c>
       <c r="BZ16">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="CA16">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="CB16" t="s">
-        <v>136</v>
+        <v>141</v>
       </c>
     </row>
     <row r="17" spans="1:80">
@@ -4639,13 +4654,13 @@
         <v>91</v>
       </c>
       <c r="C17" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="D17" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="E17" t="s">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="F17">
         <v>2.22</v>
@@ -4657,31 +4672,31 @@
         <v>3.35</v>
       </c>
       <c r="I17">
-        <v>3.95</v>
+        <v>3.8</v>
       </c>
       <c r="J17">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="K17">
         <v>3.6</v>
       </c>
       <c r="L17">
-        <v>1.39</v>
+        <v>1.44</v>
       </c>
       <c r="M17">
         <v>1.08</v>
       </c>
       <c r="N17">
-        <v>3.1</v>
+        <v>3.25</v>
       </c>
       <c r="O17">
         <v>1.37</v>
       </c>
       <c r="P17">
-        <v>1.75</v>
+        <v>1.77</v>
       </c>
       <c r="Q17">
-        <v>2.06</v>
+        <v>2.08</v>
       </c>
       <c r="R17">
         <v>1.28</v>
@@ -4690,13 +4705,13 @@
         <v>3.75</v>
       </c>
       <c r="T17">
-        <v>1.82</v>
+        <v>1.83</v>
       </c>
       <c r="U17">
-        <v>1.98</v>
+        <v>2</v>
       </c>
       <c r="V17">
-        <v>1.33</v>
+        <v>1.37</v>
       </c>
       <c r="W17">
         <v>1.7</v>
@@ -4711,7 +4726,7 @@
         <v>30</v>
       </c>
       <c r="AA17">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="AB17">
         <v>10.5</v>
@@ -4768,7 +4783,7 @@
         <v>4.8</v>
       </c>
       <c r="AT17">
-        <v>7.6</v>
+        <v>7</v>
       </c>
       <c r="AU17">
         <v>6</v>
@@ -4783,7 +4798,7 @@
         <v>11</v>
       </c>
       <c r="AY17">
-        <v>8.6</v>
+        <v>9.6</v>
       </c>
       <c r="AZ17">
         <v>14</v>
@@ -4870,249 +4885,733 @@
         <v>7.8</v>
       </c>
       <c r="CB17" t="s">
-        <v>136</v>
+        <v>141</v>
       </c>
     </row>
     <row r="18" spans="1:80">
       <c r="A18" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="B18" t="s">
         <v>91</v>
       </c>
       <c r="C18" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="D18" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="E18" t="s">
-        <v>135</v>
+        <v>138</v>
       </c>
       <c r="F18">
-        <v>1.65</v>
+        <v>2.82</v>
       </c>
       <c r="G18">
-        <v>1.81</v>
+        <v>2.98</v>
       </c>
       <c r="H18">
-        <v>5.9</v>
+        <v>2.72</v>
       </c>
       <c r="I18">
-        <v>7.8</v>
+        <v>2.88</v>
       </c>
       <c r="J18">
-        <v>3.45</v>
+        <v>3.2</v>
       </c>
       <c r="K18">
-        <v>4.1</v>
+        <v>3.5</v>
       </c>
       <c r="L18">
-        <v>1.33</v>
+        <v>1.37</v>
       </c>
       <c r="M18">
         <v>1.09</v>
       </c>
       <c r="N18">
-        <v>3</v>
+        <v>3.3</v>
       </c>
       <c r="O18">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="P18">
-        <v>1.67</v>
+        <v>1.76</v>
       </c>
       <c r="Q18">
-        <v>2.2</v>
+        <v>2.18</v>
       </c>
       <c r="R18">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="S18">
         <v>4</v>
       </c>
       <c r="T18">
+        <v>1.84</v>
+      </c>
+      <c r="U18">
+        <v>2.06</v>
+      </c>
+      <c r="V18">
+        <v>1.53</v>
+      </c>
+      <c r="W18">
+        <v>1.51</v>
+      </c>
+      <c r="X18">
+        <v>12</v>
+      </c>
+      <c r="Y18">
+        <v>10.5</v>
+      </c>
+      <c r="Z18">
+        <v>18.5</v>
+      </c>
+      <c r="AA18">
+        <v>55</v>
+      </c>
+      <c r="AB18">
+        <v>11</v>
+      </c>
+      <c r="AC18">
+        <v>7.8</v>
+      </c>
+      <c r="AD18">
+        <v>13</v>
+      </c>
+      <c r="AE18">
+        <v>55</v>
+      </c>
+      <c r="AF18">
+        <v>21</v>
+      </c>
+      <c r="AG18">
+        <v>14</v>
+      </c>
+      <c r="AH18">
+        <v>19.5</v>
+      </c>
+      <c r="AI18">
+        <v>60</v>
+      </c>
+      <c r="AJ18">
+        <v>55</v>
+      </c>
+      <c r="AK18">
+        <v>44</v>
+      </c>
+      <c r="AL18">
+        <v>65</v>
+      </c>
+      <c r="AM18">
+        <v>170</v>
+      </c>
+      <c r="AN18">
+        <v>65</v>
+      </c>
+      <c r="AO18">
+        <v>50</v>
+      </c>
+      <c r="AP18">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AQ18">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AR18">
+        <v>14</v>
+      </c>
+      <c r="AS18">
+        <v>32</v>
+      </c>
+      <c r="AT18">
+        <v>8</v>
+      </c>
+      <c r="AU18">
+        <v>5.7</v>
+      </c>
+      <c r="AV18">
+        <v>10</v>
+      </c>
+      <c r="AW18">
+        <v>24</v>
+      </c>
+      <c r="AX18">
+        <v>15</v>
+      </c>
+      <c r="AY18">
+        <v>10.5</v>
+      </c>
+      <c r="AZ18">
+        <v>15</v>
+      </c>
+      <c r="BA18">
+        <v>36</v>
+      </c>
+      <c r="BB18">
+        <v>34</v>
+      </c>
+      <c r="BC18">
+        <v>27</v>
+      </c>
+      <c r="BD18">
+        <v>8</v>
+      </c>
+      <c r="BE18">
+        <v>8.4</v>
+      </c>
+      <c r="BF18">
+        <v>25</v>
+      </c>
+      <c r="BG18">
+        <v>22</v>
+      </c>
+      <c r="BH18">
+        <v>1000</v>
+      </c>
+      <c r="BI18">
+        <v>1.04</v>
+      </c>
+      <c r="BJ18">
+        <v>1000</v>
+      </c>
+      <c r="BK18">
+        <v>1.04</v>
+      </c>
+      <c r="BL18">
+        <v>1000</v>
+      </c>
+      <c r="BM18">
+        <v>1.04</v>
+      </c>
+      <c r="BN18">
+        <v>1000</v>
+      </c>
+      <c r="BO18">
+        <v>1.04</v>
+      </c>
+      <c r="BP18">
+        <v>1000</v>
+      </c>
+      <c r="BQ18">
+        <v>1.04</v>
+      </c>
+      <c r="BR18">
+        <v>1000</v>
+      </c>
+      <c r="BS18">
+        <v>1.04</v>
+      </c>
+      <c r="BT18">
+        <v>1000</v>
+      </c>
+      <c r="BU18">
+        <v>1.04</v>
+      </c>
+      <c r="BV18">
+        <v>1000</v>
+      </c>
+      <c r="BW18">
+        <v>1.04</v>
+      </c>
+      <c r="BX18">
+        <v>1000</v>
+      </c>
+      <c r="BY18">
+        <v>1.04</v>
+      </c>
+      <c r="BZ18">
+        <v>1000</v>
+      </c>
+      <c r="CA18">
+        <v>1.04</v>
+      </c>
+      <c r="CB18" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="19" spans="1:80">
+      <c r="A19" t="s">
+        <v>86</v>
+      </c>
+      <c r="B19" t="s">
+        <v>91</v>
+      </c>
+      <c r="C19" t="s">
+        <v>102</v>
+      </c>
+      <c r="D19" t="s">
+        <v>120</v>
+      </c>
+      <c r="E19" t="s">
+        <v>139</v>
+      </c>
+      <c r="F19">
+        <v>1.65</v>
+      </c>
+      <c r="G19">
+        <v>1.81</v>
+      </c>
+      <c r="H19">
+        <v>5.3</v>
+      </c>
+      <c r="I19">
+        <v>7.6</v>
+      </c>
+      <c r="J19">
+        <v>3.5</v>
+      </c>
+      <c r="K19">
+        <v>4.1</v>
+      </c>
+      <c r="L19">
+        <v>1.33</v>
+      </c>
+      <c r="M19">
+        <v>1.09</v>
+      </c>
+      <c r="N19">
+        <v>2.98</v>
+      </c>
+      <c r="O19">
+        <v>1.36</v>
+      </c>
+      <c r="P19">
+        <v>1.67</v>
+      </c>
+      <c r="Q19">
         <v>2.08</v>
       </c>
-      <c r="U18">
-        <v>1.73</v>
-      </c>
-      <c r="V18">
-        <v>1.14</v>
-      </c>
-      <c r="W18">
+      <c r="R19">
+        <v>1.25</v>
+      </c>
+      <c r="S19">
+        <v>3.9</v>
+      </c>
+      <c r="T19">
+        <v>2.08</v>
+      </c>
+      <c r="U19">
+        <v>1.74</v>
+      </c>
+      <c r="V19">
+        <v>1.15</v>
+      </c>
+      <c r="W19">
         <v>2.22</v>
       </c>
-      <c r="X18">
+      <c r="X19">
         <v>13</v>
       </c>
-      <c r="Y18">
-        <v>18</v>
-      </c>
-      <c r="Z18">
+      <c r="Y19">
+        <v>20</v>
+      </c>
+      <c r="Z19">
         <v>60</v>
       </c>
-      <c r="AA18">
+      <c r="AA19">
         <v>250</v>
       </c>
-      <c r="AB18">
+      <c r="AB19">
         <v>7.8</v>
       </c>
-      <c r="AC18">
-        <v>9</v>
-      </c>
-      <c r="AD18">
+      <c r="AC19">
+        <v>9.6</v>
+      </c>
+      <c r="AD19">
         <v>30</v>
       </c>
-      <c r="AE18">
+      <c r="AE19">
         <v>140</v>
       </c>
-      <c r="AF18">
+      <c r="AF19">
         <v>11</v>
       </c>
-      <c r="AG18">
+      <c r="AG19">
+        <v>12</v>
+      </c>
+      <c r="AH19">
+        <v>30</v>
+      </c>
+      <c r="AI19">
+        <v>140</v>
+      </c>
+      <c r="AJ19">
+        <v>21</v>
+      </c>
+      <c r="AK19">
+        <v>25</v>
+      </c>
+      <c r="AL19">
+        <v>60</v>
+      </c>
+      <c r="AM19">
+        <v>220</v>
+      </c>
+      <c r="AN19">
+        <v>17</v>
+      </c>
+      <c r="AO19">
+        <v>220</v>
+      </c>
+      <c r="AP19">
+        <v>8.6</v>
+      </c>
+      <c r="AQ19">
+        <v>13</v>
+      </c>
+      <c r="AR19">
+        <v>4.7</v>
+      </c>
+      <c r="AS19">
+        <v>5</v>
+      </c>
+      <c r="AT19">
+        <v>5.3</v>
+      </c>
+      <c r="AU19">
+        <v>7.2</v>
+      </c>
+      <c r="AV19">
+        <v>19</v>
+      </c>
+      <c r="AW19">
+        <v>5</v>
+      </c>
+      <c r="AX19">
+        <v>7.2</v>
+      </c>
+      <c r="AY19">
+        <v>8</v>
+      </c>
+      <c r="AZ19">
+        <v>19.5</v>
+      </c>
+      <c r="BA19">
+        <v>5</v>
+      </c>
+      <c r="BB19">
+        <v>13.5</v>
+      </c>
+      <c r="BC19">
+        <v>16</v>
+      </c>
+      <c r="BD19">
+        <v>4.7</v>
+      </c>
+      <c r="BE19">
+        <v>5</v>
+      </c>
+      <c r="BF19">
         <v>11</v>
       </c>
-      <c r="AH18">
+      <c r="BG19">
+        <v>5</v>
+      </c>
+      <c r="BH19">
+        <v>1000</v>
+      </c>
+      <c r="BI19">
+        <v>1.83</v>
+      </c>
+      <c r="BJ19">
+        <v>16</v>
+      </c>
+      <c r="BK19">
+        <v>1.64</v>
+      </c>
+      <c r="BL19">
+        <v>1000</v>
+      </c>
+      <c r="BM19">
+        <v>1.83</v>
+      </c>
+      <c r="BN19">
+        <v>5.3</v>
+      </c>
+      <c r="BO19">
+        <v>2.84</v>
+      </c>
+      <c r="BP19">
+        <v>17</v>
+      </c>
+      <c r="BQ19">
+        <v>1.65</v>
+      </c>
+      <c r="BR19">
+        <v>46</v>
+      </c>
+      <c r="BS19">
+        <v>1.76</v>
+      </c>
+      <c r="BT19">
+        <v>13</v>
+      </c>
+      <c r="BU19">
+        <v>1.61</v>
+      </c>
+      <c r="BV19">
+        <v>1000</v>
+      </c>
+      <c r="BW19">
+        <v>1.8</v>
+      </c>
+      <c r="BX19">
+        <v>1000</v>
+      </c>
+      <c r="BY19">
+        <v>1.8</v>
+      </c>
+      <c r="BZ19">
+        <v>0</v>
+      </c>
+      <c r="CA19">
+        <v>0</v>
+      </c>
+      <c r="CB19" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="20" spans="1:80">
+      <c r="A20" t="s">
+        <v>86</v>
+      </c>
+      <c r="B20" t="s">
+        <v>91</v>
+      </c>
+      <c r="C20" t="s">
+        <v>102</v>
+      </c>
+      <c r="D20" t="s">
+        <v>121</v>
+      </c>
+      <c r="E20" t="s">
+        <v>140</v>
+      </c>
+      <c r="F20">
+        <v>2.66</v>
+      </c>
+      <c r="G20">
+        <v>3.05</v>
+      </c>
+      <c r="H20">
+        <v>2.8</v>
+      </c>
+      <c r="I20">
+        <v>3.3</v>
+      </c>
+      <c r="J20">
+        <v>2.72</v>
+      </c>
+      <c r="K20">
+        <v>3.3</v>
+      </c>
+      <c r="L20">
+        <v>1.48</v>
+      </c>
+      <c r="M20">
+        <v>1.1</v>
+      </c>
+      <c r="N20">
+        <v>2.62</v>
+      </c>
+      <c r="O20">
+        <v>1.52</v>
+      </c>
+      <c r="P20">
+        <v>1.54</v>
+      </c>
+      <c r="Q20">
+        <v>2.44</v>
+      </c>
+      <c r="R20">
+        <v>1.16</v>
+      </c>
+      <c r="S20">
+        <v>5.7</v>
+      </c>
+      <c r="T20">
+        <v>1.78</v>
+      </c>
+      <c r="U20">
+        <v>1.66</v>
+      </c>
+      <c r="V20">
+        <v>1.44</v>
+      </c>
+      <c r="W20">
+        <v>1.49</v>
+      </c>
+      <c r="X20">
+        <v>9.6</v>
+      </c>
+      <c r="Y20">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="Z20">
+        <v>22</v>
+      </c>
+      <c r="AA20">
+        <v>75</v>
+      </c>
+      <c r="AB20">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AC20">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AD20">
+        <v>970</v>
+      </c>
+      <c r="AE20">
+        <v>65</v>
+      </c>
+      <c r="AF20">
+        <v>19</v>
+      </c>
+      <c r="AG20">
+        <v>16.5</v>
+      </c>
+      <c r="AH20">
         <v>30</v>
       </c>
-      <c r="AI18">
-        <v>140</v>
-      </c>
-      <c r="AJ18">
-        <v>20</v>
-      </c>
-      <c r="AK18">
-        <v>25</v>
-      </c>
-      <c r="AL18">
+      <c r="AI20">
+        <v>100</v>
+      </c>
+      <c r="AJ20">
         <v>60</v>
       </c>
-      <c r="AM18">
-        <v>220</v>
-      </c>
-      <c r="AN18">
-        <v>15.5</v>
-      </c>
-      <c r="AO18">
-        <v>220</v>
-      </c>
-      <c r="AP18">
-        <v>8.6</v>
-      </c>
-      <c r="AQ18">
+      <c r="AK20">
+        <v>60</v>
+      </c>
+      <c r="AL20">
+        <v>95</v>
+      </c>
+      <c r="AM20">
+        <v>230</v>
+      </c>
+      <c r="AN20">
+        <v>85</v>
+      </c>
+      <c r="AO20">
+        <v>90</v>
+      </c>
+      <c r="AP20">
+        <v>6.6</v>
+      </c>
+      <c r="AQ20">
+        <v>6.8</v>
+      </c>
+      <c r="AR20">
+        <v>14.5</v>
+      </c>
+      <c r="AS20">
+        <v>44</v>
+      </c>
+      <c r="AT20">
+        <v>6.2</v>
+      </c>
+      <c r="AU20">
+        <v>5.4</v>
+      </c>
+      <c r="AV20">
+        <v>11.5</v>
+      </c>
+      <c r="AW20">
+        <v>34</v>
+      </c>
+      <c r="AX20">
         <v>13</v>
       </c>
-      <c r="AR18">
-        <v>5.5</v>
-      </c>
-      <c r="AS18">
-        <v>5.9</v>
-      </c>
-      <c r="AT18">
-        <v>5.3</v>
-      </c>
-      <c r="AU18">
-        <v>7.2</v>
-      </c>
-      <c r="AV18">
-        <v>21</v>
-      </c>
-      <c r="AW18">
-        <v>5.8</v>
-      </c>
-      <c r="AX18">
-        <v>7.8</v>
-      </c>
-      <c r="AY18">
-        <v>8</v>
-      </c>
-      <c r="AZ18">
-        <v>21</v>
-      </c>
-      <c r="BA18">
-        <v>5.8</v>
-      </c>
-      <c r="BB18">
-        <v>13.5</v>
-      </c>
-      <c r="BC18">
-        <v>16</v>
-      </c>
-      <c r="BD18">
-        <v>5.5</v>
-      </c>
-      <c r="BE18">
-        <v>5.9</v>
-      </c>
-      <c r="BF18">
-        <v>11</v>
-      </c>
-      <c r="BG18">
-        <v>5.9</v>
-      </c>
-      <c r="BH18">
-        <v>1000</v>
-      </c>
-      <c r="BI18">
-        <v>1.83</v>
-      </c>
-      <c r="BJ18">
-        <v>16</v>
-      </c>
-      <c r="BK18">
-        <v>1.64</v>
-      </c>
-      <c r="BL18">
-        <v>1000</v>
-      </c>
-      <c r="BM18">
-        <v>1.83</v>
-      </c>
-      <c r="BN18">
-        <v>5.3</v>
-      </c>
-      <c r="BO18">
-        <v>2.84</v>
-      </c>
-      <c r="BP18">
-        <v>17</v>
-      </c>
-      <c r="BQ18">
-        <v>1.65</v>
-      </c>
-      <c r="BR18">
+      <c r="AY20">
+        <v>10.5</v>
+      </c>
+      <c r="AZ20">
+        <v>19</v>
+      </c>
+      <c r="BA20">
+        <v>55</v>
+      </c>
+      <c r="BB20">
+        <v>34</v>
+      </c>
+      <c r="BC20">
+        <v>30</v>
+      </c>
+      <c r="BD20">
         <v>46</v>
       </c>
-      <c r="BS18">
-        <v>1.76</v>
-      </c>
-      <c r="BT18">
-        <v>13</v>
-      </c>
-      <c r="BU18">
-        <v>1.61</v>
-      </c>
-      <c r="BV18">
-        <v>1000</v>
-      </c>
-      <c r="BW18">
-        <v>1.8</v>
-      </c>
-      <c r="BX18">
-        <v>1000</v>
-      </c>
-      <c r="BY18">
-        <v>1.8</v>
-      </c>
-      <c r="BZ18">
-        <v>0</v>
-      </c>
-      <c r="CA18">
-        <v>0</v>
-      </c>
-      <c r="CB18" t="s">
-        <v>136</v>
+      <c r="BE20">
+        <v>4.7</v>
+      </c>
+      <c r="BF20">
+        <v>44</v>
+      </c>
+      <c r="BG20">
+        <v>46</v>
+      </c>
+      <c r="BH20">
+        <v>1000</v>
+      </c>
+      <c r="BI20">
+        <v>1.04</v>
+      </c>
+      <c r="BJ20">
+        <v>1000</v>
+      </c>
+      <c r="BK20">
+        <v>1.04</v>
+      </c>
+      <c r="BL20">
+        <v>1000</v>
+      </c>
+      <c r="BM20">
+        <v>1.04</v>
+      </c>
+      <c r="BN20">
+        <v>1000</v>
+      </c>
+      <c r="BO20">
+        <v>1.04</v>
+      </c>
+      <c r="BP20">
+        <v>1000</v>
+      </c>
+      <c r="BQ20">
+        <v>1.04</v>
+      </c>
+      <c r="BR20">
+        <v>1000</v>
+      </c>
+      <c r="BS20">
+        <v>1.04</v>
+      </c>
+      <c r="BT20">
+        <v>1000</v>
+      </c>
+      <c r="BU20">
+        <v>1.04</v>
+      </c>
+      <c r="BV20">
+        <v>1000</v>
+      </c>
+      <c r="BW20">
+        <v>1.04</v>
+      </c>
+      <c r="BX20">
+        <v>1000</v>
+      </c>
+      <c r="BY20">
+        <v>1.04</v>
+      </c>
+      <c r="BZ20">
+        <v>1000</v>
+      </c>
+      <c r="CA20">
+        <v>1.04</v>
+      </c>
+      <c r="CB20" t="s">
+        <v>141</v>
       </c>
     </row>
   </sheetData>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-08-11.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-08-11.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="194" uniqueCount="142">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="152" uniqueCount="122">
   <si>
     <t>League</t>
   </si>
@@ -274,12 +274,6 @@
     <t>South African Premier Division</t>
   </si>
   <si>
-    <t>Colombian Primera B</t>
-  </si>
-  <si>
-    <t>Colombian Primera A</t>
-  </si>
-  <si>
     <t>CONMEBOL Copa Libertadores</t>
   </si>
   <si>
@@ -304,24 +298,12 @@
     <t>17:30:00</t>
   </si>
   <si>
-    <t>19:00:00</t>
-  </si>
-  <si>
-    <t>20:30:00</t>
-  </si>
-  <si>
-    <t>21:00:00</t>
-  </si>
-  <si>
     <t>22:00:00</t>
   </si>
   <si>
     <t>22:30:00</t>
   </si>
   <si>
-    <t>22:45:00</t>
-  </si>
-  <si>
     <t>23:00:00</t>
   </si>
   <si>
@@ -352,36 +334,15 @@
     <t>Marumo Gallants FC</t>
   </si>
   <si>
-    <t>Tigres FC Zipaquira</t>
-  </si>
-  <si>
-    <t>Real Santander</t>
-  </si>
-  <si>
-    <t>Aguilas Doradas</t>
-  </si>
-  <si>
     <t>Fluminense</t>
   </si>
   <si>
     <t>Avai</t>
   </si>
   <si>
-    <t>Real Cartagena</t>
-  </si>
-  <si>
     <t>Puerto Montt</t>
   </si>
   <si>
-    <t>Ind Medellin</t>
-  </si>
-  <si>
-    <t>Boyaca Patriotas</t>
-  </si>
-  <si>
-    <t>Leones FC</t>
-  </si>
-  <si>
     <t>CR Flamengo (W)</t>
   </si>
   <si>
@@ -409,37 +370,16 @@
     <t>Kruger United FC</t>
   </si>
   <si>
-    <t>Envigado</t>
-  </si>
-  <si>
-    <t>Barranquilla</t>
-  </si>
-  <si>
-    <t>Llaneros FC</t>
-  </si>
-  <si>
     <t>Independiente Rivadavia</t>
   </si>
   <si>
     <t>CRB</t>
   </si>
   <si>
-    <t>Bogota</t>
-  </si>
-  <si>
     <t>Union Espanola</t>
   </si>
   <si>
-    <t>Millonarios</t>
-  </si>
-  <si>
-    <t>Orsomarso</t>
-  </si>
-  <si>
-    <t>Real Soacha Cundinamarca FC</t>
-  </si>
-  <si>
-    <t>2026-08-10 16:49:46</t>
+    <t>2026-08-10 18:57:53</t>
   </si>
 </sst>
 </file>
@@ -771,7 +711,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:CB20"/>
+  <dimension ref="A1:CB13"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:80">
@@ -1021,34 +961,34 @@
         <v>80</v>
       </c>
       <c r="B2" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="C2" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="D2" t="s">
-        <v>103</v>
+        <v>97</v>
       </c>
       <c r="E2" t="s">
-        <v>122</v>
+        <v>109</v>
       </c>
       <c r="F2">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="G2">
         <v>16</v>
       </c>
       <c r="H2">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="I2">
         <v>1.35</v>
       </c>
       <c r="J2">
-        <v>5</v>
+        <v>5.3</v>
       </c>
       <c r="K2">
-        <v>7.2</v>
+        <v>6.4</v>
       </c>
       <c r="L2">
         <v>1.33</v>
@@ -1057,187 +997,187 @@
         <v>1.05</v>
       </c>
       <c r="N2">
-        <v>4.2</v>
+        <v>4.6</v>
       </c>
       <c r="O2">
-        <v>1.26</v>
+        <v>1.24</v>
       </c>
       <c r="P2">
+        <v>2.28</v>
+      </c>
+      <c r="Q2">
+        <v>1.7</v>
+      </c>
+      <c r="R2">
+        <v>1.53</v>
+      </c>
+      <c r="S2">
+        <v>2.74</v>
+      </c>
+      <c r="T2">
         <v>2.16</v>
       </c>
-      <c r="Q2">
+      <c r="U2">
         <v>1.73</v>
       </c>
-      <c r="R2">
-        <v>1.46</v>
-      </c>
-      <c r="S2">
-        <v>2.82</v>
-      </c>
-      <c r="T2">
-        <v>2.2</v>
-      </c>
-      <c r="U2">
-        <v>1.71</v>
-      </c>
       <c r="V2">
-        <v>3.75</v>
+        <v>3.85</v>
       </c>
       <c r="W2">
         <v>1.06</v>
       </c>
       <c r="X2">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="Y2">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="Z2">
         <v>8.199999999999999</v>
       </c>
-      <c r="Z2">
-        <v>8</v>
-      </c>
       <c r="AA2">
-        <v>10.5</v>
+        <v>12.5</v>
       </c>
       <c r="AB2">
-        <v>46</v>
+        <v>55</v>
       </c>
       <c r="AC2">
-        <v>13.5</v>
+        <v>14.5</v>
       </c>
       <c r="AD2">
         <v>11.5</v>
       </c>
       <c r="AE2">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="AF2">
         <v>160</v>
       </c>
       <c r="AG2">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="AH2">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="AI2">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="AJ2">
         <v>1000</v>
       </c>
       <c r="AK2">
-        <v>320</v>
+        <v>290</v>
       </c>
       <c r="AL2">
-        <v>240</v>
+        <v>220</v>
       </c>
       <c r="AM2">
-        <v>250</v>
+        <v>220</v>
       </c>
       <c r="AN2">
-        <v>480</v>
+        <v>420</v>
       </c>
       <c r="AO2">
-        <v>6</v>
+        <v>5.4</v>
       </c>
       <c r="AP2">
-        <v>6</v>
+        <v>5.7</v>
       </c>
       <c r="AQ2">
         <v>4.2</v>
       </c>
       <c r="AR2">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="AS2">
+        <v>4.8</v>
+      </c>
+      <c r="AT2">
+        <v>6.6</v>
+      </c>
+      <c r="AU2">
+        <v>5</v>
+      </c>
+      <c r="AV2">
         <v>4.7</v>
       </c>
-      <c r="AT2">
-        <v>7</v>
-      </c>
-      <c r="AU2">
+      <c r="AW2">
         <v>5.1</v>
       </c>
-      <c r="AV2">
-        <v>4.9</v>
-      </c>
-      <c r="AW2">
-        <v>5.5</v>
-      </c>
       <c r="AX2">
-        <v>7.8</v>
+        <v>7.2</v>
       </c>
       <c r="AY2">
-        <v>7.2</v>
+        <v>6.8</v>
       </c>
       <c r="AZ2">
-        <v>6.8</v>
+        <v>6.4</v>
       </c>
       <c r="BA2">
-        <v>7</v>
+        <v>6.4</v>
       </c>
       <c r="BB2">
-        <v>8.199999999999999</v>
+        <v>7.6</v>
       </c>
       <c r="BC2">
-        <v>8</v>
+        <v>7.4</v>
       </c>
       <c r="BD2">
-        <v>8</v>
+        <v>8.4</v>
       </c>
       <c r="BE2">
-        <v>8</v>
+        <v>8.4</v>
       </c>
       <c r="BF2">
-        <v>8</v>
+        <v>7.6</v>
       </c>
       <c r="BG2">
-        <v>4.8</v>
+        <v>3.8</v>
       </c>
       <c r="BH2">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="BI2">
-        <v>2.52</v>
+        <v>2.44</v>
       </c>
       <c r="BJ2">
         <v>15.5</v>
       </c>
       <c r="BK2">
-        <v>4.1</v>
+        <v>3.95</v>
       </c>
       <c r="BL2">
         <v>1000</v>
       </c>
       <c r="BM2">
-        <v>5.4</v>
+        <v>5.2</v>
       </c>
       <c r="BN2">
         <v>17.5</v>
       </c>
       <c r="BO2">
+        <v>4.1</v>
+      </c>
+      <c r="BP2">
+        <v>1000</v>
+      </c>
+      <c r="BQ2">
+        <v>5.1</v>
+      </c>
+      <c r="BR2">
+        <v>1000</v>
+      </c>
+      <c r="BS2">
+        <v>5.1</v>
+      </c>
+      <c r="BT2">
         <v>4.2</v>
       </c>
-      <c r="BP2">
-        <v>1000</v>
-      </c>
-      <c r="BQ2">
-        <v>5.3</v>
-      </c>
-      <c r="BR2">
-        <v>1000</v>
-      </c>
-      <c r="BS2">
-        <v>5.3</v>
-      </c>
-      <c r="BT2">
-        <v>4.1</v>
-      </c>
       <c r="BU2">
-        <v>2.92</v>
+        <v>2.94</v>
       </c>
       <c r="BV2">
-        <v>8.6</v>
+        <v>9</v>
       </c>
       <c r="BW2">
         <v>3.35</v>
@@ -1246,16 +1186,16 @@
         <v>30</v>
       </c>
       <c r="BY2">
-        <v>4.7</v>
+        <v>4.5</v>
       </c>
       <c r="BZ2">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="CA2">
-        <v>4</v>
+        <v>3.95</v>
       </c>
       <c r="CB2" t="s">
-        <v>141</v>
+        <v>121</v>
       </c>
     </row>
     <row r="3" spans="1:80">
@@ -1263,34 +1203,34 @@
         <v>81</v>
       </c>
       <c r="B3" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="C3" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="D3" t="s">
-        <v>104</v>
+        <v>98</v>
       </c>
       <c r="E3" t="s">
-        <v>123</v>
+        <v>110</v>
       </c>
       <c r="F3">
-        <v>2.44</v>
+        <v>2.46</v>
       </c>
       <c r="G3">
         <v>2.5</v>
       </c>
       <c r="H3">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="I3">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="J3">
+        <v>3.4</v>
+      </c>
+      <c r="K3">
         <v>3.5</v>
-      </c>
-      <c r="K3">
-        <v>3.65</v>
       </c>
       <c r="L3">
         <v>1.47</v>
@@ -1302,43 +1242,43 @@
         <v>3.45</v>
       </c>
       <c r="O3">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="P3">
-        <v>1.84</v>
+        <v>1.82</v>
       </c>
       <c r="Q3">
-        <v>2.16</v>
+        <v>2.18</v>
       </c>
       <c r="R3">
-        <v>1.32</v>
+        <v>1.31</v>
       </c>
       <c r="S3">
         <v>4</v>
       </c>
       <c r="T3">
-        <v>1.85</v>
+        <v>1.87</v>
       </c>
       <c r="U3">
         <v>2.08</v>
       </c>
       <c r="V3">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="W3">
         <v>1.66</v>
       </c>
       <c r="X3">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="Y3">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="Z3">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AA3">
-        <v>70</v>
+        <v>60</v>
       </c>
       <c r="AB3">
         <v>9.6</v>
@@ -1350,7 +1290,7 @@
         <v>14</v>
       </c>
       <c r="AE3">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="AF3">
         <v>15.5</v>
@@ -1359,100 +1299,100 @@
         <v>11.5</v>
       </c>
       <c r="AH3">
-        <v>23</v>
+        <v>19.5</v>
       </c>
       <c r="AI3">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="AJ3">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="AK3">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AL3">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="AM3">
-        <v>1000</v>
+        <v>120</v>
       </c>
       <c r="AN3">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="AO3">
         <v>46</v>
       </c>
       <c r="AP3">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AQ3">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AR3">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="AS3">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="AT3">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AU3">
         <v>7</v>
       </c>
       <c r="AV3">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="AW3">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="AX3">
         <v>13.5</v>
       </c>
       <c r="AY3">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AZ3">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="BA3">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="BB3">
+        <v>28</v>
+      </c>
+      <c r="BC3">
         <v>25</v>
       </c>
-      <c r="BC3">
-        <v>23</v>
-      </c>
       <c r="BD3">
+        <v>38</v>
+      </c>
+      <c r="BE3">
+        <v>85</v>
+      </c>
+      <c r="BF3">
+        <v>22</v>
+      </c>
+      <c r="BG3">
         <v>34</v>
       </c>
-      <c r="BE3">
-        <v>40</v>
-      </c>
-      <c r="BF3">
-        <v>18</v>
-      </c>
-      <c r="BG3">
-        <v>29</v>
-      </c>
       <c r="BH3">
-        <v>3.7</v>
+        <v>3.65</v>
       </c>
       <c r="BI3">
-        <v>2.62</v>
+        <v>2.64</v>
       </c>
       <c r="BJ3">
         <v>9.800000000000001</v>
       </c>
       <c r="BK3">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="BL3">
         <v>1000</v>
       </c>
       <c r="BM3">
-        <v>8.6</v>
+        <v>9</v>
       </c>
       <c r="BN3">
         <v>5.3</v>
@@ -1461,7 +1401,7 @@
         <v>4.1</v>
       </c>
       <c r="BP3">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="BQ3">
         <v>6.2</v>
@@ -1470,7 +1410,7 @@
         <v>42</v>
       </c>
       <c r="BS3">
-        <v>7.2</v>
+        <v>7.6</v>
       </c>
       <c r="BT3">
         <v>6.4</v>
@@ -1482,22 +1422,22 @@
         <v>27</v>
       </c>
       <c r="BW3">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="BX3">
         <v>50</v>
       </c>
       <c r="BY3">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="BZ3">
         <v>32</v>
       </c>
       <c r="CA3">
-        <v>7</v>
+        <v>7.4</v>
       </c>
       <c r="CB3" t="s">
-        <v>141</v>
+        <v>121</v>
       </c>
     </row>
     <row r="4" spans="1:80">
@@ -1505,157 +1445,157 @@
         <v>82</v>
       </c>
       <c r="B4" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="C4" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="D4" t="s">
-        <v>105</v>
+        <v>99</v>
       </c>
       <c r="E4" t="s">
-        <v>124</v>
+        <v>111</v>
       </c>
       <c r="F4">
-        <v>1.74</v>
+        <v>1.71</v>
       </c>
       <c r="G4">
-        <v>1.79</v>
+        <v>1.75</v>
       </c>
       <c r="H4">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="I4">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="J4">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="K4">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="L4">
-        <v>1.49</v>
+        <v>1.48</v>
       </c>
       <c r="M4">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="N4">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="O4">
         <v>1.44</v>
       </c>
       <c r="P4">
-        <v>1.73</v>
+        <v>1.71</v>
       </c>
       <c r="Q4">
-        <v>2.3</v>
+        <v>2.32</v>
       </c>
       <c r="R4">
         <v>1.26</v>
       </c>
       <c r="S4">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="T4">
-        <v>2.16</v>
+        <v>2.26</v>
       </c>
       <c r="U4">
-        <v>1.79</v>
+        <v>1.74</v>
       </c>
       <c r="V4">
-        <v>1.19</v>
+        <v>1.17</v>
       </c>
       <c r="W4">
-        <v>2.26</v>
+        <v>2.32</v>
       </c>
       <c r="X4">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="Y4">
-        <v>17</v>
+        <v>17.5</v>
       </c>
       <c r="Z4">
-        <v>70</v>
+        <v>980</v>
       </c>
       <c r="AA4">
         <v>200</v>
       </c>
       <c r="AB4">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="AC4">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="AD4">
         <v>25</v>
       </c>
       <c r="AE4">
-        <v>160</v>
+        <v>120</v>
       </c>
       <c r="AF4">
-        <v>9.6</v>
+        <v>9</v>
       </c>
       <c r="AG4">
         <v>11</v>
       </c>
       <c r="AH4">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AI4">
-        <v>130</v>
+        <v>140</v>
       </c>
       <c r="AJ4">
-        <v>19</v>
+        <v>17.5</v>
       </c>
       <c r="AK4">
         <v>22</v>
       </c>
       <c r="AL4">
-        <v>75</v>
+        <v>55</v>
       </c>
       <c r="AM4">
-        <v>200</v>
+        <v>220</v>
       </c>
       <c r="AN4">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="AO4">
         <v>190</v>
       </c>
       <c r="AP4">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AQ4">
-        <v>14</v>
+        <v>16.5</v>
       </c>
       <c r="AR4">
         <v>32</v>
       </c>
       <c r="AS4">
-        <v>9.6</v>
+        <v>15</v>
       </c>
       <c r="AT4">
-        <v>5.9</v>
+        <v>6.2</v>
       </c>
       <c r="AU4">
-        <v>7.4</v>
+        <v>7.8</v>
       </c>
       <c r="AV4">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="AW4">
         <v>55</v>
       </c>
       <c r="AX4">
-        <v>8.199999999999999</v>
+        <v>7.8</v>
       </c>
       <c r="AY4">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="AZ4">
-        <v>19.5</v>
+        <v>24</v>
       </c>
       <c r="BA4">
         <v>55</v>
@@ -1664,82 +1604,82 @@
         <v>15.5</v>
       </c>
       <c r="BC4">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="BD4">
-        <v>30</v>
+        <v>44</v>
       </c>
       <c r="BE4">
-        <v>9.6</v>
+        <v>14</v>
       </c>
       <c r="BF4">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="BG4">
         <v>90</v>
       </c>
       <c r="BH4">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="BI4">
-        <v>2.6</v>
+        <v>2.84</v>
       </c>
       <c r="BJ4">
-        <v>11.5</v>
+        <v>12.5</v>
       </c>
       <c r="BK4">
-        <v>5.8</v>
+        <v>6.8</v>
       </c>
       <c r="BL4">
         <v>1000</v>
       </c>
       <c r="BM4">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="BN4">
-        <v>4.3</v>
+        <v>3.95</v>
       </c>
       <c r="BO4">
-        <v>3.4</v>
+        <v>3.55</v>
       </c>
       <c r="BP4">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="BQ4">
+        <v>6.8</v>
+      </c>
+      <c r="BR4">
+        <v>1000</v>
+      </c>
+      <c r="BS4">
+        <v>10.5</v>
+      </c>
+      <c r="BT4">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="BU4">
         <v>6.2</v>
       </c>
-      <c r="BR4">
-        <v>1000</v>
-      </c>
-      <c r="BS4">
-        <v>8.6</v>
-      </c>
-      <c r="BT4">
-        <v>9.4</v>
-      </c>
-      <c r="BU4">
-        <v>7</v>
-      </c>
       <c r="BV4">
         <v>1000</v>
       </c>
       <c r="BW4">
-        <v>9.800000000000001</v>
+        <v>12</v>
       </c>
       <c r="BX4">
-        <v>1000</v>
+        <v>85</v>
       </c>
       <c r="BY4">
-        <v>10</v>
+        <v>12.5</v>
       </c>
       <c r="BZ4">
         <v>29</v>
       </c>
       <c r="CA4">
-        <v>8.4</v>
+        <v>10</v>
       </c>
       <c r="CB4" t="s">
-        <v>141</v>
+        <v>121</v>
       </c>
     </row>
     <row r="5" spans="1:80">
@@ -1747,97 +1687,97 @@
         <v>83</v>
       </c>
       <c r="B5" t="s">
+        <v>89</v>
+      </c>
+      <c r="C5" t="s">
         <v>91</v>
       </c>
-      <c r="C5" t="s">
-        <v>93</v>
-      </c>
       <c r="D5" t="s">
-        <v>106</v>
+        <v>100</v>
       </c>
       <c r="E5" t="s">
-        <v>125</v>
+        <v>112</v>
       </c>
       <c r="F5">
-        <v>1.57</v>
+        <v>1.6</v>
       </c>
       <c r="G5">
-        <v>1.59</v>
+        <v>1.62</v>
       </c>
       <c r="H5">
-        <v>7.6</v>
+        <v>7.2</v>
       </c>
       <c r="I5">
         <v>7.8</v>
       </c>
       <c r="J5">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="K5">
-        <v>4.4</v>
+        <v>4.2</v>
       </c>
       <c r="L5">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="M5">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="N5">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="O5">
         <v>1.4</v>
       </c>
       <c r="P5">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="Q5">
         <v>2.2</v>
       </c>
       <c r="R5">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="S5">
         <v>4.2</v>
       </c>
       <c r="T5">
-        <v>2.24</v>
+        <v>2.26</v>
       </c>
       <c r="U5">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="V5">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="W5">
-        <v>2.68</v>
+        <v>2.6</v>
       </c>
       <c r="X5">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="Y5">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="Z5">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="AA5">
-        <v>320</v>
+        <v>280</v>
       </c>
       <c r="AB5">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="AC5">
-        <v>9.4</v>
+        <v>9</v>
       </c>
       <c r="AD5">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="AE5">
-        <v>1000</v>
+        <v>150</v>
       </c>
       <c r="AF5">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AG5">
         <v>10.5</v>
@@ -1846,61 +1786,61 @@
         <v>29</v>
       </c>
       <c r="AI5">
-        <v>150</v>
+        <v>140</v>
       </c>
       <c r="AJ5">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="AK5">
         <v>19</v>
       </c>
       <c r="AL5">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="AM5">
-        <v>1000</v>
+        <v>210</v>
       </c>
       <c r="AN5">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AO5">
-        <v>280</v>
+        <v>240</v>
       </c>
       <c r="AP5">
         <v>11</v>
       </c>
       <c r="AQ5">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="AR5">
-        <v>42</v>
+        <v>50</v>
       </c>
       <c r="AS5">
-        <v>70</v>
+        <v>48</v>
       </c>
       <c r="AT5">
-        <v>6.2</v>
+        <v>6.6</v>
       </c>
       <c r="AU5">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="AV5">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AW5">
-        <v>50</v>
+        <v>85</v>
       </c>
       <c r="AX5">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="AY5">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="AZ5">
         <v>25</v>
       </c>
       <c r="BA5">
-        <v>55</v>
+        <v>80</v>
       </c>
       <c r="BB5">
         <v>12.5</v>
@@ -1909,7 +1849,7 @@
         <v>17</v>
       </c>
       <c r="BD5">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="BE5">
         <v>48</v>
@@ -1918,70 +1858,70 @@
         <v>10</v>
       </c>
       <c r="BG5">
-        <v>100</v>
+        <v>110</v>
       </c>
       <c r="BH5">
-        <v>3.3</v>
+        <v>3.15</v>
       </c>
       <c r="BI5">
-        <v>2.66</v>
+        <v>2.96</v>
       </c>
       <c r="BJ5">
         <v>13</v>
       </c>
       <c r="BK5">
-        <v>5.9</v>
+        <v>10</v>
       </c>
       <c r="BL5">
-        <v>1000</v>
+        <v>210</v>
       </c>
       <c r="BM5">
-        <v>10.5</v>
+        <v>15.5</v>
       </c>
       <c r="BN5">
-        <v>3.95</v>
+        <v>3.8</v>
       </c>
       <c r="BO5">
-        <v>3.1</v>
+        <v>3.55</v>
       </c>
       <c r="BP5">
         <v>11</v>
       </c>
       <c r="BQ5">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="BR5">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="BS5">
-        <v>8.199999999999999</v>
+        <v>11</v>
       </c>
       <c r="BT5">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="BU5">
-        <v>8.4</v>
+        <v>9</v>
       </c>
       <c r="BV5">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="BW5">
-        <v>9.6</v>
+        <v>13.5</v>
       </c>
       <c r="BX5">
         <v>90</v>
       </c>
       <c r="BY5">
-        <v>9.800000000000001</v>
+        <v>14</v>
       </c>
       <c r="BZ5">
         <v>24</v>
       </c>
       <c r="CA5">
-        <v>7.4</v>
+        <v>14.5</v>
       </c>
       <c r="CB5" t="s">
-        <v>141</v>
+        <v>121</v>
       </c>
     </row>
     <row r="6" spans="1:80">
@@ -1989,34 +1929,34 @@
         <v>84</v>
       </c>
       <c r="B6" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="C6" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="D6" t="s">
-        <v>107</v>
+        <v>101</v>
       </c>
       <c r="E6" t="s">
-        <v>126</v>
+        <v>113</v>
       </c>
       <c r="F6">
-        <v>2.14</v>
+        <v>2.08</v>
       </c>
       <c r="G6">
-        <v>2.24</v>
+        <v>2.2</v>
       </c>
       <c r="H6">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="I6">
-        <v>3.55</v>
+        <v>3.65</v>
       </c>
       <c r="J6">
         <v>3.9</v>
       </c>
       <c r="K6">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="L6">
         <v>1.33</v>
@@ -2028,49 +1968,49 @@
         <v>5.2</v>
       </c>
       <c r="O6">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="P6">
-        <v>2.38</v>
+        <v>2.42</v>
       </c>
       <c r="Q6">
-        <v>1.64</v>
+        <v>1.63</v>
       </c>
       <c r="R6">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="S6">
-        <v>2.58</v>
+        <v>2.56</v>
       </c>
       <c r="T6">
         <v>1.59</v>
       </c>
       <c r="U6">
-        <v>2.5</v>
+        <v>2.52</v>
       </c>
       <c r="V6">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="W6">
-        <v>1.8</v>
+        <v>1.83</v>
       </c>
       <c r="X6">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="Y6">
-        <v>22</v>
+        <v>18.5</v>
       </c>
       <c r="Z6">
         <v>36</v>
       </c>
       <c r="AA6">
-        <v>80</v>
+        <v>500</v>
       </c>
       <c r="AB6">
         <v>13.5</v>
       </c>
       <c r="AC6">
-        <v>9.4</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AD6">
         <v>15</v>
@@ -2082,7 +2022,7 @@
         <v>21</v>
       </c>
       <c r="AG6">
-        <v>13.5</v>
+        <v>12</v>
       </c>
       <c r="AH6">
         <v>20</v>
@@ -2100,25 +2040,25 @@
         <v>38</v>
       </c>
       <c r="AM6">
-        <v>85</v>
+        <v>200</v>
       </c>
       <c r="AN6">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="AO6">
         <v>32</v>
       </c>
       <c r="AP6">
-        <v>7.2</v>
+        <v>9</v>
       </c>
       <c r="AQ6">
         <v>15</v>
       </c>
       <c r="AR6">
-        <v>7</v>
+        <v>24</v>
       </c>
       <c r="AS6">
-        <v>8.199999999999999</v>
+        <v>10</v>
       </c>
       <c r="AT6">
         <v>11.5</v>
@@ -2130,7 +2070,7 @@
         <v>13</v>
       </c>
       <c r="AW6">
-        <v>7.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AX6">
         <v>14</v>
@@ -2142,22 +2082,22 @@
         <v>13.5</v>
       </c>
       <c r="BA6">
-        <v>7.6</v>
+        <v>9.6</v>
       </c>
       <c r="BB6">
-        <v>7</v>
+        <v>20</v>
       </c>
       <c r="BC6">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="BD6">
-        <v>7.4</v>
+        <v>8.6</v>
       </c>
       <c r="BE6">
-        <v>8.199999999999999</v>
+        <v>28</v>
       </c>
       <c r="BF6">
-        <v>10.5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BG6">
         <v>21</v>
@@ -2166,7 +2106,7 @@
         <v>4.1</v>
       </c>
       <c r="BI6">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="BJ6">
         <v>8.800000000000001</v>
@@ -2223,7 +2163,7 @@
         <v>0</v>
       </c>
       <c r="CB6" t="s">
-        <v>141</v>
+        <v>121</v>
       </c>
     </row>
     <row r="7" spans="1:80">
@@ -2231,19 +2171,19 @@
         <v>85</v>
       </c>
       <c r="B7" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="C7" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="D7" t="s">
-        <v>108</v>
+        <v>102</v>
       </c>
       <c r="E7" t="s">
-        <v>127</v>
+        <v>114</v>
       </c>
       <c r="F7">
-        <v>2.9</v>
+        <v>2.92</v>
       </c>
       <c r="G7">
         <v>3.25</v>
@@ -2255,10 +2195,10 @@
         <v>3.15</v>
       </c>
       <c r="J7">
-        <v>2.76</v>
+        <v>2.8</v>
       </c>
       <c r="K7">
-        <v>3.1</v>
+        <v>3.05</v>
       </c>
       <c r="L7">
         <v>1.61</v>
@@ -2285,7 +2225,7 @@
         <v>6</v>
       </c>
       <c r="T7">
-        <v>2.2</v>
+        <v>2.18</v>
       </c>
       <c r="U7">
         <v>1.71</v>
@@ -2342,10 +2282,10 @@
         <v>100</v>
       </c>
       <c r="AM7">
-        <v>270</v>
+        <v>500</v>
       </c>
       <c r="AN7">
-        <v>70</v>
+        <v>500</v>
       </c>
       <c r="AO7">
         <v>70</v>
@@ -2354,7 +2294,7 @@
         <v>5.8</v>
       </c>
       <c r="AQ7">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AR7">
         <v>15</v>
@@ -2465,7 +2405,7 @@
         <v>9.4</v>
       </c>
       <c r="CB7" t="s">
-        <v>141</v>
+        <v>121</v>
       </c>
     </row>
     <row r="8" spans="1:80">
@@ -2473,16 +2413,16 @@
         <v>85</v>
       </c>
       <c r="B8" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="C8" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="D8" t="s">
-        <v>109</v>
+        <v>103</v>
       </c>
       <c r="E8" t="s">
-        <v>128</v>
+        <v>115</v>
       </c>
       <c r="F8">
         <v>7</v>
@@ -2503,7 +2443,7 @@
         <v>4.4</v>
       </c>
       <c r="L8">
-        <v>1.41</v>
+        <v>1.37</v>
       </c>
       <c r="M8">
         <v>1.07</v>
@@ -2515,10 +2455,10 @@
         <v>1.34</v>
       </c>
       <c r="P8">
-        <v>1.84</v>
+        <v>1.86</v>
       </c>
       <c r="Q8">
-        <v>2.04</v>
+        <v>2.02</v>
       </c>
       <c r="R8">
         <v>1.32</v>
@@ -2533,7 +2473,7 @@
         <v>1.8</v>
       </c>
       <c r="V8">
-        <v>2.58</v>
+        <v>2.56</v>
       </c>
       <c r="W8">
         <v>1.14</v>
@@ -2560,7 +2500,7 @@
         <v>12.5</v>
       </c>
       <c r="AE8">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AF8">
         <v>75</v>
@@ -2569,25 +2509,25 @@
         <v>34</v>
       </c>
       <c r="AH8">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="AI8">
         <v>55</v>
       </c>
       <c r="AJ8">
-        <v>310</v>
+        <v>700</v>
       </c>
       <c r="AK8">
-        <v>160</v>
+        <v>700</v>
       </c>
       <c r="AL8">
-        <v>150</v>
+        <v>700</v>
       </c>
       <c r="AM8">
-        <v>210</v>
+        <v>700</v>
       </c>
       <c r="AN8">
-        <v>240</v>
+        <v>700</v>
       </c>
       <c r="AO8">
         <v>12.5</v>
@@ -2596,7 +2536,7 @@
         <v>10</v>
       </c>
       <c r="AQ8">
-        <v>5.5</v>
+        <v>6.4</v>
       </c>
       <c r="AR8">
         <v>6.6</v>
@@ -2605,7 +2545,7 @@
         <v>10.5</v>
       </c>
       <c r="AT8">
-        <v>3.75</v>
+        <v>4.2</v>
       </c>
       <c r="AU8">
         <v>7</v>
@@ -2617,7 +2557,7 @@
         <v>16</v>
       </c>
       <c r="AX8">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="AY8">
         <v>20</v>
@@ -2626,22 +2566,22 @@
         <v>18</v>
       </c>
       <c r="BA8">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="BB8">
+        <v>4.4</v>
+      </c>
+      <c r="BC8">
+        <v>4.4</v>
+      </c>
+      <c r="BD8">
         <v>4.3</v>
       </c>
-      <c r="BC8">
-        <v>4.3</v>
-      </c>
-      <c r="BD8">
-        <v>4.2</v>
-      </c>
       <c r="BE8">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="BF8">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="BG8">
         <v>7.8</v>
@@ -2707,7 +2647,7 @@
         <v>4.1</v>
       </c>
       <c r="CB8" t="s">
-        <v>141</v>
+        <v>121</v>
       </c>
     </row>
     <row r="9" spans="1:80">
@@ -2715,37 +2655,37 @@
         <v>85</v>
       </c>
       <c r="B9" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="C9" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="D9" t="s">
-        <v>110</v>
+        <v>104</v>
       </c>
       <c r="E9" t="s">
-        <v>129</v>
+        <v>116</v>
       </c>
       <c r="F9">
-        <v>2.48</v>
+        <v>2.5</v>
       </c>
       <c r="G9">
         <v>2.7</v>
       </c>
       <c r="H9">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="I9">
         <v>3.95</v>
       </c>
       <c r="J9">
-        <v>2.7</v>
+        <v>2.68</v>
       </c>
       <c r="K9">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="L9">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="M9">
         <v>1.16</v>
@@ -2760,7 +2700,7 @@
         <v>1.4</v>
       </c>
       <c r="Q9">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="R9">
         <v>1.13</v>
@@ -2784,13 +2724,13 @@
         <v>8.199999999999999</v>
       </c>
       <c r="Y9">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="Z9">
         <v>27</v>
       </c>
       <c r="AA9">
-        <v>110</v>
+        <v>500</v>
       </c>
       <c r="AB9">
         <v>7.2</v>
@@ -2805,7 +2745,7 @@
         <v>85</v>
       </c>
       <c r="AF9">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="AG9">
         <v>14.5</v>
@@ -2814,7 +2754,7 @@
         <v>29</v>
       </c>
       <c r="AI9">
-        <v>130</v>
+        <v>500</v>
       </c>
       <c r="AJ9">
         <v>55</v>
@@ -2826,13 +2766,13 @@
         <v>100</v>
       </c>
       <c r="AM9">
-        <v>300</v>
+        <v>500</v>
       </c>
       <c r="AN9">
         <v>65</v>
       </c>
       <c r="AO9">
-        <v>130</v>
+        <v>500</v>
       </c>
       <c r="AP9">
         <v>5.4</v>
@@ -2889,10 +2829,10 @@
         <v>7.4</v>
       </c>
       <c r="BH9">
-        <v>2.76</v>
+        <v>2.74</v>
       </c>
       <c r="BI9">
-        <v>2.04</v>
+        <v>2.02</v>
       </c>
       <c r="BJ9">
         <v>15</v>
@@ -2904,25 +2844,25 @@
         <v>1000</v>
       </c>
       <c r="BM9">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="BN9">
         <v>5.4</v>
       </c>
       <c r="BO9">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="BP9">
         <v>32</v>
       </c>
       <c r="BQ9">
-        <v>5.7</v>
+        <v>5.9</v>
       </c>
       <c r="BR9">
         <v>70</v>
       </c>
       <c r="BS9">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="BT9">
         <v>6.8</v>
@@ -2934,22 +2874,22 @@
         <v>48</v>
       </c>
       <c r="BW9">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="BX9">
         <v>1000</v>
       </c>
       <c r="BY9">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="BZ9">
-        <v>85</v>
+        <v>1000</v>
       </c>
       <c r="CA9">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="CB9" t="s">
-        <v>141</v>
+        <v>121</v>
       </c>
     </row>
     <row r="10" spans="1:80">
@@ -2957,25 +2897,25 @@
         <v>85</v>
       </c>
       <c r="B10" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="C10" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="D10" t="s">
-        <v>111</v>
+        <v>105</v>
       </c>
       <c r="E10" t="s">
-        <v>130</v>
+        <v>117</v>
       </c>
       <c r="F10">
-        <v>2.42</v>
+        <v>2.4</v>
       </c>
       <c r="G10">
         <v>2.58</v>
       </c>
       <c r="H10">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="I10">
         <v>4.5</v>
@@ -3002,7 +2942,7 @@
         <v>1.43</v>
       </c>
       <c r="Q10">
-        <v>2.68</v>
+        <v>2.78</v>
       </c>
       <c r="R10">
         <v>1.13</v>
@@ -3014,25 +2954,25 @@
         <v>2.14</v>
       </c>
       <c r="U10">
-        <v>1.58</v>
+        <v>1.57</v>
       </c>
       <c r="V10">
-        <v>1.32</v>
+        <v>1.29</v>
       </c>
       <c r="W10">
         <v>1.63</v>
       </c>
       <c r="X10">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="Y10">
         <v>13</v>
       </c>
       <c r="Z10">
-        <v>34</v>
+        <v>500</v>
       </c>
       <c r="AA10">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AB10">
         <v>9.800000000000001</v>
@@ -3044,7 +2984,7 @@
         <v>25</v>
       </c>
       <c r="AE10">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AF10">
         <v>21</v>
@@ -3056,28 +2996,28 @@
         <v>950</v>
       </c>
       <c r="AI10">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AJ10">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AK10">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AL10">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AM10">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AN10">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AO10">
         <v>1000</v>
       </c>
       <c r="AP10">
-        <v>1.9</v>
+        <v>2.16</v>
       </c>
       <c r="AQ10">
         <v>5.9</v>
@@ -3086,7 +3026,7 @@
         <v>14.5</v>
       </c>
       <c r="AS10">
-        <v>1.91</v>
+        <v>2.48</v>
       </c>
       <c r="AT10">
         <v>4.6</v>
@@ -3098,7 +3038,7 @@
         <v>11</v>
       </c>
       <c r="AW10">
-        <v>1.91</v>
+        <v>2.42</v>
       </c>
       <c r="AX10">
         <v>9</v>
@@ -3110,25 +3050,25 @@
         <v>16</v>
       </c>
       <c r="BA10">
-        <v>1.91</v>
+        <v>2.48</v>
       </c>
       <c r="BB10">
-        <v>1.91</v>
+        <v>2.38</v>
       </c>
       <c r="BC10">
-        <v>1.91</v>
+        <v>2.4</v>
       </c>
       <c r="BD10">
-        <v>1.91</v>
+        <v>2.48</v>
       </c>
       <c r="BE10">
-        <v>1.91</v>
+        <v>2.48</v>
       </c>
       <c r="BF10">
-        <v>1.91</v>
+        <v>2.4</v>
       </c>
       <c r="BG10">
-        <v>1.91</v>
+        <v>2.48</v>
       </c>
       <c r="BH10">
         <v>1000</v>
@@ -3191,7 +3131,7 @@
         <v>1.04</v>
       </c>
       <c r="CB10" t="s">
-        <v>141</v>
+        <v>121</v>
       </c>
     </row>
     <row r="11" spans="1:80">
@@ -3199,339 +3139,339 @@
         <v>86</v>
       </c>
       <c r="B11" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="C11" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="D11" t="s">
-        <v>112</v>
+        <v>106</v>
       </c>
       <c r="E11" t="s">
-        <v>131</v>
+        <v>118</v>
       </c>
       <c r="F11">
-        <v>3.15</v>
+        <v>1.72</v>
       </c>
       <c r="G11">
+        <v>1.78</v>
+      </c>
+      <c r="H11">
+        <v>5.7</v>
+      </c>
+      <c r="I11">
+        <v>6.2</v>
+      </c>
+      <c r="J11">
+        <v>3.8</v>
+      </c>
+      <c r="K11">
         <v>3.9</v>
       </c>
-      <c r="H11">
-        <v>2.48</v>
-      </c>
-      <c r="I11">
-        <v>2.96</v>
-      </c>
-      <c r="J11">
-        <v>2.7</v>
-      </c>
-      <c r="K11">
-        <v>2.94</v>
-      </c>
       <c r="L11">
-        <v>1.28</v>
+        <v>1.41</v>
       </c>
       <c r="M11">
-        <v>1.01</v>
+        <v>1.08</v>
       </c>
       <c r="N11">
-        <v>1.02</v>
+        <v>3.1</v>
       </c>
       <c r="O11">
-        <v>1.01</v>
+        <v>1.43</v>
       </c>
       <c r="P11">
-        <v>1.18</v>
+        <v>1.72</v>
       </c>
       <c r="Q11">
+        <v>2.3</v>
+      </c>
+      <c r="R11">
+        <v>1.27</v>
+      </c>
+      <c r="S11">
+        <v>4.3</v>
+      </c>
+      <c r="T11">
+        <v>2.12</v>
+      </c>
+      <c r="U11">
+        <v>1.8</v>
+      </c>
+      <c r="V11">
         <v>1.19</v>
       </c>
-      <c r="R11">
-        <v>1.02</v>
-      </c>
-      <c r="S11">
-        <v>1.05</v>
-      </c>
-      <c r="T11">
-        <v>1.8</v>
-      </c>
-      <c r="U11">
-        <v>1.71</v>
-      </c>
-      <c r="V11">
-        <v>1.01</v>
-      </c>
       <c r="W11">
-        <v>1.01</v>
+        <v>2.28</v>
       </c>
       <c r="X11">
-        <v>970</v>
+        <v>12</v>
       </c>
       <c r="Y11">
+        <v>16</v>
+      </c>
+      <c r="Z11">
+        <v>60</v>
+      </c>
+      <c r="AA11">
+        <v>700</v>
+      </c>
+      <c r="AB11">
+        <v>6.8</v>
+      </c>
+      <c r="AC11">
         <v>8.800000000000001</v>
       </c>
-      <c r="Z11">
-        <v>17.5</v>
-      </c>
-      <c r="AA11">
+      <c r="AD11">
+        <v>23</v>
+      </c>
+      <c r="AE11">
+        <v>120</v>
+      </c>
+      <c r="AF11">
+        <v>9.4</v>
+      </c>
+      <c r="AG11">
+        <v>10.5</v>
+      </c>
+      <c r="AH11">
+        <v>26</v>
+      </c>
+      <c r="AI11">
+        <v>120</v>
+      </c>
+      <c r="AJ11">
+        <v>19</v>
+      </c>
+      <c r="AK11">
+        <v>21</v>
+      </c>
+      <c r="AL11">
         <v>60</v>
       </c>
-      <c r="AB11">
-        <v>10</v>
-      </c>
-      <c r="AC11">
+      <c r="AM11">
+        <v>500</v>
+      </c>
+      <c r="AN11">
+        <v>15.5</v>
+      </c>
+      <c r="AO11">
+        <v>700</v>
+      </c>
+      <c r="AP11">
+        <v>10.5</v>
+      </c>
+      <c r="AQ11">
+        <v>13.5</v>
+      </c>
+      <c r="AR11">
+        <v>30</v>
+      </c>
+      <c r="AS11">
+        <v>13.5</v>
+      </c>
+      <c r="AT11">
+        <v>6</v>
+      </c>
+      <c r="AU11">
         <v>7.8</v>
       </c>
-      <c r="AD11">
-        <v>970</v>
-      </c>
-      <c r="AE11">
-        <v>55</v>
-      </c>
-      <c r="AF11">
-        <v>25</v>
-      </c>
-      <c r="AG11">
+      <c r="AV11">
         <v>20</v>
       </c>
-      <c r="AH11">
-        <v>32</v>
-      </c>
-      <c r="AI11">
-        <v>95</v>
-      </c>
-      <c r="AJ11">
-        <v>90</v>
-      </c>
-      <c r="AK11">
-        <v>80</v>
-      </c>
-      <c r="AL11">
-        <v>110</v>
-      </c>
-      <c r="AM11">
-        <v>230</v>
-      </c>
-      <c r="AN11">
-        <v>160</v>
-      </c>
-      <c r="AO11">
-        <v>65</v>
-      </c>
-      <c r="AP11">
-        <v>6.2</v>
-      </c>
-      <c r="AQ11">
-        <v>6.2</v>
-      </c>
-      <c r="AR11">
-        <v>12</v>
-      </c>
-      <c r="AS11">
-        <v>30</v>
-      </c>
-      <c r="AT11">
-        <v>7</v>
-      </c>
-      <c r="AU11">
-        <v>5.5</v>
-      </c>
-      <c r="AV11">
-        <v>10</v>
-      </c>
       <c r="AW11">
-        <v>29</v>
+        <v>12.5</v>
       </c>
       <c r="AX11">
-        <v>17</v>
+        <v>8.4</v>
       </c>
       <c r="AY11">
-        <v>11.5</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AZ11">
         <v>20</v>
       </c>
       <c r="BA11">
-        <v>50</v>
+        <v>12.5</v>
       </c>
       <c r="BB11">
-        <v>46</v>
+        <v>16.5</v>
       </c>
       <c r="BC11">
-        <v>40</v>
+        <v>18.5</v>
       </c>
       <c r="BD11">
-        <v>55</v>
+        <v>11</v>
       </c>
       <c r="BE11">
-        <v>5</v>
+        <v>13.5</v>
       </c>
       <c r="BF11">
-        <v>5.5</v>
+        <v>11.5</v>
       </c>
       <c r="BG11">
-        <v>36</v>
+        <v>13</v>
       </c>
       <c r="BH11">
-        <v>1000</v>
+        <v>3.75</v>
       </c>
       <c r="BI11">
-        <v>1.04</v>
+        <v>2.5</v>
       </c>
       <c r="BJ11">
         <v>1000</v>
       </c>
       <c r="BK11">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="BL11">
         <v>1000</v>
       </c>
       <c r="BM11">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="BN11">
         <v>1000</v>
       </c>
       <c r="BO11">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="BP11">
         <v>1000</v>
       </c>
       <c r="BQ11">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="BR11">
         <v>1000</v>
       </c>
       <c r="BS11">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="BT11">
         <v>1000</v>
       </c>
       <c r="BU11">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="BV11">
         <v>1000</v>
       </c>
       <c r="BW11">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="BX11">
         <v>1000</v>
       </c>
       <c r="BY11">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="BZ11">
         <v>1000</v>
       </c>
       <c r="CA11">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="CB11" t="s">
-        <v>141</v>
+        <v>121</v>
       </c>
     </row>
     <row r="12" spans="1:80">
       <c r="A12" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="B12" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="C12" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="D12" t="s">
-        <v>113</v>
+        <v>107</v>
       </c>
       <c r="E12" t="s">
-        <v>132</v>
+        <v>119</v>
       </c>
       <c r="F12">
-        <v>2.34</v>
+        <v>2.78</v>
       </c>
       <c r="G12">
-        <v>2.94</v>
+        <v>2.9</v>
       </c>
       <c r="H12">
-        <v>2.8</v>
+        <v>2.82</v>
       </c>
       <c r="I12">
-        <v>3.95</v>
+        <v>2.9</v>
       </c>
       <c r="J12">
-        <v>2.72</v>
+        <v>3.2</v>
       </c>
       <c r="K12">
-        <v>3.65</v>
+        <v>3.45</v>
       </c>
       <c r="L12">
-        <v>1.43</v>
+        <v>1.46</v>
       </c>
       <c r="M12">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="N12">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="O12">
-        <v>1.37</v>
+        <v>1.39</v>
       </c>
       <c r="P12">
-        <v>1.66</v>
+        <v>1.77</v>
       </c>
       <c r="Q12">
-        <v>2.02</v>
+        <v>2.14</v>
       </c>
       <c r="R12">
         <v>1.29</v>
       </c>
       <c r="S12">
-        <v>3.45</v>
+        <v>4</v>
       </c>
       <c r="T12">
-        <v>1.11</v>
+        <v>1.85</v>
       </c>
       <c r="U12">
-        <v>1.11</v>
+        <v>2.04</v>
       </c>
       <c r="V12">
-        <v>1.34</v>
+        <v>1.52</v>
       </c>
       <c r="W12">
-        <v>1.51</v>
+        <v>1.52</v>
       </c>
       <c r="X12">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="Y12">
-        <v>11.5</v>
+        <v>10.5</v>
       </c>
       <c r="Z12">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="AA12">
-        <v>55</v>
+        <v>65</v>
       </c>
       <c r="AB12">
         <v>10.5</v>
       </c>
       <c r="AC12">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="AD12">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AE12">
-        <v>38</v>
+        <v>50</v>
       </c>
       <c r="AF12">
-        <v>17.5</v>
+        <v>19.5</v>
       </c>
       <c r="AG12">
         <v>13</v>
@@ -3540,174 +3480,174 @@
         <v>18.5</v>
       </c>
       <c r="AI12">
-        <v>55</v>
+        <v>70</v>
       </c>
       <c r="AJ12">
-        <v>42</v>
+        <v>320</v>
       </c>
       <c r="AK12">
+        <v>50</v>
+      </c>
+      <c r="AL12">
+        <v>290</v>
+      </c>
+      <c r="AM12">
+        <v>450</v>
+      </c>
+      <c r="AN12">
+        <v>50</v>
+      </c>
+      <c r="AO12">
         <v>32</v>
       </c>
-      <c r="AL12">
-        <v>48</v>
-      </c>
-      <c r="AM12">
-        <v>120</v>
-      </c>
-      <c r="AN12">
-        <v>34</v>
-      </c>
-      <c r="AO12">
-        <v>38</v>
-      </c>
       <c r="AP12">
+        <v>10.5</v>
+      </c>
+      <c r="AQ12">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AR12">
+        <v>15.5</v>
+      </c>
+      <c r="AS12">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AT12">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AU12">
+        <v>6.6</v>
+      </c>
+      <c r="AV12">
+        <v>11</v>
+      </c>
+      <c r="AW12">
+        <v>14.5</v>
+      </c>
+      <c r="AX12">
+        <v>16.5</v>
+      </c>
+      <c r="AY12">
+        <v>11.5</v>
+      </c>
+      <c r="AZ12">
+        <v>16</v>
+      </c>
+      <c r="BA12">
         <v>9.4</v>
       </c>
-      <c r="AQ12">
+      <c r="BB12">
+        <v>29</v>
+      </c>
+      <c r="BC12">
+        <v>16</v>
+      </c>
+      <c r="BD12">
         <v>9.4</v>
       </c>
-      <c r="AR12">
-        <v>17</v>
-      </c>
-      <c r="AS12">
-        <v>38</v>
-      </c>
-      <c r="AT12">
-        <v>8.6</v>
-      </c>
-      <c r="AU12">
-        <v>6.4</v>
-      </c>
-      <c r="AV12">
-        <v>11.5</v>
-      </c>
-      <c r="AW12">
-        <v>29</v>
-      </c>
-      <c r="AX12">
-        <v>14</v>
-      </c>
-      <c r="AY12">
+      <c r="BE12">
         <v>10.5</v>
       </c>
-      <c r="AZ12">
-        <v>15.5</v>
-      </c>
-      <c r="BA12">
-        <v>36</v>
-      </c>
-      <c r="BB12">
-        <v>7.4</v>
-      </c>
-      <c r="BC12">
-        <v>19.5</v>
-      </c>
-      <c r="BD12">
-        <v>7.6</v>
-      </c>
-      <c r="BE12">
+      <c r="BF12">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="BG12">
         <v>8.4</v>
       </c>
-      <c r="BF12">
-        <v>21</v>
-      </c>
-      <c r="BG12">
-        <v>7.4</v>
-      </c>
       <c r="BH12">
-        <v>3.25</v>
+        <v>3.15</v>
       </c>
       <c r="BI12">
-        <v>2.86</v>
+        <v>2.6</v>
       </c>
       <c r="BJ12">
         <v>10</v>
       </c>
       <c r="BK12">
-        <v>5.4</v>
+        <v>6</v>
       </c>
       <c r="BL12">
         <v>1000</v>
       </c>
       <c r="BM12">
+        <v>13.5</v>
+      </c>
+      <c r="BN12">
+        <v>5.9</v>
+      </c>
+      <c r="BO12">
+        <v>4.4</v>
+      </c>
+      <c r="BP12">
+        <v>24</v>
+      </c>
+      <c r="BQ12">
+        <v>9.4</v>
+      </c>
+      <c r="BR12">
+        <v>40</v>
+      </c>
+      <c r="BS12">
         <v>11</v>
       </c>
-      <c r="BN12">
-        <v>5.6</v>
-      </c>
-      <c r="BO12">
+      <c r="BT12">
+        <v>5.7</v>
+      </c>
+      <c r="BU12">
         <v>4.3</v>
       </c>
-      <c r="BP12">
-        <v>21</v>
-      </c>
-      <c r="BQ12">
-        <v>7.6</v>
-      </c>
-      <c r="BR12">
-        <v>36</v>
-      </c>
-      <c r="BS12">
-        <v>9</v>
-      </c>
-      <c r="BT12">
-        <v>6.4</v>
-      </c>
-      <c r="BU12">
-        <v>4.8</v>
-      </c>
       <c r="BV12">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="BW12">
-        <v>8.199999999999999</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BX12">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="BY12">
-        <v>9.199999999999999</v>
+        <v>10.5</v>
       </c>
       <c r="BZ12">
         <v>34</v>
       </c>
       <c r="CA12">
-        <v>8.800000000000001</v>
+        <v>10.5</v>
       </c>
       <c r="CB12" t="s">
-        <v>141</v>
+        <v>121</v>
       </c>
     </row>
     <row r="13" spans="1:80">
       <c r="A13" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="B13" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="C13" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="D13" t="s">
-        <v>114</v>
+        <v>108</v>
       </c>
       <c r="E13" t="s">
-        <v>133</v>
+        <v>120</v>
       </c>
       <c r="F13">
-        <v>1.92</v>
+        <v>2.22</v>
       </c>
       <c r="G13">
-        <v>2.02</v>
+        <v>2.42</v>
       </c>
       <c r="H13">
-        <v>4.3</v>
+        <v>3.35</v>
       </c>
       <c r="I13">
-        <v>5.1</v>
+        <v>3.8</v>
       </c>
       <c r="J13">
-        <v>3.5</v>
+        <v>3.25</v>
       </c>
       <c r="K13">
         <v>3.6</v>
@@ -3716,1902 +3656,208 @@
         <v>1.44</v>
       </c>
       <c r="M13">
-        <v>1.1</v>
+        <v>1.08</v>
       </c>
       <c r="N13">
-        <v>3.05</v>
+        <v>3.25</v>
       </c>
       <c r="O13">
-        <v>1.45</v>
+        <v>1.37</v>
       </c>
       <c r="P13">
-        <v>1.71</v>
+        <v>1.77</v>
       </c>
       <c r="Q13">
-        <v>2.32</v>
+        <v>2.08</v>
       </c>
       <c r="R13">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="S13">
-        <v>4.5</v>
+        <v>3.75</v>
       </c>
       <c r="T13">
-        <v>2.08</v>
+        <v>1.83</v>
       </c>
       <c r="U13">
-        <v>1.84</v>
+        <v>2</v>
       </c>
       <c r="V13">
-        <v>1.26</v>
+        <v>1.37</v>
       </c>
       <c r="W13">
-        <v>1.98</v>
+        <v>1.7</v>
       </c>
       <c r="X13">
-        <v>11</v>
+        <v>14.5</v>
       </c>
       <c r="Y13">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="Z13">
-        <v>85</v>
+        <v>29</v>
       </c>
       <c r="AA13">
-        <v>500</v>
+        <v>75</v>
       </c>
       <c r="AB13">
-        <v>7.4</v>
+        <v>10.5</v>
       </c>
       <c r="AC13">
-        <v>8</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AD13">
-        <v>23</v>
+        <v>17.5</v>
       </c>
       <c r="AE13">
-        <v>190</v>
+        <v>55</v>
       </c>
       <c r="AF13">
-        <v>11</v>
+        <v>16.5</v>
       </c>
       <c r="AG13">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="AH13">
-        <v>42</v>
+        <v>22</v>
       </c>
       <c r="AI13">
-        <v>230</v>
+        <v>70</v>
       </c>
       <c r="AJ13">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="AK13">
-        <v>46</v>
+        <v>30</v>
       </c>
       <c r="AL13">
+        <v>48</v>
+      </c>
+      <c r="AM13">
+        <v>130</v>
+      </c>
+      <c r="AN13">
+        <v>24</v>
+      </c>
+      <c r="AO13">
         <v>60</v>
       </c>
-      <c r="AM13">
-        <v>580</v>
-      </c>
-      <c r="AN13">
-        <v>23</v>
-      </c>
-      <c r="AO13">
-        <v>140</v>
-      </c>
       <c r="AP13">
-        <v>8.6</v>
+        <v>9.4</v>
       </c>
       <c r="AQ13">
-        <v>11.5</v>
+        <v>9.6</v>
       </c>
       <c r="AR13">
-        <v>15.5</v>
+        <v>19</v>
       </c>
       <c r="AS13">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="AT13">
-        <v>5.7</v>
+        <v>7</v>
       </c>
       <c r="AU13">
         <v>6</v>
       </c>
       <c r="AV13">
-        <v>15</v>
+        <v>11.5</v>
       </c>
       <c r="AW13">
-        <v>23</v>
+        <v>4.9</v>
       </c>
       <c r="AX13">
-        <v>8.800000000000001</v>
+        <v>11</v>
       </c>
       <c r="AY13">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="AZ13">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="BA13">
-        <v>28</v>
+        <v>5</v>
       </c>
       <c r="BB13">
-        <v>12</v>
+        <v>4.7</v>
       </c>
       <c r="BC13">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="BD13">
-        <v>34</v>
+        <v>4.8</v>
       </c>
       <c r="BE13">
-        <v>10</v>
+        <v>5.1</v>
       </c>
       <c r="BF13">
-        <v>15</v>
+        <v>16.5</v>
       </c>
       <c r="BG13">
-        <v>10</v>
+        <v>4.9</v>
       </c>
       <c r="BH13">
         <v>3.3</v>
       </c>
       <c r="BI13">
-        <v>2.48</v>
+        <v>2.64</v>
       </c>
       <c r="BJ13">
-        <v>13</v>
+        <v>10.5</v>
       </c>
       <c r="BK13">
-        <v>4.1</v>
+        <v>5.2</v>
       </c>
       <c r="BL13">
         <v>1000</v>
       </c>
       <c r="BM13">
-        <v>5.8</v>
+        <v>9.6</v>
       </c>
       <c r="BN13">
-        <v>5</v>
+        <v>5.2</v>
       </c>
       <c r="BO13">
-        <v>3.6</v>
+        <v>4</v>
       </c>
       <c r="BP13">
-        <v>17</v>
+        <v>18.5</v>
       </c>
       <c r="BQ13">
-        <v>4.4</v>
+        <v>6.6</v>
       </c>
       <c r="BR13">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="BS13">
-        <v>5.2</v>
+        <v>8</v>
       </c>
       <c r="BT13">
-        <v>9.199999999999999</v>
+        <v>7</v>
       </c>
       <c r="BU13">
-        <v>3.6</v>
+        <v>5.3</v>
       </c>
       <c r="BV13">
         <v>1000</v>
       </c>
       <c r="BW13">
-        <v>5.4</v>
+        <v>7.8</v>
       </c>
       <c r="BX13">
         <v>1000</v>
       </c>
       <c r="BY13">
-        <v>5.5</v>
+        <v>8.4</v>
       </c>
       <c r="BZ13">
-        <v>40</v>
+        <v>34</v>
       </c>
       <c r="CA13">
-        <v>5.2</v>
+        <v>7.8</v>
       </c>
       <c r="CB13" t="s">
-        <v>141</v>
-      </c>
-    </row>
-    <row r="14" spans="1:80">
-      <c r="A14" t="s">
-        <v>88</v>
-      </c>
-      <c r="B14" t="s">
-        <v>91</v>
-      </c>
-      <c r="C14" t="s">
-        <v>99</v>
-      </c>
-      <c r="D14" t="s">
-        <v>115</v>
-      </c>
-      <c r="E14" t="s">
-        <v>134</v>
-      </c>
-      <c r="F14">
-        <v>0</v>
-      </c>
-      <c r="G14">
-        <v>0</v>
-      </c>
-      <c r="H14">
-        <v>0</v>
-      </c>
-      <c r="I14">
-        <v>0</v>
-      </c>
-      <c r="J14">
-        <v>0</v>
-      </c>
-      <c r="K14">
-        <v>0</v>
-      </c>
-      <c r="L14">
-        <v>0</v>
-      </c>
-      <c r="M14">
-        <v>0</v>
-      </c>
-      <c r="N14">
-        <v>0</v>
-      </c>
-      <c r="O14">
-        <v>0</v>
-      </c>
-      <c r="P14">
-        <v>1.25</v>
-      </c>
-      <c r="Q14">
-        <v>1.9</v>
-      </c>
-      <c r="R14">
-        <v>0</v>
-      </c>
-      <c r="S14">
-        <v>0</v>
-      </c>
-      <c r="T14">
-        <v>0</v>
-      </c>
-      <c r="U14">
-        <v>0</v>
-      </c>
-      <c r="V14">
-        <v>0</v>
-      </c>
-      <c r="W14">
-        <v>0</v>
-      </c>
-      <c r="X14">
-        <v>0</v>
-      </c>
-      <c r="Y14">
-        <v>0</v>
-      </c>
-      <c r="Z14">
-        <v>0</v>
-      </c>
-      <c r="AA14">
-        <v>0</v>
-      </c>
-      <c r="AB14">
-        <v>0</v>
-      </c>
-      <c r="AC14">
-        <v>0</v>
-      </c>
-      <c r="AD14">
-        <v>0</v>
-      </c>
-      <c r="AE14">
-        <v>0</v>
-      </c>
-      <c r="AF14">
-        <v>0</v>
-      </c>
-      <c r="AG14">
-        <v>0</v>
-      </c>
-      <c r="AH14">
-        <v>0</v>
-      </c>
-      <c r="AI14">
-        <v>0</v>
-      </c>
-      <c r="AJ14">
-        <v>0</v>
-      </c>
-      <c r="AK14">
-        <v>0</v>
-      </c>
-      <c r="AL14">
-        <v>0</v>
-      </c>
-      <c r="AM14">
-        <v>0</v>
-      </c>
-      <c r="AN14">
-        <v>0</v>
-      </c>
-      <c r="AO14">
-        <v>0</v>
-      </c>
-      <c r="AP14">
-        <v>0</v>
-      </c>
-      <c r="AQ14">
-        <v>0</v>
-      </c>
-      <c r="AR14">
-        <v>0</v>
-      </c>
-      <c r="AS14">
-        <v>0</v>
-      </c>
-      <c r="AT14">
-        <v>0</v>
-      </c>
-      <c r="AU14">
-        <v>0</v>
-      </c>
-      <c r="AV14">
-        <v>0</v>
-      </c>
-      <c r="AW14">
-        <v>0</v>
-      </c>
-      <c r="AX14">
-        <v>0</v>
-      </c>
-      <c r="AY14">
-        <v>0</v>
-      </c>
-      <c r="AZ14">
-        <v>0</v>
-      </c>
-      <c r="BA14">
-        <v>0</v>
-      </c>
-      <c r="BB14">
-        <v>0</v>
-      </c>
-      <c r="BC14">
-        <v>0</v>
-      </c>
-      <c r="BD14">
-        <v>0</v>
-      </c>
-      <c r="BE14">
-        <v>0</v>
-      </c>
-      <c r="BF14">
-        <v>0</v>
-      </c>
-      <c r="BG14">
-        <v>0</v>
-      </c>
-      <c r="BH14">
-        <v>0</v>
-      </c>
-      <c r="BI14">
-        <v>0</v>
-      </c>
-      <c r="BJ14">
-        <v>0</v>
-      </c>
-      <c r="BK14">
-        <v>0</v>
-      </c>
-      <c r="BL14">
-        <v>0</v>
-      </c>
-      <c r="BM14">
-        <v>0</v>
-      </c>
-      <c r="BN14">
-        <v>0</v>
-      </c>
-      <c r="BO14">
-        <v>0</v>
-      </c>
-      <c r="BP14">
-        <v>0</v>
-      </c>
-      <c r="BQ14">
-        <v>0</v>
-      </c>
-      <c r="BR14">
-        <v>0</v>
-      </c>
-      <c r="BS14">
-        <v>0</v>
-      </c>
-      <c r="BT14">
-        <v>0</v>
-      </c>
-      <c r="BU14">
-        <v>0</v>
-      </c>
-      <c r="BV14">
-        <v>0</v>
-      </c>
-      <c r="BW14">
-        <v>0</v>
-      </c>
-      <c r="BX14">
-        <v>0</v>
-      </c>
-      <c r="BY14">
-        <v>0</v>
-      </c>
-      <c r="BZ14">
-        <v>0</v>
-      </c>
-      <c r="CA14">
-        <v>0</v>
-      </c>
-      <c r="CB14" t="s">
-        <v>141</v>
-      </c>
-    </row>
-    <row r="15" spans="1:80">
-      <c r="A15" t="s">
-        <v>89</v>
-      </c>
-      <c r="B15" t="s">
-        <v>91</v>
-      </c>
-      <c r="C15" t="s">
-        <v>100</v>
-      </c>
-      <c r="D15" t="s">
-        <v>116</v>
-      </c>
-      <c r="E15" t="s">
-        <v>135</v>
-      </c>
-      <c r="F15">
-        <v>2.8</v>
-      </c>
-      <c r="G15">
-        <v>2.98</v>
-      </c>
-      <c r="H15">
-        <v>2.74</v>
-      </c>
-      <c r="I15">
-        <v>2.9</v>
-      </c>
-      <c r="J15">
-        <v>3.2</v>
-      </c>
-      <c r="K15">
-        <v>3.5</v>
-      </c>
-      <c r="L15">
-        <v>1.38</v>
-      </c>
-      <c r="M15">
-        <v>1.09</v>
-      </c>
-      <c r="N15">
-        <v>3.2</v>
-      </c>
-      <c r="O15">
-        <v>1.39</v>
-      </c>
-      <c r="P15">
-        <v>1.77</v>
-      </c>
-      <c r="Q15">
-        <v>2.14</v>
-      </c>
-      <c r="R15">
-        <v>1.29</v>
-      </c>
-      <c r="S15">
-        <v>4</v>
-      </c>
-      <c r="T15">
-        <v>1.85</v>
-      </c>
-      <c r="U15">
-        <v>2.02</v>
-      </c>
-      <c r="V15">
-        <v>1.53</v>
-      </c>
-      <c r="W15">
-        <v>1.51</v>
-      </c>
-      <c r="X15">
-        <v>14.5</v>
-      </c>
-      <c r="Y15">
-        <v>10.5</v>
-      </c>
-      <c r="Z15">
-        <v>18</v>
-      </c>
-      <c r="AA15">
-        <v>65</v>
-      </c>
-      <c r="AB15">
-        <v>10.5</v>
-      </c>
-      <c r="AC15">
-        <v>7.6</v>
-      </c>
-      <c r="AD15">
-        <v>13</v>
-      </c>
-      <c r="AE15">
-        <v>50</v>
-      </c>
-      <c r="AF15">
-        <v>19.5</v>
-      </c>
-      <c r="AG15">
-        <v>13</v>
-      </c>
-      <c r="AH15">
-        <v>18.5</v>
-      </c>
-      <c r="AI15">
-        <v>70</v>
-      </c>
-      <c r="AJ15">
-        <v>70</v>
-      </c>
-      <c r="AK15">
-        <v>50</v>
-      </c>
-      <c r="AL15">
-        <v>50</v>
-      </c>
-      <c r="AM15">
-        <v>130</v>
-      </c>
-      <c r="AN15">
-        <v>50</v>
-      </c>
-      <c r="AO15">
-        <v>32</v>
-      </c>
-      <c r="AP15">
-        <v>9</v>
-      </c>
-      <c r="AQ15">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AR15">
-        <v>15.5</v>
-      </c>
-      <c r="AS15">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AT15">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AU15">
-        <v>6.6</v>
-      </c>
-      <c r="AV15">
-        <v>11</v>
-      </c>
-      <c r="AW15">
-        <v>8.6</v>
-      </c>
-      <c r="AX15">
-        <v>16.5</v>
-      </c>
-      <c r="AY15">
-        <v>11.5</v>
-      </c>
-      <c r="AZ15">
-        <v>16</v>
-      </c>
-      <c r="BA15">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="BB15">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="BC15">
-        <v>8.6</v>
-      </c>
-      <c r="BD15">
-        <v>30</v>
-      </c>
-      <c r="BE15">
-        <v>10.5</v>
-      </c>
-      <c r="BF15">
-        <v>8.6</v>
-      </c>
-      <c r="BG15">
-        <v>8.4</v>
-      </c>
-      <c r="BH15">
-        <v>3.15</v>
-      </c>
-      <c r="BI15">
-        <v>2.6</v>
-      </c>
-      <c r="BJ15">
-        <v>10</v>
-      </c>
-      <c r="BK15">
-        <v>6</v>
-      </c>
-      <c r="BL15">
-        <v>1000</v>
-      </c>
-      <c r="BM15">
-        <v>13.5</v>
-      </c>
-      <c r="BN15">
-        <v>5.9</v>
-      </c>
-      <c r="BO15">
-        <v>4.4</v>
-      </c>
-      <c r="BP15">
-        <v>24</v>
-      </c>
-      <c r="BQ15">
-        <v>9.4</v>
-      </c>
-      <c r="BR15">
-        <v>40</v>
-      </c>
-      <c r="BS15">
-        <v>11</v>
-      </c>
-      <c r="BT15">
-        <v>5.7</v>
-      </c>
-      <c r="BU15">
-        <v>4.3</v>
-      </c>
-      <c r="BV15">
-        <v>23</v>
-      </c>
-      <c r="BW15">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="BX15">
-        <v>38</v>
-      </c>
-      <c r="BY15">
-        <v>10.5</v>
-      </c>
-      <c r="BZ15">
-        <v>34</v>
-      </c>
-      <c r="CA15">
-        <v>10.5</v>
-      </c>
-      <c r="CB15" t="s">
-        <v>141</v>
-      </c>
-    </row>
-    <row r="16" spans="1:80">
-      <c r="A16" t="s">
-        <v>86</v>
-      </c>
-      <c r="B16" t="s">
-        <v>91</v>
-      </c>
-      <c r="C16" t="s">
-        <v>101</v>
-      </c>
-      <c r="D16" t="s">
-        <v>117</v>
-      </c>
-      <c r="E16" t="s">
-        <v>136</v>
-      </c>
-      <c r="F16">
-        <v>1.48</v>
-      </c>
-      <c r="G16">
-        <v>1.66</v>
-      </c>
-      <c r="H16">
-        <v>6.2</v>
-      </c>
-      <c r="I16">
-        <v>9.4</v>
-      </c>
-      <c r="J16">
-        <v>3.45</v>
-      </c>
-      <c r="K16">
-        <v>4.7</v>
-      </c>
-      <c r="L16">
-        <v>1.38</v>
-      </c>
-      <c r="M16">
-        <v>1.07</v>
-      </c>
-      <c r="N16">
-        <v>3.35</v>
-      </c>
-      <c r="O16">
-        <v>1.33</v>
-      </c>
-      <c r="P16">
-        <v>1.82</v>
-      </c>
-      <c r="Q16">
-        <v>1.92</v>
-      </c>
-      <c r="R16">
-        <v>1.31</v>
-      </c>
-      <c r="S16">
-        <v>3.5</v>
-      </c>
-      <c r="T16">
-        <v>2.04</v>
-      </c>
-      <c r="U16">
-        <v>1.77</v>
-      </c>
-      <c r="V16">
-        <v>1.11</v>
-      </c>
-      <c r="W16">
-        <v>2.46</v>
-      </c>
-      <c r="X16">
-        <v>16</v>
-      </c>
-      <c r="Y16">
-        <v>25</v>
-      </c>
-      <c r="Z16">
-        <v>75</v>
-      </c>
-      <c r="AA16">
-        <v>310</v>
-      </c>
-      <c r="AB16">
-        <v>7.6</v>
-      </c>
-      <c r="AC16">
-        <v>11</v>
-      </c>
-      <c r="AD16">
-        <v>34</v>
-      </c>
-      <c r="AE16">
-        <v>160</v>
-      </c>
-      <c r="AF16">
-        <v>10</v>
-      </c>
-      <c r="AG16">
-        <v>12</v>
-      </c>
-      <c r="AH16">
-        <v>30</v>
-      </c>
-      <c r="AI16">
-        <v>140</v>
-      </c>
-      <c r="AJ16">
-        <v>16.5</v>
-      </c>
-      <c r="AK16">
-        <v>21</v>
-      </c>
-      <c r="AL16">
-        <v>50</v>
-      </c>
-      <c r="AM16">
-        <v>200</v>
-      </c>
-      <c r="AN16">
-        <v>11.5</v>
-      </c>
-      <c r="AO16">
-        <v>240</v>
-      </c>
-      <c r="AP16">
-        <v>4.2</v>
-      </c>
-      <c r="AQ16">
-        <v>4.6</v>
-      </c>
-      <c r="AR16">
-        <v>5.3</v>
-      </c>
-      <c r="AS16">
-        <v>5.6</v>
-      </c>
-      <c r="AT16">
-        <v>3.25</v>
-      </c>
-      <c r="AU16">
-        <v>3.75</v>
-      </c>
-      <c r="AV16">
-        <v>4.9</v>
-      </c>
-      <c r="AW16">
-        <v>5.5</v>
-      </c>
-      <c r="AX16">
-        <v>3.6</v>
-      </c>
-      <c r="AY16">
-        <v>3.85</v>
-      </c>
-      <c r="AZ16">
-        <v>4.8</v>
-      </c>
-      <c r="BA16">
-        <v>5.5</v>
-      </c>
-      <c r="BB16">
-        <v>4.2</v>
-      </c>
-      <c r="BC16">
-        <v>4.4</v>
-      </c>
-      <c r="BD16">
-        <v>5.1</v>
-      </c>
-      <c r="BE16">
-        <v>5.5</v>
-      </c>
-      <c r="BF16">
-        <v>3.8</v>
-      </c>
-      <c r="BG16">
-        <v>5.5</v>
-      </c>
-      <c r="BH16">
-        <v>3.5</v>
-      </c>
-      <c r="BI16">
-        <v>2.78</v>
-      </c>
-      <c r="BJ16">
-        <v>12.5</v>
-      </c>
-      <c r="BK16">
-        <v>5.4</v>
-      </c>
-      <c r="BL16">
-        <v>1000</v>
-      </c>
-      <c r="BM16">
-        <v>9</v>
-      </c>
-      <c r="BN16">
-        <v>4.1</v>
-      </c>
-      <c r="BO16">
-        <v>3.15</v>
-      </c>
-      <c r="BP16">
-        <v>11</v>
-      </c>
-      <c r="BQ16">
-        <v>5.1</v>
-      </c>
-      <c r="BR16">
-        <v>1000</v>
-      </c>
-      <c r="BS16">
-        <v>7.2</v>
-      </c>
-      <c r="BT16">
-        <v>11.5</v>
-      </c>
-      <c r="BU16">
-        <v>5.2</v>
-      </c>
-      <c r="BV16">
-        <v>1000</v>
-      </c>
-      <c r="BW16">
-        <v>8.4</v>
-      </c>
-      <c r="BX16">
-        <v>1000</v>
-      </c>
-      <c r="BY16">
-        <v>8.6</v>
-      </c>
-      <c r="BZ16">
-        <v>0</v>
-      </c>
-      <c r="CA16">
-        <v>0</v>
-      </c>
-      <c r="CB16" t="s">
-        <v>141</v>
-      </c>
-    </row>
-    <row r="17" spans="1:80">
-      <c r="A17" t="s">
-        <v>90</v>
-      </c>
-      <c r="B17" t="s">
-        <v>91</v>
-      </c>
-      <c r="C17" t="s">
-        <v>102</v>
-      </c>
-      <c r="D17" t="s">
-        <v>118</v>
-      </c>
-      <c r="E17" t="s">
-        <v>137</v>
-      </c>
-      <c r="F17">
-        <v>2.22</v>
-      </c>
-      <c r="G17">
-        <v>2.42</v>
-      </c>
-      <c r="H17">
-        <v>3.35</v>
-      </c>
-      <c r="I17">
-        <v>3.8</v>
-      </c>
-      <c r="J17">
-        <v>3.25</v>
-      </c>
-      <c r="K17">
-        <v>3.6</v>
-      </c>
-      <c r="L17">
-        <v>1.44</v>
-      </c>
-      <c r="M17">
-        <v>1.08</v>
-      </c>
-      <c r="N17">
-        <v>3.25</v>
-      </c>
-      <c r="O17">
-        <v>1.37</v>
-      </c>
-      <c r="P17">
-        <v>1.77</v>
-      </c>
-      <c r="Q17">
-        <v>2.08</v>
-      </c>
-      <c r="R17">
-        <v>1.28</v>
-      </c>
-      <c r="S17">
-        <v>3.75</v>
-      </c>
-      <c r="T17">
-        <v>1.83</v>
-      </c>
-      <c r="U17">
-        <v>2</v>
-      </c>
-      <c r="V17">
-        <v>1.37</v>
-      </c>
-      <c r="W17">
-        <v>1.7</v>
-      </c>
-      <c r="X17">
-        <v>14.5</v>
-      </c>
-      <c r="Y17">
-        <v>14.5</v>
-      </c>
-      <c r="Z17">
-        <v>30</v>
-      </c>
-      <c r="AA17">
-        <v>75</v>
-      </c>
-      <c r="AB17">
-        <v>10.5</v>
-      </c>
-      <c r="AC17">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AD17">
-        <v>18</v>
-      </c>
-      <c r="AE17">
-        <v>55</v>
-      </c>
-      <c r="AF17">
-        <v>16.5</v>
-      </c>
-      <c r="AG17">
-        <v>13</v>
-      </c>
-      <c r="AH17">
-        <v>22</v>
-      </c>
-      <c r="AI17">
-        <v>70</v>
-      </c>
-      <c r="AJ17">
-        <v>36</v>
-      </c>
-      <c r="AK17">
-        <v>32</v>
-      </c>
-      <c r="AL17">
-        <v>50</v>
-      </c>
-      <c r="AM17">
-        <v>130</v>
-      </c>
-      <c r="AN17">
-        <v>26</v>
-      </c>
-      <c r="AO17">
-        <v>60</v>
-      </c>
-      <c r="AP17">
-        <v>9.4</v>
-      </c>
-      <c r="AQ17">
-        <v>9.6</v>
-      </c>
-      <c r="AR17">
-        <v>19</v>
-      </c>
-      <c r="AS17">
-        <v>4.8</v>
-      </c>
-      <c r="AT17">
-        <v>7</v>
-      </c>
-      <c r="AU17">
-        <v>6</v>
-      </c>
-      <c r="AV17">
-        <v>11.5</v>
-      </c>
-      <c r="AW17">
-        <v>4.7</v>
-      </c>
-      <c r="AX17">
-        <v>11</v>
-      </c>
-      <c r="AY17">
-        <v>9.6</v>
-      </c>
-      <c r="AZ17">
-        <v>14</v>
-      </c>
-      <c r="BA17">
-        <v>4.8</v>
-      </c>
-      <c r="BB17">
-        <v>4.5</v>
-      </c>
-      <c r="BC17">
-        <v>20</v>
-      </c>
-      <c r="BD17">
-        <v>4.6</v>
-      </c>
-      <c r="BE17">
-        <v>4.9</v>
-      </c>
-      <c r="BF17">
-        <v>16.5</v>
-      </c>
-      <c r="BG17">
-        <v>4.7</v>
-      </c>
-      <c r="BH17">
-        <v>3.3</v>
-      </c>
-      <c r="BI17">
-        <v>2.64</v>
-      </c>
-      <c r="BJ17">
-        <v>10.5</v>
-      </c>
-      <c r="BK17">
-        <v>5.2</v>
-      </c>
-      <c r="BL17">
-        <v>1000</v>
-      </c>
-      <c r="BM17">
-        <v>9.6</v>
-      </c>
-      <c r="BN17">
-        <v>5.2</v>
-      </c>
-      <c r="BO17">
-        <v>4</v>
-      </c>
-      <c r="BP17">
-        <v>18.5</v>
-      </c>
-      <c r="BQ17">
-        <v>6.6</v>
-      </c>
-      <c r="BR17">
-        <v>36</v>
-      </c>
-      <c r="BS17">
-        <v>8</v>
-      </c>
-      <c r="BT17">
-        <v>7</v>
-      </c>
-      <c r="BU17">
-        <v>5.3</v>
-      </c>
-      <c r="BV17">
-        <v>1000</v>
-      </c>
-      <c r="BW17">
-        <v>7.8</v>
-      </c>
-      <c r="BX17">
-        <v>1000</v>
-      </c>
-      <c r="BY17">
-        <v>8.4</v>
-      </c>
-      <c r="BZ17">
-        <v>34</v>
-      </c>
-      <c r="CA17">
-        <v>7.8</v>
-      </c>
-      <c r="CB17" t="s">
-        <v>141</v>
-      </c>
-    </row>
-    <row r="18" spans="1:80">
-      <c r="A18" t="s">
-        <v>87</v>
-      </c>
-      <c r="B18" t="s">
-        <v>91</v>
-      </c>
-      <c r="C18" t="s">
-        <v>102</v>
-      </c>
-      <c r="D18" t="s">
-        <v>119</v>
-      </c>
-      <c r="E18" t="s">
-        <v>138</v>
-      </c>
-      <c r="F18">
-        <v>2.82</v>
-      </c>
-      <c r="G18">
-        <v>2.98</v>
-      </c>
-      <c r="H18">
-        <v>2.72</v>
-      </c>
-      <c r="I18">
-        <v>2.88</v>
-      </c>
-      <c r="J18">
-        <v>3.2</v>
-      </c>
-      <c r="K18">
-        <v>3.5</v>
-      </c>
-      <c r="L18">
-        <v>1.37</v>
-      </c>
-      <c r="M18">
-        <v>1.09</v>
-      </c>
-      <c r="N18">
-        <v>3.3</v>
-      </c>
-      <c r="O18">
-        <v>1.4</v>
-      </c>
-      <c r="P18">
-        <v>1.76</v>
-      </c>
-      <c r="Q18">
-        <v>2.18</v>
-      </c>
-      <c r="R18">
-        <v>1.3</v>
-      </c>
-      <c r="S18">
-        <v>4</v>
-      </c>
-      <c r="T18">
-        <v>1.84</v>
-      </c>
-      <c r="U18">
-        <v>2.06</v>
-      </c>
-      <c r="V18">
-        <v>1.53</v>
-      </c>
-      <c r="W18">
-        <v>1.51</v>
-      </c>
-      <c r="X18">
-        <v>12</v>
-      </c>
-      <c r="Y18">
-        <v>10.5</v>
-      </c>
-      <c r="Z18">
-        <v>18.5</v>
-      </c>
-      <c r="AA18">
-        <v>55</v>
-      </c>
-      <c r="AB18">
-        <v>11</v>
-      </c>
-      <c r="AC18">
-        <v>7.8</v>
-      </c>
-      <c r="AD18">
-        <v>13</v>
-      </c>
-      <c r="AE18">
-        <v>55</v>
-      </c>
-      <c r="AF18">
-        <v>21</v>
-      </c>
-      <c r="AG18">
-        <v>14</v>
-      </c>
-      <c r="AH18">
-        <v>19.5</v>
-      </c>
-      <c r="AI18">
-        <v>60</v>
-      </c>
-      <c r="AJ18">
-        <v>55</v>
-      </c>
-      <c r="AK18">
-        <v>44</v>
-      </c>
-      <c r="AL18">
-        <v>65</v>
-      </c>
-      <c r="AM18">
-        <v>170</v>
-      </c>
-      <c r="AN18">
-        <v>65</v>
-      </c>
-      <c r="AO18">
-        <v>50</v>
-      </c>
-      <c r="AP18">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AQ18">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AR18">
-        <v>14</v>
-      </c>
-      <c r="AS18">
-        <v>32</v>
-      </c>
-      <c r="AT18">
-        <v>8</v>
-      </c>
-      <c r="AU18">
-        <v>5.7</v>
-      </c>
-      <c r="AV18">
-        <v>10</v>
-      </c>
-      <c r="AW18">
-        <v>24</v>
-      </c>
-      <c r="AX18">
-        <v>15</v>
-      </c>
-      <c r="AY18">
-        <v>10.5</v>
-      </c>
-      <c r="AZ18">
-        <v>15</v>
-      </c>
-      <c r="BA18">
-        <v>36</v>
-      </c>
-      <c r="BB18">
-        <v>34</v>
-      </c>
-      <c r="BC18">
-        <v>27</v>
-      </c>
-      <c r="BD18">
-        <v>8</v>
-      </c>
-      <c r="BE18">
-        <v>8.4</v>
-      </c>
-      <c r="BF18">
-        <v>25</v>
-      </c>
-      <c r="BG18">
-        <v>22</v>
-      </c>
-      <c r="BH18">
-        <v>1000</v>
-      </c>
-      <c r="BI18">
-        <v>1.04</v>
-      </c>
-      <c r="BJ18">
-        <v>1000</v>
-      </c>
-      <c r="BK18">
-        <v>1.04</v>
-      </c>
-      <c r="BL18">
-        <v>1000</v>
-      </c>
-      <c r="BM18">
-        <v>1.04</v>
-      </c>
-      <c r="BN18">
-        <v>1000</v>
-      </c>
-      <c r="BO18">
-        <v>1.04</v>
-      </c>
-      <c r="BP18">
-        <v>1000</v>
-      </c>
-      <c r="BQ18">
-        <v>1.04</v>
-      </c>
-      <c r="BR18">
-        <v>1000</v>
-      </c>
-      <c r="BS18">
-        <v>1.04</v>
-      </c>
-      <c r="BT18">
-        <v>1000</v>
-      </c>
-      <c r="BU18">
-        <v>1.04</v>
-      </c>
-      <c r="BV18">
-        <v>1000</v>
-      </c>
-      <c r="BW18">
-        <v>1.04</v>
-      </c>
-      <c r="BX18">
-        <v>1000</v>
-      </c>
-      <c r="BY18">
-        <v>1.04</v>
-      </c>
-      <c r="BZ18">
-        <v>1000</v>
-      </c>
-      <c r="CA18">
-        <v>1.04</v>
-      </c>
-      <c r="CB18" t="s">
-        <v>141</v>
-      </c>
-    </row>
-    <row r="19" spans="1:80">
-      <c r="A19" t="s">
-        <v>86</v>
-      </c>
-      <c r="B19" t="s">
-        <v>91</v>
-      </c>
-      <c r="C19" t="s">
-        <v>102</v>
-      </c>
-      <c r="D19" t="s">
-        <v>120</v>
-      </c>
-      <c r="E19" t="s">
-        <v>139</v>
-      </c>
-      <c r="F19">
-        <v>1.65</v>
-      </c>
-      <c r="G19">
-        <v>1.81</v>
-      </c>
-      <c r="H19">
-        <v>5.3</v>
-      </c>
-      <c r="I19">
-        <v>7.6</v>
-      </c>
-      <c r="J19">
-        <v>3.5</v>
-      </c>
-      <c r="K19">
-        <v>4.1</v>
-      </c>
-      <c r="L19">
-        <v>1.33</v>
-      </c>
-      <c r="M19">
-        <v>1.09</v>
-      </c>
-      <c r="N19">
-        <v>2.98</v>
-      </c>
-      <c r="O19">
-        <v>1.36</v>
-      </c>
-      <c r="P19">
-        <v>1.67</v>
-      </c>
-      <c r="Q19">
-        <v>2.08</v>
-      </c>
-      <c r="R19">
-        <v>1.25</v>
-      </c>
-      <c r="S19">
-        <v>3.9</v>
-      </c>
-      <c r="T19">
-        <v>2.08</v>
-      </c>
-      <c r="U19">
-        <v>1.74</v>
-      </c>
-      <c r="V19">
-        <v>1.15</v>
-      </c>
-      <c r="W19">
-        <v>2.22</v>
-      </c>
-      <c r="X19">
-        <v>13</v>
-      </c>
-      <c r="Y19">
-        <v>20</v>
-      </c>
-      <c r="Z19">
-        <v>60</v>
-      </c>
-      <c r="AA19">
-        <v>250</v>
-      </c>
-      <c r="AB19">
-        <v>7.8</v>
-      </c>
-      <c r="AC19">
-        <v>9.6</v>
-      </c>
-      <c r="AD19">
-        <v>30</v>
-      </c>
-      <c r="AE19">
-        <v>140</v>
-      </c>
-      <c r="AF19">
-        <v>11</v>
-      </c>
-      <c r="AG19">
-        <v>12</v>
-      </c>
-      <c r="AH19">
-        <v>30</v>
-      </c>
-      <c r="AI19">
-        <v>140</v>
-      </c>
-      <c r="AJ19">
-        <v>21</v>
-      </c>
-      <c r="AK19">
-        <v>25</v>
-      </c>
-      <c r="AL19">
-        <v>60</v>
-      </c>
-      <c r="AM19">
-        <v>220</v>
-      </c>
-      <c r="AN19">
-        <v>17</v>
-      </c>
-      <c r="AO19">
-        <v>220</v>
-      </c>
-      <c r="AP19">
-        <v>8.6</v>
-      </c>
-      <c r="AQ19">
-        <v>13</v>
-      </c>
-      <c r="AR19">
-        <v>4.7</v>
-      </c>
-      <c r="AS19">
-        <v>5</v>
-      </c>
-      <c r="AT19">
-        <v>5.3</v>
-      </c>
-      <c r="AU19">
-        <v>7.2</v>
-      </c>
-      <c r="AV19">
-        <v>19</v>
-      </c>
-      <c r="AW19">
-        <v>5</v>
-      </c>
-      <c r="AX19">
-        <v>7.2</v>
-      </c>
-      <c r="AY19">
-        <v>8</v>
-      </c>
-      <c r="AZ19">
-        <v>19.5</v>
-      </c>
-      <c r="BA19">
-        <v>5</v>
-      </c>
-      <c r="BB19">
-        <v>13.5</v>
-      </c>
-      <c r="BC19">
-        <v>16</v>
-      </c>
-      <c r="BD19">
-        <v>4.7</v>
-      </c>
-      <c r="BE19">
-        <v>5</v>
-      </c>
-      <c r="BF19">
-        <v>11</v>
-      </c>
-      <c r="BG19">
-        <v>5</v>
-      </c>
-      <c r="BH19">
-        <v>1000</v>
-      </c>
-      <c r="BI19">
-        <v>1.83</v>
-      </c>
-      <c r="BJ19">
-        <v>16</v>
-      </c>
-      <c r="BK19">
-        <v>1.64</v>
-      </c>
-      <c r="BL19">
-        <v>1000</v>
-      </c>
-      <c r="BM19">
-        <v>1.83</v>
-      </c>
-      <c r="BN19">
-        <v>5.3</v>
-      </c>
-      <c r="BO19">
-        <v>2.84</v>
-      </c>
-      <c r="BP19">
-        <v>17</v>
-      </c>
-      <c r="BQ19">
-        <v>1.65</v>
-      </c>
-      <c r="BR19">
-        <v>46</v>
-      </c>
-      <c r="BS19">
-        <v>1.76</v>
-      </c>
-      <c r="BT19">
-        <v>13</v>
-      </c>
-      <c r="BU19">
-        <v>1.61</v>
-      </c>
-      <c r="BV19">
-        <v>1000</v>
-      </c>
-      <c r="BW19">
-        <v>1.8</v>
-      </c>
-      <c r="BX19">
-        <v>1000</v>
-      </c>
-      <c r="BY19">
-        <v>1.8</v>
-      </c>
-      <c r="BZ19">
-        <v>0</v>
-      </c>
-      <c r="CA19">
-        <v>0</v>
-      </c>
-      <c r="CB19" t="s">
-        <v>141</v>
-      </c>
-    </row>
-    <row r="20" spans="1:80">
-      <c r="A20" t="s">
-        <v>86</v>
-      </c>
-      <c r="B20" t="s">
-        <v>91</v>
-      </c>
-      <c r="C20" t="s">
-        <v>102</v>
-      </c>
-      <c r="D20" t="s">
         <v>121</v>
-      </c>
-      <c r="E20" t="s">
-        <v>140</v>
-      </c>
-      <c r="F20">
-        <v>2.66</v>
-      </c>
-      <c r="G20">
-        <v>3.05</v>
-      </c>
-      <c r="H20">
-        <v>2.8</v>
-      </c>
-      <c r="I20">
-        <v>3.3</v>
-      </c>
-      <c r="J20">
-        <v>2.72</v>
-      </c>
-      <c r="K20">
-        <v>3.3</v>
-      </c>
-      <c r="L20">
-        <v>1.48</v>
-      </c>
-      <c r="M20">
-        <v>1.1</v>
-      </c>
-      <c r="N20">
-        <v>2.62</v>
-      </c>
-      <c r="O20">
-        <v>1.52</v>
-      </c>
-      <c r="P20">
-        <v>1.54</v>
-      </c>
-      <c r="Q20">
-        <v>2.44</v>
-      </c>
-      <c r="R20">
-        <v>1.16</v>
-      </c>
-      <c r="S20">
-        <v>5.7</v>
-      </c>
-      <c r="T20">
-        <v>1.78</v>
-      </c>
-      <c r="U20">
-        <v>1.66</v>
-      </c>
-      <c r="V20">
-        <v>1.44</v>
-      </c>
-      <c r="W20">
-        <v>1.49</v>
-      </c>
-      <c r="X20">
-        <v>9.6</v>
-      </c>
-      <c r="Y20">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="Z20">
-        <v>22</v>
-      </c>
-      <c r="AA20">
-        <v>75</v>
-      </c>
-      <c r="AB20">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AC20">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AD20">
-        <v>970</v>
-      </c>
-      <c r="AE20">
-        <v>65</v>
-      </c>
-      <c r="AF20">
-        <v>19</v>
-      </c>
-      <c r="AG20">
-        <v>16.5</v>
-      </c>
-      <c r="AH20">
-        <v>30</v>
-      </c>
-      <c r="AI20">
-        <v>100</v>
-      </c>
-      <c r="AJ20">
-        <v>60</v>
-      </c>
-      <c r="AK20">
-        <v>60</v>
-      </c>
-      <c r="AL20">
-        <v>95</v>
-      </c>
-      <c r="AM20">
-        <v>230</v>
-      </c>
-      <c r="AN20">
-        <v>85</v>
-      </c>
-      <c r="AO20">
-        <v>90</v>
-      </c>
-      <c r="AP20">
-        <v>6.6</v>
-      </c>
-      <c r="AQ20">
-        <v>6.8</v>
-      </c>
-      <c r="AR20">
-        <v>14.5</v>
-      </c>
-      <c r="AS20">
-        <v>44</v>
-      </c>
-      <c r="AT20">
-        <v>6.2</v>
-      </c>
-      <c r="AU20">
-        <v>5.4</v>
-      </c>
-      <c r="AV20">
-        <v>11.5</v>
-      </c>
-      <c r="AW20">
-        <v>34</v>
-      </c>
-      <c r="AX20">
-        <v>13</v>
-      </c>
-      <c r="AY20">
-        <v>10.5</v>
-      </c>
-      <c r="AZ20">
-        <v>19</v>
-      </c>
-      <c r="BA20">
-        <v>55</v>
-      </c>
-      <c r="BB20">
-        <v>34</v>
-      </c>
-      <c r="BC20">
-        <v>30</v>
-      </c>
-      <c r="BD20">
-        <v>46</v>
-      </c>
-      <c r="BE20">
-        <v>4.7</v>
-      </c>
-      <c r="BF20">
-        <v>44</v>
-      </c>
-      <c r="BG20">
-        <v>46</v>
-      </c>
-      <c r="BH20">
-        <v>1000</v>
-      </c>
-      <c r="BI20">
-        <v>1.04</v>
-      </c>
-      <c r="BJ20">
-        <v>1000</v>
-      </c>
-      <c r="BK20">
-        <v>1.04</v>
-      </c>
-      <c r="BL20">
-        <v>1000</v>
-      </c>
-      <c r="BM20">
-        <v>1.04</v>
-      </c>
-      <c r="BN20">
-        <v>1000</v>
-      </c>
-      <c r="BO20">
-        <v>1.04</v>
-      </c>
-      <c r="BP20">
-        <v>1000</v>
-      </c>
-      <c r="BQ20">
-        <v>1.04</v>
-      </c>
-      <c r="BR20">
-        <v>1000</v>
-      </c>
-      <c r="BS20">
-        <v>1.04</v>
-      </c>
-      <c r="BT20">
-        <v>1000</v>
-      </c>
-      <c r="BU20">
-        <v>1.04</v>
-      </c>
-      <c r="BV20">
-        <v>1000</v>
-      </c>
-      <c r="BW20">
-        <v>1.04</v>
-      </c>
-      <c r="BX20">
-        <v>1000</v>
-      </c>
-      <c r="BY20">
-        <v>1.04</v>
-      </c>
-      <c r="BZ20">
-        <v>1000</v>
-      </c>
-      <c r="CA20">
-        <v>1.04</v>
-      </c>
-      <c r="CB20" t="s">
-        <v>141</v>
       </c>
     </row>
   </sheetData>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-08-11.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-08-11.xlsx
@@ -379,7 +379,7 @@
     <t>Union Espanola</t>
   </si>
   <si>
-    <t>2026-08-10 18:57:53</t>
+    <t>2026-08-10 21:05:03</t>
   </si>
 </sst>
 </file>
@@ -973,226 +973,226 @@
         <v>109</v>
       </c>
       <c r="F2">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="G2">
-        <v>16</v>
+        <v>17.5</v>
       </c>
       <c r="H2">
         <v>1.29</v>
       </c>
       <c r="I2">
-        <v>1.35</v>
+        <v>1.32</v>
       </c>
       <c r="J2">
-        <v>5.3</v>
+        <v>5.8</v>
       </c>
       <c r="K2">
         <v>6.4</v>
       </c>
       <c r="L2">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="M2">
         <v>1.05</v>
       </c>
       <c r="N2">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="O2">
-        <v>1.24</v>
+        <v>1.26</v>
       </c>
       <c r="P2">
-        <v>2.28</v>
+        <v>2.2</v>
       </c>
       <c r="Q2">
-        <v>1.7</v>
+        <v>1.8</v>
       </c>
       <c r="R2">
-        <v>1.53</v>
+        <v>1.45</v>
       </c>
       <c r="S2">
-        <v>2.74</v>
+        <v>3.05</v>
       </c>
       <c r="T2">
-        <v>2.16</v>
+        <v>2.32</v>
       </c>
       <c r="U2">
-        <v>1.73</v>
+        <v>1.67</v>
       </c>
       <c r="V2">
-        <v>3.85</v>
+        <v>4.1</v>
       </c>
       <c r="W2">
         <v>1.06</v>
       </c>
       <c r="X2">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="Y2">
-        <v>8.800000000000001</v>
+        <v>8</v>
       </c>
       <c r="Z2">
-        <v>8.199999999999999</v>
+        <v>7.4</v>
       </c>
       <c r="AA2">
-        <v>12.5</v>
+        <v>10.5</v>
       </c>
       <c r="AB2">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="AC2">
         <v>14.5</v>
       </c>
       <c r="AD2">
-        <v>11.5</v>
+        <v>13</v>
       </c>
       <c r="AE2">
         <v>15.5</v>
       </c>
       <c r="AF2">
-        <v>160</v>
+        <v>180</v>
       </c>
       <c r="AG2">
-        <v>60</v>
+        <v>70</v>
       </c>
       <c r="AH2">
-        <v>38</v>
+        <v>48</v>
       </c>
       <c r="AI2">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="AJ2">
         <v>1000</v>
       </c>
       <c r="AK2">
-        <v>290</v>
+        <v>390</v>
       </c>
       <c r="AL2">
-        <v>220</v>
+        <v>280</v>
       </c>
       <c r="AM2">
-        <v>220</v>
+        <v>330</v>
       </c>
       <c r="AN2">
-        <v>420</v>
+        <v>610</v>
       </c>
       <c r="AO2">
-        <v>5.4</v>
+        <v>5.9</v>
       </c>
       <c r="AP2">
-        <v>5.7</v>
+        <v>12</v>
       </c>
       <c r="AQ2">
-        <v>4.2</v>
+        <v>7.2</v>
       </c>
       <c r="AR2">
-        <v>4</v>
+        <v>6.6</v>
       </c>
       <c r="AS2">
-        <v>4.8</v>
+        <v>8.6</v>
       </c>
       <c r="AT2">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="AU2">
-        <v>5</v>
+        <v>9.6</v>
       </c>
       <c r="AV2">
-        <v>4.7</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AW2">
-        <v>5.1</v>
+        <v>12</v>
       </c>
       <c r="AX2">
+        <v>7.4</v>
+      </c>
+      <c r="AY2">
         <v>7.2</v>
       </c>
-      <c r="AY2">
-        <v>6.8</v>
-      </c>
       <c r="AZ2">
-        <v>6.4</v>
+        <v>7.4</v>
       </c>
       <c r="BA2">
-        <v>6.4</v>
+        <v>8</v>
       </c>
       <c r="BB2">
+        <v>7.8</v>
+      </c>
+      <c r="BC2">
         <v>7.6</v>
       </c>
-      <c r="BC2">
-        <v>7.4</v>
-      </c>
       <c r="BD2">
-        <v>8.4</v>
+        <v>7.6</v>
       </c>
       <c r="BE2">
-        <v>8.4</v>
+        <v>100</v>
       </c>
       <c r="BF2">
         <v>7.6</v>
       </c>
       <c r="BG2">
-        <v>3.8</v>
+        <v>4.9</v>
       </c>
       <c r="BH2">
-        <v>4.5</v>
+        <v>1000</v>
       </c>
       <c r="BI2">
-        <v>2.44</v>
+        <v>1.04</v>
       </c>
       <c r="BJ2">
-        <v>15.5</v>
+        <v>1000</v>
       </c>
       <c r="BK2">
-        <v>3.95</v>
+        <v>1.04</v>
       </c>
       <c r="BL2">
         <v>1000</v>
       </c>
       <c r="BM2">
-        <v>5.2</v>
+        <v>130</v>
       </c>
       <c r="BN2">
-        <v>17.5</v>
+        <v>1000</v>
       </c>
       <c r="BO2">
-        <v>4.1</v>
+        <v>1.04</v>
       </c>
       <c r="BP2">
         <v>1000</v>
       </c>
       <c r="BQ2">
-        <v>5.1</v>
+        <v>1.04</v>
       </c>
       <c r="BR2">
         <v>1000</v>
       </c>
       <c r="BS2">
-        <v>5.1</v>
+        <v>1.04</v>
       </c>
       <c r="BT2">
-        <v>4.2</v>
+        <v>1000</v>
       </c>
       <c r="BU2">
-        <v>2.94</v>
+        <v>1.04</v>
       </c>
       <c r="BV2">
-        <v>9</v>
+        <v>1000</v>
       </c>
       <c r="BW2">
-        <v>3.35</v>
+        <v>1.04</v>
       </c>
       <c r="BX2">
-        <v>30</v>
+        <v>1000</v>
       </c>
       <c r="BY2">
-        <v>4.5</v>
+        <v>1.04</v>
       </c>
       <c r="BZ2">
-        <v>15</v>
+        <v>1000</v>
       </c>
       <c r="CA2">
-        <v>3.95</v>
+        <v>1.04</v>
       </c>
       <c r="CB2" t="s">
         <v>121</v>
@@ -1215,226 +1215,226 @@
         <v>110</v>
       </c>
       <c r="F3">
-        <v>2.46</v>
+        <v>2.52</v>
       </c>
       <c r="G3">
-        <v>2.5</v>
+        <v>2.64</v>
       </c>
       <c r="H3">
-        <v>3.2</v>
+        <v>3.15</v>
       </c>
       <c r="I3">
         <v>3.3</v>
       </c>
       <c r="J3">
+        <v>3.25</v>
+      </c>
+      <c r="K3">
         <v>3.4</v>
       </c>
-      <c r="K3">
-        <v>3.5</v>
-      </c>
       <c r="L3">
-        <v>1.47</v>
+        <v>1.54</v>
       </c>
       <c r="M3">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="N3">
-        <v>3.45</v>
+        <v>3.1</v>
       </c>
       <c r="O3">
-        <v>1.39</v>
+        <v>1.43</v>
       </c>
       <c r="P3">
-        <v>1.82</v>
+        <v>1.69</v>
       </c>
       <c r="Q3">
-        <v>2.18</v>
+        <v>2.4</v>
       </c>
       <c r="R3">
-        <v>1.31</v>
+        <v>1.26</v>
       </c>
       <c r="S3">
-        <v>4</v>
+        <v>4.4</v>
       </c>
       <c r="T3">
-        <v>1.87</v>
+        <v>1.95</v>
       </c>
       <c r="U3">
-        <v>2.08</v>
+        <v>1.93</v>
       </c>
       <c r="V3">
         <v>1.43</v>
       </c>
       <c r="W3">
-        <v>1.66</v>
+        <v>1.6</v>
       </c>
       <c r="X3">
-        <v>12.5</v>
+        <v>11</v>
       </c>
       <c r="Y3">
-        <v>11.5</v>
+        <v>10.5</v>
       </c>
       <c r="Z3">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="AA3">
-        <v>60</v>
+        <v>75</v>
       </c>
       <c r="AB3">
-        <v>9.6</v>
+        <v>9</v>
       </c>
       <c r="AC3">
-        <v>7.8</v>
+        <v>7.4</v>
       </c>
       <c r="AD3">
         <v>14</v>
       </c>
       <c r="AE3">
-        <v>42</v>
+        <v>55</v>
       </c>
       <c r="AF3">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="AG3">
-        <v>11.5</v>
+        <v>12.5</v>
       </c>
       <c r="AH3">
-        <v>19.5</v>
+        <v>24</v>
       </c>
       <c r="AI3">
+        <v>75</v>
+      </c>
+      <c r="AJ3">
+        <v>48</v>
+      </c>
+      <c r="AK3">
+        <v>40</v>
+      </c>
+      <c r="AL3">
+        <v>65</v>
+      </c>
+      <c r="AM3">
+        <v>170</v>
+      </c>
+      <c r="AN3">
+        <v>40</v>
+      </c>
+      <c r="AO3">
         <v>55</v>
       </c>
-      <c r="AJ3">
-        <v>36</v>
-      </c>
-      <c r="AK3">
-        <v>29</v>
-      </c>
-      <c r="AL3">
-        <v>44</v>
-      </c>
-      <c r="AM3">
-        <v>120</v>
-      </c>
-      <c r="AN3">
-        <v>25</v>
-      </c>
-      <c r="AO3">
-        <v>46</v>
-      </c>
       <c r="AP3">
-        <v>11</v>
+        <v>9.6</v>
       </c>
       <c r="AQ3">
-        <v>10.5</v>
+        <v>9</v>
       </c>
       <c r="AR3">
         <v>19</v>
       </c>
       <c r="AS3">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="AT3">
-        <v>8.800000000000001</v>
+        <v>8</v>
       </c>
       <c r="AU3">
-        <v>7</v>
+        <v>6.6</v>
       </c>
       <c r="AV3">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AW3">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="AX3">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="AY3">
         <v>10.5</v>
       </c>
       <c r="AZ3">
-        <v>17</v>
+        <v>17.5</v>
       </c>
       <c r="BA3">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="BB3">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="BC3">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="BD3">
         <v>38</v>
       </c>
       <c r="BE3">
-        <v>85</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BF3">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="BG3">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="BH3">
-        <v>3.65</v>
+        <v>2.78</v>
       </c>
       <c r="BI3">
-        <v>2.64</v>
+        <v>2.62</v>
       </c>
       <c r="BJ3">
-        <v>9.800000000000001</v>
+        <v>11</v>
       </c>
       <c r="BK3">
-        <v>4.8</v>
+        <v>10</v>
       </c>
       <c r="BL3">
-        <v>1000</v>
+        <v>210</v>
       </c>
       <c r="BM3">
-        <v>9</v>
+        <v>130</v>
       </c>
       <c r="BN3">
         <v>5.3</v>
       </c>
       <c r="BO3">
-        <v>4.1</v>
+        <v>4.7</v>
       </c>
       <c r="BP3">
-        <v>19</v>
+        <v>28</v>
       </c>
       <c r="BQ3">
+        <v>20</v>
+      </c>
+      <c r="BR3">
+        <v>50</v>
+      </c>
+      <c r="BS3">
+        <v>36</v>
+      </c>
+      <c r="BT3">
         <v>6.2</v>
       </c>
-      <c r="BR3">
+      <c r="BU3">
+        <v>5.5</v>
+      </c>
+      <c r="BV3">
+        <v>36</v>
+      </c>
+      <c r="BW3">
+        <v>25</v>
+      </c>
+      <c r="BX3">
+        <v>60</v>
+      </c>
+      <c r="BY3">
         <v>42</v>
       </c>
-      <c r="BS3">
-        <v>7.6</v>
-      </c>
-      <c r="BT3">
-        <v>6.4</v>
-      </c>
-      <c r="BU3">
-        <v>4.8</v>
-      </c>
-      <c r="BV3">
-        <v>27</v>
-      </c>
-      <c r="BW3">
-        <v>7</v>
-      </c>
-      <c r="BX3">
+      <c r="BZ3">
         <v>50</v>
       </c>
-      <c r="BY3">
-        <v>7.8</v>
-      </c>
-      <c r="BZ3">
-        <v>32</v>
-      </c>
       <c r="CA3">
-        <v>7.4</v>
+        <v>36</v>
       </c>
       <c r="CB3" t="s">
         <v>121</v>
@@ -1457,226 +1457,226 @@
         <v>111</v>
       </c>
       <c r="F4">
-        <v>1.71</v>
+        <v>1.72</v>
       </c>
       <c r="G4">
-        <v>1.75</v>
+        <v>1.77</v>
       </c>
       <c r="H4">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="I4">
         <v>6.6</v>
       </c>
       <c r="J4">
-        <v>3.7</v>
+        <v>3.6</v>
       </c>
       <c r="K4">
-        <v>3.9</v>
+        <v>3.8</v>
       </c>
       <c r="L4">
+        <v>1.47</v>
+      </c>
+      <c r="M4">
+        <v>1.11</v>
+      </c>
+      <c r="N4">
+        <v>2.92</v>
+      </c>
+      <c r="O4">
         <v>1.48</v>
       </c>
-      <c r="M4">
-        <v>1.1</v>
-      </c>
-      <c r="N4">
-        <v>3.1</v>
-      </c>
-      <c r="O4">
-        <v>1.44</v>
-      </c>
       <c r="P4">
+        <v>1.6</v>
+      </c>
+      <c r="Q4">
+        <v>2.56</v>
+      </c>
+      <c r="R4">
+        <v>1.21</v>
+      </c>
+      <c r="S4">
+        <v>5.3</v>
+      </c>
+      <c r="T4">
+        <v>2.2</v>
+      </c>
+      <c r="U4">
         <v>1.71</v>
       </c>
-      <c r="Q4">
-        <v>2.32</v>
-      </c>
-      <c r="R4">
-        <v>1.26</v>
-      </c>
-      <c r="S4">
-        <v>4.5</v>
-      </c>
-      <c r="T4">
-        <v>2.26</v>
-      </c>
-      <c r="U4">
-        <v>1.74</v>
-      </c>
       <c r="V4">
-        <v>1.17</v>
+        <v>1.2</v>
       </c>
       <c r="W4">
-        <v>2.32</v>
+        <v>2.22</v>
       </c>
       <c r="X4">
-        <v>11</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="Y4">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="Z4">
-        <v>980</v>
+        <v>55</v>
       </c>
       <c r="AA4">
-        <v>200</v>
+        <v>240</v>
       </c>
       <c r="AB4">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="AC4">
-        <v>8.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AD4">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="AE4">
-        <v>120</v>
+        <v>140</v>
       </c>
       <c r="AF4">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AG4">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AH4">
-        <v>27</v>
+        <v>38</v>
       </c>
       <c r="AI4">
-        <v>140</v>
+        <v>160</v>
       </c>
       <c r="AJ4">
-        <v>17.5</v>
+        <v>21</v>
       </c>
       <c r="AK4">
-        <v>22</v>
+        <v>29</v>
       </c>
       <c r="AL4">
-        <v>55</v>
+        <v>75</v>
       </c>
       <c r="AM4">
-        <v>220</v>
+        <v>310</v>
       </c>
       <c r="AN4">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="AO4">
-        <v>190</v>
+        <v>270</v>
       </c>
       <c r="AP4">
-        <v>9.800000000000001</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AQ4">
-        <v>16.5</v>
+        <v>13.5</v>
       </c>
       <c r="AR4">
         <v>32</v>
       </c>
       <c r="AS4">
+        <v>7.6</v>
+      </c>
+      <c r="AT4">
+        <v>5.9</v>
+      </c>
+      <c r="AU4">
+        <v>7.2</v>
+      </c>
+      <c r="AV4">
+        <v>21</v>
+      </c>
+      <c r="AW4">
+        <v>80</v>
+      </c>
+      <c r="AX4">
+        <v>7.6</v>
+      </c>
+      <c r="AY4">
+        <v>9.6</v>
+      </c>
+      <c r="AZ4">
+        <v>23</v>
+      </c>
+      <c r="BA4">
+        <v>100</v>
+      </c>
+      <c r="BB4">
         <v>15</v>
       </c>
-      <c r="AT4">
-        <v>6.2</v>
-      </c>
-      <c r="AU4">
-        <v>7.8</v>
-      </c>
-      <c r="AV4">
-        <v>22</v>
-      </c>
-      <c r="AW4">
-        <v>55</v>
-      </c>
-      <c r="AX4">
-        <v>7.8</v>
-      </c>
-      <c r="AY4">
-        <v>9.4</v>
-      </c>
-      <c r="AZ4">
-        <v>24</v>
-      </c>
-      <c r="BA4">
-        <v>55</v>
-      </c>
-      <c r="BB4">
-        <v>15.5</v>
-      </c>
       <c r="BC4">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="BD4">
         <v>44</v>
       </c>
       <c r="BE4">
-        <v>14</v>
+        <v>7.6</v>
       </c>
       <c r="BF4">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="BG4">
-        <v>90</v>
+        <v>7.6</v>
       </c>
       <c r="BH4">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="BI4">
         <v>2.84</v>
       </c>
       <c r="BJ4">
-        <v>12.5</v>
+        <v>950</v>
       </c>
       <c r="BK4">
+        <v>11.5</v>
+      </c>
+      <c r="BL4">
+        <v>940</v>
+      </c>
+      <c r="BM4">
+        <v>6.6</v>
+      </c>
+      <c r="BN4">
+        <v>3.7</v>
+      </c>
+      <c r="BO4">
+        <v>3.4</v>
+      </c>
+      <c r="BP4">
+        <v>12</v>
+      </c>
+      <c r="BQ4">
+        <v>9.4</v>
+      </c>
+      <c r="BR4">
+        <v>860</v>
+      </c>
+      <c r="BS4">
+        <v>25</v>
+      </c>
+      <c r="BT4">
+        <v>10</v>
+      </c>
+      <c r="BU4">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="BV4">
+        <v>1000</v>
+      </c>
+      <c r="BW4">
+        <v>10.5</v>
+      </c>
+      <c r="BX4">
+        <v>920</v>
+      </c>
+      <c r="BY4">
+        <v>6.6</v>
+      </c>
+      <c r="BZ4">
+        <v>960</v>
+      </c>
+      <c r="CA4">
         <v>6.8</v>
-      </c>
-      <c r="BL4">
-        <v>1000</v>
-      </c>
-      <c r="BM4">
-        <v>14</v>
-      </c>
-      <c r="BN4">
-        <v>3.95</v>
-      </c>
-      <c r="BO4">
-        <v>3.55</v>
-      </c>
-      <c r="BP4">
-        <v>12.5</v>
-      </c>
-      <c r="BQ4">
-        <v>6.8</v>
-      </c>
-      <c r="BR4">
-        <v>1000</v>
-      </c>
-      <c r="BS4">
-        <v>10.5</v>
-      </c>
-      <c r="BT4">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="BU4">
-        <v>6.2</v>
-      </c>
-      <c r="BV4">
-        <v>1000</v>
-      </c>
-      <c r="BW4">
-        <v>12</v>
-      </c>
-      <c r="BX4">
-        <v>85</v>
-      </c>
-      <c r="BY4">
-        <v>12.5</v>
-      </c>
-      <c r="BZ4">
-        <v>29</v>
-      </c>
-      <c r="CA4">
-        <v>10</v>
       </c>
       <c r="CB4" t="s">
         <v>121</v>
@@ -1699,223 +1699,223 @@
         <v>112</v>
       </c>
       <c r="F5">
-        <v>1.6</v>
+        <v>1.72</v>
       </c>
       <c r="G5">
-        <v>1.62</v>
+        <v>1.75</v>
       </c>
       <c r="H5">
-        <v>7.2</v>
+        <v>6.2</v>
       </c>
       <c r="I5">
-        <v>7.8</v>
+        <v>6.4</v>
       </c>
       <c r="J5">
-        <v>4</v>
+        <v>3.7</v>
       </c>
       <c r="K5">
-        <v>4.2</v>
+        <v>3.85</v>
       </c>
       <c r="L5">
+        <v>1.52</v>
+      </c>
+      <c r="M5">
+        <v>1.1</v>
+      </c>
+      <c r="N5">
+        <v>3</v>
+      </c>
+      <c r="O5">
         <v>1.47</v>
       </c>
-      <c r="M5">
-        <v>1.09</v>
-      </c>
-      <c r="N5">
-        <v>3.35</v>
-      </c>
-      <c r="O5">
-        <v>1.4</v>
-      </c>
       <c r="P5">
-        <v>1.81</v>
+        <v>1.71</v>
       </c>
       <c r="Q5">
-        <v>2.2</v>
+        <v>2.36</v>
       </c>
       <c r="R5">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="S5">
-        <v>4.2</v>
+        <v>4.8</v>
       </c>
       <c r="T5">
-        <v>2.26</v>
+        <v>2.24</v>
       </c>
       <c r="U5">
-        <v>1.76</v>
+        <v>1.77</v>
       </c>
       <c r="V5">
-        <v>1.15</v>
+        <v>1.18</v>
       </c>
       <c r="W5">
-        <v>2.6</v>
+        <v>2.34</v>
       </c>
       <c r="X5">
-        <v>12</v>
+        <v>10.5</v>
       </c>
       <c r="Y5">
-        <v>19</v>
+        <v>15.5</v>
       </c>
       <c r="Z5">
-        <v>65</v>
+        <v>48</v>
       </c>
       <c r="AA5">
-        <v>280</v>
+        <v>210</v>
       </c>
       <c r="AB5">
-        <v>6.8</v>
+        <v>6.2</v>
       </c>
       <c r="AC5">
-        <v>9</v>
+        <v>8.4</v>
       </c>
       <c r="AD5">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="AE5">
-        <v>150</v>
+        <v>120</v>
       </c>
       <c r="AF5">
-        <v>8.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="AG5">
         <v>10.5</v>
       </c>
       <c r="AH5">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="AI5">
-        <v>140</v>
+        <v>120</v>
       </c>
       <c r="AJ5">
-        <v>14.5</v>
+        <v>18</v>
       </c>
       <c r="AK5">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="AL5">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="AM5">
         <v>210</v>
       </c>
       <c r="AN5">
+        <v>15.5</v>
+      </c>
+      <c r="AO5">
+        <v>190</v>
+      </c>
+      <c r="AP5">
+        <v>10</v>
+      </c>
+      <c r="AQ5">
+        <v>14.5</v>
+      </c>
+      <c r="AR5">
+        <v>42</v>
+      </c>
+      <c r="AS5">
+        <v>90</v>
+      </c>
+      <c r="AT5">
+        <v>5.9</v>
+      </c>
+      <c r="AU5">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AV5">
+        <v>22</v>
+      </c>
+      <c r="AW5">
+        <v>95</v>
+      </c>
+      <c r="AX5">
+        <v>8</v>
+      </c>
+      <c r="AY5">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AZ5">
+        <v>24</v>
+      </c>
+      <c r="BA5">
+        <v>100</v>
+      </c>
+      <c r="BB5">
+        <v>16.5</v>
+      </c>
+      <c r="BC5">
+        <v>20</v>
+      </c>
+      <c r="BD5">
+        <v>44</v>
+      </c>
+      <c r="BE5">
+        <v>140</v>
+      </c>
+      <c r="BF5">
+        <v>14.5</v>
+      </c>
+      <c r="BG5">
+        <v>160</v>
+      </c>
+      <c r="BH5">
+        <v>2.9</v>
+      </c>
+      <c r="BI5">
+        <v>2.74</v>
+      </c>
+      <c r="BJ5">
+        <v>12</v>
+      </c>
+      <c r="BK5">
+        <v>10.5</v>
+      </c>
+      <c r="BL5">
+        <v>230</v>
+      </c>
+      <c r="BM5">
+        <v>160</v>
+      </c>
+      <c r="BN5">
+        <v>3.95</v>
+      </c>
+      <c r="BO5">
+        <v>3.75</v>
+      </c>
+      <c r="BP5">
+        <v>12.5</v>
+      </c>
+      <c r="BQ5">
         <v>11.5</v>
       </c>
-      <c r="AO5">
-        <v>240</v>
-      </c>
-      <c r="AP5">
-        <v>11</v>
-      </c>
-      <c r="AQ5">
-        <v>17</v>
-      </c>
-      <c r="AR5">
-        <v>50</v>
-      </c>
-      <c r="AS5">
-        <v>48</v>
-      </c>
-      <c r="AT5">
-        <v>6.6</v>
-      </c>
-      <c r="AU5">
-        <v>8.4</v>
-      </c>
-      <c r="AV5">
-        <v>25</v>
-      </c>
-      <c r="AW5">
-        <v>85</v>
-      </c>
-      <c r="AX5">
-        <v>7.6</v>
-      </c>
-      <c r="AY5">
-        <v>9.4</v>
-      </c>
-      <c r="AZ5">
-        <v>25</v>
-      </c>
-      <c r="BA5">
+      <c r="BR5">
+        <v>36</v>
+      </c>
+      <c r="BS5">
+        <v>15.5</v>
+      </c>
+      <c r="BT5">
+        <v>9</v>
+      </c>
+      <c r="BU5">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BV5">
+        <v>65</v>
+      </c>
+      <c r="BW5">
+        <v>19.5</v>
+      </c>
+      <c r="BX5">
         <v>80</v>
       </c>
-      <c r="BB5">
-        <v>12.5</v>
-      </c>
-      <c r="BC5">
-        <v>17</v>
-      </c>
-      <c r="BD5">
-        <v>42</v>
-      </c>
-      <c r="BE5">
-        <v>48</v>
-      </c>
-      <c r="BF5">
-        <v>10</v>
-      </c>
-      <c r="BG5">
-        <v>110</v>
-      </c>
-      <c r="BH5">
-        <v>3.15</v>
-      </c>
-      <c r="BI5">
-        <v>2.96</v>
-      </c>
-      <c r="BJ5">
-        <v>13</v>
-      </c>
-      <c r="BK5">
-        <v>10</v>
-      </c>
-      <c r="BL5">
-        <v>210</v>
-      </c>
-      <c r="BM5">
-        <v>15.5</v>
-      </c>
-      <c r="BN5">
-        <v>3.8</v>
-      </c>
-      <c r="BO5">
-        <v>3.55</v>
-      </c>
-      <c r="BP5">
-        <v>11</v>
-      </c>
-      <c r="BQ5">
-        <v>9</v>
-      </c>
-      <c r="BR5">
+      <c r="BY5">
+        <v>20</v>
+      </c>
+      <c r="BZ5">
         <v>32</v>
-      </c>
-      <c r="BS5">
-        <v>11</v>
-      </c>
-      <c r="BT5">
-        <v>11</v>
-      </c>
-      <c r="BU5">
-        <v>9</v>
-      </c>
-      <c r="BV5">
-        <v>80</v>
-      </c>
-      <c r="BW5">
-        <v>13.5</v>
-      </c>
-      <c r="BX5">
-        <v>90</v>
-      </c>
-      <c r="BY5">
-        <v>14</v>
-      </c>
-      <c r="BZ5">
-        <v>24</v>
       </c>
       <c r="CA5">
         <v>14.5</v>
@@ -1941,22 +1941,22 @@
         <v>113</v>
       </c>
       <c r="F6">
-        <v>2.08</v>
+        <v>2.42</v>
       </c>
       <c r="G6">
-        <v>2.2</v>
+        <v>2.48</v>
       </c>
       <c r="H6">
-        <v>3.35</v>
+        <v>2.96</v>
       </c>
       <c r="I6">
-        <v>3.65</v>
+        <v>3.05</v>
       </c>
       <c r="J6">
+        <v>3.7</v>
+      </c>
+      <c r="K6">
         <v>3.9</v>
-      </c>
-      <c r="K6">
-        <v>4.2</v>
       </c>
       <c r="L6">
         <v>1.33</v>
@@ -1968,187 +1968,187 @@
         <v>5.2</v>
       </c>
       <c r="O6">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="P6">
-        <v>2.42</v>
+        <v>2.38</v>
       </c>
       <c r="Q6">
-        <v>1.63</v>
+        <v>1.65</v>
       </c>
       <c r="R6">
         <v>1.57</v>
       </c>
       <c r="S6">
-        <v>2.56</v>
+        <v>2.6</v>
       </c>
       <c r="T6">
-        <v>1.59</v>
+        <v>1.56</v>
       </c>
       <c r="U6">
-        <v>2.52</v>
+        <v>2.6</v>
       </c>
       <c r="V6">
-        <v>1.38</v>
+        <v>1.48</v>
       </c>
       <c r="W6">
-        <v>1.83</v>
+        <v>1.67</v>
       </c>
       <c r="X6">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="Y6">
-        <v>18.5</v>
+        <v>16.5</v>
       </c>
       <c r="Z6">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="AA6">
-        <v>500</v>
+        <v>120</v>
       </c>
       <c r="AB6">
+        <v>15</v>
+      </c>
+      <c r="AC6">
+        <v>8.6</v>
+      </c>
+      <c r="AD6">
         <v>13.5</v>
       </c>
-      <c r="AC6">
+      <c r="AE6">
+        <v>30</v>
+      </c>
+      <c r="AF6">
+        <v>19</v>
+      </c>
+      <c r="AG6">
+        <v>12.5</v>
+      </c>
+      <c r="AH6">
+        <v>14.5</v>
+      </c>
+      <c r="AI6">
+        <v>34</v>
+      </c>
+      <c r="AJ6">
+        <v>60</v>
+      </c>
+      <c r="AK6">
+        <v>32</v>
+      </c>
+      <c r="AL6">
+        <v>60</v>
+      </c>
+      <c r="AM6">
+        <v>190</v>
+      </c>
+      <c r="AN6">
+        <v>14</v>
+      </c>
+      <c r="AO6">
+        <v>21</v>
+      </c>
+      <c r="AP6">
+        <v>18</v>
+      </c>
+      <c r="AQ6">
+        <v>14</v>
+      </c>
+      <c r="AR6">
+        <v>19</v>
+      </c>
+      <c r="AS6">
+        <v>38</v>
+      </c>
+      <c r="AT6">
+        <v>13</v>
+      </c>
+      <c r="AU6">
+        <v>7.8</v>
+      </c>
+      <c r="AV6">
+        <v>12</v>
+      </c>
+      <c r="AW6">
+        <v>19</v>
+      </c>
+      <c r="AX6">
+        <v>17</v>
+      </c>
+      <c r="AY6">
         <v>9.800000000000001</v>
       </c>
-      <c r="AD6">
-        <v>15</v>
-      </c>
-      <c r="AE6">
-        <v>44</v>
-      </c>
-      <c r="AF6">
+      <c r="AZ6">
+        <v>13</v>
+      </c>
+      <c r="BA6">
+        <v>22</v>
+      </c>
+      <c r="BB6">
         <v>21</v>
       </c>
-      <c r="AG6">
+      <c r="BC6">
+        <v>20</v>
+      </c>
+      <c r="BD6">
+        <v>22</v>
+      </c>
+      <c r="BE6">
+        <v>34</v>
+      </c>
+      <c r="BF6">
         <v>12</v>
       </c>
-      <c r="AH6">
-        <v>20</v>
-      </c>
-      <c r="AI6">
-        <v>46</v>
-      </c>
-      <c r="AJ6">
-        <v>36</v>
-      </c>
-      <c r="AK6">
-        <v>25</v>
-      </c>
-      <c r="AL6">
-        <v>38</v>
-      </c>
-      <c r="AM6">
-        <v>200</v>
-      </c>
-      <c r="AN6">
-        <v>11</v>
-      </c>
-      <c r="AO6">
-        <v>32</v>
-      </c>
-      <c r="AP6">
-        <v>9</v>
-      </c>
-      <c r="AQ6">
-        <v>15</v>
-      </c>
-      <c r="AR6">
-        <v>24</v>
-      </c>
-      <c r="AS6">
-        <v>10</v>
-      </c>
-      <c r="AT6">
-        <v>11.5</v>
-      </c>
-      <c r="AU6">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AV6">
-        <v>13</v>
-      </c>
-      <c r="AW6">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AX6">
-        <v>14</v>
-      </c>
-      <c r="AY6">
-        <v>10</v>
-      </c>
-      <c r="AZ6">
-        <v>13.5</v>
-      </c>
-      <c r="BA6">
-        <v>9.6</v>
-      </c>
-      <c r="BB6">
-        <v>20</v>
-      </c>
-      <c r="BC6">
-        <v>16</v>
-      </c>
-      <c r="BD6">
-        <v>8.6</v>
-      </c>
-      <c r="BE6">
-        <v>28</v>
-      </c>
-      <c r="BF6">
-        <v>9.800000000000001</v>
-      </c>
       <c r="BG6">
-        <v>21</v>
+        <v>17.5</v>
       </c>
       <c r="BH6">
         <v>4.1</v>
       </c>
       <c r="BI6">
-        <v>3.7</v>
+        <v>3.65</v>
       </c>
       <c r="BJ6">
         <v>8.800000000000001</v>
       </c>
       <c r="BK6">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="BL6">
         <v>1000</v>
       </c>
       <c r="BM6">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="BN6">
-        <v>5.3</v>
+        <v>5.5</v>
       </c>
       <c r="BO6">
-        <v>4.7</v>
+        <v>4.9</v>
       </c>
       <c r="BP6">
-        <v>1000</v>
+        <v>16</v>
       </c>
       <c r="BQ6">
-        <v>11</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BR6">
         <v>1000</v>
       </c>
       <c r="BS6">
+        <v>10</v>
+      </c>
+      <c r="BT6">
+        <v>6.6</v>
+      </c>
+      <c r="BU6">
+        <v>5.8</v>
+      </c>
+      <c r="BV6">
+        <v>1000</v>
+      </c>
+      <c r="BW6">
         <v>9.6</v>
-      </c>
-      <c r="BT6">
-        <v>7</v>
-      </c>
-      <c r="BU6">
-        <v>5</v>
-      </c>
-      <c r="BV6">
-        <v>1000</v>
-      </c>
-      <c r="BW6">
-        <v>9.800000000000001</v>
       </c>
       <c r="BX6">
         <v>1000</v>
@@ -2189,7 +2189,7 @@
         <v>3.25</v>
       </c>
       <c r="H7">
-        <v>2.84</v>
+        <v>2.86</v>
       </c>
       <c r="I7">
         <v>3.15</v>
@@ -2204,13 +2204,13 @@
         <v>1.61</v>
       </c>
       <c r="M7">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="N7">
-        <v>2.4</v>
+        <v>2.38</v>
       </c>
       <c r="O7">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="P7">
         <v>1.45</v>
@@ -2237,7 +2237,7 @@
         <v>1.44</v>
       </c>
       <c r="X7">
-        <v>9.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="Y7">
         <v>9.6</v>
@@ -2249,7 +2249,7 @@
         <v>70</v>
       </c>
       <c r="AB7">
-        <v>9.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="AC7">
         <v>7.4</v>
@@ -2273,7 +2273,7 @@
         <v>100</v>
       </c>
       <c r="AJ7">
-        <v>65</v>
+        <v>150</v>
       </c>
       <c r="AK7">
         <v>55</v>
@@ -2285,13 +2285,13 @@
         <v>500</v>
       </c>
       <c r="AN7">
-        <v>500</v>
+        <v>210</v>
       </c>
       <c r="AO7">
         <v>70</v>
       </c>
       <c r="AP7">
-        <v>5.8</v>
+        <v>6.6</v>
       </c>
       <c r="AQ7">
         <v>7</v>
@@ -2300,10 +2300,10 @@
         <v>15</v>
       </c>
       <c r="AS7">
-        <v>4.9</v>
+        <v>20</v>
       </c>
       <c r="AT7">
-        <v>6.2</v>
+        <v>7</v>
       </c>
       <c r="AU7">
         <v>6</v>
@@ -2312,7 +2312,7 @@
         <v>12</v>
       </c>
       <c r="AW7">
-        <v>4.8</v>
+        <v>5.8</v>
       </c>
       <c r="AX7">
         <v>15.5</v>
@@ -2324,25 +2324,25 @@
         <v>20</v>
       </c>
       <c r="BA7">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="BB7">
-        <v>4.9</v>
+        <v>18</v>
       </c>
       <c r="BC7">
-        <v>4.8</v>
+        <v>5.8</v>
       </c>
       <c r="BD7">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="BE7">
-        <v>5.2</v>
+        <v>6.2</v>
       </c>
       <c r="BF7">
-        <v>4.9</v>
+        <v>11.5</v>
       </c>
       <c r="BG7">
-        <v>4.9</v>
+        <v>5.9</v>
       </c>
       <c r="BH7">
         <v>2.64</v>
@@ -2369,10 +2369,10 @@
         <v>4.4</v>
       </c>
       <c r="BP7">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="BQ7">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="BR7">
         <v>60</v>
@@ -2387,10 +2387,10 @@
         <v>4.4</v>
       </c>
       <c r="BV7">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="BW7">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BX7">
         <v>60</v>
@@ -2428,7 +2428,7 @@
         <v>7</v>
       </c>
       <c r="G8">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="H8">
         <v>1.55</v>
@@ -2443,7 +2443,7 @@
         <v>4.4</v>
       </c>
       <c r="L8">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="M8">
         <v>1.07</v>
@@ -2455,7 +2455,7 @@
         <v>1.34</v>
       </c>
       <c r="P8">
-        <v>1.86</v>
+        <v>1.84</v>
       </c>
       <c r="Q8">
         <v>2.02</v>
@@ -2467,7 +2467,7 @@
         <v>3.65</v>
       </c>
       <c r="T8">
-        <v>2.06</v>
+        <v>2.08</v>
       </c>
       <c r="U8">
         <v>1.8</v>
@@ -2545,13 +2545,13 @@
         <v>10.5</v>
       </c>
       <c r="AT8">
-        <v>4.2</v>
+        <v>9</v>
       </c>
       <c r="AU8">
         <v>7</v>
       </c>
       <c r="AV8">
-        <v>7.6</v>
+        <v>9</v>
       </c>
       <c r="AW8">
         <v>16</v>
@@ -2670,10 +2670,10 @@
         <v>2.5</v>
       </c>
       <c r="G9">
-        <v>2.7</v>
+        <v>2.74</v>
       </c>
       <c r="H9">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="I9">
         <v>3.95</v>
@@ -2691,7 +2691,7 @@
         <v>1.16</v>
       </c>
       <c r="N9">
-        <v>2.22</v>
+        <v>2.26</v>
       </c>
       <c r="O9">
         <v>1.66</v>
@@ -2709,16 +2709,16 @@
         <v>6</v>
       </c>
       <c r="T9">
-        <v>2.32</v>
+        <v>2.34</v>
       </c>
       <c r="U9">
-        <v>1.64</v>
+        <v>1.63</v>
       </c>
       <c r="V9">
         <v>1.34</v>
       </c>
       <c r="W9">
-        <v>1.59</v>
+        <v>1.58</v>
       </c>
       <c r="X9">
         <v>8.199999999999999</v>
@@ -2754,7 +2754,7 @@
         <v>29</v>
       </c>
       <c r="AI9">
-        <v>500</v>
+        <v>540</v>
       </c>
       <c r="AJ9">
         <v>55</v>
@@ -2763,7 +2763,7 @@
         <v>55</v>
       </c>
       <c r="AL9">
-        <v>100</v>
+        <v>230</v>
       </c>
       <c r="AM9">
         <v>500</v>
@@ -2796,10 +2796,10 @@
         <v>14.5</v>
       </c>
       <c r="AW9">
-        <v>7.2</v>
+        <v>23</v>
       </c>
       <c r="AX9">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="AY9">
         <v>11.5</v>
@@ -2829,7 +2829,7 @@
         <v>7.4</v>
       </c>
       <c r="BH9">
-        <v>2.74</v>
+        <v>2.76</v>
       </c>
       <c r="BI9">
         <v>2.02</v>
@@ -2838,55 +2838,55 @@
         <v>15</v>
       </c>
       <c r="BK9">
-        <v>9.199999999999999</v>
+        <v>3.9</v>
       </c>
       <c r="BL9">
         <v>1000</v>
       </c>
       <c r="BM9">
-        <v>7</v>
+        <v>5.2</v>
       </c>
       <c r="BN9">
-        <v>5.4</v>
+        <v>6.2</v>
       </c>
       <c r="BO9">
-        <v>4.6</v>
+        <v>4</v>
       </c>
       <c r="BP9">
         <v>32</v>
       </c>
       <c r="BQ9">
-        <v>5.9</v>
+        <v>4.5</v>
       </c>
       <c r="BR9">
-        <v>70</v>
+        <v>1000</v>
       </c>
       <c r="BS9">
-        <v>6.4</v>
+        <v>4.9</v>
       </c>
       <c r="BT9">
-        <v>6.8</v>
+        <v>7.8</v>
       </c>
       <c r="BU9">
-        <v>5.6</v>
+        <v>4.9</v>
       </c>
       <c r="BV9">
         <v>48</v>
       </c>
       <c r="BW9">
-        <v>6</v>
+        <v>4.7</v>
       </c>
       <c r="BX9">
         <v>1000</v>
       </c>
       <c r="BY9">
-        <v>6.6</v>
+        <v>4.9</v>
       </c>
       <c r="BZ9">
         <v>1000</v>
       </c>
       <c r="CA9">
-        <v>6.6</v>
+        <v>4.9</v>
       </c>
       <c r="CB9" t="s">
         <v>121</v>
@@ -2909,7 +2909,7 @@
         <v>117</v>
       </c>
       <c r="F10">
-        <v>2.4</v>
+        <v>2.42</v>
       </c>
       <c r="G10">
         <v>2.58</v>
@@ -2963,16 +2963,16 @@
         <v>1.63</v>
       </c>
       <c r="X10">
-        <v>950</v>
+        <v>970</v>
       </c>
       <c r="Y10">
         <v>13</v>
       </c>
       <c r="Z10">
-        <v>500</v>
+        <v>55</v>
       </c>
       <c r="AA10">
-        <v>500</v>
+        <v>900</v>
       </c>
       <c r="AB10">
         <v>9.800000000000001</v>
@@ -2993,13 +2993,13 @@
         <v>19.5</v>
       </c>
       <c r="AH10">
-        <v>950</v>
+        <v>85</v>
       </c>
       <c r="AI10">
-        <v>500</v>
+        <v>540</v>
       </c>
       <c r="AJ10">
-        <v>500</v>
+        <v>220</v>
       </c>
       <c r="AK10">
         <v>500</v>
@@ -3017,7 +3017,7 @@
         <v>1000</v>
       </c>
       <c r="AP10">
-        <v>2.16</v>
+        <v>3.85</v>
       </c>
       <c r="AQ10">
         <v>5.9</v>
@@ -3026,7 +3026,7 @@
         <v>14.5</v>
       </c>
       <c r="AS10">
-        <v>2.48</v>
+        <v>2.54</v>
       </c>
       <c r="AT10">
         <v>4.6</v>
@@ -3038,10 +3038,10 @@
         <v>11</v>
       </c>
       <c r="AW10">
-        <v>2.42</v>
+        <v>2.5</v>
       </c>
       <c r="AX10">
-        <v>9</v>
+        <v>7.2</v>
       </c>
       <c r="AY10">
         <v>8.4</v>
@@ -3050,25 +3050,25 @@
         <v>16</v>
       </c>
       <c r="BA10">
-        <v>2.48</v>
+        <v>2.54</v>
       </c>
       <c r="BB10">
-        <v>2.38</v>
+        <v>16</v>
       </c>
       <c r="BC10">
-        <v>2.4</v>
+        <v>18</v>
       </c>
       <c r="BD10">
-        <v>2.48</v>
+        <v>2.54</v>
       </c>
       <c r="BE10">
-        <v>2.48</v>
+        <v>2.56</v>
       </c>
       <c r="BF10">
-        <v>2.4</v>
+        <v>9.4</v>
       </c>
       <c r="BG10">
-        <v>2.48</v>
+        <v>2.56</v>
       </c>
       <c r="BH10">
         <v>1000</v>
@@ -3151,76 +3151,76 @@
         <v>118</v>
       </c>
       <c r="F11">
-        <v>1.72</v>
+        <v>1.76</v>
       </c>
       <c r="G11">
-        <v>1.78</v>
+        <v>1.84</v>
       </c>
       <c r="H11">
         <v>5.7</v>
       </c>
       <c r="I11">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="J11">
+        <v>3.55</v>
+      </c>
+      <c r="K11">
         <v>3.8</v>
-      </c>
-      <c r="K11">
-        <v>3.9</v>
       </c>
       <c r="L11">
         <v>1.41</v>
       </c>
       <c r="M11">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="N11">
-        <v>3.1</v>
+        <v>2.98</v>
       </c>
       <c r="O11">
-        <v>1.43</v>
+        <v>1.46</v>
       </c>
       <c r="P11">
-        <v>1.72</v>
+        <v>1.69</v>
       </c>
       <c r="Q11">
-        <v>2.3</v>
+        <v>2.36</v>
       </c>
       <c r="R11">
-        <v>1.27</v>
+        <v>1.24</v>
       </c>
       <c r="S11">
-        <v>4.3</v>
+        <v>4.6</v>
       </c>
       <c r="T11">
         <v>2.12</v>
       </c>
       <c r="U11">
-        <v>1.8</v>
+        <v>1.79</v>
       </c>
       <c r="V11">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="W11">
-        <v>2.28</v>
+        <v>2.18</v>
       </c>
       <c r="X11">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="Y11">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="Z11">
-        <v>60</v>
+        <v>46</v>
       </c>
       <c r="AA11">
-        <v>700</v>
+        <v>900</v>
       </c>
       <c r="AB11">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="AC11">
-        <v>8.800000000000001</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AD11">
         <v>23</v>
@@ -3229,7 +3229,7 @@
         <v>120</v>
       </c>
       <c r="AF11">
-        <v>9.4</v>
+        <v>10</v>
       </c>
       <c r="AG11">
         <v>10.5</v>
@@ -3238,31 +3238,31 @@
         <v>26</v>
       </c>
       <c r="AI11">
-        <v>120</v>
+        <v>260</v>
       </c>
       <c r="AJ11">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="AK11">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AL11">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AM11">
-        <v>500</v>
+        <v>580</v>
       </c>
       <c r="AN11">
-        <v>15.5</v>
+        <v>17</v>
       </c>
       <c r="AO11">
         <v>700</v>
       </c>
       <c r="AP11">
-        <v>10.5</v>
+        <v>9.6</v>
       </c>
       <c r="AQ11">
-        <v>13.5</v>
+        <v>12.5</v>
       </c>
       <c r="AR11">
         <v>30</v>
@@ -3274,13 +3274,13 @@
         <v>6</v>
       </c>
       <c r="AU11">
-        <v>7.8</v>
+        <v>7.4</v>
       </c>
       <c r="AV11">
         <v>20</v>
       </c>
       <c r="AW11">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="AX11">
         <v>8.4</v>
@@ -3292,31 +3292,31 @@
         <v>20</v>
       </c>
       <c r="BA11">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="BB11">
-        <v>16.5</v>
+        <v>18</v>
       </c>
       <c r="BC11">
         <v>18.5</v>
       </c>
       <c r="BD11">
-        <v>11</v>
+        <v>40</v>
       </c>
       <c r="BE11">
         <v>13.5</v>
       </c>
       <c r="BF11">
-        <v>11.5</v>
+        <v>15</v>
       </c>
       <c r="BG11">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="BH11">
-        <v>3.75</v>
+        <v>1000</v>
       </c>
       <c r="BI11">
-        <v>2.5</v>
+        <v>2.52</v>
       </c>
       <c r="BJ11">
         <v>1000</v>
@@ -3393,7 +3393,7 @@
         <v>119</v>
       </c>
       <c r="F12">
-        <v>2.78</v>
+        <v>2.82</v>
       </c>
       <c r="G12">
         <v>2.9</v>
@@ -3411,34 +3411,34 @@
         <v>3.45</v>
       </c>
       <c r="L12">
-        <v>1.46</v>
+        <v>1.01</v>
       </c>
       <c r="M12">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="N12">
-        <v>3.2</v>
+        <v>3</v>
       </c>
       <c r="O12">
-        <v>1.39</v>
+        <v>1.43</v>
       </c>
       <c r="P12">
-        <v>1.77</v>
+        <v>1.68</v>
       </c>
       <c r="Q12">
-        <v>2.14</v>
+        <v>2.28</v>
       </c>
       <c r="R12">
-        <v>1.29</v>
+        <v>1.26</v>
       </c>
       <c r="S12">
-        <v>4</v>
+        <v>4.3</v>
       </c>
       <c r="T12">
-        <v>1.85</v>
+        <v>1.93</v>
       </c>
       <c r="U12">
-        <v>2.04</v>
+        <v>1.96</v>
       </c>
       <c r="V12">
         <v>1.52</v>
@@ -3450,7 +3450,7 @@
         <v>14.5</v>
       </c>
       <c r="Y12">
-        <v>10.5</v>
+        <v>9.4</v>
       </c>
       <c r="Z12">
         <v>18</v>
@@ -3459,10 +3459,10 @@
         <v>65</v>
       </c>
       <c r="AB12">
-        <v>10.5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AC12">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="AD12">
         <v>13</v>
@@ -3471,49 +3471,49 @@
         <v>50</v>
       </c>
       <c r="AF12">
+        <v>19</v>
+      </c>
+      <c r="AG12">
+        <v>13.5</v>
+      </c>
+      <c r="AH12">
         <v>19.5</v>
       </c>
-      <c r="AG12">
-        <v>13</v>
-      </c>
-      <c r="AH12">
-        <v>18.5</v>
-      </c>
       <c r="AI12">
-        <v>70</v>
+        <v>55</v>
       </c>
       <c r="AJ12">
-        <v>320</v>
+        <v>55</v>
       </c>
       <c r="AK12">
         <v>50</v>
       </c>
       <c r="AL12">
-        <v>290</v>
+        <v>70</v>
       </c>
       <c r="AM12">
-        <v>450</v>
+        <v>580</v>
       </c>
       <c r="AN12">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="AO12">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="AP12">
-        <v>10.5</v>
+        <v>9.4</v>
       </c>
       <c r="AQ12">
-        <v>8.800000000000001</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AR12">
         <v>15.5</v>
       </c>
       <c r="AS12">
-        <v>9.199999999999999</v>
+        <v>38</v>
       </c>
       <c r="AT12">
-        <v>9.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="AU12">
         <v>6.6</v>
@@ -3534,7 +3534,7 @@
         <v>16</v>
       </c>
       <c r="BA12">
-        <v>9.4</v>
+        <v>38</v>
       </c>
       <c r="BB12">
         <v>29</v>
@@ -3543,46 +3543,46 @@
         <v>16</v>
       </c>
       <c r="BD12">
-        <v>9.4</v>
+        <v>44</v>
       </c>
       <c r="BE12">
+        <v>13</v>
+      </c>
+      <c r="BF12">
         <v>10.5</v>
       </c>
-      <c r="BF12">
-        <v>8.800000000000001</v>
-      </c>
       <c r="BG12">
-        <v>8.4</v>
+        <v>11.5</v>
       </c>
       <c r="BH12">
-        <v>3.15</v>
+        <v>3.05</v>
       </c>
       <c r="BI12">
-        <v>2.6</v>
+        <v>2.8</v>
       </c>
       <c r="BJ12">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="BK12">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="BL12">
         <v>1000</v>
       </c>
       <c r="BM12">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="BN12">
         <v>5.9</v>
       </c>
       <c r="BO12">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="BP12">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="BQ12">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="BR12">
         <v>40</v>
@@ -3603,13 +3603,13 @@
         <v>9.199999999999999</v>
       </c>
       <c r="BX12">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="BY12">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="BZ12">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="CA12">
         <v>10.5</v>
@@ -3638,13 +3638,13 @@
         <v>2.22</v>
       </c>
       <c r="G13">
-        <v>2.42</v>
+        <v>2.44</v>
       </c>
       <c r="H13">
         <v>3.35</v>
       </c>
       <c r="I13">
-        <v>3.8</v>
+        <v>3.9</v>
       </c>
       <c r="J13">
         <v>3.25</v>
@@ -3674,7 +3674,7 @@
         <v>1.28</v>
       </c>
       <c r="S13">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="T13">
         <v>1.83</v>
@@ -3686,34 +3686,34 @@
         <v>1.37</v>
       </c>
       <c r="W13">
-        <v>1.7</v>
+        <v>1.69</v>
       </c>
       <c r="X13">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="Y13">
         <v>14.5</v>
       </c>
       <c r="Z13">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="AA13">
         <v>75</v>
       </c>
       <c r="AB13">
-        <v>10.5</v>
+        <v>9.4</v>
       </c>
       <c r="AC13">
-        <v>8.800000000000001</v>
+        <v>8</v>
       </c>
       <c r="AD13">
-        <v>17.5</v>
+        <v>16</v>
       </c>
       <c r="AE13">
         <v>55</v>
       </c>
       <c r="AF13">
-        <v>16.5</v>
+        <v>15</v>
       </c>
       <c r="AG13">
         <v>13</v>
@@ -3722,10 +3722,10 @@
         <v>22</v>
       </c>
       <c r="AI13">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="AJ13">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="AK13">
         <v>30</v>
@@ -3740,61 +3740,61 @@
         <v>24</v>
       </c>
       <c r="AO13">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AP13">
         <v>9.4</v>
       </c>
       <c r="AQ13">
-        <v>9.6</v>
+        <v>10.5</v>
       </c>
       <c r="AR13">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="AS13">
-        <v>5</v>
+        <v>6.4</v>
       </c>
       <c r="AT13">
-        <v>7</v>
+        <v>7.8</v>
       </c>
       <c r="AU13">
-        <v>6</v>
+        <v>6.6</v>
       </c>
       <c r="AV13">
-        <v>11.5</v>
+        <v>12.5</v>
       </c>
       <c r="AW13">
-        <v>4.9</v>
+        <v>6.2</v>
       </c>
       <c r="AX13">
         <v>11</v>
       </c>
       <c r="AY13">
-        <v>8.6</v>
+        <v>9.6</v>
       </c>
       <c r="AZ13">
         <v>14</v>
       </c>
       <c r="BA13">
-        <v>5</v>
+        <v>6.4</v>
       </c>
       <c r="BB13">
-        <v>4.7</v>
+        <v>5.8</v>
       </c>
       <c r="BC13">
-        <v>20</v>
+        <v>5.7</v>
       </c>
       <c r="BD13">
-        <v>4.8</v>
+        <v>6.2</v>
       </c>
       <c r="BE13">
-        <v>5.1</v>
+        <v>6.6</v>
       </c>
       <c r="BF13">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="BG13">
-        <v>4.9</v>
+        <v>6.2</v>
       </c>
       <c r="BH13">
         <v>3.3</v>
@@ -3806,16 +3806,16 @@
         <v>10.5</v>
       </c>
       <c r="BK13">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="BL13">
         <v>1000</v>
       </c>
       <c r="BM13">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="BN13">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="BO13">
         <v>4</v>
@@ -3824,37 +3824,37 @@
         <v>18.5</v>
       </c>
       <c r="BQ13">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="BR13">
         <v>36</v>
       </c>
       <c r="BS13">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="BT13">
         <v>7</v>
       </c>
       <c r="BU13">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="BV13">
         <v>1000</v>
       </c>
       <c r="BW13">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="BX13">
         <v>1000</v>
       </c>
       <c r="BY13">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BZ13">
         <v>34</v>
       </c>
       <c r="CA13">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="CB13" t="s">
         <v>121</v>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-08-11.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-08-11.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="152" uniqueCount="122">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="134" uniqueCount="112">
   <si>
     <t>League</t>
   </si>
@@ -256,15 +256,6 @@
     <t>SnapshotTS</t>
   </si>
   <si>
-    <t>Brazilian Campeonato Women</t>
-  </si>
-  <si>
-    <t>Chilean Primera Division</t>
-  </si>
-  <si>
-    <t>Ecuadorian Serie A</t>
-  </si>
-  <si>
     <t>Argentinian Primera Division</t>
   </si>
   <si>
@@ -286,9 +277,6 @@
     <t>2026-08-11</t>
   </si>
   <si>
-    <t>00:00:00</t>
-  </si>
-  <si>
     <t>00:15:00</t>
   </si>
   <si>
@@ -307,15 +295,6 @@
     <t>23:00:00</t>
   </si>
   <si>
-    <t>America MG (W)</t>
-  </si>
-  <si>
-    <t>Audax Italiano</t>
-  </si>
-  <si>
-    <t>Deportivo Cuenca</t>
-  </si>
-  <si>
     <t>Union Santa Fe</t>
   </si>
   <si>
@@ -343,15 +322,6 @@
     <t>Puerto Montt</t>
   </si>
   <si>
-    <t>CR Flamengo (W)</t>
-  </si>
-  <si>
-    <t>Nublense</t>
-  </si>
-  <si>
-    <t>Manta FC</t>
-  </si>
-  <si>
     <t>Central Cordoba (SdE)</t>
   </si>
   <si>
@@ -379,7 +349,7 @@
     <t>Union Espanola</t>
   </si>
   <si>
-    <t>2026-08-10 21:05:03</t>
+    <t>2026-08-10 23:12:02</t>
   </si>
 </sst>
 </file>
@@ -711,7 +681,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:CB13"/>
+  <dimension ref="A1:CB10"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:80">
@@ -961,241 +931,241 @@
         <v>80</v>
       </c>
       <c r="B2" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="C2" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="D2" t="s">
-        <v>97</v>
+        <v>93</v>
       </c>
       <c r="E2" t="s">
-        <v>109</v>
+        <v>102</v>
       </c>
       <c r="F2">
-        <v>14</v>
+        <v>1000</v>
       </c>
       <c r="G2">
-        <v>17.5</v>
+        <v>1000</v>
       </c>
       <c r="H2">
-        <v>1.29</v>
+        <v>1.06</v>
       </c>
       <c r="I2">
-        <v>1.32</v>
+        <v>1.08</v>
       </c>
       <c r="J2">
-        <v>5.8</v>
+        <v>13.5</v>
       </c>
       <c r="K2">
-        <v>6.4</v>
+        <v>22</v>
       </c>
       <c r="L2">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="M2">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="N2">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="O2">
+        <v>0</v>
+      </c>
+      <c r="P2">
+        <v>0</v>
+      </c>
+      <c r="Q2">
+        <v>0</v>
+      </c>
+      <c r="R2">
+        <v>1.07</v>
+      </c>
+      <c r="S2">
+        <v>11.5</v>
+      </c>
+      <c r="T2">
+        <v>0</v>
+      </c>
+      <c r="U2">
+        <v>0</v>
+      </c>
+      <c r="V2">
+        <v>1.01</v>
+      </c>
+      <c r="W2">
+        <v>1.01</v>
+      </c>
+      <c r="X2">
+        <v>1000</v>
+      </c>
+      <c r="Y2">
+        <v>1000</v>
+      </c>
+      <c r="Z2">
+        <v>1000</v>
+      </c>
+      <c r="AA2">
+        <v>1000</v>
+      </c>
+      <c r="AB2">
+        <v>1000</v>
+      </c>
+      <c r="AC2">
+        <v>1000</v>
+      </c>
+      <c r="AD2">
+        <v>1.08</v>
+      </c>
+      <c r="AE2">
+        <v>1000</v>
+      </c>
+      <c r="AF2">
+        <v>1000</v>
+      </c>
+      <c r="AG2">
+        <v>1000</v>
+      </c>
+      <c r="AH2">
+        <v>1000</v>
+      </c>
+      <c r="AI2">
+        <v>1000</v>
+      </c>
+      <c r="AJ2">
+        <v>1000</v>
+      </c>
+      <c r="AK2">
+        <v>1000</v>
+      </c>
+      <c r="AL2">
+        <v>1000</v>
+      </c>
+      <c r="AM2">
+        <v>1000</v>
+      </c>
+      <c r="AN2">
+        <v>1000</v>
+      </c>
+      <c r="AO2">
+        <v>1000</v>
+      </c>
+      <c r="AP2">
         <v>1.26</v>
       </c>
-      <c r="P2">
-        <v>2.2</v>
-      </c>
-      <c r="Q2">
-        <v>1.8</v>
-      </c>
-      <c r="R2">
+      <c r="AQ2">
+        <v>1.26</v>
+      </c>
+      <c r="AR2">
+        <v>1.26</v>
+      </c>
+      <c r="AS2">
+        <v>1.26</v>
+      </c>
+      <c r="AT2">
+        <v>1.26</v>
+      </c>
+      <c r="AU2">
+        <v>1.26</v>
+      </c>
+      <c r="AV2">
+        <v>1.01</v>
+      </c>
+      <c r="AW2">
+        <v>7.4</v>
+      </c>
+      <c r="AX2">
+        <v>1.26</v>
+      </c>
+      <c r="AY2">
+        <v>2</v>
+      </c>
+      <c r="AZ2">
+        <v>13.5</v>
+      </c>
+      <c r="BA2">
+        <v>1.26</v>
+      </c>
+      <c r="BB2">
+        <v>1.26</v>
+      </c>
+      <c r="BC2">
+        <v>1.26</v>
+      </c>
+      <c r="BD2">
+        <v>1.26</v>
+      </c>
+      <c r="BE2">
         <v>1.45</v>
       </c>
-      <c r="S2">
-        <v>3.05</v>
-      </c>
-      <c r="T2">
-        <v>2.32</v>
-      </c>
-      <c r="U2">
-        <v>1.67</v>
-      </c>
-      <c r="V2">
-        <v>4.1</v>
-      </c>
-      <c r="W2">
-        <v>1.06</v>
-      </c>
-      <c r="X2">
-        <v>21</v>
-      </c>
-      <c r="Y2">
-        <v>8</v>
-      </c>
-      <c r="Z2">
-        <v>7.4</v>
-      </c>
-      <c r="AA2">
-        <v>10.5</v>
-      </c>
-      <c r="AB2">
-        <v>50</v>
-      </c>
-      <c r="AC2">
-        <v>14.5</v>
-      </c>
-      <c r="AD2">
-        <v>13</v>
-      </c>
-      <c r="AE2">
-        <v>15.5</v>
-      </c>
-      <c r="AF2">
-        <v>180</v>
-      </c>
-      <c r="AG2">
-        <v>70</v>
-      </c>
-      <c r="AH2">
-        <v>48</v>
-      </c>
-      <c r="AI2">
-        <v>55</v>
-      </c>
-      <c r="AJ2">
-        <v>1000</v>
-      </c>
-      <c r="AK2">
-        <v>390</v>
-      </c>
-      <c r="AL2">
-        <v>280</v>
-      </c>
-      <c r="AM2">
-        <v>330</v>
-      </c>
-      <c r="AN2">
-        <v>610</v>
-      </c>
-      <c r="AO2">
-        <v>5.9</v>
-      </c>
-      <c r="AP2">
-        <v>12</v>
-      </c>
-      <c r="AQ2">
-        <v>7.2</v>
-      </c>
-      <c r="AR2">
-        <v>6.6</v>
-      </c>
-      <c r="AS2">
-        <v>8.6</v>
-      </c>
-      <c r="AT2">
-        <v>6.8</v>
-      </c>
-      <c r="AU2">
-        <v>9.6</v>
-      </c>
-      <c r="AV2">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AW2">
-        <v>12</v>
-      </c>
-      <c r="AX2">
-        <v>7.4</v>
-      </c>
-      <c r="AY2">
-        <v>7.2</v>
-      </c>
-      <c r="AZ2">
-        <v>7.4</v>
-      </c>
-      <c r="BA2">
-        <v>8</v>
-      </c>
-      <c r="BB2">
-        <v>7.8</v>
-      </c>
-      <c r="BC2">
-        <v>7.6</v>
-      </c>
-      <c r="BD2">
-        <v>7.6</v>
-      </c>
-      <c r="BE2">
-        <v>100</v>
-      </c>
       <c r="BF2">
-        <v>7.6</v>
+        <v>1.26</v>
       </c>
       <c r="BG2">
-        <v>4.9</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BH2">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BI2">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="BJ2">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BK2">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="BL2">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BM2">
-        <v>130</v>
+        <v>0</v>
       </c>
       <c r="BN2">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BO2">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="BP2">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BQ2">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="BR2">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BS2">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="BT2">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BU2">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="BV2">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BW2">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="BX2">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BY2">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="BZ2">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="CA2">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="CB2" t="s">
-        <v>121</v>
+        <v>111</v>
       </c>
     </row>
     <row r="3" spans="1:80">
@@ -1203,241 +1173,241 @@
         <v>81</v>
       </c>
       <c r="B3" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="C3" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="D3" t="s">
-        <v>98</v>
+        <v>94</v>
       </c>
       <c r="E3" t="s">
-        <v>110</v>
+        <v>103</v>
       </c>
       <c r="F3">
-        <v>2.52</v>
+        <v>2.42</v>
       </c>
       <c r="G3">
-        <v>2.64</v>
+        <v>2.5</v>
       </c>
       <c r="H3">
-        <v>3.15</v>
+        <v>2.96</v>
       </c>
       <c r="I3">
-        <v>3.3</v>
+        <v>3.1</v>
       </c>
       <c r="J3">
-        <v>3.25</v>
+        <v>3.75</v>
       </c>
       <c r="K3">
-        <v>3.4</v>
+        <v>3.9</v>
       </c>
       <c r="L3">
-        <v>1.54</v>
+        <v>1.33</v>
       </c>
       <c r="M3">
-        <v>1.1</v>
+        <v>1.04</v>
       </c>
       <c r="N3">
-        <v>3.1</v>
+        <v>5.2</v>
       </c>
       <c r="O3">
-        <v>1.43</v>
+        <v>1.22</v>
       </c>
       <c r="P3">
-        <v>1.69</v>
+        <v>2.38</v>
       </c>
       <c r="Q3">
-        <v>2.4</v>
+        <v>1.65</v>
       </c>
       <c r="R3">
-        <v>1.26</v>
+        <v>1.57</v>
       </c>
       <c r="S3">
-        <v>4.4</v>
+        <v>2.6</v>
       </c>
       <c r="T3">
-        <v>1.95</v>
+        <v>1.56</v>
       </c>
       <c r="U3">
-        <v>1.93</v>
+        <v>2.6</v>
       </c>
       <c r="V3">
-        <v>1.43</v>
+        <v>1.47</v>
       </c>
       <c r="W3">
-        <v>1.6</v>
+        <v>1.66</v>
       </c>
       <c r="X3">
-        <v>11</v>
+        <v>21</v>
       </c>
       <c r="Y3">
-        <v>10.5</v>
+        <v>16.5</v>
       </c>
       <c r="Z3">
         <v>24</v>
       </c>
       <c r="AA3">
-        <v>75</v>
+        <v>50</v>
       </c>
       <c r="AB3">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="AC3">
-        <v>7.4</v>
+        <v>8.6</v>
       </c>
       <c r="AD3">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="AE3">
-        <v>55</v>
+        <v>29</v>
       </c>
       <c r="AF3">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="AG3">
         <v>12.5</v>
       </c>
       <c r="AH3">
-        <v>24</v>
+        <v>14.5</v>
       </c>
       <c r="AI3">
-        <v>75</v>
+        <v>34</v>
       </c>
       <c r="AJ3">
-        <v>48</v>
+        <v>60</v>
       </c>
       <c r="AK3">
-        <v>40</v>
+        <v>23</v>
       </c>
       <c r="AL3">
-        <v>65</v>
+        <v>34</v>
       </c>
       <c r="AM3">
-        <v>170</v>
+        <v>60</v>
       </c>
       <c r="AN3">
-        <v>40</v>
+        <v>14</v>
       </c>
       <c r="AO3">
-        <v>55</v>
+        <v>20</v>
       </c>
       <c r="AP3">
-        <v>9.6</v>
+        <v>18</v>
       </c>
       <c r="AQ3">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="AR3">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="AS3">
         <v>42</v>
       </c>
       <c r="AT3">
+        <v>13</v>
+      </c>
+      <c r="AU3">
         <v>8</v>
-      </c>
-      <c r="AU3">
-        <v>6.6</v>
       </c>
       <c r="AV3">
         <v>12</v>
       </c>
       <c r="AW3">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="AX3">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="AY3">
         <v>10.5</v>
       </c>
       <c r="AZ3">
-        <v>17.5</v>
+        <v>13.5</v>
       </c>
       <c r="BA3">
-        <v>50</v>
+        <v>30</v>
       </c>
       <c r="BB3">
         <v>29</v>
       </c>
       <c r="BC3">
+        <v>20</v>
+      </c>
+      <c r="BD3">
         <v>27</v>
       </c>
-      <c r="BD3">
-        <v>38</v>
-      </c>
       <c r="BE3">
-        <v>8.199999999999999</v>
+        <v>48</v>
       </c>
       <c r="BF3">
-        <v>26</v>
+        <v>12</v>
       </c>
       <c r="BG3">
-        <v>36</v>
+        <v>17.5</v>
       </c>
       <c r="BH3">
-        <v>2.78</v>
+        <v>4.1</v>
       </c>
       <c r="BI3">
-        <v>2.62</v>
+        <v>3.65</v>
       </c>
       <c r="BJ3">
-        <v>11</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BK3">
+        <v>5.8</v>
+      </c>
+      <c r="BL3">
+        <v>1000</v>
+      </c>
+      <c r="BM3">
+        <v>14</v>
+      </c>
+      <c r="BN3">
+        <v>5.5</v>
+      </c>
+      <c r="BO3">
+        <v>4.9</v>
+      </c>
+      <c r="BP3">
+        <v>16</v>
+      </c>
+      <c r="BQ3">
+        <v>8.4</v>
+      </c>
+      <c r="BR3">
+        <v>1000</v>
+      </c>
+      <c r="BS3">
         <v>10</v>
       </c>
-      <c r="BL3">
-        <v>210</v>
-      </c>
-      <c r="BM3">
-        <v>130</v>
-      </c>
-      <c r="BN3">
-        <v>5.3</v>
-      </c>
-      <c r="BO3">
-        <v>4.7</v>
-      </c>
-      <c r="BP3">
-        <v>28</v>
-      </c>
-      <c r="BQ3">
-        <v>20</v>
-      </c>
-      <c r="BR3">
-        <v>50</v>
-      </c>
-      <c r="BS3">
-        <v>36</v>
-      </c>
       <c r="BT3">
-        <v>6.2</v>
+        <v>6.6</v>
       </c>
       <c r="BU3">
-        <v>5.5</v>
+        <v>5.8</v>
       </c>
       <c r="BV3">
-        <v>36</v>
+        <v>1000</v>
       </c>
       <c r="BW3">
-        <v>25</v>
+        <v>9.6</v>
       </c>
       <c r="BX3">
-        <v>60</v>
+        <v>1000</v>
       </c>
       <c r="BY3">
-        <v>42</v>
+        <v>10.5</v>
       </c>
       <c r="BZ3">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="CA3">
-        <v>36</v>
+        <v>0</v>
       </c>
       <c r="CB3" t="s">
-        <v>121</v>
+        <v>111</v>
       </c>
     </row>
     <row r="4" spans="1:80">
@@ -1445,58 +1415,58 @@
         <v>82</v>
       </c>
       <c r="B4" t="s">
+        <v>86</v>
+      </c>
+      <c r="C4" t="s">
         <v>89</v>
       </c>
-      <c r="C4" t="s">
-        <v>90</v>
-      </c>
       <c r="D4" t="s">
-        <v>99</v>
+        <v>95</v>
       </c>
       <c r="E4" t="s">
-        <v>111</v>
+        <v>104</v>
       </c>
       <c r="F4">
-        <v>1.72</v>
+        <v>2.9</v>
       </c>
       <c r="G4">
-        <v>1.77</v>
+        <v>3.25</v>
       </c>
       <c r="H4">
-        <v>6.2</v>
+        <v>2.88</v>
       </c>
       <c r="I4">
-        <v>6.6</v>
+        <v>3.15</v>
       </c>
       <c r="J4">
-        <v>3.6</v>
+        <v>2.82</v>
       </c>
       <c r="K4">
-        <v>3.8</v>
+        <v>3.05</v>
       </c>
       <c r="L4">
-        <v>1.47</v>
+        <v>1.61</v>
       </c>
       <c r="M4">
-        <v>1.11</v>
+        <v>1.14</v>
       </c>
       <c r="N4">
-        <v>2.92</v>
+        <v>2.38</v>
       </c>
       <c r="O4">
-        <v>1.48</v>
+        <v>1.62</v>
       </c>
       <c r="P4">
-        <v>1.6</v>
+        <v>1.45</v>
       </c>
       <c r="Q4">
-        <v>2.56</v>
+        <v>2.84</v>
       </c>
       <c r="R4">
-        <v>1.21</v>
+        <v>1.16</v>
       </c>
       <c r="S4">
-        <v>5.3</v>
+        <v>6</v>
       </c>
       <c r="T4">
         <v>2.2</v>
@@ -1505,1391 +1475,1391 @@
         <v>1.71</v>
       </c>
       <c r="V4">
-        <v>1.2</v>
+        <v>1.47</v>
       </c>
       <c r="W4">
-        <v>2.22</v>
+        <v>1.44</v>
       </c>
       <c r="X4">
-        <v>9.800000000000001</v>
+        <v>8</v>
       </c>
       <c r="Y4">
-        <v>17</v>
+        <v>9.6</v>
       </c>
       <c r="Z4">
+        <v>21</v>
+      </c>
+      <c r="AA4">
+        <v>70</v>
+      </c>
+      <c r="AB4">
+        <v>8.6</v>
+      </c>
+      <c r="AC4">
+        <v>7.4</v>
+      </c>
+      <c r="AD4">
+        <v>15.5</v>
+      </c>
+      <c r="AE4">
         <v>55</v>
       </c>
-      <c r="AA4">
-        <v>240</v>
-      </c>
-      <c r="AB4">
-        <v>7.2</v>
-      </c>
-      <c r="AC4">
+      <c r="AF4">
+        <v>22</v>
+      </c>
+      <c r="AG4">
+        <v>17.5</v>
+      </c>
+      <c r="AH4">
+        <v>30</v>
+      </c>
+      <c r="AI4">
+        <v>100</v>
+      </c>
+      <c r="AJ4">
+        <v>150</v>
+      </c>
+      <c r="AK4">
+        <v>55</v>
+      </c>
+      <c r="AL4">
+        <v>100</v>
+      </c>
+      <c r="AM4">
+        <v>500</v>
+      </c>
+      <c r="AN4">
+        <v>210</v>
+      </c>
+      <c r="AO4">
+        <v>70</v>
+      </c>
+      <c r="AP4">
+        <v>6.6</v>
+      </c>
+      <c r="AQ4">
+        <v>7</v>
+      </c>
+      <c r="AR4">
+        <v>15</v>
+      </c>
+      <c r="AS4">
+        <v>20</v>
+      </c>
+      <c r="AT4">
+        <v>7</v>
+      </c>
+      <c r="AU4">
+        <v>6</v>
+      </c>
+      <c r="AV4">
+        <v>12</v>
+      </c>
+      <c r="AW4">
+        <v>6</v>
+      </c>
+      <c r="AX4">
+        <v>15.5</v>
+      </c>
+      <c r="AY4">
+        <v>12.5</v>
+      </c>
+      <c r="AZ4">
+        <v>20</v>
+      </c>
+      <c r="BA4">
+        <v>6.2</v>
+      </c>
+      <c r="BB4">
+        <v>18</v>
+      </c>
+      <c r="BC4">
+        <v>6</v>
+      </c>
+      <c r="BD4">
+        <v>6.2</v>
+      </c>
+      <c r="BE4">
+        <v>6.4</v>
+      </c>
+      <c r="BF4">
+        <v>11.5</v>
+      </c>
+      <c r="BG4">
+        <v>6</v>
+      </c>
+      <c r="BH4">
+        <v>2.62</v>
+      </c>
+      <c r="BI4">
+        <v>2.12</v>
+      </c>
+      <c r="BJ4">
+        <v>12.5</v>
+      </c>
+      <c r="BK4">
+        <v>5.9</v>
+      </c>
+      <c r="BL4">
+        <v>1000</v>
+      </c>
+      <c r="BM4">
+        <v>10.5</v>
+      </c>
+      <c r="BN4">
+        <v>6</v>
+      </c>
+      <c r="BO4">
+        <v>4.4</v>
+      </c>
+      <c r="BP4">
+        <v>30</v>
+      </c>
+      <c r="BQ4">
         <v>8.199999999999999</v>
       </c>
-      <c r="AD4">
-        <v>28</v>
-      </c>
-      <c r="AE4">
-        <v>140</v>
-      </c>
-      <c r="AF4">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AG4">
-        <v>11.5</v>
-      </c>
-      <c r="AH4">
-        <v>38</v>
-      </c>
-      <c r="AI4">
-        <v>160</v>
-      </c>
-      <c r="AJ4">
-        <v>21</v>
-      </c>
-      <c r="AK4">
-        <v>29</v>
-      </c>
-      <c r="AL4">
-        <v>75</v>
-      </c>
-      <c r="AM4">
-        <v>310</v>
-      </c>
-      <c r="AN4">
-        <v>21</v>
-      </c>
-      <c r="AO4">
-        <v>270</v>
-      </c>
-      <c r="AP4">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AQ4">
-        <v>13.5</v>
-      </c>
-      <c r="AR4">
+      <c r="BR4">
+        <v>60</v>
+      </c>
+      <c r="BS4">
+        <v>9.4</v>
+      </c>
+      <c r="BT4">
+        <v>6</v>
+      </c>
+      <c r="BU4">
+        <v>4.4</v>
+      </c>
+      <c r="BV4">
         <v>32</v>
       </c>
-      <c r="AS4">
-        <v>7.6</v>
-      </c>
-      <c r="AT4">
-        <v>5.9</v>
-      </c>
-      <c r="AU4">
-        <v>7.2</v>
-      </c>
-      <c r="AV4">
-        <v>21</v>
-      </c>
-      <c r="AW4">
-        <v>80</v>
-      </c>
-      <c r="AX4">
-        <v>7.6</v>
-      </c>
-      <c r="AY4">
+      <c r="BW4">
+        <v>8.4</v>
+      </c>
+      <c r="BX4">
+        <v>60</v>
+      </c>
+      <c r="BY4">
+        <v>9.4</v>
+      </c>
+      <c r="BZ4">
+        <v>65</v>
+      </c>
+      <c r="CA4">
         <v>9.6</v>
       </c>
-      <c r="AZ4">
-        <v>23</v>
-      </c>
-      <c r="BA4">
-        <v>100</v>
-      </c>
-      <c r="BB4">
-        <v>15</v>
-      </c>
-      <c r="BC4">
-        <v>20</v>
-      </c>
-      <c r="BD4">
-        <v>44</v>
-      </c>
-      <c r="BE4">
-        <v>7.6</v>
-      </c>
-      <c r="BF4">
-        <v>15</v>
-      </c>
-      <c r="BG4">
-        <v>7.6</v>
-      </c>
-      <c r="BH4">
-        <v>3</v>
-      </c>
-      <c r="BI4">
-        <v>2.84</v>
-      </c>
-      <c r="BJ4">
-        <v>950</v>
-      </c>
-      <c r="BK4">
-        <v>11.5</v>
-      </c>
-      <c r="BL4">
-        <v>940</v>
-      </c>
-      <c r="BM4">
-        <v>6.6</v>
-      </c>
-      <c r="BN4">
-        <v>3.7</v>
-      </c>
-      <c r="BO4">
-        <v>3.4</v>
-      </c>
-      <c r="BP4">
-        <v>12</v>
-      </c>
-      <c r="BQ4">
-        <v>9.4</v>
-      </c>
-      <c r="BR4">
-        <v>860</v>
-      </c>
-      <c r="BS4">
-        <v>25</v>
-      </c>
-      <c r="BT4">
-        <v>10</v>
-      </c>
-      <c r="BU4">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="BV4">
-        <v>1000</v>
-      </c>
-      <c r="BW4">
-        <v>10.5</v>
-      </c>
-      <c r="BX4">
-        <v>920</v>
-      </c>
-      <c r="BY4">
-        <v>6.6</v>
-      </c>
-      <c r="BZ4">
-        <v>960</v>
-      </c>
-      <c r="CA4">
-        <v>6.8</v>
-      </c>
       <c r="CB4" t="s">
-        <v>121</v>
+        <v>111</v>
       </c>
     </row>
     <row r="5" spans="1:80">
       <c r="A5" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B5" t="s">
+        <v>86</v>
+      </c>
+      <c r="C5" t="s">
         <v>89</v>
       </c>
-      <c r="C5" t="s">
-        <v>91</v>
-      </c>
       <c r="D5" t="s">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="E5" t="s">
-        <v>112</v>
+        <v>105</v>
       </c>
       <c r="F5">
-        <v>1.72</v>
+        <v>7</v>
       </c>
       <c r="G5">
-        <v>1.75</v>
+        <v>8</v>
       </c>
       <c r="H5">
-        <v>6.2</v>
+        <v>1.55</v>
       </c>
       <c r="I5">
-        <v>6.4</v>
+        <v>1.63</v>
       </c>
       <c r="J5">
-        <v>3.7</v>
+        <v>3.95</v>
       </c>
       <c r="K5">
-        <v>3.85</v>
+        <v>4.8</v>
       </c>
       <c r="L5">
-        <v>1.52</v>
+        <v>1.36</v>
       </c>
       <c r="M5">
-        <v>1.1</v>
+        <v>1.07</v>
       </c>
       <c r="N5">
-        <v>3</v>
+        <v>3.45</v>
       </c>
       <c r="O5">
-        <v>1.47</v>
+        <v>1.34</v>
       </c>
       <c r="P5">
-        <v>1.71</v>
+        <v>1.86</v>
       </c>
       <c r="Q5">
-        <v>2.36</v>
+        <v>2.02</v>
       </c>
       <c r="R5">
-        <v>1.25</v>
+        <v>1.32</v>
       </c>
       <c r="S5">
-        <v>4.8</v>
+        <v>3.65</v>
       </c>
       <c r="T5">
-        <v>2.24</v>
+        <v>2.08</v>
       </c>
       <c r="U5">
-        <v>1.77</v>
+        <v>1.81</v>
       </c>
       <c r="V5">
-        <v>1.18</v>
+        <v>2.56</v>
       </c>
       <c r="W5">
-        <v>2.34</v>
+        <v>1.14</v>
       </c>
       <c r="X5">
+        <v>16.5</v>
+      </c>
+      <c r="Y5">
+        <v>8.6</v>
+      </c>
+      <c r="Z5">
         <v>10.5</v>
       </c>
-      <c r="Y5">
-        <v>15.5</v>
-      </c>
-      <c r="Z5">
-        <v>48</v>
-      </c>
       <c r="AA5">
-        <v>210</v>
+        <v>18</v>
       </c>
       <c r="AB5">
-        <v>6.2</v>
+        <v>26</v>
       </c>
       <c r="AC5">
-        <v>8.4</v>
+        <v>11.5</v>
       </c>
       <c r="AD5">
-        <v>24</v>
+        <v>12.5</v>
       </c>
       <c r="AE5">
-        <v>120</v>
+        <v>22</v>
       </c>
       <c r="AF5">
-        <v>8.6</v>
+        <v>75</v>
       </c>
       <c r="AG5">
-        <v>10.5</v>
+        <v>34</v>
       </c>
       <c r="AH5">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="AI5">
-        <v>120</v>
+        <v>55</v>
       </c>
       <c r="AJ5">
-        <v>18</v>
+        <v>700</v>
       </c>
       <c r="AK5">
-        <v>22</v>
+        <v>700</v>
       </c>
       <c r="AL5">
-        <v>50</v>
+        <v>700</v>
       </c>
       <c r="AM5">
-        <v>210</v>
+        <v>700</v>
       </c>
       <c r="AN5">
-        <v>15.5</v>
+        <v>700</v>
       </c>
       <c r="AO5">
-        <v>190</v>
+        <v>12.5</v>
       </c>
       <c r="AP5">
         <v>10</v>
       </c>
       <c r="AQ5">
-        <v>14.5</v>
+        <v>6.4</v>
       </c>
       <c r="AR5">
-        <v>42</v>
+        <v>7.6</v>
       </c>
       <c r="AS5">
-        <v>90</v>
+        <v>10.5</v>
       </c>
       <c r="AT5">
-        <v>5.9</v>
+        <v>9</v>
       </c>
       <c r="AU5">
-        <v>8.199999999999999</v>
+        <v>7</v>
       </c>
       <c r="AV5">
-        <v>22</v>
+        <v>9</v>
       </c>
       <c r="AW5">
-        <v>95</v>
+        <v>16</v>
       </c>
       <c r="AX5">
-        <v>8</v>
+        <v>4.2</v>
       </c>
       <c r="AY5">
-        <v>9.800000000000001</v>
+        <v>20</v>
       </c>
       <c r="AZ5">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="BA5">
-        <v>100</v>
+        <v>4.1</v>
       </c>
       <c r="BB5">
-        <v>16.5</v>
+        <v>4.4</v>
       </c>
       <c r="BC5">
-        <v>20</v>
+        <v>4.4</v>
       </c>
       <c r="BD5">
-        <v>44</v>
+        <v>4.3</v>
       </c>
       <c r="BE5">
-        <v>140</v>
+        <v>4.4</v>
       </c>
       <c r="BF5">
-        <v>14.5</v>
+        <v>4.4</v>
       </c>
       <c r="BG5">
-        <v>160</v>
+        <v>7.8</v>
       </c>
       <c r="BH5">
-        <v>2.9</v>
+        <v>3.85</v>
       </c>
       <c r="BI5">
-        <v>2.74</v>
+        <v>2.68</v>
       </c>
       <c r="BJ5">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="BK5">
-        <v>10.5</v>
+        <v>3.65</v>
       </c>
       <c r="BL5">
-        <v>230</v>
+        <v>1000</v>
       </c>
       <c r="BM5">
-        <v>160</v>
+        <v>4.8</v>
       </c>
       <c r="BN5">
-        <v>3.95</v>
+        <v>13</v>
       </c>
       <c r="BO5">
-        <v>3.75</v>
+        <v>3.55</v>
       </c>
       <c r="BP5">
+        <v>1000</v>
+      </c>
+      <c r="BQ5">
+        <v>4.6</v>
+      </c>
+      <c r="BR5">
+        <v>1000</v>
+      </c>
+      <c r="BS5">
+        <v>4.7</v>
+      </c>
+      <c r="BT5">
+        <v>4.6</v>
+      </c>
+      <c r="BU5">
+        <v>3.1</v>
+      </c>
+      <c r="BV5">
         <v>12.5</v>
       </c>
-      <c r="BQ5">
-        <v>11.5</v>
-      </c>
-      <c r="BR5">
+      <c r="BW5">
+        <v>3.5</v>
+      </c>
+      <c r="BX5">
         <v>36</v>
       </c>
-      <c r="BS5">
-        <v>15.5</v>
-      </c>
-      <c r="BT5">
-        <v>9</v>
-      </c>
-      <c r="BU5">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="BV5">
-        <v>65</v>
-      </c>
-      <c r="BW5">
-        <v>19.5</v>
-      </c>
-      <c r="BX5">
-        <v>80</v>
-      </c>
       <c r="BY5">
-        <v>20</v>
+        <v>4.3</v>
       </c>
       <c r="BZ5">
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="CA5">
-        <v>14.5</v>
+        <v>4.1</v>
       </c>
       <c r="CB5" t="s">
-        <v>121</v>
+        <v>111</v>
       </c>
     </row>
     <row r="6" spans="1:80">
       <c r="A6" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="B6" t="s">
+        <v>86</v>
+      </c>
+      <c r="C6" t="s">
         <v>89</v>
       </c>
-      <c r="C6" t="s">
-        <v>92</v>
-      </c>
       <c r="D6" t="s">
-        <v>101</v>
+        <v>97</v>
       </c>
       <c r="E6" t="s">
-        <v>113</v>
+        <v>106</v>
       </c>
       <c r="F6">
-        <v>2.42</v>
+        <v>2.52</v>
       </c>
       <c r="G6">
-        <v>2.48</v>
+        <v>2.72</v>
       </c>
       <c r="H6">
-        <v>2.96</v>
+        <v>3.45</v>
       </c>
       <c r="I6">
+        <v>3.95</v>
+      </c>
+      <c r="J6">
+        <v>2.72</v>
+      </c>
+      <c r="K6">
         <v>3.05</v>
       </c>
-      <c r="J6">
-        <v>3.7</v>
-      </c>
-      <c r="K6">
-        <v>3.9</v>
-      </c>
       <c r="L6">
-        <v>1.33</v>
+        <v>1.66</v>
       </c>
       <c r="M6">
-        <v>1.04</v>
+        <v>1.16</v>
       </c>
       <c r="N6">
-        <v>5.2</v>
+        <v>2.24</v>
       </c>
       <c r="O6">
-        <v>1.22</v>
+        <v>1.66</v>
       </c>
       <c r="P6">
-        <v>2.38</v>
+        <v>1.4</v>
       </c>
       <c r="Q6">
-        <v>1.65</v>
+        <v>3.05</v>
       </c>
       <c r="R6">
-        <v>1.57</v>
+        <v>1.13</v>
       </c>
       <c r="S6">
-        <v>2.6</v>
+        <v>6</v>
       </c>
       <c r="T6">
-        <v>1.56</v>
+        <v>2.34</v>
       </c>
       <c r="U6">
-        <v>2.6</v>
+        <v>1.63</v>
       </c>
       <c r="V6">
-        <v>1.48</v>
+        <v>1.34</v>
       </c>
       <c r="W6">
-        <v>1.67</v>
+        <v>1.58</v>
       </c>
       <c r="X6">
-        <v>22</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="Y6">
-        <v>16.5</v>
+        <v>9</v>
       </c>
       <c r="Z6">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="AA6">
-        <v>120</v>
+        <v>500</v>
       </c>
       <c r="AB6">
-        <v>15</v>
+        <v>7.2</v>
       </c>
       <c r="AC6">
-        <v>8.6</v>
+        <v>7.2</v>
       </c>
       <c r="AD6">
-        <v>13.5</v>
+        <v>18.5</v>
       </c>
       <c r="AE6">
-        <v>30</v>
+        <v>85</v>
       </c>
       <c r="AF6">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="AG6">
-        <v>12.5</v>
+        <v>14.5</v>
       </c>
       <c r="AH6">
-        <v>14.5</v>
+        <v>29</v>
       </c>
       <c r="AI6">
-        <v>34</v>
+        <v>540</v>
       </c>
       <c r="AJ6">
+        <v>55</v>
+      </c>
+      <c r="AK6">
         <v>60</v>
       </c>
-      <c r="AK6">
-        <v>32</v>
-      </c>
       <c r="AL6">
-        <v>60</v>
+        <v>460</v>
       </c>
       <c r="AM6">
-        <v>190</v>
+        <v>500</v>
       </c>
       <c r="AN6">
-        <v>14</v>
+        <v>65</v>
       </c>
       <c r="AO6">
-        <v>21</v>
+        <v>500</v>
       </c>
       <c r="AP6">
-        <v>18</v>
+        <v>5.4</v>
       </c>
       <c r="AQ6">
-        <v>14</v>
+        <v>7.4</v>
       </c>
       <c r="AR6">
         <v>19</v>
       </c>
       <c r="AS6">
-        <v>38</v>
+        <v>7.4</v>
       </c>
       <c r="AT6">
-        <v>13</v>
+        <v>5.9</v>
       </c>
       <c r="AU6">
+        <v>6</v>
+      </c>
+      <c r="AV6">
+        <v>14.5</v>
+      </c>
+      <c r="AW6">
+        <v>23</v>
+      </c>
+      <c r="AX6">
+        <v>12.5</v>
+      </c>
+      <c r="AY6">
+        <v>11.5</v>
+      </c>
+      <c r="AZ6">
+        <v>20</v>
+      </c>
+      <c r="BA6">
+        <v>7.4</v>
+      </c>
+      <c r="BB6">
+        <v>29</v>
+      </c>
+      <c r="BC6">
+        <v>27</v>
+      </c>
+      <c r="BD6">
+        <v>7.4</v>
+      </c>
+      <c r="BE6">
         <v>7.8</v>
       </c>
-      <c r="AV6">
-        <v>12</v>
-      </c>
-      <c r="AW6">
-        <v>19</v>
-      </c>
-      <c r="AX6">
-        <v>17</v>
-      </c>
-      <c r="AY6">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AZ6">
-        <v>13</v>
-      </c>
-      <c r="BA6">
-        <v>22</v>
-      </c>
-      <c r="BB6">
-        <v>21</v>
-      </c>
-      <c r="BC6">
-        <v>20</v>
-      </c>
-      <c r="BD6">
-        <v>22</v>
-      </c>
-      <c r="BE6">
-        <v>34</v>
-      </c>
       <c r="BF6">
-        <v>12</v>
+        <v>32</v>
       </c>
       <c r="BG6">
-        <v>17.5</v>
+        <v>7.4</v>
       </c>
       <c r="BH6">
-        <v>4.1</v>
+        <v>2.76</v>
       </c>
       <c r="BI6">
-        <v>3.65</v>
+        <v>2.02</v>
       </c>
       <c r="BJ6">
-        <v>8.800000000000001</v>
+        <v>15</v>
       </c>
       <c r="BK6">
-        <v>5.8</v>
+        <v>3.9</v>
       </c>
       <c r="BL6">
         <v>1000</v>
       </c>
       <c r="BM6">
-        <v>14</v>
+        <v>5.2</v>
       </c>
       <c r="BN6">
-        <v>5.5</v>
+        <v>6.2</v>
       </c>
       <c r="BO6">
+        <v>4</v>
+      </c>
+      <c r="BP6">
+        <v>32</v>
+      </c>
+      <c r="BQ6">
+        <v>4.5</v>
+      </c>
+      <c r="BR6">
+        <v>1000</v>
+      </c>
+      <c r="BS6">
         <v>4.9</v>
       </c>
-      <c r="BP6">
-        <v>16</v>
-      </c>
-      <c r="BQ6">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="BR6">
-        <v>1000</v>
-      </c>
-      <c r="BS6">
-        <v>10</v>
-      </c>
       <c r="BT6">
-        <v>6.6</v>
+        <v>7.8</v>
       </c>
       <c r="BU6">
-        <v>5.8</v>
+        <v>4.9</v>
       </c>
       <c r="BV6">
-        <v>1000</v>
+        <v>48</v>
       </c>
       <c r="BW6">
-        <v>9.6</v>
+        <v>4.7</v>
       </c>
       <c r="BX6">
         <v>1000</v>
       </c>
       <c r="BY6">
-        <v>10.5</v>
+        <v>4.9</v>
       </c>
       <c r="BZ6">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA6">
-        <v>0</v>
+        <v>4.9</v>
       </c>
       <c r="CB6" t="s">
-        <v>121</v>
+        <v>111</v>
       </c>
     </row>
     <row r="7" spans="1:80">
       <c r="A7" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="B7" t="s">
+        <v>86</v>
+      </c>
+      <c r="C7" t="s">
         <v>89</v>
       </c>
-      <c r="C7" t="s">
-        <v>93</v>
-      </c>
       <c r="D7" t="s">
-        <v>102</v>
+        <v>98</v>
       </c>
       <c r="E7" t="s">
-        <v>114</v>
+        <v>107</v>
       </c>
       <c r="F7">
-        <v>2.92</v>
+        <v>2.42</v>
       </c>
       <c r="G7">
-        <v>3.25</v>
+        <v>2.58</v>
       </c>
       <c r="H7">
-        <v>2.86</v>
+        <v>3.55</v>
       </c>
       <c r="I7">
-        <v>3.15</v>
+        <v>4.4</v>
       </c>
       <c r="J7">
-        <v>2.8</v>
+        <v>2.76</v>
       </c>
       <c r="K7">
-        <v>3.05</v>
+        <v>3</v>
       </c>
       <c r="L7">
+        <v>1.01</v>
+      </c>
+      <c r="M7">
+        <v>1.11</v>
+      </c>
+      <c r="N7">
+        <v>2.28</v>
+      </c>
+      <c r="O7">
         <v>1.61</v>
-      </c>
-      <c r="M7">
-        <v>1.14</v>
-      </c>
-      <c r="N7">
-        <v>2.38</v>
-      </c>
-      <c r="O7">
-        <v>1.62</v>
       </c>
       <c r="P7">
         <v>1.45</v>
       </c>
       <c r="Q7">
-        <v>2.84</v>
+        <v>2.78</v>
       </c>
       <c r="R7">
-        <v>1.16</v>
+        <v>1.14</v>
       </c>
       <c r="S7">
-        <v>6</v>
+        <v>4.8</v>
       </c>
       <c r="T7">
-        <v>2.18</v>
+        <v>2.14</v>
       </c>
       <c r="U7">
-        <v>1.71</v>
+        <v>1.57</v>
       </c>
       <c r="V7">
-        <v>1.47</v>
+        <v>1.29</v>
       </c>
       <c r="W7">
-        <v>1.44</v>
+        <v>1.63</v>
       </c>
       <c r="X7">
-        <v>8</v>
+        <v>970</v>
       </c>
       <c r="Y7">
-        <v>9.6</v>
+        <v>13</v>
       </c>
       <c r="Z7">
+        <v>55</v>
+      </c>
+      <c r="AA7">
+        <v>900</v>
+      </c>
+      <c r="AB7">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AC7">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AD7">
+        <v>25</v>
+      </c>
+      <c r="AE7">
+        <v>500</v>
+      </c>
+      <c r="AF7">
         <v>21</v>
       </c>
-      <c r="AA7">
-        <v>70</v>
-      </c>
-      <c r="AB7">
-        <v>8.6</v>
-      </c>
-      <c r="AC7">
-        <v>7.4</v>
-      </c>
-      <c r="AD7">
-        <v>17</v>
-      </c>
-      <c r="AE7">
-        <v>55</v>
-      </c>
-      <c r="AF7">
-        <v>22</v>
-      </c>
       <c r="AG7">
-        <v>17.5</v>
+        <v>19.5</v>
       </c>
       <c r="AH7">
-        <v>30</v>
+        <v>85</v>
       </c>
       <c r="AI7">
-        <v>100</v>
+        <v>540</v>
       </c>
       <c r="AJ7">
-        <v>150</v>
+        <v>220</v>
       </c>
       <c r="AK7">
-        <v>55</v>
+        <v>500</v>
       </c>
       <c r="AL7">
-        <v>100</v>
+        <v>500</v>
       </c>
       <c r="AM7">
         <v>500</v>
       </c>
       <c r="AN7">
-        <v>210</v>
+        <v>500</v>
       </c>
       <c r="AO7">
-        <v>70</v>
+        <v>1000</v>
       </c>
       <c r="AP7">
-        <v>6.6</v>
+        <v>3.85</v>
       </c>
       <c r="AQ7">
-        <v>7</v>
+        <v>5.9</v>
       </c>
       <c r="AR7">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="AS7">
-        <v>20</v>
+        <v>2.54</v>
       </c>
       <c r="AT7">
-        <v>7</v>
+        <v>4.6</v>
       </c>
       <c r="AU7">
-        <v>6</v>
+        <v>4.6</v>
       </c>
       <c r="AV7">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AW7">
-        <v>5.8</v>
+        <v>2.5</v>
       </c>
       <c r="AX7">
-        <v>15.5</v>
+        <v>11</v>
       </c>
       <c r="AY7">
-        <v>12.5</v>
+        <v>8.4</v>
       </c>
       <c r="AZ7">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="BA7">
-        <v>6</v>
+        <v>2.54</v>
       </c>
       <c r="BB7">
+        <v>16</v>
+      </c>
+      <c r="BC7">
         <v>18</v>
       </c>
-      <c r="BC7">
-        <v>5.8</v>
-      </c>
       <c r="BD7">
-        <v>6</v>
+        <v>2.54</v>
       </c>
       <c r="BE7">
-        <v>6.2</v>
+        <v>2.56</v>
       </c>
       <c r="BF7">
-        <v>11.5</v>
+        <v>9.4</v>
       </c>
       <c r="BG7">
-        <v>5.9</v>
+        <v>2.56</v>
       </c>
       <c r="BH7">
-        <v>2.64</v>
+        <v>1000</v>
       </c>
       <c r="BI7">
-        <v>2.12</v>
+        <v>1.04</v>
       </c>
       <c r="BJ7">
-        <v>12.5</v>
+        <v>1000</v>
       </c>
       <c r="BK7">
-        <v>5.8</v>
+        <v>1.04</v>
       </c>
       <c r="BL7">
         <v>1000</v>
       </c>
       <c r="BM7">
-        <v>10.5</v>
+        <v>1.04</v>
       </c>
       <c r="BN7">
-        <v>6</v>
+        <v>1000</v>
       </c>
       <c r="BO7">
-        <v>4.4</v>
+        <v>1.04</v>
       </c>
       <c r="BP7">
-        <v>30</v>
+        <v>1000</v>
       </c>
       <c r="BQ7">
-        <v>8</v>
+        <v>1.04</v>
       </c>
       <c r="BR7">
-        <v>60</v>
+        <v>1000</v>
       </c>
       <c r="BS7">
-        <v>9.199999999999999</v>
+        <v>1.04</v>
       </c>
       <c r="BT7">
-        <v>6</v>
+        <v>1000</v>
       </c>
       <c r="BU7">
-        <v>4.4</v>
+        <v>1.04</v>
       </c>
       <c r="BV7">
-        <v>32</v>
+        <v>1000</v>
       </c>
       <c r="BW7">
-        <v>8.199999999999999</v>
+        <v>1.04</v>
       </c>
       <c r="BX7">
-        <v>60</v>
+        <v>1000</v>
       </c>
       <c r="BY7">
-        <v>9.199999999999999</v>
+        <v>1.04</v>
       </c>
       <c r="BZ7">
-        <v>65</v>
+        <v>1000</v>
       </c>
       <c r="CA7">
-        <v>9.4</v>
+        <v>1.04</v>
       </c>
       <c r="CB7" t="s">
-        <v>121</v>
+        <v>111</v>
       </c>
     </row>
     <row r="8" spans="1:80">
       <c r="A8" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="B8" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="C8" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="D8" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
       <c r="E8" t="s">
-        <v>115</v>
+        <v>108</v>
       </c>
       <c r="F8">
-        <v>7</v>
+        <v>1.76</v>
       </c>
       <c r="G8">
-        <v>8</v>
+        <v>1.81</v>
       </c>
       <c r="H8">
-        <v>1.55</v>
+        <v>5.7</v>
       </c>
       <c r="I8">
-        <v>1.63</v>
+        <v>6.2</v>
       </c>
       <c r="J8">
-        <v>3.95</v>
+        <v>3.65</v>
       </c>
       <c r="K8">
-        <v>4.4</v>
+        <v>3.9</v>
       </c>
       <c r="L8">
-        <v>1.36</v>
+        <v>1.48</v>
       </c>
       <c r="M8">
-        <v>1.07</v>
+        <v>1.1</v>
       </c>
       <c r="N8">
-        <v>3.45</v>
+        <v>3.05</v>
       </c>
       <c r="O8">
-        <v>1.34</v>
+        <v>1.44</v>
       </c>
       <c r="P8">
-        <v>1.84</v>
+        <v>1.69</v>
       </c>
       <c r="Q8">
-        <v>2.02</v>
+        <v>2.32</v>
       </c>
       <c r="R8">
-        <v>1.32</v>
+        <v>1.25</v>
       </c>
       <c r="S8">
-        <v>3.65</v>
+        <v>4.5</v>
       </c>
       <c r="T8">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="U8">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="V8">
-        <v>2.56</v>
+        <v>1.19</v>
       </c>
       <c r="W8">
-        <v>1.14</v>
+        <v>2.24</v>
       </c>
       <c r="X8">
+        <v>11.5</v>
+      </c>
+      <c r="Y8">
         <v>16.5</v>
       </c>
-      <c r="Y8">
-        <v>8.6</v>
-      </c>
       <c r="Z8">
+        <v>100</v>
+      </c>
+      <c r="AA8">
+        <v>900</v>
+      </c>
+      <c r="AB8">
+        <v>6.6</v>
+      </c>
+      <c r="AC8">
+        <v>8.4</v>
+      </c>
+      <c r="AD8">
+        <v>23</v>
+      </c>
+      <c r="AE8">
+        <v>700</v>
+      </c>
+      <c r="AF8">
+        <v>9.6</v>
+      </c>
+      <c r="AG8">
         <v>10.5</v>
       </c>
-      <c r="AA8">
+      <c r="AH8">
+        <v>34</v>
+      </c>
+      <c r="AI8">
+        <v>260</v>
+      </c>
+      <c r="AJ8">
+        <v>21</v>
+      </c>
+      <c r="AK8">
+        <v>27</v>
+      </c>
+      <c r="AL8">
+        <v>380</v>
+      </c>
+      <c r="AM8">
+        <v>580</v>
+      </c>
+      <c r="AN8">
         <v>18</v>
       </c>
-      <c r="AB8">
-        <v>26</v>
-      </c>
-      <c r="AC8">
-        <v>11.5</v>
-      </c>
-      <c r="AD8">
-        <v>12.5</v>
-      </c>
-      <c r="AE8">
-        <v>22</v>
-      </c>
-      <c r="AF8">
-        <v>75</v>
-      </c>
-      <c r="AG8">
-        <v>34</v>
-      </c>
-      <c r="AH8">
-        <v>30</v>
-      </c>
-      <c r="AI8">
-        <v>55</v>
-      </c>
-      <c r="AJ8">
+      <c r="AO8">
         <v>700</v>
-      </c>
-      <c r="AK8">
-        <v>700</v>
-      </c>
-      <c r="AL8">
-        <v>700</v>
-      </c>
-      <c r="AM8">
-        <v>700</v>
-      </c>
-      <c r="AN8">
-        <v>700</v>
-      </c>
-      <c r="AO8">
-        <v>12.5</v>
       </c>
       <c r="AP8">
         <v>10</v>
       </c>
       <c r="AQ8">
-        <v>6.4</v>
+        <v>15.5</v>
       </c>
       <c r="AR8">
-        <v>6.6</v>
+        <v>30</v>
       </c>
       <c r="AS8">
-        <v>10.5</v>
+        <v>14</v>
       </c>
       <c r="AT8">
-        <v>9</v>
+        <v>5.9</v>
       </c>
       <c r="AU8">
-        <v>7</v>
+        <v>7.4</v>
       </c>
       <c r="AV8">
-        <v>9</v>
+        <v>20</v>
       </c>
       <c r="AW8">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="AX8">
-        <v>4.2</v>
+        <v>8.4</v>
       </c>
       <c r="AY8">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AZ8">
         <v>20</v>
       </c>
-      <c r="AZ8">
-        <v>18</v>
-      </c>
       <c r="BA8">
-        <v>4.1</v>
+        <v>13</v>
       </c>
       <c r="BB8">
-        <v>4.4</v>
+        <v>13</v>
       </c>
       <c r="BC8">
-        <v>4.4</v>
+        <v>18.5</v>
       </c>
       <c r="BD8">
-        <v>4.3</v>
+        <v>40</v>
       </c>
       <c r="BE8">
-        <v>4.4</v>
+        <v>14</v>
       </c>
       <c r="BF8">
-        <v>4.4</v>
+        <v>14</v>
       </c>
       <c r="BG8">
-        <v>7.8</v>
+        <v>13.5</v>
       </c>
       <c r="BH8">
-        <v>3.85</v>
+        <v>1000</v>
       </c>
       <c r="BI8">
-        <v>2.68</v>
+        <v>1.04</v>
       </c>
       <c r="BJ8">
-        <v>14</v>
+        <v>1000</v>
       </c>
       <c r="BK8">
-        <v>3.65</v>
+        <v>1.04</v>
       </c>
       <c r="BL8">
         <v>1000</v>
       </c>
       <c r="BM8">
-        <v>4.8</v>
+        <v>1.04</v>
       </c>
       <c r="BN8">
-        <v>13</v>
+        <v>1000</v>
       </c>
       <c r="BO8">
-        <v>3.55</v>
+        <v>1.04</v>
       </c>
       <c r="BP8">
         <v>1000</v>
       </c>
       <c r="BQ8">
-        <v>4.6</v>
+        <v>1.04</v>
       </c>
       <c r="BR8">
         <v>1000</v>
       </c>
       <c r="BS8">
-        <v>4.7</v>
+        <v>1.04</v>
       </c>
       <c r="BT8">
-        <v>4.6</v>
+        <v>1000</v>
       </c>
       <c r="BU8">
-        <v>3.1</v>
+        <v>1.04</v>
       </c>
       <c r="BV8">
-        <v>12.5</v>
+        <v>1000</v>
       </c>
       <c r="BW8">
-        <v>3.5</v>
+        <v>1.04</v>
       </c>
       <c r="BX8">
-        <v>36</v>
+        <v>1000</v>
       </c>
       <c r="BY8">
-        <v>4.3</v>
+        <v>1.04</v>
       </c>
       <c r="BZ8">
-        <v>26</v>
+        <v>1000</v>
       </c>
       <c r="CA8">
-        <v>4.1</v>
+        <v>1.04</v>
       </c>
       <c r="CB8" t="s">
-        <v>121</v>
+        <v>111</v>
       </c>
     </row>
     <row r="9" spans="1:80">
       <c r="A9" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="B9" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="C9" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="D9" t="s">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="E9" t="s">
-        <v>116</v>
+        <v>109</v>
       </c>
       <c r="F9">
-        <v>2.5</v>
+        <v>2.82</v>
       </c>
       <c r="G9">
-        <v>2.74</v>
+        <v>2.9</v>
       </c>
       <c r="H9">
-        <v>3.4</v>
+        <v>2.84</v>
       </c>
       <c r="I9">
-        <v>3.95</v>
+        <v>2.9</v>
       </c>
       <c r="J9">
-        <v>2.68</v>
+        <v>3.2</v>
       </c>
       <c r="K9">
-        <v>3.05</v>
+        <v>3.45</v>
       </c>
       <c r="L9">
-        <v>1.66</v>
+        <v>1.45</v>
       </c>
       <c r="M9">
-        <v>1.16</v>
+        <v>1.09</v>
       </c>
       <c r="N9">
-        <v>2.26</v>
+        <v>3.1</v>
       </c>
       <c r="O9">
-        <v>1.66</v>
+        <v>1.43</v>
       </c>
       <c r="P9">
-        <v>1.4</v>
+        <v>1.69</v>
       </c>
       <c r="Q9">
-        <v>3.05</v>
+        <v>2.28</v>
       </c>
       <c r="R9">
-        <v>1.13</v>
+        <v>1.26</v>
       </c>
       <c r="S9">
-        <v>6</v>
+        <v>4.3</v>
       </c>
       <c r="T9">
-        <v>2.34</v>
+        <v>1.93</v>
       </c>
       <c r="U9">
-        <v>1.63</v>
+        <v>1.99</v>
       </c>
       <c r="V9">
-        <v>1.34</v>
+        <v>1.52</v>
       </c>
       <c r="W9">
-        <v>1.58</v>
+        <v>1.52</v>
       </c>
       <c r="X9">
-        <v>8.199999999999999</v>
+        <v>14.5</v>
       </c>
       <c r="Y9">
-        <v>9</v>
+        <v>9.4</v>
       </c>
       <c r="Z9">
-        <v>27</v>
+        <v>17.5</v>
       </c>
       <c r="AA9">
-        <v>500</v>
+        <v>65</v>
       </c>
       <c r="AB9">
-        <v>7.2</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AC9">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="AD9">
-        <v>18.5</v>
+        <v>13</v>
       </c>
       <c r="AE9">
-        <v>85</v>
+        <v>50</v>
       </c>
       <c r="AF9">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="AG9">
-        <v>14.5</v>
+        <v>13.5</v>
       </c>
       <c r="AH9">
-        <v>29</v>
+        <v>19.5</v>
       </c>
       <c r="AI9">
-        <v>540</v>
+        <v>55</v>
       </c>
       <c r="AJ9">
         <v>55</v>
       </c>
       <c r="AK9">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="AL9">
-        <v>230</v>
+        <v>70</v>
       </c>
       <c r="AM9">
-        <v>500</v>
+        <v>580</v>
       </c>
       <c r="AN9">
-        <v>65</v>
+        <v>40</v>
       </c>
       <c r="AO9">
-        <v>500</v>
+        <v>36</v>
       </c>
       <c r="AP9">
-        <v>5.4</v>
+        <v>10</v>
       </c>
       <c r="AQ9">
-        <v>7.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AR9">
-        <v>19</v>
+        <v>15.5</v>
       </c>
       <c r="AS9">
-        <v>7.2</v>
+        <v>38</v>
       </c>
       <c r="AT9">
-        <v>5.9</v>
+        <v>8.6</v>
       </c>
       <c r="AU9">
-        <v>6</v>
+        <v>6.6</v>
       </c>
       <c r="AV9">
+        <v>11</v>
+      </c>
+      <c r="AW9">
         <v>14.5</v>
       </c>
-      <c r="AW9">
-        <v>23</v>
-      </c>
       <c r="AX9">
-        <v>12.5</v>
+        <v>16.5</v>
       </c>
       <c r="AY9">
         <v>11.5</v>
       </c>
       <c r="AZ9">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="BA9">
-        <v>7.4</v>
+        <v>38</v>
       </c>
       <c r="BB9">
         <v>29</v>
       </c>
       <c r="BC9">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="BD9">
-        <v>7.2</v>
+        <v>44</v>
       </c>
       <c r="BE9">
-        <v>7.6</v>
+        <v>13</v>
       </c>
       <c r="BF9">
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="BG9">
-        <v>7.4</v>
+        <v>12</v>
       </c>
       <c r="BH9">
-        <v>2.76</v>
+        <v>3.05</v>
       </c>
       <c r="BI9">
-        <v>2.02</v>
+        <v>2.8</v>
       </c>
       <c r="BJ9">
-        <v>15</v>
+        <v>10.5</v>
       </c>
       <c r="BK9">
-        <v>3.9</v>
+        <v>6.2</v>
       </c>
       <c r="BL9">
         <v>1000</v>
       </c>
       <c r="BM9">
-        <v>5.2</v>
+        <v>14</v>
       </c>
       <c r="BN9">
-        <v>6.2</v>
+        <v>5.9</v>
       </c>
       <c r="BO9">
-        <v>4</v>
+        <v>4.5</v>
       </c>
       <c r="BP9">
-        <v>32</v>
+        <v>25</v>
       </c>
       <c r="BQ9">
-        <v>4.5</v>
+        <v>9.6</v>
       </c>
       <c r="BR9">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="BS9">
-        <v>4.9</v>
+        <v>11</v>
       </c>
       <c r="BT9">
-        <v>7.8</v>
+        <v>5.7</v>
       </c>
       <c r="BU9">
-        <v>4.9</v>
+        <v>4.3</v>
       </c>
       <c r="BV9">
-        <v>48</v>
+        <v>23</v>
       </c>
       <c r="BW9">
-        <v>4.7</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BX9">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="BY9">
-        <v>4.9</v>
+        <v>11</v>
       </c>
       <c r="BZ9">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="CA9">
-        <v>4.9</v>
+        <v>10.5</v>
       </c>
       <c r="CB9" t="s">
-        <v>121</v>
+        <v>111</v>
       </c>
     </row>
     <row r="10" spans="1:80">
@@ -2897,967 +2867,241 @@
         <v>85</v>
       </c>
       <c r="B10" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="C10" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="D10" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="E10" t="s">
-        <v>117</v>
+        <v>110</v>
       </c>
       <c r="F10">
-        <v>2.42</v>
+        <v>2.22</v>
       </c>
       <c r="G10">
-        <v>2.58</v>
+        <v>2.44</v>
       </c>
       <c r="H10">
-        <v>3.5</v>
+        <v>3.35</v>
       </c>
       <c r="I10">
-        <v>4.5</v>
+        <v>3.9</v>
       </c>
       <c r="J10">
-        <v>2.76</v>
+        <v>3.25</v>
       </c>
       <c r="K10">
-        <v>3.1</v>
+        <v>3.6</v>
       </c>
       <c r="L10">
-        <v>1.01</v>
+        <v>1.44</v>
       </c>
       <c r="M10">
-        <v>1.11</v>
+        <v>1.08</v>
       </c>
       <c r="N10">
-        <v>2.28</v>
+        <v>3.25</v>
       </c>
       <c r="O10">
-        <v>1.62</v>
+        <v>1.37</v>
       </c>
       <c r="P10">
-        <v>1.43</v>
+        <v>1.77</v>
       </c>
       <c r="Q10">
-        <v>2.78</v>
+        <v>2.08</v>
       </c>
       <c r="R10">
-        <v>1.13</v>
+        <v>1.28</v>
       </c>
       <c r="S10">
-        <v>4.8</v>
+        <v>3.85</v>
       </c>
       <c r="T10">
-        <v>2.14</v>
+        <v>1.84</v>
       </c>
       <c r="U10">
-        <v>1.57</v>
+        <v>2</v>
       </c>
       <c r="V10">
-        <v>1.29</v>
+        <v>1.37</v>
       </c>
       <c r="W10">
-        <v>1.63</v>
+        <v>1.69</v>
       </c>
       <c r="X10">
-        <v>970</v>
+        <v>14</v>
       </c>
       <c r="Y10">
+        <v>14.5</v>
+      </c>
+      <c r="Z10">
+        <v>26</v>
+      </c>
+      <c r="AA10">
+        <v>75</v>
+      </c>
+      <c r="AB10">
+        <v>9.4</v>
+      </c>
+      <c r="AC10">
+        <v>8</v>
+      </c>
+      <c r="AD10">
+        <v>16</v>
+      </c>
+      <c r="AE10">
+        <v>55</v>
+      </c>
+      <c r="AF10">
+        <v>15</v>
+      </c>
+      <c r="AG10">
         <v>13</v>
       </c>
-      <c r="Z10">
+      <c r="AH10">
+        <v>22</v>
+      </c>
+      <c r="AI10">
+        <v>65</v>
+      </c>
+      <c r="AJ10">
+        <v>34</v>
+      </c>
+      <c r="AK10">
+        <v>30</v>
+      </c>
+      <c r="AL10">
+        <v>48</v>
+      </c>
+      <c r="AM10">
+        <v>130</v>
+      </c>
+      <c r="AN10">
+        <v>24</v>
+      </c>
+      <c r="AO10">
         <v>55</v>
       </c>
-      <c r="AA10">
-        <v>900</v>
-      </c>
-      <c r="AB10">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AC10">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AD10">
-        <v>25</v>
-      </c>
-      <c r="AE10">
-        <v>500</v>
-      </c>
-      <c r="AF10">
+      <c r="AP10">
+        <v>9.4</v>
+      </c>
+      <c r="AQ10">
+        <v>10.5</v>
+      </c>
+      <c r="AR10">
         <v>21</v>
       </c>
-      <c r="AG10">
-        <v>19.5</v>
-      </c>
-      <c r="AH10">
-        <v>85</v>
-      </c>
-      <c r="AI10">
-        <v>540</v>
-      </c>
-      <c r="AJ10">
-        <v>220</v>
-      </c>
-      <c r="AK10">
-        <v>500</v>
-      </c>
-      <c r="AL10">
-        <v>500</v>
-      </c>
-      <c r="AM10">
-        <v>500</v>
-      </c>
-      <c r="AN10">
-        <v>500</v>
-      </c>
-      <c r="AO10">
-        <v>1000</v>
-      </c>
-      <c r="AP10">
-        <v>3.85</v>
-      </c>
-      <c r="AQ10">
-        <v>5.9</v>
-      </c>
-      <c r="AR10">
-        <v>14.5</v>
-      </c>
       <c r="AS10">
-        <v>2.54</v>
+        <v>6.4</v>
       </c>
       <c r="AT10">
-        <v>4.6</v>
+        <v>7.8</v>
       </c>
       <c r="AU10">
-        <v>4.6</v>
+        <v>6.6</v>
       </c>
       <c r="AV10">
+        <v>12.5</v>
+      </c>
+      <c r="AW10">
+        <v>6.2</v>
+      </c>
+      <c r="AX10">
         <v>11</v>
       </c>
-      <c r="AW10">
-        <v>2.5</v>
-      </c>
-      <c r="AX10">
-        <v>7.2</v>
-      </c>
       <c r="AY10">
-        <v>8.4</v>
+        <v>9.6</v>
       </c>
       <c r="AZ10">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="BA10">
-        <v>2.54</v>
+        <v>6.4</v>
       </c>
       <c r="BB10">
-        <v>16</v>
+        <v>5.8</v>
       </c>
       <c r="BC10">
-        <v>18</v>
+        <v>5.7</v>
       </c>
       <c r="BD10">
-        <v>2.54</v>
+        <v>6.2</v>
       </c>
       <c r="BE10">
-        <v>2.56</v>
+        <v>6.6</v>
       </c>
       <c r="BF10">
+        <v>17</v>
+      </c>
+      <c r="BG10">
+        <v>6.2</v>
+      </c>
+      <c r="BH10">
+        <v>3.3</v>
+      </c>
+      <c r="BI10">
+        <v>2.64</v>
+      </c>
+      <c r="BJ10">
+        <v>10.5</v>
+      </c>
+      <c r="BK10">
+        <v>5.1</v>
+      </c>
+      <c r="BL10">
+        <v>1000</v>
+      </c>
+      <c r="BM10">
         <v>9.4</v>
       </c>
-      <c r="BG10">
-        <v>2.56</v>
-      </c>
-      <c r="BH10">
-        <v>1000</v>
-      </c>
-      <c r="BI10">
-        <v>1.04</v>
-      </c>
-      <c r="BJ10">
-        <v>1000</v>
-      </c>
-      <c r="BK10">
-        <v>1.04</v>
-      </c>
-      <c r="BL10">
-        <v>1000</v>
-      </c>
-      <c r="BM10">
-        <v>1.04</v>
-      </c>
       <c r="BN10">
-        <v>1000</v>
+        <v>5.3</v>
       </c>
       <c r="BO10">
-        <v>1.04</v>
+        <v>4</v>
       </c>
       <c r="BP10">
-        <v>1000</v>
+        <v>18.5</v>
       </c>
       <c r="BQ10">
-        <v>1.04</v>
+        <v>6.4</v>
       </c>
       <c r="BR10">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="BS10">
-        <v>1.04</v>
+        <v>7.8</v>
       </c>
       <c r="BT10">
-        <v>1000</v>
+        <v>7</v>
       </c>
       <c r="BU10">
-        <v>1.04</v>
+        <v>5.2</v>
       </c>
       <c r="BV10">
         <v>1000</v>
       </c>
       <c r="BW10">
-        <v>1.04</v>
+        <v>7.6</v>
       </c>
       <c r="BX10">
         <v>1000</v>
       </c>
       <c r="BY10">
-        <v>1.04</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BZ10">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="CA10">
-        <v>1.04</v>
+        <v>7.6</v>
       </c>
       <c r="CB10" t="s">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="11" spans="1:80">
-      <c r="A11" t="s">
-        <v>86</v>
-      </c>
-      <c r="B11" t="s">
-        <v>89</v>
-      </c>
-      <c r="C11" t="s">
-        <v>94</v>
-      </c>
-      <c r="D11" t="s">
-        <v>106</v>
-      </c>
-      <c r="E11" t="s">
-        <v>118</v>
-      </c>
-      <c r="F11">
-        <v>1.76</v>
-      </c>
-      <c r="G11">
-        <v>1.84</v>
-      </c>
-      <c r="H11">
-        <v>5.7</v>
-      </c>
-      <c r="I11">
-        <v>6</v>
-      </c>
-      <c r="J11">
-        <v>3.55</v>
-      </c>
-      <c r="K11">
-        <v>3.8</v>
-      </c>
-      <c r="L11">
-        <v>1.41</v>
-      </c>
-      <c r="M11">
-        <v>1.1</v>
-      </c>
-      <c r="N11">
-        <v>2.98</v>
-      </c>
-      <c r="O11">
-        <v>1.46</v>
-      </c>
-      <c r="P11">
-        <v>1.69</v>
-      </c>
-      <c r="Q11">
-        <v>2.36</v>
-      </c>
-      <c r="R11">
-        <v>1.24</v>
-      </c>
-      <c r="S11">
-        <v>4.6</v>
-      </c>
-      <c r="T11">
-        <v>2.12</v>
-      </c>
-      <c r="U11">
-        <v>1.79</v>
-      </c>
-      <c r="V11">
-        <v>1.2</v>
-      </c>
-      <c r="W11">
-        <v>2.18</v>
-      </c>
-      <c r="X11">
-        <v>11</v>
-      </c>
-      <c r="Y11">
-        <v>15.5</v>
-      </c>
-      <c r="Z11">
-        <v>46</v>
-      </c>
-      <c r="AA11">
-        <v>900</v>
-      </c>
-      <c r="AB11">
-        <v>6.6</v>
-      </c>
-      <c r="AC11">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AD11">
-        <v>23</v>
-      </c>
-      <c r="AE11">
-        <v>120</v>
-      </c>
-      <c r="AF11">
-        <v>10</v>
-      </c>
-      <c r="AG11">
-        <v>10.5</v>
-      </c>
-      <c r="AH11">
-        <v>26</v>
-      </c>
-      <c r="AI11">
-        <v>260</v>
-      </c>
-      <c r="AJ11">
-        <v>21</v>
-      </c>
-      <c r="AK11">
-        <v>22</v>
-      </c>
-      <c r="AL11">
-        <v>55</v>
-      </c>
-      <c r="AM11">
-        <v>580</v>
-      </c>
-      <c r="AN11">
-        <v>17</v>
-      </c>
-      <c r="AO11">
-        <v>700</v>
-      </c>
-      <c r="AP11">
-        <v>9.6</v>
-      </c>
-      <c r="AQ11">
-        <v>12.5</v>
-      </c>
-      <c r="AR11">
-        <v>30</v>
-      </c>
-      <c r="AS11">
-        <v>13.5</v>
-      </c>
-      <c r="AT11">
-        <v>6</v>
-      </c>
-      <c r="AU11">
-        <v>7.4</v>
-      </c>
-      <c r="AV11">
-        <v>20</v>
-      </c>
-      <c r="AW11">
-        <v>13</v>
-      </c>
-      <c r="AX11">
-        <v>8.4</v>
-      </c>
-      <c r="AY11">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AZ11">
-        <v>20</v>
-      </c>
-      <c r="BA11">
-        <v>13</v>
-      </c>
-      <c r="BB11">
-        <v>18</v>
-      </c>
-      <c r="BC11">
-        <v>18.5</v>
-      </c>
-      <c r="BD11">
-        <v>40</v>
-      </c>
-      <c r="BE11">
-        <v>13.5</v>
-      </c>
-      <c r="BF11">
-        <v>15</v>
-      </c>
-      <c r="BG11">
-        <v>13.5</v>
-      </c>
-      <c r="BH11">
-        <v>1000</v>
-      </c>
-      <c r="BI11">
-        <v>2.52</v>
-      </c>
-      <c r="BJ11">
-        <v>1000</v>
-      </c>
-      <c r="BK11">
-        <v>1.01</v>
-      </c>
-      <c r="BL11">
-        <v>1000</v>
-      </c>
-      <c r="BM11">
-        <v>1.01</v>
-      </c>
-      <c r="BN11">
-        <v>1000</v>
-      </c>
-      <c r="BO11">
-        <v>1.01</v>
-      </c>
-      <c r="BP11">
-        <v>1000</v>
-      </c>
-      <c r="BQ11">
-        <v>1.01</v>
-      </c>
-      <c r="BR11">
-        <v>1000</v>
-      </c>
-      <c r="BS11">
-        <v>1.01</v>
-      </c>
-      <c r="BT11">
-        <v>1000</v>
-      </c>
-      <c r="BU11">
-        <v>1.01</v>
-      </c>
-      <c r="BV11">
-        <v>1000</v>
-      </c>
-      <c r="BW11">
-        <v>1.01</v>
-      </c>
-      <c r="BX11">
-        <v>1000</v>
-      </c>
-      <c r="BY11">
-        <v>1.01</v>
-      </c>
-      <c r="BZ11">
-        <v>1000</v>
-      </c>
-      <c r="CA11">
-        <v>1.01</v>
-      </c>
-      <c r="CB11" t="s">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="12" spans="1:80">
-      <c r="A12" t="s">
-        <v>87</v>
-      </c>
-      <c r="B12" t="s">
-        <v>89</v>
-      </c>
-      <c r="C12" t="s">
-        <v>95</v>
-      </c>
-      <c r="D12" t="s">
-        <v>107</v>
-      </c>
-      <c r="E12" t="s">
-        <v>119</v>
-      </c>
-      <c r="F12">
-        <v>2.82</v>
-      </c>
-      <c r="G12">
-        <v>2.9</v>
-      </c>
-      <c r="H12">
-        <v>2.82</v>
-      </c>
-      <c r="I12">
-        <v>2.9</v>
-      </c>
-      <c r="J12">
-        <v>3.2</v>
-      </c>
-      <c r="K12">
-        <v>3.45</v>
-      </c>
-      <c r="L12">
-        <v>1.01</v>
-      </c>
-      <c r="M12">
-        <v>1.1</v>
-      </c>
-      <c r="N12">
-        <v>3</v>
-      </c>
-      <c r="O12">
-        <v>1.43</v>
-      </c>
-      <c r="P12">
-        <v>1.68</v>
-      </c>
-      <c r="Q12">
-        <v>2.28</v>
-      </c>
-      <c r="R12">
-        <v>1.26</v>
-      </c>
-      <c r="S12">
-        <v>4.3</v>
-      </c>
-      <c r="T12">
-        <v>1.93</v>
-      </c>
-      <c r="U12">
-        <v>1.96</v>
-      </c>
-      <c r="V12">
-        <v>1.52</v>
-      </c>
-      <c r="W12">
-        <v>1.52</v>
-      </c>
-      <c r="X12">
-        <v>14.5</v>
-      </c>
-      <c r="Y12">
-        <v>9.4</v>
-      </c>
-      <c r="Z12">
-        <v>18</v>
-      </c>
-      <c r="AA12">
-        <v>65</v>
-      </c>
-      <c r="AB12">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AC12">
-        <v>7.4</v>
-      </c>
-      <c r="AD12">
-        <v>13</v>
-      </c>
-      <c r="AE12">
-        <v>50</v>
-      </c>
-      <c r="AF12">
-        <v>19</v>
-      </c>
-      <c r="AG12">
-        <v>13.5</v>
-      </c>
-      <c r="AH12">
-        <v>19.5</v>
-      </c>
-      <c r="AI12">
-        <v>55</v>
-      </c>
-      <c r="AJ12">
-        <v>55</v>
-      </c>
-      <c r="AK12">
-        <v>50</v>
-      </c>
-      <c r="AL12">
-        <v>70</v>
-      </c>
-      <c r="AM12">
-        <v>580</v>
-      </c>
-      <c r="AN12">
-        <v>40</v>
-      </c>
-      <c r="AO12">
-        <v>36</v>
-      </c>
-      <c r="AP12">
-        <v>9.4</v>
-      </c>
-      <c r="AQ12">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AR12">
-        <v>15.5</v>
-      </c>
-      <c r="AS12">
-        <v>38</v>
-      </c>
-      <c r="AT12">
-        <v>8.6</v>
-      </c>
-      <c r="AU12">
-        <v>6.6</v>
-      </c>
-      <c r="AV12">
-        <v>11</v>
-      </c>
-      <c r="AW12">
-        <v>14.5</v>
-      </c>
-      <c r="AX12">
-        <v>16.5</v>
-      </c>
-      <c r="AY12">
-        <v>11.5</v>
-      </c>
-      <c r="AZ12">
-        <v>16</v>
-      </c>
-      <c r="BA12">
-        <v>38</v>
-      </c>
-      <c r="BB12">
-        <v>29</v>
-      </c>
-      <c r="BC12">
-        <v>16</v>
-      </c>
-      <c r="BD12">
-        <v>44</v>
-      </c>
-      <c r="BE12">
-        <v>13</v>
-      </c>
-      <c r="BF12">
-        <v>10.5</v>
-      </c>
-      <c r="BG12">
-        <v>11.5</v>
-      </c>
-      <c r="BH12">
-        <v>3.05</v>
-      </c>
-      <c r="BI12">
-        <v>2.8</v>
-      </c>
-      <c r="BJ12">
-        <v>10.5</v>
-      </c>
-      <c r="BK12">
-        <v>6.2</v>
-      </c>
-      <c r="BL12">
-        <v>1000</v>
-      </c>
-      <c r="BM12">
-        <v>14</v>
-      </c>
-      <c r="BN12">
-        <v>5.9</v>
-      </c>
-      <c r="BO12">
-        <v>4.5</v>
-      </c>
-      <c r="BP12">
-        <v>25</v>
-      </c>
-      <c r="BQ12">
-        <v>9.6</v>
-      </c>
-      <c r="BR12">
-        <v>40</v>
-      </c>
-      <c r="BS12">
-        <v>11</v>
-      </c>
-      <c r="BT12">
-        <v>5.7</v>
-      </c>
-      <c r="BU12">
-        <v>4.3</v>
-      </c>
-      <c r="BV12">
-        <v>23</v>
-      </c>
-      <c r="BW12">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="BX12">
-        <v>40</v>
-      </c>
-      <c r="BY12">
-        <v>11</v>
-      </c>
-      <c r="BZ12">
-        <v>36</v>
-      </c>
-      <c r="CA12">
-        <v>10.5</v>
-      </c>
-      <c r="CB12" t="s">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="13" spans="1:80">
-      <c r="A13" t="s">
-        <v>88</v>
-      </c>
-      <c r="B13" t="s">
-        <v>89</v>
-      </c>
-      <c r="C13" t="s">
-        <v>96</v>
-      </c>
-      <c r="D13" t="s">
-        <v>108</v>
-      </c>
-      <c r="E13" t="s">
-        <v>120</v>
-      </c>
-      <c r="F13">
-        <v>2.22</v>
-      </c>
-      <c r="G13">
-        <v>2.44</v>
-      </c>
-      <c r="H13">
-        <v>3.35</v>
-      </c>
-      <c r="I13">
-        <v>3.9</v>
-      </c>
-      <c r="J13">
-        <v>3.25</v>
-      </c>
-      <c r="K13">
-        <v>3.6</v>
-      </c>
-      <c r="L13">
-        <v>1.44</v>
-      </c>
-      <c r="M13">
-        <v>1.08</v>
-      </c>
-      <c r="N13">
-        <v>3.25</v>
-      </c>
-      <c r="O13">
-        <v>1.37</v>
-      </c>
-      <c r="P13">
-        <v>1.77</v>
-      </c>
-      <c r="Q13">
-        <v>2.08</v>
-      </c>
-      <c r="R13">
-        <v>1.28</v>
-      </c>
-      <c r="S13">
-        <v>3.8</v>
-      </c>
-      <c r="T13">
-        <v>1.83</v>
-      </c>
-      <c r="U13">
-        <v>2</v>
-      </c>
-      <c r="V13">
-        <v>1.37</v>
-      </c>
-      <c r="W13">
-        <v>1.69</v>
-      </c>
-      <c r="X13">
-        <v>14</v>
-      </c>
-      <c r="Y13">
-        <v>14.5</v>
-      </c>
-      <c r="Z13">
-        <v>26</v>
-      </c>
-      <c r="AA13">
-        <v>75</v>
-      </c>
-      <c r="AB13">
-        <v>9.4</v>
-      </c>
-      <c r="AC13">
-        <v>8</v>
-      </c>
-      <c r="AD13">
-        <v>16</v>
-      </c>
-      <c r="AE13">
-        <v>55</v>
-      </c>
-      <c r="AF13">
-        <v>15</v>
-      </c>
-      <c r="AG13">
-        <v>13</v>
-      </c>
-      <c r="AH13">
-        <v>22</v>
-      </c>
-      <c r="AI13">
-        <v>65</v>
-      </c>
-      <c r="AJ13">
-        <v>34</v>
-      </c>
-      <c r="AK13">
-        <v>30</v>
-      </c>
-      <c r="AL13">
-        <v>48</v>
-      </c>
-      <c r="AM13">
-        <v>130</v>
-      </c>
-      <c r="AN13">
-        <v>24</v>
-      </c>
-      <c r="AO13">
-        <v>55</v>
-      </c>
-      <c r="AP13">
-        <v>9.4</v>
-      </c>
-      <c r="AQ13">
-        <v>10.5</v>
-      </c>
-      <c r="AR13">
-        <v>21</v>
-      </c>
-      <c r="AS13">
-        <v>6.4</v>
-      </c>
-      <c r="AT13">
-        <v>7.8</v>
-      </c>
-      <c r="AU13">
-        <v>6.6</v>
-      </c>
-      <c r="AV13">
-        <v>12.5</v>
-      </c>
-      <c r="AW13">
-        <v>6.2</v>
-      </c>
-      <c r="AX13">
-        <v>11</v>
-      </c>
-      <c r="AY13">
-        <v>9.6</v>
-      </c>
-      <c r="AZ13">
-        <v>14</v>
-      </c>
-      <c r="BA13">
-        <v>6.4</v>
-      </c>
-      <c r="BB13">
-        <v>5.8</v>
-      </c>
-      <c r="BC13">
-        <v>5.7</v>
-      </c>
-      <c r="BD13">
-        <v>6.2</v>
-      </c>
-      <c r="BE13">
-        <v>6.6</v>
-      </c>
-      <c r="BF13">
-        <v>17</v>
-      </c>
-      <c r="BG13">
-        <v>6.2</v>
-      </c>
-      <c r="BH13">
-        <v>3.3</v>
-      </c>
-      <c r="BI13">
-        <v>2.64</v>
-      </c>
-      <c r="BJ13">
-        <v>10.5</v>
-      </c>
-      <c r="BK13">
-        <v>5.1</v>
-      </c>
-      <c r="BL13">
-        <v>1000</v>
-      </c>
-      <c r="BM13">
-        <v>9.4</v>
-      </c>
-      <c r="BN13">
-        <v>5.3</v>
-      </c>
-      <c r="BO13">
-        <v>4</v>
-      </c>
-      <c r="BP13">
-        <v>18.5</v>
-      </c>
-      <c r="BQ13">
-        <v>6.4</v>
-      </c>
-      <c r="BR13">
-        <v>36</v>
-      </c>
-      <c r="BS13">
-        <v>7.8</v>
-      </c>
-      <c r="BT13">
-        <v>7</v>
-      </c>
-      <c r="BU13">
-        <v>5.2</v>
-      </c>
-      <c r="BV13">
-        <v>1000</v>
-      </c>
-      <c r="BW13">
-        <v>7.6</v>
-      </c>
-      <c r="BX13">
-        <v>1000</v>
-      </c>
-      <c r="BY13">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="BZ13">
-        <v>34</v>
-      </c>
-      <c r="CA13">
-        <v>7.6</v>
-      </c>
-      <c r="CB13" t="s">
-        <v>121</v>
+        <v>111</v>
       </c>
     </row>
   </sheetData>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-08-11.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-08-11.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="134" uniqueCount="112">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="128" uniqueCount="108">
   <si>
     <t>League</t>
   </si>
@@ -256,9 +256,6 @@
     <t>SnapshotTS</t>
   </si>
   <si>
-    <t>Argentinian Primera Division</t>
-  </si>
-  <si>
     <t>Swedish Superettan</t>
   </si>
   <si>
@@ -277,9 +274,6 @@
     <t>2026-08-11</t>
   </si>
   <si>
-    <t>00:15:00</t>
-  </si>
-  <si>
     <t>17:00:00</t>
   </si>
   <si>
@@ -295,9 +289,6 @@
     <t>23:00:00</t>
   </si>
   <si>
-    <t>Union Santa Fe</t>
-  </si>
-  <si>
     <t>Helsingborgs</t>
   </si>
   <si>
@@ -322,9 +313,6 @@
     <t>Puerto Montt</t>
   </si>
   <si>
-    <t>Central Cordoba (SdE)</t>
-  </si>
-  <si>
     <t>Varnamo</t>
   </si>
   <si>
@@ -349,7 +337,7 @@
     <t>Union Espanola</t>
   </si>
   <si>
-    <t>2026-08-10 23:12:02</t>
+    <t>2026-08-11 01:19:23</t>
   </si>
 </sst>
 </file>
@@ -681,7 +669,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:CB10"/>
+  <dimension ref="A1:CB9"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:80">
@@ -931,232 +919,232 @@
         <v>80</v>
       </c>
       <c r="B2" t="s">
+        <v>85</v>
+      </c>
+      <c r="C2" t="s">
         <v>86</v>
       </c>
-      <c r="C2" t="s">
-        <v>87</v>
-      </c>
       <c r="D2" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="E2" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="F2">
-        <v>1000</v>
+        <v>2.44</v>
       </c>
       <c r="G2">
-        <v>1000</v>
+        <v>2.48</v>
       </c>
       <c r="H2">
-        <v>1.06</v>
+        <v>3</v>
       </c>
       <c r="I2">
-        <v>1.08</v>
+        <v>3.05</v>
       </c>
       <c r="J2">
+        <v>3.75</v>
+      </c>
+      <c r="K2">
+        <v>3.9</v>
+      </c>
+      <c r="L2">
+        <v>1.33</v>
+      </c>
+      <c r="M2">
+        <v>1.04</v>
+      </c>
+      <c r="N2">
+        <v>5.2</v>
+      </c>
+      <c r="O2">
+        <v>1.22</v>
+      </c>
+      <c r="P2">
+        <v>2.4</v>
+      </c>
+      <c r="Q2">
+        <v>1.69</v>
+      </c>
+      <c r="R2">
+        <v>1.56</v>
+      </c>
+      <c r="S2">
+        <v>2.72</v>
+      </c>
+      <c r="T2">
+        <v>1.58</v>
+      </c>
+      <c r="U2">
+        <v>2.6</v>
+      </c>
+      <c r="V2">
+        <v>1.48</v>
+      </c>
+      <c r="W2">
+        <v>1.67</v>
+      </c>
+      <c r="X2">
+        <v>21</v>
+      </c>
+      <c r="Y2">
+        <v>20</v>
+      </c>
+      <c r="Z2">
+        <v>23</v>
+      </c>
+      <c r="AA2">
+        <v>50</v>
+      </c>
+      <c r="AB2">
+        <v>14.5</v>
+      </c>
+      <c r="AC2">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AD2">
         <v>13.5</v>
       </c>
-      <c r="K2">
-        <v>22</v>
-      </c>
-      <c r="L2">
-        <v>0</v>
-      </c>
-      <c r="M2">
-        <v>0</v>
-      </c>
-      <c r="N2">
-        <v>0</v>
-      </c>
-      <c r="O2">
-        <v>0</v>
-      </c>
-      <c r="P2">
-        <v>0</v>
-      </c>
-      <c r="Q2">
-        <v>0</v>
-      </c>
-      <c r="R2">
-        <v>1.07</v>
-      </c>
-      <c r="S2">
-        <v>11.5</v>
-      </c>
-      <c r="T2">
-        <v>0</v>
-      </c>
-      <c r="U2">
-        <v>0</v>
-      </c>
-      <c r="V2">
-        <v>1.01</v>
-      </c>
-      <c r="W2">
-        <v>1.01</v>
-      </c>
-      <c r="X2">
-        <v>1000</v>
-      </c>
-      <c r="Y2">
-        <v>1000</v>
-      </c>
-      <c r="Z2">
-        <v>1000</v>
-      </c>
-      <c r="AA2">
-        <v>1000</v>
-      </c>
-      <c r="AB2">
-        <v>1000</v>
-      </c>
-      <c r="AC2">
-        <v>1000</v>
-      </c>
-      <c r="AD2">
-        <v>1.08</v>
-      </c>
       <c r="AE2">
-        <v>1000</v>
+        <v>48</v>
       </c>
       <c r="AF2">
-        <v>1000</v>
+        <v>18.5</v>
       </c>
       <c r="AG2">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="AH2">
-        <v>1000</v>
+        <v>14.5</v>
       </c>
       <c r="AI2">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AJ2">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AK2">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="AL2">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="AM2">
-        <v>1000</v>
+        <v>190</v>
       </c>
       <c r="AN2">
-        <v>1000</v>
+        <v>14</v>
       </c>
       <c r="AO2">
-        <v>1000</v>
+        <v>20</v>
       </c>
       <c r="AP2">
-        <v>1.26</v>
+        <v>18.5</v>
       </c>
       <c r="AQ2">
-        <v>1.26</v>
+        <v>15</v>
       </c>
       <c r="AR2">
-        <v>1.26</v>
+        <v>19</v>
       </c>
       <c r="AS2">
-        <v>1.26</v>
+        <v>42</v>
       </c>
       <c r="AT2">
-        <v>1.26</v>
+        <v>13</v>
       </c>
       <c r="AU2">
-        <v>1.26</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AV2">
-        <v>1.01</v>
+        <v>12</v>
       </c>
       <c r="AW2">
-        <v>7.4</v>
+        <v>25</v>
       </c>
       <c r="AX2">
-        <v>1.26</v>
+        <v>16.5</v>
       </c>
       <c r="AY2">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="AZ2">
         <v>13.5</v>
       </c>
       <c r="BA2">
-        <v>1.26</v>
+        <v>30</v>
       </c>
       <c r="BB2">
-        <v>1.26</v>
+        <v>30</v>
       </c>
       <c r="BC2">
-        <v>1.26</v>
+        <v>20</v>
       </c>
       <c r="BD2">
-        <v>1.26</v>
+        <v>27</v>
       </c>
       <c r="BE2">
-        <v>1.45</v>
+        <v>48</v>
       </c>
       <c r="BF2">
-        <v>1.26</v>
+        <v>13</v>
       </c>
       <c r="BG2">
+        <v>18</v>
+      </c>
+      <c r="BH2">
+        <v>4.1</v>
+      </c>
+      <c r="BI2">
+        <v>3.65</v>
+      </c>
+      <c r="BJ2">
+        <v>8.6</v>
+      </c>
+      <c r="BK2">
+        <v>5.6</v>
+      </c>
+      <c r="BL2">
+        <v>1000</v>
+      </c>
+      <c r="BM2">
+        <v>13.5</v>
+      </c>
+      <c r="BN2">
+        <v>5.7</v>
+      </c>
+      <c r="BO2">
+        <v>4.9</v>
+      </c>
+      <c r="BP2">
+        <v>23</v>
+      </c>
+      <c r="BQ2">
         <v>8.199999999999999</v>
       </c>
-      <c r="BH2">
-        <v>0</v>
-      </c>
-      <c r="BI2">
-        <v>0</v>
-      </c>
-      <c r="BJ2">
-        <v>0</v>
-      </c>
-      <c r="BK2">
-        <v>0</v>
-      </c>
-      <c r="BL2">
-        <v>0</v>
-      </c>
-      <c r="BM2">
-        <v>0</v>
-      </c>
-      <c r="BN2">
-        <v>0</v>
-      </c>
-      <c r="BO2">
-        <v>0</v>
-      </c>
-      <c r="BP2">
-        <v>0</v>
-      </c>
-      <c r="BQ2">
-        <v>0</v>
-      </c>
       <c r="BR2">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="BS2">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="BT2">
-        <v>0</v>
+        <v>6.4</v>
       </c>
       <c r="BU2">
-        <v>0</v>
+        <v>5.8</v>
       </c>
       <c r="BV2">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW2">
-        <v>0</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BX2">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY2">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="BZ2">
         <v>0</v>
@@ -1165,7 +1153,7 @@
         <v>0</v>
       </c>
       <c r="CB2" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
     </row>
     <row r="3" spans="1:80">
@@ -1173,865 +1161,865 @@
         <v>81</v>
       </c>
       <c r="B3" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="C3" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="D3" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="E3" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="F3">
-        <v>2.42</v>
+        <v>2.88</v>
       </c>
       <c r="G3">
-        <v>2.5</v>
+        <v>3.15</v>
       </c>
       <c r="H3">
-        <v>2.96</v>
+        <v>2.92</v>
       </c>
       <c r="I3">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="J3">
-        <v>3.75</v>
+        <v>2.82</v>
       </c>
       <c r="K3">
-        <v>3.9</v>
+        <v>3.05</v>
       </c>
       <c r="L3">
-        <v>1.33</v>
+        <v>1.65</v>
       </c>
       <c r="M3">
-        <v>1.04</v>
+        <v>1.16</v>
       </c>
       <c r="N3">
-        <v>5.2</v>
+        <v>2.4</v>
       </c>
       <c r="O3">
-        <v>1.22</v>
+        <v>1.64</v>
       </c>
       <c r="P3">
-        <v>2.38</v>
+        <v>1.45</v>
       </c>
       <c r="Q3">
-        <v>1.65</v>
+        <v>3.05</v>
       </c>
       <c r="R3">
-        <v>1.57</v>
+        <v>1.16</v>
       </c>
       <c r="S3">
-        <v>2.6</v>
+        <v>6.4</v>
       </c>
       <c r="T3">
-        <v>1.56</v>
+        <v>2.2</v>
       </c>
       <c r="U3">
-        <v>2.6</v>
+        <v>1.7</v>
       </c>
       <c r="V3">
-        <v>1.47</v>
+        <v>1.45</v>
       </c>
       <c r="W3">
-        <v>1.66</v>
+        <v>1.46</v>
       </c>
       <c r="X3">
-        <v>21</v>
+        <v>7.8</v>
       </c>
       <c r="Y3">
-        <v>16.5</v>
+        <v>8.6</v>
       </c>
       <c r="Z3">
-        <v>24</v>
+        <v>19.5</v>
       </c>
       <c r="AA3">
-        <v>50</v>
+        <v>65</v>
       </c>
       <c r="AB3">
+        <v>8.4</v>
+      </c>
+      <c r="AC3">
+        <v>7.4</v>
+      </c>
+      <c r="AD3">
+        <v>15.5</v>
+      </c>
+      <c r="AE3">
+        <v>55</v>
+      </c>
+      <c r="AF3">
+        <v>22</v>
+      </c>
+      <c r="AG3">
+        <v>17.5</v>
+      </c>
+      <c r="AH3">
+        <v>26</v>
+      </c>
+      <c r="AI3">
+        <v>100</v>
+      </c>
+      <c r="AJ3">
+        <v>150</v>
+      </c>
+      <c r="AK3">
+        <v>120</v>
+      </c>
+      <c r="AL3">
+        <v>460</v>
+      </c>
+      <c r="AM3">
+        <v>500</v>
+      </c>
+      <c r="AN3">
+        <v>500</v>
+      </c>
+      <c r="AO3">
+        <v>70</v>
+      </c>
+      <c r="AP3">
+        <v>6.6</v>
+      </c>
+      <c r="AQ3">
+        <v>7</v>
+      </c>
+      <c r="AR3">
         <v>15</v>
       </c>
-      <c r="AC3">
-        <v>8.6</v>
-      </c>
-      <c r="AD3">
-        <v>13.5</v>
-      </c>
-      <c r="AE3">
-        <v>29</v>
-      </c>
-      <c r="AF3">
-        <v>19</v>
-      </c>
-      <c r="AG3">
-        <v>12.5</v>
-      </c>
-      <c r="AH3">
-        <v>14.5</v>
-      </c>
-      <c r="AI3">
-        <v>34</v>
-      </c>
-      <c r="AJ3">
-        <v>60</v>
-      </c>
-      <c r="AK3">
-        <v>23</v>
-      </c>
-      <c r="AL3">
-        <v>34</v>
-      </c>
-      <c r="AM3">
-        <v>60</v>
-      </c>
-      <c r="AN3">
-        <v>14</v>
-      </c>
-      <c r="AO3">
+      <c r="AS3">
         <v>20</v>
       </c>
-      <c r="AP3">
-        <v>18</v>
-      </c>
-      <c r="AQ3">
-        <v>15</v>
-      </c>
-      <c r="AR3">
-        <v>21</v>
-      </c>
-      <c r="AS3">
-        <v>42</v>
-      </c>
       <c r="AT3">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="AU3">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="AV3">
         <v>12</v>
       </c>
       <c r="AW3">
-        <v>26</v>
+        <v>7.2</v>
       </c>
       <c r="AX3">
-        <v>17</v>
+        <v>15.5</v>
       </c>
       <c r="AY3">
+        <v>12.5</v>
+      </c>
+      <c r="AZ3">
+        <v>20</v>
+      </c>
+      <c r="BA3">
+        <v>7.6</v>
+      </c>
+      <c r="BB3">
+        <v>7.4</v>
+      </c>
+      <c r="BC3">
+        <v>7.2</v>
+      </c>
+      <c r="BD3">
+        <v>7.6</v>
+      </c>
+      <c r="BE3">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BF3">
+        <v>7.4</v>
+      </c>
+      <c r="BG3">
+        <v>7.4</v>
+      </c>
+      <c r="BH3">
+        <v>2.6</v>
+      </c>
+      <c r="BI3">
+        <v>2.1</v>
+      </c>
+      <c r="BJ3">
+        <v>12.5</v>
+      </c>
+      <c r="BK3">
+        <v>5.9</v>
+      </c>
+      <c r="BL3">
+        <v>1000</v>
+      </c>
+      <c r="BM3">
         <v>10.5</v>
       </c>
-      <c r="AZ3">
-        <v>13.5</v>
-      </c>
-      <c r="BA3">
+      <c r="BN3">
+        <v>5.9</v>
+      </c>
+      <c r="BO3">
+        <v>4.3</v>
+      </c>
+      <c r="BP3">
         <v>30</v>
       </c>
-      <c r="BB3">
-        <v>29</v>
-      </c>
-      <c r="BC3">
-        <v>20</v>
-      </c>
-      <c r="BD3">
-        <v>27</v>
-      </c>
-      <c r="BE3">
-        <v>48</v>
-      </c>
-      <c r="BF3">
-        <v>12</v>
-      </c>
-      <c r="BG3">
-        <v>17.5</v>
-      </c>
-      <c r="BH3">
-        <v>4.1</v>
-      </c>
-      <c r="BI3">
-        <v>3.65</v>
-      </c>
-      <c r="BJ3">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="BK3">
-        <v>5.8</v>
-      </c>
-      <c r="BL3">
-        <v>1000</v>
-      </c>
-      <c r="BM3">
-        <v>14</v>
-      </c>
-      <c r="BN3">
-        <v>5.5</v>
-      </c>
-      <c r="BO3">
-        <v>4.9</v>
-      </c>
-      <c r="BP3">
-        <v>16</v>
-      </c>
       <c r="BQ3">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BR3">
+        <v>60</v>
+      </c>
+      <c r="BS3">
+        <v>9.6</v>
+      </c>
+      <c r="BT3">
+        <v>6.2</v>
+      </c>
+      <c r="BU3">
+        <v>4.5</v>
+      </c>
+      <c r="BV3">
+        <v>32</v>
+      </c>
+      <c r="BW3">
         <v>8.4</v>
       </c>
-      <c r="BR3">
-        <v>1000</v>
-      </c>
-      <c r="BS3">
-        <v>10</v>
-      </c>
-      <c r="BT3">
-        <v>6.6</v>
-      </c>
-      <c r="BU3">
-        <v>5.8</v>
-      </c>
-      <c r="BV3">
-        <v>1000</v>
-      </c>
-      <c r="BW3">
+      <c r="BX3">
+        <v>60</v>
+      </c>
+      <c r="BY3">
         <v>9.6</v>
       </c>
-      <c r="BX3">
-        <v>1000</v>
-      </c>
-      <c r="BY3">
-        <v>10.5</v>
-      </c>
       <c r="BZ3">
-        <v>0</v>
+        <v>65</v>
       </c>
       <c r="CA3">
-        <v>0</v>
+        <v>9.6</v>
       </c>
       <c r="CB3" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
     </row>
     <row r="4" spans="1:80">
       <c r="A4" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B4" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="C4" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="D4" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="E4" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="F4">
-        <v>2.9</v>
+        <v>7.2</v>
       </c>
       <c r="G4">
-        <v>3.25</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="H4">
-        <v>2.88</v>
+        <v>1.58</v>
       </c>
       <c r="I4">
-        <v>3.15</v>
+        <v>1.62</v>
       </c>
       <c r="J4">
-        <v>2.82</v>
+        <v>3.95</v>
       </c>
       <c r="K4">
-        <v>3.05</v>
+        <v>4.4</v>
       </c>
       <c r="L4">
-        <v>1.61</v>
+        <v>1.42</v>
       </c>
       <c r="M4">
-        <v>1.14</v>
+        <v>1.07</v>
       </c>
       <c r="N4">
-        <v>2.38</v>
+        <v>3.55</v>
       </c>
       <c r="O4">
-        <v>1.62</v>
+        <v>1.35</v>
       </c>
       <c r="P4">
-        <v>1.45</v>
+        <v>1.86</v>
       </c>
       <c r="Q4">
-        <v>2.84</v>
+        <v>2.06</v>
       </c>
       <c r="R4">
-        <v>1.16</v>
+        <v>1.32</v>
       </c>
       <c r="S4">
-        <v>6</v>
+        <v>3.75</v>
       </c>
       <c r="T4">
-        <v>2.2</v>
+        <v>2.12</v>
       </c>
       <c r="U4">
-        <v>1.71</v>
+        <v>1.77</v>
       </c>
       <c r="V4">
-        <v>1.47</v>
+        <v>2.6</v>
       </c>
       <c r="W4">
-        <v>1.44</v>
+        <v>1.15</v>
       </c>
       <c r="X4">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="Y4">
-        <v>9.6</v>
+        <v>8.6</v>
       </c>
       <c r="Z4">
+        <v>10</v>
+      </c>
+      <c r="AA4">
+        <v>17.5</v>
+      </c>
+      <c r="AB4">
+        <v>25</v>
+      </c>
+      <c r="AC4">
+        <v>11.5</v>
+      </c>
+      <c r="AD4">
+        <v>12</v>
+      </c>
+      <c r="AE4">
         <v>21</v>
       </c>
-      <c r="AA4">
-        <v>70</v>
-      </c>
-      <c r="AB4">
-        <v>8.6</v>
-      </c>
-      <c r="AC4">
-        <v>7.4</v>
-      </c>
-      <c r="AD4">
-        <v>15.5</v>
-      </c>
-      <c r="AE4">
-        <v>55</v>
-      </c>
       <c r="AF4">
-        <v>22</v>
+        <v>75</v>
       </c>
       <c r="AG4">
-        <v>17.5</v>
+        <v>34</v>
       </c>
       <c r="AH4">
         <v>30</v>
       </c>
       <c r="AI4">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="AJ4">
-        <v>150</v>
+        <v>700</v>
       </c>
       <c r="AK4">
-        <v>55</v>
+        <v>700</v>
       </c>
       <c r="AL4">
-        <v>100</v>
+        <v>700</v>
       </c>
       <c r="AM4">
-        <v>500</v>
+        <v>700</v>
       </c>
       <c r="AN4">
-        <v>210</v>
+        <v>700</v>
       </c>
       <c r="AO4">
-        <v>70</v>
+        <v>12</v>
       </c>
       <c r="AP4">
-        <v>6.6</v>
+        <v>10</v>
       </c>
       <c r="AQ4">
+        <v>6.4</v>
+      </c>
+      <c r="AR4">
+        <v>7.6</v>
+      </c>
+      <c r="AS4">
+        <v>10.5</v>
+      </c>
+      <c r="AT4">
+        <v>18</v>
+      </c>
+      <c r="AU4">
         <v>7</v>
       </c>
-      <c r="AR4">
-        <v>15</v>
-      </c>
-      <c r="AS4">
+      <c r="AV4">
+        <v>9</v>
+      </c>
+      <c r="AW4">
+        <v>16</v>
+      </c>
+      <c r="AX4">
+        <v>4.7</v>
+      </c>
+      <c r="AY4">
         <v>20</v>
       </c>
-      <c r="AT4">
-        <v>7</v>
-      </c>
-      <c r="AU4">
-        <v>6</v>
-      </c>
-      <c r="AV4">
-        <v>12</v>
-      </c>
-      <c r="AW4">
-        <v>6</v>
-      </c>
-      <c r="AX4">
-        <v>15.5</v>
-      </c>
-      <c r="AY4">
+      <c r="AZ4">
+        <v>14.5</v>
+      </c>
+      <c r="BA4">
+        <v>30</v>
+      </c>
+      <c r="BB4">
+        <v>4.9</v>
+      </c>
+      <c r="BC4">
+        <v>4.9</v>
+      </c>
+      <c r="BD4">
+        <v>4.9</v>
+      </c>
+      <c r="BE4">
+        <v>4.9</v>
+      </c>
+      <c r="BF4">
+        <v>4.9</v>
+      </c>
+      <c r="BG4">
+        <v>7.8</v>
+      </c>
+      <c r="BH4">
+        <v>3.85</v>
+      </c>
+      <c r="BI4">
+        <v>2.66</v>
+      </c>
+      <c r="BJ4">
+        <v>14.5</v>
+      </c>
+      <c r="BK4">
+        <v>3.65</v>
+      </c>
+      <c r="BL4">
+        <v>1000</v>
+      </c>
+      <c r="BM4">
+        <v>4.8</v>
+      </c>
+      <c r="BN4">
+        <v>13</v>
+      </c>
+      <c r="BO4">
+        <v>3.55</v>
+      </c>
+      <c r="BP4">
+        <v>1000</v>
+      </c>
+      <c r="BQ4">
+        <v>4.6</v>
+      </c>
+      <c r="BR4">
+        <v>1000</v>
+      </c>
+      <c r="BS4">
+        <v>4.7</v>
+      </c>
+      <c r="BT4">
+        <v>4.5</v>
+      </c>
+      <c r="BU4">
+        <v>3.05</v>
+      </c>
+      <c r="BV4">
         <v>12.5</v>
       </c>
-      <c r="AZ4">
-        <v>20</v>
-      </c>
-      <c r="BA4">
-        <v>6.2</v>
-      </c>
-      <c r="BB4">
-        <v>18</v>
-      </c>
-      <c r="BC4">
-        <v>6</v>
-      </c>
-      <c r="BD4">
-        <v>6.2</v>
-      </c>
-      <c r="BE4">
-        <v>6.4</v>
-      </c>
-      <c r="BF4">
-        <v>11.5</v>
-      </c>
-      <c r="BG4">
-        <v>6</v>
-      </c>
-      <c r="BH4">
-        <v>2.62</v>
-      </c>
-      <c r="BI4">
-        <v>2.12</v>
-      </c>
-      <c r="BJ4">
-        <v>12.5</v>
-      </c>
-      <c r="BK4">
-        <v>5.9</v>
-      </c>
-      <c r="BL4">
-        <v>1000</v>
-      </c>
-      <c r="BM4">
-        <v>10.5</v>
-      </c>
-      <c r="BN4">
-        <v>6</v>
-      </c>
-      <c r="BO4">
-        <v>4.4</v>
-      </c>
-      <c r="BP4">
-        <v>30</v>
-      </c>
-      <c r="BQ4">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="BR4">
-        <v>60</v>
-      </c>
-      <c r="BS4">
-        <v>9.4</v>
-      </c>
-      <c r="BT4">
-        <v>6</v>
-      </c>
-      <c r="BU4">
-        <v>4.4</v>
-      </c>
-      <c r="BV4">
-        <v>32</v>
-      </c>
       <c r="BW4">
-        <v>8.4</v>
+        <v>3.5</v>
       </c>
       <c r="BX4">
-        <v>60</v>
+        <v>36</v>
       </c>
       <c r="BY4">
-        <v>9.4</v>
+        <v>4.3</v>
       </c>
       <c r="BZ4">
-        <v>65</v>
+        <v>27</v>
       </c>
       <c r="CA4">
-        <v>9.6</v>
+        <v>4.1</v>
       </c>
       <c r="CB4" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
     </row>
     <row r="5" spans="1:80">
       <c r="A5" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B5" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="C5" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="D5" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="E5" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="F5">
-        <v>7</v>
+        <v>2.56</v>
       </c>
       <c r="G5">
-        <v>8</v>
+        <v>2.74</v>
       </c>
       <c r="H5">
-        <v>1.55</v>
+        <v>3.4</v>
       </c>
       <c r="I5">
-        <v>1.63</v>
+        <v>3.8</v>
       </c>
       <c r="J5">
-        <v>3.95</v>
+        <v>2.7</v>
       </c>
       <c r="K5">
-        <v>4.8</v>
+        <v>2.94</v>
       </c>
       <c r="L5">
+        <v>1.7</v>
+      </c>
+      <c r="M5">
+        <v>1.17</v>
+      </c>
+      <c r="N5">
+        <v>2.28</v>
+      </c>
+      <c r="O5">
+        <v>1.7</v>
+      </c>
+      <c r="P5">
+        <v>1.4</v>
+      </c>
+      <c r="Q5">
+        <v>3.25</v>
+      </c>
+      <c r="R5">
+        <v>1.14</v>
+      </c>
+      <c r="S5">
+        <v>7.2</v>
+      </c>
+      <c r="T5">
+        <v>2.34</v>
+      </c>
+      <c r="U5">
+        <v>1.64</v>
+      </c>
+      <c r="V5">
         <v>1.36</v>
       </c>
-      <c r="M5">
-        <v>1.07</v>
-      </c>
-      <c r="N5">
-        <v>3.45</v>
-      </c>
-      <c r="O5">
-        <v>1.34</v>
-      </c>
-      <c r="P5">
-        <v>1.86</v>
-      </c>
-      <c r="Q5">
-        <v>2.02</v>
-      </c>
-      <c r="R5">
-        <v>1.32</v>
-      </c>
-      <c r="S5">
-        <v>3.65</v>
-      </c>
-      <c r="T5">
-        <v>2.08</v>
-      </c>
-      <c r="U5">
-        <v>1.81</v>
-      </c>
-      <c r="V5">
-        <v>2.56</v>
-      </c>
       <c r="W5">
-        <v>1.14</v>
+        <v>1.57</v>
       </c>
       <c r="X5">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="Y5">
+        <v>9</v>
+      </c>
+      <c r="Z5">
+        <v>27</v>
+      </c>
+      <c r="AA5">
+        <v>420</v>
+      </c>
+      <c r="AB5">
+        <v>7.2</v>
+      </c>
+      <c r="AC5">
+        <v>7.2</v>
+      </c>
+      <c r="AD5">
+        <v>17.5</v>
+      </c>
+      <c r="AE5">
+        <v>85</v>
+      </c>
+      <c r="AF5">
         <v>16.5</v>
       </c>
-      <c r="Y5">
-        <v>8.6</v>
-      </c>
-      <c r="Z5">
-        <v>10.5</v>
-      </c>
-      <c r="AA5">
-        <v>18</v>
-      </c>
-      <c r="AB5">
-        <v>26</v>
-      </c>
-      <c r="AC5">
+      <c r="AG5">
+        <v>14.5</v>
+      </c>
+      <c r="AH5">
+        <v>40</v>
+      </c>
+      <c r="AI5">
+        <v>540</v>
+      </c>
+      <c r="AJ5">
+        <v>55</v>
+      </c>
+      <c r="AK5">
+        <v>60</v>
+      </c>
+      <c r="AL5">
+        <v>460</v>
+      </c>
+      <c r="AM5">
+        <v>500</v>
+      </c>
+      <c r="AN5">
+        <v>65</v>
+      </c>
+      <c r="AO5">
+        <v>500</v>
+      </c>
+      <c r="AP5">
+        <v>6</v>
+      </c>
+      <c r="AQ5">
+        <v>7.4</v>
+      </c>
+      <c r="AR5">
+        <v>19</v>
+      </c>
+      <c r="AS5">
+        <v>7.6</v>
+      </c>
+      <c r="AT5">
+        <v>5.9</v>
+      </c>
+      <c r="AU5">
+        <v>6</v>
+      </c>
+      <c r="AV5">
+        <v>14.5</v>
+      </c>
+      <c r="AW5">
+        <v>23</v>
+      </c>
+      <c r="AX5">
+        <v>12.5</v>
+      </c>
+      <c r="AY5">
         <v>11.5</v>
       </c>
-      <c r="AD5">
-        <v>12.5</v>
-      </c>
-      <c r="AE5">
-        <v>22</v>
-      </c>
-      <c r="AF5">
-        <v>75</v>
-      </c>
-      <c r="AG5">
-        <v>34</v>
-      </c>
-      <c r="AH5">
-        <v>30</v>
-      </c>
-      <c r="AI5">
-        <v>55</v>
-      </c>
-      <c r="AJ5">
-        <v>700</v>
-      </c>
-      <c r="AK5">
-        <v>700</v>
-      </c>
-      <c r="AL5">
-        <v>700</v>
-      </c>
-      <c r="AM5">
-        <v>700</v>
-      </c>
-      <c r="AN5">
-        <v>700</v>
-      </c>
-      <c r="AO5">
-        <v>12.5</v>
-      </c>
-      <c r="AP5">
-        <v>10</v>
-      </c>
-      <c r="AQ5">
-        <v>6.4</v>
-      </c>
-      <c r="AR5">
+      <c r="AZ5">
+        <v>20</v>
+      </c>
+      <c r="BA5">
+        <v>7.8</v>
+      </c>
+      <c r="BB5">
+        <v>29</v>
+      </c>
+      <c r="BC5">
+        <v>27</v>
+      </c>
+      <c r="BD5">
         <v>7.6</v>
       </c>
-      <c r="AS5">
-        <v>10.5</v>
-      </c>
-      <c r="AT5">
-        <v>9</v>
-      </c>
-      <c r="AU5">
-        <v>7</v>
-      </c>
-      <c r="AV5">
-        <v>9</v>
-      </c>
-      <c r="AW5">
-        <v>16</v>
-      </c>
-      <c r="AX5">
-        <v>4.2</v>
-      </c>
-      <c r="AY5">
-        <v>20</v>
-      </c>
-      <c r="AZ5">
-        <v>18</v>
-      </c>
-      <c r="BA5">
-        <v>4.1</v>
-      </c>
-      <c r="BB5">
-        <v>4.4</v>
-      </c>
-      <c r="BC5">
-        <v>4.4</v>
-      </c>
-      <c r="BD5">
-        <v>4.3</v>
-      </c>
       <c r="BE5">
-        <v>4.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BF5">
-        <v>4.4</v>
+        <v>32</v>
       </c>
       <c r="BG5">
         <v>7.8</v>
       </c>
       <c r="BH5">
+        <v>2.78</v>
+      </c>
+      <c r="BI5">
+        <v>2.04</v>
+      </c>
+      <c r="BJ5">
+        <v>15</v>
+      </c>
+      <c r="BK5">
         <v>3.85</v>
       </c>
-      <c r="BI5">
-        <v>2.68</v>
-      </c>
-      <c r="BJ5">
-        <v>14</v>
-      </c>
-      <c r="BK5">
-        <v>3.65</v>
-      </c>
       <c r="BL5">
         <v>1000</v>
       </c>
       <c r="BM5">
+        <v>5.1</v>
+      </c>
+      <c r="BN5">
+        <v>6.4</v>
+      </c>
+      <c r="BO5">
+        <v>4.1</v>
+      </c>
+      <c r="BP5">
+        <v>32</v>
+      </c>
+      <c r="BQ5">
+        <v>4.5</v>
+      </c>
+      <c r="BR5">
+        <v>1000</v>
+      </c>
+      <c r="BS5">
         <v>4.8</v>
       </c>
-      <c r="BN5">
-        <v>13</v>
-      </c>
-      <c r="BO5">
-        <v>3.55</v>
-      </c>
-      <c r="BP5">
-        <v>1000</v>
-      </c>
-      <c r="BQ5">
-        <v>4.6</v>
-      </c>
-      <c r="BR5">
-        <v>1000</v>
-      </c>
-      <c r="BS5">
+      <c r="BT5">
+        <v>7.6</v>
+      </c>
+      <c r="BU5">
+        <v>4.8</v>
+      </c>
+      <c r="BV5">
+        <v>46</v>
+      </c>
+      <c r="BW5">
         <v>4.7</v>
       </c>
-      <c r="BT5">
-        <v>4.6</v>
-      </c>
-      <c r="BU5">
-        <v>3.1</v>
-      </c>
-      <c r="BV5">
-        <v>12.5</v>
-      </c>
-      <c r="BW5">
-        <v>3.5</v>
-      </c>
       <c r="BX5">
-        <v>36</v>
+        <v>1000</v>
       </c>
       <c r="BY5">
-        <v>4.3</v>
+        <v>4.9</v>
       </c>
       <c r="BZ5">
-        <v>26</v>
+        <v>1000</v>
       </c>
       <c r="CA5">
-        <v>4.1</v>
+        <v>4.9</v>
       </c>
       <c r="CB5" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
     </row>
     <row r="6" spans="1:80">
       <c r="A6" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B6" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="C6" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="D6" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="E6" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="F6">
-        <v>2.52</v>
+        <v>2.48</v>
       </c>
       <c r="G6">
-        <v>2.72</v>
+        <v>2.58</v>
       </c>
       <c r="H6">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="I6">
-        <v>3.95</v>
+        <v>3.9</v>
       </c>
       <c r="J6">
-        <v>2.72</v>
+        <v>2.86</v>
       </c>
       <c r="K6">
         <v>3.05</v>
       </c>
       <c r="L6">
+        <v>1.68</v>
+      </c>
+      <c r="M6">
+        <v>1.15</v>
+      </c>
+      <c r="N6">
+        <v>2.32</v>
+      </c>
+      <c r="O6">
+        <v>1.67</v>
+      </c>
+      <c r="P6">
+        <v>1.42</v>
+      </c>
+      <c r="Q6">
+        <v>3.1</v>
+      </c>
+      <c r="R6">
+        <v>1.14</v>
+      </c>
+      <c r="S6">
+        <v>6.6</v>
+      </c>
+      <c r="T6">
+        <v>2.22</v>
+      </c>
+      <c r="U6">
         <v>1.66</v>
       </c>
-      <c r="M6">
-        <v>1.16</v>
-      </c>
-      <c r="N6">
-        <v>2.24</v>
-      </c>
-      <c r="O6">
-        <v>1.66</v>
-      </c>
-      <c r="P6">
-        <v>1.4</v>
-      </c>
-      <c r="Q6">
-        <v>3.05</v>
-      </c>
-      <c r="R6">
-        <v>1.13</v>
-      </c>
-      <c r="S6">
-        <v>6</v>
-      </c>
-      <c r="T6">
-        <v>2.34</v>
-      </c>
-      <c r="U6">
+      <c r="V6">
+        <v>1.36</v>
+      </c>
+      <c r="W6">
         <v>1.63</v>
       </c>
-      <c r="V6">
-        <v>1.34</v>
-      </c>
-      <c r="W6">
-        <v>1.58</v>
-      </c>
       <c r="X6">
-        <v>8.199999999999999</v>
+        <v>7.6</v>
       </c>
       <c r="Y6">
-        <v>9</v>
+        <v>9.4</v>
       </c>
       <c r="Z6">
-        <v>27</v>
+        <v>34</v>
       </c>
       <c r="AA6">
-        <v>500</v>
+        <v>900</v>
       </c>
       <c r="AB6">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="AC6">
         <v>7.2</v>
       </c>
       <c r="AD6">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="AE6">
-        <v>85</v>
+        <v>440</v>
       </c>
       <c r="AF6">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="AG6">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="AH6">
-        <v>29</v>
+        <v>38</v>
       </c>
       <c r="AI6">
-        <v>540</v>
+        <v>500</v>
       </c>
       <c r="AJ6">
-        <v>55</v>
+        <v>120</v>
       </c>
       <c r="AK6">
-        <v>60</v>
+        <v>150</v>
       </c>
       <c r="AL6">
-        <v>460</v>
+        <v>230</v>
       </c>
       <c r="AM6">
         <v>500</v>
       </c>
       <c r="AN6">
-        <v>65</v>
+        <v>180</v>
       </c>
       <c r="AO6">
-        <v>500</v>
+        <v>130</v>
       </c>
       <c r="AP6">
-        <v>5.4</v>
+        <v>6</v>
       </c>
       <c r="AQ6">
-        <v>7.4</v>
+        <v>8</v>
       </c>
       <c r="AR6">
-        <v>19</v>
+        <v>14.5</v>
       </c>
       <c r="AS6">
-        <v>7.4</v>
+        <v>9</v>
       </c>
       <c r="AT6">
-        <v>5.9</v>
+        <v>5.8</v>
       </c>
       <c r="AU6">
         <v>6</v>
@@ -2049,91 +2037,91 @@
         <v>11.5</v>
       </c>
       <c r="AZ6">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="BA6">
-        <v>7.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BB6">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="BC6">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="BD6">
-        <v>7.4</v>
+        <v>9</v>
       </c>
       <c r="BE6">
-        <v>7.8</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BF6">
         <v>32</v>
       </c>
       <c r="BG6">
-        <v>7.4</v>
+        <v>9.4</v>
       </c>
       <c r="BH6">
-        <v>2.76</v>
+        <v>1000</v>
       </c>
       <c r="BI6">
-        <v>2.02</v>
+        <v>1.04</v>
       </c>
       <c r="BJ6">
-        <v>15</v>
+        <v>1000</v>
       </c>
       <c r="BK6">
-        <v>3.9</v>
+        <v>1.04</v>
       </c>
       <c r="BL6">
         <v>1000</v>
       </c>
       <c r="BM6">
-        <v>5.2</v>
+        <v>1.04</v>
       </c>
       <c r="BN6">
-        <v>6.2</v>
+        <v>1000</v>
       </c>
       <c r="BO6">
-        <v>4</v>
+        <v>1.04</v>
       </c>
       <c r="BP6">
-        <v>32</v>
+        <v>1000</v>
       </c>
       <c r="BQ6">
-        <v>4.5</v>
+        <v>1.04</v>
       </c>
       <c r="BR6">
         <v>1000</v>
       </c>
       <c r="BS6">
-        <v>4.9</v>
+        <v>1.04</v>
       </c>
       <c r="BT6">
-        <v>7.8</v>
+        <v>1000</v>
       </c>
       <c r="BU6">
-        <v>4.9</v>
+        <v>1.04</v>
       </c>
       <c r="BV6">
-        <v>48</v>
+        <v>1000</v>
       </c>
       <c r="BW6">
-        <v>4.7</v>
+        <v>1.04</v>
       </c>
       <c r="BX6">
         <v>1000</v>
       </c>
       <c r="BY6">
-        <v>4.9</v>
+        <v>1.04</v>
       </c>
       <c r="BZ6">
         <v>1000</v>
       </c>
       <c r="CA6">
-        <v>4.9</v>
+        <v>1.04</v>
       </c>
       <c r="CB6" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
     </row>
     <row r="7" spans="1:80">
@@ -2141,178 +2129,178 @@
         <v>82</v>
       </c>
       <c r="B7" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="C7" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="D7" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="E7" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
       <c r="F7">
-        <v>2.42</v>
+        <v>1.76</v>
       </c>
       <c r="G7">
-        <v>2.58</v>
+        <v>1.79</v>
       </c>
       <c r="H7">
-        <v>3.55</v>
+        <v>5.7</v>
       </c>
       <c r="I7">
-        <v>4.4</v>
+        <v>6</v>
       </c>
       <c r="J7">
-        <v>2.76</v>
+        <v>3.7</v>
       </c>
       <c r="K7">
-        <v>3</v>
+        <v>3.8</v>
       </c>
       <c r="L7">
-        <v>1.01</v>
+        <v>1.5</v>
       </c>
       <c r="M7">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="N7">
-        <v>2.28</v>
+        <v>3.15</v>
       </c>
       <c r="O7">
-        <v>1.61</v>
+        <v>1.45</v>
       </c>
       <c r="P7">
-        <v>1.45</v>
+        <v>1.7</v>
       </c>
       <c r="Q7">
-        <v>2.78</v>
+        <v>2.34</v>
       </c>
       <c r="R7">
-        <v>1.14</v>
+        <v>1.25</v>
       </c>
       <c r="S7">
-        <v>4.8</v>
+        <v>4.6</v>
       </c>
       <c r="T7">
-        <v>2.14</v>
+        <v>2.12</v>
       </c>
       <c r="U7">
-        <v>1.57</v>
+        <v>1.84</v>
       </c>
       <c r="V7">
-        <v>1.29</v>
+        <v>1.2</v>
       </c>
       <c r="W7">
-        <v>1.63</v>
+        <v>2.26</v>
       </c>
       <c r="X7">
-        <v>970</v>
+        <v>12</v>
       </c>
       <c r="Y7">
-        <v>13</v>
+        <v>16.5</v>
       </c>
       <c r="Z7">
-        <v>55</v>
+        <v>100</v>
       </c>
       <c r="AA7">
         <v>900</v>
       </c>
       <c r="AB7">
-        <v>9.800000000000001</v>
+        <v>6.6</v>
       </c>
       <c r="AC7">
-        <v>9.800000000000001</v>
+        <v>8.4</v>
       </c>
       <c r="AD7">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="AE7">
-        <v>500</v>
+        <v>700</v>
       </c>
       <c r="AF7">
-        <v>21</v>
+        <v>9.4</v>
       </c>
       <c r="AG7">
-        <v>19.5</v>
+        <v>10.5</v>
       </c>
       <c r="AH7">
-        <v>85</v>
+        <v>27</v>
       </c>
       <c r="AI7">
-        <v>540</v>
+        <v>260</v>
       </c>
       <c r="AJ7">
-        <v>220</v>
+        <v>19</v>
       </c>
       <c r="AK7">
-        <v>500</v>
+        <v>27</v>
       </c>
       <c r="AL7">
-        <v>500</v>
+        <v>380</v>
       </c>
       <c r="AM7">
-        <v>500</v>
+        <v>580</v>
       </c>
       <c r="AN7">
-        <v>500</v>
+        <v>16.5</v>
       </c>
       <c r="AO7">
-        <v>1000</v>
+        <v>700</v>
       </c>
       <c r="AP7">
-        <v>3.85</v>
+        <v>10</v>
       </c>
       <c r="AQ7">
+        <v>15.5</v>
+      </c>
+      <c r="AR7">
+        <v>30</v>
+      </c>
+      <c r="AS7">
+        <v>14.5</v>
+      </c>
+      <c r="AT7">
         <v>5.9</v>
       </c>
-      <c r="AR7">
+      <c r="AU7">
+        <v>7.6</v>
+      </c>
+      <c r="AV7">
+        <v>18.5</v>
+      </c>
+      <c r="AW7">
+        <v>13</v>
+      </c>
+      <c r="AX7">
+        <v>8.4</v>
+      </c>
+      <c r="AY7">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AZ7">
+        <v>20</v>
+      </c>
+      <c r="BA7">
+        <v>13.5</v>
+      </c>
+      <c r="BB7">
+        <v>16.5</v>
+      </c>
+      <c r="BC7">
+        <v>18.5</v>
+      </c>
+      <c r="BD7">
+        <v>40</v>
+      </c>
+      <c r="BE7">
         <v>14.5</v>
       </c>
-      <c r="AS7">
-        <v>2.54</v>
-      </c>
-      <c r="AT7">
-        <v>4.6</v>
-      </c>
-      <c r="AU7">
-        <v>4.6</v>
-      </c>
-      <c r="AV7">
-        <v>11</v>
-      </c>
-      <c r="AW7">
-        <v>2.5</v>
-      </c>
-      <c r="AX7">
-        <v>11</v>
-      </c>
-      <c r="AY7">
-        <v>8.4</v>
-      </c>
-      <c r="AZ7">
-        <v>16</v>
-      </c>
-      <c r="BA7">
-        <v>2.54</v>
-      </c>
-      <c r="BB7">
-        <v>16</v>
-      </c>
-      <c r="BC7">
-        <v>18</v>
-      </c>
-      <c r="BD7">
-        <v>2.54</v>
-      </c>
-      <c r="BE7">
-        <v>2.56</v>
-      </c>
       <c r="BF7">
-        <v>9.4</v>
+        <v>14</v>
       </c>
       <c r="BG7">
-        <v>2.56</v>
+        <v>14</v>
       </c>
       <c r="BH7">
         <v>1000</v>
@@ -2375,7 +2363,7 @@
         <v>1.04</v>
       </c>
       <c r="CB7" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
     </row>
     <row r="8" spans="1:80">
@@ -2383,241 +2371,241 @@
         <v>83</v>
       </c>
       <c r="B8" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="C8" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="D8" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="E8" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="F8">
-        <v>1.76</v>
+        <v>2.84</v>
       </c>
       <c r="G8">
-        <v>1.81</v>
+        <v>2.92</v>
       </c>
       <c r="H8">
-        <v>5.7</v>
+        <v>2.86</v>
       </c>
       <c r="I8">
-        <v>6.2</v>
+        <v>2.92</v>
       </c>
       <c r="J8">
-        <v>3.65</v>
+        <v>3.2</v>
       </c>
       <c r="K8">
-        <v>3.9</v>
+        <v>3.3</v>
       </c>
       <c r="L8">
         <v>1.48</v>
       </c>
       <c r="M8">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="N8">
-        <v>3.05</v>
+        <v>3.2</v>
       </c>
       <c r="O8">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="P8">
-        <v>1.69</v>
+        <v>1.71</v>
       </c>
       <c r="Q8">
-        <v>2.32</v>
+        <v>2.28</v>
       </c>
       <c r="R8">
-        <v>1.25</v>
+        <v>1.27</v>
       </c>
       <c r="S8">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="T8">
-        <v>2.1</v>
+        <v>1.91</v>
       </c>
       <c r="U8">
-        <v>1.81</v>
+        <v>1.99</v>
       </c>
       <c r="V8">
-        <v>1.19</v>
+        <v>1.52</v>
       </c>
       <c r="W8">
-        <v>2.24</v>
+        <v>1.52</v>
       </c>
       <c r="X8">
-        <v>11.5</v>
+        <v>14.5</v>
       </c>
       <c r="Y8">
-        <v>16.5</v>
+        <v>9.4</v>
       </c>
       <c r="Z8">
-        <v>100</v>
+        <v>17.5</v>
       </c>
       <c r="AA8">
-        <v>900</v>
+        <v>65</v>
       </c>
       <c r="AB8">
-        <v>6.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AC8">
-        <v>8.4</v>
+        <v>7.4</v>
       </c>
       <c r="AD8">
-        <v>23</v>
+        <v>13</v>
       </c>
       <c r="AE8">
-        <v>700</v>
+        <v>50</v>
       </c>
       <c r="AF8">
-        <v>9.6</v>
+        <v>18.5</v>
       </c>
       <c r="AG8">
-        <v>10.5</v>
+        <v>13.5</v>
       </c>
       <c r="AH8">
-        <v>34</v>
+        <v>19.5</v>
       </c>
       <c r="AI8">
-        <v>260</v>
+        <v>55</v>
       </c>
       <c r="AJ8">
-        <v>21</v>
+        <v>55</v>
       </c>
       <c r="AK8">
-        <v>27</v>
+        <v>50</v>
       </c>
       <c r="AL8">
-        <v>380</v>
+        <v>70</v>
       </c>
       <c r="AM8">
         <v>580</v>
       </c>
       <c r="AN8">
-        <v>18</v>
+        <v>40</v>
       </c>
       <c r="AO8">
-        <v>700</v>
+        <v>36</v>
       </c>
       <c r="AP8">
         <v>10</v>
       </c>
       <c r="AQ8">
+        <v>8.4</v>
+      </c>
+      <c r="AR8">
         <v>15.5</v>
       </c>
-      <c r="AR8">
+      <c r="AS8">
+        <v>38</v>
+      </c>
+      <c r="AT8">
+        <v>8.6</v>
+      </c>
+      <c r="AU8">
+        <v>6.6</v>
+      </c>
+      <c r="AV8">
+        <v>11.5</v>
+      </c>
+      <c r="AW8">
         <v>30</v>
       </c>
-      <c r="AS8">
-        <v>14</v>
-      </c>
-      <c r="AT8">
-        <v>5.9</v>
-      </c>
-      <c r="AU8">
-        <v>7.4</v>
-      </c>
-      <c r="AV8">
-        <v>20</v>
-      </c>
-      <c r="AW8">
-        <v>13</v>
-      </c>
       <c r="AX8">
-        <v>8.4</v>
+        <v>16.5</v>
       </c>
       <c r="AY8">
-        <v>9.199999999999999</v>
+        <v>11.5</v>
       </c>
       <c r="AZ8">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="BA8">
-        <v>13</v>
+        <v>38</v>
       </c>
       <c r="BB8">
-        <v>13</v>
+        <v>29</v>
       </c>
       <c r="BC8">
-        <v>18.5</v>
+        <v>28</v>
       </c>
       <c r="BD8">
+        <v>23</v>
+      </c>
+      <c r="BE8">
+        <v>14.5</v>
+      </c>
+      <c r="BF8">
+        <v>30</v>
+      </c>
+      <c r="BG8">
+        <v>27</v>
+      </c>
+      <c r="BH8">
+        <v>3.05</v>
+      </c>
+      <c r="BI8">
+        <v>2.8</v>
+      </c>
+      <c r="BJ8">
+        <v>10</v>
+      </c>
+      <c r="BK8">
+        <v>6.2</v>
+      </c>
+      <c r="BL8">
+        <v>1000</v>
+      </c>
+      <c r="BM8">
+        <v>15.5</v>
+      </c>
+      <c r="BN8">
+        <v>5.8</v>
+      </c>
+      <c r="BO8">
+        <v>4.5</v>
+      </c>
+      <c r="BP8">
+        <v>25</v>
+      </c>
+      <c r="BQ8">
+        <v>10</v>
+      </c>
+      <c r="BR8">
         <v>40</v>
       </c>
-      <c r="BE8">
-        <v>14</v>
-      </c>
-      <c r="BF8">
-        <v>14</v>
-      </c>
-      <c r="BG8">
-        <v>13.5</v>
-      </c>
-      <c r="BH8">
-        <v>1000</v>
-      </c>
-      <c r="BI8">
-        <v>1.04</v>
-      </c>
-      <c r="BJ8">
-        <v>1000</v>
-      </c>
-      <c r="BK8">
-        <v>1.04</v>
-      </c>
-      <c r="BL8">
-        <v>1000</v>
-      </c>
-      <c r="BM8">
-        <v>1.04</v>
-      </c>
-      <c r="BN8">
-        <v>1000</v>
-      </c>
-      <c r="BO8">
-        <v>1.04</v>
-      </c>
-      <c r="BP8">
-        <v>1000</v>
-      </c>
-      <c r="BQ8">
-        <v>1.04</v>
-      </c>
-      <c r="BR8">
-        <v>1000</v>
-      </c>
       <c r="BS8">
-        <v>1.04</v>
+        <v>12</v>
       </c>
       <c r="BT8">
-        <v>1000</v>
+        <v>5.7</v>
       </c>
       <c r="BU8">
-        <v>1.04</v>
+        <v>4.3</v>
       </c>
       <c r="BV8">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="BW8">
-        <v>1.04</v>
+        <v>10</v>
       </c>
       <c r="BX8">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="BY8">
-        <v>1.04</v>
+        <v>12</v>
       </c>
       <c r="BZ8">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="CA8">
-        <v>1.04</v>
+        <v>11.5</v>
       </c>
       <c r="CB8" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
     </row>
     <row r="9" spans="1:80">
@@ -2625,483 +2613,241 @@
         <v>84</v>
       </c>
       <c r="B9" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="C9" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="D9" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="E9" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="F9">
-        <v>2.82</v>
+        <v>2.14</v>
       </c>
       <c r="G9">
-        <v>2.9</v>
+        <v>2.26</v>
       </c>
       <c r="H9">
-        <v>2.84</v>
+        <v>3.55</v>
       </c>
       <c r="I9">
-        <v>2.9</v>
+        <v>4.1</v>
       </c>
       <c r="J9">
-        <v>3.2</v>
+        <v>3.35</v>
       </c>
       <c r="K9">
-        <v>3.45</v>
+        <v>3.7</v>
       </c>
       <c r="L9">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="M9">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="N9">
-        <v>3.1</v>
+        <v>3.5</v>
       </c>
       <c r="O9">
-        <v>1.43</v>
+        <v>1.36</v>
       </c>
       <c r="P9">
-        <v>1.69</v>
+        <v>1.83</v>
       </c>
       <c r="Q9">
-        <v>2.28</v>
+        <v>2.08</v>
       </c>
       <c r="R9">
-        <v>1.26</v>
+        <v>1.31</v>
       </c>
       <c r="S9">
-        <v>4.3</v>
+        <v>3.75</v>
       </c>
       <c r="T9">
-        <v>1.93</v>
+        <v>1.83</v>
       </c>
       <c r="U9">
-        <v>1.99</v>
+        <v>2.02</v>
       </c>
       <c r="V9">
-        <v>1.52</v>
+        <v>1.33</v>
       </c>
       <c r="W9">
-        <v>1.52</v>
+        <v>1.79</v>
       </c>
       <c r="X9">
+        <v>14</v>
+      </c>
+      <c r="Y9">
         <v>14.5</v>
       </c>
-      <c r="Y9">
+      <c r="Z9">
+        <v>27</v>
+      </c>
+      <c r="AA9">
+        <v>85</v>
+      </c>
+      <c r="AB9">
         <v>9.4</v>
       </c>
-      <c r="Z9">
-        <v>17.5</v>
-      </c>
-      <c r="AA9">
-        <v>65</v>
-      </c>
-      <c r="AB9">
-        <v>9.800000000000001</v>
-      </c>
       <c r="AC9">
-        <v>7.4</v>
+        <v>8</v>
       </c>
       <c r="AD9">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="AE9">
         <v>50</v>
       </c>
       <c r="AF9">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="AG9">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AH9">
-        <v>19.5</v>
+        <v>21</v>
       </c>
       <c r="AI9">
-        <v>55</v>
+        <v>65</v>
       </c>
       <c r="AJ9">
-        <v>55</v>
+        <v>32</v>
       </c>
       <c r="AK9">
-        <v>50</v>
+        <v>29</v>
       </c>
       <c r="AL9">
-        <v>70</v>
+        <v>46</v>
       </c>
       <c r="AM9">
-        <v>580</v>
+        <v>120</v>
       </c>
       <c r="AN9">
-        <v>40</v>
+        <v>22</v>
       </c>
       <c r="AO9">
-        <v>36</v>
+        <v>60</v>
       </c>
       <c r="AP9">
-        <v>10</v>
+        <v>9.4</v>
       </c>
       <c r="AQ9">
-        <v>8.199999999999999</v>
+        <v>10.5</v>
       </c>
       <c r="AR9">
-        <v>15.5</v>
+        <v>21</v>
       </c>
       <c r="AS9">
-        <v>38</v>
+        <v>6.8</v>
       </c>
       <c r="AT9">
-        <v>8.6</v>
+        <v>7.8</v>
       </c>
       <c r="AU9">
         <v>6.6</v>
       </c>
       <c r="AV9">
+        <v>12.5</v>
+      </c>
+      <c r="AW9">
+        <v>6.4</v>
+      </c>
+      <c r="AX9">
         <v>11</v>
       </c>
-      <c r="AW9">
-        <v>14.5</v>
-      </c>
-      <c r="AX9">
-        <v>16.5</v>
-      </c>
       <c r="AY9">
-        <v>11.5</v>
+        <v>9.6</v>
       </c>
       <c r="AZ9">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="BA9">
-        <v>38</v>
+        <v>6.6</v>
       </c>
       <c r="BB9">
-        <v>29</v>
+        <v>6</v>
       </c>
       <c r="BC9">
-        <v>28</v>
+        <v>5.9</v>
       </c>
       <c r="BD9">
-        <v>44</v>
+        <v>6.4</v>
       </c>
       <c r="BE9">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="BF9">
-        <v>26</v>
+        <v>17</v>
       </c>
       <c r="BG9">
-        <v>12</v>
+        <v>6.6</v>
       </c>
       <c r="BH9">
-        <v>3.05</v>
+        <v>3.35</v>
       </c>
       <c r="BI9">
-        <v>2.8</v>
+        <v>2.68</v>
       </c>
       <c r="BJ9">
         <v>10.5</v>
       </c>
       <c r="BK9">
-        <v>6.2</v>
+        <v>5.2</v>
       </c>
       <c r="BL9">
         <v>1000</v>
       </c>
       <c r="BM9">
-        <v>14</v>
+        <v>9.6</v>
       </c>
       <c r="BN9">
-        <v>5.9</v>
+        <v>5.1</v>
       </c>
       <c r="BO9">
-        <v>4.5</v>
+        <v>3.95</v>
       </c>
       <c r="BP9">
-        <v>25</v>
+        <v>17.5</v>
       </c>
       <c r="BQ9">
-        <v>9.6</v>
+        <v>6.4</v>
       </c>
       <c r="BR9">
-        <v>40</v>
+        <v>34</v>
       </c>
       <c r="BS9">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="BT9">
-        <v>5.7</v>
+        <v>7.2</v>
       </c>
       <c r="BU9">
-        <v>4.3</v>
+        <v>5.4</v>
       </c>
       <c r="BV9">
-        <v>23</v>
+        <v>34</v>
       </c>
       <c r="BW9">
-        <v>9.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="BX9">
-        <v>40</v>
+        <v>1000</v>
       </c>
       <c r="BY9">
-        <v>11</v>
+        <v>8.4</v>
       </c>
       <c r="BZ9">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="CA9">
-        <v>10.5</v>
+        <v>7.8</v>
       </c>
       <c r="CB9" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="10" spans="1:80">
-      <c r="A10" t="s">
-        <v>85</v>
-      </c>
-      <c r="B10" t="s">
-        <v>86</v>
-      </c>
-      <c r="C10" t="s">
-        <v>92</v>
-      </c>
-      <c r="D10" t="s">
-        <v>101</v>
-      </c>
-      <c r="E10" t="s">
-        <v>110</v>
-      </c>
-      <c r="F10">
-        <v>2.22</v>
-      </c>
-      <c r="G10">
-        <v>2.44</v>
-      </c>
-      <c r="H10">
-        <v>3.35</v>
-      </c>
-      <c r="I10">
-        <v>3.9</v>
-      </c>
-      <c r="J10">
-        <v>3.25</v>
-      </c>
-      <c r="K10">
-        <v>3.6</v>
-      </c>
-      <c r="L10">
-        <v>1.44</v>
-      </c>
-      <c r="M10">
-        <v>1.08</v>
-      </c>
-      <c r="N10">
-        <v>3.25</v>
-      </c>
-      <c r="O10">
-        <v>1.37</v>
-      </c>
-      <c r="P10">
-        <v>1.77</v>
-      </c>
-      <c r="Q10">
-        <v>2.08</v>
-      </c>
-      <c r="R10">
-        <v>1.28</v>
-      </c>
-      <c r="S10">
-        <v>3.85</v>
-      </c>
-      <c r="T10">
-        <v>1.84</v>
-      </c>
-      <c r="U10">
-        <v>2</v>
-      </c>
-      <c r="V10">
-        <v>1.37</v>
-      </c>
-      <c r="W10">
-        <v>1.69</v>
-      </c>
-      <c r="X10">
-        <v>14</v>
-      </c>
-      <c r="Y10">
-        <v>14.5</v>
-      </c>
-      <c r="Z10">
-        <v>26</v>
-      </c>
-      <c r="AA10">
-        <v>75</v>
-      </c>
-      <c r="AB10">
-        <v>9.4</v>
-      </c>
-      <c r="AC10">
-        <v>8</v>
-      </c>
-      <c r="AD10">
-        <v>16</v>
-      </c>
-      <c r="AE10">
-        <v>55</v>
-      </c>
-      <c r="AF10">
-        <v>15</v>
-      </c>
-      <c r="AG10">
-        <v>13</v>
-      </c>
-      <c r="AH10">
-        <v>22</v>
-      </c>
-      <c r="AI10">
-        <v>65</v>
-      </c>
-      <c r="AJ10">
-        <v>34</v>
-      </c>
-      <c r="AK10">
-        <v>30</v>
-      </c>
-      <c r="AL10">
-        <v>48</v>
-      </c>
-      <c r="AM10">
-        <v>130</v>
-      </c>
-      <c r="AN10">
-        <v>24</v>
-      </c>
-      <c r="AO10">
-        <v>55</v>
-      </c>
-      <c r="AP10">
-        <v>9.4</v>
-      </c>
-      <c r="AQ10">
-        <v>10.5</v>
-      </c>
-      <c r="AR10">
-        <v>21</v>
-      </c>
-      <c r="AS10">
-        <v>6.4</v>
-      </c>
-      <c r="AT10">
-        <v>7.8</v>
-      </c>
-      <c r="AU10">
-        <v>6.6</v>
-      </c>
-      <c r="AV10">
-        <v>12.5</v>
-      </c>
-      <c r="AW10">
-        <v>6.2</v>
-      </c>
-      <c r="AX10">
-        <v>11</v>
-      </c>
-      <c r="AY10">
-        <v>9.6</v>
-      </c>
-      <c r="AZ10">
-        <v>14</v>
-      </c>
-      <c r="BA10">
-        <v>6.4</v>
-      </c>
-      <c r="BB10">
-        <v>5.8</v>
-      </c>
-      <c r="BC10">
-        <v>5.7</v>
-      </c>
-      <c r="BD10">
-        <v>6.2</v>
-      </c>
-      <c r="BE10">
-        <v>6.6</v>
-      </c>
-      <c r="BF10">
-        <v>17</v>
-      </c>
-      <c r="BG10">
-        <v>6.2</v>
-      </c>
-      <c r="BH10">
-        <v>3.3</v>
-      </c>
-      <c r="BI10">
-        <v>2.64</v>
-      </c>
-      <c r="BJ10">
-        <v>10.5</v>
-      </c>
-      <c r="BK10">
-        <v>5.1</v>
-      </c>
-      <c r="BL10">
-        <v>1000</v>
-      </c>
-      <c r="BM10">
-        <v>9.4</v>
-      </c>
-      <c r="BN10">
-        <v>5.3</v>
-      </c>
-      <c r="BO10">
-        <v>4</v>
-      </c>
-      <c r="BP10">
-        <v>18.5</v>
-      </c>
-      <c r="BQ10">
-        <v>6.4</v>
-      </c>
-      <c r="BR10">
-        <v>36</v>
-      </c>
-      <c r="BS10">
-        <v>7.8</v>
-      </c>
-      <c r="BT10">
-        <v>7</v>
-      </c>
-      <c r="BU10">
-        <v>5.2</v>
-      </c>
-      <c r="BV10">
-        <v>1000</v>
-      </c>
-      <c r="BW10">
-        <v>7.6</v>
-      </c>
-      <c r="BX10">
-        <v>1000</v>
-      </c>
-      <c r="BY10">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="BZ10">
-        <v>34</v>
-      </c>
-      <c r="CA10">
-        <v>7.6</v>
-      </c>
-      <c r="CB10" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
     </row>
   </sheetData>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-08-11.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-08-11.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="128" uniqueCount="108">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="134" uniqueCount="112">
   <si>
     <t>League</t>
   </si>
@@ -256,6 +256,9 @@
     <t>SnapshotTS</t>
   </si>
   <si>
+    <t>Chinese League 2</t>
+  </si>
+  <si>
     <t>Swedish Superettan</t>
   </si>
   <si>
@@ -274,6 +277,9 @@
     <t>2026-08-11</t>
   </si>
   <si>
+    <t>11:30:00</t>
+  </si>
+  <si>
     <t>17:00:00</t>
   </si>
   <si>
@@ -289,6 +295,9 @@
     <t>23:00:00</t>
   </si>
   <si>
+    <t>Hangzhou Linping Wuyue</t>
+  </si>
+  <si>
     <t>Helsingborgs</t>
   </si>
   <si>
@@ -313,6 +322,9 @@
     <t>Puerto Montt</t>
   </si>
   <si>
+    <t>Guizhou Zhucheng Athletic</t>
+  </si>
+  <si>
     <t>Varnamo</t>
   </si>
   <si>
@@ -337,7 +349,7 @@
     <t>Union Espanola</t>
   </si>
   <si>
-    <t>2026-08-11 01:19:23</t>
+    <t>2026-08-11 03:26:12</t>
   </si>
 </sst>
 </file>
@@ -669,7 +681,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:CB9"/>
+  <dimension ref="A1:CB10"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:80">
@@ -919,232 +931,232 @@
         <v>80</v>
       </c>
       <c r="B2" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C2" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="D2" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="E2" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="F2">
-        <v>2.44</v>
+        <v>5.6</v>
       </c>
       <c r="G2">
+        <v>6.8</v>
+      </c>
+      <c r="H2">
+        <v>1.75</v>
+      </c>
+      <c r="I2">
+        <v>1.91</v>
+      </c>
+      <c r="J2">
+        <v>3.2</v>
+      </c>
+      <c r="K2">
+        <v>3.65</v>
+      </c>
+      <c r="L2">
+        <v>1.49</v>
+      </c>
+      <c r="M2">
+        <v>1.12</v>
+      </c>
+      <c r="N2">
+        <v>2.56</v>
+      </c>
+      <c r="O2">
+        <v>1.52</v>
+      </c>
+      <c r="P2">
+        <v>1.53</v>
+      </c>
+      <c r="Q2">
+        <v>2.54</v>
+      </c>
+      <c r="R2">
+        <v>1.19</v>
+      </c>
+      <c r="S2">
+        <v>5.1</v>
+      </c>
+      <c r="T2">
+        <v>2.24</v>
+      </c>
+      <c r="U2">
+        <v>1.65</v>
+      </c>
+      <c r="V2">
+        <v>2.08</v>
+      </c>
+      <c r="W2">
+        <v>1.17</v>
+      </c>
+      <c r="X2">
+        <v>10.5</v>
+      </c>
+      <c r="Y2">
+        <v>6.4</v>
+      </c>
+      <c r="Z2">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AA2">
+        <v>22</v>
+      </c>
+      <c r="AB2">
+        <v>15.5</v>
+      </c>
+      <c r="AC2">
+        <v>8.4</v>
+      </c>
+      <c r="AD2">
+        <v>11.5</v>
+      </c>
+      <c r="AE2">
+        <v>27</v>
+      </c>
+      <c r="AF2">
+        <v>55</v>
+      </c>
+      <c r="AG2">
+        <v>27</v>
+      </c>
+      <c r="AH2">
+        <v>30</v>
+      </c>
+      <c r="AI2">
+        <v>70</v>
+      </c>
+      <c r="AJ2">
+        <v>250</v>
+      </c>
+      <c r="AK2">
+        <v>150</v>
+      </c>
+      <c r="AL2">
+        <v>170</v>
+      </c>
+      <c r="AM2">
+        <v>290</v>
+      </c>
+      <c r="AN2">
+        <v>280</v>
+      </c>
+      <c r="AO2">
+        <v>22</v>
+      </c>
+      <c r="AP2">
+        <v>7</v>
+      </c>
+      <c r="AQ2">
+        <v>5.2</v>
+      </c>
+      <c r="AR2">
+        <v>7.2</v>
+      </c>
+      <c r="AS2">
+        <v>17</v>
+      </c>
+      <c r="AT2">
+        <v>11</v>
+      </c>
+      <c r="AU2">
+        <v>6.2</v>
+      </c>
+      <c r="AV2">
+        <v>8.4</v>
+      </c>
+      <c r="AW2">
+        <v>21</v>
+      </c>
+      <c r="AX2">
+        <v>7</v>
+      </c>
+      <c r="AY2">
+        <v>21</v>
+      </c>
+      <c r="AZ2">
+        <v>21</v>
+      </c>
+      <c r="BA2">
+        <v>7.2</v>
+      </c>
+      <c r="BB2">
+        <v>7.8</v>
+      </c>
+      <c r="BC2">
+        <v>7.6</v>
+      </c>
+      <c r="BD2">
+        <v>7.8</v>
+      </c>
+      <c r="BE2">
+        <v>7.8</v>
+      </c>
+      <c r="BF2">
+        <v>7.8</v>
+      </c>
+      <c r="BG2">
+        <v>17</v>
+      </c>
+      <c r="BH2">
+        <v>2.84</v>
+      </c>
+      <c r="BI2">
         <v>2.48</v>
       </c>
-      <c r="H2">
-        <v>3</v>
-      </c>
-      <c r="I2">
-        <v>3.05</v>
-      </c>
-      <c r="J2">
-        <v>3.75</v>
-      </c>
-      <c r="K2">
-        <v>3.9</v>
-      </c>
-      <c r="L2">
-        <v>1.33</v>
-      </c>
-      <c r="M2">
-        <v>1.04</v>
-      </c>
-      <c r="N2">
-        <v>5.2</v>
-      </c>
-      <c r="O2">
-        <v>1.22</v>
-      </c>
-      <c r="P2">
-        <v>2.4</v>
-      </c>
-      <c r="Q2">
-        <v>1.69</v>
-      </c>
-      <c r="R2">
-        <v>1.56</v>
-      </c>
-      <c r="S2">
-        <v>2.72</v>
-      </c>
-      <c r="T2">
-        <v>1.58</v>
-      </c>
-      <c r="U2">
-        <v>2.6</v>
-      </c>
-      <c r="V2">
-        <v>1.48</v>
-      </c>
-      <c r="W2">
-        <v>1.67</v>
-      </c>
-      <c r="X2">
-        <v>21</v>
-      </c>
-      <c r="Y2">
-        <v>20</v>
-      </c>
-      <c r="Z2">
-        <v>23</v>
-      </c>
-      <c r="AA2">
-        <v>50</v>
-      </c>
-      <c r="AB2">
+      <c r="BJ2">
         <v>14.5</v>
       </c>
-      <c r="AC2">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AD2">
-        <v>13.5</v>
-      </c>
-      <c r="AE2">
-        <v>48</v>
-      </c>
-      <c r="AF2">
-        <v>18.5</v>
-      </c>
-      <c r="AG2">
-        <v>12</v>
-      </c>
-      <c r="AH2">
-        <v>14.5</v>
-      </c>
-      <c r="AI2">
-        <v>65</v>
-      </c>
-      <c r="AJ2">
-        <v>60</v>
-      </c>
-      <c r="AK2">
-        <v>23</v>
-      </c>
-      <c r="AL2">
-        <v>34</v>
-      </c>
-      <c r="AM2">
-        <v>190</v>
-      </c>
-      <c r="AN2">
-        <v>14</v>
-      </c>
-      <c r="AO2">
-        <v>20</v>
-      </c>
-      <c r="AP2">
-        <v>18.5</v>
-      </c>
-      <c r="AQ2">
-        <v>15</v>
-      </c>
-      <c r="AR2">
-        <v>19</v>
-      </c>
-      <c r="AS2">
-        <v>42</v>
-      </c>
-      <c r="AT2">
-        <v>13</v>
-      </c>
-      <c r="AU2">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AV2">
-        <v>12</v>
-      </c>
-      <c r="AW2">
-        <v>25</v>
-      </c>
-      <c r="AX2">
-        <v>16.5</v>
-      </c>
-      <c r="AY2">
-        <v>11</v>
-      </c>
-      <c r="AZ2">
-        <v>13.5</v>
-      </c>
-      <c r="BA2">
-        <v>30</v>
-      </c>
-      <c r="BB2">
-        <v>30</v>
-      </c>
-      <c r="BC2">
-        <v>20</v>
-      </c>
-      <c r="BD2">
-        <v>27</v>
-      </c>
-      <c r="BE2">
-        <v>48</v>
-      </c>
-      <c r="BF2">
-        <v>13</v>
-      </c>
-      <c r="BG2">
-        <v>18</v>
-      </c>
-      <c r="BH2">
-        <v>4.1</v>
-      </c>
-      <c r="BI2">
-        <v>3.65</v>
-      </c>
-      <c r="BJ2">
-        <v>8.6</v>
-      </c>
       <c r="BK2">
-        <v>5.6</v>
+        <v>4.8</v>
       </c>
       <c r="BL2">
         <v>1000</v>
       </c>
       <c r="BM2">
-        <v>13.5</v>
+        <v>7.2</v>
       </c>
       <c r="BN2">
-        <v>5.7</v>
+        <v>10.5</v>
       </c>
       <c r="BO2">
-        <v>4.9</v>
+        <v>4.3</v>
       </c>
       <c r="BP2">
-        <v>23</v>
+        <v>80</v>
       </c>
       <c r="BQ2">
-        <v>8.199999999999999</v>
+        <v>6.6</v>
       </c>
       <c r="BR2">
-        <v>36</v>
+        <v>100</v>
       </c>
       <c r="BS2">
-        <v>10</v>
+        <v>6.8</v>
       </c>
       <c r="BT2">
-        <v>6.4</v>
+        <v>4.6</v>
       </c>
       <c r="BU2">
-        <v>5.8</v>
+        <v>3.35</v>
       </c>
       <c r="BV2">
-        <v>1000</v>
+        <v>16.5</v>
       </c>
       <c r="BW2">
-        <v>9.199999999999999</v>
+        <v>5.1</v>
       </c>
       <c r="BX2">
-        <v>1000</v>
+        <v>46</v>
       </c>
       <c r="BY2">
-        <v>10.5</v>
+        <v>6.2</v>
       </c>
       <c r="BZ2">
         <v>0</v>
@@ -1153,7 +1165,7 @@
         <v>0</v>
       </c>
       <c r="CB2" t="s">
-        <v>107</v>
+        <v>111</v>
       </c>
     </row>
     <row r="3" spans="1:80">
@@ -1161,775 +1173,775 @@
         <v>81</v>
       </c>
       <c r="B3" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C3" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="D3" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="E3" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="F3">
-        <v>2.88</v>
+        <v>2.32</v>
       </c>
       <c r="G3">
+        <v>2.38</v>
+      </c>
+      <c r="H3">
+        <v>3.05</v>
+      </c>
+      <c r="I3">
         <v>3.15</v>
       </c>
-      <c r="H3">
-        <v>2.92</v>
-      </c>
-      <c r="I3">
-        <v>3.2</v>
-      </c>
       <c r="J3">
-        <v>2.82</v>
+        <v>3.85</v>
       </c>
       <c r="K3">
-        <v>3.05</v>
+        <v>3.95</v>
       </c>
       <c r="L3">
-        <v>1.65</v>
+        <v>1.32</v>
       </c>
       <c r="M3">
-        <v>1.16</v>
+        <v>1.04</v>
       </c>
       <c r="N3">
-        <v>2.4</v>
+        <v>5.2</v>
       </c>
       <c r="O3">
+        <v>1.22</v>
+      </c>
+      <c r="P3">
+        <v>2.42</v>
+      </c>
+      <c r="Q3">
         <v>1.64</v>
       </c>
-      <c r="P3">
-        <v>1.45</v>
-      </c>
-      <c r="Q3">
-        <v>3.05</v>
-      </c>
       <c r="R3">
-        <v>1.16</v>
+        <v>1.57</v>
       </c>
       <c r="S3">
-        <v>6.4</v>
+        <v>2.62</v>
       </c>
       <c r="T3">
-        <v>2.2</v>
+        <v>1.59</v>
       </c>
       <c r="U3">
-        <v>1.7</v>
+        <v>2.58</v>
       </c>
       <c r="V3">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="W3">
-        <v>1.46</v>
+        <v>1.72</v>
       </c>
       <c r="X3">
-        <v>7.8</v>
+        <v>21</v>
       </c>
       <c r="Y3">
-        <v>8.6</v>
+        <v>17</v>
       </c>
       <c r="Z3">
-        <v>19.5</v>
+        <v>25</v>
       </c>
       <c r="AA3">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="AB3">
+        <v>14.5</v>
+      </c>
+      <c r="AC3">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AD3">
+        <v>14</v>
+      </c>
+      <c r="AE3">
+        <v>32</v>
+      </c>
+      <c r="AF3">
+        <v>17.5</v>
+      </c>
+      <c r="AG3">
+        <v>11.5</v>
+      </c>
+      <c r="AH3">
+        <v>15</v>
+      </c>
+      <c r="AI3">
+        <v>36</v>
+      </c>
+      <c r="AJ3">
+        <v>55</v>
+      </c>
+      <c r="AK3">
+        <v>22</v>
+      </c>
+      <c r="AL3">
+        <v>28</v>
+      </c>
+      <c r="AM3">
+        <v>190</v>
+      </c>
+      <c r="AN3">
+        <v>13</v>
+      </c>
+      <c r="AO3">
+        <v>25</v>
+      </c>
+      <c r="AP3">
+        <v>19</v>
+      </c>
+      <c r="AQ3">
+        <v>15.5</v>
+      </c>
+      <c r="AR3">
+        <v>22</v>
+      </c>
+      <c r="AS3">
+        <v>44</v>
+      </c>
+      <c r="AT3">
+        <v>13</v>
+      </c>
+      <c r="AU3">
         <v>8.4</v>
-      </c>
-      <c r="AC3">
-        <v>7.4</v>
-      </c>
-      <c r="AD3">
-        <v>15.5</v>
-      </c>
-      <c r="AE3">
-        <v>55</v>
-      </c>
-      <c r="AF3">
-        <v>22</v>
-      </c>
-      <c r="AG3">
-        <v>17.5</v>
-      </c>
-      <c r="AH3">
-        <v>26</v>
-      </c>
-      <c r="AI3">
-        <v>100</v>
-      </c>
-      <c r="AJ3">
-        <v>150</v>
-      </c>
-      <c r="AK3">
-        <v>120</v>
-      </c>
-      <c r="AL3">
-        <v>460</v>
-      </c>
-      <c r="AM3">
-        <v>500</v>
-      </c>
-      <c r="AN3">
-        <v>500</v>
-      </c>
-      <c r="AO3">
-        <v>70</v>
-      </c>
-      <c r="AP3">
-        <v>6.6</v>
-      </c>
-      <c r="AQ3">
-        <v>7</v>
-      </c>
-      <c r="AR3">
-        <v>15</v>
-      </c>
-      <c r="AS3">
-        <v>20</v>
-      </c>
-      <c r="AT3">
-        <v>7</v>
-      </c>
-      <c r="AU3">
-        <v>6</v>
       </c>
       <c r="AV3">
         <v>12</v>
       </c>
       <c r="AW3">
-        <v>7.2</v>
+        <v>19.5</v>
       </c>
       <c r="AX3">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="AY3">
-        <v>12.5</v>
+        <v>10.5</v>
       </c>
       <c r="AZ3">
+        <v>13.5</v>
+      </c>
+      <c r="BA3">
+        <v>30</v>
+      </c>
+      <c r="BB3">
+        <v>29</v>
+      </c>
+      <c r="BC3">
         <v>20</v>
       </c>
-      <c r="BA3">
-        <v>7.6</v>
-      </c>
-      <c r="BB3">
-        <v>7.4</v>
-      </c>
-      <c r="BC3">
-        <v>7.2</v>
-      </c>
       <c r="BD3">
-        <v>7.6</v>
+        <v>26</v>
       </c>
       <c r="BE3">
-        <v>8.199999999999999</v>
+        <v>50</v>
       </c>
       <c r="BF3">
-        <v>7.4</v>
+        <v>12</v>
       </c>
       <c r="BG3">
-        <v>7.4</v>
+        <v>19</v>
       </c>
       <c r="BH3">
-        <v>2.6</v>
+        <v>4.1</v>
       </c>
       <c r="BI3">
-        <v>2.1</v>
+        <v>3.65</v>
       </c>
       <c r="BJ3">
-        <v>12.5</v>
+        <v>8.6</v>
       </c>
       <c r="BK3">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="BL3">
         <v>1000</v>
       </c>
       <c r="BM3">
-        <v>10.5</v>
+        <v>3.45</v>
       </c>
       <c r="BN3">
-        <v>5.9</v>
+        <v>5.6</v>
       </c>
       <c r="BO3">
-        <v>4.3</v>
+        <v>5.1</v>
       </c>
       <c r="BP3">
-        <v>30</v>
+        <v>16</v>
       </c>
       <c r="BQ3">
-        <v>8.199999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BR3">
-        <v>60</v>
+        <v>36</v>
       </c>
       <c r="BS3">
-        <v>9.6</v>
+        <v>11</v>
       </c>
       <c r="BT3">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="BU3">
-        <v>4.5</v>
+        <v>5.8</v>
       </c>
       <c r="BV3">
-        <v>32</v>
+        <v>1000</v>
       </c>
       <c r="BW3">
-        <v>8.4</v>
+        <v>10</v>
       </c>
       <c r="BX3">
-        <v>60</v>
+        <v>38</v>
       </c>
       <c r="BY3">
-        <v>9.6</v>
+        <v>11.5</v>
       </c>
       <c r="BZ3">
-        <v>65</v>
+        <v>0</v>
       </c>
       <c r="CA3">
-        <v>9.6</v>
+        <v>0</v>
       </c>
       <c r="CB3" t="s">
-        <v>107</v>
+        <v>111</v>
       </c>
     </row>
     <row r="4" spans="1:80">
       <c r="A4" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="B4" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C4" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="D4" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="E4" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="F4">
-        <v>7.2</v>
+        <v>2.92</v>
       </c>
       <c r="G4">
-        <v>8.800000000000001</v>
+        <v>3.25</v>
       </c>
       <c r="H4">
-        <v>1.58</v>
+        <v>2.88</v>
       </c>
       <c r="I4">
+        <v>3.15</v>
+      </c>
+      <c r="J4">
+        <v>2.8</v>
+      </c>
+      <c r="K4">
+        <v>3.05</v>
+      </c>
+      <c r="L4">
         <v>1.62</v>
       </c>
-      <c r="J4">
-        <v>3.95</v>
-      </c>
-      <c r="K4">
-        <v>4.4</v>
-      </c>
-      <c r="L4">
-        <v>1.42</v>
-      </c>
       <c r="M4">
-        <v>1.07</v>
+        <v>1.15</v>
       </c>
       <c r="N4">
-        <v>3.55</v>
+        <v>2.42</v>
       </c>
       <c r="O4">
-        <v>1.35</v>
+        <v>1.63</v>
       </c>
       <c r="P4">
-        <v>1.86</v>
+        <v>1.47</v>
       </c>
       <c r="Q4">
-        <v>2.06</v>
+        <v>2.86</v>
       </c>
       <c r="R4">
-        <v>1.32</v>
+        <v>1.16</v>
       </c>
       <c r="S4">
-        <v>3.75</v>
+        <v>6</v>
       </c>
       <c r="T4">
+        <v>2.2</v>
+      </c>
+      <c r="U4">
+        <v>1.71</v>
+      </c>
+      <c r="V4">
+        <v>1.47</v>
+      </c>
+      <c r="W4">
+        <v>1.46</v>
+      </c>
+      <c r="X4">
+        <v>7.8</v>
+      </c>
+      <c r="Y4">
+        <v>8.4</v>
+      </c>
+      <c r="Z4">
+        <v>19</v>
+      </c>
+      <c r="AA4">
+        <v>150</v>
+      </c>
+      <c r="AB4">
+        <v>8.4</v>
+      </c>
+      <c r="AC4">
+        <v>7.4</v>
+      </c>
+      <c r="AD4">
+        <v>15</v>
+      </c>
+      <c r="AE4">
+        <v>55</v>
+      </c>
+      <c r="AF4">
+        <v>22</v>
+      </c>
+      <c r="AG4">
+        <v>17.5</v>
+      </c>
+      <c r="AH4">
+        <v>25</v>
+      </c>
+      <c r="AI4">
+        <v>90</v>
+      </c>
+      <c r="AJ4">
+        <v>150</v>
+      </c>
+      <c r="AK4">
+        <v>120</v>
+      </c>
+      <c r="AL4">
+        <v>95</v>
+      </c>
+      <c r="AM4">
+        <v>500</v>
+      </c>
+      <c r="AN4">
+        <v>75</v>
+      </c>
+      <c r="AO4">
+        <v>70</v>
+      </c>
+      <c r="AP4">
+        <v>6.6</v>
+      </c>
+      <c r="AQ4">
+        <v>7</v>
+      </c>
+      <c r="AR4">
+        <v>15</v>
+      </c>
+      <c r="AS4">
+        <v>20</v>
+      </c>
+      <c r="AT4">
+        <v>7</v>
+      </c>
+      <c r="AU4">
+        <v>6</v>
+      </c>
+      <c r="AV4">
+        <v>12</v>
+      </c>
+      <c r="AW4">
+        <v>38</v>
+      </c>
+      <c r="AX4">
+        <v>15.5</v>
+      </c>
+      <c r="AY4">
+        <v>12.5</v>
+      </c>
+      <c r="AZ4">
+        <v>20</v>
+      </c>
+      <c r="BA4">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BB4">
+        <v>7.8</v>
+      </c>
+      <c r="BC4">
+        <v>36</v>
+      </c>
+      <c r="BD4">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BE4">
+        <v>8.6</v>
+      </c>
+      <c r="BF4">
+        <v>11.5</v>
+      </c>
+      <c r="BG4">
+        <v>8</v>
+      </c>
+      <c r="BH4">
+        <v>2.62</v>
+      </c>
+      <c r="BI4">
         <v>2.12</v>
       </c>
-      <c r="U4">
-        <v>1.77</v>
-      </c>
-      <c r="V4">
-        <v>2.6</v>
-      </c>
-      <c r="W4">
-        <v>1.15</v>
-      </c>
-      <c r="X4">
-        <v>16</v>
-      </c>
-      <c r="Y4">
-        <v>8.6</v>
-      </c>
-      <c r="Z4">
-        <v>10</v>
-      </c>
-      <c r="AA4">
-        <v>17.5</v>
-      </c>
-      <c r="AB4">
-        <v>25</v>
-      </c>
-      <c r="AC4">
-        <v>11.5</v>
-      </c>
-      <c r="AD4">
-        <v>12</v>
-      </c>
-      <c r="AE4">
-        <v>21</v>
-      </c>
-      <c r="AF4">
-        <v>75</v>
-      </c>
-      <c r="AG4">
-        <v>34</v>
-      </c>
-      <c r="AH4">
-        <v>30</v>
-      </c>
-      <c r="AI4">
-        <v>50</v>
-      </c>
-      <c r="AJ4">
-        <v>700</v>
-      </c>
-      <c r="AK4">
-        <v>700</v>
-      </c>
-      <c r="AL4">
-        <v>700</v>
-      </c>
-      <c r="AM4">
-        <v>700</v>
-      </c>
-      <c r="AN4">
-        <v>700</v>
-      </c>
-      <c r="AO4">
-        <v>12</v>
-      </c>
-      <c r="AP4">
-        <v>10</v>
-      </c>
-      <c r="AQ4">
-        <v>6.4</v>
-      </c>
-      <c r="AR4">
-        <v>7.6</v>
-      </c>
-      <c r="AS4">
-        <v>10.5</v>
-      </c>
-      <c r="AT4">
-        <v>18</v>
-      </c>
-      <c r="AU4">
-        <v>7</v>
-      </c>
-      <c r="AV4">
-        <v>9</v>
-      </c>
-      <c r="AW4">
-        <v>16</v>
-      </c>
-      <c r="AX4">
-        <v>4.7</v>
-      </c>
-      <c r="AY4">
-        <v>20</v>
-      </c>
-      <c r="AZ4">
-        <v>14.5</v>
-      </c>
-      <c r="BA4">
-        <v>30</v>
-      </c>
-      <c r="BB4">
-        <v>4.9</v>
-      </c>
-      <c r="BC4">
-        <v>4.9</v>
-      </c>
-      <c r="BD4">
-        <v>4.9</v>
-      </c>
-      <c r="BE4">
-        <v>4.9</v>
-      </c>
-      <c r="BF4">
-        <v>4.9</v>
-      </c>
-      <c r="BG4">
-        <v>7.8</v>
-      </c>
-      <c r="BH4">
-        <v>3.85</v>
-      </c>
-      <c r="BI4">
-        <v>2.66</v>
-      </c>
       <c r="BJ4">
-        <v>14.5</v>
+        <v>12.5</v>
       </c>
       <c r="BK4">
-        <v>3.65</v>
+        <v>5.8</v>
       </c>
       <c r="BL4">
         <v>1000</v>
       </c>
       <c r="BM4">
-        <v>4.8</v>
+        <v>10.5</v>
       </c>
       <c r="BN4">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="BO4">
-        <v>3.55</v>
+        <v>4.4</v>
       </c>
       <c r="BP4">
+        <v>32</v>
+      </c>
+      <c r="BQ4">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BR4">
+        <v>60</v>
+      </c>
+      <c r="BS4">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="BT4">
+        <v>6</v>
+      </c>
+      <c r="BU4">
+        <v>4.4</v>
+      </c>
+      <c r="BV4">
+        <v>32</v>
+      </c>
+      <c r="BW4">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BX4">
+        <v>60</v>
+      </c>
+      <c r="BY4">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="BZ4">
         <v>1000</v>
       </c>
-      <c r="BQ4">
-        <v>4.6</v>
-      </c>
-      <c r="BR4">
-        <v>1000</v>
-      </c>
-      <c r="BS4">
-        <v>4.7</v>
-      </c>
-      <c r="BT4">
-        <v>4.5</v>
-      </c>
-      <c r="BU4">
-        <v>3.05</v>
-      </c>
-      <c r="BV4">
-        <v>12.5</v>
-      </c>
-      <c r="BW4">
-        <v>3.5</v>
-      </c>
-      <c r="BX4">
-        <v>36</v>
-      </c>
-      <c r="BY4">
-        <v>4.3</v>
-      </c>
-      <c r="BZ4">
-        <v>27</v>
-      </c>
       <c r="CA4">
-        <v>4.1</v>
+        <v>9.4</v>
       </c>
       <c r="CB4" t="s">
-        <v>107</v>
+        <v>111</v>
       </c>
     </row>
     <row r="5" spans="1:80">
       <c r="A5" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="B5" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C5" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="D5" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="E5" t="s">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="F5">
+        <v>6.8</v>
+      </c>
+      <c r="G5">
+        <v>8</v>
+      </c>
+      <c r="H5">
+        <v>1.58</v>
+      </c>
+      <c r="I5">
+        <v>1.64</v>
+      </c>
+      <c r="J5">
+        <v>3.95</v>
+      </c>
+      <c r="K5">
+        <v>4.6</v>
+      </c>
+      <c r="L5">
+        <v>1.41</v>
+      </c>
+      <c r="M5">
+        <v>1.07</v>
+      </c>
+      <c r="N5">
+        <v>3.5</v>
+      </c>
+      <c r="O5">
+        <v>1.35</v>
+      </c>
+      <c r="P5">
+        <v>1.86</v>
+      </c>
+      <c r="Q5">
+        <v>2</v>
+      </c>
+      <c r="R5">
+        <v>1.33</v>
+      </c>
+      <c r="S5">
+        <v>3.6</v>
+      </c>
+      <c r="T5">
+        <v>2.04</v>
+      </c>
+      <c r="U5">
+        <v>1.82</v>
+      </c>
+      <c r="V5">
         <v>2.56</v>
       </c>
-      <c r="G5">
-        <v>2.74</v>
-      </c>
-      <c r="H5">
-        <v>3.4</v>
-      </c>
-      <c r="I5">
-        <v>3.8</v>
-      </c>
-      <c r="J5">
+      <c r="W5">
+        <v>1.14</v>
+      </c>
+      <c r="X5">
+        <v>16</v>
+      </c>
+      <c r="Y5">
+        <v>8.6</v>
+      </c>
+      <c r="Z5">
+        <v>10.5</v>
+      </c>
+      <c r="AA5">
+        <v>17.5</v>
+      </c>
+      <c r="AB5">
+        <v>25</v>
+      </c>
+      <c r="AC5">
+        <v>11.5</v>
+      </c>
+      <c r="AD5">
+        <v>12</v>
+      </c>
+      <c r="AE5">
+        <v>21</v>
+      </c>
+      <c r="AF5">
+        <v>75</v>
+      </c>
+      <c r="AG5">
+        <v>34</v>
+      </c>
+      <c r="AH5">
+        <v>30</v>
+      </c>
+      <c r="AI5">
+        <v>50</v>
+      </c>
+      <c r="AJ5">
+        <v>700</v>
+      </c>
+      <c r="AK5">
+        <v>700</v>
+      </c>
+      <c r="AL5">
+        <v>700</v>
+      </c>
+      <c r="AM5">
+        <v>700</v>
+      </c>
+      <c r="AN5">
+        <v>700</v>
+      </c>
+      <c r="AO5">
+        <v>12.5</v>
+      </c>
+      <c r="AP5">
+        <v>10</v>
+      </c>
+      <c r="AQ5">
+        <v>6.2</v>
+      </c>
+      <c r="AR5">
+        <v>7.6</v>
+      </c>
+      <c r="AS5">
+        <v>10.5</v>
+      </c>
+      <c r="AT5">
+        <v>9</v>
+      </c>
+      <c r="AU5">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AV5">
+        <v>9</v>
+      </c>
+      <c r="AW5">
+        <v>16</v>
+      </c>
+      <c r="AX5">
+        <v>4.5</v>
+      </c>
+      <c r="AY5">
+        <v>20</v>
+      </c>
+      <c r="AZ5">
+        <v>21</v>
+      </c>
+      <c r="BA5">
+        <v>30</v>
+      </c>
+      <c r="BB5">
+        <v>4.8</v>
+      </c>
+      <c r="BC5">
+        <v>4.7</v>
+      </c>
+      <c r="BD5">
+        <v>4.7</v>
+      </c>
+      <c r="BE5">
+        <v>4.7</v>
+      </c>
+      <c r="BF5">
+        <v>4.7</v>
+      </c>
+      <c r="BG5">
+        <v>9</v>
+      </c>
+      <c r="BH5">
+        <v>3.9</v>
+      </c>
+      <c r="BI5">
         <v>2.7</v>
       </c>
-      <c r="K5">
-        <v>2.94</v>
-      </c>
-      <c r="L5">
-        <v>1.7</v>
-      </c>
-      <c r="M5">
-        <v>1.17</v>
-      </c>
-      <c r="N5">
-        <v>2.28</v>
-      </c>
-      <c r="O5">
-        <v>1.7</v>
-      </c>
-      <c r="P5">
-        <v>1.4</v>
-      </c>
-      <c r="Q5">
-        <v>3.25</v>
-      </c>
-      <c r="R5">
-        <v>1.14</v>
-      </c>
-      <c r="S5">
-        <v>7.2</v>
-      </c>
-      <c r="T5">
-        <v>2.34</v>
-      </c>
-      <c r="U5">
-        <v>1.64</v>
-      </c>
-      <c r="V5">
-        <v>1.36</v>
-      </c>
-      <c r="W5">
-        <v>1.57</v>
-      </c>
-      <c r="X5">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="Y5">
-        <v>9</v>
-      </c>
-      <c r="Z5">
-        <v>27</v>
-      </c>
-      <c r="AA5">
-        <v>420</v>
-      </c>
-      <c r="AB5">
-        <v>7.2</v>
-      </c>
-      <c r="AC5">
-        <v>7.2</v>
-      </c>
-      <c r="AD5">
-        <v>17.5</v>
-      </c>
-      <c r="AE5">
-        <v>85</v>
-      </c>
-      <c r="AF5">
-        <v>16.5</v>
-      </c>
-      <c r="AG5">
-        <v>14.5</v>
-      </c>
-      <c r="AH5">
-        <v>40</v>
-      </c>
-      <c r="AI5">
-        <v>540</v>
-      </c>
-      <c r="AJ5">
-        <v>55</v>
-      </c>
-      <c r="AK5">
-        <v>60</v>
-      </c>
-      <c r="AL5">
-        <v>460</v>
-      </c>
-      <c r="AM5">
-        <v>500</v>
-      </c>
-      <c r="AN5">
-        <v>65</v>
-      </c>
-      <c r="AO5">
-        <v>500</v>
-      </c>
-      <c r="AP5">
-        <v>6</v>
-      </c>
-      <c r="AQ5">
-        <v>7.4</v>
-      </c>
-      <c r="AR5">
-        <v>19</v>
-      </c>
-      <c r="AS5">
-        <v>7.6</v>
-      </c>
-      <c r="AT5">
-        <v>5.9</v>
-      </c>
-      <c r="AU5">
-        <v>6</v>
-      </c>
-      <c r="AV5">
-        <v>14.5</v>
-      </c>
-      <c r="AW5">
-        <v>23</v>
-      </c>
-      <c r="AX5">
-        <v>12.5</v>
-      </c>
-      <c r="AY5">
-        <v>11.5</v>
-      </c>
-      <c r="AZ5">
-        <v>20</v>
-      </c>
-      <c r="BA5">
-        <v>7.8</v>
-      </c>
-      <c r="BB5">
-        <v>29</v>
-      </c>
-      <c r="BC5">
-        <v>27</v>
-      </c>
-      <c r="BD5">
-        <v>7.6</v>
-      </c>
-      <c r="BE5">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="BF5">
-        <v>32</v>
-      </c>
-      <c r="BG5">
-        <v>7.8</v>
-      </c>
-      <c r="BH5">
-        <v>2.78</v>
-      </c>
-      <c r="BI5">
-        <v>2.04</v>
-      </c>
       <c r="BJ5">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="BK5">
-        <v>3.85</v>
+        <v>3.65</v>
       </c>
       <c r="BL5">
         <v>1000</v>
       </c>
       <c r="BM5">
-        <v>5.1</v>
+        <v>4.8</v>
       </c>
       <c r="BN5">
-        <v>6.4</v>
+        <v>12.5</v>
       </c>
       <c r="BO5">
-        <v>4.1</v>
+        <v>3.55</v>
       </c>
       <c r="BP5">
-        <v>32</v>
+        <v>1000</v>
       </c>
       <c r="BQ5">
-        <v>4.5</v>
+        <v>4.7</v>
       </c>
       <c r="BR5">
         <v>1000</v>
       </c>
       <c r="BS5">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="BT5">
-        <v>7.6</v>
+        <v>4.6</v>
       </c>
       <c r="BU5">
-        <v>4.8</v>
+        <v>3.1</v>
       </c>
       <c r="BV5">
-        <v>46</v>
+        <v>12.5</v>
       </c>
       <c r="BW5">
-        <v>4.7</v>
+        <v>3.55</v>
       </c>
       <c r="BX5">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="BY5">
-        <v>4.9</v>
+        <v>4.3</v>
       </c>
       <c r="BZ5">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="CA5">
-        <v>4.9</v>
+        <v>4.1</v>
       </c>
       <c r="CB5" t="s">
-        <v>107</v>
+        <v>111</v>
       </c>
     </row>
     <row r="6" spans="1:80">
       <c r="A6" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="B6" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C6" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="D6" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="E6" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="F6">
-        <v>2.48</v>
+        <v>2.54</v>
       </c>
       <c r="G6">
-        <v>2.58</v>
+        <v>2.78</v>
       </c>
       <c r="H6">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="I6">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="J6">
-        <v>2.86</v>
+        <v>2.8</v>
       </c>
       <c r="K6">
-        <v>3.05</v>
+        <v>2.96</v>
       </c>
       <c r="L6">
         <v>1.68</v>
       </c>
       <c r="M6">
-        <v>1.15</v>
+        <v>1.16</v>
       </c>
       <c r="N6">
-        <v>2.32</v>
+        <v>2.26</v>
       </c>
       <c r="O6">
-        <v>1.67</v>
+        <v>1.69</v>
       </c>
       <c r="P6">
-        <v>1.42</v>
+        <v>1.4</v>
       </c>
       <c r="Q6">
         <v>3.1</v>
@@ -1938,88 +1950,88 @@
         <v>1.14</v>
       </c>
       <c r="S6">
-        <v>6.6</v>
+        <v>7.2</v>
       </c>
       <c r="T6">
-        <v>2.22</v>
+        <v>2.34</v>
       </c>
       <c r="U6">
-        <v>1.66</v>
+        <v>1.64</v>
       </c>
       <c r="V6">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="W6">
-        <v>1.63</v>
+        <v>1.56</v>
       </c>
       <c r="X6">
-        <v>7.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="Y6">
-        <v>9.4</v>
+        <v>9</v>
       </c>
       <c r="Z6">
-        <v>34</v>
+        <v>25</v>
       </c>
       <c r="AA6">
-        <v>900</v>
+        <v>420</v>
       </c>
       <c r="AB6">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="AC6">
         <v>7.2</v>
       </c>
       <c r="AD6">
-        <v>18</v>
+        <v>18.5</v>
       </c>
       <c r="AE6">
-        <v>440</v>
+        <v>85</v>
       </c>
       <c r="AF6">
         <v>15.5</v>
       </c>
       <c r="AG6">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="AH6">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="AI6">
-        <v>500</v>
+        <v>540</v>
       </c>
       <c r="AJ6">
-        <v>120</v>
+        <v>55</v>
       </c>
       <c r="AK6">
-        <v>150</v>
+        <v>60</v>
       </c>
       <c r="AL6">
-        <v>230</v>
+        <v>460</v>
       </c>
       <c r="AM6">
         <v>500</v>
       </c>
       <c r="AN6">
-        <v>180</v>
+        <v>65</v>
       </c>
       <c r="AO6">
-        <v>130</v>
+        <v>600</v>
       </c>
       <c r="AP6">
         <v>6</v>
       </c>
       <c r="AQ6">
-        <v>8</v>
+        <v>7.4</v>
       </c>
       <c r="AR6">
-        <v>14.5</v>
+        <v>19</v>
       </c>
       <c r="AS6">
-        <v>9</v>
+        <v>7.6</v>
       </c>
       <c r="AT6">
-        <v>5.8</v>
+        <v>5.9</v>
       </c>
       <c r="AU6">
         <v>6</v>
@@ -2037,91 +2049,91 @@
         <v>11.5</v>
       </c>
       <c r="AZ6">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="BA6">
-        <v>9.199999999999999</v>
+        <v>7.6</v>
       </c>
       <c r="BB6">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="BC6">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="BD6">
-        <v>9</v>
+        <v>7.6</v>
       </c>
       <c r="BE6">
-        <v>9.800000000000001</v>
+        <v>8</v>
       </c>
       <c r="BF6">
         <v>32</v>
       </c>
       <c r="BG6">
-        <v>9.4</v>
+        <v>7.6</v>
       </c>
       <c r="BH6">
-        <v>1000</v>
+        <v>2.74</v>
       </c>
       <c r="BI6">
-        <v>1.04</v>
+        <v>2.02</v>
       </c>
       <c r="BJ6">
-        <v>1000</v>
+        <v>15</v>
       </c>
       <c r="BK6">
-        <v>1.04</v>
+        <v>3.95</v>
       </c>
       <c r="BL6">
         <v>1000</v>
       </c>
       <c r="BM6">
-        <v>1.04</v>
+        <v>5.2</v>
       </c>
       <c r="BN6">
-        <v>1000</v>
+        <v>6.2</v>
       </c>
       <c r="BO6">
-        <v>1.04</v>
+        <v>4</v>
       </c>
       <c r="BP6">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="BQ6">
-        <v>1.04</v>
+        <v>4.6</v>
       </c>
       <c r="BR6">
         <v>1000</v>
       </c>
       <c r="BS6">
-        <v>1.04</v>
+        <v>4.9</v>
       </c>
       <c r="BT6">
-        <v>1000</v>
+        <v>7.8</v>
       </c>
       <c r="BU6">
-        <v>1.04</v>
+        <v>4.9</v>
       </c>
       <c r="BV6">
-        <v>1000</v>
+        <v>48</v>
       </c>
       <c r="BW6">
-        <v>1.04</v>
+        <v>4.8</v>
       </c>
       <c r="BX6">
         <v>1000</v>
       </c>
       <c r="BY6">
-        <v>1.04</v>
+        <v>5</v>
       </c>
       <c r="BZ6">
         <v>1000</v>
       </c>
       <c r="CA6">
-        <v>1.04</v>
+        <v>5</v>
       </c>
       <c r="CB6" t="s">
-        <v>107</v>
+        <v>111</v>
       </c>
     </row>
     <row r="7" spans="1:80">
@@ -2129,241 +2141,241 @@
         <v>82</v>
       </c>
       <c r="B7" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C7" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="D7" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="E7" t="s">
-        <v>104</v>
+        <v>107</v>
       </c>
       <c r="F7">
-        <v>1.76</v>
+        <v>2.42</v>
       </c>
       <c r="G7">
-        <v>1.79</v>
+        <v>2.58</v>
       </c>
       <c r="H7">
-        <v>5.7</v>
+        <v>3.55</v>
       </c>
       <c r="I7">
-        <v>6</v>
+        <v>4.3</v>
       </c>
       <c r="J7">
-        <v>3.7</v>
+        <v>2.72</v>
       </c>
       <c r="K7">
-        <v>3.8</v>
+        <v>3.1</v>
       </c>
       <c r="L7">
-        <v>1.5</v>
+        <v>1.68</v>
       </c>
       <c r="M7">
-        <v>1.1</v>
+        <v>1.16</v>
       </c>
       <c r="N7">
-        <v>3.15</v>
+        <v>2.28</v>
       </c>
       <c r="O7">
-        <v>1.45</v>
+        <v>1.66</v>
       </c>
       <c r="P7">
-        <v>1.7</v>
+        <v>1.41</v>
       </c>
       <c r="Q7">
-        <v>2.34</v>
+        <v>3</v>
       </c>
       <c r="R7">
-        <v>1.25</v>
+        <v>1.14</v>
       </c>
       <c r="S7">
-        <v>4.6</v>
+        <v>6.4</v>
       </c>
       <c r="T7">
-        <v>2.12</v>
+        <v>2.3</v>
       </c>
       <c r="U7">
-        <v>1.84</v>
+        <v>1.63</v>
       </c>
       <c r="V7">
-        <v>1.2</v>
+        <v>1.31</v>
       </c>
       <c r="W7">
-        <v>2.26</v>
+        <v>1.63</v>
       </c>
       <c r="X7">
-        <v>12</v>
+        <v>7.2</v>
       </c>
       <c r="Y7">
-        <v>16.5</v>
+        <v>9.6</v>
       </c>
       <c r="Z7">
-        <v>100</v>
+        <v>34</v>
       </c>
       <c r="AA7">
         <v>900</v>
       </c>
       <c r="AB7">
-        <v>6.6</v>
+        <v>7</v>
       </c>
       <c r="AC7">
-        <v>8.4</v>
+        <v>7.2</v>
       </c>
       <c r="AD7">
+        <v>19</v>
+      </c>
+      <c r="AE7">
+        <v>440</v>
+      </c>
+      <c r="AF7">
+        <v>15</v>
+      </c>
+      <c r="AG7">
+        <v>14</v>
+      </c>
+      <c r="AH7">
+        <v>38</v>
+      </c>
+      <c r="AI7">
+        <v>500</v>
+      </c>
+      <c r="AJ7">
+        <v>55</v>
+      </c>
+      <c r="AK7">
+        <v>150</v>
+      </c>
+      <c r="AL7">
+        <v>460</v>
+      </c>
+      <c r="AM7">
+        <v>500</v>
+      </c>
+      <c r="AN7">
+        <v>180</v>
+      </c>
+      <c r="AO7">
+        <v>600</v>
+      </c>
+      <c r="AP7">
+        <v>6</v>
+      </c>
+      <c r="AQ7">
+        <v>7.6</v>
+      </c>
+      <c r="AR7">
+        <v>14.5</v>
+      </c>
+      <c r="AS7">
+        <v>9.4</v>
+      </c>
+      <c r="AT7">
+        <v>5.8</v>
+      </c>
+      <c r="AU7">
+        <v>6</v>
+      </c>
+      <c r="AV7">
+        <v>14.5</v>
+      </c>
+      <c r="AW7">
         <v>23</v>
       </c>
-      <c r="AE7">
-        <v>700</v>
-      </c>
-      <c r="AF7">
+      <c r="AX7">
+        <v>12.5</v>
+      </c>
+      <c r="AY7">
+        <v>11.5</v>
+      </c>
+      <c r="AZ7">
+        <v>16</v>
+      </c>
+      <c r="BA7">
+        <v>9.6</v>
+      </c>
+      <c r="BB7">
+        <v>26</v>
+      </c>
+      <c r="BC7">
+        <v>26</v>
+      </c>
+      <c r="BD7">
         <v>9.4</v>
       </c>
-      <c r="AG7">
-        <v>10.5</v>
-      </c>
-      <c r="AH7">
-        <v>27</v>
-      </c>
-      <c r="AI7">
-        <v>260</v>
-      </c>
-      <c r="AJ7">
-        <v>19</v>
-      </c>
-      <c r="AK7">
-        <v>27</v>
-      </c>
-      <c r="AL7">
-        <v>380</v>
-      </c>
-      <c r="AM7">
-        <v>580</v>
-      </c>
-      <c r="AN7">
-        <v>16.5</v>
-      </c>
-      <c r="AO7">
-        <v>700</v>
-      </c>
-      <c r="AP7">
+      <c r="BE7">
         <v>10</v>
       </c>
-      <c r="AQ7">
-        <v>15.5</v>
-      </c>
-      <c r="AR7">
-        <v>30</v>
-      </c>
-      <c r="AS7">
-        <v>14.5</v>
-      </c>
-      <c r="AT7">
-        <v>5.9</v>
-      </c>
-      <c r="AU7">
-        <v>7.6</v>
-      </c>
-      <c r="AV7">
-        <v>18.5</v>
-      </c>
-      <c r="AW7">
+      <c r="BF7">
+        <v>32</v>
+      </c>
+      <c r="BG7">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="BH7">
+        <v>2.52</v>
+      </c>
+      <c r="BI7">
+        <v>2.08</v>
+      </c>
+      <c r="BJ7">
         <v>13</v>
       </c>
-      <c r="AX7">
-        <v>8.4</v>
-      </c>
-      <c r="AY7">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AZ7">
-        <v>20</v>
-      </c>
-      <c r="BA7">
-        <v>13.5</v>
-      </c>
-      <c r="BB7">
-        <v>16.5</v>
-      </c>
-      <c r="BC7">
-        <v>18.5</v>
-      </c>
-      <c r="BD7">
-        <v>40</v>
-      </c>
-      <c r="BE7">
-        <v>14.5</v>
-      </c>
-      <c r="BF7">
-        <v>14</v>
-      </c>
-      <c r="BG7">
-        <v>14</v>
-      </c>
-      <c r="BH7">
-        <v>1000</v>
-      </c>
-      <c r="BI7">
-        <v>1.04</v>
-      </c>
-      <c r="BJ7">
-        <v>1000</v>
-      </c>
       <c r="BK7">
-        <v>1.04</v>
+        <v>6.2</v>
       </c>
       <c r="BL7">
         <v>1000</v>
       </c>
       <c r="BM7">
-        <v>1.04</v>
+        <v>11.5</v>
       </c>
       <c r="BN7">
-        <v>1000</v>
+        <v>5.3</v>
       </c>
       <c r="BO7">
-        <v>1.04</v>
+        <v>3.95</v>
       </c>
       <c r="BP7">
         <v>1000</v>
       </c>
       <c r="BQ7">
-        <v>1.04</v>
+        <v>8</v>
       </c>
       <c r="BR7">
         <v>1000</v>
       </c>
       <c r="BS7">
-        <v>1.04</v>
+        <v>10</v>
       </c>
       <c r="BT7">
-        <v>1000</v>
+        <v>7</v>
       </c>
       <c r="BU7">
-        <v>1.04</v>
+        <v>5</v>
       </c>
       <c r="BV7">
         <v>1000</v>
       </c>
       <c r="BW7">
-        <v>1.04</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BX7">
         <v>1000</v>
       </c>
       <c r="BY7">
-        <v>1.04</v>
+        <v>10</v>
       </c>
       <c r="BZ7">
         <v>1000</v>
       </c>
       <c r="CA7">
-        <v>1.04</v>
+        <v>10</v>
       </c>
       <c r="CB7" t="s">
-        <v>107</v>
+        <v>111</v>
       </c>
     </row>
     <row r="8" spans="1:80">
@@ -2371,52 +2383,52 @@
         <v>83</v>
       </c>
       <c r="B8" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C8" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="D8" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="E8" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="F8">
-        <v>2.84</v>
+        <v>1.75</v>
       </c>
       <c r="G8">
-        <v>2.92</v>
+        <v>1.76</v>
       </c>
       <c r="H8">
-        <v>2.86</v>
+        <v>5.9</v>
       </c>
       <c r="I8">
-        <v>2.92</v>
+        <v>6.2</v>
       </c>
       <c r="J8">
-        <v>3.2</v>
+        <v>3.75</v>
       </c>
       <c r="K8">
-        <v>3.3</v>
+        <v>3.8</v>
       </c>
       <c r="L8">
-        <v>1.48</v>
+        <v>1.5</v>
       </c>
       <c r="M8">
         <v>1.09</v>
       </c>
       <c r="N8">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="O8">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="P8">
         <v>1.71</v>
       </c>
       <c r="Q8">
-        <v>2.28</v>
+        <v>2.3</v>
       </c>
       <c r="R8">
         <v>1.27</v>
@@ -2425,136 +2437,136 @@
         <v>4.4</v>
       </c>
       <c r="T8">
-        <v>1.91</v>
+        <v>2.14</v>
       </c>
       <c r="U8">
-        <v>1.99</v>
+        <v>1.81</v>
       </c>
       <c r="V8">
-        <v>1.52</v>
+        <v>1.19</v>
       </c>
       <c r="W8">
-        <v>1.52</v>
+        <v>2.3</v>
       </c>
       <c r="X8">
-        <v>14.5</v>
+        <v>12</v>
       </c>
       <c r="Y8">
+        <v>17</v>
+      </c>
+      <c r="Z8">
+        <v>100</v>
+      </c>
+      <c r="AA8">
+        <v>900</v>
+      </c>
+      <c r="AB8">
+        <v>6.4</v>
+      </c>
+      <c r="AC8">
+        <v>8.6</v>
+      </c>
+      <c r="AD8">
+        <v>23</v>
+      </c>
+      <c r="AE8">
+        <v>700</v>
+      </c>
+      <c r="AF8">
         <v>9.4</v>
       </c>
-      <c r="Z8">
-        <v>17.5</v>
-      </c>
-      <c r="AA8">
-        <v>65</v>
-      </c>
-      <c r="AB8">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AC8">
-        <v>7.4</v>
-      </c>
-      <c r="AD8">
-        <v>13</v>
-      </c>
-      <c r="AE8">
-        <v>50</v>
-      </c>
-      <c r="AF8">
+      <c r="AG8">
+        <v>10.5</v>
+      </c>
+      <c r="AH8">
+        <v>28</v>
+      </c>
+      <c r="AI8">
+        <v>260</v>
+      </c>
+      <c r="AJ8">
         <v>18.5</v>
       </c>
-      <c r="AG8">
-        <v>13.5</v>
-      </c>
-      <c r="AH8">
-        <v>19.5</v>
-      </c>
-      <c r="AI8">
+      <c r="AK8">
+        <v>21</v>
+      </c>
+      <c r="AL8">
         <v>55</v>
-      </c>
-      <c r="AJ8">
-        <v>55</v>
-      </c>
-      <c r="AK8">
-        <v>50</v>
-      </c>
-      <c r="AL8">
-        <v>70</v>
       </c>
       <c r="AM8">
         <v>580</v>
       </c>
       <c r="AN8">
-        <v>40</v>
+        <v>17</v>
       </c>
       <c r="AO8">
-        <v>36</v>
+        <v>700</v>
       </c>
       <c r="AP8">
         <v>10</v>
       </c>
       <c r="AQ8">
+        <v>15</v>
+      </c>
+      <c r="AR8">
+        <v>30</v>
+      </c>
+      <c r="AS8">
+        <v>13.5</v>
+      </c>
+      <c r="AT8">
+        <v>5.8</v>
+      </c>
+      <c r="AU8">
+        <v>7.6</v>
+      </c>
+      <c r="AV8">
+        <v>20</v>
+      </c>
+      <c r="AW8">
+        <v>28</v>
+      </c>
+      <c r="AX8">
         <v>8.4</v>
       </c>
-      <c r="AR8">
-        <v>15.5</v>
-      </c>
-      <c r="AS8">
-        <v>38</v>
-      </c>
-      <c r="AT8">
-        <v>8.6</v>
-      </c>
-      <c r="AU8">
-        <v>6.6</v>
-      </c>
-      <c r="AV8">
-        <v>11.5</v>
-      </c>
-      <c r="AW8">
-        <v>30</v>
-      </c>
-      <c r="AX8">
-        <v>16.5</v>
-      </c>
       <c r="AY8">
-        <v>11.5</v>
+        <v>9</v>
       </c>
       <c r="AZ8">
+        <v>24</v>
+      </c>
+      <c r="BA8">
+        <v>12.5</v>
+      </c>
+      <c r="BB8">
         <v>16</v>
       </c>
-      <c r="BA8">
-        <v>38</v>
-      </c>
-      <c r="BB8">
-        <v>29</v>
-      </c>
       <c r="BC8">
-        <v>28</v>
+        <v>18.5</v>
       </c>
       <c r="BD8">
-        <v>23</v>
+        <v>40</v>
       </c>
       <c r="BE8">
-        <v>14.5</v>
+        <v>13.5</v>
       </c>
       <c r="BF8">
-        <v>30</v>
+        <v>14</v>
       </c>
       <c r="BG8">
-        <v>27</v>
+        <v>13</v>
       </c>
       <c r="BH8">
         <v>3.05</v>
       </c>
       <c r="BI8">
-        <v>2.8</v>
+        <v>2.78</v>
       </c>
       <c r="BJ8">
-        <v>10</v>
+        <v>11.5</v>
       </c>
       <c r="BK8">
-        <v>6.2</v>
+        <v>9</v>
       </c>
       <c r="BL8">
         <v>1000</v>
@@ -2563,49 +2575,49 @@
         <v>15.5</v>
       </c>
       <c r="BN8">
-        <v>5.8</v>
+        <v>4.1</v>
       </c>
       <c r="BO8">
-        <v>4.5</v>
+        <v>3.7</v>
       </c>
       <c r="BP8">
-        <v>25</v>
+        <v>12.5</v>
       </c>
       <c r="BQ8">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BR8">
-        <v>40</v>
+        <v>34</v>
       </c>
       <c r="BS8">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="BT8">
-        <v>5.7</v>
+        <v>9.4</v>
       </c>
       <c r="BU8">
-        <v>4.3</v>
+        <v>7.4</v>
       </c>
       <c r="BV8">
-        <v>23</v>
+        <v>1000</v>
       </c>
       <c r="BW8">
-        <v>10</v>
+        <v>13.5</v>
       </c>
       <c r="BX8">
-        <v>40</v>
+        <v>1000</v>
       </c>
       <c r="BY8">
-        <v>12</v>
+        <v>13.5</v>
       </c>
       <c r="BZ8">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="CA8">
-        <v>11.5</v>
+        <v>10.5</v>
       </c>
       <c r="CB8" t="s">
-        <v>107</v>
+        <v>111</v>
       </c>
     </row>
     <row r="9" spans="1:80">
@@ -2613,241 +2625,483 @@
         <v>84</v>
       </c>
       <c r="B9" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C9" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="D9" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="E9" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="F9">
-        <v>2.14</v>
+        <v>2.8</v>
       </c>
       <c r="G9">
-        <v>2.26</v>
+        <v>2.94</v>
       </c>
       <c r="H9">
-        <v>3.55</v>
+        <v>2.86</v>
       </c>
       <c r="I9">
-        <v>4.1</v>
+        <v>2.94</v>
       </c>
       <c r="J9">
-        <v>3.35</v>
+        <v>3.15</v>
       </c>
       <c r="K9">
-        <v>3.7</v>
+        <v>3.3</v>
       </c>
       <c r="L9">
-        <v>1.44</v>
+        <v>1.48</v>
       </c>
       <c r="M9">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="N9">
-        <v>3.5</v>
+        <v>3.1</v>
       </c>
       <c r="O9">
-        <v>1.36</v>
+        <v>1.43</v>
       </c>
       <c r="P9">
-        <v>1.83</v>
+        <v>1.69</v>
       </c>
       <c r="Q9">
-        <v>2.08</v>
+        <v>2.28</v>
       </c>
       <c r="R9">
-        <v>1.31</v>
+        <v>1.27</v>
       </c>
       <c r="S9">
-        <v>3.75</v>
+        <v>4.3</v>
       </c>
       <c r="T9">
-        <v>1.83</v>
+        <v>1.91</v>
       </c>
       <c r="U9">
-        <v>2.02</v>
+        <v>1.99</v>
       </c>
       <c r="V9">
-        <v>1.33</v>
+        <v>1.51</v>
       </c>
       <c r="W9">
-        <v>1.79</v>
+        <v>1.52</v>
       </c>
       <c r="X9">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="Y9">
-        <v>14.5</v>
+        <v>9.4</v>
       </c>
       <c r="Z9">
-        <v>27</v>
+        <v>18</v>
       </c>
       <c r="AA9">
-        <v>85</v>
+        <v>65</v>
       </c>
       <c r="AB9">
-        <v>9.4</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AC9">
-        <v>8</v>
+        <v>7.4</v>
       </c>
       <c r="AD9">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="AE9">
         <v>50</v>
       </c>
       <c r="AF9">
-        <v>15</v>
+        <v>18.5</v>
       </c>
       <c r="AG9">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="AH9">
-        <v>21</v>
+        <v>19.5</v>
       </c>
       <c r="AI9">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="AJ9">
-        <v>32</v>
+        <v>55</v>
       </c>
       <c r="AK9">
-        <v>29</v>
+        <v>50</v>
       </c>
       <c r="AL9">
+        <v>70</v>
+      </c>
+      <c r="AM9">
+        <v>580</v>
+      </c>
+      <c r="AN9">
+        <v>40</v>
+      </c>
+      <c r="AO9">
         <v>46</v>
       </c>
-      <c r="AM9">
-        <v>120</v>
-      </c>
-      <c r="AN9">
-        <v>22</v>
-      </c>
-      <c r="AO9">
-        <v>60</v>
-      </c>
       <c r="AP9">
-        <v>9.4</v>
+        <v>10</v>
       </c>
       <c r="AQ9">
-        <v>10.5</v>
+        <v>8.4</v>
       </c>
       <c r="AR9">
-        <v>21</v>
+        <v>15.5</v>
       </c>
       <c r="AS9">
-        <v>6.8</v>
+        <v>38</v>
       </c>
       <c r="AT9">
-        <v>7.8</v>
+        <v>8.4</v>
       </c>
       <c r="AU9">
         <v>6.6</v>
       </c>
       <c r="AV9">
-        <v>12.5</v>
+        <v>11.5</v>
       </c>
       <c r="AW9">
-        <v>6.4</v>
+        <v>30</v>
       </c>
       <c r="AX9">
-        <v>11</v>
+        <v>16.5</v>
       </c>
       <c r="AY9">
-        <v>9.6</v>
+        <v>11.5</v>
       </c>
       <c r="AZ9">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="BA9">
-        <v>6.6</v>
+        <v>38</v>
       </c>
       <c r="BB9">
-        <v>6</v>
+        <v>29</v>
       </c>
       <c r="BC9">
-        <v>5.9</v>
+        <v>28</v>
       </c>
       <c r="BD9">
-        <v>6.4</v>
+        <v>23</v>
       </c>
       <c r="BE9">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="BF9">
-        <v>17</v>
+        <v>30</v>
       </c>
       <c r="BG9">
-        <v>6.6</v>
+        <v>27</v>
       </c>
       <c r="BH9">
-        <v>3.35</v>
+        <v>3.05</v>
       </c>
       <c r="BI9">
-        <v>2.68</v>
+        <v>2.8</v>
       </c>
       <c r="BJ9">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="BK9">
-        <v>5.2</v>
+        <v>6.2</v>
       </c>
       <c r="BL9">
         <v>1000</v>
       </c>
       <c r="BM9">
+        <v>15.5</v>
+      </c>
+      <c r="BN9">
+        <v>5.8</v>
+      </c>
+      <c r="BO9">
+        <v>4.5</v>
+      </c>
+      <c r="BP9">
+        <v>25</v>
+      </c>
+      <c r="BQ9">
+        <v>10</v>
+      </c>
+      <c r="BR9">
+        <v>40</v>
+      </c>
+      <c r="BS9">
+        <v>12</v>
+      </c>
+      <c r="BT9">
+        <v>5.7</v>
+      </c>
+      <c r="BU9">
+        <v>4.3</v>
+      </c>
+      <c r="BV9">
+        <v>23</v>
+      </c>
+      <c r="BW9">
+        <v>10</v>
+      </c>
+      <c r="BX9">
+        <v>40</v>
+      </c>
+      <c r="BY9">
+        <v>12</v>
+      </c>
+      <c r="BZ9">
+        <v>36</v>
+      </c>
+      <c r="CA9">
+        <v>11.5</v>
+      </c>
+      <c r="CB9" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="10" spans="1:80">
+      <c r="A10" t="s">
+        <v>85</v>
+      </c>
+      <c r="B10" t="s">
+        <v>86</v>
+      </c>
+      <c r="C10" t="s">
+        <v>92</v>
+      </c>
+      <c r="D10" t="s">
+        <v>101</v>
+      </c>
+      <c r="E10" t="s">
+        <v>110</v>
+      </c>
+      <c r="F10">
+        <v>2.08</v>
+      </c>
+      <c r="G10">
+        <v>2.26</v>
+      </c>
+      <c r="H10">
+        <v>3.65</v>
+      </c>
+      <c r="I10">
+        <v>4.3</v>
+      </c>
+      <c r="J10">
+        <v>3.3</v>
+      </c>
+      <c r="K10">
+        <v>3.8</v>
+      </c>
+      <c r="L10">
+        <v>1.42</v>
+      </c>
+      <c r="M10">
+        <v>1.08</v>
+      </c>
+      <c r="N10">
+        <v>3.35</v>
+      </c>
+      <c r="O10">
+        <v>1.36</v>
+      </c>
+      <c r="P10">
+        <v>1.81</v>
+      </c>
+      <c r="Q10">
+        <v>2.08</v>
+      </c>
+      <c r="R10">
+        <v>1.31</v>
+      </c>
+      <c r="S10">
+        <v>3.7</v>
+      </c>
+      <c r="T10">
+        <v>1.83</v>
+      </c>
+      <c r="U10">
+        <v>2.02</v>
+      </c>
+      <c r="V10">
+        <v>1.31</v>
+      </c>
+      <c r="W10">
+        <v>1.79</v>
+      </c>
+      <c r="X10">
+        <v>14</v>
+      </c>
+      <c r="Y10">
+        <v>14.5</v>
+      </c>
+      <c r="Z10">
+        <v>29</v>
+      </c>
+      <c r="AA10">
+        <v>85</v>
+      </c>
+      <c r="AB10">
+        <v>9.4</v>
+      </c>
+      <c r="AC10">
+        <v>8</v>
+      </c>
+      <c r="AD10">
+        <v>17.5</v>
+      </c>
+      <c r="AE10">
+        <v>55</v>
+      </c>
+      <c r="AF10">
+        <v>15</v>
+      </c>
+      <c r="AG10">
+        <v>12.5</v>
+      </c>
+      <c r="AH10">
+        <v>21</v>
+      </c>
+      <c r="AI10">
+        <v>65</v>
+      </c>
+      <c r="AJ10">
+        <v>28</v>
+      </c>
+      <c r="AK10">
+        <v>28</v>
+      </c>
+      <c r="AL10">
+        <v>46</v>
+      </c>
+      <c r="AM10">
+        <v>120</v>
+      </c>
+      <c r="AN10">
+        <v>22</v>
+      </c>
+      <c r="AO10">
+        <v>60</v>
+      </c>
+      <c r="AP10">
+        <v>9.4</v>
+      </c>
+      <c r="AQ10">
+        <v>10.5</v>
+      </c>
+      <c r="AR10">
+        <v>21</v>
+      </c>
+      <c r="AS10">
+        <v>7</v>
+      </c>
+      <c r="AT10">
+        <v>7.8</v>
+      </c>
+      <c r="AU10">
+        <v>6.6</v>
+      </c>
+      <c r="AV10">
+        <v>12.5</v>
+      </c>
+      <c r="AW10">
+        <v>6.6</v>
+      </c>
+      <c r="AX10">
+        <v>11</v>
+      </c>
+      <c r="AY10">
         <v>9.6</v>
       </c>
-      <c r="BN9">
+      <c r="AZ10">
+        <v>15.5</v>
+      </c>
+      <c r="BA10">
+        <v>6.8</v>
+      </c>
+      <c r="BB10">
+        <v>20</v>
+      </c>
+      <c r="BC10">
+        <v>18</v>
+      </c>
+      <c r="BD10">
+        <v>6.4</v>
+      </c>
+      <c r="BE10">
+        <v>7</v>
+      </c>
+      <c r="BF10">
+        <v>15.5</v>
+      </c>
+      <c r="BG10">
+        <v>6.6</v>
+      </c>
+      <c r="BH10">
+        <v>3.35</v>
+      </c>
+      <c r="BI10">
+        <v>2.7</v>
+      </c>
+      <c r="BJ10">
+        <v>10.5</v>
+      </c>
+      <c r="BK10">
+        <v>5.2</v>
+      </c>
+      <c r="BL10">
+        <v>1000</v>
+      </c>
+      <c r="BM10">
+        <v>9.6</v>
+      </c>
+      <c r="BN10">
         <v>5.1</v>
       </c>
-      <c r="BO9">
-        <v>3.95</v>
-      </c>
-      <c r="BP9">
-        <v>17.5</v>
-      </c>
-      <c r="BQ9">
-        <v>6.4</v>
-      </c>
-      <c r="BR9">
-        <v>34</v>
-      </c>
-      <c r="BS9">
+      <c r="BO10">
+        <v>3.9</v>
+      </c>
+      <c r="BP10">
+        <v>16.5</v>
+      </c>
+      <c r="BQ10">
+        <v>6.2</v>
+      </c>
+      <c r="BR10">
+        <v>1000</v>
+      </c>
+      <c r="BS10">
+        <v>7.8</v>
+      </c>
+      <c r="BT10">
+        <v>7.4</v>
+      </c>
+      <c r="BU10">
+        <v>5.6</v>
+      </c>
+      <c r="BV10">
+        <v>36</v>
+      </c>
+      <c r="BW10">
         <v>8</v>
       </c>
-      <c r="BT9">
-        <v>7.2</v>
-      </c>
-      <c r="BU9">
-        <v>5.4</v>
-      </c>
-      <c r="BV9">
-        <v>34</v>
-      </c>
-      <c r="BW9">
-        <v>8</v>
-      </c>
-      <c r="BX9">
+      <c r="BX10">
         <v>1000</v>
       </c>
-      <c r="BY9">
+      <c r="BY10">
         <v>8.4</v>
       </c>
-      <c r="BZ9">
-        <v>32</v>
-      </c>
-      <c r="CA9">
-        <v>7.8</v>
-      </c>
-      <c r="CB9" t="s">
-        <v>107</v>
+      <c r="BZ10">
+        <v>1000</v>
+      </c>
+      <c r="CA10">
+        <v>7.6</v>
+      </c>
+      <c r="CB10" t="s">
+        <v>111</v>
       </c>
     </row>
   </sheetData>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-08-11.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-08-11.xlsx
@@ -277,7 +277,7 @@
     <t>2026-08-11</t>
   </si>
   <si>
-    <t>11:30:00</t>
+    <t>09:30:00</t>
   </si>
   <si>
     <t>17:00:00</t>
@@ -349,7 +349,7 @@
     <t>Union Espanola</t>
   </si>
   <si>
-    <t>2026-08-11 03:26:12</t>
+    <t>2026-08-11 05:33:11</t>
   </si>
 </sst>
 </file>
@@ -949,31 +949,31 @@
         <v>6.8</v>
       </c>
       <c r="H2">
-        <v>1.75</v>
+        <v>1.77</v>
       </c>
       <c r="I2">
-        <v>1.91</v>
+        <v>1.93</v>
       </c>
       <c r="J2">
-        <v>3.2</v>
+        <v>3.15</v>
       </c>
       <c r="K2">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="L2">
-        <v>1.49</v>
+        <v>1.55</v>
       </c>
       <c r="M2">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="N2">
-        <v>2.56</v>
+        <v>2.66</v>
       </c>
       <c r="O2">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="P2">
-        <v>1.53</v>
+        <v>1.55</v>
       </c>
       <c r="Q2">
         <v>2.54</v>
@@ -982,13 +982,13 @@
         <v>1.19</v>
       </c>
       <c r="S2">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="T2">
-        <v>2.24</v>
+        <v>2.22</v>
       </c>
       <c r="U2">
-        <v>1.65</v>
+        <v>1.68</v>
       </c>
       <c r="V2">
         <v>2.08</v>
@@ -997,109 +997,109 @@
         <v>1.17</v>
       </c>
       <c r="X2">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="Y2">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="Z2">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="AA2">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AB2">
         <v>15.5</v>
       </c>
       <c r="AC2">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AD2">
         <v>11.5</v>
       </c>
       <c r="AE2">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AF2">
-        <v>55</v>
+        <v>48</v>
       </c>
       <c r="AG2">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AH2">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AI2">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="AJ2">
-        <v>250</v>
+        <v>900</v>
       </c>
       <c r="AK2">
-        <v>150</v>
+        <v>140</v>
       </c>
       <c r="AL2">
-        <v>170</v>
+        <v>160</v>
       </c>
       <c r="AM2">
-        <v>290</v>
+        <v>580</v>
       </c>
       <c r="AN2">
-        <v>280</v>
+        <v>260</v>
       </c>
       <c r="AO2">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AP2">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AQ2">
-        <v>5.2</v>
+        <v>5.5</v>
       </c>
       <c r="AR2">
-        <v>7.2</v>
+        <v>8</v>
       </c>
       <c r="AS2">
         <v>17</v>
       </c>
       <c r="AT2">
-        <v>11</v>
+        <v>12.5</v>
       </c>
       <c r="AU2">
-        <v>6.2</v>
+        <v>7</v>
       </c>
       <c r="AV2">
-        <v>8.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AW2">
         <v>21</v>
       </c>
       <c r="AX2">
-        <v>7</v>
+        <v>36</v>
       </c>
       <c r="AY2">
         <v>21</v>
       </c>
       <c r="AZ2">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="BA2">
-        <v>7.2</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BB2">
-        <v>7.8</v>
+        <v>8.4</v>
       </c>
       <c r="BC2">
-        <v>7.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BD2">
-        <v>7.8</v>
+        <v>8.4</v>
       </c>
       <c r="BE2">
-        <v>7.8</v>
+        <v>8.6</v>
       </c>
       <c r="BF2">
-        <v>7.8</v>
+        <v>8.6</v>
       </c>
       <c r="BG2">
         <v>17</v>
@@ -1114,7 +1114,7 @@
         <v>14.5</v>
       </c>
       <c r="BK2">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="BL2">
         <v>1000</v>
@@ -1129,7 +1129,7 @@
         <v>4.3</v>
       </c>
       <c r="BP2">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="BQ2">
         <v>6.6</v>
@@ -1156,7 +1156,7 @@
         <v>46</v>
       </c>
       <c r="BY2">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="BZ2">
         <v>0</v>
@@ -1185,19 +1185,19 @@
         <v>103</v>
       </c>
       <c r="F3">
-        <v>2.32</v>
+        <v>2.38</v>
       </c>
       <c r="G3">
-        <v>2.38</v>
+        <v>2.4</v>
       </c>
       <c r="H3">
+        <v>3</v>
+      </c>
+      <c r="I3">
         <v>3.05</v>
       </c>
-      <c r="I3">
-        <v>3.15</v>
-      </c>
       <c r="J3">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="K3">
         <v>3.95</v>
@@ -1209,7 +1209,7 @@
         <v>1.04</v>
       </c>
       <c r="N3">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="O3">
         <v>1.22</v>
@@ -1218,37 +1218,37 @@
         <v>2.42</v>
       </c>
       <c r="Q3">
-        <v>1.64</v>
+        <v>1.67</v>
       </c>
       <c r="R3">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="S3">
-        <v>2.62</v>
+        <v>2.68</v>
       </c>
       <c r="T3">
-        <v>1.59</v>
+        <v>1.6</v>
       </c>
       <c r="U3">
         <v>2.58</v>
       </c>
       <c r="V3">
-        <v>1.46</v>
+        <v>1.48</v>
       </c>
       <c r="W3">
-        <v>1.72</v>
+        <v>1.71</v>
       </c>
       <c r="X3">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="Y3">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="Z3">
         <v>25</v>
       </c>
       <c r="AA3">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="AB3">
         <v>14.5</v>
@@ -1257,10 +1257,10 @@
         <v>9.199999999999999</v>
       </c>
       <c r="AD3">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="AE3">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="AF3">
         <v>17.5</v>
@@ -1269,28 +1269,28 @@
         <v>11.5</v>
       </c>
       <c r="AH3">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="AI3">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="AJ3">
-        <v>55</v>
+        <v>34</v>
       </c>
       <c r="AK3">
         <v>22</v>
       </c>
       <c r="AL3">
-        <v>28</v>
+        <v>55</v>
       </c>
       <c r="AM3">
-        <v>190</v>
+        <v>60</v>
       </c>
       <c r="AN3">
         <v>13</v>
       </c>
       <c r="AO3">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="AP3">
         <v>19</v>
@@ -1302,7 +1302,7 @@
         <v>22</v>
       </c>
       <c r="AS3">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="AT3">
         <v>13</v>
@@ -1314,7 +1314,7 @@
         <v>12</v>
       </c>
       <c r="AW3">
-        <v>19.5</v>
+        <v>27</v>
       </c>
       <c r="AX3">
         <v>16</v>
@@ -1332,7 +1332,7 @@
         <v>29</v>
       </c>
       <c r="BC3">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="BD3">
         <v>26</v>
@@ -1341,16 +1341,16 @@
         <v>50</v>
       </c>
       <c r="BF3">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="BG3">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="BH3">
         <v>4.1</v>
       </c>
       <c r="BI3">
-        <v>3.65</v>
+        <v>3.75</v>
       </c>
       <c r="BJ3">
         <v>8.6</v>
@@ -1430,76 +1430,76 @@
         <v>2.92</v>
       </c>
       <c r="G4">
+        <v>3.15</v>
+      </c>
+      <c r="H4">
+        <v>3</v>
+      </c>
+      <c r="I4">
         <v>3.25</v>
       </c>
-      <c r="H4">
-        <v>2.88</v>
-      </c>
-      <c r="I4">
-        <v>3.15</v>
-      </c>
       <c r="J4">
-        <v>2.8</v>
+        <v>2.78</v>
       </c>
       <c r="K4">
-        <v>3.05</v>
+        <v>2.98</v>
       </c>
       <c r="L4">
-        <v>1.62</v>
+        <v>1.67</v>
       </c>
       <c r="M4">
-        <v>1.15</v>
+        <v>1.16</v>
       </c>
       <c r="N4">
-        <v>2.42</v>
+        <v>2.34</v>
       </c>
       <c r="O4">
-        <v>1.63</v>
+        <v>1.7</v>
       </c>
       <c r="P4">
-        <v>1.47</v>
+        <v>1.42</v>
       </c>
       <c r="Q4">
-        <v>2.86</v>
+        <v>3.1</v>
       </c>
       <c r="R4">
-        <v>1.16</v>
+        <v>1.14</v>
       </c>
       <c r="S4">
-        <v>6</v>
+        <v>6.6</v>
       </c>
       <c r="T4">
-        <v>2.2</v>
+        <v>2.32</v>
       </c>
       <c r="U4">
-        <v>1.71</v>
+        <v>1.64</v>
       </c>
       <c r="V4">
-        <v>1.47</v>
+        <v>1.45</v>
       </c>
       <c r="W4">
         <v>1.46</v>
       </c>
       <c r="X4">
+        <v>7.2</v>
+      </c>
+      <c r="Y4">
         <v>7.8</v>
       </c>
-      <c r="Y4">
-        <v>8.4</v>
-      </c>
       <c r="Z4">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="AA4">
         <v>150</v>
       </c>
       <c r="AB4">
-        <v>8.4</v>
+        <v>7.8</v>
       </c>
       <c r="AC4">
         <v>7.4</v>
       </c>
       <c r="AD4">
-        <v>15</v>
+        <v>18.5</v>
       </c>
       <c r="AE4">
         <v>55</v>
@@ -1511,19 +1511,19 @@
         <v>17.5</v>
       </c>
       <c r="AH4">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="AI4">
-        <v>90</v>
+        <v>540</v>
       </c>
       <c r="AJ4">
-        <v>150</v>
+        <v>65</v>
       </c>
       <c r="AK4">
         <v>120</v>
       </c>
       <c r="AL4">
-        <v>95</v>
+        <v>230</v>
       </c>
       <c r="AM4">
         <v>500</v>
@@ -1532,49 +1532,49 @@
         <v>75</v>
       </c>
       <c r="AO4">
-        <v>70</v>
+        <v>600</v>
       </c>
       <c r="AP4">
-        <v>6.6</v>
+        <v>6</v>
       </c>
       <c r="AQ4">
-        <v>7</v>
+        <v>6.4</v>
       </c>
       <c r="AR4">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="AS4">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="AT4">
-        <v>7</v>
+        <v>6.4</v>
       </c>
       <c r="AU4">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="AV4">
-        <v>12</v>
+        <v>13.5</v>
       </c>
       <c r="AW4">
-        <v>38</v>
+        <v>8</v>
       </c>
       <c r="AX4">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="AY4">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="AZ4">
-        <v>20</v>
+        <v>14.5</v>
       </c>
       <c r="BA4">
         <v>8.199999999999999</v>
       </c>
       <c r="BB4">
-        <v>7.8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BC4">
-        <v>36</v>
+        <v>8</v>
       </c>
       <c r="BD4">
         <v>8.199999999999999</v>
@@ -1583,16 +1583,16 @@
         <v>8.6</v>
       </c>
       <c r="BF4">
-        <v>11.5</v>
+        <v>8.4</v>
       </c>
       <c r="BG4">
-        <v>8</v>
+        <v>8.4</v>
       </c>
       <c r="BH4">
         <v>2.62</v>
       </c>
       <c r="BI4">
-        <v>2.12</v>
+        <v>2.1</v>
       </c>
       <c r="BJ4">
         <v>12.5</v>
@@ -1607,16 +1607,16 @@
         <v>10.5</v>
       </c>
       <c r="BN4">
-        <v>6</v>
+        <v>5.9</v>
       </c>
       <c r="BO4">
-        <v>4.4</v>
+        <v>4.9</v>
       </c>
       <c r="BP4">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="BQ4">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="BR4">
         <v>60</v>
@@ -1625,7 +1625,7 @@
         <v>9.199999999999999</v>
       </c>
       <c r="BT4">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="BU4">
         <v>4.4</v>
@@ -1669,61 +1669,61 @@
         <v>105</v>
       </c>
       <c r="F5">
-        <v>6.8</v>
+        <v>7.2</v>
       </c>
       <c r="G5">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="H5">
-        <v>1.58</v>
+        <v>1.6</v>
       </c>
       <c r="I5">
         <v>1.64</v>
       </c>
       <c r="J5">
-        <v>3.95</v>
+        <v>3.9</v>
       </c>
       <c r="K5">
-        <v>4.6</v>
+        <v>4.3</v>
       </c>
       <c r="L5">
-        <v>1.41</v>
+        <v>1.44</v>
       </c>
       <c r="M5">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="N5">
-        <v>3.5</v>
+        <v>3.35</v>
       </c>
       <c r="O5">
-        <v>1.35</v>
+        <v>1.4</v>
       </c>
       <c r="P5">
-        <v>1.86</v>
+        <v>1.81</v>
       </c>
       <c r="Q5">
-        <v>2</v>
+        <v>2.18</v>
       </c>
       <c r="R5">
-        <v>1.33</v>
+        <v>1.29</v>
       </c>
       <c r="S5">
-        <v>3.6</v>
+        <v>4.2</v>
       </c>
       <c r="T5">
-        <v>2.04</v>
+        <v>2.2</v>
       </c>
       <c r="U5">
-        <v>1.82</v>
+        <v>1.74</v>
       </c>
       <c r="V5">
         <v>2.56</v>
       </c>
       <c r="W5">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="X5">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="Y5">
         <v>8.6</v>
@@ -1735,28 +1735,28 @@
         <v>17.5</v>
       </c>
       <c r="AB5">
-        <v>25</v>
+        <v>19.5</v>
       </c>
       <c r="AC5">
-        <v>11.5</v>
+        <v>9</v>
       </c>
       <c r="AD5">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="AE5">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="AF5">
         <v>75</v>
       </c>
       <c r="AG5">
-        <v>34</v>
+        <v>85</v>
       </c>
       <c r="AH5">
         <v>30</v>
       </c>
       <c r="AI5">
-        <v>50</v>
+        <v>65</v>
       </c>
       <c r="AJ5">
         <v>700</v>
@@ -1777,70 +1777,70 @@
         <v>12.5</v>
       </c>
       <c r="AP5">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AQ5">
-        <v>6.2</v>
+        <v>5.8</v>
       </c>
       <c r="AR5">
-        <v>7.6</v>
+        <v>7</v>
       </c>
       <c r="AS5">
+        <v>14</v>
+      </c>
+      <c r="AT5">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AU5">
+        <v>7.8</v>
+      </c>
+      <c r="AV5">
+        <v>7.2</v>
+      </c>
+      <c r="AW5">
+        <v>18</v>
+      </c>
+      <c r="AX5">
+        <v>27</v>
+      </c>
+      <c r="AY5">
+        <v>14.5</v>
+      </c>
+      <c r="AZ5">
+        <v>15</v>
+      </c>
+      <c r="BA5">
+        <v>24</v>
+      </c>
+      <c r="BB5">
+        <v>5.3</v>
+      </c>
+      <c r="BC5">
+        <v>5.7</v>
+      </c>
+      <c r="BD5">
+        <v>5.3</v>
+      </c>
+      <c r="BE5">
+        <v>5.3</v>
+      </c>
+      <c r="BF5">
+        <v>5.3</v>
+      </c>
+      <c r="BG5">
         <v>10.5</v>
       </c>
-      <c r="AT5">
-        <v>9</v>
-      </c>
-      <c r="AU5">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AV5">
-        <v>9</v>
-      </c>
-      <c r="AW5">
-        <v>16</v>
-      </c>
-      <c r="AX5">
-        <v>4.5</v>
-      </c>
-      <c r="AY5">
-        <v>20</v>
-      </c>
-      <c r="AZ5">
-        <v>21</v>
-      </c>
-      <c r="BA5">
-        <v>30</v>
-      </c>
-      <c r="BB5">
-        <v>4.8</v>
-      </c>
-      <c r="BC5">
-        <v>4.7</v>
-      </c>
-      <c r="BD5">
-        <v>4.7</v>
-      </c>
-      <c r="BE5">
-        <v>4.7</v>
-      </c>
-      <c r="BF5">
-        <v>4.7</v>
-      </c>
-      <c r="BG5">
-        <v>9</v>
-      </c>
       <c r="BH5">
-        <v>3.9</v>
+        <v>3.75</v>
       </c>
       <c r="BI5">
-        <v>2.7</v>
+        <v>2.62</v>
       </c>
       <c r="BJ5">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="BK5">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="BL5">
         <v>1000</v>
@@ -1849,10 +1849,10 @@
         <v>4.8</v>
       </c>
       <c r="BN5">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="BO5">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="BP5">
         <v>1000</v>
@@ -1867,28 +1867,28 @@
         <v>4.7</v>
       </c>
       <c r="BT5">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="BU5">
-        <v>3.1</v>
+        <v>3.05</v>
       </c>
       <c r="BV5">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="BW5">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="BX5">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="BY5">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="BZ5">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="CA5">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="CB5" t="s">
         <v>111</v>
@@ -1911,91 +1911,91 @@
         <v>106</v>
       </c>
       <c r="F6">
-        <v>2.54</v>
+        <v>2.58</v>
       </c>
       <c r="G6">
-        <v>2.78</v>
+        <v>2.84</v>
       </c>
       <c r="H6">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="I6">
-        <v>3.95</v>
+        <v>3.8</v>
       </c>
       <c r="J6">
-        <v>2.8</v>
+        <v>2.74</v>
       </c>
       <c r="K6">
-        <v>2.96</v>
+        <v>3</v>
       </c>
       <c r="L6">
-        <v>1.68</v>
+        <v>1.72</v>
       </c>
       <c r="M6">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="N6">
-        <v>2.26</v>
+        <v>2.22</v>
       </c>
       <c r="O6">
-        <v>1.69</v>
+        <v>1.76</v>
       </c>
       <c r="P6">
-        <v>1.4</v>
+        <v>1.37</v>
       </c>
       <c r="Q6">
-        <v>3.1</v>
+        <v>3.3</v>
       </c>
       <c r="R6">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="S6">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="T6">
-        <v>2.34</v>
+        <v>2.42</v>
       </c>
       <c r="U6">
-        <v>1.64</v>
+        <v>1.59</v>
       </c>
       <c r="V6">
-        <v>1.35</v>
+        <v>1.37</v>
       </c>
       <c r="W6">
-        <v>1.56</v>
+        <v>1.54</v>
       </c>
       <c r="X6">
-        <v>8.199999999999999</v>
+        <v>7.8</v>
       </c>
       <c r="Y6">
-        <v>9</v>
+        <v>8.4</v>
       </c>
       <c r="Z6">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="AA6">
         <v>420</v>
       </c>
       <c r="AB6">
-        <v>7.2</v>
+        <v>6.8</v>
       </c>
       <c r="AC6">
         <v>7.2</v>
       </c>
       <c r="AD6">
-        <v>18.5</v>
+        <v>19</v>
       </c>
       <c r="AE6">
-        <v>85</v>
+        <v>190</v>
       </c>
       <c r="AF6">
+        <v>16.5</v>
+      </c>
+      <c r="AG6">
         <v>15.5</v>
       </c>
-      <c r="AG6">
-        <v>14.5</v>
-      </c>
       <c r="AH6">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="AI6">
         <v>540</v>
@@ -2007,7 +2007,7 @@
         <v>60</v>
       </c>
       <c r="AL6">
-        <v>460</v>
+        <v>230</v>
       </c>
       <c r="AM6">
         <v>500</v>
@@ -2019,40 +2019,40 @@
         <v>600</v>
       </c>
       <c r="AP6">
-        <v>6</v>
+        <v>5.6</v>
       </c>
       <c r="AQ6">
-        <v>7.4</v>
+        <v>7</v>
       </c>
       <c r="AR6">
         <v>19</v>
       </c>
       <c r="AS6">
-        <v>7.6</v>
+        <v>20</v>
       </c>
       <c r="AT6">
-        <v>5.9</v>
+        <v>5.8</v>
       </c>
       <c r="AU6">
         <v>6</v>
       </c>
       <c r="AV6">
-        <v>14.5</v>
+        <v>15.5</v>
       </c>
       <c r="AW6">
         <v>23</v>
       </c>
       <c r="AX6">
+        <v>13.5</v>
+      </c>
+      <c r="AY6">
         <v>12.5</v>
       </c>
-      <c r="AY6">
-        <v>11.5</v>
-      </c>
       <c r="AZ6">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="BA6">
-        <v>7.6</v>
+        <v>8.4</v>
       </c>
       <c r="BB6">
         <v>29</v>
@@ -2061,19 +2061,19 @@
         <v>27</v>
       </c>
       <c r="BD6">
-        <v>7.6</v>
+        <v>28</v>
       </c>
       <c r="BE6">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BF6">
         <v>32</v>
       </c>
       <c r="BG6">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="BH6">
-        <v>2.74</v>
+        <v>2.76</v>
       </c>
       <c r="BI6">
         <v>2.02</v>
@@ -2082,25 +2082,25 @@
         <v>15</v>
       </c>
       <c r="BK6">
-        <v>3.95</v>
+        <v>3.9</v>
       </c>
       <c r="BL6">
         <v>1000</v>
       </c>
       <c r="BM6">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="BN6">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="BO6">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="BP6">
         <v>32</v>
       </c>
       <c r="BQ6">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="BR6">
         <v>1000</v>
@@ -2109,28 +2109,28 @@
         <v>4.9</v>
       </c>
       <c r="BT6">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="BU6">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="BV6">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="BW6">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="BX6">
         <v>1000</v>
       </c>
       <c r="BY6">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="BZ6">
         <v>1000</v>
       </c>
       <c r="CA6">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="CB6" t="s">
         <v>111</v>
@@ -2153,55 +2153,55 @@
         <v>107</v>
       </c>
       <c r="F7">
-        <v>2.42</v>
+        <v>2.46</v>
       </c>
       <c r="G7">
         <v>2.58</v>
       </c>
       <c r="H7">
-        <v>3.55</v>
+        <v>3.65</v>
       </c>
       <c r="I7">
-        <v>4.3</v>
+        <v>3.95</v>
       </c>
       <c r="J7">
-        <v>2.72</v>
+        <v>2.82</v>
       </c>
       <c r="K7">
-        <v>3.1</v>
+        <v>2.98</v>
       </c>
       <c r="L7">
-        <v>1.68</v>
+        <v>1.69</v>
       </c>
       <c r="M7">
         <v>1.16</v>
       </c>
       <c r="N7">
-        <v>2.28</v>
+        <v>2.3</v>
       </c>
       <c r="O7">
-        <v>1.66</v>
+        <v>1.68</v>
       </c>
       <c r="P7">
         <v>1.41</v>
       </c>
       <c r="Q7">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="R7">
         <v>1.14</v>
       </c>
       <c r="S7">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="T7">
-        <v>2.3</v>
+        <v>2.26</v>
       </c>
       <c r="U7">
-        <v>1.63</v>
+        <v>1.64</v>
       </c>
       <c r="V7">
-        <v>1.31</v>
+        <v>1.34</v>
       </c>
       <c r="W7">
         <v>1.63</v>
@@ -2210,13 +2210,13 @@
         <v>7.2</v>
       </c>
       <c r="Y7">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="Z7">
-        <v>34</v>
+        <v>25</v>
       </c>
       <c r="AA7">
-        <v>900</v>
+        <v>500</v>
       </c>
       <c r="AB7">
         <v>7</v>
@@ -2225,10 +2225,10 @@
         <v>7.2</v>
       </c>
       <c r="AD7">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AE7">
-        <v>440</v>
+        <v>230</v>
       </c>
       <c r="AF7">
         <v>15</v>
@@ -2240,7 +2240,7 @@
         <v>38</v>
       </c>
       <c r="AI7">
-        <v>500</v>
+        <v>540</v>
       </c>
       <c r="AJ7">
         <v>55</v>
@@ -2264,16 +2264,16 @@
         <v>6</v>
       </c>
       <c r="AQ7">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="AR7">
         <v>14.5</v>
       </c>
       <c r="AS7">
-        <v>9.4</v>
+        <v>10.5</v>
       </c>
       <c r="AT7">
-        <v>5.8</v>
+        <v>6</v>
       </c>
       <c r="AU7">
         <v>6</v>
@@ -2282,7 +2282,7 @@
         <v>14.5</v>
       </c>
       <c r="AW7">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="AX7">
         <v>12.5</v>
@@ -2294,7 +2294,7 @@
         <v>16</v>
       </c>
       <c r="BA7">
-        <v>9.6</v>
+        <v>11</v>
       </c>
       <c r="BB7">
         <v>26</v>
@@ -2303,19 +2303,19 @@
         <v>26</v>
       </c>
       <c r="BD7">
-        <v>9.4</v>
+        <v>28</v>
       </c>
       <c r="BE7">
-        <v>10</v>
+        <v>11.5</v>
       </c>
       <c r="BF7">
         <v>32</v>
       </c>
       <c r="BG7">
-        <v>9.800000000000001</v>
+        <v>10.5</v>
       </c>
       <c r="BH7">
-        <v>2.52</v>
+        <v>2.54</v>
       </c>
       <c r="BI7">
         <v>2.08</v>
@@ -2324,19 +2324,19 @@
         <v>13</v>
       </c>
       <c r="BK7">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="BL7">
         <v>1000</v>
       </c>
       <c r="BM7">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="BN7">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="BO7">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="BP7">
         <v>1000</v>
@@ -2348,19 +2348,19 @@
         <v>1000</v>
       </c>
       <c r="BS7">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BT7">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="BU7">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="BV7">
         <v>1000</v>
       </c>
       <c r="BW7">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="BX7">
         <v>1000</v>
@@ -2398,10 +2398,10 @@
         <v>1.75</v>
       </c>
       <c r="G8">
-        <v>1.76</v>
+        <v>1.77</v>
       </c>
       <c r="H8">
-        <v>5.9</v>
+        <v>5.8</v>
       </c>
       <c r="I8">
         <v>6.2</v>
@@ -2419,7 +2419,7 @@
         <v>1.09</v>
       </c>
       <c r="N8">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="O8">
         <v>1.44</v>
@@ -2428,16 +2428,16 @@
         <v>1.71</v>
       </c>
       <c r="Q8">
-        <v>2.3</v>
+        <v>2.34</v>
       </c>
       <c r="R8">
-        <v>1.27</v>
+        <v>1.26</v>
       </c>
       <c r="S8">
-        <v>4.4</v>
+        <v>4.6</v>
       </c>
       <c r="T8">
-        <v>2.14</v>
+        <v>2.16</v>
       </c>
       <c r="U8">
         <v>1.81</v>
@@ -2446,121 +2446,121 @@
         <v>1.19</v>
       </c>
       <c r="W8">
-        <v>2.3</v>
+        <v>2.28</v>
       </c>
       <c r="X8">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="Y8">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="Z8">
-        <v>100</v>
+        <v>46</v>
       </c>
       <c r="AA8">
-        <v>900</v>
+        <v>200</v>
       </c>
       <c r="AB8">
         <v>6.4</v>
       </c>
       <c r="AC8">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="AD8">
         <v>23</v>
       </c>
       <c r="AE8">
-        <v>700</v>
+        <v>110</v>
       </c>
       <c r="AF8">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AG8">
         <v>10.5</v>
       </c>
       <c r="AH8">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AI8">
         <v>260</v>
       </c>
       <c r="AJ8">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="AK8">
         <v>21</v>
       </c>
       <c r="AL8">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="AM8">
-        <v>580</v>
+        <v>200</v>
       </c>
       <c r="AN8">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="AO8">
-        <v>700</v>
+        <v>160</v>
       </c>
       <c r="AP8">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AQ8">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="AR8">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="AS8">
-        <v>13.5</v>
+        <v>20</v>
       </c>
       <c r="AT8">
-        <v>5.8</v>
+        <v>6</v>
       </c>
       <c r="AU8">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="AV8">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AW8">
-        <v>28</v>
+        <v>90</v>
       </c>
       <c r="AX8">
         <v>8.4</v>
       </c>
       <c r="AY8">
-        <v>9</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AZ8">
         <v>24</v>
       </c>
       <c r="BA8">
-        <v>12.5</v>
+        <v>85</v>
       </c>
       <c r="BB8">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="BC8">
-        <v>18.5</v>
+        <v>19.5</v>
       </c>
       <c r="BD8">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="BE8">
-        <v>13.5</v>
+        <v>20</v>
       </c>
       <c r="BF8">
         <v>14</v>
       </c>
       <c r="BG8">
-        <v>13</v>
+        <v>19.5</v>
       </c>
       <c r="BH8">
-        <v>3.05</v>
+        <v>3</v>
       </c>
       <c r="BI8">
-        <v>2.78</v>
+        <v>2.58</v>
       </c>
       <c r="BJ8">
         <v>11.5</v>
@@ -2572,7 +2572,7 @@
         <v>1000</v>
       </c>
       <c r="BM8">
-        <v>15.5</v>
+        <v>17</v>
       </c>
       <c r="BN8">
         <v>4.1</v>
@@ -2581,7 +2581,7 @@
         <v>3.7</v>
       </c>
       <c r="BP8">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="BQ8">
         <v>9.800000000000001</v>
@@ -2590,10 +2590,10 @@
         <v>34</v>
       </c>
       <c r="BS8">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="BT8">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BU8">
         <v>7.4</v>
@@ -2602,19 +2602,19 @@
         <v>1000</v>
       </c>
       <c r="BW8">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="BX8">
         <v>1000</v>
       </c>
       <c r="BY8">
-        <v>13.5</v>
+        <v>14.5</v>
       </c>
       <c r="BZ8">
         <v>30</v>
       </c>
       <c r="CA8">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="CB8" t="s">
         <v>111</v>
@@ -2637,64 +2637,64 @@
         <v>109</v>
       </c>
       <c r="F9">
-        <v>2.8</v>
+        <v>2.86</v>
       </c>
       <c r="G9">
         <v>2.94</v>
       </c>
       <c r="H9">
-        <v>2.86</v>
+        <v>2.84</v>
       </c>
       <c r="I9">
-        <v>2.94</v>
+        <v>2.92</v>
       </c>
       <c r="J9">
-        <v>3.15</v>
+        <v>3.25</v>
       </c>
       <c r="K9">
         <v>3.3</v>
       </c>
       <c r="L9">
-        <v>1.48</v>
+        <v>1.49</v>
       </c>
       <c r="M9">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="N9">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="O9">
         <v>1.43</v>
       </c>
       <c r="P9">
-        <v>1.69</v>
+        <v>1.71</v>
       </c>
       <c r="Q9">
-        <v>2.28</v>
+        <v>2.32</v>
       </c>
       <c r="R9">
-        <v>1.27</v>
+        <v>1.26</v>
       </c>
       <c r="S9">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="T9">
-        <v>1.91</v>
+        <v>1.9</v>
       </c>
       <c r="U9">
         <v>1.99</v>
       </c>
       <c r="V9">
+        <v>1.52</v>
+      </c>
+      <c r="W9">
         <v>1.51</v>
-      </c>
-      <c r="W9">
-        <v>1.52</v>
       </c>
       <c r="X9">
         <v>14.5</v>
       </c>
       <c r="Y9">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="Z9">
         <v>18</v>
@@ -2718,7 +2718,7 @@
         <v>18.5</v>
       </c>
       <c r="AG9">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AH9">
         <v>19.5</v>
@@ -2757,10 +2757,10 @@
         <v>38</v>
       </c>
       <c r="AT9">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="AU9">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="AV9">
         <v>11.5</v>
@@ -2769,7 +2769,7 @@
         <v>30</v>
       </c>
       <c r="AX9">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="AY9">
         <v>11.5</v>
@@ -2787,10 +2787,10 @@
         <v>28</v>
       </c>
       <c r="BD9">
-        <v>23</v>
+        <v>9.6</v>
       </c>
       <c r="BE9">
-        <v>14</v>
+        <v>10.5</v>
       </c>
       <c r="BF9">
         <v>30</v>
@@ -2808,13 +2808,13 @@
         <v>10</v>
       </c>
       <c r="BK9">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="BL9">
         <v>1000</v>
       </c>
       <c r="BM9">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="BN9">
         <v>5.8</v>
@@ -2823,7 +2823,7 @@
         <v>4.5</v>
       </c>
       <c r="BP9">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="BQ9">
         <v>10</v>
@@ -2832,7 +2832,7 @@
         <v>40</v>
       </c>
       <c r="BS9">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="BT9">
         <v>5.7</v>
@@ -2850,13 +2850,13 @@
         <v>40</v>
       </c>
       <c r="BY9">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="BZ9">
         <v>36</v>
       </c>
       <c r="CA9">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="CB9" t="s">
         <v>111</v>
@@ -2879,58 +2879,58 @@
         <v>110</v>
       </c>
       <c r="F10">
-        <v>2.08</v>
+        <v>2.12</v>
       </c>
       <c r="G10">
-        <v>2.26</v>
+        <v>2.24</v>
       </c>
       <c r="H10">
         <v>3.65</v>
       </c>
       <c r="I10">
-        <v>4.3</v>
+        <v>4.1</v>
       </c>
       <c r="J10">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="K10">
-        <v>3.8</v>
+        <v>3.6</v>
       </c>
       <c r="L10">
-        <v>1.42</v>
+        <v>1.44</v>
       </c>
       <c r="M10">
         <v>1.08</v>
       </c>
       <c r="N10">
-        <v>3.35</v>
+        <v>3.45</v>
       </c>
       <c r="O10">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="P10">
         <v>1.81</v>
       </c>
       <c r="Q10">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="R10">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="S10">
-        <v>3.7</v>
+        <v>3.9</v>
       </c>
       <c r="T10">
-        <v>1.83</v>
+        <v>1.85</v>
       </c>
       <c r="U10">
-        <v>2.02</v>
+        <v>2</v>
       </c>
       <c r="V10">
-        <v>1.31</v>
+        <v>1.33</v>
       </c>
       <c r="W10">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="X10">
         <v>14</v>
@@ -2939,19 +2939,19 @@
         <v>14.5</v>
       </c>
       <c r="Z10">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="AA10">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="AB10">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AC10">
         <v>8</v>
       </c>
       <c r="AD10">
-        <v>17.5</v>
+        <v>16.5</v>
       </c>
       <c r="AE10">
         <v>55</v>
@@ -2969,7 +2969,7 @@
         <v>65</v>
       </c>
       <c r="AJ10">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="AK10">
         <v>28</v>
@@ -2996,7 +2996,7 @@
         <v>21</v>
       </c>
       <c r="AS10">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="AT10">
         <v>7.8</v>
@@ -3041,64 +3041,64 @@
         <v>6.6</v>
       </c>
       <c r="BH10">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="BI10">
-        <v>2.7</v>
+        <v>2.64</v>
       </c>
       <c r="BJ10">
         <v>10.5</v>
       </c>
       <c r="BK10">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="BL10">
         <v>1000</v>
       </c>
       <c r="BM10">
-        <v>9.6</v>
+        <v>10</v>
       </c>
       <c r="BN10">
         <v>5.1</v>
       </c>
       <c r="BO10">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="BP10">
-        <v>16.5</v>
+        <v>17.5</v>
       </c>
       <c r="BQ10">
-        <v>6.2</v>
+        <v>6.6</v>
       </c>
       <c r="BR10">
         <v>1000</v>
       </c>
       <c r="BS10">
-        <v>7.8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BT10">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="BU10">
-        <v>5.6</v>
+        <v>5.4</v>
       </c>
       <c r="BV10">
-        <v>36</v>
+        <v>1000</v>
       </c>
       <c r="BW10">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BX10">
-        <v>1000</v>
+        <v>48</v>
       </c>
       <c r="BY10">
-        <v>8.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BZ10">
         <v>1000</v>
       </c>
       <c r="CA10">
-        <v>7.6</v>
+        <v>8</v>
       </c>
       <c r="CB10" t="s">
         <v>111</v>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-08-11.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-08-11.xlsx
@@ -277,7 +277,7 @@
     <t>2026-08-11</t>
   </si>
   <si>
-    <t>09:30:00</t>
+    <t>11:30:00</t>
   </si>
   <si>
     <t>17:00:00</t>
@@ -349,7 +349,7 @@
     <t>Union Espanola</t>
   </si>
   <si>
-    <t>2026-08-11 05:33:11</t>
+    <t>2026-08-11 07:40:26</t>
   </si>
 </sst>
 </file>
@@ -943,94 +943,94 @@
         <v>102</v>
       </c>
       <c r="F2">
-        <v>5.6</v>
+        <v>5.8</v>
       </c>
       <c r="G2">
         <v>6.8</v>
       </c>
       <c r="H2">
-        <v>1.77</v>
+        <v>1.78</v>
       </c>
       <c r="I2">
-        <v>1.93</v>
+        <v>1.9</v>
       </c>
       <c r="J2">
         <v>3.15</v>
       </c>
       <c r="K2">
-        <v>3.7</v>
+        <v>3.65</v>
       </c>
       <c r="L2">
-        <v>1.55</v>
+        <v>1.54</v>
       </c>
       <c r="M2">
         <v>1.13</v>
       </c>
       <c r="N2">
-        <v>2.66</v>
+        <v>2.76</v>
       </c>
       <c r="O2">
         <v>1.53</v>
       </c>
       <c r="P2">
-        <v>1.55</v>
+        <v>1.57</v>
       </c>
       <c r="Q2">
-        <v>2.54</v>
+        <v>2.58</v>
       </c>
       <c r="R2">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="S2">
         <v>5.2</v>
       </c>
       <c r="T2">
-        <v>2.22</v>
+        <v>2.2</v>
       </c>
       <c r="U2">
-        <v>1.68</v>
+        <v>1.72</v>
       </c>
       <c r="V2">
         <v>2.08</v>
       </c>
       <c r="W2">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="X2">
-        <v>11</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="Y2">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="Z2">
-        <v>9.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AA2">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="AB2">
-        <v>15.5</v>
+        <v>18</v>
       </c>
       <c r="AC2">
         <v>8.199999999999999</v>
       </c>
       <c r="AD2">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AE2">
         <v>26</v>
       </c>
       <c r="AF2">
-        <v>48</v>
+        <v>60</v>
       </c>
       <c r="AG2">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AH2">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AI2">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="AJ2">
         <v>900</v>
@@ -1039,7 +1039,7 @@
         <v>140</v>
       </c>
       <c r="AL2">
-        <v>160</v>
+        <v>700</v>
       </c>
       <c r="AM2">
         <v>580</v>
@@ -1048,31 +1048,31 @@
         <v>260</v>
       </c>
       <c r="AO2">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="AP2">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AQ2">
-        <v>5.5</v>
+        <v>5.8</v>
       </c>
       <c r="AR2">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="AS2">
         <v>17</v>
       </c>
       <c r="AT2">
-        <v>12.5</v>
+        <v>13.5</v>
       </c>
       <c r="AU2">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="AV2">
         <v>9.199999999999999</v>
       </c>
       <c r="AW2">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AX2">
         <v>36</v>
@@ -1084,22 +1084,22 @@
         <v>14</v>
       </c>
       <c r="BA2">
-        <v>8.199999999999999</v>
+        <v>42</v>
       </c>
       <c r="BB2">
-        <v>8.4</v>
+        <v>9</v>
       </c>
       <c r="BC2">
-        <v>8.199999999999999</v>
+        <v>10</v>
       </c>
       <c r="BD2">
-        <v>8.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BE2">
-        <v>8.6</v>
+        <v>140</v>
       </c>
       <c r="BF2">
-        <v>8.6</v>
+        <v>8</v>
       </c>
       <c r="BG2">
         <v>17</v>
@@ -1108,55 +1108,55 @@
         <v>2.84</v>
       </c>
       <c r="BI2">
-        <v>2.48</v>
+        <v>2.36</v>
       </c>
       <c r="BJ2">
-        <v>14.5</v>
+        <v>13</v>
       </c>
       <c r="BK2">
-        <v>4.9</v>
+        <v>6</v>
       </c>
       <c r="BL2">
         <v>1000</v>
       </c>
       <c r="BM2">
-        <v>7.2</v>
+        <v>170</v>
       </c>
       <c r="BN2">
-        <v>10.5</v>
+        <v>9.6</v>
       </c>
       <c r="BO2">
-        <v>4.3</v>
+        <v>5.1</v>
       </c>
       <c r="BP2">
         <v>75</v>
       </c>
       <c r="BQ2">
-        <v>6.6</v>
+        <v>9.4</v>
       </c>
       <c r="BR2">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="BS2">
-        <v>6.8</v>
+        <v>9.6</v>
       </c>
       <c r="BT2">
-        <v>4.6</v>
+        <v>4.2</v>
       </c>
       <c r="BU2">
         <v>3.35</v>
       </c>
       <c r="BV2">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="BW2">
-        <v>5.1</v>
+        <v>6.4</v>
       </c>
       <c r="BX2">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="BY2">
-        <v>6.4</v>
+        <v>8.6</v>
       </c>
       <c r="BZ2">
         <v>0</v>
@@ -1188,16 +1188,16 @@
         <v>2.38</v>
       </c>
       <c r="G3">
-        <v>2.4</v>
+        <v>2.42</v>
       </c>
       <c r="H3">
         <v>3</v>
       </c>
       <c r="I3">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="J3">
-        <v>3.9</v>
+        <v>3.85</v>
       </c>
       <c r="K3">
         <v>3.95</v>
@@ -1215,7 +1215,7 @@
         <v>1.22</v>
       </c>
       <c r="P3">
-        <v>2.42</v>
+        <v>2.44</v>
       </c>
       <c r="Q3">
         <v>1.67</v>
@@ -1227,25 +1227,25 @@
         <v>2.68</v>
       </c>
       <c r="T3">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="U3">
         <v>2.58</v>
       </c>
       <c r="V3">
-        <v>1.48</v>
+        <v>1.47</v>
       </c>
       <c r="W3">
-        <v>1.71</v>
+        <v>1.7</v>
       </c>
       <c r="X3">
         <v>22</v>
       </c>
       <c r="Y3">
-        <v>18</v>
+        <v>16.5</v>
       </c>
       <c r="Z3">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="AA3">
         <v>50</v>
@@ -1257,52 +1257,52 @@
         <v>9.199999999999999</v>
       </c>
       <c r="AD3">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="AE3">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="AF3">
-        <v>17.5</v>
+        <v>18.5</v>
       </c>
       <c r="AG3">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AH3">
         <v>14.5</v>
       </c>
       <c r="AI3">
-        <v>34</v>
+        <v>65</v>
       </c>
       <c r="AJ3">
         <v>34</v>
       </c>
       <c r="AK3">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AL3">
-        <v>55</v>
+        <v>30</v>
       </c>
       <c r="AM3">
-        <v>60</v>
+        <v>80</v>
       </c>
       <c r="AN3">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="AO3">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AP3">
-        <v>19</v>
+        <v>19.5</v>
       </c>
       <c r="AQ3">
         <v>15.5</v>
       </c>
       <c r="AR3">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AS3">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="AT3">
         <v>13</v>
@@ -1314,7 +1314,7 @@
         <v>12</v>
       </c>
       <c r="AW3">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AX3">
         <v>16</v>
@@ -1329,22 +1329,22 @@
         <v>30</v>
       </c>
       <c r="BB3">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="BC3">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="BD3">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="BE3">
         <v>50</v>
       </c>
       <c r="BF3">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="BG3">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="BH3">
         <v>4.1</v>
@@ -1356,13 +1356,13 @@
         <v>8.6</v>
       </c>
       <c r="BK3">
-        <v>6</v>
+        <v>5.9</v>
       </c>
       <c r="BL3">
         <v>1000</v>
       </c>
       <c r="BM3">
-        <v>3.45</v>
+        <v>15</v>
       </c>
       <c r="BN3">
         <v>5.6</v>
@@ -1433,13 +1433,13 @@
         <v>3.15</v>
       </c>
       <c r="H4">
-        <v>3</v>
+        <v>2.98</v>
       </c>
       <c r="I4">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="J4">
-        <v>2.78</v>
+        <v>2.8</v>
       </c>
       <c r="K4">
         <v>2.98</v>
@@ -1451,103 +1451,103 @@
         <v>1.16</v>
       </c>
       <c r="N4">
-        <v>2.34</v>
+        <v>2.38</v>
       </c>
       <c r="O4">
         <v>1.7</v>
       </c>
       <c r="P4">
-        <v>1.42</v>
+        <v>1.44</v>
       </c>
       <c r="Q4">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="R4">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="S4">
         <v>6.6</v>
       </c>
       <c r="T4">
-        <v>2.32</v>
+        <v>2.28</v>
       </c>
       <c r="U4">
-        <v>1.64</v>
+        <v>1.66</v>
       </c>
       <c r="V4">
         <v>1.45</v>
       </c>
       <c r="W4">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="X4">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="Y4">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="Z4">
-        <v>21</v>
+        <v>19.5</v>
       </c>
       <c r="AA4">
-        <v>150</v>
+        <v>95</v>
       </c>
       <c r="AB4">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="AC4">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="AD4">
-        <v>18.5</v>
+        <v>16</v>
       </c>
       <c r="AE4">
-        <v>55</v>
+        <v>90</v>
       </c>
       <c r="AF4">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="AG4">
-        <v>17.5</v>
+        <v>16.5</v>
       </c>
       <c r="AH4">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AI4">
-        <v>540</v>
+        <v>200</v>
       </c>
       <c r="AJ4">
         <v>65</v>
       </c>
       <c r="AK4">
-        <v>120</v>
+        <v>55</v>
       </c>
       <c r="AL4">
-        <v>230</v>
+        <v>460</v>
       </c>
       <c r="AM4">
         <v>500</v>
       </c>
       <c r="AN4">
+        <v>500</v>
+      </c>
+      <c r="AO4">
         <v>75</v>
       </c>
-      <c r="AO4">
-        <v>600</v>
-      </c>
       <c r="AP4">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="AQ4">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="AR4">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="AS4">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AT4">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="AU4">
         <v>6.2</v>
@@ -1556,58 +1556,58 @@
         <v>13.5</v>
       </c>
       <c r="AW4">
-        <v>8</v>
+        <v>23</v>
       </c>
       <c r="AX4">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="AY4">
         <v>13</v>
       </c>
       <c r="AZ4">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="BA4">
-        <v>8.199999999999999</v>
+        <v>34</v>
       </c>
       <c r="BB4">
-        <v>8.199999999999999</v>
+        <v>18</v>
       </c>
       <c r="BC4">
-        <v>8</v>
+        <v>36</v>
       </c>
       <c r="BD4">
-        <v>8.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="BE4">
-        <v>8.6</v>
+        <v>9.6</v>
       </c>
       <c r="BF4">
-        <v>8.4</v>
+        <v>11.5</v>
       </c>
       <c r="BG4">
-        <v>8.4</v>
+        <v>38</v>
       </c>
       <c r="BH4">
-        <v>2.62</v>
+        <v>2.64</v>
       </c>
       <c r="BI4">
-        <v>2.1</v>
+        <v>2.14</v>
       </c>
       <c r="BJ4">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="BK4">
-        <v>5.8</v>
+        <v>5.9</v>
       </c>
       <c r="BL4">
         <v>1000</v>
       </c>
       <c r="BM4">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="BN4">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="BO4">
         <v>4.9</v>
@@ -1616,16 +1616,16 @@
         <v>30</v>
       </c>
       <c r="BQ4">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BR4">
         <v>60</v>
       </c>
       <c r="BS4">
-        <v>9.199999999999999</v>
+        <v>9.6</v>
       </c>
       <c r="BT4">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="BU4">
         <v>4.4</v>
@@ -1634,19 +1634,19 @@
         <v>32</v>
       </c>
       <c r="BW4">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="BX4">
         <v>60</v>
       </c>
       <c r="BY4">
-        <v>9.199999999999999</v>
+        <v>9.6</v>
       </c>
       <c r="BZ4">
         <v>1000</v>
       </c>
       <c r="CA4">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="CB4" t="s">
         <v>111</v>
@@ -1669,94 +1669,94 @@
         <v>105</v>
       </c>
       <c r="F5">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="G5">
-        <v>8.199999999999999</v>
+        <v>7.8</v>
       </c>
       <c r="H5">
         <v>1.6</v>
       </c>
       <c r="I5">
-        <v>1.64</v>
+        <v>1.63</v>
       </c>
       <c r="J5">
-        <v>3.9</v>
+        <v>4.1</v>
       </c>
       <c r="K5">
         <v>4.3</v>
       </c>
       <c r="L5">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="M5">
         <v>1.08</v>
       </c>
       <c r="N5">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="O5">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="P5">
-        <v>1.81</v>
+        <v>1.78</v>
       </c>
       <c r="Q5">
         <v>2.18</v>
       </c>
       <c r="R5">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="S5">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="T5">
-        <v>2.2</v>
+        <v>2.14</v>
       </c>
       <c r="U5">
-        <v>1.74</v>
+        <v>1.76</v>
       </c>
       <c r="V5">
-        <v>2.56</v>
+        <v>2.58</v>
       </c>
       <c r="W5">
         <v>1.15</v>
       </c>
       <c r="X5">
+        <v>16</v>
+      </c>
+      <c r="Y5">
+        <v>7</v>
+      </c>
+      <c r="Z5">
+        <v>8.4</v>
+      </c>
+      <c r="AA5">
         <v>15.5</v>
       </c>
-      <c r="Y5">
-        <v>8.6</v>
-      </c>
-      <c r="Z5">
+      <c r="AB5">
+        <v>32</v>
+      </c>
+      <c r="AC5">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AD5">
         <v>10.5</v>
-      </c>
-      <c r="AA5">
-        <v>17.5</v>
-      </c>
-      <c r="AB5">
-        <v>19.5</v>
-      </c>
-      <c r="AC5">
-        <v>9</v>
-      </c>
-      <c r="AD5">
-        <v>12.5</v>
       </c>
       <c r="AE5">
         <v>24</v>
       </c>
       <c r="AF5">
-        <v>75</v>
+        <v>160</v>
       </c>
       <c r="AG5">
         <v>85</v>
       </c>
       <c r="AH5">
-        <v>30</v>
+        <v>65</v>
       </c>
       <c r="AI5">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="AJ5">
         <v>700</v>
@@ -1771,34 +1771,34 @@
         <v>700</v>
       </c>
       <c r="AN5">
-        <v>700</v>
+        <v>280</v>
       </c>
       <c r="AO5">
-        <v>12.5</v>
+        <v>11.5</v>
       </c>
       <c r="AP5">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AQ5">
-        <v>5.8</v>
+        <v>6</v>
       </c>
       <c r="AR5">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="AS5">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AT5">
-        <v>9.800000000000001</v>
+        <v>17</v>
       </c>
       <c r="AU5">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="AV5">
-        <v>7.2</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AW5">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AX5">
         <v>27</v>
@@ -1810,64 +1810,64 @@
         <v>15</v>
       </c>
       <c r="BA5">
-        <v>24</v>
+        <v>40</v>
       </c>
       <c r="BB5">
-        <v>5.3</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BC5">
-        <v>5.7</v>
+        <v>9.4</v>
       </c>
       <c r="BD5">
-        <v>5.3</v>
+        <v>9.6</v>
       </c>
       <c r="BE5">
-        <v>5.3</v>
+        <v>9.6</v>
       </c>
       <c r="BF5">
-        <v>5.3</v>
+        <v>9.4</v>
       </c>
       <c r="BG5">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="BH5">
         <v>3.75</v>
       </c>
       <c r="BI5">
-        <v>2.62</v>
+        <v>2.6</v>
       </c>
       <c r="BJ5">
         <v>14.5</v>
       </c>
       <c r="BK5">
-        <v>3.7</v>
+        <v>3.6</v>
       </c>
       <c r="BL5">
         <v>1000</v>
       </c>
       <c r="BM5">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="BN5">
         <v>13</v>
       </c>
       <c r="BO5">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="BP5">
         <v>1000</v>
       </c>
       <c r="BQ5">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="BR5">
         <v>1000</v>
       </c>
       <c r="BS5">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="BT5">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="BU5">
         <v>3.05</v>
@@ -1876,19 +1876,19 @@
         <v>13</v>
       </c>
       <c r="BW5">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="BX5">
         <v>38</v>
       </c>
       <c r="BY5">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="BZ5">
         <v>28</v>
       </c>
       <c r="CA5">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="CB5" t="s">
         <v>111</v>
@@ -1911,52 +1911,52 @@
         <v>106</v>
       </c>
       <c r="F6">
-        <v>2.58</v>
+        <v>2.62</v>
       </c>
       <c r="G6">
         <v>2.84</v>
       </c>
       <c r="H6">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="I6">
         <v>3.8</v>
       </c>
       <c r="J6">
-        <v>2.74</v>
+        <v>2.7</v>
       </c>
       <c r="K6">
-        <v>3</v>
+        <v>2.88</v>
       </c>
       <c r="L6">
         <v>1.72</v>
       </c>
       <c r="M6">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="N6">
-        <v>2.22</v>
+        <v>2.2</v>
       </c>
       <c r="O6">
-        <v>1.76</v>
+        <v>1.75</v>
       </c>
       <c r="P6">
         <v>1.37</v>
       </c>
       <c r="Q6">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="R6">
         <v>1.13</v>
       </c>
       <c r="S6">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="T6">
-        <v>2.42</v>
+        <v>2.4</v>
       </c>
       <c r="U6">
-        <v>1.59</v>
+        <v>1.58</v>
       </c>
       <c r="V6">
         <v>1.37</v>
@@ -1965,28 +1965,28 @@
         <v>1.54</v>
       </c>
       <c r="X6">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="Y6">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="Z6">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="AA6">
-        <v>420</v>
+        <v>110</v>
       </c>
       <c r="AB6">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="AC6">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="AD6">
         <v>19</v>
       </c>
       <c r="AE6">
-        <v>190</v>
+        <v>90</v>
       </c>
       <c r="AF6">
         <v>16.5</v>
@@ -1995,16 +1995,16 @@
         <v>15.5</v>
       </c>
       <c r="AH6">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="AI6">
         <v>540</v>
       </c>
       <c r="AJ6">
-        <v>55</v>
+        <v>65</v>
       </c>
       <c r="AK6">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="AL6">
         <v>230</v>
@@ -2013,10 +2013,10 @@
         <v>500</v>
       </c>
       <c r="AN6">
-        <v>65</v>
+        <v>85</v>
       </c>
       <c r="AO6">
-        <v>600</v>
+        <v>140</v>
       </c>
       <c r="AP6">
         <v>5.6</v>
@@ -2025,7 +2025,7 @@
         <v>7</v>
       </c>
       <c r="AR6">
-        <v>19</v>
+        <v>15.5</v>
       </c>
       <c r="AS6">
         <v>20</v>
@@ -2040,7 +2040,7 @@
         <v>15.5</v>
       </c>
       <c r="AW6">
-        <v>23</v>
+        <v>46</v>
       </c>
       <c r="AX6">
         <v>13.5</v>
@@ -2049,37 +2049,37 @@
         <v>12.5</v>
       </c>
       <c r="AZ6">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="BA6">
-        <v>8.4</v>
+        <v>7.4</v>
       </c>
       <c r="BB6">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="BC6">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="BD6">
         <v>28</v>
       </c>
       <c r="BE6">
-        <v>8.199999999999999</v>
+        <v>7.4</v>
       </c>
       <c r="BF6">
-        <v>32</v>
+        <v>40</v>
       </c>
       <c r="BG6">
-        <v>7.8</v>
+        <v>7</v>
       </c>
       <c r="BH6">
-        <v>2.76</v>
+        <v>2.72</v>
       </c>
       <c r="BI6">
-        <v>2.02</v>
+        <v>2</v>
       </c>
       <c r="BJ6">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="BK6">
         <v>3.9</v>
@@ -2097,13 +2097,13 @@
         <v>4.1</v>
       </c>
       <c r="BP6">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="BQ6">
         <v>4.5</v>
       </c>
       <c r="BR6">
-        <v>1000</v>
+        <v>75</v>
       </c>
       <c r="BS6">
         <v>4.9</v>
@@ -2153,7 +2153,7 @@
         <v>107</v>
       </c>
       <c r="F7">
-        <v>2.46</v>
+        <v>2.48</v>
       </c>
       <c r="G7">
         <v>2.58</v>
@@ -2162,10 +2162,10 @@
         <v>3.65</v>
       </c>
       <c r="I7">
-        <v>3.95</v>
+        <v>3.9</v>
       </c>
       <c r="J7">
-        <v>2.82</v>
+        <v>2.96</v>
       </c>
       <c r="K7">
         <v>2.98</v>
@@ -2177,37 +2177,37 @@
         <v>1.16</v>
       </c>
       <c r="N7">
-        <v>2.3</v>
+        <v>2.38</v>
       </c>
       <c r="O7">
         <v>1.68</v>
       </c>
       <c r="P7">
-        <v>1.41</v>
+        <v>1.44</v>
       </c>
       <c r="Q7">
         <v>3.1</v>
       </c>
       <c r="R7">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="S7">
         <v>6.6</v>
       </c>
       <c r="T7">
-        <v>2.26</v>
+        <v>2.32</v>
       </c>
       <c r="U7">
         <v>1.64</v>
       </c>
       <c r="V7">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="W7">
         <v>1.63</v>
       </c>
       <c r="X7">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="Y7">
         <v>9.4</v>
@@ -2219,43 +2219,43 @@
         <v>500</v>
       </c>
       <c r="AB7">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="AC7">
         <v>7.2</v>
       </c>
       <c r="AD7">
-        <v>18</v>
+        <v>18.5</v>
       </c>
       <c r="AE7">
         <v>230</v>
       </c>
       <c r="AF7">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="AG7">
         <v>14</v>
       </c>
       <c r="AH7">
-        <v>38</v>
+        <v>48</v>
       </c>
       <c r="AI7">
         <v>540</v>
       </c>
       <c r="AJ7">
-        <v>55</v>
+        <v>100</v>
       </c>
       <c r="AK7">
-        <v>150</v>
+        <v>46</v>
       </c>
       <c r="AL7">
-        <v>460</v>
+        <v>230</v>
       </c>
       <c r="AM7">
         <v>500</v>
       </c>
       <c r="AN7">
-        <v>180</v>
+        <v>75</v>
       </c>
       <c r="AO7">
         <v>600</v>
@@ -2267,10 +2267,10 @@
         <v>7.8</v>
       </c>
       <c r="AR7">
-        <v>14.5</v>
+        <v>20</v>
       </c>
       <c r="AS7">
-        <v>10.5</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AT7">
         <v>6</v>
@@ -2279,7 +2279,7 @@
         <v>6</v>
       </c>
       <c r="AV7">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="AW7">
         <v>27</v>
@@ -2291,28 +2291,28 @@
         <v>11.5</v>
       </c>
       <c r="AZ7">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="BA7">
-        <v>11</v>
+        <v>30</v>
       </c>
       <c r="BB7">
-        <v>26</v>
+        <v>19</v>
       </c>
       <c r="BC7">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="BD7">
-        <v>28</v>
+        <v>36</v>
       </c>
       <c r="BE7">
-        <v>11.5</v>
+        <v>10</v>
       </c>
       <c r="BF7">
-        <v>32</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BG7">
-        <v>10.5</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BH7">
         <v>2.54</v>
@@ -2395,67 +2395,67 @@
         <v>108</v>
       </c>
       <c r="F8">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="G8">
         <v>1.77</v>
       </c>
       <c r="H8">
-        <v>5.8</v>
+        <v>5.7</v>
       </c>
       <c r="I8">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="J8">
         <v>3.75</v>
       </c>
       <c r="K8">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="L8">
-        <v>1.5</v>
+        <v>1.52</v>
       </c>
       <c r="M8">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="N8">
-        <v>3.15</v>
+        <v>3.05</v>
       </c>
       <c r="O8">
-        <v>1.44</v>
+        <v>1.46</v>
       </c>
       <c r="P8">
-        <v>1.71</v>
+        <v>1.69</v>
       </c>
       <c r="Q8">
-        <v>2.34</v>
+        <v>2.4</v>
       </c>
       <c r="R8">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="S8">
-        <v>4.6</v>
+        <v>4.8</v>
       </c>
       <c r="T8">
-        <v>2.16</v>
+        <v>2.2</v>
       </c>
       <c r="U8">
-        <v>1.81</v>
+        <v>1.8</v>
       </c>
       <c r="V8">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="W8">
         <v>2.28</v>
       </c>
       <c r="X8">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="Y8">
         <v>16.5</v>
       </c>
       <c r="Z8">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="AA8">
         <v>200</v>
@@ -2482,7 +2482,7 @@
         <v>27</v>
       </c>
       <c r="AI8">
-        <v>260</v>
+        <v>120</v>
       </c>
       <c r="AJ8">
         <v>18</v>
@@ -2491,28 +2491,28 @@
         <v>21</v>
       </c>
       <c r="AL8">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="AM8">
-        <v>200</v>
+        <v>220</v>
       </c>
       <c r="AN8">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="AO8">
         <v>160</v>
       </c>
       <c r="AP8">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AQ8">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="AR8">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="AS8">
-        <v>20</v>
+        <v>16.5</v>
       </c>
       <c r="AT8">
         <v>6</v>
@@ -2536,10 +2536,10 @@
         <v>24</v>
       </c>
       <c r="BA8">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="BB8">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="BC8">
         <v>19.5</v>
@@ -2548,31 +2548,31 @@
         <v>44</v>
       </c>
       <c r="BE8">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="BF8">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="BG8">
-        <v>19.5</v>
+        <v>16.5</v>
       </c>
       <c r="BH8">
-        <v>3</v>
+        <v>2.92</v>
       </c>
       <c r="BI8">
-        <v>2.58</v>
+        <v>2.52</v>
       </c>
       <c r="BJ8">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="BK8">
-        <v>9</v>
+        <v>7.4</v>
       </c>
       <c r="BL8">
         <v>1000</v>
       </c>
       <c r="BM8">
-        <v>17</v>
+        <v>17.5</v>
       </c>
       <c r="BN8">
         <v>4.1</v>
@@ -2584,7 +2584,7 @@
         <v>13</v>
       </c>
       <c r="BQ8">
-        <v>9.800000000000001</v>
+        <v>7.6</v>
       </c>
       <c r="BR8">
         <v>34</v>
@@ -2596,25 +2596,25 @@
         <v>9.199999999999999</v>
       </c>
       <c r="BU8">
-        <v>7.4</v>
+        <v>6.2</v>
       </c>
       <c r="BV8">
         <v>1000</v>
       </c>
       <c r="BW8">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="BX8">
-        <v>1000</v>
+        <v>100</v>
       </c>
       <c r="BY8">
-        <v>14.5</v>
+        <v>15.5</v>
       </c>
       <c r="BZ8">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="CA8">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="CB8" t="s">
         <v>111</v>
@@ -2640,7 +2640,7 @@
         <v>2.86</v>
       </c>
       <c r="G9">
-        <v>2.94</v>
+        <v>2.96</v>
       </c>
       <c r="H9">
         <v>2.84</v>
@@ -2649,7 +2649,7 @@
         <v>2.92</v>
       </c>
       <c r="J9">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="K9">
         <v>3.3</v>
@@ -2658,22 +2658,22 @@
         <v>1.49</v>
       </c>
       <c r="M9">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="N9">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="O9">
-        <v>1.43</v>
+        <v>1.42</v>
       </c>
       <c r="P9">
-        <v>1.71</v>
+        <v>1.73</v>
       </c>
       <c r="Q9">
-        <v>2.32</v>
+        <v>2.3</v>
       </c>
       <c r="R9">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="S9">
         <v>4.4</v>
@@ -2691,16 +2691,16 @@
         <v>1.51</v>
       </c>
       <c r="X9">
-        <v>14.5</v>
+        <v>11.5</v>
       </c>
       <c r="Y9">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="Z9">
         <v>18</v>
       </c>
       <c r="AA9">
-        <v>65</v>
+        <v>48</v>
       </c>
       <c r="AB9">
         <v>9.800000000000001</v>
@@ -2712,7 +2712,7 @@
         <v>13</v>
       </c>
       <c r="AE9">
-        <v>50</v>
+        <v>38</v>
       </c>
       <c r="AF9">
         <v>18.5</v>
@@ -2721,43 +2721,43 @@
         <v>13</v>
       </c>
       <c r="AH9">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="AI9">
-        <v>55</v>
+        <v>75</v>
       </c>
       <c r="AJ9">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="AK9">
         <v>50</v>
       </c>
       <c r="AL9">
-        <v>70</v>
+        <v>55</v>
       </c>
       <c r="AM9">
         <v>580</v>
       </c>
       <c r="AN9">
-        <v>40</v>
+        <v>48</v>
       </c>
       <c r="AO9">
-        <v>46</v>
+        <v>38</v>
       </c>
       <c r="AP9">
         <v>10</v>
       </c>
       <c r="AQ9">
-        <v>8.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AR9">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="AS9">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="AT9">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AU9">
         <v>6.4</v>
@@ -2766,34 +2766,34 @@
         <v>11.5</v>
       </c>
       <c r="AW9">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="AX9">
         <v>16</v>
       </c>
       <c r="AY9">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AZ9">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="BA9">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="BB9">
+        <v>20</v>
+      </c>
+      <c r="BC9">
         <v>29</v>
       </c>
-      <c r="BC9">
-        <v>28</v>
-      </c>
       <c r="BD9">
-        <v>9.6</v>
+        <v>34</v>
       </c>
       <c r="BE9">
-        <v>10.5</v>
+        <v>34</v>
       </c>
       <c r="BF9">
-        <v>30</v>
+        <v>19.5</v>
       </c>
       <c r="BG9">
         <v>27</v>
@@ -2802,25 +2802,25 @@
         <v>3.05</v>
       </c>
       <c r="BI9">
-        <v>2.8</v>
+        <v>2.76</v>
       </c>
       <c r="BJ9">
         <v>10</v>
       </c>
       <c r="BK9">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="BL9">
         <v>1000</v>
       </c>
       <c r="BM9">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="BN9">
         <v>5.8</v>
       </c>
       <c r="BO9">
-        <v>4.5</v>
+        <v>5.1</v>
       </c>
       <c r="BP9">
         <v>24</v>
@@ -2829,34 +2829,34 @@
         <v>10</v>
       </c>
       <c r="BR9">
-        <v>40</v>
+        <v>1000</v>
       </c>
       <c r="BS9">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="BT9">
         <v>5.7</v>
       </c>
       <c r="BU9">
-        <v>4.3</v>
+        <v>5.1</v>
       </c>
       <c r="BV9">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="BW9">
         <v>10</v>
       </c>
       <c r="BX9">
-        <v>40</v>
+        <v>1000</v>
       </c>
       <c r="BY9">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="BZ9">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="CA9">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="CB9" t="s">
         <v>111</v>
@@ -2879,16 +2879,16 @@
         <v>110</v>
       </c>
       <c r="F10">
-        <v>2.12</v>
+        <v>2.22</v>
       </c>
       <c r="G10">
-        <v>2.24</v>
+        <v>2.36</v>
       </c>
       <c r="H10">
-        <v>3.65</v>
+        <v>3.5</v>
       </c>
       <c r="I10">
-        <v>4.1</v>
+        <v>3.9</v>
       </c>
       <c r="J10">
         <v>3.35</v>
@@ -2897,40 +2897,40 @@
         <v>3.6</v>
       </c>
       <c r="L10">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="M10">
         <v>1.08</v>
       </c>
       <c r="N10">
-        <v>3.45</v>
+        <v>3.35</v>
       </c>
       <c r="O10">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="P10">
-        <v>1.81</v>
+        <v>1.79</v>
       </c>
       <c r="Q10">
-        <v>2.1</v>
+        <v>2.16</v>
       </c>
       <c r="R10">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="S10">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="T10">
-        <v>1.85</v>
+        <v>1.84</v>
       </c>
       <c r="U10">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="V10">
-        <v>1.33</v>
+        <v>1.35</v>
       </c>
       <c r="W10">
-        <v>1.8</v>
+        <v>1.73</v>
       </c>
       <c r="X10">
         <v>14</v>
@@ -2939,112 +2939,112 @@
         <v>14.5</v>
       </c>
       <c r="Z10">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="AA10">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="AB10">
-        <v>9.199999999999999</v>
+        <v>10.5</v>
       </c>
       <c r="AC10">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="AD10">
-        <v>16.5</v>
+        <v>18</v>
       </c>
       <c r="AE10">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="AF10">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AG10">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="AH10">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AI10">
+        <v>70</v>
+      </c>
+      <c r="AJ10">
+        <v>32</v>
+      </c>
+      <c r="AK10">
+        <v>30</v>
+      </c>
+      <c r="AL10">
+        <v>50</v>
+      </c>
+      <c r="AM10">
+        <v>140</v>
+      </c>
+      <c r="AN10">
+        <v>25</v>
+      </c>
+      <c r="AO10">
         <v>65</v>
       </c>
-      <c r="AJ10">
-        <v>34</v>
-      </c>
-      <c r="AK10">
-        <v>28</v>
-      </c>
-      <c r="AL10">
-        <v>46</v>
-      </c>
-      <c r="AM10">
-        <v>120</v>
-      </c>
-      <c r="AN10">
-        <v>22</v>
-      </c>
-      <c r="AO10">
-        <v>60</v>
-      </c>
       <c r="AP10">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="AQ10">
-        <v>10.5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AR10">
-        <v>21</v>
+        <v>19.5</v>
       </c>
       <c r="AS10">
-        <v>6.8</v>
+        <v>5.4</v>
       </c>
       <c r="AT10">
         <v>7.8</v>
       </c>
       <c r="AU10">
-        <v>6.6</v>
+        <v>6</v>
       </c>
       <c r="AV10">
-        <v>12.5</v>
+        <v>11.5</v>
       </c>
       <c r="AW10">
-        <v>6.6</v>
+        <v>5.3</v>
       </c>
       <c r="AX10">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AY10">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="AZ10">
-        <v>15.5</v>
+        <v>14</v>
       </c>
       <c r="BA10">
-        <v>6.8</v>
+        <v>5.3</v>
       </c>
       <c r="BB10">
-        <v>20</v>
+        <v>4.9</v>
       </c>
       <c r="BC10">
+        <v>4.8</v>
+      </c>
+      <c r="BD10">
+        <v>36</v>
+      </c>
+      <c r="BE10">
+        <v>5.6</v>
+      </c>
+      <c r="BF10">
         <v>18</v>
       </c>
-      <c r="BD10">
-        <v>6.4</v>
-      </c>
-      <c r="BE10">
-        <v>7</v>
-      </c>
-      <c r="BF10">
-        <v>15.5</v>
-      </c>
       <c r="BG10">
-        <v>6.6</v>
+        <v>5.3</v>
       </c>
       <c r="BH10">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="BI10">
-        <v>2.64</v>
+        <v>2.62</v>
       </c>
       <c r="BJ10">
         <v>10.5</v>
@@ -3059,13 +3059,13 @@
         <v>10</v>
       </c>
       <c r="BN10">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="BO10">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="BP10">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="BQ10">
         <v>6.6</v>
@@ -3077,28 +3077,28 @@
         <v>8.199999999999999</v>
       </c>
       <c r="BT10">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="BU10">
-        <v>5.4</v>
+        <v>5.3</v>
       </c>
       <c r="BV10">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="BW10">
         <v>8.199999999999999</v>
       </c>
       <c r="BX10">
-        <v>48</v>
+        <v>1000</v>
       </c>
       <c r="BY10">
         <v>8.800000000000001</v>
       </c>
       <c r="BZ10">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="CA10">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="CB10" t="s">
         <v>111</v>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-08-11.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-08-11.xlsx
@@ -349,7 +349,7 @@
     <t>Union Espanola</t>
   </si>
   <si>
-    <t>2026-08-11 07:40:26</t>
+    <t>2026-08-11 09:48:01</t>
   </si>
 </sst>
 </file>
@@ -943,220 +943,220 @@
         <v>102</v>
       </c>
       <c r="F2">
-        <v>5.8</v>
+        <v>2</v>
       </c>
       <c r="G2">
-        <v>6.8</v>
+        <v>2.06</v>
       </c>
       <c r="H2">
-        <v>1.78</v>
+        <v>5.2</v>
       </c>
       <c r="I2">
+        <v>5.7</v>
+      </c>
+      <c r="J2">
+        <v>3.1</v>
+      </c>
+      <c r="K2">
+        <v>3.2</v>
+      </c>
+      <c r="L2">
+        <v>0</v>
+      </c>
+      <c r="M2">
+        <v>0</v>
+      </c>
+      <c r="N2">
+        <v>0</v>
+      </c>
+      <c r="O2">
+        <v>0</v>
+      </c>
+      <c r="P2">
+        <v>0</v>
+      </c>
+      <c r="Q2">
+        <v>0</v>
+      </c>
+      <c r="R2">
+        <v>3.6</v>
+      </c>
+      <c r="S2">
+        <v>1.37</v>
+      </c>
+      <c r="T2">
+        <v>0</v>
+      </c>
+      <c r="U2">
+        <v>0</v>
+      </c>
+      <c r="V2">
+        <v>1.21</v>
+      </c>
+      <c r="W2">
         <v>1.9</v>
       </c>
-      <c r="J2">
-        <v>3.15</v>
-      </c>
-      <c r="K2">
-        <v>3.65</v>
-      </c>
-      <c r="L2">
-        <v>1.54</v>
-      </c>
-      <c r="M2">
-        <v>1.13</v>
-      </c>
-      <c r="N2">
-        <v>2.76</v>
-      </c>
-      <c r="O2">
-        <v>1.53</v>
-      </c>
-      <c r="P2">
-        <v>1.57</v>
-      </c>
-      <c r="Q2">
-        <v>2.58</v>
-      </c>
-      <c r="R2">
-        <v>1.2</v>
-      </c>
-      <c r="S2">
-        <v>5.2</v>
-      </c>
-      <c r="T2">
-        <v>2.2</v>
-      </c>
-      <c r="U2">
-        <v>1.72</v>
-      </c>
-      <c r="V2">
-        <v>2.08</v>
-      </c>
-      <c r="W2">
-        <v>1.18</v>
-      </c>
       <c r="X2">
-        <v>9.800000000000001</v>
+        <v>1000</v>
       </c>
       <c r="Y2">
-        <v>6.8</v>
+        <v>1000</v>
       </c>
       <c r="Z2">
-        <v>9.199999999999999</v>
+        <v>1000</v>
       </c>
       <c r="AA2">
-        <v>24</v>
+        <v>1000</v>
       </c>
       <c r="AB2">
-        <v>18</v>
+        <v>1000</v>
       </c>
       <c r="AC2">
-        <v>8.199999999999999</v>
+        <v>1000</v>
       </c>
       <c r="AD2">
-        <v>11</v>
+        <v>1000</v>
       </c>
       <c r="AE2">
-        <v>26</v>
+        <v>1000</v>
       </c>
       <c r="AF2">
-        <v>60</v>
+        <v>1000</v>
       </c>
       <c r="AG2">
+        <v>3.85</v>
+      </c>
+      <c r="AH2">
+        <v>3.9</v>
+      </c>
+      <c r="AI2">
+        <v>8.6</v>
+      </c>
+      <c r="AJ2">
+        <v>1000</v>
+      </c>
+      <c r="AK2">
+        <v>13</v>
+      </c>
+      <c r="AL2">
+        <v>13</v>
+      </c>
+      <c r="AM2">
+        <v>34</v>
+      </c>
+      <c r="AN2">
+        <v>36</v>
+      </c>
+      <c r="AO2">
         <v>27</v>
       </c>
-      <c r="AH2">
-        <v>28</v>
-      </c>
-      <c r="AI2">
-        <v>70</v>
-      </c>
-      <c r="AJ2">
-        <v>900</v>
-      </c>
-      <c r="AK2">
-        <v>140</v>
-      </c>
-      <c r="AL2">
-        <v>700</v>
-      </c>
-      <c r="AM2">
-        <v>580</v>
-      </c>
-      <c r="AN2">
-        <v>260</v>
-      </c>
-      <c r="AO2">
-        <v>23</v>
-      </c>
       <c r="AP2">
-        <v>8.199999999999999</v>
+        <v>12</v>
       </c>
       <c r="AQ2">
-        <v>5.8</v>
+        <v>12</v>
       </c>
       <c r="AR2">
-        <v>7.8</v>
+        <v>12</v>
       </c>
       <c r="AS2">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="AT2">
-        <v>13.5</v>
+        <v>12</v>
       </c>
       <c r="AU2">
-        <v>6.8</v>
+        <v>12</v>
       </c>
       <c r="AV2">
-        <v>9.199999999999999</v>
+        <v>12</v>
       </c>
       <c r="AW2">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="AX2">
-        <v>36</v>
+        <v>8.4</v>
       </c>
       <c r="AY2">
-        <v>21</v>
+        <v>3.4</v>
       </c>
       <c r="AZ2">
-        <v>14</v>
+        <v>3.4</v>
       </c>
       <c r="BA2">
-        <v>42</v>
+        <v>6.4</v>
       </c>
       <c r="BB2">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="BC2">
         <v>10</v>
       </c>
       <c r="BD2">
-        <v>9.199999999999999</v>
+        <v>10.5</v>
       </c>
       <c r="BE2">
-        <v>140</v>
+        <v>25</v>
       </c>
       <c r="BF2">
-        <v>8</v>
+        <v>22</v>
       </c>
       <c r="BG2">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="BH2">
-        <v>2.84</v>
+        <v>0</v>
       </c>
       <c r="BI2">
-        <v>2.36</v>
+        <v>0</v>
       </c>
       <c r="BJ2">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="BK2">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="BL2">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BM2">
-        <v>170</v>
+        <v>0</v>
       </c>
       <c r="BN2">
-        <v>9.6</v>
+        <v>0</v>
       </c>
       <c r="BO2">
-        <v>5.1</v>
+        <v>0</v>
       </c>
       <c r="BP2">
-        <v>75</v>
+        <v>0</v>
       </c>
       <c r="BQ2">
-        <v>9.4</v>
+        <v>0</v>
       </c>
       <c r="BR2">
-        <v>95</v>
+        <v>0</v>
       </c>
       <c r="BS2">
-        <v>9.6</v>
+        <v>0</v>
       </c>
       <c r="BT2">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="BU2">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="BV2">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="BW2">
-        <v>6.4</v>
+        <v>0</v>
       </c>
       <c r="BX2">
-        <v>44</v>
+        <v>0</v>
       </c>
       <c r="BY2">
-        <v>8.6</v>
+        <v>0</v>
       </c>
       <c r="BZ2">
         <v>0</v>
@@ -1185,70 +1185,70 @@
         <v>103</v>
       </c>
       <c r="F3">
+        <v>2.58</v>
+      </c>
+      <c r="G3">
+        <v>2.6</v>
+      </c>
+      <c r="H3">
+        <v>2.74</v>
+      </c>
+      <c r="I3">
+        <v>2.78</v>
+      </c>
+      <c r="J3">
+        <v>3.9</v>
+      </c>
+      <c r="K3">
+        <v>4</v>
+      </c>
+      <c r="L3">
+        <v>1.33</v>
+      </c>
+      <c r="M3">
+        <v>1.05</v>
+      </c>
+      <c r="N3">
+        <v>5.1</v>
+      </c>
+      <c r="O3">
+        <v>1.23</v>
+      </c>
+      <c r="P3">
         <v>2.38</v>
       </c>
-      <c r="G3">
-        <v>2.42</v>
-      </c>
-      <c r="H3">
-        <v>3</v>
-      </c>
-      <c r="I3">
-        <v>3.1</v>
-      </c>
-      <c r="J3">
-        <v>3.85</v>
-      </c>
-      <c r="K3">
-        <v>3.95</v>
-      </c>
-      <c r="L3">
-        <v>1.32</v>
-      </c>
-      <c r="M3">
-        <v>1.04</v>
-      </c>
-      <c r="N3">
-        <v>5.3</v>
-      </c>
-      <c r="O3">
-        <v>1.22</v>
-      </c>
-      <c r="P3">
-        <v>2.44</v>
-      </c>
       <c r="Q3">
-        <v>1.67</v>
+        <v>1.69</v>
       </c>
       <c r="R3">
-        <v>1.58</v>
+        <v>1.56</v>
       </c>
       <c r="S3">
-        <v>2.68</v>
+        <v>2.74</v>
       </c>
       <c r="T3">
-        <v>1.61</v>
+        <v>1.63</v>
       </c>
       <c r="U3">
-        <v>2.58</v>
+        <v>2.46</v>
       </c>
       <c r="V3">
-        <v>1.47</v>
+        <v>1.56</v>
       </c>
       <c r="W3">
-        <v>1.7</v>
+        <v>1.62</v>
       </c>
       <c r="X3">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="Y3">
-        <v>16.5</v>
+        <v>14.5</v>
       </c>
       <c r="Z3">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="AA3">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="AB3">
         <v>14.5</v>
@@ -1257,94 +1257,94 @@
         <v>9.199999999999999</v>
       </c>
       <c r="AD3">
+        <v>12.5</v>
+      </c>
+      <c r="AE3">
+        <v>27</v>
+      </c>
+      <c r="AF3">
+        <v>19</v>
+      </c>
+      <c r="AG3">
+        <v>12.5</v>
+      </c>
+      <c r="AH3">
+        <v>15.5</v>
+      </c>
+      <c r="AI3">
+        <v>30</v>
+      </c>
+      <c r="AJ3">
+        <v>38</v>
+      </c>
+      <c r="AK3">
+        <v>26</v>
+      </c>
+      <c r="AL3">
+        <v>32</v>
+      </c>
+      <c r="AM3">
+        <v>60</v>
+      </c>
+      <c r="AN3">
+        <v>16</v>
+      </c>
+      <c r="AO3">
+        <v>17</v>
+      </c>
+      <c r="AP3">
+        <v>19</v>
+      </c>
+      <c r="AQ3">
+        <v>13</v>
+      </c>
+      <c r="AR3">
+        <v>18</v>
+      </c>
+      <c r="AS3">
+        <v>34</v>
+      </c>
+      <c r="AT3">
         <v>14</v>
-      </c>
-      <c r="AE3">
-        <v>30</v>
-      </c>
-      <c r="AF3">
-        <v>18.5</v>
-      </c>
-      <c r="AG3">
-        <v>12</v>
-      </c>
-      <c r="AH3">
-        <v>14.5</v>
-      </c>
-      <c r="AI3">
-        <v>65</v>
-      </c>
-      <c r="AJ3">
-        <v>34</v>
-      </c>
-      <c r="AK3">
-        <v>23</v>
-      </c>
-      <c r="AL3">
-        <v>30</v>
-      </c>
-      <c r="AM3">
-        <v>80</v>
-      </c>
-      <c r="AN3">
-        <v>13.5</v>
-      </c>
-      <c r="AO3">
-        <v>20</v>
-      </c>
-      <c r="AP3">
-        <v>19.5</v>
-      </c>
-      <c r="AQ3">
-        <v>15.5</v>
-      </c>
-      <c r="AR3">
-        <v>21</v>
-      </c>
-      <c r="AS3">
-        <v>40</v>
-      </c>
-      <c r="AT3">
-        <v>13</v>
       </c>
       <c r="AU3">
         <v>8.4</v>
       </c>
       <c r="AV3">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AW3">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="AX3">
-        <v>16</v>
+        <v>18.5</v>
       </c>
       <c r="AY3">
-        <v>10.5</v>
+        <v>11.5</v>
       </c>
       <c r="AZ3">
         <v>13.5</v>
       </c>
       <c r="BA3">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="BB3">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="BC3">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="BD3">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="BE3">
         <v>50</v>
       </c>
       <c r="BF3">
-        <v>12</v>
+        <v>14.5</v>
       </c>
       <c r="BG3">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="BH3">
         <v>4.1</v>
@@ -1356,49 +1356,49 @@
         <v>8.6</v>
       </c>
       <c r="BK3">
+        <v>7.6</v>
+      </c>
+      <c r="BL3">
+        <v>80</v>
+      </c>
+      <c r="BM3">
+        <v>14.5</v>
+      </c>
+      <c r="BN3">
         <v>5.9</v>
       </c>
-      <c r="BL3">
-        <v>1000</v>
-      </c>
-      <c r="BM3">
-        <v>15</v>
-      </c>
-      <c r="BN3">
-        <v>5.6</v>
-      </c>
       <c r="BO3">
-        <v>5.1</v>
+        <v>5.3</v>
       </c>
       <c r="BP3">
-        <v>16</v>
+        <v>17.5</v>
       </c>
       <c r="BQ3">
-        <v>8.800000000000001</v>
+        <v>13</v>
       </c>
       <c r="BR3">
-        <v>36</v>
+        <v>26</v>
       </c>
       <c r="BS3">
-        <v>11</v>
+        <v>18.5</v>
       </c>
       <c r="BT3">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="BU3">
-        <v>5.8</v>
+        <v>5.5</v>
       </c>
       <c r="BV3">
-        <v>1000</v>
+        <v>19</v>
       </c>
       <c r="BW3">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="BX3">
-        <v>38</v>
+        <v>27</v>
       </c>
       <c r="BY3">
-        <v>11.5</v>
+        <v>20</v>
       </c>
       <c r="BZ3">
         <v>0</v>
@@ -1427,7 +1427,7 @@
         <v>104</v>
       </c>
       <c r="F4">
-        <v>2.92</v>
+        <v>2.9</v>
       </c>
       <c r="G4">
         <v>3.15</v>
@@ -1436,7 +1436,7 @@
         <v>2.98</v>
       </c>
       <c r="I4">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="J4">
         <v>2.8</v>
@@ -1445,7 +1445,7 @@
         <v>2.98</v>
       </c>
       <c r="L4">
-        <v>1.67</v>
+        <v>1.66</v>
       </c>
       <c r="M4">
         <v>1.16</v>
@@ -1469,10 +1469,10 @@
         <v>6.6</v>
       </c>
       <c r="T4">
-        <v>2.28</v>
+        <v>2.3</v>
       </c>
       <c r="U4">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="V4">
         <v>1.45</v>
@@ -1496,7 +1496,7 @@
         <v>8</v>
       </c>
       <c r="AC4">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="AD4">
         <v>16</v>
@@ -1508,7 +1508,7 @@
         <v>19</v>
       </c>
       <c r="AG4">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="AH4">
         <v>27</v>
@@ -1523,16 +1523,16 @@
         <v>55</v>
       </c>
       <c r="AL4">
-        <v>460</v>
+        <v>230</v>
       </c>
       <c r="AM4">
         <v>500</v>
       </c>
       <c r="AN4">
-        <v>500</v>
+        <v>75</v>
       </c>
       <c r="AO4">
-        <v>75</v>
+        <v>95</v>
       </c>
       <c r="AP4">
         <v>6.2</v>
@@ -1544,7 +1544,7 @@
         <v>16.5</v>
       </c>
       <c r="AS4">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="AT4">
         <v>6.6</v>
@@ -1559,7 +1559,7 @@
         <v>23</v>
       </c>
       <c r="AX4">
-        <v>16.5</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AY4">
         <v>13</v>
@@ -1568,19 +1568,19 @@
         <v>15</v>
       </c>
       <c r="BA4">
-        <v>34</v>
+        <v>9.6</v>
       </c>
       <c r="BB4">
         <v>18</v>
       </c>
       <c r="BC4">
-        <v>36</v>
+        <v>22</v>
       </c>
       <c r="BD4">
-        <v>9</v>
+        <v>9.6</v>
       </c>
       <c r="BE4">
-        <v>9.6</v>
+        <v>10</v>
       </c>
       <c r="BF4">
         <v>11.5</v>
@@ -1592,40 +1592,40 @@
         <v>2.64</v>
       </c>
       <c r="BI4">
-        <v>2.14</v>
+        <v>2.12</v>
       </c>
       <c r="BJ4">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="BK4">
+        <v>5.7</v>
+      </c>
+      <c r="BL4">
+        <v>1000</v>
+      </c>
+      <c r="BM4">
+        <v>10</v>
+      </c>
+      <c r="BN4">
         <v>5.9</v>
       </c>
-      <c r="BL4">
-        <v>1000</v>
-      </c>
-      <c r="BM4">
-        <v>11</v>
-      </c>
-      <c r="BN4">
-        <v>6</v>
-      </c>
       <c r="BO4">
-        <v>4.9</v>
+        <v>4.3</v>
       </c>
       <c r="BP4">
         <v>30</v>
       </c>
       <c r="BQ4">
-        <v>8.199999999999999</v>
+        <v>7.8</v>
       </c>
       <c r="BR4">
         <v>60</v>
       </c>
       <c r="BS4">
-        <v>9.6</v>
+        <v>9</v>
       </c>
       <c r="BT4">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="BU4">
         <v>4.4</v>
@@ -1634,19 +1634,19 @@
         <v>32</v>
       </c>
       <c r="BW4">
-        <v>8.4</v>
+        <v>8</v>
       </c>
       <c r="BX4">
         <v>60</v>
       </c>
       <c r="BY4">
-        <v>9.6</v>
+        <v>9</v>
       </c>
       <c r="BZ4">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="CA4">
-        <v>9.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="CB4" t="s">
         <v>111</v>
@@ -1669,7 +1669,7 @@
         <v>105</v>
       </c>
       <c r="F5">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="G5">
         <v>7.8</v>
@@ -1678,10 +1678,10 @@
         <v>1.6</v>
       </c>
       <c r="I5">
-        <v>1.63</v>
+        <v>1.61</v>
       </c>
       <c r="J5">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="K5">
         <v>4.3</v>
@@ -1705,28 +1705,28 @@
         <v>2.18</v>
       </c>
       <c r="R5">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="S5">
         <v>4.1</v>
       </c>
       <c r="T5">
-        <v>2.14</v>
+        <v>2.18</v>
       </c>
       <c r="U5">
-        <v>1.76</v>
+        <v>1.74</v>
       </c>
       <c r="V5">
-        <v>2.58</v>
+        <v>2.64</v>
       </c>
       <c r="W5">
         <v>1.15</v>
       </c>
       <c r="X5">
-        <v>16</v>
+        <v>13.5</v>
       </c>
       <c r="Y5">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="Z5">
         <v>8.4</v>
@@ -1744,19 +1744,19 @@
         <v>10.5</v>
       </c>
       <c r="AE5">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AF5">
         <v>160</v>
       </c>
       <c r="AG5">
-        <v>85</v>
+        <v>38</v>
       </c>
       <c r="AH5">
-        <v>65</v>
+        <v>36</v>
       </c>
       <c r="AI5">
-        <v>60</v>
+        <v>120</v>
       </c>
       <c r="AJ5">
         <v>700</v>
@@ -1774,13 +1774,13 @@
         <v>280</v>
       </c>
       <c r="AO5">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AP5">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AQ5">
-        <v>6</v>
+        <v>5.9</v>
       </c>
       <c r="AR5">
         <v>7.2</v>
@@ -1798,76 +1798,76 @@
         <v>8.800000000000001</v>
       </c>
       <c r="AW5">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="AX5">
-        <v>27</v>
+        <v>20</v>
       </c>
       <c r="AY5">
         <v>14.5</v>
       </c>
       <c r="AZ5">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="BA5">
-        <v>40</v>
+        <v>24</v>
       </c>
       <c r="BB5">
-        <v>9.800000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BC5">
-        <v>9.4</v>
+        <v>9</v>
       </c>
       <c r="BD5">
-        <v>9.6</v>
+        <v>9</v>
       </c>
       <c r="BE5">
-        <v>9.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BF5">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BG5">
         <v>10</v>
       </c>
       <c r="BH5">
-        <v>3.75</v>
+        <v>3.65</v>
       </c>
       <c r="BI5">
-        <v>2.6</v>
+        <v>2.56</v>
       </c>
       <c r="BJ5">
         <v>14.5</v>
       </c>
       <c r="BK5">
-        <v>3.6</v>
+        <v>3.75</v>
       </c>
       <c r="BL5">
         <v>1000</v>
       </c>
       <c r="BM5">
-        <v>4.7</v>
+        <v>4.9</v>
       </c>
       <c r="BN5">
         <v>13</v>
       </c>
       <c r="BO5">
-        <v>3.5</v>
+        <v>3.65</v>
       </c>
       <c r="BP5">
         <v>1000</v>
       </c>
       <c r="BQ5">
-        <v>4.6</v>
+        <v>4.8</v>
       </c>
       <c r="BR5">
         <v>1000</v>
       </c>
       <c r="BS5">
-        <v>4.6</v>
+        <v>4.8</v>
       </c>
       <c r="BT5">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="BU5">
         <v>3.05</v>
@@ -1876,19 +1876,19 @@
         <v>13</v>
       </c>
       <c r="BW5">
-        <v>3.5</v>
+        <v>3.65</v>
       </c>
       <c r="BX5">
         <v>38</v>
       </c>
       <c r="BY5">
+        <v>4.4</v>
+      </c>
+      <c r="BZ5">
+        <v>29</v>
+      </c>
+      <c r="CA5">
         <v>4.3</v>
-      </c>
-      <c r="BZ5">
-        <v>28</v>
-      </c>
-      <c r="CA5">
-        <v>4.1</v>
       </c>
       <c r="CB5" t="s">
         <v>111</v>
@@ -1911,37 +1911,37 @@
         <v>106</v>
       </c>
       <c r="F6">
-        <v>2.62</v>
+        <v>2.56</v>
       </c>
       <c r="G6">
-        <v>2.84</v>
+        <v>2.72</v>
       </c>
       <c r="H6">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="I6">
         <v>3.8</v>
       </c>
       <c r="J6">
-        <v>2.7</v>
+        <v>2.9</v>
       </c>
       <c r="K6">
-        <v>2.88</v>
+        <v>2.96</v>
       </c>
       <c r="L6">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="M6">
         <v>1.18</v>
       </c>
       <c r="N6">
-        <v>2.2</v>
+        <v>2.22</v>
       </c>
       <c r="O6">
         <v>1.75</v>
       </c>
       <c r="P6">
-        <v>1.37</v>
+        <v>1.4</v>
       </c>
       <c r="Q6">
         <v>3.35</v>
@@ -1953,16 +1953,16 @@
         <v>7.6</v>
       </c>
       <c r="T6">
-        <v>2.4</v>
+        <v>2.44</v>
       </c>
       <c r="U6">
+        <v>1.59</v>
+      </c>
+      <c r="V6">
+        <v>1.36</v>
+      </c>
+      <c r="W6">
         <v>1.58</v>
-      </c>
-      <c r="V6">
-        <v>1.37</v>
-      </c>
-      <c r="W6">
-        <v>1.54</v>
       </c>
       <c r="X6">
         <v>7.6</v>
@@ -1971,13 +1971,13 @@
         <v>8.6</v>
       </c>
       <c r="Z6">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AA6">
-        <v>110</v>
+        <v>230</v>
       </c>
       <c r="AB6">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="AC6">
         <v>7.4</v>
@@ -1986,10 +1986,10 @@
         <v>19</v>
       </c>
       <c r="AE6">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="AF6">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="AG6">
         <v>15.5</v>
@@ -2001,10 +2001,10 @@
         <v>540</v>
       </c>
       <c r="AJ6">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="AK6">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="AL6">
         <v>230</v>
@@ -2013,16 +2013,16 @@
         <v>500</v>
       </c>
       <c r="AN6">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="AO6">
-        <v>140</v>
+        <v>160</v>
       </c>
       <c r="AP6">
-        <v>5.6</v>
+        <v>5.5</v>
       </c>
       <c r="AQ6">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="AR6">
         <v>15.5</v>
@@ -2031,7 +2031,7 @@
         <v>20</v>
       </c>
       <c r="AT6">
-        <v>5.8</v>
+        <v>5.6</v>
       </c>
       <c r="AU6">
         <v>6</v>
@@ -2043,7 +2043,7 @@
         <v>46</v>
       </c>
       <c r="AX6">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AY6">
         <v>12.5</v>
@@ -2052,7 +2052,7 @@
         <v>23</v>
       </c>
       <c r="BA6">
-        <v>7.4</v>
+        <v>7.8</v>
       </c>
       <c r="BB6">
         <v>30</v>
@@ -2064,73 +2064,73 @@
         <v>28</v>
       </c>
       <c r="BE6">
-        <v>7.4</v>
+        <v>7.8</v>
       </c>
       <c r="BF6">
         <v>40</v>
       </c>
       <c r="BG6">
-        <v>7</v>
+        <v>7.4</v>
       </c>
       <c r="BH6">
-        <v>2.72</v>
+        <v>2.7</v>
       </c>
       <c r="BI6">
-        <v>2</v>
+        <v>1.99</v>
       </c>
       <c r="BJ6">
         <v>15.5</v>
       </c>
       <c r="BK6">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="BL6">
         <v>1000</v>
       </c>
       <c r="BM6">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="BN6">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="BO6">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="BP6">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="BQ6">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="BR6">
         <v>75</v>
       </c>
       <c r="BS6">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="BT6">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="BU6">
+        <v>5</v>
+      </c>
+      <c r="BV6">
+        <v>50</v>
+      </c>
+      <c r="BW6">
         <v>4.8</v>
       </c>
-      <c r="BV6">
-        <v>46</v>
-      </c>
-      <c r="BW6">
-        <v>4.7</v>
-      </c>
       <c r="BX6">
         <v>1000</v>
       </c>
       <c r="BY6">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="BZ6">
         <v>1000</v>
       </c>
       <c r="CA6">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="CB6" t="s">
         <v>111</v>
@@ -2153,16 +2153,16 @@
         <v>107</v>
       </c>
       <c r="F7">
-        <v>2.48</v>
+        <v>2.54</v>
       </c>
       <c r="G7">
         <v>2.58</v>
       </c>
       <c r="H7">
-        <v>3.65</v>
+        <v>3.6</v>
       </c>
       <c r="I7">
-        <v>3.9</v>
+        <v>3.75</v>
       </c>
       <c r="J7">
         <v>2.96</v>
@@ -2171,13 +2171,13 @@
         <v>2.98</v>
       </c>
       <c r="L7">
-        <v>1.69</v>
+        <v>1.7</v>
       </c>
       <c r="M7">
         <v>1.16</v>
       </c>
       <c r="N7">
-        <v>2.38</v>
+        <v>2.34</v>
       </c>
       <c r="O7">
         <v>1.68</v>
@@ -2186,13 +2186,13 @@
         <v>1.44</v>
       </c>
       <c r="Q7">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="R7">
         <v>1.15</v>
       </c>
       <c r="S7">
-        <v>6.6</v>
+        <v>7</v>
       </c>
       <c r="T7">
         <v>2.32</v>
@@ -2201,13 +2201,13 @@
         <v>1.64</v>
       </c>
       <c r="V7">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="W7">
         <v>1.63</v>
       </c>
       <c r="X7">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="Y7">
         <v>9.4</v>
@@ -2219,7 +2219,7 @@
         <v>500</v>
       </c>
       <c r="AB7">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="AC7">
         <v>7.2</v>
@@ -2228,10 +2228,10 @@
         <v>18.5</v>
       </c>
       <c r="AE7">
-        <v>230</v>
+        <v>260</v>
       </c>
       <c r="AF7">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="AG7">
         <v>14</v>
@@ -2243,10 +2243,10 @@
         <v>540</v>
       </c>
       <c r="AJ7">
-        <v>100</v>
+        <v>120</v>
       </c>
       <c r="AK7">
-        <v>46</v>
+        <v>150</v>
       </c>
       <c r="AL7">
         <v>230</v>
@@ -2270,10 +2270,10 @@
         <v>20</v>
       </c>
       <c r="AS7">
-        <v>9.199999999999999</v>
+        <v>10</v>
       </c>
       <c r="AT7">
-        <v>6</v>
+        <v>5.8</v>
       </c>
       <c r="AU7">
         <v>6</v>
@@ -2282,7 +2282,7 @@
         <v>15</v>
       </c>
       <c r="AW7">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="AX7">
         <v>12.5</v>
@@ -2294,7 +2294,7 @@
         <v>15</v>
       </c>
       <c r="BA7">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="BB7">
         <v>19</v>
@@ -2303,76 +2303,76 @@
         <v>29</v>
       </c>
       <c r="BD7">
-        <v>36</v>
+        <v>10</v>
       </c>
       <c r="BE7">
+        <v>11</v>
+      </c>
+      <c r="BF7">
+        <v>9.4</v>
+      </c>
+      <c r="BG7">
         <v>10</v>
       </c>
-      <c r="BF7">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="BG7">
-        <v>9.199999999999999</v>
-      </c>
       <c r="BH7">
-        <v>2.54</v>
+        <v>2.48</v>
       </c>
       <c r="BI7">
-        <v>2.08</v>
+        <v>2.06</v>
       </c>
       <c r="BJ7">
         <v>13</v>
       </c>
       <c r="BK7">
-        <v>6</v>
+        <v>6.4</v>
       </c>
       <c r="BL7">
         <v>1000</v>
       </c>
       <c r="BM7">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="BN7">
-        <v>5.4</v>
+        <v>5.3</v>
       </c>
       <c r="BO7">
-        <v>4</v>
+        <v>3.95</v>
       </c>
       <c r="BP7">
         <v>1000</v>
       </c>
       <c r="BQ7">
-        <v>8</v>
+        <v>8.4</v>
       </c>
       <c r="BR7">
         <v>1000</v>
       </c>
       <c r="BS7">
-        <v>9.800000000000001</v>
+        <v>10.5</v>
       </c>
       <c r="BT7">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="BU7">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="BV7">
         <v>1000</v>
       </c>
       <c r="BW7">
-        <v>9</v>
+        <v>9.6</v>
       </c>
       <c r="BX7">
         <v>1000</v>
       </c>
       <c r="BY7">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="BZ7">
         <v>1000</v>
       </c>
       <c r="CA7">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="CB7" t="s">
         <v>111</v>
@@ -2395,64 +2395,64 @@
         <v>108</v>
       </c>
       <c r="F8">
-        <v>1.76</v>
+        <v>1.79</v>
       </c>
       <c r="G8">
-        <v>1.77</v>
+        <v>1.81</v>
       </c>
       <c r="H8">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="I8">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="J8">
+        <v>3.6</v>
+      </c>
+      <c r="K8">
         <v>3.75</v>
       </c>
-      <c r="K8">
-        <v>3.85</v>
-      </c>
       <c r="L8">
-        <v>1.52</v>
+        <v>1.55</v>
       </c>
       <c r="M8">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="N8">
-        <v>3.05</v>
+        <v>2.84</v>
       </c>
       <c r="O8">
-        <v>1.46</v>
+        <v>1.53</v>
       </c>
       <c r="P8">
-        <v>1.69</v>
+        <v>1.6</v>
       </c>
       <c r="Q8">
-        <v>2.4</v>
+        <v>2.58</v>
       </c>
       <c r="R8">
-        <v>1.25</v>
+        <v>1.21</v>
       </c>
       <c r="S8">
-        <v>4.8</v>
+        <v>5.3</v>
       </c>
       <c r="T8">
-        <v>2.2</v>
+        <v>2.32</v>
       </c>
       <c r="U8">
-        <v>1.8</v>
+        <v>1.7</v>
       </c>
       <c r="V8">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="W8">
-        <v>2.28</v>
+        <v>2.22</v>
       </c>
       <c r="X8">
-        <v>11.5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="Y8">
-        <v>16.5</v>
+        <v>14.5</v>
       </c>
       <c r="Z8">
         <v>44</v>
@@ -2461,109 +2461,109 @@
         <v>200</v>
       </c>
       <c r="AB8">
-        <v>6.4</v>
+        <v>5.9</v>
       </c>
       <c r="AC8">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AD8">
+        <v>25</v>
+      </c>
+      <c r="AE8">
+        <v>700</v>
+      </c>
+      <c r="AF8">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AG8">
+        <v>11</v>
+      </c>
+      <c r="AH8">
+        <v>29</v>
+      </c>
+      <c r="AI8">
+        <v>700</v>
+      </c>
+      <c r="AJ8">
+        <v>20</v>
+      </c>
+      <c r="AK8">
         <v>23</v>
       </c>
-      <c r="AE8">
-        <v>110</v>
-      </c>
-      <c r="AF8">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AG8">
-        <v>10.5</v>
-      </c>
-      <c r="AH8">
-        <v>27</v>
-      </c>
-      <c r="AI8">
-        <v>120</v>
-      </c>
-      <c r="AJ8">
-        <v>18</v>
-      </c>
-      <c r="AK8">
-        <v>21</v>
-      </c>
       <c r="AL8">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="AM8">
-        <v>220</v>
+        <v>250</v>
       </c>
       <c r="AN8">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="AO8">
-        <v>160</v>
+        <v>600</v>
       </c>
       <c r="AP8">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AQ8">
-        <v>15</v>
+        <v>13.5</v>
       </c>
       <c r="AR8">
         <v>38</v>
       </c>
       <c r="AS8">
-        <v>16.5</v>
+        <v>21</v>
       </c>
       <c r="AT8">
-        <v>6</v>
+        <v>5.7</v>
       </c>
       <c r="AU8">
         <v>7.8</v>
       </c>
       <c r="AV8">
+        <v>23</v>
+      </c>
+      <c r="AW8">
+        <v>95</v>
+      </c>
+      <c r="AX8">
+        <v>8</v>
+      </c>
+      <c r="AY8">
+        <v>10</v>
+      </c>
+      <c r="AZ8">
+        <v>27</v>
+      </c>
+      <c r="BA8">
+        <v>29</v>
+      </c>
+      <c r="BB8">
+        <v>18.5</v>
+      </c>
+      <c r="BC8">
+        <v>22</v>
+      </c>
+      <c r="BD8">
+        <v>50</v>
+      </c>
+      <c r="BE8">
+        <v>36</v>
+      </c>
+      <c r="BF8">
+        <v>17</v>
+      </c>
+      <c r="BG8">
         <v>21</v>
       </c>
-      <c r="AW8">
-        <v>90</v>
-      </c>
-      <c r="AX8">
-        <v>8.4</v>
-      </c>
-      <c r="AY8">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AZ8">
-        <v>24</v>
-      </c>
-      <c r="BA8">
-        <v>90</v>
-      </c>
-      <c r="BB8">
-        <v>17</v>
-      </c>
-      <c r="BC8">
-        <v>19.5</v>
-      </c>
-      <c r="BD8">
-        <v>44</v>
-      </c>
-      <c r="BE8">
-        <v>17</v>
-      </c>
-      <c r="BF8">
-        <v>15</v>
-      </c>
-      <c r="BG8">
-        <v>16.5</v>
-      </c>
       <c r="BH8">
-        <v>2.92</v>
+        <v>2.82</v>
       </c>
       <c r="BI8">
-        <v>2.52</v>
+        <v>2.44</v>
       </c>
       <c r="BJ8">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="BK8">
         <v>7.4</v>
@@ -2572,7 +2572,7 @@
         <v>1000</v>
       </c>
       <c r="BM8">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="BN8">
         <v>4.1</v>
@@ -2581,13 +2581,13 @@
         <v>3.7</v>
       </c>
       <c r="BP8">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="BQ8">
         <v>7.6</v>
       </c>
       <c r="BR8">
-        <v>34</v>
+        <v>1000</v>
       </c>
       <c r="BS8">
         <v>12</v>
@@ -2596,7 +2596,7 @@
         <v>9.199999999999999</v>
       </c>
       <c r="BU8">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="BV8">
         <v>1000</v>
@@ -2605,13 +2605,13 @@
         <v>14.5</v>
       </c>
       <c r="BX8">
-        <v>100</v>
+        <v>1000</v>
       </c>
       <c r="BY8">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="BZ8">
-        <v>32</v>
+        <v>1000</v>
       </c>
       <c r="CA8">
         <v>12</v>
@@ -2637,73 +2637,73 @@
         <v>109</v>
       </c>
       <c r="F9">
-        <v>2.86</v>
+        <v>2.88</v>
       </c>
       <c r="G9">
-        <v>2.96</v>
+        <v>3</v>
       </c>
       <c r="H9">
         <v>2.84</v>
       </c>
       <c r="I9">
-        <v>2.92</v>
+        <v>2.94</v>
       </c>
       <c r="J9">
         <v>3.2</v>
       </c>
       <c r="K9">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="L9">
         <v>1.49</v>
       </c>
       <c r="M9">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="N9">
-        <v>3.25</v>
+        <v>3.15</v>
       </c>
       <c r="O9">
-        <v>1.42</v>
+        <v>1.44</v>
       </c>
       <c r="P9">
-        <v>1.73</v>
+        <v>1.72</v>
       </c>
       <c r="Q9">
-        <v>2.3</v>
+        <v>2.36</v>
       </c>
       <c r="R9">
-        <v>1.27</v>
+        <v>1.26</v>
       </c>
       <c r="S9">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="T9">
-        <v>1.9</v>
+        <v>1.91</v>
       </c>
       <c r="U9">
-        <v>1.99</v>
+        <v>2</v>
       </c>
       <c r="V9">
-        <v>1.52</v>
+        <v>1.51</v>
       </c>
       <c r="W9">
-        <v>1.51</v>
+        <v>1.5</v>
       </c>
       <c r="X9">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="Y9">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="Z9">
         <v>18</v>
       </c>
       <c r="AA9">
-        <v>48</v>
+        <v>100</v>
       </c>
       <c r="AB9">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="AC9">
         <v>7.4</v>
@@ -2712,7 +2712,7 @@
         <v>13</v>
       </c>
       <c r="AE9">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="AF9">
         <v>18.5</v>
@@ -2721,37 +2721,37 @@
         <v>13</v>
       </c>
       <c r="AH9">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="AI9">
         <v>75</v>
       </c>
       <c r="AJ9">
-        <v>50</v>
+        <v>110</v>
       </c>
       <c r="AK9">
-        <v>50</v>
+        <v>38</v>
       </c>
       <c r="AL9">
-        <v>55</v>
+        <v>120</v>
       </c>
       <c r="AM9">
         <v>580</v>
       </c>
       <c r="AN9">
-        <v>48</v>
+        <v>40</v>
       </c>
       <c r="AO9">
         <v>38</v>
       </c>
       <c r="AP9">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AQ9">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="AR9">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="AS9">
         <v>32</v>
@@ -2778,10 +2778,10 @@
         <v>17</v>
       </c>
       <c r="BA9">
-        <v>42</v>
+        <v>23</v>
       </c>
       <c r="BB9">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="BC9">
         <v>29</v>
@@ -2793,70 +2793,70 @@
         <v>34</v>
       </c>
       <c r="BF9">
-        <v>19.5</v>
+        <v>22</v>
       </c>
       <c r="BG9">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="BH9">
         <v>3.05</v>
       </c>
       <c r="BI9">
-        <v>2.76</v>
+        <v>2.54</v>
       </c>
       <c r="BJ9">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="BK9">
-        <v>6.2</v>
+        <v>7.4</v>
       </c>
       <c r="BL9">
         <v>1000</v>
       </c>
       <c r="BM9">
-        <v>15</v>
+        <v>13.5</v>
       </c>
       <c r="BN9">
         <v>5.8</v>
       </c>
       <c r="BO9">
-        <v>5.1</v>
+        <v>4.4</v>
       </c>
       <c r="BP9">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="BQ9">
-        <v>10</v>
+        <v>9.4</v>
       </c>
       <c r="BR9">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="BS9">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="BT9">
         <v>5.7</v>
       </c>
       <c r="BU9">
-        <v>5.1</v>
+        <v>4.3</v>
       </c>
       <c r="BV9">
         <v>24</v>
       </c>
       <c r="BW9">
-        <v>10</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BX9">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="BY9">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="BZ9">
         <v>38</v>
       </c>
       <c r="CA9">
-        <v>11.5</v>
+        <v>10.5</v>
       </c>
       <c r="CB9" t="s">
         <v>111</v>
@@ -2879,22 +2879,22 @@
         <v>110</v>
       </c>
       <c r="F10">
-        <v>2.22</v>
+        <v>2.24</v>
       </c>
       <c r="G10">
         <v>2.36</v>
       </c>
       <c r="H10">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="I10">
-        <v>3.9</v>
+        <v>3.85</v>
       </c>
       <c r="J10">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="K10">
-        <v>3.6</v>
+        <v>3.55</v>
       </c>
       <c r="L10">
         <v>1.45</v>
@@ -2912,7 +2912,7 @@
         <v>1.79</v>
       </c>
       <c r="Q10">
-        <v>2.16</v>
+        <v>2.18</v>
       </c>
       <c r="R10">
         <v>1.29</v>
@@ -2930,40 +2930,40 @@
         <v>1.35</v>
       </c>
       <c r="W10">
-        <v>1.73</v>
+        <v>1.75</v>
       </c>
       <c r="X10">
         <v>14</v>
       </c>
       <c r="Y10">
-        <v>14.5</v>
+        <v>13.5</v>
       </c>
       <c r="Z10">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="AA10">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="AB10">
-        <v>10.5</v>
+        <v>9.6</v>
       </c>
       <c r="AC10">
         <v>7.8</v>
       </c>
       <c r="AD10">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="AE10">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AF10">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AG10">
         <v>13</v>
       </c>
       <c r="AH10">
-        <v>22</v>
+        <v>19.5</v>
       </c>
       <c r="AI10">
         <v>70</v>
@@ -2972,91 +2972,91 @@
         <v>32</v>
       </c>
       <c r="AK10">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="AL10">
         <v>50</v>
       </c>
       <c r="AM10">
-        <v>140</v>
+        <v>130</v>
       </c>
       <c r="AN10">
         <v>25</v>
       </c>
       <c r="AO10">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="AP10">
-        <v>9.6</v>
+        <v>10.5</v>
       </c>
       <c r="AQ10">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="AR10">
-        <v>19.5</v>
+        <v>21</v>
       </c>
       <c r="AS10">
-        <v>5.4</v>
+        <v>7</v>
       </c>
       <c r="AT10">
         <v>7.8</v>
       </c>
       <c r="AU10">
-        <v>6</v>
+        <v>6.4</v>
       </c>
       <c r="AV10">
+        <v>12.5</v>
+      </c>
+      <c r="AW10">
+        <v>6.8</v>
+      </c>
+      <c r="AX10">
         <v>11.5</v>
-      </c>
-      <c r="AW10">
-        <v>5.3</v>
-      </c>
-      <c r="AX10">
-        <v>10.5</v>
       </c>
       <c r="AY10">
         <v>9.4</v>
       </c>
       <c r="AZ10">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="BA10">
-        <v>5.3</v>
+        <v>6.8</v>
       </c>
       <c r="BB10">
-        <v>4.9</v>
+        <v>6.2</v>
       </c>
       <c r="BC10">
-        <v>4.8</v>
+        <v>6</v>
       </c>
       <c r="BD10">
-        <v>36</v>
+        <v>6.6</v>
       </c>
       <c r="BE10">
-        <v>5.6</v>
+        <v>7.2</v>
       </c>
       <c r="BF10">
-        <v>18</v>
+        <v>16.5</v>
       </c>
       <c r="BG10">
-        <v>5.3</v>
+        <v>6.8</v>
       </c>
       <c r="BH10">
         <v>3.25</v>
       </c>
       <c r="BI10">
-        <v>2.62</v>
+        <v>2.68</v>
       </c>
       <c r="BJ10">
         <v>10.5</v>
       </c>
       <c r="BK10">
-        <v>5.3</v>
+        <v>5.5</v>
       </c>
       <c r="BL10">
         <v>1000</v>
       </c>
       <c r="BM10">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="BN10">
         <v>5.2</v>
@@ -3068,13 +3068,13 @@
         <v>18</v>
       </c>
       <c r="BQ10">
-        <v>6.6</v>
+        <v>7</v>
       </c>
       <c r="BR10">
         <v>1000</v>
       </c>
       <c r="BS10">
-        <v>8.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="BT10">
         <v>7</v>
@@ -3083,22 +3083,22 @@
         <v>5.3</v>
       </c>
       <c r="BV10">
-        <v>34</v>
+        <v>1000</v>
       </c>
       <c r="BW10">
-        <v>8.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="BX10">
         <v>1000</v>
       </c>
       <c r="BY10">
-        <v>8.800000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BZ10">
-        <v>34</v>
+        <v>1000</v>
       </c>
       <c r="CA10">
-        <v>8.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="CB10" t="s">
         <v>111</v>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-08-11.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-08-11.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="134" uniqueCount="112">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="128" uniqueCount="108">
   <si>
     <t>League</t>
   </si>
@@ -256,9 +256,6 @@
     <t>SnapshotTS</t>
   </si>
   <si>
-    <t>Chinese League 2</t>
-  </si>
-  <si>
     <t>Swedish Superettan</t>
   </si>
   <si>
@@ -277,9 +274,6 @@
     <t>2026-08-11</t>
   </si>
   <si>
-    <t>11:30:00</t>
-  </si>
-  <si>
     <t>17:00:00</t>
   </si>
   <si>
@@ -295,9 +289,6 @@
     <t>23:00:00</t>
   </si>
   <si>
-    <t>Hangzhou Linping Wuyue</t>
-  </si>
-  <si>
     <t>Helsingborgs</t>
   </si>
   <si>
@@ -322,9 +313,6 @@
     <t>Puerto Montt</t>
   </si>
   <si>
-    <t>Guizhou Zhucheng Athletic</t>
-  </si>
-  <si>
     <t>Varnamo</t>
   </si>
   <si>
@@ -349,7 +337,7 @@
     <t>Union Espanola</t>
   </si>
   <si>
-    <t>2026-08-11 09:48:01</t>
+    <t>2026-08-11 11:55:15</t>
   </si>
 </sst>
 </file>
@@ -681,7 +669,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:CB10"/>
+  <dimension ref="A1:CB9"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:80">
@@ -931,232 +919,232 @@
         <v>80</v>
       </c>
       <c r="B2" t="s">
+        <v>85</v>
+      </c>
+      <c r="C2" t="s">
         <v>86</v>
       </c>
-      <c r="C2" t="s">
-        <v>87</v>
-      </c>
       <c r="D2" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="E2" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="F2">
-        <v>2</v>
+        <v>2.62</v>
       </c>
       <c r="G2">
-        <v>2.06</v>
+        <v>2.64</v>
       </c>
       <c r="H2">
-        <v>5.2</v>
+        <v>2.7</v>
       </c>
       <c r="I2">
-        <v>5.7</v>
+        <v>2.74</v>
       </c>
       <c r="J2">
-        <v>3.1</v>
+        <v>3.9</v>
       </c>
       <c r="K2">
-        <v>3.2</v>
+        <v>4</v>
       </c>
       <c r="L2">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="N2">
-        <v>0</v>
+        <v>5.1</v>
       </c>
       <c r="O2">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="P2">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="Q2">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="R2">
-        <v>3.6</v>
+        <v>1.55</v>
       </c>
       <c r="S2">
-        <v>1.37</v>
+        <v>2.74</v>
       </c>
       <c r="T2">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="U2">
-        <v>0</v>
+        <v>2.52</v>
       </c>
       <c r="V2">
-        <v>1.21</v>
+        <v>1.56</v>
       </c>
       <c r="W2">
-        <v>1.9</v>
+        <v>1.6</v>
       </c>
       <c r="X2">
-        <v>1000</v>
+        <v>20</v>
       </c>
       <c r="Y2">
-        <v>1000</v>
+        <v>14.5</v>
       </c>
       <c r="Z2">
-        <v>1000</v>
+        <v>20</v>
       </c>
       <c r="AA2">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="AB2">
-        <v>1000</v>
+        <v>14.5</v>
       </c>
       <c r="AC2">
-        <v>1000</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AD2">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="AE2">
-        <v>1000</v>
+        <v>27</v>
       </c>
       <c r="AF2">
-        <v>1000</v>
+        <v>20</v>
       </c>
       <c r="AG2">
-        <v>3.85</v>
+        <v>12.5</v>
       </c>
       <c r="AH2">
-        <v>3.9</v>
+        <v>15</v>
       </c>
       <c r="AI2">
+        <v>32</v>
+      </c>
+      <c r="AJ2">
+        <v>38</v>
+      </c>
+      <c r="AK2">
+        <v>25</v>
+      </c>
+      <c r="AL2">
+        <v>32</v>
+      </c>
+      <c r="AM2">
+        <v>60</v>
+      </c>
+      <c r="AN2">
+        <v>16</v>
+      </c>
+      <c r="AO2">
+        <v>17</v>
+      </c>
+      <c r="AP2">
+        <v>19</v>
+      </c>
+      <c r="AQ2">
+        <v>13.5</v>
+      </c>
+      <c r="AR2">
+        <v>18.5</v>
+      </c>
+      <c r="AS2">
+        <v>36</v>
+      </c>
+      <c r="AT2">
+        <v>14</v>
+      </c>
+      <c r="AU2">
+        <v>8.4</v>
+      </c>
+      <c r="AV2">
+        <v>11.5</v>
+      </c>
+      <c r="AW2">
+        <v>24</v>
+      </c>
+      <c r="AX2">
+        <v>19.5</v>
+      </c>
+      <c r="AY2">
+        <v>11.5</v>
+      </c>
+      <c r="AZ2">
+        <v>13.5</v>
+      </c>
+      <c r="BA2">
+        <v>29</v>
+      </c>
+      <c r="BB2">
+        <v>36</v>
+      </c>
+      <c r="BC2">
+        <v>23</v>
+      </c>
+      <c r="BD2">
+        <v>29</v>
+      </c>
+      <c r="BE2">
+        <v>50</v>
+      </c>
+      <c r="BF2">
+        <v>14.5</v>
+      </c>
+      <c r="BG2">
+        <v>16</v>
+      </c>
+      <c r="BH2">
+        <v>4.1</v>
+      </c>
+      <c r="BI2">
+        <v>3.75</v>
+      </c>
+      <c r="BJ2">
         <v>8.6</v>
       </c>
-      <c r="AJ2">
-        <v>1000</v>
-      </c>
-      <c r="AK2">
-        <v>13</v>
-      </c>
-      <c r="AL2">
-        <v>13</v>
-      </c>
-      <c r="AM2">
-        <v>34</v>
-      </c>
-      <c r="AN2">
-        <v>36</v>
-      </c>
-      <c r="AO2">
+      <c r="BK2">
+        <v>7.6</v>
+      </c>
+      <c r="BL2">
+        <v>80</v>
+      </c>
+      <c r="BM2">
+        <v>14</v>
+      </c>
+      <c r="BN2">
+        <v>6</v>
+      </c>
+      <c r="BO2">
+        <v>5.3</v>
+      </c>
+      <c r="BP2">
+        <v>17.5</v>
+      </c>
+      <c r="BQ2">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="BR2">
+        <v>26</v>
+      </c>
+      <c r="BS2">
+        <v>10.5</v>
+      </c>
+      <c r="BT2">
+        <v>6.2</v>
+      </c>
+      <c r="BU2">
+        <v>5.4</v>
+      </c>
+      <c r="BV2">
+        <v>18.5</v>
+      </c>
+      <c r="BW2">
+        <v>9</v>
+      </c>
+      <c r="BX2">
         <v>27</v>
       </c>
-      <c r="AP2">
-        <v>12</v>
-      </c>
-      <c r="AQ2">
-        <v>12</v>
-      </c>
-      <c r="AR2">
-        <v>12</v>
-      </c>
-      <c r="AS2">
-        <v>12</v>
-      </c>
-      <c r="AT2">
-        <v>12</v>
-      </c>
-      <c r="AU2">
-        <v>12</v>
-      </c>
-      <c r="AV2">
-        <v>12</v>
-      </c>
-      <c r="AW2">
-        <v>12</v>
-      </c>
-      <c r="AX2">
-        <v>8.4</v>
-      </c>
-      <c r="AY2">
-        <v>3.4</v>
-      </c>
-      <c r="AZ2">
-        <v>3.4</v>
-      </c>
-      <c r="BA2">
-        <v>6.4</v>
-      </c>
-      <c r="BB2">
-        <v>12</v>
-      </c>
-      <c r="BC2">
-        <v>10</v>
-      </c>
-      <c r="BD2">
+      <c r="BY2">
         <v>10.5</v>
-      </c>
-      <c r="BE2">
-        <v>25</v>
-      </c>
-      <c r="BF2">
-        <v>22</v>
-      </c>
-      <c r="BG2">
-        <v>18</v>
-      </c>
-      <c r="BH2">
-        <v>0</v>
-      </c>
-      <c r="BI2">
-        <v>0</v>
-      </c>
-      <c r="BJ2">
-        <v>0</v>
-      </c>
-      <c r="BK2">
-        <v>0</v>
-      </c>
-      <c r="BL2">
-        <v>0</v>
-      </c>
-      <c r="BM2">
-        <v>0</v>
-      </c>
-      <c r="BN2">
-        <v>0</v>
-      </c>
-      <c r="BO2">
-        <v>0</v>
-      </c>
-      <c r="BP2">
-        <v>0</v>
-      </c>
-      <c r="BQ2">
-        <v>0</v>
-      </c>
-      <c r="BR2">
-        <v>0</v>
-      </c>
-      <c r="BS2">
-        <v>0</v>
-      </c>
-      <c r="BT2">
-        <v>0</v>
-      </c>
-      <c r="BU2">
-        <v>0</v>
-      </c>
-      <c r="BV2">
-        <v>0</v>
-      </c>
-      <c r="BW2">
-        <v>0</v>
-      </c>
-      <c r="BX2">
-        <v>0</v>
-      </c>
-      <c r="BY2">
-        <v>0</v>
       </c>
       <c r="BZ2">
         <v>0</v>
@@ -1165,7 +1153,7 @@
         <v>0</v>
       </c>
       <c r="CB2" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
     </row>
     <row r="3" spans="1:80">
@@ -1173,778 +1161,778 @@
         <v>81</v>
       </c>
       <c r="B3" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="C3" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="D3" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="E3" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="F3">
+        <v>3</v>
+      </c>
+      <c r="G3">
+        <v>3.2</v>
+      </c>
+      <c r="H3">
+        <v>2.94</v>
+      </c>
+      <c r="I3">
+        <v>3.15</v>
+      </c>
+      <c r="J3">
+        <v>2.8</v>
+      </c>
+      <c r="K3">
+        <v>2.96</v>
+      </c>
+      <c r="L3">
+        <v>1.66</v>
+      </c>
+      <c r="M3">
+        <v>1.16</v>
+      </c>
+      <c r="N3">
+        <v>2.4</v>
+      </c>
+      <c r="O3">
+        <v>1.7</v>
+      </c>
+      <c r="P3">
+        <v>1.45</v>
+      </c>
+      <c r="Q3">
+        <v>2.96</v>
+      </c>
+      <c r="R3">
+        <v>1.15</v>
+      </c>
+      <c r="S3">
+        <v>6.8</v>
+      </c>
+      <c r="T3">
+        <v>2.24</v>
+      </c>
+      <c r="U3">
+        <v>1.67</v>
+      </c>
+      <c r="V3">
+        <v>1.47</v>
+      </c>
+      <c r="W3">
+        <v>1.46</v>
+      </c>
+      <c r="X3">
+        <v>7.8</v>
+      </c>
+      <c r="Y3">
+        <v>8</v>
+      </c>
+      <c r="Z3">
+        <v>19</v>
+      </c>
+      <c r="AA3">
+        <v>90</v>
+      </c>
+      <c r="AB3">
+        <v>8</v>
+      </c>
+      <c r="AC3">
+        <v>7.4</v>
+      </c>
+      <c r="AD3">
+        <v>15.5</v>
+      </c>
+      <c r="AE3">
+        <v>55</v>
+      </c>
+      <c r="AF3">
+        <v>19.5</v>
+      </c>
+      <c r="AG3">
+        <v>16</v>
+      </c>
+      <c r="AH3">
+        <v>27</v>
+      </c>
+      <c r="AI3">
+        <v>200</v>
+      </c>
+      <c r="AJ3">
+        <v>150</v>
+      </c>
+      <c r="AK3">
+        <v>85</v>
+      </c>
+      <c r="AL3">
+        <v>460</v>
+      </c>
+      <c r="AM3">
+        <v>500</v>
+      </c>
+      <c r="AN3">
+        <v>210</v>
+      </c>
+      <c r="AO3">
+        <v>70</v>
+      </c>
+      <c r="AP3">
+        <v>6.4</v>
+      </c>
+      <c r="AQ3">
+        <v>6.8</v>
+      </c>
+      <c r="AR3">
+        <v>16</v>
+      </c>
+      <c r="AS3">
+        <v>20</v>
+      </c>
+      <c r="AT3">
+        <v>6.6</v>
+      </c>
+      <c r="AU3">
+        <v>6.2</v>
+      </c>
+      <c r="AV3">
+        <v>12.5</v>
+      </c>
+      <c r="AW3">
+        <v>20</v>
+      </c>
+      <c r="AX3">
+        <v>16.5</v>
+      </c>
+      <c r="AY3">
+        <v>13</v>
+      </c>
+      <c r="AZ3">
+        <v>15</v>
+      </c>
+      <c r="BA3">
+        <v>9.4</v>
+      </c>
+      <c r="BB3">
+        <v>18</v>
+      </c>
+      <c r="BC3">
+        <v>20</v>
+      </c>
+      <c r="BD3">
+        <v>9.4</v>
+      </c>
+      <c r="BE3">
+        <v>10</v>
+      </c>
+      <c r="BF3">
+        <v>11.5</v>
+      </c>
+      <c r="BG3">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="BH3">
         <v>2.58</v>
       </c>
-      <c r="G3">
-        <v>2.6</v>
-      </c>
-      <c r="H3">
-        <v>2.74</v>
-      </c>
-      <c r="I3">
-        <v>2.78</v>
-      </c>
-      <c r="J3">
-        <v>3.9</v>
-      </c>
-      <c r="K3">
-        <v>4</v>
-      </c>
-      <c r="L3">
-        <v>1.33</v>
-      </c>
-      <c r="M3">
-        <v>1.05</v>
-      </c>
-      <c r="N3">
-        <v>5.1</v>
-      </c>
-      <c r="O3">
-        <v>1.23</v>
-      </c>
-      <c r="P3">
-        <v>2.38</v>
-      </c>
-      <c r="Q3">
-        <v>1.69</v>
-      </c>
-      <c r="R3">
-        <v>1.56</v>
-      </c>
-      <c r="S3">
-        <v>2.74</v>
-      </c>
-      <c r="T3">
-        <v>1.63</v>
-      </c>
-      <c r="U3">
-        <v>2.46</v>
-      </c>
-      <c r="V3">
-        <v>1.56</v>
-      </c>
-      <c r="W3">
-        <v>1.62</v>
-      </c>
-      <c r="X3">
-        <v>21</v>
-      </c>
-      <c r="Y3">
-        <v>14.5</v>
-      </c>
-      <c r="Z3">
-        <v>21</v>
-      </c>
-      <c r="AA3">
-        <v>40</v>
-      </c>
-      <c r="AB3">
-        <v>14.5</v>
-      </c>
-      <c r="AC3">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AD3">
-        <v>12.5</v>
-      </c>
-      <c r="AE3">
-        <v>27</v>
-      </c>
-      <c r="AF3">
-        <v>19</v>
-      </c>
-      <c r="AG3">
-        <v>12.5</v>
-      </c>
-      <c r="AH3">
-        <v>15.5</v>
-      </c>
-      <c r="AI3">
-        <v>30</v>
-      </c>
-      <c r="AJ3">
-        <v>38</v>
-      </c>
-      <c r="AK3">
-        <v>26</v>
-      </c>
-      <c r="AL3">
-        <v>32</v>
-      </c>
-      <c r="AM3">
-        <v>60</v>
-      </c>
-      <c r="AN3">
-        <v>16</v>
-      </c>
-      <c r="AO3">
-        <v>17</v>
-      </c>
-      <c r="AP3">
-        <v>19</v>
-      </c>
-      <c r="AQ3">
-        <v>13</v>
-      </c>
-      <c r="AR3">
-        <v>18</v>
-      </c>
-      <c r="AS3">
-        <v>34</v>
-      </c>
-      <c r="AT3">
+      <c r="BI3">
+        <v>2.2</v>
+      </c>
+      <c r="BJ3">
+        <v>12</v>
+      </c>
+      <c r="BK3">
+        <v>6.6</v>
+      </c>
+      <c r="BL3">
+        <v>1000</v>
+      </c>
+      <c r="BM3">
         <v>14</v>
-      </c>
-      <c r="AU3">
-        <v>8.4</v>
-      </c>
-      <c r="AV3">
-        <v>11.5</v>
-      </c>
-      <c r="AW3">
-        <v>24</v>
-      </c>
-      <c r="AX3">
-        <v>18.5</v>
-      </c>
-      <c r="AY3">
-        <v>11.5</v>
-      </c>
-      <c r="AZ3">
-        <v>13.5</v>
-      </c>
-      <c r="BA3">
-        <v>29</v>
-      </c>
-      <c r="BB3">
-        <v>34</v>
-      </c>
-      <c r="BC3">
-        <v>22</v>
-      </c>
-      <c r="BD3">
-        <v>29</v>
-      </c>
-      <c r="BE3">
-        <v>50</v>
-      </c>
-      <c r="BF3">
-        <v>14.5</v>
-      </c>
-      <c r="BG3">
-        <v>16</v>
-      </c>
-      <c r="BH3">
-        <v>4.1</v>
-      </c>
-      <c r="BI3">
-        <v>3.75</v>
-      </c>
-      <c r="BJ3">
-        <v>8.6</v>
-      </c>
-      <c r="BK3">
-        <v>7.6</v>
-      </c>
-      <c r="BL3">
-        <v>80</v>
-      </c>
-      <c r="BM3">
-        <v>14.5</v>
       </c>
       <c r="BN3">
         <v>5.9</v>
       </c>
       <c r="BO3">
-        <v>5.3</v>
+        <v>5</v>
       </c>
       <c r="BP3">
-        <v>17.5</v>
+        <v>30</v>
       </c>
       <c r="BQ3">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="BR3">
-        <v>26</v>
+        <v>60</v>
       </c>
       <c r="BS3">
-        <v>18.5</v>
+        <v>12</v>
       </c>
       <c r="BT3">
-        <v>6.2</v>
+        <v>5.9</v>
       </c>
       <c r="BU3">
-        <v>5.5</v>
+        <v>4.9</v>
       </c>
       <c r="BV3">
-        <v>19</v>
+        <v>29</v>
       </c>
       <c r="BW3">
-        <v>14</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BX3">
-        <v>27</v>
+        <v>1000</v>
       </c>
       <c r="BY3">
-        <v>20</v>
+        <v>11.5</v>
       </c>
       <c r="BZ3">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA3">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="CB3" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
     </row>
     <row r="4" spans="1:80">
       <c r="A4" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B4" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="C4" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="D4" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="E4" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="F4">
-        <v>2.9</v>
+        <v>7.2</v>
       </c>
       <c r="G4">
-        <v>3.15</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="H4">
-        <v>2.98</v>
+        <v>1.57</v>
       </c>
       <c r="I4">
-        <v>3.25</v>
+        <v>1.62</v>
       </c>
       <c r="J4">
-        <v>2.8</v>
+        <v>4.1</v>
       </c>
       <c r="K4">
-        <v>2.98</v>
+        <v>4.3</v>
       </c>
       <c r="L4">
-        <v>1.66</v>
+        <v>1.45</v>
       </c>
       <c r="M4">
-        <v>1.16</v>
+        <v>1.08</v>
       </c>
       <c r="N4">
-        <v>2.38</v>
+        <v>3.3</v>
       </c>
       <c r="O4">
-        <v>1.7</v>
+        <v>1.4</v>
       </c>
       <c r="P4">
-        <v>1.44</v>
+        <v>1.81</v>
       </c>
       <c r="Q4">
-        <v>3</v>
+        <v>2.16</v>
       </c>
       <c r="R4">
-        <v>1.15</v>
+        <v>1.28</v>
       </c>
       <c r="S4">
-        <v>6.6</v>
+        <v>4.1</v>
       </c>
       <c r="T4">
-        <v>2.3</v>
+        <v>2.18</v>
       </c>
       <c r="U4">
-        <v>1.67</v>
+        <v>1.75</v>
       </c>
       <c r="V4">
-        <v>1.45</v>
+        <v>2.6</v>
       </c>
       <c r="W4">
-        <v>1.47</v>
+        <v>1.14</v>
       </c>
       <c r="X4">
-        <v>7.4</v>
+        <v>15.5</v>
       </c>
       <c r="Y4">
-        <v>8</v>
+        <v>6.8</v>
       </c>
       <c r="Z4">
-        <v>19.5</v>
+        <v>8.4</v>
       </c>
       <c r="AA4">
-        <v>95</v>
+        <v>15.5</v>
       </c>
       <c r="AB4">
-        <v>8</v>
+        <v>32</v>
       </c>
       <c r="AC4">
-        <v>7.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AD4">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="AE4">
-        <v>90</v>
+        <v>23</v>
       </c>
       <c r="AF4">
-        <v>19</v>
+        <v>160</v>
       </c>
       <c r="AG4">
-        <v>16</v>
+        <v>46</v>
       </c>
       <c r="AH4">
-        <v>27</v>
+        <v>36</v>
       </c>
       <c r="AI4">
-        <v>200</v>
+        <v>120</v>
       </c>
       <c r="AJ4">
-        <v>65</v>
+        <v>700</v>
       </c>
       <c r="AK4">
-        <v>55</v>
+        <v>700</v>
       </c>
       <c r="AL4">
-        <v>230</v>
+        <v>700</v>
       </c>
       <c r="AM4">
-        <v>500</v>
+        <v>700</v>
       </c>
       <c r="AN4">
-        <v>75</v>
+        <v>280</v>
       </c>
       <c r="AO4">
-        <v>95</v>
+        <v>11.5</v>
       </c>
       <c r="AP4">
-        <v>6.2</v>
+        <v>11</v>
       </c>
       <c r="AQ4">
-        <v>6.6</v>
+        <v>5.9</v>
       </c>
       <c r="AR4">
-        <v>16.5</v>
+        <v>7.2</v>
       </c>
       <c r="AS4">
+        <v>13</v>
+      </c>
+      <c r="AT4">
+        <v>17</v>
+      </c>
+      <c r="AU4">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AV4">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AW4">
+        <v>11</v>
+      </c>
+      <c r="AX4">
         <v>20</v>
       </c>
-      <c r="AT4">
-        <v>6.6</v>
-      </c>
-      <c r="AU4">
-        <v>6.2</v>
-      </c>
-      <c r="AV4">
-        <v>13.5</v>
-      </c>
-      <c r="AW4">
+      <c r="AY4">
+        <v>15</v>
+      </c>
+      <c r="AZ4">
         <v>23</v>
       </c>
-      <c r="AX4">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AY4">
-        <v>13</v>
-      </c>
-      <c r="AZ4">
-        <v>15</v>
-      </c>
       <c r="BA4">
-        <v>9.6</v>
+        <v>24</v>
       </c>
       <c r="BB4">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="BC4">
-        <v>22</v>
+        <v>10</v>
       </c>
       <c r="BD4">
-        <v>9.6</v>
+        <v>10</v>
       </c>
       <c r="BE4">
         <v>10</v>
       </c>
       <c r="BF4">
-        <v>11.5</v>
+        <v>10</v>
       </c>
       <c r="BG4">
-        <v>38</v>
+        <v>10</v>
       </c>
       <c r="BH4">
-        <v>2.64</v>
+        <v>3.65</v>
       </c>
       <c r="BI4">
-        <v>2.12</v>
+        <v>2.58</v>
       </c>
       <c r="BJ4">
-        <v>12.5</v>
+        <v>14.5</v>
       </c>
       <c r="BK4">
-        <v>5.7</v>
+        <v>3.75</v>
       </c>
       <c r="BL4">
         <v>1000</v>
       </c>
       <c r="BM4">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="BN4">
-        <v>5.9</v>
+        <v>13</v>
       </c>
       <c r="BO4">
+        <v>3.65</v>
+      </c>
+      <c r="BP4">
+        <v>1000</v>
+      </c>
+      <c r="BQ4">
+        <v>4.8</v>
+      </c>
+      <c r="BR4">
+        <v>1000</v>
+      </c>
+      <c r="BS4">
+        <v>4.8</v>
+      </c>
+      <c r="BT4">
+        <v>4.5</v>
+      </c>
+      <c r="BU4">
+        <v>3.05</v>
+      </c>
+      <c r="BV4">
+        <v>13</v>
+      </c>
+      <c r="BW4">
+        <v>3.65</v>
+      </c>
+      <c r="BX4">
+        <v>38</v>
+      </c>
+      <c r="BY4">
+        <v>4.5</v>
+      </c>
+      <c r="BZ4">
+        <v>28</v>
+      </c>
+      <c r="CA4">
         <v>4.3</v>
       </c>
-      <c r="BP4">
-        <v>30</v>
-      </c>
-      <c r="BQ4">
-        <v>7.8</v>
-      </c>
-      <c r="BR4">
-        <v>60</v>
-      </c>
-      <c r="BS4">
-        <v>9</v>
-      </c>
-      <c r="BT4">
-        <v>6.2</v>
-      </c>
-      <c r="BU4">
-        <v>4.4</v>
-      </c>
-      <c r="BV4">
-        <v>32</v>
-      </c>
-      <c r="BW4">
-        <v>8</v>
-      </c>
-      <c r="BX4">
-        <v>60</v>
-      </c>
-      <c r="BY4">
-        <v>9</v>
-      </c>
-      <c r="BZ4">
-        <v>65</v>
-      </c>
-      <c r="CA4">
-        <v>9.199999999999999</v>
-      </c>
       <c r="CB4" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
     </row>
     <row r="5" spans="1:80">
       <c r="A5" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B5" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="C5" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="D5" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="E5" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="F5">
+        <v>2.56</v>
+      </c>
+      <c r="G5">
+        <v>2.68</v>
+      </c>
+      <c r="H5">
+        <v>3.5</v>
+      </c>
+      <c r="I5">
+        <v>3.75</v>
+      </c>
+      <c r="J5">
+        <v>2.9</v>
+      </c>
+      <c r="K5">
+        <v>2.92</v>
+      </c>
+      <c r="L5">
+        <v>1.73</v>
+      </c>
+      <c r="M5">
+        <v>1.18</v>
+      </c>
+      <c r="N5">
+        <v>2.2</v>
+      </c>
+      <c r="O5">
+        <v>1.78</v>
+      </c>
+      <c r="P5">
+        <v>1.37</v>
+      </c>
+      <c r="Q5">
+        <v>3.35</v>
+      </c>
+      <c r="R5">
+        <v>1.13</v>
+      </c>
+      <c r="S5">
+        <v>8</v>
+      </c>
+      <c r="T5">
+        <v>2.44</v>
+      </c>
+      <c r="U5">
+        <v>1.6</v>
+      </c>
+      <c r="V5">
+        <v>1.36</v>
+      </c>
+      <c r="W5">
+        <v>1.59</v>
+      </c>
+      <c r="X5">
+        <v>7.8</v>
+      </c>
+      <c r="Y5">
+        <v>8.6</v>
+      </c>
+      <c r="Z5">
+        <v>36</v>
+      </c>
+      <c r="AA5">
+        <v>230</v>
+      </c>
+      <c r="AB5">
+        <v>6.8</v>
+      </c>
+      <c r="AC5">
         <v>7.2</v>
       </c>
-      <c r="G5">
-        <v>7.8</v>
-      </c>
-      <c r="H5">
-        <v>1.6</v>
-      </c>
-      <c r="I5">
-        <v>1.61</v>
-      </c>
-      <c r="J5">
-        <v>4.2</v>
-      </c>
-      <c r="K5">
-        <v>4.3</v>
-      </c>
-      <c r="L5">
-        <v>1.45</v>
-      </c>
-      <c r="M5">
-        <v>1.08</v>
-      </c>
-      <c r="N5">
-        <v>3.3</v>
-      </c>
-      <c r="O5">
-        <v>1.39</v>
-      </c>
-      <c r="P5">
-        <v>1.78</v>
-      </c>
-      <c r="Q5">
-        <v>2.18</v>
-      </c>
-      <c r="R5">
-        <v>1.28</v>
-      </c>
-      <c r="S5">
-        <v>4.1</v>
-      </c>
-      <c r="T5">
-        <v>2.18</v>
-      </c>
-      <c r="U5">
-        <v>1.74</v>
-      </c>
-      <c r="V5">
-        <v>2.64</v>
-      </c>
-      <c r="W5">
-        <v>1.15</v>
-      </c>
-      <c r="X5">
-        <v>13.5</v>
-      </c>
-      <c r="Y5">
-        <v>6.8</v>
-      </c>
-      <c r="Z5">
-        <v>8.4</v>
-      </c>
-      <c r="AA5">
+      <c r="AD5">
+        <v>20</v>
+      </c>
+      <c r="AE5">
+        <v>90</v>
+      </c>
+      <c r="AF5">
         <v>15.5</v>
       </c>
-      <c r="AB5">
-        <v>32</v>
-      </c>
-      <c r="AC5">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AD5">
+      <c r="AG5">
+        <v>15</v>
+      </c>
+      <c r="AH5">
+        <v>34</v>
+      </c>
+      <c r="AI5">
+        <v>540</v>
+      </c>
+      <c r="AJ5">
+        <v>60</v>
+      </c>
+      <c r="AK5">
+        <v>60</v>
+      </c>
+      <c r="AL5">
+        <v>230</v>
+      </c>
+      <c r="AM5">
+        <v>500</v>
+      </c>
+      <c r="AN5">
+        <v>75</v>
+      </c>
+      <c r="AO5">
+        <v>150</v>
+      </c>
+      <c r="AP5">
+        <v>5.7</v>
+      </c>
+      <c r="AQ5">
+        <v>7.4</v>
+      </c>
+      <c r="AR5">
         <v>10.5</v>
       </c>
-      <c r="AE5">
+      <c r="AS5">
+        <v>20</v>
+      </c>
+      <c r="AT5">
+        <v>5.9</v>
+      </c>
+      <c r="AU5">
+        <v>6</v>
+      </c>
+      <c r="AV5">
+        <v>15.5</v>
+      </c>
+      <c r="AW5">
         <v>23</v>
       </c>
-      <c r="AF5">
-        <v>160</v>
-      </c>
-      <c r="AG5">
-        <v>38</v>
-      </c>
-      <c r="AH5">
-        <v>36</v>
-      </c>
-      <c r="AI5">
-        <v>120</v>
-      </c>
-      <c r="AJ5">
-        <v>700</v>
-      </c>
-      <c r="AK5">
-        <v>700</v>
-      </c>
-      <c r="AL5">
-        <v>700</v>
-      </c>
-      <c r="AM5">
-        <v>700</v>
-      </c>
-      <c r="AN5">
-        <v>280</v>
-      </c>
-      <c r="AO5">
-        <v>12</v>
-      </c>
-      <c r="AP5">
-        <v>11</v>
-      </c>
-      <c r="AQ5">
-        <v>5.9</v>
-      </c>
-      <c r="AR5">
-        <v>7.2</v>
-      </c>
-      <c r="AS5">
+      <c r="AX5">
         <v>13</v>
       </c>
-      <c r="AT5">
-        <v>17</v>
-      </c>
-      <c r="AU5">
-        <v>8</v>
-      </c>
-      <c r="AV5">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AW5">
-        <v>11</v>
-      </c>
-      <c r="AX5">
-        <v>20</v>
-      </c>
       <c r="AY5">
-        <v>14.5</v>
+        <v>12.5</v>
       </c>
       <c r="AZ5">
         <v>23</v>
       </c>
       <c r="BA5">
-        <v>24</v>
+        <v>7.8</v>
       </c>
       <c r="BB5">
-        <v>9.199999999999999</v>
+        <v>19.5</v>
       </c>
       <c r="BC5">
-        <v>9</v>
+        <v>32</v>
       </c>
       <c r="BD5">
-        <v>9</v>
+        <v>7.6</v>
       </c>
       <c r="BE5">
-        <v>9.199999999999999</v>
+        <v>7.8</v>
       </c>
       <c r="BF5">
-        <v>9.199999999999999</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BG5">
-        <v>10</v>
+        <v>7.6</v>
       </c>
       <c r="BH5">
-        <v>3.65</v>
+        <v>2.64</v>
       </c>
       <c r="BI5">
-        <v>2.56</v>
+        <v>2.02</v>
       </c>
       <c r="BJ5">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="BK5">
-        <v>3.75</v>
+        <v>4.5</v>
       </c>
       <c r="BL5">
         <v>1000</v>
       </c>
       <c r="BM5">
-        <v>4.9</v>
+        <v>6.4</v>
       </c>
       <c r="BN5">
-        <v>13</v>
+        <v>6.2</v>
       </c>
       <c r="BO5">
-        <v>3.65</v>
+        <v>4</v>
       </c>
       <c r="BP5">
+        <v>32</v>
+      </c>
+      <c r="BQ5">
+        <v>5.4</v>
+      </c>
+      <c r="BR5">
+        <v>70</v>
+      </c>
+      <c r="BS5">
+        <v>5.9</v>
+      </c>
+      <c r="BT5">
+        <v>6.8</v>
+      </c>
+      <c r="BU5">
+        <v>5</v>
+      </c>
+      <c r="BV5">
+        <v>48</v>
+      </c>
+      <c r="BW5">
+        <v>5.7</v>
+      </c>
+      <c r="BX5">
         <v>1000</v>
       </c>
-      <c r="BQ5">
-        <v>4.8</v>
-      </c>
-      <c r="BR5">
-        <v>1000</v>
-      </c>
-      <c r="BS5">
-        <v>4.8</v>
-      </c>
-      <c r="BT5">
-        <v>4.5</v>
-      </c>
-      <c r="BU5">
-        <v>3.05</v>
-      </c>
-      <c r="BV5">
-        <v>13</v>
-      </c>
-      <c r="BW5">
-        <v>3.65</v>
-      </c>
-      <c r="BX5">
-        <v>38</v>
-      </c>
       <c r="BY5">
-        <v>4.4</v>
+        <v>6</v>
       </c>
       <c r="BZ5">
-        <v>29</v>
+        <v>85</v>
       </c>
       <c r="CA5">
-        <v>4.3</v>
+        <v>6</v>
       </c>
       <c r="CB5" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
     </row>
     <row r="6" spans="1:80">
       <c r="A6" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B6" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="C6" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="D6" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="E6" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="F6">
-        <v>2.56</v>
+        <v>2.5</v>
       </c>
       <c r="G6">
-        <v>2.72</v>
+        <v>2.68</v>
       </c>
       <c r="H6">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="I6">
-        <v>3.8</v>
+        <v>3.95</v>
       </c>
       <c r="J6">
-        <v>2.9</v>
+        <v>2.88</v>
       </c>
       <c r="K6">
-        <v>2.96</v>
+        <v>2.94</v>
       </c>
       <c r="L6">
-        <v>1.73</v>
+        <v>1.72</v>
       </c>
       <c r="M6">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="N6">
-        <v>2.22</v>
+        <v>2.24</v>
       </c>
       <c r="O6">
-        <v>1.75</v>
+        <v>1.72</v>
       </c>
       <c r="P6">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="Q6">
-        <v>3.35</v>
+        <v>3.25</v>
       </c>
       <c r="R6">
         <v>1.13</v>
@@ -1953,58 +1941,58 @@
         <v>7.6</v>
       </c>
       <c r="T6">
-        <v>2.44</v>
+        <v>2.38</v>
       </c>
       <c r="U6">
-        <v>1.59</v>
+        <v>1.6</v>
       </c>
       <c r="V6">
-        <v>1.36</v>
+        <v>1.34</v>
       </c>
       <c r="W6">
-        <v>1.58</v>
+        <v>1.6</v>
       </c>
       <c r="X6">
-        <v>7.6</v>
+        <v>6.8</v>
       </c>
       <c r="Y6">
-        <v>8.6</v>
+        <v>9</v>
       </c>
       <c r="Z6">
         <v>25</v>
       </c>
       <c r="AA6">
-        <v>230</v>
+        <v>500</v>
       </c>
       <c r="AB6">
         <v>6.8</v>
       </c>
       <c r="AC6">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="AD6">
         <v>19</v>
       </c>
       <c r="AE6">
-        <v>95</v>
+        <v>230</v>
       </c>
       <c r="AF6">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AG6">
-        <v>15.5</v>
+        <v>14.5</v>
       </c>
       <c r="AH6">
-        <v>40</v>
+        <v>32</v>
       </c>
       <c r="AI6">
         <v>540</v>
       </c>
       <c r="AJ6">
-        <v>60</v>
+        <v>120</v>
       </c>
       <c r="AK6">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="AL6">
         <v>230</v>
@@ -2016,124 +2004,124 @@
         <v>80</v>
       </c>
       <c r="AO6">
-        <v>160</v>
+        <v>600</v>
       </c>
       <c r="AP6">
-        <v>5.5</v>
+        <v>5.7</v>
       </c>
       <c r="AQ6">
-        <v>7.2</v>
+        <v>7.6</v>
       </c>
       <c r="AR6">
-        <v>15.5</v>
+        <v>20</v>
       </c>
       <c r="AS6">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="AT6">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="AU6">
         <v>6</v>
       </c>
       <c r="AV6">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="AW6">
-        <v>46</v>
+        <v>23</v>
       </c>
       <c r="AX6">
+        <v>12.5</v>
+      </c>
+      <c r="AY6">
+        <v>11.5</v>
+      </c>
+      <c r="AZ6">
+        <v>24</v>
+      </c>
+      <c r="BA6">
+        <v>29</v>
+      </c>
+      <c r="BB6">
+        <v>18.5</v>
+      </c>
+      <c r="BC6">
+        <v>18.5</v>
+      </c>
+      <c r="BD6">
+        <v>10</v>
+      </c>
+      <c r="BE6">
+        <v>11</v>
+      </c>
+      <c r="BF6">
+        <v>9.6</v>
+      </c>
+      <c r="BG6">
+        <v>10.5</v>
+      </c>
+      <c r="BH6">
+        <v>2.42</v>
+      </c>
+      <c r="BI6">
+        <v>2.08</v>
+      </c>
+      <c r="BJ6">
         <v>13</v>
       </c>
-      <c r="AY6">
-        <v>12.5</v>
-      </c>
-      <c r="AZ6">
-        <v>23</v>
-      </c>
-      <c r="BA6">
-        <v>7.8</v>
-      </c>
-      <c r="BB6">
-        <v>30</v>
-      </c>
-      <c r="BC6">
-        <v>30</v>
-      </c>
-      <c r="BD6">
-        <v>28</v>
-      </c>
-      <c r="BE6">
-        <v>7.8</v>
-      </c>
-      <c r="BF6">
-        <v>40</v>
-      </c>
-      <c r="BG6">
-        <v>7.4</v>
-      </c>
-      <c r="BH6">
-        <v>2.7</v>
-      </c>
-      <c r="BI6">
-        <v>1.99</v>
-      </c>
-      <c r="BJ6">
-        <v>15.5</v>
-      </c>
       <c r="BK6">
-        <v>3.95</v>
+        <v>7</v>
       </c>
       <c r="BL6">
         <v>1000</v>
       </c>
       <c r="BM6">
-        <v>5.2</v>
+        <v>2.08</v>
       </c>
       <c r="BN6">
-        <v>6.2</v>
+        <v>5.3</v>
       </c>
       <c r="BO6">
         <v>4</v>
       </c>
       <c r="BP6">
-        <v>32</v>
+        <v>1000</v>
       </c>
       <c r="BQ6">
-        <v>4.6</v>
+        <v>9.6</v>
       </c>
       <c r="BR6">
-        <v>75</v>
+        <v>1000</v>
       </c>
       <c r="BS6">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="BT6">
-        <v>7.8</v>
+        <v>6.8</v>
       </c>
       <c r="BU6">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="BV6">
-        <v>50</v>
+        <v>1000</v>
       </c>
       <c r="BW6">
-        <v>4.8</v>
+        <v>11</v>
       </c>
       <c r="BX6">
         <v>1000</v>
       </c>
       <c r="BY6">
-        <v>5</v>
+        <v>12.5</v>
       </c>
       <c r="BZ6">
         <v>1000</v>
       </c>
       <c r="CA6">
-        <v>5</v>
+        <v>12.5</v>
       </c>
       <c r="CB6" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
     </row>
     <row r="7" spans="1:80">
@@ -2141,241 +2129,241 @@
         <v>82</v>
       </c>
       <c r="B7" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="C7" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="D7" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="E7" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
       <c r="F7">
-        <v>2.54</v>
+        <v>1.76</v>
       </c>
       <c r="G7">
-        <v>2.58</v>
+        <v>1.78</v>
       </c>
       <c r="H7">
+        <v>6</v>
+      </c>
+      <c r="I7">
+        <v>6.2</v>
+      </c>
+      <c r="J7">
         <v>3.6</v>
       </c>
-      <c r="I7">
-        <v>3.75</v>
-      </c>
-      <c r="J7">
-        <v>2.96</v>
-      </c>
       <c r="K7">
-        <v>2.98</v>
+        <v>3.7</v>
       </c>
       <c r="L7">
-        <v>1.7</v>
+        <v>1.57</v>
       </c>
       <c r="M7">
-        <v>1.16</v>
+        <v>1.12</v>
       </c>
       <c r="N7">
-        <v>2.34</v>
+        <v>2.84</v>
       </c>
       <c r="O7">
-        <v>1.68</v>
+        <v>1.53</v>
       </c>
       <c r="P7">
-        <v>1.44</v>
+        <v>1.61</v>
       </c>
       <c r="Q7">
-        <v>3.15</v>
+        <v>2.6</v>
       </c>
       <c r="R7">
-        <v>1.15</v>
+        <v>1.22</v>
       </c>
       <c r="S7">
-        <v>7</v>
+        <v>5.4</v>
       </c>
       <c r="T7">
         <v>2.32</v>
       </c>
       <c r="U7">
-        <v>1.64</v>
+        <v>1.69</v>
       </c>
       <c r="V7">
-        <v>1.36</v>
+        <v>1.19</v>
       </c>
       <c r="W7">
-        <v>1.63</v>
+        <v>2.28</v>
       </c>
       <c r="X7">
-        <v>7.2</v>
+        <v>9.6</v>
       </c>
       <c r="Y7">
-        <v>9.4</v>
+        <v>14.5</v>
       </c>
       <c r="Z7">
+        <v>50</v>
+      </c>
+      <c r="AA7">
+        <v>200</v>
+      </c>
+      <c r="AB7">
+        <v>5.9</v>
+      </c>
+      <c r="AC7">
+        <v>8</v>
+      </c>
+      <c r="AD7">
         <v>25</v>
-      </c>
-      <c r="AA7">
-        <v>500</v>
-      </c>
-      <c r="AB7">
-        <v>7</v>
-      </c>
-      <c r="AC7">
-        <v>7.2</v>
-      </c>
-      <c r="AD7">
-        <v>18.5</v>
       </c>
       <c r="AE7">
         <v>260</v>
       </c>
       <c r="AF7">
-        <v>15</v>
+        <v>8.6</v>
       </c>
       <c r="AG7">
+        <v>11</v>
+      </c>
+      <c r="AH7">
+        <v>32</v>
+      </c>
+      <c r="AI7">
+        <v>140</v>
+      </c>
+      <c r="AJ7">
+        <v>18.5</v>
+      </c>
+      <c r="AK7">
+        <v>23</v>
+      </c>
+      <c r="AL7">
+        <v>60</v>
+      </c>
+      <c r="AM7">
+        <v>250</v>
+      </c>
+      <c r="AN7">
+        <v>17.5</v>
+      </c>
+      <c r="AO7">
+        <v>700</v>
+      </c>
+      <c r="AP7">
+        <v>9</v>
+      </c>
+      <c r="AQ7">
         <v>14</v>
       </c>
-      <c r="AH7">
-        <v>48</v>
-      </c>
-      <c r="AI7">
-        <v>540</v>
-      </c>
-      <c r="AJ7">
-        <v>120</v>
-      </c>
-      <c r="AK7">
+      <c r="AR7">
+        <v>40</v>
+      </c>
+      <c r="AS7">
+        <v>27</v>
+      </c>
+      <c r="AT7">
+        <v>5.7</v>
+      </c>
+      <c r="AU7">
+        <v>7.8</v>
+      </c>
+      <c r="AV7">
+        <v>23</v>
+      </c>
+      <c r="AW7">
+        <v>95</v>
+      </c>
+      <c r="AX7">
+        <v>8.4</v>
+      </c>
+      <c r="AY7">
+        <v>10</v>
+      </c>
+      <c r="AZ7">
+        <v>27</v>
+      </c>
+      <c r="BA7">
+        <v>29</v>
+      </c>
+      <c r="BB7">
+        <v>17</v>
+      </c>
+      <c r="BC7">
+        <v>22</v>
+      </c>
+      <c r="BD7">
+        <v>50</v>
+      </c>
+      <c r="BE7">
         <v>150</v>
       </c>
-      <c r="AL7">
-        <v>230</v>
-      </c>
-      <c r="AM7">
-        <v>500</v>
-      </c>
-      <c r="AN7">
-        <v>75</v>
-      </c>
-      <c r="AO7">
-        <v>600</v>
-      </c>
-      <c r="AP7">
-        <v>6</v>
-      </c>
-      <c r="AQ7">
-        <v>7.8</v>
-      </c>
-      <c r="AR7">
-        <v>20</v>
-      </c>
-      <c r="AS7">
-        <v>10</v>
-      </c>
-      <c r="AT7">
-        <v>5.8</v>
-      </c>
-      <c r="AU7">
-        <v>6</v>
-      </c>
-      <c r="AV7">
-        <v>15</v>
-      </c>
-      <c r="AW7">
-        <v>23</v>
-      </c>
-      <c r="AX7">
+      <c r="BF7">
+        <v>16.5</v>
+      </c>
+      <c r="BG7">
+        <v>30</v>
+      </c>
+      <c r="BH7">
+        <v>2.8</v>
+      </c>
+      <c r="BI7">
+        <v>2.46</v>
+      </c>
+      <c r="BJ7">
         <v>12.5</v>
       </c>
-      <c r="AY7">
-        <v>11.5</v>
-      </c>
-      <c r="AZ7">
-        <v>15</v>
-      </c>
-      <c r="BA7">
-        <v>10</v>
-      </c>
-      <c r="BB7">
-        <v>19</v>
-      </c>
-      <c r="BC7">
-        <v>29</v>
-      </c>
-      <c r="BD7">
-        <v>10</v>
-      </c>
-      <c r="BE7">
-        <v>11</v>
-      </c>
-      <c r="BF7">
-        <v>9.4</v>
-      </c>
-      <c r="BG7">
-        <v>10</v>
-      </c>
-      <c r="BH7">
-        <v>2.48</v>
-      </c>
-      <c r="BI7">
-        <v>2.06</v>
-      </c>
-      <c r="BJ7">
-        <v>13</v>
-      </c>
       <c r="BK7">
-        <v>6.4</v>
+        <v>7.6</v>
       </c>
       <c r="BL7">
         <v>1000</v>
       </c>
       <c r="BM7">
-        <v>12</v>
+        <v>180</v>
       </c>
       <c r="BN7">
-        <v>5.3</v>
+        <v>4</v>
       </c>
       <c r="BO7">
-        <v>3.95</v>
+        <v>3.7</v>
       </c>
       <c r="BP7">
-        <v>1000</v>
+        <v>13</v>
       </c>
       <c r="BQ7">
-        <v>8.4</v>
+        <v>7.8</v>
       </c>
       <c r="BR7">
         <v>1000</v>
       </c>
       <c r="BS7">
-        <v>10.5</v>
+        <v>13</v>
       </c>
       <c r="BT7">
-        <v>7</v>
+        <v>9.6</v>
       </c>
       <c r="BU7">
-        <v>5</v>
+        <v>7.6</v>
       </c>
       <c r="BV7">
         <v>1000</v>
       </c>
       <c r="BW7">
-        <v>9.6</v>
+        <v>2.38</v>
       </c>
       <c r="BX7">
         <v>1000</v>
       </c>
       <c r="BY7">
-        <v>10.5</v>
+        <v>16.5</v>
       </c>
       <c r="BZ7">
         <v>1000</v>
       </c>
       <c r="CA7">
-        <v>10.5</v>
+        <v>13</v>
       </c>
       <c r="CB7" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
     </row>
     <row r="8" spans="1:80">
@@ -2383,241 +2371,241 @@
         <v>83</v>
       </c>
       <c r="B8" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="C8" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="D8" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="E8" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="F8">
-        <v>1.79</v>
+        <v>2.86</v>
       </c>
       <c r="G8">
-        <v>1.81</v>
+        <v>2.9</v>
       </c>
       <c r="H8">
-        <v>5.8</v>
+        <v>2.9</v>
       </c>
       <c r="I8">
-        <v>6.2</v>
+        <v>2.96</v>
       </c>
       <c r="J8">
-        <v>3.6</v>
+        <v>3.2</v>
       </c>
       <c r="K8">
-        <v>3.75</v>
+        <v>3.25</v>
       </c>
       <c r="L8">
-        <v>1.55</v>
+        <v>1.49</v>
       </c>
       <c r="M8">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="N8">
-        <v>2.84</v>
+        <v>3.15</v>
       </c>
       <c r="O8">
-        <v>1.53</v>
+        <v>1.43</v>
       </c>
       <c r="P8">
-        <v>1.6</v>
+        <v>1.72</v>
       </c>
       <c r="Q8">
-        <v>2.58</v>
+        <v>2.34</v>
       </c>
       <c r="R8">
-        <v>1.21</v>
+        <v>1.27</v>
       </c>
       <c r="S8">
-        <v>5.3</v>
+        <v>4.5</v>
       </c>
       <c r="T8">
-        <v>2.32</v>
+        <v>1.91</v>
       </c>
       <c r="U8">
-        <v>1.7</v>
+        <v>2</v>
       </c>
       <c r="V8">
-        <v>1.19</v>
+        <v>1.51</v>
       </c>
       <c r="W8">
-        <v>2.22</v>
+        <v>1.52</v>
       </c>
       <c r="X8">
+        <v>11</v>
+      </c>
+      <c r="Y8">
         <v>9.800000000000001</v>
       </c>
-      <c r="Y8">
-        <v>14.5</v>
-      </c>
       <c r="Z8">
-        <v>44</v>
+        <v>18.5</v>
       </c>
       <c r="AA8">
-        <v>200</v>
+        <v>48</v>
       </c>
       <c r="AB8">
-        <v>5.9</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AC8">
-        <v>8.199999999999999</v>
+        <v>7.4</v>
       </c>
       <c r="AD8">
-        <v>25</v>
+        <v>13</v>
       </c>
       <c r="AE8">
-        <v>700</v>
+        <v>38</v>
       </c>
       <c r="AF8">
-        <v>8.800000000000001</v>
+        <v>18</v>
       </c>
       <c r="AG8">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="AH8">
-        <v>29</v>
+        <v>19.5</v>
       </c>
       <c r="AI8">
-        <v>700</v>
+        <v>55</v>
       </c>
       <c r="AJ8">
-        <v>20</v>
+        <v>48</v>
       </c>
       <c r="AK8">
-        <v>23</v>
+        <v>38</v>
       </c>
       <c r="AL8">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AM8">
-        <v>250</v>
+        <v>130</v>
       </c>
       <c r="AN8">
-        <v>19</v>
+        <v>38</v>
       </c>
       <c r="AO8">
-        <v>600</v>
+        <v>38</v>
       </c>
       <c r="AP8">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AQ8">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AR8">
+        <v>17.5</v>
+      </c>
+      <c r="AS8">
+        <v>42</v>
+      </c>
+      <c r="AT8">
         <v>9</v>
       </c>
-      <c r="AQ8">
-        <v>13.5</v>
-      </c>
-      <c r="AR8">
-        <v>38</v>
-      </c>
-      <c r="AS8">
-        <v>21</v>
-      </c>
-      <c r="AT8">
-        <v>5.7</v>
-      </c>
       <c r="AU8">
-        <v>7.8</v>
+        <v>6.6</v>
       </c>
       <c r="AV8">
-        <v>23</v>
+        <v>12</v>
       </c>
       <c r="AW8">
-        <v>95</v>
+        <v>32</v>
       </c>
       <c r="AX8">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="AY8">
+        <v>11.5</v>
+      </c>
+      <c r="AZ8">
+        <v>17.5</v>
+      </c>
+      <c r="BA8">
+        <v>46</v>
+      </c>
+      <c r="BB8">
+        <v>40</v>
+      </c>
+      <c r="BC8">
+        <v>32</v>
+      </c>
+      <c r="BD8">
+        <v>46</v>
+      </c>
+      <c r="BE8">
+        <v>100</v>
+      </c>
+      <c r="BF8">
+        <v>32</v>
+      </c>
+      <c r="BG8">
+        <v>34</v>
+      </c>
+      <c r="BH8">
+        <v>3</v>
+      </c>
+      <c r="BI8">
+        <v>2.78</v>
+      </c>
+      <c r="BJ8">
         <v>10</v>
       </c>
-      <c r="AZ8">
-        <v>27</v>
-      </c>
-      <c r="BA8">
-        <v>29</v>
-      </c>
-      <c r="BB8">
-        <v>18.5</v>
-      </c>
-      <c r="BC8">
-        <v>22</v>
-      </c>
-      <c r="BD8">
-        <v>50</v>
-      </c>
-      <c r="BE8">
-        <v>36</v>
-      </c>
-      <c r="BF8">
-        <v>17</v>
-      </c>
-      <c r="BG8">
-        <v>21</v>
-      </c>
-      <c r="BH8">
-        <v>2.82</v>
-      </c>
-      <c r="BI8">
-        <v>2.44</v>
-      </c>
-      <c r="BJ8">
-        <v>12.5</v>
-      </c>
       <c r="BK8">
-        <v>7.4</v>
+        <v>6.4</v>
       </c>
       <c r="BL8">
         <v>1000</v>
       </c>
       <c r="BM8">
-        <v>17</v>
+        <v>130</v>
       </c>
       <c r="BN8">
-        <v>4.1</v>
+        <v>5.8</v>
       </c>
       <c r="BO8">
-        <v>3.7</v>
+        <v>5.2</v>
       </c>
       <c r="BP8">
-        <v>13.5</v>
+        <v>24</v>
       </c>
       <c r="BQ8">
-        <v>7.6</v>
+        <v>10.5</v>
       </c>
       <c r="BR8">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="BS8">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="BT8">
-        <v>9.199999999999999</v>
+        <v>5.7</v>
       </c>
       <c r="BU8">
-        <v>6</v>
+        <v>5.1</v>
       </c>
       <c r="BV8">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="BW8">
-        <v>14.5</v>
+        <v>10.5</v>
       </c>
       <c r="BX8">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="BY8">
-        <v>15</v>
+        <v>12.5</v>
       </c>
       <c r="BZ8">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="CA8">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="CB8" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
     </row>
     <row r="9" spans="1:80">
@@ -2625,97 +2613,97 @@
         <v>84</v>
       </c>
       <c r="B9" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="C9" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="D9" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="E9" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="F9">
-        <v>2.88</v>
+        <v>2.26</v>
       </c>
       <c r="G9">
-        <v>3</v>
+        <v>2.36</v>
       </c>
       <c r="H9">
-        <v>2.84</v>
+        <v>3.4</v>
       </c>
       <c r="I9">
-        <v>2.94</v>
+        <v>3.75</v>
       </c>
       <c r="J9">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="K9">
-        <v>3.25</v>
+        <v>3.5</v>
       </c>
       <c r="L9">
-        <v>1.49</v>
+        <v>1.45</v>
       </c>
       <c r="M9">
-        <v>1.1</v>
+        <v>1.08</v>
       </c>
       <c r="N9">
-        <v>3.15</v>
+        <v>3.35</v>
       </c>
       <c r="O9">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="P9">
-        <v>1.72</v>
+        <v>1.79</v>
       </c>
       <c r="Q9">
-        <v>2.36</v>
+        <v>2.18</v>
       </c>
       <c r="R9">
-        <v>1.26</v>
+        <v>1.29</v>
       </c>
       <c r="S9">
-        <v>4.5</v>
+        <v>4</v>
       </c>
       <c r="T9">
-        <v>1.91</v>
+        <v>1.85</v>
       </c>
       <c r="U9">
-        <v>2</v>
+        <v>2.04</v>
       </c>
       <c r="V9">
-        <v>1.51</v>
+        <v>1.37</v>
       </c>
       <c r="W9">
-        <v>1.5</v>
+        <v>1.73</v>
       </c>
       <c r="X9">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="Y9">
+        <v>13.5</v>
+      </c>
+      <c r="Z9">
+        <v>26</v>
+      </c>
+      <c r="AA9">
+        <v>70</v>
+      </c>
+      <c r="AB9">
         <v>9.6</v>
       </c>
-      <c r="Z9">
-        <v>18</v>
-      </c>
-      <c r="AA9">
-        <v>100</v>
-      </c>
-      <c r="AB9">
-        <v>10</v>
-      </c>
       <c r="AC9">
-        <v>7.4</v>
+        <v>7.8</v>
       </c>
       <c r="AD9">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="AE9">
-        <v>36</v>
+        <v>55</v>
       </c>
       <c r="AF9">
-        <v>18.5</v>
+        <v>16</v>
       </c>
       <c r="AG9">
         <v>13</v>
@@ -2724,384 +2712,142 @@
         <v>19.5</v>
       </c>
       <c r="AI9">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="AJ9">
-        <v>110</v>
+        <v>32</v>
       </c>
       <c r="AK9">
-        <v>38</v>
+        <v>27</v>
       </c>
       <c r="AL9">
-        <v>120</v>
+        <v>50</v>
       </c>
       <c r="AM9">
-        <v>580</v>
+        <v>130</v>
       </c>
       <c r="AN9">
-        <v>40</v>
+        <v>25</v>
       </c>
       <c r="AO9">
-        <v>38</v>
+        <v>60</v>
       </c>
       <c r="AP9">
-        <v>9.800000000000001</v>
+        <v>10.5</v>
       </c>
       <c r="AQ9">
-        <v>8.6</v>
+        <v>10.5</v>
       </c>
       <c r="AR9">
-        <v>15.5</v>
+        <v>21</v>
       </c>
       <c r="AS9">
-        <v>32</v>
+        <v>6.8</v>
       </c>
       <c r="AT9">
-        <v>8.800000000000001</v>
+        <v>7.8</v>
       </c>
       <c r="AU9">
         <v>6.4</v>
       </c>
       <c r="AV9">
+        <v>12.5</v>
+      </c>
+      <c r="AW9">
+        <v>6.6</v>
+      </c>
+      <c r="AX9">
         <v>11.5</v>
       </c>
-      <c r="AW9">
-        <v>22</v>
-      </c>
-      <c r="AX9">
+      <c r="AY9">
+        <v>9.4</v>
+      </c>
+      <c r="AZ9">
         <v>16</v>
       </c>
-      <c r="AY9">
-        <v>11</v>
-      </c>
-      <c r="AZ9">
-        <v>17</v>
-      </c>
       <c r="BA9">
-        <v>23</v>
+        <v>6.8</v>
       </c>
       <c r="BB9">
-        <v>23</v>
+        <v>6</v>
       </c>
       <c r="BC9">
-        <v>29</v>
+        <v>5.9</v>
       </c>
       <c r="BD9">
-        <v>34</v>
+        <v>6.6</v>
       </c>
       <c r="BE9">
-        <v>34</v>
+        <v>7.2</v>
       </c>
       <c r="BF9">
-        <v>22</v>
+        <v>16.5</v>
       </c>
       <c r="BG9">
-        <v>28</v>
+        <v>6.6</v>
       </c>
       <c r="BH9">
-        <v>3.05</v>
+        <v>3.25</v>
       </c>
       <c r="BI9">
-        <v>2.54</v>
+        <v>2.68</v>
       </c>
       <c r="BJ9">
         <v>10.5</v>
       </c>
       <c r="BK9">
-        <v>7.4</v>
+        <v>5.5</v>
       </c>
       <c r="BL9">
         <v>1000</v>
       </c>
       <c r="BM9">
-        <v>13.5</v>
+        <v>10.5</v>
       </c>
       <c r="BN9">
-        <v>5.8</v>
+        <v>5.2</v>
       </c>
       <c r="BO9">
-        <v>4.4</v>
+        <v>4.1</v>
       </c>
       <c r="BP9">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="BQ9">
-        <v>9.4</v>
+        <v>7</v>
       </c>
       <c r="BR9">
-        <v>42</v>
+        <v>1000</v>
       </c>
       <c r="BS9">
-        <v>11</v>
+        <v>8.6</v>
       </c>
       <c r="BT9">
-        <v>5.7</v>
+        <v>7</v>
       </c>
       <c r="BU9">
-        <v>4.3</v>
+        <v>5.3</v>
       </c>
       <c r="BV9">
-        <v>24</v>
+        <v>1000</v>
       </c>
       <c r="BW9">
+        <v>8.6</v>
+      </c>
+      <c r="BX9">
+        <v>1000</v>
+      </c>
+      <c r="BY9">
         <v>9.199999999999999</v>
       </c>
-      <c r="BX9">
-        <v>40</v>
-      </c>
-      <c r="BY9">
-        <v>11</v>
-      </c>
       <c r="BZ9">
-        <v>38</v>
+        <v>1000</v>
       </c>
       <c r="CA9">
-        <v>10.5</v>
+        <v>8.6</v>
       </c>
       <c r="CB9" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="10" spans="1:80">
-      <c r="A10" t="s">
-        <v>85</v>
-      </c>
-      <c r="B10" t="s">
-        <v>86</v>
-      </c>
-      <c r="C10" t="s">
-        <v>92</v>
-      </c>
-      <c r="D10" t="s">
-        <v>101</v>
-      </c>
-      <c r="E10" t="s">
-        <v>110</v>
-      </c>
-      <c r="F10">
-        <v>2.24</v>
-      </c>
-      <c r="G10">
-        <v>2.36</v>
-      </c>
-      <c r="H10">
-        <v>3.45</v>
-      </c>
-      <c r="I10">
-        <v>3.85</v>
-      </c>
-      <c r="J10">
-        <v>3.3</v>
-      </c>
-      <c r="K10">
-        <v>3.55</v>
-      </c>
-      <c r="L10">
-        <v>1.45</v>
-      </c>
-      <c r="M10">
-        <v>1.08</v>
-      </c>
-      <c r="N10">
-        <v>3.35</v>
-      </c>
-      <c r="O10">
-        <v>1.38</v>
-      </c>
-      <c r="P10">
-        <v>1.79</v>
-      </c>
-      <c r="Q10">
-        <v>2.18</v>
-      </c>
-      <c r="R10">
-        <v>1.29</v>
-      </c>
-      <c r="S10">
-        <v>4</v>
-      </c>
-      <c r="T10">
-        <v>1.84</v>
-      </c>
-      <c r="U10">
-        <v>2.02</v>
-      </c>
-      <c r="V10">
-        <v>1.35</v>
-      </c>
-      <c r="W10">
-        <v>1.75</v>
-      </c>
-      <c r="X10">
-        <v>14</v>
-      </c>
-      <c r="Y10">
-        <v>13.5</v>
-      </c>
-      <c r="Z10">
-        <v>26</v>
-      </c>
-      <c r="AA10">
-        <v>80</v>
-      </c>
-      <c r="AB10">
-        <v>9.6</v>
-      </c>
-      <c r="AC10">
-        <v>7.8</v>
-      </c>
-      <c r="AD10">
-        <v>16</v>
-      </c>
-      <c r="AE10">
-        <v>55</v>
-      </c>
-      <c r="AF10">
-        <v>15</v>
-      </c>
-      <c r="AG10">
-        <v>13</v>
-      </c>
-      <c r="AH10">
-        <v>19.5</v>
-      </c>
-      <c r="AI10">
-        <v>70</v>
-      </c>
-      <c r="AJ10">
-        <v>32</v>
-      </c>
-      <c r="AK10">
-        <v>27</v>
-      </c>
-      <c r="AL10">
-        <v>50</v>
-      </c>
-      <c r="AM10">
-        <v>130</v>
-      </c>
-      <c r="AN10">
-        <v>25</v>
-      </c>
-      <c r="AO10">
-        <v>60</v>
-      </c>
-      <c r="AP10">
-        <v>10.5</v>
-      </c>
-      <c r="AQ10">
-        <v>10</v>
-      </c>
-      <c r="AR10">
-        <v>21</v>
-      </c>
-      <c r="AS10">
-        <v>7</v>
-      </c>
-      <c r="AT10">
-        <v>7.8</v>
-      </c>
-      <c r="AU10">
-        <v>6.4</v>
-      </c>
-      <c r="AV10">
-        <v>12.5</v>
-      </c>
-      <c r="AW10">
-        <v>6.8</v>
-      </c>
-      <c r="AX10">
-        <v>11.5</v>
-      </c>
-      <c r="AY10">
-        <v>9.4</v>
-      </c>
-      <c r="AZ10">
-        <v>16</v>
-      </c>
-      <c r="BA10">
-        <v>6.8</v>
-      </c>
-      <c r="BB10">
-        <v>6.2</v>
-      </c>
-      <c r="BC10">
-        <v>6</v>
-      </c>
-      <c r="BD10">
-        <v>6.6</v>
-      </c>
-      <c r="BE10">
-        <v>7.2</v>
-      </c>
-      <c r="BF10">
-        <v>16.5</v>
-      </c>
-      <c r="BG10">
-        <v>6.8</v>
-      </c>
-      <c r="BH10">
-        <v>3.25</v>
-      </c>
-      <c r="BI10">
-        <v>2.68</v>
-      </c>
-      <c r="BJ10">
-        <v>10.5</v>
-      </c>
-      <c r="BK10">
-        <v>5.5</v>
-      </c>
-      <c r="BL10">
-        <v>1000</v>
-      </c>
-      <c r="BM10">
-        <v>10.5</v>
-      </c>
-      <c r="BN10">
-        <v>5.2</v>
-      </c>
-      <c r="BO10">
-        <v>4</v>
-      </c>
-      <c r="BP10">
-        <v>18</v>
-      </c>
-      <c r="BQ10">
-        <v>7</v>
-      </c>
-      <c r="BR10">
-        <v>1000</v>
-      </c>
-      <c r="BS10">
-        <v>8.6</v>
-      </c>
-      <c r="BT10">
-        <v>7</v>
-      </c>
-      <c r="BU10">
-        <v>5.3</v>
-      </c>
-      <c r="BV10">
-        <v>1000</v>
-      </c>
-      <c r="BW10">
-        <v>8.6</v>
-      </c>
-      <c r="BX10">
-        <v>1000</v>
-      </c>
-      <c r="BY10">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="BZ10">
-        <v>1000</v>
-      </c>
-      <c r="CA10">
-        <v>8.6</v>
-      </c>
-      <c r="CB10" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
     </row>
   </sheetData>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-08-11.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-08-11.xlsx
@@ -337,7 +337,7 @@
     <t>Union Espanola</t>
   </si>
   <si>
-    <t>2026-08-11 11:55:15</t>
+    <t>2026-08-11 14:02:40</t>
   </si>
 </sst>
 </file>
@@ -931,16 +931,16 @@
         <v>99</v>
       </c>
       <c r="F2">
-        <v>2.62</v>
+        <v>3</v>
       </c>
       <c r="G2">
-        <v>2.64</v>
+        <v>3.1</v>
       </c>
       <c r="H2">
-        <v>2.7</v>
+        <v>2.36</v>
       </c>
       <c r="I2">
-        <v>2.74</v>
+        <v>2.4</v>
       </c>
       <c r="J2">
         <v>3.9</v>
@@ -955,145 +955,145 @@
         <v>1.05</v>
       </c>
       <c r="N2">
-        <v>5.1</v>
+        <v>5.4</v>
       </c>
       <c r="O2">
-        <v>1.23</v>
+        <v>1.21</v>
       </c>
       <c r="P2">
-        <v>2.4</v>
+        <v>2.5</v>
       </c>
       <c r="Q2">
-        <v>1.7</v>
+        <v>1.66</v>
       </c>
       <c r="R2">
-        <v>1.55</v>
+        <v>1.6</v>
       </c>
       <c r="S2">
-        <v>2.74</v>
+        <v>2.66</v>
       </c>
       <c r="T2">
-        <v>1.63</v>
+        <v>1.6</v>
       </c>
       <c r="U2">
-        <v>2.52</v>
+        <v>2.58</v>
       </c>
       <c r="V2">
-        <v>1.56</v>
+        <v>1.71</v>
       </c>
       <c r="W2">
-        <v>1.6</v>
+        <v>1.47</v>
       </c>
       <c r="X2">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="Y2">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="Z2">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="AA2">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="AB2">
-        <v>14.5</v>
+        <v>18</v>
       </c>
       <c r="AC2">
-        <v>9.199999999999999</v>
+        <v>9.6</v>
       </c>
       <c r="AD2">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AE2">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="AF2">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="AG2">
-        <v>12.5</v>
+        <v>14</v>
       </c>
       <c r="AH2">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="AI2">
         <v>32</v>
       </c>
       <c r="AJ2">
-        <v>38</v>
+        <v>50</v>
       </c>
       <c r="AK2">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="AL2">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="AM2">
         <v>60</v>
       </c>
       <c r="AN2">
+        <v>19</v>
+      </c>
+      <c r="AO2">
+        <v>13.5</v>
+      </c>
+      <c r="AP2">
+        <v>19.5</v>
+      </c>
+      <c r="AQ2">
+        <v>13</v>
+      </c>
+      <c r="AR2">
         <v>16</v>
       </c>
-      <c r="AO2">
-        <v>17</v>
-      </c>
-      <c r="AP2">
-        <v>19</v>
-      </c>
-      <c r="AQ2">
-        <v>13.5</v>
-      </c>
-      <c r="AR2">
-        <v>18.5</v>
-      </c>
       <c r="AS2">
-        <v>36</v>
+        <v>28</v>
       </c>
       <c r="AT2">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="AU2">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="AV2">
-        <v>11.5</v>
+        <v>10.5</v>
       </c>
       <c r="AW2">
-        <v>24</v>
+        <v>19.5</v>
       </c>
       <c r="AX2">
-        <v>19.5</v>
+        <v>21</v>
       </c>
       <c r="AY2">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AZ2">
         <v>13.5</v>
       </c>
       <c r="BA2">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="BB2">
-        <v>36</v>
+        <v>44</v>
       </c>
       <c r="BC2">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="BD2">
         <v>29</v>
       </c>
       <c r="BE2">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="BF2">
-        <v>14.5</v>
+        <v>17</v>
       </c>
       <c r="BG2">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="BH2">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="BI2">
         <v>3.75</v>
@@ -1102,49 +1102,49 @@
         <v>8.6</v>
       </c>
       <c r="BK2">
-        <v>7.6</v>
+        <v>7.2</v>
       </c>
       <c r="BL2">
-        <v>80</v>
+        <v>100</v>
       </c>
       <c r="BM2">
-        <v>14</v>
+        <v>55</v>
       </c>
       <c r="BN2">
-        <v>6</v>
+        <v>6.4</v>
       </c>
       <c r="BO2">
-        <v>5.3</v>
+        <v>5.5</v>
       </c>
       <c r="BP2">
-        <v>17.5</v>
+        <v>21</v>
       </c>
       <c r="BQ2">
-        <v>8.800000000000001</v>
+        <v>18</v>
       </c>
       <c r="BR2">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="BS2">
-        <v>10.5</v>
+        <v>24</v>
       </c>
       <c r="BT2">
-        <v>6.2</v>
+        <v>5.7</v>
       </c>
       <c r="BU2">
-        <v>5.4</v>
+        <v>5.1</v>
       </c>
       <c r="BV2">
-        <v>18.5</v>
+        <v>16.5</v>
       </c>
       <c r="BW2">
-        <v>9</v>
+        <v>14.5</v>
       </c>
       <c r="BX2">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="BY2">
-        <v>10.5</v>
+        <v>22</v>
       </c>
       <c r="BZ2">
         <v>0</v>
@@ -1173,19 +1173,19 @@
         <v>100</v>
       </c>
       <c r="F3">
-        <v>3</v>
+        <v>3.3</v>
       </c>
       <c r="G3">
-        <v>3.2</v>
+        <v>3.4</v>
       </c>
       <c r="H3">
-        <v>2.94</v>
+        <v>2.72</v>
       </c>
       <c r="I3">
-        <v>3.15</v>
+        <v>2.78</v>
       </c>
       <c r="J3">
-        <v>2.8</v>
+        <v>2.88</v>
       </c>
       <c r="K3">
         <v>2.96</v>
@@ -1194,40 +1194,40 @@
         <v>1.66</v>
       </c>
       <c r="M3">
-        <v>1.16</v>
+        <v>1.15</v>
       </c>
       <c r="N3">
-        <v>2.4</v>
+        <v>2.44</v>
       </c>
       <c r="O3">
-        <v>1.7</v>
+        <v>1.68</v>
       </c>
       <c r="P3">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="Q3">
         <v>2.96</v>
       </c>
       <c r="R3">
-        <v>1.15</v>
+        <v>1.16</v>
       </c>
       <c r="S3">
         <v>6.8</v>
       </c>
       <c r="T3">
-        <v>2.24</v>
+        <v>2.22</v>
       </c>
       <c r="U3">
-        <v>1.67</v>
+        <v>1.72</v>
       </c>
       <c r="V3">
-        <v>1.47</v>
+        <v>1.54</v>
       </c>
       <c r="W3">
-        <v>1.46</v>
+        <v>1.4</v>
       </c>
       <c r="X3">
-        <v>7.8</v>
+        <v>7.4</v>
       </c>
       <c r="Y3">
         <v>8</v>
@@ -1236,22 +1236,22 @@
         <v>19</v>
       </c>
       <c r="AA3">
-        <v>90</v>
+        <v>150</v>
       </c>
       <c r="AB3">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AC3">
         <v>7.4</v>
       </c>
       <c r="AD3">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="AE3">
         <v>55</v>
       </c>
       <c r="AF3">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="AG3">
         <v>16</v>
@@ -1260,49 +1260,49 @@
         <v>27</v>
       </c>
       <c r="AI3">
-        <v>200</v>
+        <v>170</v>
       </c>
       <c r="AJ3">
-        <v>150</v>
+        <v>65</v>
       </c>
       <c r="AK3">
-        <v>85</v>
+        <v>55</v>
       </c>
       <c r="AL3">
-        <v>460</v>
+        <v>230</v>
       </c>
       <c r="AM3">
         <v>500</v>
       </c>
       <c r="AN3">
-        <v>210</v>
+        <v>75</v>
       </c>
       <c r="AO3">
-        <v>70</v>
+        <v>100</v>
       </c>
       <c r="AP3">
         <v>6.4</v>
       </c>
       <c r="AQ3">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="AR3">
         <v>16</v>
       </c>
       <c r="AS3">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="AT3">
-        <v>6.6</v>
+        <v>7</v>
       </c>
       <c r="AU3">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="AV3">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="AW3">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="AX3">
         <v>16.5</v>
@@ -1320,79 +1320,79 @@
         <v>18</v>
       </c>
       <c r="BC3">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="BD3">
-        <v>9.4</v>
+        <v>34</v>
       </c>
       <c r="BE3">
         <v>10</v>
       </c>
       <c r="BF3">
-        <v>11.5</v>
+        <v>22</v>
       </c>
       <c r="BG3">
-        <v>9.199999999999999</v>
+        <v>21</v>
       </c>
       <c r="BH3">
-        <v>2.58</v>
+        <v>2.68</v>
       </c>
       <c r="BI3">
-        <v>2.2</v>
+        <v>2.16</v>
       </c>
       <c r="BJ3">
         <v>12</v>
       </c>
       <c r="BK3">
-        <v>6.6</v>
+        <v>5.8</v>
       </c>
       <c r="BL3">
         <v>1000</v>
       </c>
       <c r="BM3">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="BN3">
-        <v>5.9</v>
+        <v>6.4</v>
       </c>
       <c r="BO3">
-        <v>5</v>
+        <v>4.7</v>
       </c>
       <c r="BP3">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="BQ3">
-        <v>10</v>
+        <v>8.6</v>
       </c>
       <c r="BR3">
         <v>60</v>
       </c>
       <c r="BS3">
-        <v>12</v>
+        <v>9.6</v>
       </c>
       <c r="BT3">
-        <v>5.9</v>
+        <v>5.6</v>
       </c>
       <c r="BU3">
-        <v>4.9</v>
+        <v>4.1</v>
       </c>
       <c r="BV3">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="BW3">
-        <v>9.800000000000001</v>
+        <v>8</v>
       </c>
       <c r="BX3">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="BY3">
-        <v>11.5</v>
+        <v>9.4</v>
       </c>
       <c r="BZ3">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="CA3">
-        <v>12</v>
+        <v>9.6</v>
       </c>
       <c r="CB3" t="s">
         <v>107</v>
@@ -1415,25 +1415,25 @@
         <v>101</v>
       </c>
       <c r="F4">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="G4">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="H4">
+        <v>1.56</v>
+      </c>
+      <c r="I4">
         <v>1.57</v>
       </c>
-      <c r="I4">
-        <v>1.62</v>
-      </c>
       <c r="J4">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="K4">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="L4">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="M4">
         <v>1.08</v>
@@ -1445,61 +1445,61 @@
         <v>1.4</v>
       </c>
       <c r="P4">
-        <v>1.81</v>
+        <v>1.83</v>
       </c>
       <c r="Q4">
         <v>2.16</v>
       </c>
       <c r="R4">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="S4">
         <v>4.1</v>
       </c>
       <c r="T4">
-        <v>2.18</v>
+        <v>2.24</v>
       </c>
       <c r="U4">
-        <v>1.75</v>
+        <v>1.74</v>
       </c>
       <c r="V4">
-        <v>2.6</v>
+        <v>2.58</v>
       </c>
       <c r="W4">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="X4">
         <v>15.5</v>
       </c>
       <c r="Y4">
-        <v>6.8</v>
+        <v>8</v>
       </c>
       <c r="Z4">
-        <v>8.4</v>
+        <v>17.5</v>
       </c>
       <c r="AA4">
-        <v>15.5</v>
+        <v>30</v>
       </c>
       <c r="AB4">
-        <v>32</v>
+        <v>970</v>
       </c>
       <c r="AC4">
-        <v>9.199999999999999</v>
+        <v>12</v>
       </c>
       <c r="AD4">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AE4">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="AF4">
-        <v>160</v>
+        <v>330</v>
       </c>
       <c r="AG4">
-        <v>46</v>
+        <v>60</v>
       </c>
       <c r="AH4">
-        <v>36</v>
+        <v>50</v>
       </c>
       <c r="AI4">
         <v>120</v>
@@ -1517,124 +1517,124 @@
         <v>700</v>
       </c>
       <c r="AN4">
-        <v>280</v>
+        <v>1000</v>
       </c>
       <c r="AO4">
-        <v>11.5</v>
+        <v>29</v>
       </c>
       <c r="AP4">
-        <v>11</v>
+        <v>6.2</v>
       </c>
       <c r="AQ4">
-        <v>5.9</v>
+        <v>4.2</v>
       </c>
       <c r="AR4">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="AS4">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AT4">
-        <v>17</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AU4">
-        <v>8.199999999999999</v>
+        <v>7.4</v>
       </c>
       <c r="AV4">
-        <v>8.800000000000001</v>
+        <v>7.4</v>
       </c>
       <c r="AW4">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AX4">
-        <v>20</v>
+        <v>5.7</v>
       </c>
       <c r="AY4">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="AZ4">
-        <v>23</v>
+        <v>13.5</v>
       </c>
       <c r="BA4">
-        <v>24</v>
+        <v>5.5</v>
       </c>
       <c r="BB4">
-        <v>10</v>
+        <v>4.7</v>
       </c>
       <c r="BC4">
-        <v>10</v>
+        <v>5.8</v>
       </c>
       <c r="BD4">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="BE4">
-        <v>10</v>
+        <v>3.95</v>
       </c>
       <c r="BF4">
-        <v>10</v>
+        <v>4.7</v>
       </c>
       <c r="BG4">
-        <v>10</v>
+        <v>3.5</v>
       </c>
       <c r="BH4">
-        <v>3.65</v>
+        <v>1000</v>
       </c>
       <c r="BI4">
-        <v>2.58</v>
+        <v>1.04</v>
       </c>
       <c r="BJ4">
-        <v>14.5</v>
+        <v>1000</v>
       </c>
       <c r="BK4">
-        <v>3.75</v>
+        <v>1.04</v>
       </c>
       <c r="BL4">
         <v>1000</v>
       </c>
       <c r="BM4">
-        <v>5</v>
+        <v>1.04</v>
       </c>
       <c r="BN4">
-        <v>13</v>
+        <v>1000</v>
       </c>
       <c r="BO4">
-        <v>3.65</v>
+        <v>1.04</v>
       </c>
       <c r="BP4">
         <v>1000</v>
       </c>
       <c r="BQ4">
-        <v>4.8</v>
+        <v>1.04</v>
       </c>
       <c r="BR4">
         <v>1000</v>
       </c>
       <c r="BS4">
-        <v>4.8</v>
+        <v>1.04</v>
       </c>
       <c r="BT4">
-        <v>4.5</v>
+        <v>1000</v>
       </c>
       <c r="BU4">
-        <v>3.05</v>
+        <v>1.04</v>
       </c>
       <c r="BV4">
-        <v>13</v>
+        <v>1000</v>
       </c>
       <c r="BW4">
-        <v>3.65</v>
+        <v>1.04</v>
       </c>
       <c r="BX4">
-        <v>38</v>
+        <v>1000</v>
       </c>
       <c r="BY4">
-        <v>4.5</v>
+        <v>1.04</v>
       </c>
       <c r="BZ4">
-        <v>28</v>
+        <v>1000</v>
       </c>
       <c r="CA4">
-        <v>4.3</v>
+        <v>1.04</v>
       </c>
       <c r="CB4" t="s">
         <v>107</v>
@@ -1660,16 +1660,16 @@
         <v>2.56</v>
       </c>
       <c r="G5">
-        <v>2.68</v>
+        <v>2.7</v>
       </c>
       <c r="H5">
         <v>3.5</v>
       </c>
       <c r="I5">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="J5">
-        <v>2.9</v>
+        <v>2.86</v>
       </c>
       <c r="K5">
         <v>2.92</v>
@@ -1681,7 +1681,7 @@
         <v>1.18</v>
       </c>
       <c r="N5">
-        <v>2.2</v>
+        <v>2.22</v>
       </c>
       <c r="O5">
         <v>1.78</v>
@@ -1690,37 +1690,37 @@
         <v>1.37</v>
       </c>
       <c r="Q5">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="R5">
         <v>1.13</v>
       </c>
       <c r="S5">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="T5">
-        <v>2.44</v>
+        <v>2.16</v>
       </c>
       <c r="U5">
-        <v>1.6</v>
+        <v>1.5</v>
       </c>
       <c r="V5">
         <v>1.36</v>
       </c>
       <c r="W5">
-        <v>1.59</v>
+        <v>1.58</v>
       </c>
       <c r="X5">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="Y5">
         <v>8.6</v>
       </c>
       <c r="Z5">
-        <v>36</v>
+        <v>29</v>
       </c>
       <c r="AA5">
-        <v>230</v>
+        <v>240</v>
       </c>
       <c r="AB5">
         <v>6.8</v>
@@ -1729,19 +1729,19 @@
         <v>7.2</v>
       </c>
       <c r="AD5">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AE5">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="AF5">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="AG5">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="AH5">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="AI5">
         <v>540</v>
@@ -1765,28 +1765,28 @@
         <v>150</v>
       </c>
       <c r="AP5">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="AQ5">
         <v>7.4</v>
       </c>
       <c r="AR5">
-        <v>10.5</v>
+        <v>20</v>
       </c>
       <c r="AS5">
-        <v>20</v>
+        <v>7.8</v>
       </c>
       <c r="AT5">
         <v>5.9</v>
       </c>
       <c r="AU5">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="AV5">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="AW5">
-        <v>23</v>
+        <v>8</v>
       </c>
       <c r="AX5">
         <v>13</v>
@@ -1795,46 +1795,46 @@
         <v>12.5</v>
       </c>
       <c r="AZ5">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="BA5">
+        <v>29</v>
+      </c>
+      <c r="BB5">
+        <v>20</v>
+      </c>
+      <c r="BC5">
+        <v>40</v>
+      </c>
+      <c r="BD5">
         <v>7.8</v>
       </c>
-      <c r="BB5">
-        <v>19.5</v>
-      </c>
-      <c r="BC5">
-        <v>32</v>
-      </c>
-      <c r="BD5">
+      <c r="BE5">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BF5">
         <v>7.6</v>
       </c>
-      <c r="BE5">
-        <v>7.8</v>
-      </c>
-      <c r="BF5">
-        <v>9.800000000000001</v>
-      </c>
       <c r="BG5">
-        <v>7.6</v>
+        <v>8</v>
       </c>
       <c r="BH5">
-        <v>2.64</v>
+        <v>2.72</v>
       </c>
       <c r="BI5">
-        <v>2.02</v>
+        <v>2</v>
       </c>
       <c r="BJ5">
         <v>15</v>
       </c>
       <c r="BK5">
-        <v>4.5</v>
+        <v>4</v>
       </c>
       <c r="BL5">
         <v>1000</v>
       </c>
       <c r="BM5">
-        <v>6.4</v>
+        <v>5.5</v>
       </c>
       <c r="BN5">
         <v>6.2</v>
@@ -1846,37 +1846,37 @@
         <v>32</v>
       </c>
       <c r="BQ5">
-        <v>5.4</v>
+        <v>4.7</v>
       </c>
       <c r="BR5">
         <v>70</v>
       </c>
       <c r="BS5">
-        <v>5.9</v>
+        <v>5.1</v>
       </c>
       <c r="BT5">
-        <v>6.8</v>
+        <v>7.8</v>
       </c>
       <c r="BU5">
         <v>5</v>
       </c>
       <c r="BV5">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="BW5">
-        <v>5.7</v>
+        <v>4.9</v>
       </c>
       <c r="BX5">
+        <v>90</v>
+      </c>
+      <c r="BY5">
+        <v>5.2</v>
+      </c>
+      <c r="BZ5">
         <v>1000</v>
       </c>
-      <c r="BY5">
-        <v>6</v>
-      </c>
-      <c r="BZ5">
-        <v>85</v>
-      </c>
       <c r="CA5">
-        <v>6</v>
+        <v>5.2</v>
       </c>
       <c r="CB5" t="s">
         <v>107</v>
@@ -1902,16 +1902,16 @@
         <v>2.5</v>
       </c>
       <c r="G6">
-        <v>2.68</v>
+        <v>2.66</v>
       </c>
       <c r="H6">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="I6">
-        <v>3.95</v>
+        <v>3.9</v>
       </c>
       <c r="J6">
-        <v>2.88</v>
+        <v>2.78</v>
       </c>
       <c r="K6">
         <v>2.94</v>
@@ -1920,31 +1920,31 @@
         <v>1.72</v>
       </c>
       <c r="M6">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="N6">
-        <v>2.24</v>
+        <v>2.26</v>
       </c>
       <c r="O6">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="P6">
         <v>1.39</v>
       </c>
       <c r="Q6">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="R6">
         <v>1.13</v>
       </c>
       <c r="S6">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="T6">
-        <v>2.38</v>
+        <v>2.4</v>
       </c>
       <c r="U6">
-        <v>1.6</v>
+        <v>1.62</v>
       </c>
       <c r="V6">
         <v>1.34</v>
@@ -1956,13 +1956,13 @@
         <v>6.8</v>
       </c>
       <c r="Y6">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="Z6">
-        <v>25</v>
+        <v>55</v>
       </c>
       <c r="AA6">
-        <v>500</v>
+        <v>290</v>
       </c>
       <c r="AB6">
         <v>6.8</v>
@@ -1971,31 +1971,31 @@
         <v>7.2</v>
       </c>
       <c r="AD6">
-        <v>19</v>
+        <v>30</v>
       </c>
       <c r="AE6">
-        <v>230</v>
+        <v>440</v>
       </c>
       <c r="AF6">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="AG6">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="AH6">
-        <v>32</v>
+        <v>85</v>
       </c>
       <c r="AI6">
-        <v>540</v>
+        <v>500</v>
       </c>
       <c r="AJ6">
-        <v>120</v>
+        <v>170</v>
       </c>
       <c r="AK6">
-        <v>50</v>
+        <v>150</v>
       </c>
       <c r="AL6">
-        <v>230</v>
+        <v>460</v>
       </c>
       <c r="AM6">
         <v>500</v>
@@ -2004,73 +2004,73 @@
         <v>80</v>
       </c>
       <c r="AO6">
-        <v>600</v>
+        <v>140</v>
       </c>
       <c r="AP6">
-        <v>5.7</v>
+        <v>5.9</v>
       </c>
       <c r="AQ6">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="AR6">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AS6">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AT6">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="AU6">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="AV6">
         <v>16</v>
       </c>
       <c r="AW6">
-        <v>23</v>
+        <v>46</v>
       </c>
       <c r="AX6">
         <v>12.5</v>
       </c>
       <c r="AY6">
+        <v>12</v>
+      </c>
+      <c r="AZ6">
+        <v>14.5</v>
+      </c>
+      <c r="BA6">
+        <v>11</v>
+      </c>
+      <c r="BB6">
+        <v>36</v>
+      </c>
+      <c r="BC6">
+        <v>30</v>
+      </c>
+      <c r="BD6">
+        <v>28</v>
+      </c>
+      <c r="BE6">
+        <v>12</v>
+      </c>
+      <c r="BF6">
+        <v>34</v>
+      </c>
+      <c r="BG6">
         <v>11.5</v>
-      </c>
-      <c r="AZ6">
-        <v>24</v>
-      </c>
-      <c r="BA6">
-        <v>29</v>
-      </c>
-      <c r="BB6">
-        <v>18.5</v>
-      </c>
-      <c r="BC6">
-        <v>18.5</v>
-      </c>
-      <c r="BD6">
-        <v>10</v>
-      </c>
-      <c r="BE6">
-        <v>11</v>
-      </c>
-      <c r="BF6">
-        <v>9.6</v>
-      </c>
-      <c r="BG6">
-        <v>10.5</v>
       </c>
       <c r="BH6">
         <v>2.42</v>
       </c>
       <c r="BI6">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="BJ6">
         <v>13</v>
       </c>
       <c r="BK6">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="BL6">
         <v>1000</v>
@@ -2079,22 +2079,22 @@
         <v>2.08</v>
       </c>
       <c r="BN6">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="BO6">
-        <v>4</v>
+        <v>3.95</v>
       </c>
       <c r="BP6">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="BQ6">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BR6">
         <v>1000</v>
       </c>
       <c r="BS6">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="BT6">
         <v>6.8</v>
@@ -2106,19 +2106,19 @@
         <v>1000</v>
       </c>
       <c r="BW6">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="BX6">
         <v>1000</v>
       </c>
       <c r="BY6">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="BZ6">
         <v>1000</v>
       </c>
       <c r="CA6">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="CB6" t="s">
         <v>107</v>
@@ -2141,19 +2141,19 @@
         <v>104</v>
       </c>
       <c r="F7">
+        <v>1.74</v>
+      </c>
+      <c r="G7">
         <v>1.76</v>
       </c>
-      <c r="G7">
-        <v>1.78</v>
-      </c>
       <c r="H7">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="I7">
-        <v>6.2</v>
+        <v>6.6</v>
       </c>
       <c r="J7">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="K7">
         <v>3.7</v>
@@ -2162,10 +2162,10 @@
         <v>1.57</v>
       </c>
       <c r="M7">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="N7">
-        <v>2.84</v>
+        <v>2.82</v>
       </c>
       <c r="O7">
         <v>1.53</v>
@@ -2177,22 +2177,22 @@
         <v>2.6</v>
       </c>
       <c r="R7">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="S7">
-        <v>5.4</v>
+        <v>5.3</v>
       </c>
       <c r="T7">
-        <v>2.32</v>
+        <v>2.38</v>
       </c>
       <c r="U7">
         <v>1.69</v>
       </c>
       <c r="V7">
-        <v>1.19</v>
+        <v>1.17</v>
       </c>
       <c r="W7">
-        <v>2.28</v>
+        <v>2.3</v>
       </c>
       <c r="X7">
         <v>9.6</v>
@@ -2201,22 +2201,22 @@
         <v>14.5</v>
       </c>
       <c r="Z7">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="AA7">
-        <v>200</v>
+        <v>230</v>
       </c>
       <c r="AB7">
         <v>5.9</v>
       </c>
       <c r="AC7">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AD7">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AE7">
-        <v>260</v>
+        <v>140</v>
       </c>
       <c r="AF7">
         <v>8.6</v>
@@ -2228,25 +2228,25 @@
         <v>32</v>
       </c>
       <c r="AI7">
-        <v>140</v>
+        <v>260</v>
       </c>
       <c r="AJ7">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="AK7">
         <v>23</v>
       </c>
       <c r="AL7">
-        <v>60</v>
+        <v>75</v>
       </c>
       <c r="AM7">
         <v>250</v>
       </c>
       <c r="AN7">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="AO7">
-        <v>700</v>
+        <v>240</v>
       </c>
       <c r="AP7">
         <v>9</v>
@@ -2255,13 +2255,13 @@
         <v>14</v>
       </c>
       <c r="AR7">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="AS7">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="AT7">
-        <v>5.7</v>
+        <v>5.6</v>
       </c>
       <c r="AU7">
         <v>7.8</v>
@@ -2279,16 +2279,16 @@
         <v>10</v>
       </c>
       <c r="AZ7">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="BA7">
-        <v>29</v>
+        <v>22</v>
       </c>
       <c r="BB7">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="BC7">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="BD7">
         <v>50</v>
@@ -2297,13 +2297,13 @@
         <v>150</v>
       </c>
       <c r="BF7">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="BG7">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="BH7">
-        <v>2.8</v>
+        <v>2.82</v>
       </c>
       <c r="BI7">
         <v>2.46</v>
@@ -2324,7 +2324,7 @@
         <v>4</v>
       </c>
       <c r="BO7">
-        <v>3.7</v>
+        <v>3.6</v>
       </c>
       <c r="BP7">
         <v>13</v>
@@ -2342,25 +2342,25 @@
         <v>9.6</v>
       </c>
       <c r="BU7">
-        <v>7.6</v>
+        <v>6.4</v>
       </c>
       <c r="BV7">
         <v>1000</v>
       </c>
       <c r="BW7">
-        <v>2.38</v>
+        <v>15.5</v>
       </c>
       <c r="BX7">
         <v>1000</v>
       </c>
       <c r="BY7">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="BZ7">
         <v>1000</v>
       </c>
       <c r="CA7">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="CB7" t="s">
         <v>107</v>
@@ -2383,16 +2383,16 @@
         <v>105</v>
       </c>
       <c r="F8">
-        <v>2.86</v>
+        <v>2.92</v>
       </c>
       <c r="G8">
-        <v>2.9</v>
+        <v>3</v>
       </c>
       <c r="H8">
-        <v>2.9</v>
+        <v>2.8</v>
       </c>
       <c r="I8">
-        <v>2.96</v>
+        <v>2.88</v>
       </c>
       <c r="J8">
         <v>3.2</v>
@@ -2401,7 +2401,7 @@
         <v>3.25</v>
       </c>
       <c r="L8">
-        <v>1.49</v>
+        <v>1.5</v>
       </c>
       <c r="M8">
         <v>1.1</v>
@@ -2410,16 +2410,16 @@
         <v>3.15</v>
       </c>
       <c r="O8">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="P8">
-        <v>1.72</v>
+        <v>1.71</v>
       </c>
       <c r="Q8">
         <v>2.34</v>
       </c>
       <c r="R8">
-        <v>1.27</v>
+        <v>1.26</v>
       </c>
       <c r="S8">
         <v>4.5</v>
@@ -2431,25 +2431,25 @@
         <v>2</v>
       </c>
       <c r="V8">
-        <v>1.51</v>
+        <v>1.53</v>
       </c>
       <c r="W8">
-        <v>1.52</v>
+        <v>1.5</v>
       </c>
       <c r="X8">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="Y8">
         <v>9.800000000000001</v>
       </c>
       <c r="Z8">
-        <v>18.5</v>
+        <v>17.5</v>
       </c>
       <c r="AA8">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="AB8">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="AC8">
         <v>7.4</v>
@@ -2458,13 +2458,13 @@
         <v>13</v>
       </c>
       <c r="AE8">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="AF8">
-        <v>18</v>
+        <v>18.5</v>
       </c>
       <c r="AG8">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="AH8">
         <v>19.5</v>
@@ -2473,7 +2473,7 @@
         <v>55</v>
       </c>
       <c r="AJ8">
-        <v>48</v>
+        <v>55</v>
       </c>
       <c r="AK8">
         <v>38</v>
@@ -2485,22 +2485,22 @@
         <v>130</v>
       </c>
       <c r="AN8">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="AO8">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="AP8">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="AQ8">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="AR8">
-        <v>17.5</v>
+        <v>15.5</v>
       </c>
       <c r="AS8">
-        <v>42</v>
+        <v>34</v>
       </c>
       <c r="AT8">
         <v>9</v>
@@ -2509,49 +2509,49 @@
         <v>6.6</v>
       </c>
       <c r="AV8">
+        <v>11.5</v>
+      </c>
+      <c r="AW8">
+        <v>30</v>
+      </c>
+      <c r="AX8">
+        <v>16.5</v>
+      </c>
+      <c r="AY8">
         <v>12</v>
       </c>
-      <c r="AW8">
-        <v>32</v>
-      </c>
-      <c r="AX8">
-        <v>16</v>
-      </c>
-      <c r="AY8">
-        <v>11.5</v>
-      </c>
       <c r="AZ8">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="BA8">
         <v>46</v>
       </c>
       <c r="BB8">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="BC8">
         <v>32</v>
       </c>
       <c r="BD8">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="BE8">
         <v>100</v>
       </c>
       <c r="BF8">
+        <v>36</v>
+      </c>
+      <c r="BG8">
         <v>32</v>
-      </c>
-      <c r="BG8">
-        <v>34</v>
       </c>
       <c r="BH8">
         <v>3</v>
       </c>
       <c r="BI8">
-        <v>2.78</v>
+        <v>2.76</v>
       </c>
       <c r="BJ8">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="BK8">
         <v>6.4</v>
@@ -2563,46 +2563,46 @@
         <v>130</v>
       </c>
       <c r="BN8">
-        <v>5.8</v>
+        <v>5.9</v>
       </c>
       <c r="BO8">
         <v>5.2</v>
       </c>
       <c r="BP8">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="BQ8">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="BR8">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="BS8">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="BT8">
-        <v>5.7</v>
+        <v>5.6</v>
       </c>
       <c r="BU8">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="BV8">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="BW8">
-        <v>10.5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BX8">
         <v>40</v>
       </c>
       <c r="BY8">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="BZ8">
         <v>38</v>
       </c>
       <c r="CA8">
-        <v>12.5</v>
+        <v>11.5</v>
       </c>
       <c r="CB8" t="s">
         <v>107</v>
@@ -2625,55 +2625,55 @@
         <v>106</v>
       </c>
       <c r="F9">
-        <v>2.26</v>
+        <v>2.24</v>
       </c>
       <c r="G9">
         <v>2.36</v>
       </c>
       <c r="H9">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="I9">
         <v>3.75</v>
       </c>
       <c r="J9">
-        <v>3.25</v>
+        <v>3.35</v>
       </c>
       <c r="K9">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="L9">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="M9">
         <v>1.08</v>
       </c>
       <c r="N9">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="O9">
-        <v>1.4</v>
+        <v>1.37</v>
       </c>
       <c r="P9">
         <v>1.79</v>
       </c>
       <c r="Q9">
-        <v>2.18</v>
+        <v>2.16</v>
       </c>
       <c r="R9">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="S9">
         <v>4</v>
       </c>
       <c r="T9">
-        <v>1.85</v>
+        <v>1.84</v>
       </c>
       <c r="U9">
-        <v>2.04</v>
+        <v>2.02</v>
       </c>
       <c r="V9">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="W9">
         <v>1.73</v>
@@ -2682,46 +2682,46 @@
         <v>14</v>
       </c>
       <c r="Y9">
-        <v>13.5</v>
+        <v>14.5</v>
       </c>
       <c r="Z9">
         <v>26</v>
       </c>
       <c r="AA9">
-        <v>70</v>
+        <v>80</v>
       </c>
       <c r="AB9">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AC9">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="AD9">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AE9">
         <v>55</v>
       </c>
       <c r="AF9">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="AG9">
         <v>13</v>
       </c>
       <c r="AH9">
-        <v>19.5</v>
+        <v>22</v>
       </c>
       <c r="AI9">
         <v>70</v>
       </c>
       <c r="AJ9">
+        <v>38</v>
+      </c>
+      <c r="AK9">
         <v>32</v>
       </c>
-      <c r="AK9">
-        <v>27</v>
-      </c>
       <c r="AL9">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="AM9">
         <v>130</v>
@@ -2730,19 +2730,19 @@
         <v>25</v>
       </c>
       <c r="AO9">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AP9">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AQ9">
         <v>10.5</v>
       </c>
       <c r="AR9">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AS9">
-        <v>6.8</v>
+        <v>5.6</v>
       </c>
       <c r="AT9">
         <v>7.8</v>
@@ -2754,97 +2754,97 @@
         <v>12.5</v>
       </c>
       <c r="AW9">
-        <v>6.6</v>
+        <v>5.5</v>
       </c>
       <c r="AX9">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AY9">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="AZ9">
         <v>16</v>
       </c>
       <c r="BA9">
-        <v>6.8</v>
+        <v>5.6</v>
       </c>
       <c r="BB9">
-        <v>6</v>
+        <v>5.2</v>
       </c>
       <c r="BC9">
-        <v>5.9</v>
+        <v>5.1</v>
       </c>
       <c r="BD9">
-        <v>6.6</v>
+        <v>5.4</v>
       </c>
       <c r="BE9">
-        <v>7.2</v>
+        <v>5.8</v>
       </c>
       <c r="BF9">
-        <v>16.5</v>
+        <v>17.5</v>
       </c>
       <c r="BG9">
-        <v>6.6</v>
+        <v>5.5</v>
       </c>
       <c r="BH9">
         <v>3.25</v>
       </c>
       <c r="BI9">
-        <v>2.68</v>
+        <v>2.64</v>
       </c>
       <c r="BJ9">
         <v>10.5</v>
       </c>
       <c r="BK9">
-        <v>5.5</v>
+        <v>5.3</v>
       </c>
       <c r="BL9">
         <v>1000</v>
       </c>
       <c r="BM9">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="BN9">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="BO9">
         <v>4.1</v>
       </c>
       <c r="BP9">
-        <v>18</v>
+        <v>18.5</v>
       </c>
       <c r="BQ9">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="BR9">
         <v>1000</v>
       </c>
       <c r="BS9">
-        <v>8.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BT9">
         <v>7</v>
       </c>
       <c r="BU9">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="BV9">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="BW9">
-        <v>8.6</v>
+        <v>8</v>
       </c>
       <c r="BX9">
         <v>1000</v>
       </c>
       <c r="BY9">
-        <v>9.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="BZ9">
         <v>1000</v>
       </c>
       <c r="CA9">
-        <v>8.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="CB9" t="s">
         <v>107</v>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-08-11.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-08-11.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="128" uniqueCount="108">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="122" uniqueCount="104">
   <si>
     <t>League</t>
   </si>
@@ -256,9 +256,6 @@
     <t>SnapshotTS</t>
   </si>
   <si>
-    <t>Swedish Superettan</t>
-  </si>
-  <si>
     <t>South African Premier Division</t>
   </si>
   <si>
@@ -274,9 +271,6 @@
     <t>2026-08-11</t>
   </si>
   <si>
-    <t>17:00:00</t>
-  </si>
-  <si>
     <t>17:30:00</t>
   </si>
   <si>
@@ -289,9 +283,6 @@
     <t>23:00:00</t>
   </si>
   <si>
-    <t>Helsingborgs</t>
-  </si>
-  <si>
     <t>Chippa Utd</t>
   </si>
   <si>
@@ -313,9 +304,6 @@
     <t>Puerto Montt</t>
   </si>
   <si>
-    <t>Varnamo</t>
-  </si>
-  <si>
     <t>Richards Bay FC</t>
   </si>
   <si>
@@ -337,7 +325,7 @@
     <t>Union Espanola</t>
   </si>
   <si>
-    <t>2026-08-11 14:02:40</t>
+    <t>2026-08-11 16:11:59</t>
   </si>
 </sst>
 </file>
@@ -669,7 +657,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:CB9"/>
+  <dimension ref="A1:CB8"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:80">
@@ -919,232 +907,232 @@
         <v>80</v>
       </c>
       <c r="B2" t="s">
+        <v>84</v>
+      </c>
+      <c r="C2" t="s">
         <v>85</v>
       </c>
-      <c r="C2" t="s">
-        <v>86</v>
-      </c>
       <c r="D2" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="E2" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="F2">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="G2">
-        <v>3.1</v>
+        <v>6.6</v>
       </c>
       <c r="H2">
-        <v>2.36</v>
+        <v>5</v>
       </c>
       <c r="I2">
-        <v>2.4</v>
+        <v>5.4</v>
       </c>
       <c r="J2">
-        <v>3.9</v>
+        <v>1.53</v>
       </c>
       <c r="K2">
-        <v>4</v>
+        <v>1.57</v>
       </c>
       <c r="L2">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="M2">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="N2">
-        <v>5.4</v>
+        <v>0</v>
       </c>
       <c r="O2">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="P2">
-        <v>2.5</v>
+        <v>1.65</v>
       </c>
       <c r="Q2">
-        <v>1.66</v>
+        <v>2.46</v>
       </c>
       <c r="R2">
-        <v>1.6</v>
+        <v>1.09</v>
       </c>
       <c r="S2">
-        <v>2.66</v>
+        <v>10.5</v>
       </c>
       <c r="T2">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="U2">
-        <v>2.58</v>
+        <v>0</v>
       </c>
       <c r="V2">
-        <v>1.71</v>
+        <v>1.23</v>
       </c>
       <c r="W2">
-        <v>1.47</v>
+        <v>1.18</v>
       </c>
       <c r="X2">
-        <v>22</v>
+        <v>1000</v>
       </c>
       <c r="Y2">
-        <v>15</v>
+        <v>1000</v>
       </c>
       <c r="Z2">
+        <v>1000</v>
+      </c>
+      <c r="AA2">
+        <v>1000</v>
+      </c>
+      <c r="AB2">
+        <v>1000</v>
+      </c>
+      <c r="AC2">
+        <v>1.72</v>
+      </c>
+      <c r="AD2">
+        <v>6.4</v>
+      </c>
+      <c r="AE2">
+        <v>70</v>
+      </c>
+      <c r="AF2">
+        <v>1000</v>
+      </c>
+      <c r="AG2">
+        <v>7.4</v>
+      </c>
+      <c r="AH2">
+        <v>24</v>
+      </c>
+      <c r="AI2">
+        <v>240</v>
+      </c>
+      <c r="AJ2">
+        <v>1000</v>
+      </c>
+      <c r="AK2">
+        <v>80</v>
+      </c>
+      <c r="AL2">
+        <v>310</v>
+      </c>
+      <c r="AM2">
+        <v>1000</v>
+      </c>
+      <c r="AN2">
+        <v>1000</v>
+      </c>
+      <c r="AO2">
+        <v>1000</v>
+      </c>
+      <c r="AP2">
         <v>18</v>
       </c>
-      <c r="AA2">
-        <v>38</v>
-      </c>
-      <c r="AB2">
+      <c r="AQ2">
         <v>18</v>
       </c>
-      <c r="AC2">
-        <v>9.6</v>
-      </c>
-      <c r="AD2">
-        <v>12</v>
-      </c>
-      <c r="AE2">
-        <v>24</v>
-      </c>
-      <c r="AF2">
-        <v>26</v>
-      </c>
-      <c r="AG2">
-        <v>14</v>
-      </c>
-      <c r="AH2">
-        <v>15.5</v>
-      </c>
-      <c r="AI2">
-        <v>32</v>
-      </c>
-      <c r="AJ2">
-        <v>50</v>
-      </c>
-      <c r="AK2">
-        <v>29</v>
-      </c>
-      <c r="AL2">
-        <v>34</v>
-      </c>
-      <c r="AM2">
-        <v>60</v>
-      </c>
-      <c r="AN2">
-        <v>19</v>
-      </c>
-      <c r="AO2">
-        <v>13.5</v>
-      </c>
-      <c r="AP2">
-        <v>19.5</v>
-      </c>
-      <c r="AQ2">
-        <v>13</v>
-      </c>
       <c r="AR2">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="AS2">
-        <v>28</v>
+        <v>18</v>
       </c>
       <c r="AT2">
-        <v>14.5</v>
+        <v>18</v>
       </c>
       <c r="AU2">
-        <v>8.6</v>
+        <v>1.67</v>
       </c>
       <c r="AV2">
-        <v>10.5</v>
+        <v>5.7</v>
       </c>
       <c r="AW2">
-        <v>19.5</v>
+        <v>42</v>
       </c>
       <c r="AX2">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="AY2">
-        <v>12</v>
+        <v>6.6</v>
       </c>
       <c r="AZ2">
-        <v>13.5</v>
+        <v>20</v>
       </c>
       <c r="BA2">
-        <v>25</v>
+        <v>110</v>
       </c>
       <c r="BB2">
+        <v>18</v>
+      </c>
+      <c r="BC2">
         <v>44</v>
       </c>
-      <c r="BC2">
-        <v>25</v>
-      </c>
       <c r="BD2">
-        <v>29</v>
+        <v>150</v>
       </c>
       <c r="BE2">
-        <v>46</v>
+        <v>280</v>
       </c>
       <c r="BF2">
-        <v>17</v>
+        <v>290</v>
       </c>
       <c r="BG2">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="BH2">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="BI2">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="BJ2">
-        <v>8.6</v>
+        <v>0</v>
       </c>
       <c r="BK2">
-        <v>7.2</v>
+        <v>0</v>
       </c>
       <c r="BL2">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="BM2">
-        <v>55</v>
+        <v>0</v>
       </c>
       <c r="BN2">
-        <v>6.4</v>
+        <v>0</v>
       </c>
       <c r="BO2">
-        <v>5.5</v>
+        <v>0</v>
       </c>
       <c r="BP2">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="BQ2">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="BR2">
-        <v>34</v>
+        <v>0</v>
       </c>
       <c r="BS2">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="BT2">
-        <v>5.7</v>
+        <v>0</v>
       </c>
       <c r="BU2">
-        <v>5.1</v>
+        <v>0</v>
       </c>
       <c r="BV2">
-        <v>16.5</v>
+        <v>0</v>
       </c>
       <c r="BW2">
-        <v>14.5</v>
+        <v>0</v>
       </c>
       <c r="BX2">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="BY2">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="BZ2">
         <v>0</v>
@@ -1153,733 +1141,733 @@
         <v>0</v>
       </c>
       <c r="CB2" t="s">
-        <v>107</v>
+        <v>103</v>
       </c>
     </row>
     <row r="3" spans="1:80">
       <c r="A3" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B3" t="s">
+        <v>84</v>
+      </c>
+      <c r="C3" t="s">
         <v>85</v>
       </c>
-      <c r="C3" t="s">
-        <v>87</v>
-      </c>
       <c r="D3" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="E3" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="F3">
+        <v>1.4</v>
+      </c>
+      <c r="G3">
+        <v>1.43</v>
+      </c>
+      <c r="H3">
+        <v>20</v>
+      </c>
+      <c r="I3">
+        <v>25</v>
+      </c>
+      <c r="J3">
+        <v>3.9</v>
+      </c>
+      <c r="K3">
+        <v>4.1</v>
+      </c>
+      <c r="L3">
+        <v>0</v>
+      </c>
+      <c r="M3">
+        <v>0</v>
+      </c>
+      <c r="N3">
+        <v>0</v>
+      </c>
+      <c r="O3">
+        <v>0</v>
+      </c>
+      <c r="P3">
+        <v>0</v>
+      </c>
+      <c r="Q3">
+        <v>0</v>
+      </c>
+      <c r="R3">
+        <v>1.65</v>
+      </c>
+      <c r="S3">
+        <v>2.46</v>
+      </c>
+      <c r="T3">
+        <v>0</v>
+      </c>
+      <c r="U3">
+        <v>0</v>
+      </c>
+      <c r="V3">
+        <v>1.04</v>
+      </c>
+      <c r="W3">
         <v>3.3</v>
       </c>
-      <c r="G3">
-        <v>3.4</v>
-      </c>
-      <c r="H3">
-        <v>2.72</v>
-      </c>
-      <c r="I3">
-        <v>2.78</v>
-      </c>
-      <c r="J3">
-        <v>2.88</v>
-      </c>
-      <c r="K3">
-        <v>2.96</v>
-      </c>
-      <c r="L3">
+      <c r="X3">
+        <v>1000</v>
+      </c>
+      <c r="Y3">
+        <v>1000</v>
+      </c>
+      <c r="Z3">
+        <v>1000</v>
+      </c>
+      <c r="AA3">
+        <v>1000</v>
+      </c>
+      <c r="AB3">
+        <v>1000</v>
+      </c>
+      <c r="AC3">
+        <v>1000</v>
+      </c>
+      <c r="AD3">
+        <v>1000</v>
+      </c>
+      <c r="AE3">
+        <v>1000</v>
+      </c>
+      <c r="AF3">
+        <v>1000</v>
+      </c>
+      <c r="AG3">
+        <v>1.71</v>
+      </c>
+      <c r="AH3">
+        <v>4</v>
+      </c>
+      <c r="AI3">
+        <v>1000</v>
+      </c>
+      <c r="AJ3">
+        <v>1000</v>
+      </c>
+      <c r="AK3">
+        <v>730</v>
+      </c>
+      <c r="AL3">
+        <v>1000</v>
+      </c>
+      <c r="AM3">
+        <v>1000</v>
+      </c>
+      <c r="AN3">
+        <v>1000</v>
+      </c>
+      <c r="AO3">
+        <v>1000</v>
+      </c>
+      <c r="AP3">
+        <v>11</v>
+      </c>
+      <c r="AQ3">
+        <v>11</v>
+      </c>
+      <c r="AR3">
+        <v>11</v>
+      </c>
+      <c r="AS3">
+        <v>11</v>
+      </c>
+      <c r="AT3">
+        <v>11</v>
+      </c>
+      <c r="AU3">
+        <v>6.8</v>
+      </c>
+      <c r="AV3">
+        <v>6.8</v>
+      </c>
+      <c r="AW3">
+        <v>6.8</v>
+      </c>
+      <c r="AX3">
+        <v>11</v>
+      </c>
+      <c r="AY3">
         <v>1.66</v>
       </c>
-      <c r="M3">
-        <v>1.15</v>
-      </c>
-      <c r="N3">
-        <v>2.44</v>
-      </c>
-      <c r="O3">
-        <v>1.68</v>
-      </c>
-      <c r="P3">
-        <v>1.46</v>
-      </c>
-      <c r="Q3">
-        <v>2.96</v>
-      </c>
-      <c r="R3">
-        <v>1.16</v>
-      </c>
-      <c r="S3">
+      <c r="AZ3">
+        <v>3.6</v>
+      </c>
+      <c r="BA3">
         <v>6.8</v>
       </c>
-      <c r="T3">
-        <v>2.22</v>
-      </c>
-      <c r="U3">
-        <v>1.72</v>
-      </c>
-      <c r="V3">
-        <v>1.54</v>
-      </c>
-      <c r="W3">
-        <v>1.4</v>
-      </c>
-      <c r="X3">
-        <v>7.4</v>
-      </c>
-      <c r="Y3">
-        <v>8</v>
-      </c>
-      <c r="Z3">
-        <v>19</v>
-      </c>
-      <c r="AA3">
-        <v>150</v>
-      </c>
-      <c r="AB3">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AC3">
-        <v>7.4</v>
-      </c>
-      <c r="AD3">
-        <v>16</v>
-      </c>
-      <c r="AE3">
-        <v>55</v>
-      </c>
-      <c r="AF3">
-        <v>19</v>
-      </c>
-      <c r="AG3">
-        <v>16</v>
-      </c>
-      <c r="AH3">
-        <v>27</v>
-      </c>
-      <c r="AI3">
-        <v>170</v>
-      </c>
-      <c r="AJ3">
-        <v>65</v>
-      </c>
-      <c r="AK3">
-        <v>55</v>
-      </c>
-      <c r="AL3">
-        <v>230</v>
-      </c>
-      <c r="AM3">
-        <v>500</v>
-      </c>
-      <c r="AN3">
-        <v>75</v>
-      </c>
-      <c r="AO3">
-        <v>100</v>
-      </c>
-      <c r="AP3">
-        <v>6.4</v>
-      </c>
-      <c r="AQ3">
-        <v>6.6</v>
-      </c>
-      <c r="AR3">
-        <v>16</v>
-      </c>
-      <c r="AS3">
-        <v>25</v>
-      </c>
-      <c r="AT3">
-        <v>7</v>
-      </c>
-      <c r="AU3">
-        <v>6</v>
-      </c>
-      <c r="AV3">
-        <v>13</v>
-      </c>
-      <c r="AW3">
-        <v>24</v>
-      </c>
-      <c r="AX3">
-        <v>16.5</v>
-      </c>
-      <c r="AY3">
-        <v>13</v>
-      </c>
-      <c r="AZ3">
-        <v>15</v>
-      </c>
-      <c r="BA3">
-        <v>9.4</v>
-      </c>
       <c r="BB3">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="BC3">
-        <v>23</v>
+        <v>10.5</v>
       </c>
       <c r="BD3">
-        <v>34</v>
+        <v>6.8</v>
       </c>
       <c r="BE3">
-        <v>10</v>
+        <v>6.8</v>
       </c>
       <c r="BF3">
-        <v>22</v>
+        <v>6.8</v>
       </c>
       <c r="BG3">
-        <v>21</v>
+        <v>6.8</v>
       </c>
       <c r="BH3">
-        <v>2.68</v>
+        <v>0</v>
       </c>
       <c r="BI3">
-        <v>2.16</v>
+        <v>0</v>
       </c>
       <c r="BJ3">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="BK3">
-        <v>5.8</v>
+        <v>0</v>
       </c>
       <c r="BL3">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BM3">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="BN3">
-        <v>6.4</v>
+        <v>0</v>
       </c>
       <c r="BO3">
-        <v>4.7</v>
+        <v>0</v>
       </c>
       <c r="BP3">
-        <v>34</v>
+        <v>0</v>
       </c>
       <c r="BQ3">
-        <v>8.6</v>
+        <v>0</v>
       </c>
       <c r="BR3">
-        <v>60</v>
+        <v>0</v>
       </c>
       <c r="BS3">
-        <v>9.6</v>
+        <v>0</v>
       </c>
       <c r="BT3">
-        <v>5.6</v>
+        <v>0</v>
       </c>
       <c r="BU3">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="BV3">
-        <v>27</v>
+        <v>0</v>
       </c>
       <c r="BW3">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="BX3">
-        <v>55</v>
+        <v>0</v>
       </c>
       <c r="BY3">
-        <v>9.4</v>
+        <v>0</v>
       </c>
       <c r="BZ3">
-        <v>60</v>
+        <v>0</v>
       </c>
       <c r="CA3">
-        <v>9.6</v>
+        <v>0</v>
       </c>
       <c r="CB3" t="s">
-        <v>107</v>
+        <v>103</v>
       </c>
     </row>
     <row r="4" spans="1:80">
       <c r="A4" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B4" t="s">
+        <v>84</v>
+      </c>
+      <c r="C4" t="s">
         <v>85</v>
       </c>
-      <c r="C4" t="s">
-        <v>87</v>
-      </c>
       <c r="D4" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="E4" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="F4">
-        <v>7.4</v>
+        <v>7.8</v>
       </c>
       <c r="G4">
-        <v>8.4</v>
+        <v>9</v>
       </c>
       <c r="H4">
-        <v>1.56</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="I4">
-        <v>1.57</v>
+        <v>10.5</v>
       </c>
       <c r="J4">
-        <v>4.2</v>
+        <v>1.28</v>
       </c>
       <c r="K4">
-        <v>4.4</v>
+        <v>1.31</v>
       </c>
       <c r="L4">
-        <v>1.46</v>
+        <v>0</v>
       </c>
       <c r="M4">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="N4">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="O4">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="P4">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="Q4">
-        <v>2.16</v>
+        <v>0</v>
       </c>
       <c r="R4">
+        <v>0</v>
+      </c>
+      <c r="S4">
+        <v>0</v>
+      </c>
+      <c r="T4">
+        <v>0</v>
+      </c>
+      <c r="U4">
+        <v>0</v>
+      </c>
+      <c r="V4">
+        <v>1.1</v>
+      </c>
+      <c r="W4">
+        <v>1.14</v>
+      </c>
+      <c r="X4">
+        <v>1000</v>
+      </c>
+      <c r="Y4">
+        <v>1000</v>
+      </c>
+      <c r="Z4">
+        <v>1000</v>
+      </c>
+      <c r="AA4">
+        <v>1000</v>
+      </c>
+      <c r="AB4">
+        <v>1000</v>
+      </c>
+      <c r="AC4">
+        <v>1000</v>
+      </c>
+      <c r="AD4">
+        <v>1000</v>
+      </c>
+      <c r="AE4">
+        <v>1000</v>
+      </c>
+      <c r="AF4">
+        <v>1000</v>
+      </c>
+      <c r="AG4">
+        <v>1000</v>
+      </c>
+      <c r="AH4">
+        <v>1000</v>
+      </c>
+      <c r="AI4">
+        <v>1000</v>
+      </c>
+      <c r="AJ4">
+        <v>1000</v>
+      </c>
+      <c r="AK4">
+        <v>1000</v>
+      </c>
+      <c r="AL4">
+        <v>1000</v>
+      </c>
+      <c r="AM4">
+        <v>1.35</v>
+      </c>
+      <c r="AN4">
+        <v>11</v>
+      </c>
+      <c r="AO4">
+        <v>13</v>
+      </c>
+      <c r="AP4">
+        <v>11</v>
+      </c>
+      <c r="AQ4">
+        <v>11</v>
+      </c>
+      <c r="AR4">
+        <v>11</v>
+      </c>
+      <c r="AS4">
+        <v>11</v>
+      </c>
+      <c r="AT4">
+        <v>11</v>
+      </c>
+      <c r="AU4">
+        <v>11</v>
+      </c>
+      <c r="AV4">
+        <v>11</v>
+      </c>
+      <c r="AW4">
+        <v>11</v>
+      </c>
+      <c r="AX4">
+        <v>11</v>
+      </c>
+      <c r="AY4">
+        <v>11</v>
+      </c>
+      <c r="AZ4">
+        <v>11</v>
+      </c>
+      <c r="BA4">
+        <v>11</v>
+      </c>
+      <c r="BB4">
+        <v>11</v>
+      </c>
+      <c r="BC4">
+        <v>11</v>
+      </c>
+      <c r="BD4">
+        <v>11</v>
+      </c>
+      <c r="BE4">
         <v>1.3</v>
       </c>
-      <c r="S4">
-        <v>4.1</v>
-      </c>
-      <c r="T4">
-        <v>2.24</v>
-      </c>
-      <c r="U4">
-        <v>1.74</v>
-      </c>
-      <c r="V4">
-        <v>2.58</v>
-      </c>
-      <c r="W4">
-        <v>1.15</v>
-      </c>
-      <c r="X4">
-        <v>15.5</v>
-      </c>
-      <c r="Y4">
-        <v>8</v>
-      </c>
-      <c r="Z4">
-        <v>17.5</v>
-      </c>
-      <c r="AA4">
-        <v>30</v>
-      </c>
-      <c r="AB4">
-        <v>970</v>
-      </c>
-      <c r="AC4">
-        <v>12</v>
-      </c>
-      <c r="AD4">
-        <v>10.5</v>
-      </c>
-      <c r="AE4">
-        <v>28</v>
-      </c>
-      <c r="AF4">
-        <v>330</v>
-      </c>
-      <c r="AG4">
-        <v>60</v>
-      </c>
-      <c r="AH4">
-        <v>50</v>
-      </c>
-      <c r="AI4">
-        <v>120</v>
-      </c>
-      <c r="AJ4">
-        <v>700</v>
-      </c>
-      <c r="AK4">
-        <v>700</v>
-      </c>
-      <c r="AL4">
-        <v>700</v>
-      </c>
-      <c r="AM4">
-        <v>700</v>
-      </c>
-      <c r="AN4">
-        <v>1000</v>
-      </c>
-      <c r="AO4">
-        <v>29</v>
-      </c>
-      <c r="AP4">
-        <v>6.2</v>
-      </c>
-      <c r="AQ4">
-        <v>4.2</v>
-      </c>
-      <c r="AR4">
-        <v>7</v>
-      </c>
-      <c r="AS4">
-        <v>12</v>
-      </c>
-      <c r="AT4">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AU4">
-        <v>7.4</v>
-      </c>
-      <c r="AV4">
-        <v>7.4</v>
-      </c>
-      <c r="AW4">
-        <v>10.5</v>
-      </c>
-      <c r="AX4">
-        <v>5.7</v>
-      </c>
-      <c r="AY4">
-        <v>14.5</v>
-      </c>
-      <c r="AZ4">
-        <v>13.5</v>
-      </c>
-      <c r="BA4">
-        <v>5.5</v>
-      </c>
-      <c r="BB4">
-        <v>4.7</v>
-      </c>
-      <c r="BC4">
-        <v>5.8</v>
-      </c>
-      <c r="BD4">
-        <v>7</v>
-      </c>
-      <c r="BE4">
-        <v>3.95</v>
-      </c>
       <c r="BF4">
-        <v>4.7</v>
+        <v>7.6</v>
       </c>
       <c r="BG4">
-        <v>3.5</v>
+        <v>8.6</v>
       </c>
       <c r="BH4">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BI4">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="BJ4">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BK4">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="BL4">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BM4">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="BN4">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BO4">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="BP4">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BQ4">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="BR4">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BS4">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="BT4">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BU4">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="BV4">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BW4">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="BX4">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BY4">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="BZ4">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="CA4">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="CB4" t="s">
-        <v>107</v>
+        <v>103</v>
       </c>
     </row>
     <row r="5" spans="1:80">
       <c r="A5" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B5" t="s">
+        <v>84</v>
+      </c>
+      <c r="C5" t="s">
         <v>85</v>
       </c>
-      <c r="C5" t="s">
-        <v>87</v>
-      </c>
       <c r="D5" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="E5" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="F5">
-        <v>2.56</v>
+        <v>5.7</v>
       </c>
       <c r="G5">
-        <v>2.7</v>
+        <v>6.4</v>
       </c>
       <c r="H5">
+        <v>9.6</v>
+      </c>
+      <c r="I5">
+        <v>11.5</v>
+      </c>
+      <c r="J5">
+        <v>1.35</v>
+      </c>
+      <c r="K5">
+        <v>1.38</v>
+      </c>
+      <c r="L5">
+        <v>0</v>
+      </c>
+      <c r="M5">
         <v>3.5</v>
       </c>
-      <c r="I5">
-        <v>3.8</v>
-      </c>
-      <c r="J5">
-        <v>2.86</v>
-      </c>
-      <c r="K5">
-        <v>2.92</v>
-      </c>
-      <c r="L5">
-        <v>1.73</v>
-      </c>
-      <c r="M5">
-        <v>1.18</v>
-      </c>
       <c r="N5">
-        <v>2.22</v>
+        <v>1.04</v>
       </c>
       <c r="O5">
-        <v>1.78</v>
+        <v>23</v>
       </c>
       <c r="P5">
-        <v>1.37</v>
+        <v>1.01</v>
       </c>
       <c r="Q5">
-        <v>3.4</v>
+        <v>110</v>
       </c>
       <c r="R5">
-        <v>1.13</v>
+        <v>1.01</v>
       </c>
       <c r="S5">
-        <v>7.8</v>
+        <v>300</v>
       </c>
       <c r="T5">
-        <v>2.16</v>
+        <v>26</v>
       </c>
       <c r="U5">
-        <v>1.5</v>
+        <v>1.02</v>
       </c>
       <c r="V5">
-        <v>1.36</v>
+        <v>1.11</v>
       </c>
       <c r="W5">
-        <v>1.58</v>
+        <v>1.19</v>
       </c>
       <c r="X5">
-        <v>7.6</v>
+        <v>1.42</v>
       </c>
       <c r="Y5">
-        <v>8.6</v>
+        <v>11.5</v>
       </c>
       <c r="Z5">
-        <v>29</v>
+        <v>240</v>
       </c>
       <c r="AA5">
-        <v>240</v>
+        <v>1000</v>
       </c>
       <c r="AB5">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="AC5">
-        <v>7.2</v>
+        <v>48</v>
       </c>
       <c r="AD5">
-        <v>19</v>
+        <v>1000</v>
       </c>
       <c r="AE5">
-        <v>95</v>
+        <v>1000</v>
       </c>
       <c r="AF5">
-        <v>15</v>
+        <v>100</v>
       </c>
       <c r="AG5">
-        <v>14.5</v>
+        <v>1000</v>
       </c>
       <c r="AH5">
-        <v>36</v>
+        <v>1000</v>
       </c>
       <c r="AI5">
-        <v>540</v>
+        <v>1000</v>
       </c>
       <c r="AJ5">
-        <v>60</v>
+        <v>1000</v>
       </c>
       <c r="AK5">
-        <v>60</v>
+        <v>1000</v>
       </c>
       <c r="AL5">
-        <v>230</v>
+        <v>1000</v>
       </c>
       <c r="AM5">
-        <v>500</v>
+        <v>1000</v>
       </c>
       <c r="AN5">
-        <v>75</v>
+        <v>1000</v>
       </c>
       <c r="AO5">
-        <v>150</v>
+        <v>1000</v>
       </c>
       <c r="AP5">
-        <v>5.8</v>
+        <v>1.39</v>
       </c>
       <c r="AQ5">
-        <v>7.4</v>
+        <v>10</v>
       </c>
       <c r="AR5">
-        <v>20</v>
+        <v>100</v>
       </c>
       <c r="AS5">
-        <v>7.8</v>
+        <v>80</v>
       </c>
       <c r="AT5">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="AU5">
-        <v>6.2</v>
+        <v>38</v>
       </c>
       <c r="AV5">
-        <v>16</v>
+        <v>90</v>
       </c>
       <c r="AW5">
-        <v>8</v>
+        <v>80</v>
       </c>
       <c r="AX5">
-        <v>13</v>
+        <v>55</v>
       </c>
       <c r="AY5">
-        <v>12.5</v>
+        <v>280</v>
       </c>
       <c r="AZ5">
-        <v>15</v>
+        <v>80</v>
       </c>
       <c r="BA5">
-        <v>29</v>
+        <v>80</v>
       </c>
       <c r="BB5">
-        <v>20</v>
+        <v>120</v>
       </c>
       <c r="BC5">
-        <v>40</v>
+        <v>80</v>
       </c>
       <c r="BD5">
-        <v>7.8</v>
+        <v>80</v>
       </c>
       <c r="BE5">
-        <v>8.199999999999999</v>
+        <v>19.5</v>
       </c>
       <c r="BF5">
-        <v>7.6</v>
+        <v>130</v>
       </c>
       <c r="BG5">
-        <v>8</v>
+        <v>130</v>
       </c>
       <c r="BH5">
-        <v>2.72</v>
+        <v>0</v>
       </c>
       <c r="BI5">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="BJ5">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="BK5">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="BL5">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BM5">
-        <v>5.5</v>
+        <v>0</v>
       </c>
       <c r="BN5">
-        <v>6.2</v>
+        <v>0</v>
       </c>
       <c r="BO5">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="BP5">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="BQ5">
-        <v>4.7</v>
+        <v>0</v>
       </c>
       <c r="BR5">
-        <v>70</v>
+        <v>0</v>
       </c>
       <c r="BS5">
-        <v>5.1</v>
+        <v>0</v>
       </c>
       <c r="BT5">
-        <v>7.8</v>
+        <v>0</v>
       </c>
       <c r="BU5">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="BV5">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="BW5">
-        <v>4.9</v>
+        <v>0</v>
       </c>
       <c r="BX5">
-        <v>90</v>
+        <v>0</v>
       </c>
       <c r="BY5">
-        <v>5.2</v>
+        <v>0</v>
       </c>
       <c r="BZ5">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="CA5">
-        <v>5.2</v>
+        <v>0</v>
       </c>
       <c r="CB5" t="s">
-        <v>107</v>
+        <v>103</v>
       </c>
     </row>
     <row r="6" spans="1:80">
@@ -1887,241 +1875,241 @@
         <v>81</v>
       </c>
       <c r="B6" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="C6" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="D6" t="s">
+        <v>93</v>
+      </c>
+      <c r="E6" t="s">
+        <v>100</v>
+      </c>
+      <c r="F6">
+        <v>1.75</v>
+      </c>
+      <c r="G6">
+        <v>1.76</v>
+      </c>
+      <c r="H6">
+        <v>6.4</v>
+      </c>
+      <c r="I6">
+        <v>6.6</v>
+      </c>
+      <c r="J6">
+        <v>3.6</v>
+      </c>
+      <c r="K6">
+        <v>3.7</v>
+      </c>
+      <c r="L6">
+        <v>1.58</v>
+      </c>
+      <c r="M6">
+        <v>1.12</v>
+      </c>
+      <c r="N6">
+        <v>2.8</v>
+      </c>
+      <c r="O6">
+        <v>1.53</v>
+      </c>
+      <c r="P6">
+        <v>1.58</v>
+      </c>
+      <c r="Q6">
+        <v>2.64</v>
+      </c>
+      <c r="R6">
+        <v>1.21</v>
+      </c>
+      <c r="S6">
+        <v>5.4</v>
+      </c>
+      <c r="T6">
+        <v>2.38</v>
+      </c>
+      <c r="U6">
+        <v>1.66</v>
+      </c>
+      <c r="V6">
+        <v>1.17</v>
+      </c>
+      <c r="W6">
+        <v>2.3</v>
+      </c>
+      <c r="X6">
+        <v>9.4</v>
+      </c>
+      <c r="Y6">
+        <v>15.5</v>
+      </c>
+      <c r="Z6">
+        <v>50</v>
+      </c>
+      <c r="AA6">
+        <v>230</v>
+      </c>
+      <c r="AB6">
+        <v>5.8</v>
+      </c>
+      <c r="AC6">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AD6">
+        <v>26</v>
+      </c>
+      <c r="AE6">
+        <v>140</v>
+      </c>
+      <c r="AF6">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AG6">
+        <v>11</v>
+      </c>
+      <c r="AH6">
+        <v>34</v>
+      </c>
+      <c r="AI6">
+        <v>160</v>
+      </c>
+      <c r="AJ6">
+        <v>18</v>
+      </c>
+      <c r="AK6">
+        <v>23</v>
+      </c>
+      <c r="AL6">
+        <v>100</v>
+      </c>
+      <c r="AM6">
+        <v>280</v>
+      </c>
+      <c r="AN6">
+        <v>18.5</v>
+      </c>
+      <c r="AO6">
+        <v>280</v>
+      </c>
+      <c r="AP6">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AQ6">
+        <v>15</v>
+      </c>
+      <c r="AR6">
+        <v>42</v>
+      </c>
+      <c r="AS6">
+        <v>60</v>
+      </c>
+      <c r="AT6">
+        <v>5.6</v>
+      </c>
+      <c r="AU6">
+        <v>7.8</v>
+      </c>
+      <c r="AV6">
+        <v>24</v>
+      </c>
+      <c r="AW6">
+        <v>100</v>
+      </c>
+      <c r="AX6">
+        <v>7.8</v>
+      </c>
+      <c r="AY6">
+        <v>10</v>
+      </c>
+      <c r="AZ6">
+        <v>29</v>
+      </c>
+      <c r="BA6">
         <v>95</v>
       </c>
-      <c r="E6" t="s">
+      <c r="BB6">
+        <v>16.5</v>
+      </c>
+      <c r="BC6">
+        <v>21</v>
+      </c>
+      <c r="BD6">
+        <v>50</v>
+      </c>
+      <c r="BE6">
+        <v>150</v>
+      </c>
+      <c r="BF6">
+        <v>17</v>
+      </c>
+      <c r="BG6">
+        <v>27</v>
+      </c>
+      <c r="BH6">
+        <v>2.72</v>
+      </c>
+      <c r="BI6">
+        <v>2.64</v>
+      </c>
+      <c r="BJ6">
+        <v>12.5</v>
+      </c>
+      <c r="BK6">
+        <v>11</v>
+      </c>
+      <c r="BL6">
+        <v>1000</v>
+      </c>
+      <c r="BM6">
+        <v>180</v>
+      </c>
+      <c r="BN6">
+        <v>3.9</v>
+      </c>
+      <c r="BO6">
+        <v>3.6</v>
+      </c>
+      <c r="BP6">
+        <v>13.5</v>
+      </c>
+      <c r="BQ6">
+        <v>11.5</v>
+      </c>
+      <c r="BR6">
+        <v>38</v>
+      </c>
+      <c r="BS6">
+        <v>2.34</v>
+      </c>
+      <c r="BT6">
+        <v>9.4</v>
+      </c>
+      <c r="BU6">
+        <v>8.6</v>
+      </c>
+      <c r="BV6">
+        <v>1000</v>
+      </c>
+      <c r="BW6">
+        <v>21</v>
+      </c>
+      <c r="BX6">
+        <v>1000</v>
+      </c>
+      <c r="BY6">
+        <v>22</v>
+      </c>
+      <c r="BZ6">
+        <v>36</v>
+      </c>
+      <c r="CA6">
+        <v>16</v>
+      </c>
+      <c r="CB6" t="s">
         <v>103</v>
-      </c>
-      <c r="F6">
-        <v>2.5</v>
-      </c>
-      <c r="G6">
-        <v>2.66</v>
-      </c>
-      <c r="H6">
-        <v>3.65</v>
-      </c>
-      <c r="I6">
-        <v>3.9</v>
-      </c>
-      <c r="J6">
-        <v>2.78</v>
-      </c>
-      <c r="K6">
-        <v>2.94</v>
-      </c>
-      <c r="L6">
-        <v>1.72</v>
-      </c>
-      <c r="M6">
-        <v>1.18</v>
-      </c>
-      <c r="N6">
-        <v>2.26</v>
-      </c>
-      <c r="O6">
-        <v>1.73</v>
-      </c>
-      <c r="P6">
-        <v>1.39</v>
-      </c>
-      <c r="Q6">
-        <v>3.3</v>
-      </c>
-      <c r="R6">
-        <v>1.13</v>
-      </c>
-      <c r="S6">
-        <v>7.4</v>
-      </c>
-      <c r="T6">
-        <v>2.4</v>
-      </c>
-      <c r="U6">
-        <v>1.62</v>
-      </c>
-      <c r="V6">
-        <v>1.34</v>
-      </c>
-      <c r="W6">
-        <v>1.6</v>
-      </c>
-      <c r="X6">
-        <v>6.8</v>
-      </c>
-      <c r="Y6">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="Z6">
-        <v>55</v>
-      </c>
-      <c r="AA6">
-        <v>290</v>
-      </c>
-      <c r="AB6">
-        <v>6.8</v>
-      </c>
-      <c r="AC6">
-        <v>7.2</v>
-      </c>
-      <c r="AD6">
-        <v>30</v>
-      </c>
-      <c r="AE6">
-        <v>440</v>
-      </c>
-      <c r="AF6">
-        <v>14.5</v>
-      </c>
-      <c r="AG6">
-        <v>14</v>
-      </c>
-      <c r="AH6">
-        <v>85</v>
-      </c>
-      <c r="AI6">
-        <v>500</v>
-      </c>
-      <c r="AJ6">
-        <v>170</v>
-      </c>
-      <c r="AK6">
-        <v>150</v>
-      </c>
-      <c r="AL6">
-        <v>460</v>
-      </c>
-      <c r="AM6">
-        <v>500</v>
-      </c>
-      <c r="AN6">
-        <v>80</v>
-      </c>
-      <c r="AO6">
-        <v>140</v>
-      </c>
-      <c r="AP6">
-        <v>5.9</v>
-      </c>
-      <c r="AQ6">
-        <v>7.8</v>
-      </c>
-      <c r="AR6">
-        <v>21</v>
-      </c>
-      <c r="AS6">
-        <v>11</v>
-      </c>
-      <c r="AT6">
-        <v>5.8</v>
-      </c>
-      <c r="AU6">
-        <v>6.2</v>
-      </c>
-      <c r="AV6">
-        <v>16</v>
-      </c>
-      <c r="AW6">
-        <v>46</v>
-      </c>
-      <c r="AX6">
-        <v>12.5</v>
-      </c>
-      <c r="AY6">
-        <v>12</v>
-      </c>
-      <c r="AZ6">
-        <v>14.5</v>
-      </c>
-      <c r="BA6">
-        <v>11</v>
-      </c>
-      <c r="BB6">
-        <v>36</v>
-      </c>
-      <c r="BC6">
-        <v>30</v>
-      </c>
-      <c r="BD6">
-        <v>28</v>
-      </c>
-      <c r="BE6">
-        <v>12</v>
-      </c>
-      <c r="BF6">
-        <v>34</v>
-      </c>
-      <c r="BG6">
-        <v>11.5</v>
-      </c>
-      <c r="BH6">
-        <v>2.42</v>
-      </c>
-      <c r="BI6">
-        <v>2.1</v>
-      </c>
-      <c r="BJ6">
-        <v>13</v>
-      </c>
-      <c r="BK6">
-        <v>7.2</v>
-      </c>
-      <c r="BL6">
-        <v>1000</v>
-      </c>
-      <c r="BM6">
-        <v>2.08</v>
-      </c>
-      <c r="BN6">
-        <v>5.2</v>
-      </c>
-      <c r="BO6">
-        <v>3.95</v>
-      </c>
-      <c r="BP6">
-        <v>26</v>
-      </c>
-      <c r="BQ6">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="BR6">
-        <v>1000</v>
-      </c>
-      <c r="BS6">
-        <v>12.5</v>
-      </c>
-      <c r="BT6">
-        <v>6.8</v>
-      </c>
-      <c r="BU6">
-        <v>5.1</v>
-      </c>
-      <c r="BV6">
-        <v>1000</v>
-      </c>
-      <c r="BW6">
-        <v>11.5</v>
-      </c>
-      <c r="BX6">
-        <v>1000</v>
-      </c>
-      <c r="BY6">
-        <v>13</v>
-      </c>
-      <c r="BZ6">
-        <v>1000</v>
-      </c>
-      <c r="CA6">
-        <v>13</v>
-      </c>
-      <c r="CB6" t="s">
-        <v>107</v>
       </c>
     </row>
     <row r="7" spans="1:80">
@@ -2129,241 +2117,241 @@
         <v>82</v>
       </c>
       <c r="B7" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="C7" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="D7" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="E7" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="F7">
-        <v>1.74</v>
+        <v>2.92</v>
       </c>
       <c r="G7">
-        <v>1.76</v>
+        <v>2.96</v>
       </c>
       <c r="H7">
-        <v>6.2</v>
+        <v>2.86</v>
       </c>
       <c r="I7">
+        <v>2.88</v>
+      </c>
+      <c r="J7">
+        <v>3.2</v>
+      </c>
+      <c r="K7">
+        <v>3.25</v>
+      </c>
+      <c r="L7">
+        <v>1.52</v>
+      </c>
+      <c r="M7">
+        <v>1.1</v>
+      </c>
+      <c r="N7">
+        <v>3.15</v>
+      </c>
+      <c r="O7">
+        <v>1.45</v>
+      </c>
+      <c r="P7">
+        <v>1.72</v>
+      </c>
+      <c r="Q7">
+        <v>2.36</v>
+      </c>
+      <c r="R7">
+        <v>1.26</v>
+      </c>
+      <c r="S7">
+        <v>4.6</v>
+      </c>
+      <c r="T7">
+        <v>1.92</v>
+      </c>
+      <c r="U7">
+        <v>2</v>
+      </c>
+      <c r="V7">
+        <v>1.53</v>
+      </c>
+      <c r="W7">
+        <v>1.51</v>
+      </c>
+      <c r="X7">
+        <v>11</v>
+      </c>
+      <c r="Y7">
+        <v>9.6</v>
+      </c>
+      <c r="Z7">
+        <v>17.5</v>
+      </c>
+      <c r="AA7">
+        <v>46</v>
+      </c>
+      <c r="AB7">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AC7">
+        <v>7.2</v>
+      </c>
+      <c r="AD7">
+        <v>13</v>
+      </c>
+      <c r="AE7">
+        <v>36</v>
+      </c>
+      <c r="AF7">
+        <v>19</v>
+      </c>
+      <c r="AG7">
+        <v>13.5</v>
+      </c>
+      <c r="AH7">
+        <v>19.5</v>
+      </c>
+      <c r="AI7">
+        <v>55</v>
+      </c>
+      <c r="AJ7">
+        <v>55</v>
+      </c>
+      <c r="AK7">
+        <v>38</v>
+      </c>
+      <c r="AL7">
+        <v>55</v>
+      </c>
+      <c r="AM7">
+        <v>130</v>
+      </c>
+      <c r="AN7">
+        <v>40</v>
+      </c>
+      <c r="AO7">
+        <v>38</v>
+      </c>
+      <c r="AP7">
+        <v>9.6</v>
+      </c>
+      <c r="AQ7">
+        <v>9</v>
+      </c>
+      <c r="AR7">
+        <v>15</v>
+      </c>
+      <c r="AS7">
+        <v>40</v>
+      </c>
+      <c r="AT7">
+        <v>9</v>
+      </c>
+      <c r="AU7">
         <v>6.6</v>
       </c>
-      <c r="J7">
-        <v>3.65</v>
-      </c>
-      <c r="K7">
-        <v>3.7</v>
-      </c>
-      <c r="L7">
-        <v>1.57</v>
-      </c>
-      <c r="M7">
-        <v>1.11</v>
-      </c>
-      <c r="N7">
-        <v>2.82</v>
-      </c>
-      <c r="O7">
-        <v>1.53</v>
-      </c>
-      <c r="P7">
-        <v>1.61</v>
-      </c>
-      <c r="Q7">
-        <v>2.6</v>
-      </c>
-      <c r="R7">
-        <v>1.21</v>
-      </c>
-      <c r="S7">
-        <v>5.3</v>
-      </c>
-      <c r="T7">
-        <v>2.38</v>
-      </c>
-      <c r="U7">
-        <v>1.69</v>
-      </c>
-      <c r="V7">
-        <v>1.17</v>
-      </c>
-      <c r="W7">
-        <v>2.3</v>
-      </c>
-      <c r="X7">
-        <v>9.6</v>
-      </c>
-      <c r="Y7">
-        <v>14.5</v>
-      </c>
-      <c r="Z7">
+      <c r="AV7">
+        <v>11.5</v>
+      </c>
+      <c r="AW7">
+        <v>30</v>
+      </c>
+      <c r="AX7">
+        <v>17</v>
+      </c>
+      <c r="AY7">
+        <v>12</v>
+      </c>
+      <c r="AZ7">
+        <v>17</v>
+      </c>
+      <c r="BA7">
+        <v>46</v>
+      </c>
+      <c r="BB7">
+        <v>44</v>
+      </c>
+      <c r="BC7">
+        <v>34</v>
+      </c>
+      <c r="BD7">
         <v>48</v>
       </c>
-      <c r="AA7">
-        <v>230</v>
-      </c>
-      <c r="AB7">
+      <c r="BE7">
+        <v>100</v>
+      </c>
+      <c r="BF7">
+        <v>34</v>
+      </c>
+      <c r="BG7">
+        <v>32</v>
+      </c>
+      <c r="BH7">
+        <v>2.98</v>
+      </c>
+      <c r="BI7">
+        <v>2.76</v>
+      </c>
+      <c r="BJ7">
+        <v>10.5</v>
+      </c>
+      <c r="BK7">
+        <v>6.6</v>
+      </c>
+      <c r="BL7">
+        <v>1000</v>
+      </c>
+      <c r="BM7">
+        <v>130</v>
+      </c>
+      <c r="BN7">
         <v>5.9</v>
       </c>
-      <c r="AC7">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AD7">
-        <v>26</v>
-      </c>
-      <c r="AE7">
-        <v>140</v>
-      </c>
-      <c r="AF7">
-        <v>8.6</v>
-      </c>
-      <c r="AG7">
-        <v>11</v>
-      </c>
-      <c r="AH7">
-        <v>32</v>
-      </c>
-      <c r="AI7">
-        <v>260</v>
-      </c>
-      <c r="AJ7">
-        <v>18</v>
-      </c>
-      <c r="AK7">
+      <c r="BO7">
+        <v>5.2</v>
+      </c>
+      <c r="BP7">
+        <v>25</v>
+      </c>
+      <c r="BQ7">
+        <v>10</v>
+      </c>
+      <c r="BR7">
+        <v>42</v>
+      </c>
+      <c r="BS7">
+        <v>12.5</v>
+      </c>
+      <c r="BT7">
+        <v>5.6</v>
+      </c>
+      <c r="BU7">
+        <v>5</v>
+      </c>
+      <c r="BV7">
         <v>23</v>
       </c>
-      <c r="AL7">
-        <v>75</v>
-      </c>
-      <c r="AM7">
-        <v>250</v>
-      </c>
-      <c r="AN7">
-        <v>18</v>
-      </c>
-      <c r="AO7">
-        <v>240</v>
-      </c>
-      <c r="AP7">
-        <v>9</v>
-      </c>
-      <c r="AQ7">
-        <v>14</v>
-      </c>
-      <c r="AR7">
-        <v>42</v>
-      </c>
-      <c r="AS7">
-        <v>24</v>
-      </c>
-      <c r="AT7">
-        <v>5.6</v>
-      </c>
-      <c r="AU7">
-        <v>7.8</v>
-      </c>
-      <c r="AV7">
-        <v>23</v>
-      </c>
-      <c r="AW7">
-        <v>95</v>
-      </c>
-      <c r="AX7">
-        <v>8.4</v>
-      </c>
-      <c r="AY7">
+      <c r="BW7">
         <v>10</v>
       </c>
-      <c r="AZ7">
-        <v>28</v>
-      </c>
-      <c r="BA7">
-        <v>22</v>
-      </c>
-      <c r="BB7">
-        <v>16.5</v>
-      </c>
-      <c r="BC7">
-        <v>21</v>
-      </c>
-      <c r="BD7">
-        <v>50</v>
-      </c>
-      <c r="BE7">
-        <v>150</v>
-      </c>
-      <c r="BF7">
-        <v>16</v>
-      </c>
-      <c r="BG7">
-        <v>24</v>
-      </c>
-      <c r="BH7">
-        <v>2.82</v>
-      </c>
-      <c r="BI7">
-        <v>2.46</v>
-      </c>
-      <c r="BJ7">
-        <v>12.5</v>
-      </c>
-      <c r="BK7">
-        <v>7.6</v>
-      </c>
-      <c r="BL7">
-        <v>1000</v>
-      </c>
-      <c r="BM7">
-        <v>180</v>
-      </c>
-      <c r="BN7">
-        <v>4</v>
-      </c>
-      <c r="BO7">
-        <v>3.6</v>
-      </c>
-      <c r="BP7">
-        <v>13</v>
-      </c>
-      <c r="BQ7">
-        <v>7.8</v>
-      </c>
-      <c r="BR7">
-        <v>1000</v>
-      </c>
-      <c r="BS7">
-        <v>13</v>
-      </c>
-      <c r="BT7">
-        <v>9.6</v>
-      </c>
-      <c r="BU7">
-        <v>6.4</v>
-      </c>
-      <c r="BV7">
-        <v>1000</v>
-      </c>
-      <c r="BW7">
-        <v>15.5</v>
-      </c>
       <c r="BX7">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="BY7">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="BZ7">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="CA7">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="CB7" t="s">
-        <v>107</v>
+        <v>103</v>
       </c>
     </row>
     <row r="8" spans="1:80">
@@ -2371,483 +2359,241 @@
         <v>83</v>
       </c>
       <c r="B8" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="C8" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="D8" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="E8" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="F8">
-        <v>2.92</v>
+        <v>2.24</v>
       </c>
       <c r="G8">
-        <v>3</v>
+        <v>2.36</v>
       </c>
       <c r="H8">
-        <v>2.8</v>
+        <v>3.45</v>
       </c>
       <c r="I8">
-        <v>2.88</v>
+        <v>3.75</v>
       </c>
       <c r="J8">
-        <v>3.2</v>
+        <v>3.35</v>
       </c>
       <c r="K8">
-        <v>3.25</v>
+        <v>3.55</v>
       </c>
       <c r="L8">
-        <v>1.5</v>
+        <v>1.45</v>
       </c>
       <c r="M8">
-        <v>1.1</v>
+        <v>1.08</v>
       </c>
       <c r="N8">
-        <v>3.15</v>
+        <v>3.4</v>
       </c>
       <c r="O8">
-        <v>1.44</v>
+        <v>1.37</v>
       </c>
       <c r="P8">
-        <v>1.71</v>
+        <v>1.79</v>
       </c>
       <c r="Q8">
-        <v>2.34</v>
+        <v>2.16</v>
       </c>
       <c r="R8">
-        <v>1.26</v>
+        <v>1.3</v>
       </c>
       <c r="S8">
-        <v>4.5</v>
+        <v>4</v>
       </c>
       <c r="T8">
-        <v>1.91</v>
+        <v>1.85</v>
       </c>
       <c r="U8">
-        <v>2</v>
+        <v>2.04</v>
       </c>
       <c r="V8">
-        <v>1.53</v>
+        <v>1.36</v>
       </c>
       <c r="W8">
-        <v>1.5</v>
+        <v>1.73</v>
       </c>
       <c r="X8">
-        <v>10.5</v>
+        <v>14</v>
       </c>
       <c r="Y8">
+        <v>14.5</v>
+      </c>
+      <c r="Z8">
+        <v>26</v>
+      </c>
+      <c r="AA8">
+        <v>80</v>
+      </c>
+      <c r="AB8">
         <v>9.800000000000001</v>
       </c>
-      <c r="Z8">
-        <v>17.5</v>
-      </c>
-      <c r="AA8">
-        <v>46</v>
-      </c>
-      <c r="AB8">
-        <v>10</v>
-      </c>
       <c r="AC8">
-        <v>7.4</v>
+        <v>8</v>
       </c>
       <c r="AD8">
+        <v>17</v>
+      </c>
+      <c r="AE8">
+        <v>55</v>
+      </c>
+      <c r="AF8">
+        <v>16.5</v>
+      </c>
+      <c r="AG8">
         <v>13</v>
       </c>
-      <c r="AE8">
-        <v>36</v>
-      </c>
-      <c r="AF8">
-        <v>18.5</v>
-      </c>
-      <c r="AG8">
-        <v>13.5</v>
-      </c>
       <c r="AH8">
-        <v>19.5</v>
+        <v>22</v>
       </c>
       <c r="AI8">
-        <v>55</v>
+        <v>70</v>
       </c>
       <c r="AJ8">
-        <v>55</v>
+        <v>38</v>
       </c>
       <c r="AK8">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="AL8">
-        <v>55</v>
+        <v>48</v>
       </c>
       <c r="AM8">
         <v>130</v>
       </c>
       <c r="AN8">
-        <v>42</v>
+        <v>23</v>
       </c>
       <c r="AO8">
-        <v>36</v>
+        <v>55</v>
       </c>
       <c r="AP8">
+        <v>10</v>
+      </c>
+      <c r="AQ8">
+        <v>10.5</v>
+      </c>
+      <c r="AR8">
+        <v>20</v>
+      </c>
+      <c r="AS8">
+        <v>5.9</v>
+      </c>
+      <c r="AT8">
+        <v>7.8</v>
+      </c>
+      <c r="AU8">
+        <v>6.4</v>
+      </c>
+      <c r="AV8">
+        <v>12.5</v>
+      </c>
+      <c r="AW8">
+        <v>5.7</v>
+      </c>
+      <c r="AX8">
+        <v>12</v>
+      </c>
+      <c r="AY8">
         <v>9.6</v>
       </c>
-      <c r="AQ8">
-        <v>9</v>
-      </c>
-      <c r="AR8">
-        <v>15.5</v>
-      </c>
-      <c r="AS8">
-        <v>34</v>
-      </c>
-      <c r="AT8">
-        <v>9</v>
-      </c>
-      <c r="AU8">
-        <v>6.6</v>
-      </c>
-      <c r="AV8">
-        <v>11.5</v>
-      </c>
-      <c r="AW8">
-        <v>30</v>
-      </c>
-      <c r="AX8">
-        <v>16.5</v>
-      </c>
-      <c r="AY8">
-        <v>12</v>
-      </c>
       <c r="AZ8">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="BA8">
-        <v>46</v>
+        <v>5.9</v>
       </c>
       <c r="BB8">
-        <v>44</v>
+        <v>5.5</v>
       </c>
       <c r="BC8">
-        <v>32</v>
+        <v>5.2</v>
       </c>
       <c r="BD8">
-        <v>48</v>
+        <v>5.6</v>
       </c>
       <c r="BE8">
-        <v>100</v>
+        <v>6</v>
       </c>
       <c r="BF8">
-        <v>36</v>
+        <v>17.5</v>
       </c>
       <c r="BG8">
-        <v>32</v>
+        <v>5.7</v>
       </c>
       <c r="BH8">
-        <v>3</v>
+        <v>3.25</v>
       </c>
       <c r="BI8">
-        <v>2.76</v>
+        <v>2.64</v>
       </c>
       <c r="BJ8">
         <v>10.5</v>
       </c>
       <c r="BK8">
-        <v>6.4</v>
+        <v>5.3</v>
       </c>
       <c r="BL8">
         <v>1000</v>
       </c>
       <c r="BM8">
-        <v>130</v>
+        <v>10</v>
       </c>
       <c r="BN8">
-        <v>5.9</v>
+        <v>5.3</v>
       </c>
       <c r="BO8">
+        <v>4.1</v>
+      </c>
+      <c r="BP8">
+        <v>18.5</v>
+      </c>
+      <c r="BQ8">
+        <v>6.8</v>
+      </c>
+      <c r="BR8">
+        <v>1000</v>
+      </c>
+      <c r="BS8">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BT8">
+        <v>7</v>
+      </c>
+      <c r="BU8">
         <v>5.2</v>
       </c>
-      <c r="BP8">
-        <v>25</v>
-      </c>
-      <c r="BQ8">
-        <v>10</v>
-      </c>
-      <c r="BR8">
-        <v>42</v>
-      </c>
-      <c r="BS8">
-        <v>12</v>
-      </c>
-      <c r="BT8">
-        <v>5.6</v>
-      </c>
-      <c r="BU8">
-        <v>5</v>
-      </c>
       <c r="BV8">
-        <v>23</v>
+        <v>32</v>
       </c>
       <c r="BW8">
-        <v>9.800000000000001</v>
+        <v>8</v>
       </c>
       <c r="BX8">
-        <v>40</v>
+        <v>1000</v>
       </c>
       <c r="BY8">
-        <v>12</v>
+        <v>8.6</v>
       </c>
       <c r="BZ8">
-        <v>38</v>
+        <v>1000</v>
       </c>
       <c r="CA8">
-        <v>11.5</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="CB8" t="s">
-        <v>107</v>
-      </c>
-    </row>
-    <row r="9" spans="1:80">
-      <c r="A9" t="s">
-        <v>84</v>
-      </c>
-      <c r="B9" t="s">
-        <v>85</v>
-      </c>
-      <c r="C9" t="s">
-        <v>90</v>
-      </c>
-      <c r="D9" t="s">
-        <v>98</v>
-      </c>
-      <c r="E9" t="s">
-        <v>106</v>
-      </c>
-      <c r="F9">
-        <v>2.24</v>
-      </c>
-      <c r="G9">
-        <v>2.36</v>
-      </c>
-      <c r="H9">
-        <v>3.45</v>
-      </c>
-      <c r="I9">
-        <v>3.75</v>
-      </c>
-      <c r="J9">
-        <v>3.35</v>
-      </c>
-      <c r="K9">
-        <v>3.55</v>
-      </c>
-      <c r="L9">
-        <v>1.46</v>
-      </c>
-      <c r="M9">
-        <v>1.08</v>
-      </c>
-      <c r="N9">
-        <v>3.4</v>
-      </c>
-      <c r="O9">
-        <v>1.37</v>
-      </c>
-      <c r="P9">
-        <v>1.79</v>
-      </c>
-      <c r="Q9">
-        <v>2.16</v>
-      </c>
-      <c r="R9">
-        <v>1.3</v>
-      </c>
-      <c r="S9">
-        <v>4</v>
-      </c>
-      <c r="T9">
-        <v>1.84</v>
-      </c>
-      <c r="U9">
-        <v>2.02</v>
-      </c>
-      <c r="V9">
-        <v>1.36</v>
-      </c>
-      <c r="W9">
-        <v>1.73</v>
-      </c>
-      <c r="X9">
-        <v>14</v>
-      </c>
-      <c r="Y9">
-        <v>14.5</v>
-      </c>
-      <c r="Z9">
-        <v>26</v>
-      </c>
-      <c r="AA9">
-        <v>80</v>
-      </c>
-      <c r="AB9">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AC9">
-        <v>8</v>
-      </c>
-      <c r="AD9">
-        <v>17</v>
-      </c>
-      <c r="AE9">
-        <v>55</v>
-      </c>
-      <c r="AF9">
-        <v>16.5</v>
-      </c>
-      <c r="AG9">
-        <v>13</v>
-      </c>
-      <c r="AH9">
-        <v>22</v>
-      </c>
-      <c r="AI9">
-        <v>70</v>
-      </c>
-      <c r="AJ9">
-        <v>38</v>
-      </c>
-      <c r="AK9">
-        <v>32</v>
-      </c>
-      <c r="AL9">
-        <v>48</v>
-      </c>
-      <c r="AM9">
-        <v>130</v>
-      </c>
-      <c r="AN9">
-        <v>25</v>
-      </c>
-      <c r="AO9">
-        <v>55</v>
-      </c>
-      <c r="AP9">
-        <v>10</v>
-      </c>
-      <c r="AQ9">
-        <v>10.5</v>
-      </c>
-      <c r="AR9">
-        <v>20</v>
-      </c>
-      <c r="AS9">
-        <v>5.6</v>
-      </c>
-      <c r="AT9">
-        <v>7.8</v>
-      </c>
-      <c r="AU9">
-        <v>6.4</v>
-      </c>
-      <c r="AV9">
-        <v>12.5</v>
-      </c>
-      <c r="AW9">
-        <v>5.5</v>
-      </c>
-      <c r="AX9">
-        <v>12</v>
-      </c>
-      <c r="AY9">
-        <v>9.6</v>
-      </c>
-      <c r="AZ9">
-        <v>16</v>
-      </c>
-      <c r="BA9">
-        <v>5.6</v>
-      </c>
-      <c r="BB9">
-        <v>5.2</v>
-      </c>
-      <c r="BC9">
-        <v>5.1</v>
-      </c>
-      <c r="BD9">
-        <v>5.4</v>
-      </c>
-      <c r="BE9">
-        <v>5.8</v>
-      </c>
-      <c r="BF9">
-        <v>17.5</v>
-      </c>
-      <c r="BG9">
-        <v>5.5</v>
-      </c>
-      <c r="BH9">
-        <v>3.25</v>
-      </c>
-      <c r="BI9">
-        <v>2.64</v>
-      </c>
-      <c r="BJ9">
-        <v>10.5</v>
-      </c>
-      <c r="BK9">
-        <v>5.3</v>
-      </c>
-      <c r="BL9">
-        <v>1000</v>
-      </c>
-      <c r="BM9">
-        <v>10</v>
-      </c>
-      <c r="BN9">
-        <v>5.3</v>
-      </c>
-      <c r="BO9">
-        <v>4.1</v>
-      </c>
-      <c r="BP9">
-        <v>18.5</v>
-      </c>
-      <c r="BQ9">
-        <v>6.8</v>
-      </c>
-      <c r="BR9">
-        <v>1000</v>
-      </c>
-      <c r="BS9">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="BT9">
-        <v>7</v>
-      </c>
-      <c r="BU9">
-        <v>5.2</v>
-      </c>
-      <c r="BV9">
-        <v>32</v>
-      </c>
-      <c r="BW9">
-        <v>8</v>
-      </c>
-      <c r="BX9">
-        <v>1000</v>
-      </c>
-      <c r="BY9">
-        <v>8.6</v>
-      </c>
-      <c r="BZ9">
-        <v>1000</v>
-      </c>
-      <c r="CA9">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="CB9" t="s">
-        <v>107</v>
+        <v>103</v>
       </c>
     </row>
   </sheetData>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-08-11.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-08-11.xlsx
@@ -295,7 +295,7 @@
     <t>Union Espanola</t>
   </si>
   <si>
-    <t>2026-08-11 18:20:18</t>
+    <t>2026-08-11 20:28:29</t>
   </si>
 </sst>
 </file>
@@ -889,226 +889,226 @@
         <v>90</v>
       </c>
       <c r="F2">
+        <v>3.2</v>
+      </c>
+      <c r="G2">
+        <v>3.25</v>
+      </c>
+      <c r="H2">
+        <v>8.4</v>
+      </c>
+      <c r="I2">
+        <v>8.6</v>
+      </c>
+      <c r="J2">
         <v>1.73</v>
       </c>
-      <c r="G2">
+      <c r="K2">
         <v>1.74</v>
       </c>
-      <c r="H2">
-        <v>6.6</v>
-      </c>
-      <c r="I2">
-        <v>7</v>
-      </c>
-      <c r="J2">
-        <v>3.6</v>
-      </c>
-      <c r="K2">
-        <v>3.65</v>
-      </c>
       <c r="L2">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="M2">
+        <v>2.02</v>
+      </c>
+      <c r="N2">
+        <v>1.14</v>
+      </c>
+      <c r="O2">
+        <v>7.8</v>
+      </c>
+      <c r="P2">
+        <v>1.02</v>
+      </c>
+      <c r="Q2">
+        <v>28</v>
+      </c>
+      <c r="R2">
+        <v>1.01</v>
+      </c>
+      <c r="S2">
+        <v>180</v>
+      </c>
+      <c r="T2">
+        <v>13.5</v>
+      </c>
+      <c r="U2">
+        <v>1.07</v>
+      </c>
+      <c r="V2">
         <v>1.13</v>
       </c>
-      <c r="N2">
-        <v>2.66</v>
-      </c>
-      <c r="O2">
-        <v>1.59</v>
-      </c>
-      <c r="P2">
-        <v>1.55</v>
-      </c>
-      <c r="Q2">
-        <v>2.7</v>
-      </c>
-      <c r="R2">
-        <v>1.18</v>
-      </c>
-      <c r="S2">
-        <v>6</v>
-      </c>
-      <c r="T2">
-        <v>2.48</v>
-      </c>
-      <c r="U2">
-        <v>1.62</v>
-      </c>
-      <c r="V2">
-        <v>1.16</v>
-      </c>
       <c r="W2">
-        <v>2.34</v>
+        <v>1.44</v>
       </c>
       <c r="X2">
-        <v>8.800000000000001</v>
+        <v>1.91</v>
       </c>
       <c r="Y2">
-        <v>15.5</v>
+        <v>10</v>
       </c>
       <c r="Z2">
+        <v>1000</v>
+      </c>
+      <c r="AA2">
+        <v>1000</v>
+      </c>
+      <c r="AB2">
+        <v>4.2</v>
+      </c>
+      <c r="AC2">
+        <v>24</v>
+      </c>
+      <c r="AD2">
+        <v>1000</v>
+      </c>
+      <c r="AE2">
+        <v>1000</v>
+      </c>
+      <c r="AF2">
+        <v>26</v>
+      </c>
+      <c r="AG2">
+        <v>990</v>
+      </c>
+      <c r="AH2">
+        <v>1000</v>
+      </c>
+      <c r="AI2">
+        <v>1000</v>
+      </c>
+      <c r="AJ2">
+        <v>1000</v>
+      </c>
+      <c r="AK2">
+        <v>1000</v>
+      </c>
+      <c r="AL2">
+        <v>1000</v>
+      </c>
+      <c r="AM2">
+        <v>1000</v>
+      </c>
+      <c r="AN2">
+        <v>1000</v>
+      </c>
+      <c r="AO2">
+        <v>1000</v>
+      </c>
+      <c r="AP2">
+        <v>1.88</v>
+      </c>
+      <c r="AQ2">
+        <v>9</v>
+      </c>
+      <c r="AR2">
         <v>55</v>
       </c>
-      <c r="AA2">
-        <v>280</v>
-      </c>
-      <c r="AB2">
-        <v>5.5</v>
-      </c>
-      <c r="AC2">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AD2">
-        <v>26</v>
-      </c>
-      <c r="AE2">
-        <v>150</v>
-      </c>
-      <c r="AF2">
-        <v>7.8</v>
-      </c>
-      <c r="AG2">
-        <v>10.5</v>
-      </c>
-      <c r="AH2">
-        <v>30</v>
-      </c>
-      <c r="AI2">
-        <v>180</v>
-      </c>
-      <c r="AJ2">
-        <v>18</v>
-      </c>
-      <c r="AK2">
-        <v>24</v>
-      </c>
-      <c r="AL2">
-        <v>75</v>
-      </c>
-      <c r="AM2">
+      <c r="AS2">
+        <v>380</v>
+      </c>
+      <c r="AT2">
+        <v>4</v>
+      </c>
+      <c r="AU2">
+        <v>19</v>
+      </c>
+      <c r="AV2">
+        <v>140</v>
+      </c>
+      <c r="AW2">
         <v>500</v>
       </c>
-      <c r="AN2">
-        <v>21</v>
-      </c>
-      <c r="AO2">
+      <c r="AX2">
+        <v>19</v>
+      </c>
+      <c r="AY2">
+        <v>60</v>
+      </c>
+      <c r="AZ2">
+        <v>310</v>
+      </c>
+      <c r="BA2">
+        <v>500</v>
+      </c>
+      <c r="BB2">
+        <v>100</v>
+      </c>
+      <c r="BC2">
         <v>320</v>
       </c>
-      <c r="AP2">
-        <v>8.6</v>
-      </c>
-      <c r="AQ2">
-        <v>14.5</v>
-      </c>
-      <c r="AR2">
-        <v>50</v>
-      </c>
-      <c r="AS2">
-        <v>40</v>
-      </c>
-      <c r="AT2">
-        <v>5.4</v>
-      </c>
-      <c r="AU2">
-        <v>8</v>
-      </c>
-      <c r="AV2">
-        <v>25</v>
-      </c>
-      <c r="AW2">
-        <v>110</v>
-      </c>
-      <c r="AX2">
-        <v>7.4</v>
-      </c>
-      <c r="AY2">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AZ2">
-        <v>29</v>
-      </c>
-      <c r="BA2">
-        <v>120</v>
-      </c>
-      <c r="BB2">
-        <v>17</v>
-      </c>
-      <c r="BC2">
-        <v>23</v>
-      </c>
       <c r="BD2">
-        <v>65</v>
+        <v>430</v>
       </c>
       <c r="BE2">
-        <v>150</v>
+        <v>350</v>
       </c>
       <c r="BF2">
-        <v>20</v>
+        <v>330</v>
       </c>
       <c r="BG2">
-        <v>160</v>
+        <v>490</v>
       </c>
       <c r="BH2">
-        <v>2.68</v>
+        <v>0</v>
       </c>
       <c r="BI2">
-        <v>2.54</v>
+        <v>0</v>
       </c>
       <c r="BJ2">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="BK2">
-        <v>11.5</v>
+        <v>0</v>
       </c>
       <c r="BL2">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BM2">
-        <v>17.5</v>
+        <v>0</v>
       </c>
       <c r="BN2">
-        <v>3.85</v>
+        <v>0</v>
       </c>
       <c r="BO2">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="BP2">
-        <v>13.5</v>
+        <v>0</v>
       </c>
       <c r="BQ2">
-        <v>11.5</v>
+        <v>0</v>
       </c>
       <c r="BR2">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="BS2">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="BT2">
-        <v>9.800000000000001</v>
+        <v>0</v>
       </c>
       <c r="BU2">
-        <v>7.8</v>
+        <v>0</v>
       </c>
       <c r="BV2">
-        <v>95</v>
+        <v>0</v>
       </c>
       <c r="BW2">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="BX2">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BY2">
-        <v>19.5</v>
+        <v>0</v>
       </c>
       <c r="BZ2">
-        <v>38</v>
+        <v>0</v>
       </c>
       <c r="CA2">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="CB2" t="s">
         <v>93</v>
@@ -1131,226 +1131,226 @@
         <v>91</v>
       </c>
       <c r="F3">
-        <v>2.96</v>
+        <v>6.8</v>
       </c>
       <c r="G3">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="H3">
-        <v>2.82</v>
+        <v>1.72</v>
       </c>
       <c r="I3">
-        <v>2.88</v>
+        <v>1.73</v>
       </c>
       <c r="J3">
-        <v>3.15</v>
+        <v>3.6</v>
       </c>
       <c r="K3">
-        <v>3.2</v>
+        <v>3.65</v>
       </c>
       <c r="L3">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="M3">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="N3">
-        <v>3.1</v>
+        <v>4.7</v>
       </c>
       <c r="O3">
-        <v>1.46</v>
+        <v>1.26</v>
       </c>
       <c r="P3">
-        <v>1.69</v>
+        <v>1.85</v>
       </c>
       <c r="Q3">
-        <v>2.38</v>
+        <v>2.16</v>
       </c>
       <c r="R3">
-        <v>1.27</v>
+        <v>1.23</v>
       </c>
       <c r="S3">
-        <v>4.6</v>
+        <v>5</v>
       </c>
       <c r="T3">
-        <v>1.95</v>
+        <v>1.61</v>
       </c>
       <c r="U3">
-        <v>2</v>
+        <v>2.48</v>
       </c>
       <c r="V3">
-        <v>1.53</v>
+        <v>2.36</v>
       </c>
       <c r="W3">
-        <v>1.5</v>
+        <v>1.16</v>
       </c>
       <c r="X3">
+        <v>1000</v>
+      </c>
+      <c r="Y3">
+        <v>4.9</v>
+      </c>
+      <c r="Z3">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AA3">
+        <v>26</v>
+      </c>
+      <c r="AB3">
+        <v>1000</v>
+      </c>
+      <c r="AC3">
+        <v>5</v>
+      </c>
+      <c r="AD3">
+        <v>8.4</v>
+      </c>
+      <c r="AE3">
+        <v>29</v>
+      </c>
+      <c r="AF3">
+        <v>1000</v>
+      </c>
+      <c r="AG3">
+        <v>11.5</v>
+      </c>
+      <c r="AH3">
+        <v>17.5</v>
+      </c>
+      <c r="AI3">
+        <v>70</v>
+      </c>
+      <c r="AJ3">
+        <v>1000</v>
+      </c>
+      <c r="AK3">
+        <v>44</v>
+      </c>
+      <c r="AL3">
+        <v>70</v>
+      </c>
+      <c r="AM3">
+        <v>300</v>
+      </c>
+      <c r="AN3">
+        <v>140</v>
+      </c>
+      <c r="AO3">
+        <v>50</v>
+      </c>
+      <c r="AP3">
+        <v>17.5</v>
+      </c>
+      <c r="AQ3">
+        <v>4.5</v>
+      </c>
+      <c r="AR3">
+        <v>7.2</v>
+      </c>
+      <c r="AS3">
+        <v>23</v>
+      </c>
+      <c r="AT3">
+        <v>17.5</v>
+      </c>
+      <c r="AU3">
+        <v>4.7</v>
+      </c>
+      <c r="AV3">
+        <v>7.6</v>
+      </c>
+      <c r="AW3">
+        <v>25</v>
+      </c>
+      <c r="AX3">
+        <v>17.5</v>
+      </c>
+      <c r="AY3">
         <v>10</v>
       </c>
-      <c r="Y3">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="Z3">
-        <v>18</v>
-      </c>
-      <c r="AA3">
-        <v>50</v>
-      </c>
-      <c r="AB3">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AC3">
-        <v>6.8</v>
-      </c>
-      <c r="AD3">
-        <v>12.5</v>
-      </c>
-      <c r="AE3">
-        <v>36</v>
-      </c>
-      <c r="AF3">
-        <v>19</v>
-      </c>
-      <c r="AG3">
-        <v>13</v>
-      </c>
-      <c r="AH3">
-        <v>20</v>
-      </c>
-      <c r="AI3">
+      <c r="AZ3">
+        <v>15</v>
+      </c>
+      <c r="BA3">
         <v>55</v>
       </c>
-      <c r="AJ3">
+      <c r="BB3">
+        <v>17.5</v>
+      </c>
+      <c r="BC3">
+        <v>38</v>
+      </c>
+      <c r="BD3">
         <v>60</v>
       </c>
-      <c r="AK3">
+      <c r="BE3">
+        <v>200</v>
+      </c>
+      <c r="BF3">
+        <v>100</v>
+      </c>
+      <c r="BG3">
         <v>40</v>
       </c>
-      <c r="AL3">
-        <v>60</v>
-      </c>
-      <c r="AM3">
-        <v>130</v>
-      </c>
-      <c r="AN3">
-        <v>44</v>
-      </c>
-      <c r="AO3">
-        <v>40</v>
-      </c>
-      <c r="AP3">
-        <v>9.4</v>
-      </c>
-      <c r="AQ3">
-        <v>8.4</v>
-      </c>
-      <c r="AR3">
-        <v>15.5</v>
-      </c>
-      <c r="AS3">
-        <v>42</v>
-      </c>
-      <c r="AT3">
-        <v>9</v>
-      </c>
-      <c r="AU3">
-        <v>6.2</v>
-      </c>
-      <c r="AV3">
-        <v>11.5</v>
-      </c>
-      <c r="AW3">
-        <v>30</v>
-      </c>
-      <c r="AX3">
-        <v>16.5</v>
-      </c>
-      <c r="AY3">
-        <v>12</v>
-      </c>
-      <c r="AZ3">
-        <v>18</v>
-      </c>
-      <c r="BA3">
-        <v>48</v>
-      </c>
-      <c r="BB3">
-        <v>46</v>
-      </c>
-      <c r="BC3">
-        <v>34</v>
-      </c>
-      <c r="BD3">
-        <v>50</v>
-      </c>
-      <c r="BE3">
-        <v>100</v>
-      </c>
-      <c r="BF3">
-        <v>38</v>
-      </c>
-      <c r="BG3">
-        <v>34</v>
-      </c>
       <c r="BH3">
-        <v>2.94</v>
+        <v>0</v>
       </c>
       <c r="BI3">
-        <v>2.78</v>
+        <v>0</v>
       </c>
       <c r="BJ3">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="BK3">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="BL3">
-        <v>160</v>
+        <v>0</v>
       </c>
       <c r="BM3">
-        <v>18.5</v>
+        <v>0</v>
       </c>
       <c r="BN3">
-        <v>5.7</v>
+        <v>0</v>
       </c>
       <c r="BO3">
-        <v>5.3</v>
+        <v>0</v>
       </c>
       <c r="BP3">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="BQ3">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="BR3">
-        <v>42</v>
+        <v>0</v>
       </c>
       <c r="BS3">
-        <v>23</v>
+        <v>0</v>
       </c>
       <c r="BT3">
-        <v>5.5</v>
+        <v>0</v>
       </c>
       <c r="BU3">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="BV3">
-        <v>23</v>
+        <v>0</v>
       </c>
       <c r="BW3">
-        <v>11.5</v>
+        <v>0</v>
       </c>
       <c r="BX3">
-        <v>42</v>
+        <v>0</v>
       </c>
       <c r="BY3">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="BZ3">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="CA3">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="CB3" t="s">
         <v>93</v>
@@ -1373,226 +1373,226 @@
         <v>92</v>
       </c>
       <c r="F4">
+        <v>2</v>
+      </c>
+      <c r="G4">
         <v>2.08</v>
       </c>
-      <c r="G4">
-        <v>2.14</v>
-      </c>
       <c r="H4">
-        <v>4.1</v>
+        <v>4.9</v>
       </c>
       <c r="I4">
-        <v>4.3</v>
+        <v>5.2</v>
       </c>
       <c r="J4">
-        <v>3.4</v>
+        <v>3.15</v>
       </c>
       <c r="K4">
-        <v>3.6</v>
+        <v>3.35</v>
       </c>
       <c r="L4">
+        <v>2.34</v>
+      </c>
+      <c r="M4">
+        <v>1.15</v>
+      </c>
+      <c r="N4">
+        <v>2.36</v>
+      </c>
+      <c r="O4">
+        <v>1.69</v>
+      </c>
+      <c r="P4">
         <v>1.44</v>
       </c>
-      <c r="M4">
-        <v>1.08</v>
-      </c>
-      <c r="N4">
-        <v>3.55</v>
-      </c>
-      <c r="O4">
-        <v>1.37</v>
-      </c>
-      <c r="P4">
-        <v>1.86</v>
-      </c>
       <c r="Q4">
-        <v>2.06</v>
+        <v>3.1</v>
       </c>
       <c r="R4">
-        <v>1.32</v>
+        <v>1.14</v>
       </c>
       <c r="S4">
-        <v>3.8</v>
+        <v>7</v>
       </c>
       <c r="T4">
-        <v>1.83</v>
+        <v>2.52</v>
       </c>
       <c r="U4">
-        <v>2.06</v>
+        <v>1.58</v>
       </c>
       <c r="V4">
-        <v>1.31</v>
+        <v>1.23</v>
       </c>
       <c r="W4">
-        <v>1.88</v>
+        <v>1.92</v>
       </c>
       <c r="X4">
-        <v>13.5</v>
+        <v>7.8</v>
       </c>
       <c r="Y4">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="Z4">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="AA4">
+        <v>160</v>
+      </c>
+      <c r="AB4">
+        <v>5.9</v>
+      </c>
+      <c r="AC4">
+        <v>7.8</v>
+      </c>
+      <c r="AD4">
+        <v>24</v>
+      </c>
+      <c r="AE4">
+        <v>120</v>
+      </c>
+      <c r="AF4">
+        <v>10.5</v>
+      </c>
+      <c r="AG4">
+        <v>12.5</v>
+      </c>
+      <c r="AH4">
+        <v>34</v>
+      </c>
+      <c r="AI4">
+        <v>170</v>
+      </c>
+      <c r="AJ4">
+        <v>26</v>
+      </c>
+      <c r="AK4">
+        <v>36</v>
+      </c>
+      <c r="AL4">
+        <v>90</v>
+      </c>
+      <c r="AM4">
+        <v>370</v>
+      </c>
+      <c r="AN4">
+        <v>34</v>
+      </c>
+      <c r="AO4">
+        <v>210</v>
+      </c>
+      <c r="AP4">
+        <v>7.2</v>
+      </c>
+      <c r="AQ4">
+        <v>10.5</v>
+      </c>
+      <c r="AR4">
+        <v>29</v>
+      </c>
+      <c r="AS4">
+        <v>110</v>
+      </c>
+      <c r="AT4">
+        <v>5.4</v>
+      </c>
+      <c r="AU4">
+        <v>7</v>
+      </c>
+      <c r="AV4">
+        <v>20</v>
+      </c>
+      <c r="AW4">
+        <v>80</v>
+      </c>
+      <c r="AX4">
+        <v>9</v>
+      </c>
+      <c r="AY4">
+        <v>11</v>
+      </c>
+      <c r="AZ4">
+        <v>28</v>
+      </c>
+      <c r="BA4">
         <v>130</v>
       </c>
-      <c r="AB4">
-        <v>9.4</v>
-      </c>
-      <c r="AC4">
-        <v>8</v>
-      </c>
-      <c r="AD4">
-        <v>17</v>
-      </c>
-      <c r="AE4">
-        <v>55</v>
-      </c>
-      <c r="AF4">
-        <v>13.5</v>
-      </c>
-      <c r="AG4">
-        <v>11</v>
-      </c>
-      <c r="AH4">
-        <v>19.5</v>
-      </c>
-      <c r="AI4">
-        <v>65</v>
-      </c>
-      <c r="AJ4">
-        <v>42</v>
-      </c>
-      <c r="AK4">
-        <v>24</v>
-      </c>
-      <c r="AL4">
-        <v>65</v>
-      </c>
-      <c r="AM4">
-        <v>180</v>
-      </c>
-      <c r="AN4">
-        <v>18.5</v>
-      </c>
-      <c r="AO4">
-        <v>75</v>
-      </c>
-      <c r="AP4">
-        <v>11.5</v>
-      </c>
-      <c r="AQ4">
-        <v>12.5</v>
-      </c>
-      <c r="AR4">
-        <v>8</v>
-      </c>
-      <c r="AS4">
-        <v>40</v>
-      </c>
-      <c r="AT4">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AU4">
-        <v>6.8</v>
-      </c>
-      <c r="AV4">
-        <v>14</v>
-      </c>
-      <c r="AW4">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AX4">
-        <v>10.5</v>
-      </c>
-      <c r="AY4">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AZ4">
-        <v>16</v>
-      </c>
-      <c r="BA4">
-        <v>9.6</v>
-      </c>
       <c r="BB4">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="BC4">
-        <v>19</v>
+        <v>28</v>
       </c>
       <c r="BD4">
-        <v>14.5</v>
+        <v>70</v>
       </c>
       <c r="BE4">
-        <v>10</v>
+        <v>200</v>
       </c>
       <c r="BF4">
-        <v>12.5</v>
+        <v>26</v>
       </c>
       <c r="BG4">
-        <v>9.4</v>
+        <v>150</v>
       </c>
       <c r="BH4">
-        <v>3.4</v>
+        <v>1.81</v>
       </c>
       <c r="BI4">
-        <v>2.74</v>
+        <v>1.72</v>
       </c>
       <c r="BJ4">
-        <v>10.5</v>
+        <v>27</v>
       </c>
       <c r="BK4">
-        <v>5.2</v>
+        <v>23</v>
       </c>
       <c r="BL4">
         <v>1000</v>
       </c>
       <c r="BM4">
-        <v>9.800000000000001</v>
+        <v>15.5</v>
       </c>
       <c r="BN4">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="BO4">
-        <v>3.95</v>
+        <v>4.5</v>
       </c>
       <c r="BP4">
-        <v>16.5</v>
+        <v>34</v>
       </c>
       <c r="BQ4">
-        <v>6.4</v>
+        <v>29</v>
       </c>
       <c r="BR4">
-        <v>32</v>
+        <v>150</v>
       </c>
       <c r="BS4">
-        <v>7.8</v>
+        <v>130</v>
       </c>
       <c r="BT4">
-        <v>7.4</v>
+        <v>9</v>
       </c>
       <c r="BU4">
-        <v>5.5</v>
+        <v>7.6</v>
       </c>
       <c r="BV4">
-        <v>34</v>
+        <v>110</v>
       </c>
       <c r="BW4">
-        <v>8</v>
+        <v>85</v>
       </c>
       <c r="BX4">
-        <v>46</v>
+        <v>950</v>
       </c>
       <c r="BY4">
-        <v>8.4</v>
+        <v>14.5</v>
       </c>
       <c r="BZ4">
-        <v>29</v>
+        <v>960</v>
       </c>
       <c r="CA4">
-        <v>7.6</v>
+        <v>14.5</v>
       </c>
       <c r="CB4" t="s">
         <v>93</v>
